--- a/app/convert/forest_sample_template.xlsx
+++ b/app/convert/forest_sample_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TAX-JUNGYOON\forest-app\app\convert\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{055C6830-B5A1-485D-9D52-1E626ED40DBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDB5AA08-10BB-4605-A9D8-C198BFA6BA38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="658" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3362" uniqueCount="607">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1681" uniqueCount="608">
   <si>
     <t>시설명</t>
   </si>
@@ -2137,6 +2137,10 @@
 - 21호 (장애인실)
 비추천
 - 15호 (트리하우스)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>매주 수요일 09시 · 평일 오픈</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2673,7 +2677,7 @@
         <v>113</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>6</v>
+        <v>607</v>
       </c>
       <c r="G2" s="5" t="s">
         <v>352</v>
@@ -2713,7 +2717,7 @@
         <v>113</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>6</v>
+        <v>607</v>
       </c>
       <c r="G3" s="5" t="s">
         <v>352</v>
@@ -2753,7 +2757,7 @@
         <v>113</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>6</v>
+        <v>607</v>
       </c>
       <c r="G4" s="5" t="s">
         <v>352</v>
@@ -2793,7 +2797,7 @@
         <v>113</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>6</v>
+        <v>607</v>
       </c>
       <c r="G5" s="5" t="s">
         <v>352</v>
@@ -2833,7 +2837,7 @@
         <v>113</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>6</v>
+        <v>607</v>
       </c>
       <c r="G6" s="5" t="s">
         <v>352</v>
@@ -2875,7 +2879,7 @@
         <v>113</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>6</v>
+        <v>607</v>
       </c>
       <c r="G7" s="5" t="s">
         <v>352</v>
@@ -2915,7 +2919,7 @@
         <v>113</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>6</v>
+        <v>607</v>
       </c>
       <c r="G8" s="5" t="s">
         <v>352</v>
@@ -2955,7 +2959,7 @@
         <v>113</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>6</v>
+        <v>607</v>
       </c>
       <c r="G9" s="5" t="s">
         <v>352</v>
@@ -2995,7 +2999,7 @@
         <v>113</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>6</v>
+        <v>607</v>
       </c>
       <c r="G10" s="5" t="s">
         <v>352</v>
@@ -3035,7 +3039,7 @@
         <v>113</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>6</v>
+        <v>607</v>
       </c>
       <c r="G11" s="5" t="s">
         <v>352</v>
@@ -3075,7 +3079,7 @@
         <v>113</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>6</v>
+        <v>607</v>
       </c>
       <c r="G12" s="5" t="s">
         <v>352</v>
@@ -3117,7 +3121,7 @@
         <v>113</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>6</v>
+        <v>607</v>
       </c>
       <c r="G13" s="5" t="s">
         <v>352</v>
@@ -3157,7 +3161,7 @@
         <v>113</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>6</v>
+        <v>607</v>
       </c>
       <c r="G14" s="5" t="s">
         <v>352</v>
@@ -3197,7 +3201,7 @@
         <v>113</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>6</v>
+        <v>607</v>
       </c>
       <c r="G15" s="5" t="s">
         <v>352</v>
@@ -3237,7 +3241,7 @@
         <v>113</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>6</v>
+        <v>607</v>
       </c>
       <c r="G16" s="5" t="s">
         <v>352</v>
@@ -3277,7 +3281,7 @@
         <v>113</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>6</v>
+        <v>607</v>
       </c>
       <c r="G17" s="5" t="s">
         <v>352</v>
@@ -3317,7 +3321,7 @@
         <v>113</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>6</v>
+        <v>607</v>
       </c>
       <c r="G18" s="5" t="s">
         <v>352</v>
@@ -3357,7 +3361,7 @@
         <v>113</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>6</v>
+        <v>607</v>
       </c>
       <c r="G19" s="5" t="s">
         <v>352</v>
@@ -3397,7 +3401,7 @@
         <v>113</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>6</v>
+        <v>607</v>
       </c>
       <c r="G20" s="5" t="s">
         <v>352</v>
@@ -3439,7 +3443,7 @@
         <v>113</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>6</v>
+        <v>607</v>
       </c>
       <c r="G21" s="5" t="s">
         <v>352</v>
@@ -3479,7 +3483,7 @@
         <v>113</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>6</v>
+        <v>607</v>
       </c>
       <c r="G22" s="5" t="s">
         <v>352</v>
@@ -3519,7 +3523,7 @@
         <v>113</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>6</v>
+        <v>607</v>
       </c>
       <c r="G23" s="5" t="s">
         <v>352</v>
@@ -3559,7 +3563,7 @@
         <v>113</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>6</v>
+        <v>607</v>
       </c>
       <c r="G24" s="5" t="s">
         <v>352</v>
@@ -3599,7 +3603,7 @@
         <v>113</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>6</v>
+        <v>607</v>
       </c>
       <c r="G25" s="5" t="s">
         <v>352</v>
@@ -3639,7 +3643,7 @@
         <v>113</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>6</v>
+        <v>607</v>
       </c>
       <c r="G26" s="5" t="s">
         <v>352</v>
@@ -3679,7 +3683,7 @@
         <v>113</v>
       </c>
       <c r="F27" s="5" t="s">
-        <v>6</v>
+        <v>607</v>
       </c>
       <c r="G27" s="5" t="s">
         <v>352</v>
@@ -3719,7 +3723,7 @@
         <v>113</v>
       </c>
       <c r="F28" s="5" t="s">
-        <v>6</v>
+        <v>607</v>
       </c>
       <c r="G28" s="5" t="s">
         <v>352</v>
@@ -3761,7 +3765,7 @@
         <v>113</v>
       </c>
       <c r="F29" s="5" t="s">
-        <v>6</v>
+        <v>607</v>
       </c>
       <c r="G29" s="5" t="s">
         <v>352</v>
@@ -3801,7 +3805,7 @@
         <v>113</v>
       </c>
       <c r="F30" s="5" t="s">
-        <v>6</v>
+        <v>607</v>
       </c>
       <c r="G30" s="5" t="s">
         <v>352</v>
@@ -3841,7 +3845,7 @@
         <v>113</v>
       </c>
       <c r="F31" s="5" t="s">
-        <v>6</v>
+        <v>607</v>
       </c>
       <c r="G31" s="5" t="s">
         <v>352</v>
@@ -3881,7 +3885,7 @@
         <v>113</v>
       </c>
       <c r="F32" s="5" t="s">
-        <v>6</v>
+        <v>607</v>
       </c>
       <c r="G32" s="5" t="s">
         <v>352</v>
@@ -3923,7 +3927,7 @@
         <v>113</v>
       </c>
       <c r="F33" s="5" t="s">
-        <v>6</v>
+        <v>607</v>
       </c>
       <c r="G33" s="5" t="s">
         <v>352</v>
@@ -3963,7 +3967,7 @@
         <v>113</v>
       </c>
       <c r="F34" s="5" t="s">
-        <v>6</v>
+        <v>607</v>
       </c>
       <c r="G34" s="5" t="s">
         <v>352</v>
@@ -4003,7 +4007,7 @@
         <v>113</v>
       </c>
       <c r="F35" s="5" t="s">
-        <v>6</v>
+        <v>607</v>
       </c>
       <c r="G35" s="5" t="s">
         <v>352</v>
@@ -4043,7 +4047,7 @@
         <v>113</v>
       </c>
       <c r="F36" s="5" t="s">
-        <v>6</v>
+        <v>607</v>
       </c>
       <c r="G36" s="5" t="s">
         <v>352</v>
@@ -4083,7 +4087,7 @@
         <v>113</v>
       </c>
       <c r="F37" s="5" t="s">
-        <v>6</v>
+        <v>607</v>
       </c>
       <c r="G37" s="5" t="s">
         <v>352</v>
@@ -4123,7 +4127,7 @@
         <v>113</v>
       </c>
       <c r="F38" s="5" t="s">
-        <v>6</v>
+        <v>607</v>
       </c>
       <c r="G38" s="5" t="s">
         <v>352</v>
@@ -4163,7 +4167,7 @@
         <v>113</v>
       </c>
       <c r="F39" s="5" t="s">
-        <v>6</v>
+        <v>607</v>
       </c>
       <c r="G39" s="5" t="s">
         <v>352</v>
@@ -4203,7 +4207,7 @@
         <v>113</v>
       </c>
       <c r="F40" s="5" t="s">
-        <v>6</v>
+        <v>607</v>
       </c>
       <c r="G40" s="5" t="s">
         <v>352</v>
@@ -4243,7 +4247,7 @@
         <v>113</v>
       </c>
       <c r="F41" s="5" t="s">
-        <v>6</v>
+        <v>607</v>
       </c>
       <c r="G41" s="5" t="s">
         <v>352</v>
@@ -4283,7 +4287,7 @@
         <v>113</v>
       </c>
       <c r="F42" s="5" t="s">
-        <v>6</v>
+        <v>607</v>
       </c>
       <c r="G42" s="5" t="s">
         <v>352</v>
@@ -4323,7 +4327,7 @@
         <v>113</v>
       </c>
       <c r="F43" s="5" t="s">
-        <v>6</v>
+        <v>607</v>
       </c>
       <c r="G43" s="5" t="s">
         <v>352</v>
@@ -4363,7 +4367,7 @@
         <v>113</v>
       </c>
       <c r="F44" s="5" t="s">
-        <v>6</v>
+        <v>607</v>
       </c>
       <c r="G44" s="5" t="s">
         <v>352</v>
@@ -4403,7 +4407,7 @@
         <v>113</v>
       </c>
       <c r="F45" s="5" t="s">
-        <v>6</v>
+        <v>607</v>
       </c>
       <c r="G45" s="5" t="s">
         <v>352</v>
@@ -4443,7 +4447,7 @@
         <v>113</v>
       </c>
       <c r="F46" s="5" t="s">
-        <v>6</v>
+        <v>607</v>
       </c>
       <c r="G46" s="5" t="s">
         <v>352</v>
@@ -4483,7 +4487,7 @@
         <v>113</v>
       </c>
       <c r="F47" s="5" t="s">
-        <v>6</v>
+        <v>607</v>
       </c>
       <c r="G47" s="5" t="s">
         <v>352</v>
@@ -4523,7 +4527,7 @@
         <v>113</v>
       </c>
       <c r="F48" s="5" t="s">
-        <v>6</v>
+        <v>607</v>
       </c>
       <c r="G48" s="5" t="s">
         <v>352</v>

--- a/app/convert/forest_sample_template.xlsx
+++ b/app/convert/forest_sample_template.xlsx
@@ -8,22 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TAX-JUNGYOON\forest-app\app\convert\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDB5AA08-10BB-4605-A9D8-C198BFA6BA38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{620D4363-2001-48AF-95C1-8B089E8504AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="658" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="658" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="샘플" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">샘플!$B$1:$N$180</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">샘플!$B$1:$Q$180</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1681" uniqueCount="608">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2313" uniqueCount="688">
   <si>
     <t>시설명</t>
   </si>
@@ -707,9 +707,6 @@
     <t>거창산림레포츠파크</t>
   </si>
   <si>
-    <t>거창항노화힐링랜드</t>
-  </si>
-  <si>
     <t>금원산자연휴양림</t>
   </si>
   <si>
@@ -1046,10 +1043,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>야영장</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>최대 3박4일</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1063,10 +1056,6 @@
   </si>
   <si>
     <t>양산시</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>캠핑장</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -2141,6 +2130,357 @@
   </si>
   <si>
     <t>매주 수요일 09시 · 평일 오픈</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>물놀이</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>바베큐</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>야영장</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>○</t>
+  </si>
+  <si>
+    <t>○</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>X</t>
+  </si>
+  <si>
+    <t>X</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>▲</t>
+  </si>
+  <si>
+    <t>▲</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>거창항노화힐링랜드</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.foresttrip.go.kr/indvz/main.do?hmpgId=ID02030022</t>
+  </si>
+  <si>
+    <t>황매산숲속야영장</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>합천군</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>숲애서</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>동해시</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>강원</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>최참판댁한옥호텔</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>하동군</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>정원워케이션</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>순천시</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>지리산생태체험단지</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>함양군</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>지리산정원</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>구례군</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>맹방비치캠핑장</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>연곡해변캠핑장</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>삼척시</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>강릉시</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>고래불국민야영장</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>영덕군</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>오류캠핑장</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>경주시</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>대왕암공원캠핑장</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>장호비치캠핑장</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>울산시</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>창바우마을</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>포항시 남구</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.xn--9g3b27q0ne.kr/front/site/main.php</t>
+  </si>
+  <si>
+    <t>국립공원야영장</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>매월 08일 09시 ~ 12일 24시</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>잔여자리 매월 15일 00시</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.yssisul.or.kr/forest/</t>
+  </si>
+  <si>
+    <t>https://www.hc.go.kr/09464/09467/09467.web</t>
+  </si>
+  <si>
+    <t>신청일 기준 10일후부터 2달까지</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.campingkorea.or.kr/index.do</t>
+  </si>
+  <si>
+    <t>신청일 기준 1일후부터 30일까지 11시 선착순</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>망상오토캠핑리조트</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.hadong.go.kr/hdhanok.web</t>
+  </si>
+  <si>
+    <t>매월 첫번째 수요일 09시</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.suncheon.go.kr/worcation/</t>
+  </si>
+  <si>
+    <t>https://sphjirisan.com/default/</t>
+  </si>
+  <si>
+    <t>신청일 기준 60일 이전</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>신청일 기준 약 60일 이전</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>매주 수요일 10시</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4주차 화요일까지</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://ecopark.gurye.go.kr/</t>
+  </si>
+  <si>
+    <t>http://www.samcheokcamp.com/contents/main.html</t>
+  </si>
+  <si>
+    <t>매월 01일 00시</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>다음월</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>캠핑하우스 C1 (2명/4명)
+캠핑하우스 C2 (2명/4명)
+캠핑하우스 C3 (2명/4명)
+비수기 평일 80,000원 / 주말 100,000원
+성수기 평일 120,000원 / 주말 120,000원
+동절기 평일 60,000원 / 주말 80,000원</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>신청일 기준 10시 한달후</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(예: 7월 3일 10시00분 -&gt; 8월 3일 예약가능)
+7월 4일 10시00분 -&gt; 8월 4일 예약가능)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://camping.gtdc.or.kr/</t>
+  </si>
+  <si>
+    <t>고급형 카라반 H존
+콘도형 (H-901) 4인 차량1대
+비수기 평일 120,000원 / 주말 180,000원
+준성수기 180,000원 / 성수기 220,000원
+콘도형 (H-902) 6인 차량1대
+비수기 평일 160,000원 / 주말 220,000원
+준성수기 220,000원 / 성수기 270,000원
+호텔형 (H-903) 6인 차량1대 (취사불가)
+비수기 평일 150,000원 / 주말 210,000원
+준성수기 210,000원 / 성수기 260,000원</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://stay.yd.go.kr/pages/index.htm</t>
+  </si>
+  <si>
+    <t>펜션형숙박시설
+10인용 
+성수기 200,000 / 200,000 
+비성수기 140,000 / 170,000
+8인용
+성수기 180,000 / 180,000 
+비성수기 120,000 / 150,000
+6인용
+성수기 150,000 / 150,000 
+비성수기 100,000 / 120,000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://orcp.or.kr/main/index.php</t>
+  </si>
+  <si>
+    <t>카라반
+일반형(1~18호)
+비수기 60,000 / 100,000
+준성수기 80,000 / 120,000
+성수기 150,000 / 150,000
+대형(19~28호)
+비수기 80,000 / 120,000
+준성수기 100,000 / 150,000
+성수기 180,000 / 180,000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>동구구민 매월 첫번째 월요일 10시 ~ 첫번째 화요일 23시
+일반인 매월 두번째 월요일 10시 ~ 두번째 화요일 23시</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>사전예약안내 공지사항 꼭 환인</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://daewangam.donggu.ulsan.kr/camping/main.do</t>
+  </si>
+  <si>
+    <t>http://www.janghocamping.kr/</t>
+  </si>
+  <si>
+    <t>매월 01일 09시</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>매월 01일 15시 30분</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>컨테이너하우스(A동)
+성수기(7~8월) 240,000 / 240,000
+비수기 200,000 / 220,000
+동절기(11~2월) 180,000 / 200,000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>신청일 기준 00시 90일후</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>오토캠핑장 (1~9번 1열)
+평일 50,000 / 60,000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>7일전취소 100% 환불</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>지자체</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>국립공원</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>국립야영장</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>기타숙소</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>캠핑장</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2259,7 +2599,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -2272,8 +2612,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -2293,8 +2631,32 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2599,68 +2961,79 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N182"/>
+  <dimension ref="A1:Q194"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="29" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="8.25" style="1" customWidth="1"/>
-    <col min="6" max="6" width="36.875" style="1" customWidth="1"/>
-    <col min="7" max="7" width="36.5" style="1" customWidth="1"/>
-    <col min="8" max="8" width="28.375" style="1" customWidth="1"/>
-    <col min="9" max="9" width="15.25" style="1" customWidth="1"/>
-    <col min="10" max="10" width="55.375" style="1" customWidth="1"/>
-    <col min="11" max="13" width="36.875" style="1" customWidth="1"/>
-    <col min="14" max="14" width="65.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13" style="18" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.125" style="18" customWidth="1"/>
+    <col min="3" max="3" width="29" style="18" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.875" style="18" customWidth="1"/>
+    <col min="5" max="5" width="8.25" style="18" customWidth="1"/>
+    <col min="6" max="6" width="36.875" style="18" customWidth="1"/>
+    <col min="7" max="7" width="47.25" style="18" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="28.375" style="18" customWidth="1"/>
+    <col min="9" max="9" width="15.25" style="18" customWidth="1"/>
+    <col min="10" max="10" width="55.375" style="18" customWidth="1"/>
+    <col min="11" max="11" width="36.875" style="18" customWidth="1"/>
+    <col min="12" max="13" width="36.875" style="1" customWidth="1"/>
+    <col min="14" max="16" width="36.875" style="17" customWidth="1"/>
+    <col min="17" max="17" width="65.375" style="18" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A1" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="6" t="s">
         <v>111</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="6" t="s">
         <v>110</v>
       </c>
-      <c r="F1" s="2" t="s">
-        <v>349</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>348</v>
-      </c>
-      <c r="H1" s="2" t="s">
+      <c r="F1" s="6" t="s">
+        <v>346</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>345</v>
+      </c>
+      <c r="H1" s="6" t="s">
+        <v>347</v>
+      </c>
+      <c r="I1" s="6" t="s">
         <v>350</v>
       </c>
-      <c r="I1" s="2" t="s">
-        <v>353</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>354</v>
-      </c>
-      <c r="K1" s="3" t="s">
+      <c r="J1" s="6" t="s">
+        <v>351</v>
+      </c>
+      <c r="K1" s="16" t="s">
+        <v>329</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>575</v>
+      </c>
+      <c r="M1" s="3" t="s">
+        <v>577</v>
+      </c>
+      <c r="N1" s="16" t="s">
+        <v>605</v>
+      </c>
+      <c r="O1" s="16" t="s">
+        <v>606</v>
+      </c>
+      <c r="P1" s="16" t="s">
+        <v>607</v>
+      </c>
+      <c r="Q1" s="6" t="s">
         <v>330</v>
       </c>
-      <c r="L1" s="3" t="s">
-        <v>578</v>
-      </c>
-      <c r="M1" s="3" t="s">
-        <v>580</v>
-      </c>
-      <c r="N1" s="2" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>114</v>
       </c>
@@ -2677,30 +3050,39 @@
         <v>113</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
       <c r="G2" s="5" t="s">
+        <v>349</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>348</v>
+      </c>
+      <c r="I2" s="5" t="s">
         <v>352</v>
       </c>
-      <c r="H2" s="5" t="s">
-        <v>351</v>
-      </c>
-      <c r="I2" s="5" t="s">
-        <v>355</v>
-      </c>
       <c r="J2" s="5" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="K2" s="5" t="s">
         <v>7</v>
       </c>
       <c r="L2" s="5"/>
       <c r="M2" s="5"/>
-      <c r="N2" s="5" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N2" s="13" t="s">
+        <v>609</v>
+      </c>
+      <c r="O2" s="13" t="s">
+        <v>609</v>
+      </c>
+      <c r="P2" s="13" t="s">
+        <v>609</v>
+      </c>
+      <c r="Q2" s="5" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>114</v>
       </c>
@@ -2717,30 +3099,33 @@
         <v>113</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>607</v>
-      </c>
-      <c r="G3" s="5" t="s">
-        <v>352</v>
-      </c>
+        <v>353</v>
+      </c>
+      <c r="G3" s="5"/>
       <c r="H3" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="I3" s="5" t="s">
-        <v>355</v>
-      </c>
-      <c r="J3" s="5" t="s">
-        <v>356</v>
-      </c>
+      <c r="I3" s="5"/>
+      <c r="J3" s="5"/>
       <c r="K3" s="5" t="s">
         <v>7</v>
       </c>
       <c r="L3" s="5"/>
       <c r="M3" s="5"/>
-      <c r="N3" s="5" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N3" s="14" t="s">
+        <v>609</v>
+      </c>
+      <c r="O3" s="14" t="s">
+        <v>611</v>
+      </c>
+      <c r="P3" s="14" t="s">
+        <v>611</v>
+      </c>
+      <c r="Q3" s="5" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>114</v>
       </c>
@@ -2757,30 +3142,39 @@
         <v>113</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="H4" s="5" t="s">
         <v>103</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="K4" s="5" t="s">
         <v>7</v>
       </c>
       <c r="L4" s="5"/>
       <c r="M4" s="5"/>
-      <c r="N4" s="5" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N4" s="13" t="s">
+        <v>609</v>
+      </c>
+      <c r="O4" s="13" t="s">
+        <v>611</v>
+      </c>
+      <c r="P4" s="13" t="s">
+        <v>609</v>
+      </c>
+      <c r="Q4" s="5" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
         <v>114</v>
       </c>
@@ -2797,30 +3191,39 @@
         <v>113</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="H5" s="5" t="s">
         <v>105</v>
       </c>
       <c r="I5" s="5" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="J5" s="5" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="K5" s="5" t="s">
         <v>7</v>
       </c>
       <c r="L5" s="5"/>
       <c r="M5" s="5"/>
-      <c r="N5" s="5" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" ht="40.5" x14ac:dyDescent="0.3">
+      <c r="N5" s="13" t="s">
+        <v>609</v>
+      </c>
+      <c r="O5" s="14" t="s">
+        <v>613</v>
+      </c>
+      <c r="P5" s="13" t="s">
+        <v>609</v>
+      </c>
+      <c r="Q5" s="5" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
         <v>114</v>
       </c>
@@ -2837,32 +3240,41 @@
         <v>113</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="H6" s="5" t="s">
         <v>104</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="J6" s="5" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="K6" s="5" t="s">
         <v>7</v>
       </c>
       <c r="L6" s="5"/>
-      <c r="M6" s="13" t="s">
-        <v>582</v>
-      </c>
-      <c r="N6" s="5" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="M6" s="11" t="s">
+        <v>579</v>
+      </c>
+      <c r="N6" s="13" t="s">
+        <v>609</v>
+      </c>
+      <c r="O6" s="13" t="s">
+        <v>611</v>
+      </c>
+      <c r="P6" s="13" t="s">
+        <v>611</v>
+      </c>
+      <c r="Q6" s="5" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
         <v>114</v>
       </c>
@@ -2879,30 +3291,39 @@
         <v>113</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="H7" s="5" t="s">
         <v>103</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="J7" s="5" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="K7" s="5" t="s">
         <v>7</v>
       </c>
       <c r="L7" s="5"/>
       <c r="M7" s="5"/>
-      <c r="N7" s="5" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N7" s="13" t="s">
+        <v>611</v>
+      </c>
+      <c r="O7" s="13" t="s">
+        <v>609</v>
+      </c>
+      <c r="P7" s="13" t="s">
+        <v>611</v>
+      </c>
+      <c r="Q7" s="5" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
         <v>3</v>
       </c>
@@ -2919,30 +3340,39 @@
         <v>113</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="H8" s="5" t="s">
         <v>103</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="J8" s="5" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="K8" s="5" t="s">
         <v>7</v>
       </c>
       <c r="L8" s="5"/>
       <c r="M8" s="5"/>
-      <c r="N8" s="5" t="s">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N8" s="13" t="s">
+        <v>609</v>
+      </c>
+      <c r="O8" s="13" t="s">
+        <v>611</v>
+      </c>
+      <c r="P8" s="13" t="s">
+        <v>609</v>
+      </c>
+      <c r="Q8" s="5" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
         <v>3</v>
       </c>
@@ -2959,30 +3389,39 @@
         <v>113</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="H9" s="5" t="s">
         <v>106</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="J9" s="5" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="K9" s="5" t="s">
         <v>7</v>
       </c>
       <c r="L9" s="5"/>
       <c r="M9" s="5"/>
-      <c r="N9" s="5" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N9" s="13" t="s">
+        <v>611</v>
+      </c>
+      <c r="O9" s="13" t="s">
+        <v>611</v>
+      </c>
+      <c r="P9" s="13" t="s">
+        <v>609</v>
+      </c>
+      <c r="Q9" s="5" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
         <v>3</v>
       </c>
@@ -2999,30 +3438,39 @@
         <v>113</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="H10" s="5" t="s">
         <v>103</v>
       </c>
       <c r="I10" s="5" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="J10" s="5" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="K10" s="5" t="s">
         <v>7</v>
       </c>
       <c r="L10" s="5"/>
       <c r="M10" s="5"/>
-      <c r="N10" s="5" t="s">
-        <v>422</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N10" s="13" t="s">
+        <v>609</v>
+      </c>
+      <c r="O10" s="13" t="s">
+        <v>611</v>
+      </c>
+      <c r="P10" s="13" t="s">
+        <v>609</v>
+      </c>
+      <c r="Q10" s="5" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
         <v>3</v>
       </c>
@@ -3039,30 +3487,39 @@
         <v>113</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="H11" s="5" t="s">
         <v>103</v>
       </c>
       <c r="I11" s="5" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="J11" s="5" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="K11" s="5" t="s">
         <v>7</v>
       </c>
       <c r="L11" s="5"/>
       <c r="M11" s="5"/>
-      <c r="N11" s="5" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" ht="94.5" x14ac:dyDescent="0.3">
+      <c r="N11" s="13" t="s">
+        <v>609</v>
+      </c>
+      <c r="O11" s="13" t="s">
+        <v>609</v>
+      </c>
+      <c r="P11" s="13" t="s">
+        <v>611</v>
+      </c>
+      <c r="Q11" s="5" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" ht="94.5" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
         <v>3</v>
       </c>
@@ -3079,32 +3536,41 @@
         <v>113</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="H12" s="5" t="s">
         <v>106</v>
       </c>
       <c r="I12" s="5" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="J12" s="5" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="K12" s="5" t="s">
         <v>7</v>
       </c>
       <c r="L12" s="5"/>
-      <c r="M12" s="12" t="s">
-        <v>586</v>
-      </c>
-      <c r="N12" s="5" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="M12" s="10" t="s">
+        <v>583</v>
+      </c>
+      <c r="N12" s="13" t="s">
+        <v>609</v>
+      </c>
+      <c r="O12" s="13" t="s">
+        <v>609</v>
+      </c>
+      <c r="P12" s="13" t="s">
+        <v>609</v>
+      </c>
+      <c r="Q12" s="5" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
         <v>3</v>
       </c>
@@ -3121,30 +3587,39 @@
         <v>113</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="H13" s="5" t="s">
         <v>103</v>
       </c>
       <c r="I13" s="5" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="J13" s="5" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="K13" s="5" t="s">
         <v>7</v>
       </c>
       <c r="L13" s="5"/>
       <c r="M13" s="5"/>
-      <c r="N13" s="5" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N13" s="13" t="s">
+        <v>609</v>
+      </c>
+      <c r="O13" s="13" t="s">
+        <v>611</v>
+      </c>
+      <c r="P13" s="13" t="s">
+        <v>609</v>
+      </c>
+      <c r="Q13" s="5" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
         <v>3</v>
       </c>
@@ -3161,30 +3636,39 @@
         <v>113</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="H14" s="5" t="s">
         <v>103</v>
       </c>
       <c r="I14" s="5" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="J14" s="5" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="K14" s="5" t="s">
         <v>7</v>
       </c>
       <c r="L14" s="5"/>
       <c r="M14" s="5"/>
-      <c r="N14" s="5" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N14" s="13" t="s">
+        <v>609</v>
+      </c>
+      <c r="O14" s="13" t="s">
+        <v>611</v>
+      </c>
+      <c r="P14" s="13" t="s">
+        <v>609</v>
+      </c>
+      <c r="Q14" s="5" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
         <v>3</v>
       </c>
@@ -3201,30 +3685,39 @@
         <v>113</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="H15" s="5" t="s">
         <v>103</v>
       </c>
       <c r="I15" s="5" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="J15" s="5" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="K15" s="5" t="s">
         <v>7</v>
       </c>
       <c r="L15" s="5"/>
       <c r="M15" s="5"/>
-      <c r="N15" s="5" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N15" s="13" t="s">
+        <v>609</v>
+      </c>
+      <c r="O15" s="13" t="s">
+        <v>609</v>
+      </c>
+      <c r="P15" s="13" t="s">
+        <v>611</v>
+      </c>
+      <c r="Q15" s="5" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
         <v>3</v>
       </c>
@@ -3241,30 +3734,39 @@
         <v>113</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="H16" s="5" t="s">
         <v>103</v>
       </c>
       <c r="I16" s="5" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="J16" s="5" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="K16" s="5" t="s">
         <v>7</v>
       </c>
       <c r="L16" s="5"/>
       <c r="M16" s="5"/>
-      <c r="N16" s="5" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N16" s="13" t="s">
+        <v>609</v>
+      </c>
+      <c r="O16" s="13" t="s">
+        <v>609</v>
+      </c>
+      <c r="P16" s="13" t="s">
+        <v>609</v>
+      </c>
+      <c r="Q16" s="5" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
         <v>3</v>
       </c>
@@ -3281,30 +3783,39 @@
         <v>113</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="H17" s="5" t="s">
         <v>103</v>
       </c>
       <c r="I17" s="5" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="J17" s="5" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="K17" s="5" t="s">
         <v>7</v>
       </c>
       <c r="L17" s="5"/>
       <c r="M17" s="5"/>
-      <c r="N17" s="5" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N17" s="13" t="s">
+        <v>609</v>
+      </c>
+      <c r="O17" s="13" t="s">
+        <v>609</v>
+      </c>
+      <c r="P17" s="13" t="s">
+        <v>609</v>
+      </c>
+      <c r="Q17" s="5" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
         <v>3</v>
       </c>
@@ -3321,30 +3832,39 @@
         <v>113</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="H18" s="5" t="s">
         <v>103</v>
       </c>
       <c r="I18" s="5" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="J18" s="5" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="K18" s="5" t="s">
         <v>7</v>
       </c>
       <c r="L18" s="5"/>
       <c r="M18" s="5"/>
-      <c r="N18" s="5" t="s">
-        <v>426</v>
-      </c>
-    </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N18" s="13" t="s">
+        <v>609</v>
+      </c>
+      <c r="O18" s="13" t="s">
+        <v>609</v>
+      </c>
+      <c r="P18" s="13" t="s">
+        <v>609</v>
+      </c>
+      <c r="Q18" s="5" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
         <v>3</v>
       </c>
@@ -3361,30 +3881,39 @@
         <v>113</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="H19" s="5" t="s">
         <v>107</v>
       </c>
       <c r="I19" s="5" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="J19" s="5" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="K19" s="5" t="s">
         <v>7</v>
       </c>
       <c r="L19" s="5"/>
       <c r="M19" s="5"/>
-      <c r="N19" s="5" t="s">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="20" spans="1:14" ht="148.5" x14ac:dyDescent="0.3">
+      <c r="N19" s="13" t="s">
+        <v>609</v>
+      </c>
+      <c r="O19" s="13" t="s">
+        <v>609</v>
+      </c>
+      <c r="P19" s="13" t="s">
+        <v>609</v>
+      </c>
+      <c r="Q19" s="5" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17" ht="148.5" x14ac:dyDescent="0.3">
       <c r="A20" s="4" t="s">
         <v>3</v>
       </c>
@@ -3401,32 +3930,41 @@
         <v>113</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
       <c r="G20" s="5" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="H20" s="5" t="s">
         <v>103</v>
       </c>
       <c r="I20" s="5" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="J20" s="5" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="K20" s="5" t="s">
         <v>7</v>
       </c>
       <c r="L20" s="5"/>
-      <c r="M20" s="12" t="s">
-        <v>585</v>
-      </c>
-      <c r="N20" s="5" t="s">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="M20" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="N20" s="13" t="s">
+        <v>611</v>
+      </c>
+      <c r="O20" s="14" t="s">
+        <v>613</v>
+      </c>
+      <c r="P20" s="13" t="s">
+        <v>609</v>
+      </c>
+      <c r="Q20" s="5" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
         <v>101</v>
       </c>
@@ -3443,30 +3981,39 @@
         <v>113</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
       <c r="G21" s="5" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="H21" s="5" t="s">
         <v>103</v>
       </c>
       <c r="I21" s="5" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="J21" s="5" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="K21" s="5" t="s">
         <v>7</v>
       </c>
       <c r="L21" s="5"/>
       <c r="M21" s="5"/>
-      <c r="N21" s="5" t="s">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="22" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N21" s="14" t="s">
+        <v>613</v>
+      </c>
+      <c r="O21" s="13" t="s">
+        <v>609</v>
+      </c>
+      <c r="P21" s="13" t="s">
+        <v>609</v>
+      </c>
+      <c r="Q21" s="5" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="4" t="s">
         <v>101</v>
       </c>
@@ -3483,35 +4030,44 @@
         <v>113</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
       <c r="G22" s="5" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="H22" s="5" t="s">
         <v>103</v>
       </c>
       <c r="I22" s="5" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="J22" s="5" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="K22" s="5" t="s">
         <v>7</v>
       </c>
       <c r="L22" s="5"/>
       <c r="M22" s="5"/>
-      <c r="N22" s="5" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N22" s="13" t="s">
+        <v>611</v>
+      </c>
+      <c r="O22" s="13" t="s">
+        <v>609</v>
+      </c>
+      <c r="P22" s="13" t="s">
+        <v>611</v>
+      </c>
+      <c r="Q22" s="5" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="23" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
         <v>101</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="C23" s="5" t="s">
         <v>30</v>
@@ -3523,30 +4079,39 @@
         <v>113</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="H23" s="5" t="s">
         <v>103</v>
       </c>
       <c r="I23" s="5" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="J23" s="5" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="K23" s="5" t="s">
         <v>7</v>
       </c>
       <c r="L23" s="5"/>
       <c r="M23" s="5"/>
-      <c r="N23" s="5" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N23" s="13" t="s">
+        <v>611</v>
+      </c>
+      <c r="O23" s="14" t="s">
+        <v>613</v>
+      </c>
+      <c r="P23" s="13" t="s">
+        <v>611</v>
+      </c>
+      <c r="Q23" s="5" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A24" s="4" t="s">
         <v>115</v>
       </c>
@@ -3563,30 +4128,39 @@
         <v>113</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
       <c r="G24" s="5" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="H24" s="5" t="s">
         <v>108</v>
       </c>
       <c r="I24" s="5" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="J24" s="5" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="K24" s="5" t="s">
         <v>7</v>
       </c>
       <c r="L24" s="5"/>
       <c r="M24" s="5"/>
-      <c r="N24" s="5" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N24" s="14" t="s">
+        <v>611</v>
+      </c>
+      <c r="O24" s="14" t="s">
+        <v>611</v>
+      </c>
+      <c r="P24" s="14" t="s">
+        <v>611</v>
+      </c>
+      <c r="Q24" s="5" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="25" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A25" s="4" t="s">
         <v>115</v>
       </c>
@@ -3603,30 +4177,39 @@
         <v>113</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="H25" s="5" t="s">
         <v>103</v>
       </c>
       <c r="I25" s="5" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="J25" s="5" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="K25" s="5" t="s">
         <v>7</v>
       </c>
       <c r="L25" s="5"/>
       <c r="M25" s="5"/>
-      <c r="N25" s="5" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N25" s="13" t="s">
+        <v>611</v>
+      </c>
+      <c r="O25" s="13" t="s">
+        <v>609</v>
+      </c>
+      <c r="P25" s="13" t="s">
+        <v>609</v>
+      </c>
+      <c r="Q25" s="5" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="26" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A26" s="4" t="s">
         <v>115</v>
       </c>
@@ -3643,30 +4226,39 @@
         <v>113</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="H26" s="5" t="s">
         <v>103</v>
       </c>
       <c r="I26" s="5" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="J26" s="5" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="K26" s="5" t="s">
         <v>7</v>
       </c>
       <c r="L26" s="5"/>
       <c r="M26" s="5"/>
-      <c r="N26" s="5" t="s">
-        <v>436</v>
-      </c>
-    </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N26" s="13" t="s">
+        <v>609</v>
+      </c>
+      <c r="O26" s="13" t="s">
+        <v>609</v>
+      </c>
+      <c r="P26" s="13" t="s">
+        <v>609</v>
+      </c>
+      <c r="Q26" s="5" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A27" s="4" t="s">
         <v>115</v>
       </c>
@@ -3683,30 +4275,39 @@
         <v>113</v>
       </c>
       <c r="F27" s="5" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="H27" s="5" t="s">
         <v>103</v>
       </c>
       <c r="I27" s="5" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="J27" s="5" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="K27" s="5" t="s">
         <v>7</v>
       </c>
       <c r="L27" s="5"/>
       <c r="M27" s="5"/>
-      <c r="N27" s="5" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="28" spans="1:14" ht="148.5" x14ac:dyDescent="0.3">
+      <c r="N27" s="13" t="s">
+        <v>611</v>
+      </c>
+      <c r="O27" s="14" t="s">
+        <v>613</v>
+      </c>
+      <c r="P27" s="13" t="s">
+        <v>609</v>
+      </c>
+      <c r="Q27" s="5" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="28" spans="1:17" ht="148.5" x14ac:dyDescent="0.3">
       <c r="A28" s="4" t="s">
         <v>102</v>
       </c>
@@ -3723,32 +4324,41 @@
         <v>113</v>
       </c>
       <c r="F28" s="5" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
       <c r="G28" s="5" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="H28" s="5" t="s">
         <v>103</v>
       </c>
       <c r="I28" s="5" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="J28" s="5" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="K28" s="5" t="s">
         <v>7</v>
       </c>
       <c r="L28" s="5"/>
-      <c r="M28" s="12" t="s">
-        <v>594</v>
-      </c>
-      <c r="N28" s="5" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="M28" s="10" t="s">
+        <v>591</v>
+      </c>
+      <c r="N28" s="13" t="s">
+        <v>609</v>
+      </c>
+      <c r="O28" s="13" t="s">
+        <v>611</v>
+      </c>
+      <c r="P28" s="13" t="s">
+        <v>611</v>
+      </c>
+      <c r="Q28" s="5" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="29" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A29" s="4" t="s">
         <v>102</v>
       </c>
@@ -3765,30 +4375,39 @@
         <v>113</v>
       </c>
       <c r="F29" s="5" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
       <c r="G29" s="5" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="H29" s="5" t="s">
         <v>103</v>
       </c>
       <c r="I29" s="5" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="J29" s="5" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="K29" s="5" t="s">
         <v>7</v>
       </c>
       <c r="L29" s="5"/>
       <c r="M29" s="5"/>
-      <c r="N29" s="5" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N29" s="13" t="s">
+        <v>609</v>
+      </c>
+      <c r="O29" s="13" t="s">
+        <v>609</v>
+      </c>
+      <c r="P29" s="13" t="s">
+        <v>609</v>
+      </c>
+      <c r="Q29" s="5" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="30" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A30" s="4" t="s">
         <v>102</v>
       </c>
@@ -3805,30 +4424,39 @@
         <v>113</v>
       </c>
       <c r="F30" s="5" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
       <c r="G30" s="5" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="H30" s="5" t="s">
         <v>103</v>
       </c>
       <c r="I30" s="5" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="J30" s="5" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="K30" s="5" t="s">
         <v>7</v>
       </c>
       <c r="L30" s="5"/>
       <c r="M30" s="5"/>
-      <c r="N30" s="5" t="s">
-        <v>439</v>
-      </c>
-    </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N30" s="13" t="s">
+        <v>609</v>
+      </c>
+      <c r="O30" s="13" t="s">
+        <v>611</v>
+      </c>
+      <c r="P30" s="13" t="s">
+        <v>611</v>
+      </c>
+      <c r="Q30" s="5" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="31" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A31" s="4" t="s">
         <v>102</v>
       </c>
@@ -3845,30 +4473,39 @@
         <v>113</v>
       </c>
       <c r="F31" s="5" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
       <c r="G31" s="5" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="H31" s="5" t="s">
         <v>103</v>
       </c>
       <c r="I31" s="5" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="J31" s="5" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="K31" s="5" t="s">
         <v>7</v>
       </c>
       <c r="L31" s="5"/>
       <c r="M31" s="5"/>
-      <c r="N31" s="5" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="32" spans="1:14" ht="81" x14ac:dyDescent="0.3">
+      <c r="N31" s="13" t="s">
+        <v>611</v>
+      </c>
+      <c r="O31" s="13" t="s">
+        <v>609</v>
+      </c>
+      <c r="P31" s="13" t="s">
+        <v>609</v>
+      </c>
+      <c r="Q31" s="5" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="32" spans="1:17" ht="81" x14ac:dyDescent="0.3">
       <c r="A32" s="4" t="s">
         <v>102</v>
       </c>
@@ -3885,32 +4522,41 @@
         <v>113</v>
       </c>
       <c r="F32" s="5" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
       <c r="G32" s="5" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="H32" s="5" t="s">
         <v>103</v>
       </c>
       <c r="I32" s="5" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="J32" s="5" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="K32" s="5" t="s">
         <v>7</v>
       </c>
       <c r="L32" s="5"/>
-      <c r="M32" s="12" t="s">
-        <v>596</v>
-      </c>
-      <c r="N32" s="5" t="s">
-        <v>441</v>
-      </c>
-    </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="M32" s="10" t="s">
+        <v>593</v>
+      </c>
+      <c r="N32" s="13" t="s">
+        <v>609</v>
+      </c>
+      <c r="O32" s="13" t="s">
+        <v>609</v>
+      </c>
+      <c r="P32" s="13" t="s">
+        <v>609</v>
+      </c>
+      <c r="Q32" s="5" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="33" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A33" s="4" t="s">
         <v>116</v>
       </c>
@@ -3927,30 +4573,39 @@
         <v>113</v>
       </c>
       <c r="F33" s="5" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
       <c r="G33" s="5" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="H33" s="5" t="s">
         <v>103</v>
       </c>
       <c r="I33" s="5" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="J33" s="5" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="K33" s="5" t="s">
         <v>7</v>
       </c>
       <c r="L33" s="5"/>
       <c r="M33" s="5"/>
-      <c r="N33" s="5" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N33" s="13" t="s">
+        <v>609</v>
+      </c>
+      <c r="O33" s="13" t="s">
+        <v>609</v>
+      </c>
+      <c r="P33" s="13" t="s">
+        <v>609</v>
+      </c>
+      <c r="Q33" s="5" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="34" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A34" s="4" t="s">
         <v>116</v>
       </c>
@@ -3967,30 +4622,39 @@
         <v>113</v>
       </c>
       <c r="F34" s="5" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
       <c r="G34" s="5" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="H34" s="5" t="s">
         <v>103</v>
       </c>
       <c r="I34" s="5" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="J34" s="5" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="K34" s="5" t="s">
         <v>7</v>
       </c>
       <c r="L34" s="5"/>
       <c r="M34" s="5"/>
-      <c r="N34" s="5" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N34" s="13" t="s">
+        <v>611</v>
+      </c>
+      <c r="O34" s="13" t="s">
+        <v>609</v>
+      </c>
+      <c r="P34" s="13" t="s">
+        <v>611</v>
+      </c>
+      <c r="Q34" s="5" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="35" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A35" s="4" t="s">
         <v>116</v>
       </c>
@@ -4007,30 +4671,39 @@
         <v>113</v>
       </c>
       <c r="F35" s="5" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
       <c r="G35" s="5" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="H35" s="5" t="s">
         <v>103</v>
       </c>
       <c r="I35" s="5" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="J35" s="5" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="K35" s="5" t="s">
         <v>7</v>
       </c>
       <c r="L35" s="5"/>
       <c r="M35" s="5"/>
-      <c r="N35" s="5" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N35" s="13" t="s">
+        <v>611</v>
+      </c>
+      <c r="O35" s="13" t="s">
+        <v>609</v>
+      </c>
+      <c r="P35" s="13" t="s">
+        <v>609</v>
+      </c>
+      <c r="Q35" s="5" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="36" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A36" s="4" t="s">
         <v>116</v>
       </c>
@@ -4047,30 +4720,39 @@
         <v>113</v>
       </c>
       <c r="F36" s="5" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
       <c r="G36" s="5" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="H36" s="5" t="s">
         <v>105</v>
       </c>
       <c r="I36" s="5" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="J36" s="5" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="K36" s="5" t="s">
         <v>7</v>
       </c>
       <c r="L36" s="5"/>
       <c r="M36" s="5"/>
-      <c r="N36" s="5" t="s">
-        <v>445</v>
-      </c>
-    </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N36" s="13" t="s">
+        <v>611</v>
+      </c>
+      <c r="O36" s="13" t="s">
+        <v>611</v>
+      </c>
+      <c r="P36" s="13" t="s">
+        <v>611</v>
+      </c>
+      <c r="Q36" s="5" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="37" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A37" s="4" t="s">
         <v>117</v>
       </c>
@@ -4087,30 +4769,39 @@
         <v>113</v>
       </c>
       <c r="F37" s="5" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
       <c r="G37" s="5" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="H37" s="5" t="s">
         <v>109</v>
       </c>
       <c r="I37" s="5" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="J37" s="5" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="K37" s="5" t="s">
         <v>7</v>
       </c>
       <c r="L37" s="5"/>
       <c r="M37" s="5"/>
-      <c r="N37" s="5" t="s">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N37" s="14" t="s">
+        <v>611</v>
+      </c>
+      <c r="O37" s="14" t="s">
+        <v>611</v>
+      </c>
+      <c r="P37" s="14" t="s">
+        <v>609</v>
+      </c>
+      <c r="Q37" s="5" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="38" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A38" s="4" t="s">
         <v>117</v>
       </c>
@@ -4127,30 +4818,39 @@
         <v>113</v>
       </c>
       <c r="F38" s="5" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
       <c r="G38" s="5" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="H38" s="5" t="s">
         <v>103</v>
       </c>
       <c r="I38" s="5" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="J38" s="5" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="K38" s="5" t="s">
         <v>7</v>
       </c>
       <c r="L38" s="5"/>
       <c r="M38" s="5"/>
-      <c r="N38" s="5" t="s">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N38" s="13" t="s">
+        <v>609</v>
+      </c>
+      <c r="O38" s="13" t="s">
+        <v>609</v>
+      </c>
+      <c r="P38" s="14" t="s">
+        <v>613</v>
+      </c>
+      <c r="Q38" s="5" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="39" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A39" s="4" t="s">
         <v>117</v>
       </c>
@@ -4167,30 +4867,39 @@
         <v>113</v>
       </c>
       <c r="F39" s="5" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
       <c r="G39" s="5" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="H39" s="5" t="s">
         <v>105</v>
       </c>
       <c r="I39" s="5" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="J39" s="5" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="K39" s="5" t="s">
         <v>7</v>
       </c>
       <c r="L39" s="5"/>
       <c r="M39" s="5"/>
-      <c r="N39" s="5" t="s">
-        <v>451</v>
-      </c>
-    </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N39" s="13" t="s">
+        <v>611</v>
+      </c>
+      <c r="O39" s="13" t="s">
+        <v>609</v>
+      </c>
+      <c r="P39" s="13" t="s">
+        <v>609</v>
+      </c>
+      <c r="Q39" s="5" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="40" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A40" s="4" t="s">
         <v>117</v>
       </c>
@@ -4207,30 +4916,39 @@
         <v>113</v>
       </c>
       <c r="F40" s="5" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
       <c r="G40" s="5" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="H40" s="5" t="s">
         <v>103</v>
       </c>
       <c r="I40" s="5" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="J40" s="5" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="K40" s="5" t="s">
         <v>7</v>
       </c>
       <c r="L40" s="5"/>
       <c r="M40" s="5"/>
-      <c r="N40" s="5" t="s">
-        <v>452</v>
-      </c>
-    </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N40" s="14" t="s">
+        <v>613</v>
+      </c>
+      <c r="O40" s="13" t="s">
+        <v>609</v>
+      </c>
+      <c r="P40" s="13" t="s">
+        <v>609</v>
+      </c>
+      <c r="Q40" s="5" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="41" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A41" s="4" t="s">
         <v>117</v>
       </c>
@@ -4247,30 +4965,39 @@
         <v>113</v>
       </c>
       <c r="F41" s="5" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
       <c r="G41" s="5" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="H41" s="5" t="s">
         <v>104</v>
       </c>
       <c r="I41" s="5" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="J41" s="5" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="K41" s="5" t="s">
         <v>7</v>
       </c>
       <c r="L41" s="5"/>
       <c r="M41" s="5"/>
-      <c r="N41" s="5" t="s">
-        <v>447</v>
-      </c>
-    </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N41" s="14" t="s">
+        <v>613</v>
+      </c>
+      <c r="O41" s="13" t="s">
+        <v>609</v>
+      </c>
+      <c r="P41" s="13" t="s">
+        <v>609</v>
+      </c>
+      <c r="Q41" s="5" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="42" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A42" s="4" t="s">
         <v>117</v>
       </c>
@@ -4287,30 +5014,39 @@
         <v>113</v>
       </c>
       <c r="F42" s="5" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
       <c r="G42" s="5" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="H42" s="5" t="s">
         <v>103</v>
       </c>
       <c r="I42" s="5" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="J42" s="5" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="K42" s="5" t="s">
         <v>7</v>
       </c>
       <c r="L42" s="5"/>
       <c r="M42" s="5"/>
-      <c r="N42" s="5" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N42" s="13" t="s">
+        <v>609</v>
+      </c>
+      <c r="O42" s="13" t="s">
+        <v>609</v>
+      </c>
+      <c r="P42" s="13" t="s">
+        <v>609</v>
+      </c>
+      <c r="Q42" s="5" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="43" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A43" s="4" t="s">
         <v>117</v>
       </c>
@@ -4327,30 +5063,39 @@
         <v>113</v>
       </c>
       <c r="F43" s="5" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
       <c r="G43" s="5" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="H43" s="5" t="s">
         <v>103</v>
       </c>
       <c r="I43" s="5" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="J43" s="5" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="K43" s="5" t="s">
         <v>7</v>
       </c>
       <c r="L43" s="5"/>
       <c r="M43" s="5"/>
-      <c r="N43" s="5" t="s">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N43" s="13" t="s">
+        <v>609</v>
+      </c>
+      <c r="O43" s="13" t="s">
+        <v>609</v>
+      </c>
+      <c r="P43" s="13" t="s">
+        <v>609</v>
+      </c>
+      <c r="Q43" s="5" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="44" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A44" s="4" t="s">
         <v>118</v>
       </c>
@@ -4367,30 +5112,39 @@
         <v>113</v>
       </c>
       <c r="F44" s="5" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
       <c r="G44" s="5" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="H44" s="5" t="s">
         <v>105</v>
       </c>
       <c r="I44" s="5" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="J44" s="5" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="K44" s="5" t="s">
         <v>7</v>
       </c>
       <c r="L44" s="5"/>
       <c r="M44" s="5"/>
-      <c r="N44" s="5" t="s">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N44" s="13" t="s">
+        <v>611</v>
+      </c>
+      <c r="O44" s="13" t="s">
+        <v>611</v>
+      </c>
+      <c r="P44" s="13" t="s">
+        <v>611</v>
+      </c>
+      <c r="Q44" s="5" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="45" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A45" s="4" t="s">
         <v>118</v>
       </c>
@@ -4407,30 +5161,39 @@
         <v>113</v>
       </c>
       <c r="F45" s="5" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
       <c r="G45" s="5" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="H45" s="5" t="s">
         <v>105</v>
       </c>
       <c r="I45" s="5" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="J45" s="5" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="K45" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="L45" s="12"/>
-      <c r="M45" s="12"/>
-      <c r="N45" s="5" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="L45" s="10"/>
+      <c r="M45" s="10"/>
+      <c r="N45" s="13" t="s">
+        <v>611</v>
+      </c>
+      <c r="O45" s="13" t="s">
+        <v>611</v>
+      </c>
+      <c r="P45" s="13" t="s">
+        <v>611</v>
+      </c>
+      <c r="Q45" s="5" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="46" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A46" s="4" t="s">
         <v>118</v>
       </c>
@@ -4447,30 +5210,39 @@
         <v>113</v>
       </c>
       <c r="F46" s="5" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
       <c r="G46" s="5" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="H46" s="5" t="s">
         <v>103</v>
       </c>
       <c r="I46" s="5" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="J46" s="5" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="K46" s="5" t="s">
         <v>7</v>
       </c>
       <c r="L46" s="5"/>
       <c r="M46" s="5"/>
-      <c r="N46" s="5" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N46" s="14" t="s">
+        <v>613</v>
+      </c>
+      <c r="O46" s="13" t="s">
+        <v>609</v>
+      </c>
+      <c r="P46" s="13" t="s">
+        <v>609</v>
+      </c>
+      <c r="Q46" s="5" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="47" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A47" s="4" t="s">
         <v>118</v>
       </c>
@@ -4487,30 +5259,39 @@
         <v>113</v>
       </c>
       <c r="F47" s="5" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
       <c r="G47" s="5" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="H47" s="5" t="s">
         <v>103</v>
       </c>
       <c r="I47" s="5" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="J47" s="5" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="K47" s="5" t="s">
         <v>7</v>
       </c>
       <c r="L47" s="5"/>
       <c r="M47" s="5"/>
-      <c r="N47" s="5" t="s">
-        <v>456</v>
-      </c>
-    </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N47" s="13" t="s">
+        <v>609</v>
+      </c>
+      <c r="O47" s="14" t="s">
+        <v>613</v>
+      </c>
+      <c r="P47" s="13" t="s">
+        <v>609</v>
+      </c>
+      <c r="Q47" s="5" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="48" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A48" s="4" t="s">
         <v>118</v>
       </c>
@@ -4527,30 +5308,39 @@
         <v>113</v>
       </c>
       <c r="F48" s="5" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
       <c r="G48" s="5" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="H48" s="5" t="s">
         <v>103</v>
       </c>
       <c r="I48" s="5" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="J48" s="5" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="K48" s="5" t="s">
         <v>7</v>
       </c>
       <c r="L48" s="5"/>
       <c r="M48" s="5"/>
-      <c r="N48" s="5" t="s">
-        <v>458</v>
-      </c>
-    </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N48" s="13" t="s">
+        <v>609</v>
+      </c>
+      <c r="O48" s="13" t="s">
+        <v>611</v>
+      </c>
+      <c r="P48" s="13" t="s">
+        <v>609</v>
+      </c>
+      <c r="Q48" s="5" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="49" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A49" s="4" t="s">
         <v>114</v>
       </c>
@@ -4564,11 +5354,11 @@
         <v>112</v>
       </c>
       <c r="E49" s="5" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="F49" s="5"/>
       <c r="G49" s="5" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H49" s="5"/>
       <c r="I49" s="5"/>
@@ -4576,11 +5366,20 @@
       <c r="K49" s="5"/>
       <c r="L49" s="5"/>
       <c r="M49" s="5"/>
-      <c r="N49" s="5" t="s">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N49" s="13" t="s">
+        <v>609</v>
+      </c>
+      <c r="O49" s="13" t="s">
+        <v>609</v>
+      </c>
+      <c r="P49" s="13" t="s">
+        <v>611</v>
+      </c>
+      <c r="Q49" s="5" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="50" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A50" s="4" t="s">
         <v>114</v>
       </c>
@@ -4594,30 +5393,39 @@
         <v>112</v>
       </c>
       <c r="E50" s="5" t="s">
-        <v>316</v>
-      </c>
-      <c r="F50" s="6" t="s">
-        <v>366</v>
-      </c>
-      <c r="G50" s="6"/>
-      <c r="H50" s="6"/>
-      <c r="I50" s="6"/>
-      <c r="J50" s="6"/>
-      <c r="K50" s="11" t="s">
-        <v>370</v>
-      </c>
-      <c r="L50" s="11"/>
-      <c r="M50" s="11"/>
-      <c r="N50" s="6" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.3">
+        <v>315</v>
+      </c>
+      <c r="F50" s="20" t="s">
+        <v>363</v>
+      </c>
+      <c r="G50" s="20"/>
+      <c r="H50" s="20"/>
+      <c r="I50" s="20"/>
+      <c r="J50" s="20"/>
+      <c r="K50" s="19" t="s">
+        <v>367</v>
+      </c>
+      <c r="L50" s="9"/>
+      <c r="M50" s="9"/>
+      <c r="N50" s="13" t="s">
+        <v>609</v>
+      </c>
+      <c r="O50" s="13" t="s">
+        <v>609</v>
+      </c>
+      <c r="P50" s="13" t="s">
+        <v>611</v>
+      </c>
+      <c r="Q50" s="20" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="51" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A51" s="4" t="s">
         <v>114</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C51" s="5" t="s">
         <v>121</v>
@@ -4626,30 +5434,39 @@
         <v>112</v>
       </c>
       <c r="E51" s="5" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="F51" s="5" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="G51" s="5"/>
       <c r="H51" s="5"/>
       <c r="I51" s="5"/>
       <c r="J51" s="5"/>
       <c r="K51" s="5" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="L51" s="5"/>
       <c r="M51" s="5"/>
-      <c r="N51" s="5" t="s">
-        <v>465</v>
-      </c>
-    </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N51" s="14" t="s">
+        <v>613</v>
+      </c>
+      <c r="O51" s="13" t="s">
+        <v>609</v>
+      </c>
+      <c r="P51" s="13" t="s">
+        <v>611</v>
+      </c>
+      <c r="Q51" s="5" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="52" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A52" s="4" t="s">
         <v>114</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C52" s="5" t="s">
         <v>122</v>
@@ -4658,32 +5475,41 @@
         <v>112</v>
       </c>
       <c r="E52" s="5" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="F52" s="5"/>
       <c r="G52" s="5" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H52" s="5"/>
       <c r="I52" s="5" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="J52" s="5" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="K52" s="5"/>
       <c r="L52" s="5"/>
       <c r="M52" s="5"/>
-      <c r="N52" s="5" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="53" spans="1:14" ht="162" x14ac:dyDescent="0.3">
+      <c r="N52" s="13" t="s">
+        <v>609</v>
+      </c>
+      <c r="O52" s="14" t="s">
+        <v>613</v>
+      </c>
+      <c r="P52" s="13" t="s">
+        <v>609</v>
+      </c>
+      <c r="Q52" s="5" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="53" spans="1:17" ht="162" x14ac:dyDescent="0.3">
       <c r="A53" s="4" t="s">
         <v>114</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C53" s="5" t="s">
         <v>123</v>
@@ -4692,34 +5518,43 @@
         <v>112</v>
       </c>
       <c r="E53" s="5" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="F53" s="5" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="G53" s="5"/>
       <c r="H53" s="5"/>
       <c r="I53" s="5"/>
       <c r="J53" s="5"/>
       <c r="K53" s="5" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="L53" s="5" t="s">
-        <v>605</v>
+        <v>602</v>
       </c>
       <c r="M53" s="5" t="s">
-        <v>606</v>
-      </c>
-      <c r="N53" s="5" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="54" spans="1:14" ht="148.5" x14ac:dyDescent="0.3">
+        <v>603</v>
+      </c>
+      <c r="N53" s="14" t="s">
+        <v>610</v>
+      </c>
+      <c r="O53" s="14" t="s">
+        <v>610</v>
+      </c>
+      <c r="P53" s="14" t="s">
+        <v>610</v>
+      </c>
+      <c r="Q53" s="5" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="54" spans="1:17" ht="148.5" x14ac:dyDescent="0.3">
       <c r="A54" s="4" t="s">
         <v>114</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C54" s="5" t="s">
         <v>124</v>
@@ -4728,34 +5563,43 @@
         <v>4</v>
       </c>
       <c r="E54" s="5" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F54" s="5" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="G54" s="5"/>
       <c r="H54" s="5"/>
       <c r="I54" s="5"/>
       <c r="J54" s="5"/>
       <c r="K54" s="5" t="s">
-        <v>373</v>
-      </c>
-      <c r="L54" s="12" t="s">
-        <v>579</v>
-      </c>
-      <c r="M54" s="12" t="s">
-        <v>581</v>
-      </c>
-      <c r="N54" s="5" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.3">
+        <v>370</v>
+      </c>
+      <c r="L54" s="10" t="s">
+        <v>576</v>
+      </c>
+      <c r="M54" s="10" t="s">
+        <v>578</v>
+      </c>
+      <c r="N54" s="13" t="s">
+        <v>609</v>
+      </c>
+      <c r="O54" s="13" t="s">
+        <v>609</v>
+      </c>
+      <c r="P54" s="13" t="s">
+        <v>609</v>
+      </c>
+      <c r="Q54" s="5" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="55" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A55" s="4" t="s">
         <v>114</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C55" s="5" t="s">
         <v>125</v>
@@ -4764,27 +5608,36 @@
         <v>112</v>
       </c>
       <c r="E55" s="5" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="F55" s="5"/>
-      <c r="G55" s="2" t="s">
-        <v>365</v>
-      </c>
-      <c r="H55" s="2"/>
-      <c r="I55" s="2" t="s">
-        <v>402</v>
-      </c>
-      <c r="J55" s="2" t="s">
-        <v>403</v>
-      </c>
-      <c r="K55" s="2"/>
+      <c r="G55" s="6" t="s">
+        <v>362</v>
+      </c>
+      <c r="H55" s="6"/>
+      <c r="I55" s="6" t="s">
+        <v>399</v>
+      </c>
+      <c r="J55" s="6" t="s">
+        <v>400</v>
+      </c>
+      <c r="K55" s="6"/>
       <c r="L55" s="2"/>
       <c r="M55" s="2"/>
-      <c r="N55" s="2" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="56" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N55" s="13" t="s">
+        <v>609</v>
+      </c>
+      <c r="O55" s="13" t="s">
+        <v>609</v>
+      </c>
+      <c r="P55" s="13" t="s">
+        <v>609</v>
+      </c>
+      <c r="Q55" s="6" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="56" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A56" s="4" t="s">
         <v>114</v>
       </c>
@@ -4798,25 +5651,34 @@
         <v>4</v>
       </c>
       <c r="E56" s="5" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F56" s="5" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="G56" s="5"/>
       <c r="H56" s="5"/>
       <c r="I56" s="5"/>
       <c r="J56" s="5"/>
       <c r="K56" s="5" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="L56" s="5"/>
       <c r="M56" s="5"/>
-      <c r="N56" s="5" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="57" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N56" s="13" t="s">
+        <v>609</v>
+      </c>
+      <c r="O56" s="13" t="s">
+        <v>609</v>
+      </c>
+      <c r="P56" s="13" t="s">
+        <v>609</v>
+      </c>
+      <c r="Q56" s="5" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="57" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="4" t="s">
         <v>114</v>
       </c>
@@ -4830,25 +5692,34 @@
         <v>4</v>
       </c>
       <c r="E57" s="5" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F57" s="5" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="G57" s="5"/>
       <c r="H57" s="5"/>
       <c r="I57" s="5"/>
       <c r="J57" s="5"/>
       <c r="K57" s="5" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="L57" s="5"/>
       <c r="M57" s="5"/>
-      <c r="N57" s="5" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="58" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N57" s="14" t="s">
+        <v>610</v>
+      </c>
+      <c r="O57" s="14" t="s">
+        <v>612</v>
+      </c>
+      <c r="P57" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="Q57" s="5" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="58" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A58" s="4" t="s">
         <v>114</v>
       </c>
@@ -4862,30 +5733,39 @@
         <v>4</v>
       </c>
       <c r="E58" s="5" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F58" s="5" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="G58" s="5"/>
       <c r="H58" s="5"/>
       <c r="I58" s="5"/>
       <c r="J58" s="5"/>
       <c r="K58" s="5" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="L58" s="5"/>
       <c r="M58" s="5"/>
-      <c r="N58" s="5" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="59" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N58" s="14" t="s">
+        <v>612</v>
+      </c>
+      <c r="O58" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="P58" s="14" t="s">
+        <v>611</v>
+      </c>
+      <c r="Q58" s="5" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="59" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A59" s="4" t="s">
         <v>114</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C59" s="5" t="s">
         <v>129</v>
@@ -4894,7 +5774,7 @@
         <v>4</v>
       </c>
       <c r="E59" s="5" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F59" s="5" t="s">
         <v>6</v>
@@ -4904,20 +5784,29 @@
       <c r="I59" s="5"/>
       <c r="J59" s="5"/>
       <c r="K59" s="5" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="L59" s="5"/>
       <c r="M59" s="5"/>
-      <c r="N59" s="5" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="60" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N59" s="14" t="s">
+        <v>611</v>
+      </c>
+      <c r="O59" s="14" t="s">
+        <v>612</v>
+      </c>
+      <c r="P59" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="Q59" s="5" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="60" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A60" s="4" t="s">
         <v>114</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C60" s="5" t="s">
         <v>130</v>
@@ -4926,30 +5815,39 @@
         <v>112</v>
       </c>
       <c r="E60" s="5" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="F60" s="5" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="G60" s="5"/>
       <c r="H60" s="5"/>
       <c r="I60" s="5"/>
       <c r="J60" s="5"/>
       <c r="K60" s="5" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="L60" s="5"/>
       <c r="M60" s="5"/>
-      <c r="N60" s="5" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="61" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N60" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="O60" s="14" t="s">
+        <v>611</v>
+      </c>
+      <c r="P60" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="Q60" s="5" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="61" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A61" s="4" t="s">
         <v>114</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="C61" s="5" t="s">
         <v>131</v>
@@ -4958,32 +5856,41 @@
         <v>112</v>
       </c>
       <c r="E61" s="5" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="F61" s="5"/>
       <c r="G61" s="5" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H61" s="5"/>
       <c r="I61" s="5" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="J61" s="5" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="K61" s="5"/>
       <c r="L61" s="5"/>
       <c r="M61" s="5"/>
-      <c r="N61" s="5" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="62" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N61" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="O61" s="14" t="s">
+        <v>612</v>
+      </c>
+      <c r="P61" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="Q61" s="5" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="62" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A62" s="4" t="s">
         <v>114</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C62" s="5" t="s">
         <v>132</v>
@@ -4992,27 +5899,36 @@
         <v>112</v>
       </c>
       <c r="E62" s="5" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="F62" s="5"/>
       <c r="G62" s="5" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H62" s="5"/>
       <c r="I62" s="5" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="J62" s="5" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="K62" s="5"/>
       <c r="L62" s="5"/>
       <c r="M62" s="5"/>
-      <c r="N62" s="5" t="s">
-        <v>471</v>
-      </c>
-    </row>
-    <row r="63" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N62" s="14" t="s">
+        <v>612</v>
+      </c>
+      <c r="O62" s="14" t="s">
+        <v>611</v>
+      </c>
+      <c r="P62" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="Q62" s="5" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="63" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A63" s="4" t="s">
         <v>114</v>
       </c>
@@ -5026,7 +5942,7 @@
         <v>4</v>
       </c>
       <c r="E63" s="5" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F63" s="5" t="s">
         <v>6</v>
@@ -5036,20 +5952,29 @@
       <c r="I63" s="5"/>
       <c r="J63" s="5"/>
       <c r="K63" s="5" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="L63" s="5"/>
       <c r="M63" s="5"/>
-      <c r="N63" s="5" t="s">
-        <v>472</v>
-      </c>
-    </row>
-    <row r="64" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N63" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="O63" s="14" t="s">
+        <v>612</v>
+      </c>
+      <c r="P63" s="14" t="s">
+        <v>612</v>
+      </c>
+      <c r="Q63" s="5" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="64" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A64" s="4" t="s">
         <v>114</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="C64" s="5" t="s">
         <v>134</v>
@@ -5058,25 +5983,34 @@
         <v>112</v>
       </c>
       <c r="E64" s="5" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="F64" s="5" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="G64" s="5"/>
       <c r="H64" s="5"/>
       <c r="I64" s="5"/>
       <c r="J64" s="5"/>
       <c r="K64" s="5" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="L64" s="5"/>
       <c r="M64" s="5"/>
-      <c r="N64" s="5" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="65" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N64" s="14" t="s">
+        <v>612</v>
+      </c>
+      <c r="O64" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="P64" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="Q64" s="5" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="65" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A65" s="4" t="s">
         <v>3</v>
       </c>
@@ -5090,30 +6024,39 @@
         <v>112</v>
       </c>
       <c r="E65" s="5" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="F65" s="5" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="G65" s="5"/>
       <c r="H65" s="5"/>
       <c r="I65" s="5"/>
       <c r="J65" s="5"/>
       <c r="K65" s="5" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="L65" s="5"/>
       <c r="M65" s="5"/>
-      <c r="N65" s="5" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="66" spans="1:14" ht="162" x14ac:dyDescent="0.3">
+      <c r="N65" s="14" t="s">
+        <v>611</v>
+      </c>
+      <c r="O65" s="14" t="s">
+        <v>611</v>
+      </c>
+      <c r="P65" s="14" t="s">
+        <v>611</v>
+      </c>
+      <c r="Q65" s="5" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="66" spans="1:17" ht="162" x14ac:dyDescent="0.3">
       <c r="A66" s="4" t="s">
         <v>3</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C66" s="5" t="s">
         <v>136</v>
@@ -5122,27 +6065,36 @@
         <v>112</v>
       </c>
       <c r="E66" s="5" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="F66" s="5" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="G66" s="5"/>
       <c r="H66" s="5"/>
       <c r="I66" s="5"/>
       <c r="J66" s="5"/>
       <c r="K66" s="5" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="L66" s="5"/>
-      <c r="M66" s="12" t="s">
-        <v>583</v>
-      </c>
-      <c r="N66" s="5" t="s">
-        <v>477</v>
-      </c>
-    </row>
-    <row r="67" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="M66" s="10" t="s">
+        <v>580</v>
+      </c>
+      <c r="N66" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="O66" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="P66" s="14" t="s">
+        <v>611</v>
+      </c>
+      <c r="Q66" s="5" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="67" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A67" s="4" t="s">
         <v>3</v>
       </c>
@@ -5156,7 +6108,7 @@
         <v>4</v>
       </c>
       <c r="E67" s="5" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F67" s="5" t="s">
         <v>6</v>
@@ -5166,20 +6118,29 @@
       <c r="I67" s="5"/>
       <c r="J67" s="5"/>
       <c r="K67" s="5" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="L67" s="5"/>
       <c r="M67" s="5"/>
-      <c r="N67" s="5" t="s">
-        <v>478</v>
-      </c>
-    </row>
-    <row r="68" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N67" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="O67" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="P67" s="14" t="s">
+        <v>611</v>
+      </c>
+      <c r="Q67" s="5" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="68" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A68" s="4" t="s">
         <v>3</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C68" s="5" t="s">
         <v>138</v>
@@ -5188,25 +6149,34 @@
         <v>112</v>
       </c>
       <c r="E68" s="5" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="F68" s="5" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="G68" s="5"/>
       <c r="H68" s="5"/>
       <c r="I68" s="5"/>
       <c r="J68" s="5"/>
       <c r="K68" s="5" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="L68" s="5"/>
       <c r="M68" s="5"/>
-      <c r="N68" s="5" t="s">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="69" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N68" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="O68" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="P68" s="14" t="s">
+        <v>611</v>
+      </c>
+      <c r="Q68" s="5" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="69" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A69" s="4" t="s">
         <v>3</v>
       </c>
@@ -5220,25 +6190,34 @@
         <v>112</v>
       </c>
       <c r="E69" s="5" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="F69" s="5" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="G69" s="5"/>
       <c r="H69" s="5"/>
       <c r="I69" s="5"/>
       <c r="J69" s="5"/>
       <c r="K69" s="5" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="L69" s="5"/>
       <c r="M69" s="5"/>
-      <c r="N69" s="5" t="s">
-        <v>484</v>
-      </c>
-    </row>
-    <row r="70" spans="1:14" ht="121.5" x14ac:dyDescent="0.3">
+      <c r="N69" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="O69" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="P69" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="Q69" s="5" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="70" spans="1:17" ht="121.5" x14ac:dyDescent="0.3">
       <c r="A70" s="4" t="s">
         <v>3</v>
       </c>
@@ -5252,27 +6231,36 @@
         <v>112</v>
       </c>
       <c r="E70" s="5" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="F70" s="5" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="G70" s="5"/>
       <c r="H70" s="5"/>
       <c r="I70" s="5"/>
       <c r="J70" s="5"/>
       <c r="K70" s="5" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="L70" s="5"/>
-      <c r="M70" s="12" t="s">
-        <v>584</v>
-      </c>
-      <c r="N70" s="5" t="s">
-        <v>476</v>
-      </c>
-    </row>
-    <row r="71" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="M70" s="10" t="s">
+        <v>581</v>
+      </c>
+      <c r="N70" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="O70" s="14" t="s">
+        <v>611</v>
+      </c>
+      <c r="P70" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="Q70" s="5" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="71" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A71" s="4" t="s">
         <v>3</v>
       </c>
@@ -5286,25 +6274,34 @@
         <v>112</v>
       </c>
       <c r="E71" s="5" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="F71" s="5" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="G71" s="5"/>
       <c r="H71" s="5"/>
       <c r="I71" s="5"/>
       <c r="J71" s="5"/>
       <c r="K71" s="5" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="L71" s="5"/>
       <c r="M71" s="5"/>
-      <c r="N71" s="5" t="s">
-        <v>485</v>
-      </c>
-    </row>
-    <row r="72" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N71" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="O71" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="P71" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="Q71" s="5" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="72" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="4" t="s">
         <v>3</v>
       </c>
@@ -5318,7 +6315,7 @@
         <v>4</v>
       </c>
       <c r="E72" s="5" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F72" s="5" t="s">
         <v>6</v>
@@ -5328,15 +6325,24 @@
       <c r="I72" s="5"/>
       <c r="J72" s="5"/>
       <c r="K72" s="5" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="L72" s="5"/>
       <c r="M72" s="5"/>
-      <c r="N72" s="5" t="s">
-        <v>482</v>
-      </c>
-    </row>
-    <row r="73" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N72" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="O72" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="P72" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="Q72" s="5" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="73" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A73" s="4" t="s">
         <v>3</v>
       </c>
@@ -5350,25 +6356,34 @@
         <v>112</v>
       </c>
       <c r="E73" s="5" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="F73" s="5" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="G73" s="5"/>
       <c r="H73" s="5"/>
       <c r="I73" s="5"/>
       <c r="J73" s="5"/>
       <c r="K73" s="5" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="L73" s="5"/>
       <c r="M73" s="5"/>
-      <c r="N73" s="5" t="s">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="74" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N73" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="O73" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="P73" s="14" t="s">
+        <v>611</v>
+      </c>
+      <c r="Q73" s="5" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="74" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A74" s="4" t="s">
         <v>3</v>
       </c>
@@ -5382,25 +6397,34 @@
         <v>112</v>
       </c>
       <c r="E74" s="5" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="F74" s="5" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="G74" s="5"/>
       <c r="H74" s="5"/>
       <c r="I74" s="5"/>
       <c r="J74" s="5"/>
       <c r="K74" s="5" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="L74" s="5"/>
       <c r="M74" s="5"/>
-      <c r="N74" s="5" t="s">
-        <v>481</v>
-      </c>
-    </row>
-    <row r="75" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N74" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="O74" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="P74" s="14" t="s">
+        <v>611</v>
+      </c>
+      <c r="Q74" s="5" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="75" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A75" s="4" t="s">
         <v>3</v>
       </c>
@@ -5414,30 +6438,39 @@
         <v>4</v>
       </c>
       <c r="E75" s="5" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F75" s="5" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="G75" s="5"/>
       <c r="H75" s="5"/>
       <c r="I75" s="5"/>
       <c r="J75" s="5"/>
       <c r="K75" s="5" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="L75" s="5"/>
       <c r="M75" s="5"/>
-      <c r="N75" s="5" t="s">
-        <v>483</v>
-      </c>
-    </row>
-    <row r="76" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N75" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="O75" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="P75" s="14" t="s">
+        <v>611</v>
+      </c>
+      <c r="Q75" s="5" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="76" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A76" s="4" t="s">
         <v>3</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C76" s="5" t="s">
         <v>146</v>
@@ -5446,25 +6479,34 @@
         <v>112</v>
       </c>
       <c r="E76" s="5" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="F76" s="5" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="G76" s="5"/>
       <c r="H76" s="5"/>
       <c r="I76" s="5"/>
       <c r="J76" s="5"/>
       <c r="K76" s="5" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="L76" s="5"/>
       <c r="M76" s="5"/>
-      <c r="N76" s="5" t="s">
-        <v>484</v>
-      </c>
-    </row>
-    <row r="77" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N76" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="O76" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="P76" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="Q76" s="5" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="77" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A77" s="4" t="s">
         <v>3</v>
       </c>
@@ -5478,7 +6520,7 @@
         <v>4</v>
       </c>
       <c r="E77" s="5" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F77" s="5" t="s">
         <v>6</v>
@@ -5488,15 +6530,24 @@
       <c r="I77" s="5"/>
       <c r="J77" s="5"/>
       <c r="K77" s="5" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="L77" s="5"/>
       <c r="M77" s="5"/>
-      <c r="N77" s="5" t="s">
-        <v>486</v>
-      </c>
-    </row>
-    <row r="78" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N77" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="O77" s="14" t="s">
+        <v>611</v>
+      </c>
+      <c r="P77" s="14" t="s">
+        <v>612</v>
+      </c>
+      <c r="Q77" s="5" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="78" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A78" s="4" t="s">
         <v>3</v>
       </c>
@@ -5510,7 +6561,7 @@
         <v>4</v>
       </c>
       <c r="E78" s="5" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F78" s="5" t="s">
         <v>6</v>
@@ -5520,20 +6571,29 @@
       <c r="I78" s="5"/>
       <c r="J78" s="5"/>
       <c r="K78" s="5" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="L78" s="5"/>
       <c r="M78" s="5"/>
-      <c r="N78" s="5" t="s">
-        <v>474</v>
-      </c>
-    </row>
-    <row r="79" spans="1:14" ht="94.5" x14ac:dyDescent="0.3">
+      <c r="N78" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="O78" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="P78" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="Q78" s="5" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="79" spans="1:17" ht="94.5" x14ac:dyDescent="0.3">
       <c r="A79" s="4" t="s">
         <v>101</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C79" s="5" t="s">
         <v>149</v>
@@ -5542,32 +6602,41 @@
         <v>112</v>
       </c>
       <c r="E79" s="5" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="F79" s="5" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="G79" s="5"/>
       <c r="H79" s="5"/>
       <c r="I79" s="5"/>
       <c r="J79" s="5"/>
       <c r="K79" s="5" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="L79" s="5"/>
-      <c r="M79" s="12" t="s">
-        <v>590</v>
-      </c>
-      <c r="N79" s="5" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="80" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="M79" s="10" t="s">
+        <v>587</v>
+      </c>
+      <c r="N79" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="O79" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="P79" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="Q79" s="5" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="80" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A80" s="4" t="s">
         <v>101</v>
       </c>
       <c r="B80" s="5" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C80" s="5" t="s">
         <v>150</v>
@@ -5576,7 +6645,7 @@
         <v>4</v>
       </c>
       <c r="E80" s="5" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F80" s="5" t="s">
         <v>6</v>
@@ -5586,15 +6655,24 @@
       <c r="I80" s="5"/>
       <c r="J80" s="5"/>
       <c r="K80" s="5" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="L80" s="5"/>
       <c r="M80" s="5"/>
-      <c r="N80" s="5" t="s">
-        <v>501</v>
-      </c>
-    </row>
-    <row r="81" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N80" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="O80" s="14" t="s">
+        <v>611</v>
+      </c>
+      <c r="P80" s="14" t="s">
+        <v>611</v>
+      </c>
+      <c r="Q80" s="5" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="81" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A81" s="4" t="s">
         <v>101</v>
       </c>
@@ -5608,7 +6686,7 @@
         <v>4</v>
       </c>
       <c r="E81" s="5" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F81" s="5" t="s">
         <v>6</v>
@@ -5618,15 +6696,24 @@
       <c r="I81" s="5"/>
       <c r="J81" s="5"/>
       <c r="K81" s="5" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="L81" s="5"/>
       <c r="M81" s="5"/>
-      <c r="N81" s="5" t="s">
-        <v>495</v>
-      </c>
-    </row>
-    <row r="82" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N81" s="14" t="s">
+        <v>611</v>
+      </c>
+      <c r="O81" s="14" t="s">
+        <v>612</v>
+      </c>
+      <c r="P81" s="14" t="s">
+        <v>611</v>
+      </c>
+      <c r="Q81" s="5" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="82" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A82" s="4" t="s">
         <v>101</v>
       </c>
@@ -5640,7 +6727,7 @@
         <v>4</v>
       </c>
       <c r="E82" s="5" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F82" s="5" t="s">
         <v>6</v>
@@ -5650,15 +6737,24 @@
       <c r="I82" s="5"/>
       <c r="J82" s="5"/>
       <c r="K82" s="5" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="L82" s="5"/>
       <c r="M82" s="5"/>
-      <c r="N82" s="5" t="s">
-        <v>496</v>
-      </c>
-    </row>
-    <row r="83" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N82" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="O82" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="P82" s="14" t="s">
+        <v>611</v>
+      </c>
+      <c r="Q82" s="5" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="83" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A83" s="4" t="s">
         <v>101</v>
       </c>
@@ -5672,25 +6768,34 @@
         <v>112</v>
       </c>
       <c r="E83" s="5" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="F83" s="5" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="G83" s="5"/>
       <c r="H83" s="5"/>
       <c r="I83" s="5"/>
       <c r="J83" s="5"/>
       <c r="K83" s="5" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="L83" s="5"/>
       <c r="M83" s="5"/>
-      <c r="N83" s="5" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="84" spans="1:14" ht="40.5" x14ac:dyDescent="0.3">
+      <c r="N83" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="O83" s="14" t="s">
+        <v>611</v>
+      </c>
+      <c r="P83" s="14" t="s">
+        <v>611</v>
+      </c>
+      <c r="Q83" s="5" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="84" spans="1:17" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A84" s="4" t="s">
         <v>101</v>
       </c>
@@ -5704,32 +6809,41 @@
         <v>112</v>
       </c>
       <c r="E84" s="5" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="F84" s="5" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="G84" s="5"/>
       <c r="H84" s="5"/>
       <c r="I84" s="5"/>
       <c r="J84" s="5"/>
       <c r="K84" s="5" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="L84" s="5"/>
-      <c r="M84" s="12" t="s">
-        <v>589</v>
-      </c>
-      <c r="N84" s="5" t="s">
-        <v>502</v>
-      </c>
-    </row>
-    <row r="85" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="M84" s="10" t="s">
+        <v>586</v>
+      </c>
+      <c r="N84" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="O84" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="P84" s="14" t="s">
+        <v>611</v>
+      </c>
+      <c r="Q84" s="5" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="85" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A85" s="4" t="s">
         <v>101</v>
       </c>
       <c r="B85" s="5" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C85" s="5" t="s">
         <v>155</v>
@@ -5738,30 +6852,39 @@
         <v>112</v>
       </c>
       <c r="E85" s="5" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="F85" s="5" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="G85" s="5"/>
       <c r="H85" s="5"/>
       <c r="I85" s="5"/>
       <c r="J85" s="5"/>
       <c r="K85" s="5" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="L85" s="5"/>
       <c r="M85" s="5"/>
-      <c r="N85" s="5" t="s">
-        <v>489</v>
-      </c>
-    </row>
-    <row r="86" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N85" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="O85" s="14" t="s">
+        <v>612</v>
+      </c>
+      <c r="P85" s="14" t="s">
+        <v>611</v>
+      </c>
+      <c r="Q85" s="5" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="86" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A86" s="4" t="s">
         <v>101</v>
       </c>
       <c r="B86" s="5" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C86" s="5" t="s">
         <v>156</v>
@@ -5770,7 +6893,7 @@
         <v>4</v>
       </c>
       <c r="E86" s="5" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F86" s="5" t="s">
         <v>6</v>
@@ -5780,20 +6903,29 @@
       <c r="I86" s="5"/>
       <c r="J86" s="5"/>
       <c r="K86" s="5" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="L86" s="5"/>
       <c r="M86" s="5"/>
-      <c r="N86" s="5" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="87" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N86" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="O86" s="14" t="s">
+        <v>611</v>
+      </c>
+      <c r="P86" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="Q86" s="5" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="87" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A87" s="4" t="s">
         <v>101</v>
       </c>
       <c r="B87" s="5" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C87" s="5" t="s">
         <v>157</v>
@@ -5802,7 +6934,7 @@
         <v>112</v>
       </c>
       <c r="E87" s="5" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="F87" s="5" t="s">
         <v>10</v>
@@ -5812,20 +6944,29 @@
       <c r="I87" s="5"/>
       <c r="J87" s="5"/>
       <c r="K87" s="5" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="L87" s="5"/>
       <c r="M87" s="5"/>
-      <c r="N87" s="5" t="s">
-        <v>491</v>
-      </c>
-    </row>
-    <row r="88" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N87" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="O87" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="P87" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="Q87" s="5" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="88" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A88" s="4" t="s">
         <v>101</v>
       </c>
       <c r="B88" s="5" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C88" s="5" t="s">
         <v>158</v>
@@ -5834,30 +6975,39 @@
         <v>112</v>
       </c>
       <c r="E88" s="5" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="F88" s="5" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="G88" s="5"/>
       <c r="H88" s="5"/>
       <c r="I88" s="5"/>
       <c r="J88" s="5"/>
       <c r="K88" s="5" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="L88" s="5"/>
       <c r="M88" s="5"/>
-      <c r="N88" s="5" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="89" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N88" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="O88" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="P88" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="Q88" s="5" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="89" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A89" s="4" t="s">
         <v>101</v>
       </c>
       <c r="B89" s="5" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C89" s="5" t="s">
         <v>159</v>
@@ -5866,7 +7016,7 @@
         <v>4</v>
       </c>
       <c r="E89" s="5" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F89" s="5" t="s">
         <v>6</v>
@@ -5876,20 +7026,29 @@
       <c r="I89" s="5"/>
       <c r="J89" s="5"/>
       <c r="K89" s="5" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="L89" s="5"/>
       <c r="M89" s="5"/>
-      <c r="N89" s="5" t="s">
-        <v>490</v>
-      </c>
-    </row>
-    <row r="90" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N89" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="O89" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="P89" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="Q89" s="5" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="90" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A90" s="4" t="s">
         <v>101</v>
       </c>
       <c r="B90" s="5" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C90" s="5" t="s">
         <v>160</v>
@@ -5898,7 +7057,7 @@
         <v>4</v>
       </c>
       <c r="E90" s="5" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F90" s="5" t="s">
         <v>6</v>
@@ -5908,20 +7067,29 @@
       <c r="I90" s="5"/>
       <c r="J90" s="5"/>
       <c r="K90" s="5" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="L90" s="5"/>
       <c r="M90" s="5"/>
-      <c r="N90" s="5" t="s">
-        <v>499</v>
-      </c>
-    </row>
-    <row r="91" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N90" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="O90" s="14" t="s">
+        <v>611</v>
+      </c>
+      <c r="P90" s="14" t="s">
+        <v>611</v>
+      </c>
+      <c r="Q90" s="5" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="91" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A91" s="4" t="s">
         <v>101</v>
       </c>
       <c r="B91" s="5" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C91" s="5" t="s">
         <v>161</v>
@@ -5930,7 +7098,7 @@
         <v>4</v>
       </c>
       <c r="E91" s="5" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F91" s="5" t="s">
         <v>6</v>
@@ -5940,20 +7108,29 @@
       <c r="I91" s="5"/>
       <c r="J91" s="5"/>
       <c r="K91" s="5" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="L91" s="5"/>
       <c r="M91" s="5"/>
-      <c r="N91" s="5" t="s">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="92" spans="1:14" ht="40.5" x14ac:dyDescent="0.3">
+      <c r="N91" s="14" t="s">
+        <v>611</v>
+      </c>
+      <c r="O91" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="P91" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="Q91" s="5" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="92" spans="1:17" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A92" s="4" t="s">
         <v>101</v>
       </c>
       <c r="B92" s="5" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C92" s="5" t="s">
         <v>162</v>
@@ -5962,32 +7139,41 @@
         <v>112</v>
       </c>
       <c r="E92" s="5" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="F92" s="5" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="G92" s="5"/>
       <c r="H92" s="5"/>
       <c r="I92" s="5"/>
       <c r="J92" s="5"/>
       <c r="K92" s="5" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="L92" s="5"/>
-      <c r="M92" s="12" t="s">
-        <v>588</v>
-      </c>
-      <c r="N92" s="5" t="s">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="93" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="M92" s="10" t="s">
+        <v>585</v>
+      </c>
+      <c r="N92" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="O92" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="P92" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="Q92" s="5" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="93" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A93" s="4" t="s">
         <v>101</v>
       </c>
       <c r="B93" s="5" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="C93" s="5" t="s">
         <v>163</v>
@@ -5996,38 +7182,47 @@
         <v>112</v>
       </c>
       <c r="E93" s="5" t="s">
-        <v>316</v>
-      </c>
-      <c r="F93" s="2" t="s">
-        <v>361</v>
-      </c>
-      <c r="G93" s="2" t="s">
-        <v>327</v>
-      </c>
-      <c r="H93" s="2" t="s">
-        <v>407</v>
-      </c>
-      <c r="I93" s="2" t="s">
-        <v>361</v>
-      </c>
-      <c r="J93" s="2" t="s">
-        <v>361</v>
-      </c>
-      <c r="K93" s="2" t="s">
-        <v>370</v>
+        <v>315</v>
+      </c>
+      <c r="F93" s="6" t="s">
+        <v>358</v>
+      </c>
+      <c r="G93" s="6" t="s">
+        <v>326</v>
+      </c>
+      <c r="H93" s="6" t="s">
+        <v>404</v>
+      </c>
+      <c r="I93" s="6" t="s">
+        <v>358</v>
+      </c>
+      <c r="J93" s="6" t="s">
+        <v>358</v>
+      </c>
+      <c r="K93" s="6" t="s">
+        <v>367</v>
       </c>
       <c r="L93" s="2"/>
       <c r="M93" s="2"/>
-      <c r="N93" s="2" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="94" spans="1:14" ht="175.5" x14ac:dyDescent="0.3">
+      <c r="N93" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="O93" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="P93" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="Q93" s="6" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="94" spans="1:17" ht="175.5" x14ac:dyDescent="0.3">
       <c r="A94" s="4" t="s">
         <v>101</v>
       </c>
       <c r="B94" s="5" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C94" s="5" t="s">
         <v>164</v>
@@ -6036,32 +7231,41 @@
         <v>112</v>
       </c>
       <c r="E94" s="5" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="F94" s="5" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="G94" s="5"/>
       <c r="H94" s="5"/>
       <c r="I94" s="5"/>
       <c r="J94" s="5"/>
       <c r="K94" s="5" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="L94" s="5"/>
-      <c r="M94" s="12" t="s">
-        <v>587</v>
-      </c>
-      <c r="N94" s="5" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="95" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="M94" s="10" t="s">
+        <v>584</v>
+      </c>
+      <c r="N94" s="14" t="s">
+        <v>611</v>
+      </c>
+      <c r="O94" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="P94" s="14" t="s">
+        <v>611</v>
+      </c>
+      <c r="Q94" s="5" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="95" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A95" s="4" t="s">
         <v>101</v>
       </c>
       <c r="B95" s="5" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C95" s="5" t="s">
         <v>165</v>
@@ -6070,30 +7274,39 @@
         <v>112</v>
       </c>
       <c r="E95" s="5" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="F95" s="5" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="G95" s="5"/>
       <c r="H95" s="5"/>
       <c r="I95" s="5"/>
       <c r="J95" s="5"/>
       <c r="K95" s="5" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="L95" s="5"/>
       <c r="M95" s="5"/>
-      <c r="N95" s="5" t="s">
-        <v>488</v>
-      </c>
-    </row>
-    <row r="96" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N95" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="O95" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="P95" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="Q95" s="5" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="96" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A96" s="4" t="s">
         <v>101</v>
       </c>
       <c r="B96" s="5" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C96" s="5" t="s">
         <v>166</v>
@@ -6102,30 +7315,39 @@
         <v>112</v>
       </c>
       <c r="E96" s="5" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="F96" s="5" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="G96" s="5"/>
       <c r="H96" s="5"/>
       <c r="I96" s="5"/>
       <c r="J96" s="5"/>
       <c r="K96" s="5" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="L96" s="5"/>
       <c r="M96" s="5"/>
-      <c r="N96" s="5" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="97" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N96" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="O96" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="P96" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="Q96" s="5" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="97" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A97" s="4" t="s">
         <v>115</v>
       </c>
       <c r="B97" s="5" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C97" s="5" t="s">
         <v>167</v>
@@ -6134,7 +7356,7 @@
         <v>4</v>
       </c>
       <c r="E97" s="5" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F97" s="5" t="s">
         <v>6</v>
@@ -6144,15 +7366,24 @@
       <c r="I97" s="5"/>
       <c r="J97" s="5"/>
       <c r="K97" s="5" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="L97" s="5"/>
       <c r="M97" s="5"/>
-      <c r="N97" s="5" t="s">
-        <v>504</v>
-      </c>
-    </row>
-    <row r="98" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N97" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="O97" s="14" t="s">
+        <v>611</v>
+      </c>
+      <c r="P97" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="Q97" s="5" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="98" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A98" s="4" t="s">
         <v>115</v>
       </c>
@@ -6166,30 +7397,39 @@
         <v>112</v>
       </c>
       <c r="E98" s="5" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="F98" s="5" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="G98" s="5"/>
       <c r="H98" s="5"/>
       <c r="I98" s="5"/>
       <c r="J98" s="5"/>
       <c r="K98" s="5" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="L98" s="5"/>
       <c r="M98" s="5"/>
-      <c r="N98" s="5" t="s">
-        <v>505</v>
-      </c>
-    </row>
-    <row r="99" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N98" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="O98" s="14" t="s">
+        <v>611</v>
+      </c>
+      <c r="P98" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="Q98" s="5" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="99" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A99" s="4" t="s">
         <v>115</v>
       </c>
       <c r="B99" s="5" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C99" s="5" t="s">
         <v>169</v>
@@ -6198,30 +7438,39 @@
         <v>4</v>
       </c>
       <c r="E99" s="5" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F99" s="5" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="G99" s="5"/>
       <c r="H99" s="5"/>
       <c r="I99" s="5"/>
       <c r="J99" s="5"/>
       <c r="K99" s="5" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="L99" s="5"/>
       <c r="M99" s="5"/>
-      <c r="N99" s="5" t="s">
-        <v>509</v>
-      </c>
-    </row>
-    <row r="100" spans="1:14" ht="94.5" x14ac:dyDescent="0.3">
+      <c r="N99" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="O99" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="P99" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="Q99" s="5" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="100" spans="1:17" ht="94.5" x14ac:dyDescent="0.3">
       <c r="A100" s="4" t="s">
         <v>115</v>
       </c>
       <c r="B100" s="5" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C100" s="5" t="s">
         <v>170</v>
@@ -6230,27 +7479,36 @@
         <v>112</v>
       </c>
       <c r="E100" s="5" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="F100" s="5" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="G100" s="5"/>
       <c r="H100" s="5"/>
       <c r="I100" s="5"/>
       <c r="J100" s="5"/>
       <c r="K100" s="5" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="L100" s="5"/>
-      <c r="M100" s="12" t="s">
-        <v>591</v>
-      </c>
-      <c r="N100" s="5" t="s">
-        <v>507</v>
-      </c>
-    </row>
-    <row r="101" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="M100" s="10" t="s">
+        <v>588</v>
+      </c>
+      <c r="N100" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="O100" s="14" t="s">
+        <v>611</v>
+      </c>
+      <c r="P100" s="14" t="s">
+        <v>611</v>
+      </c>
+      <c r="Q100" s="5" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="101" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A101" s="4" t="s">
         <v>115</v>
       </c>
@@ -6264,25 +7522,34 @@
         <v>112</v>
       </c>
       <c r="E101" s="5" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="F101" s="5" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="G101" s="5"/>
       <c r="H101" s="5"/>
       <c r="I101" s="5"/>
       <c r="J101" s="5"/>
       <c r="K101" s="5" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="L101" s="5"/>
       <c r="M101" s="5"/>
-      <c r="N101" s="5" t="s">
-        <v>508</v>
-      </c>
-    </row>
-    <row r="102" spans="1:14" ht="95.25" x14ac:dyDescent="0.3">
+      <c r="N101" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="O101" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="P101" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="Q101" s="5" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="102" spans="1:17" ht="95.25" x14ac:dyDescent="0.3">
       <c r="A102" s="4" t="s">
         <v>115</v>
       </c>
@@ -6296,36 +7563,45 @@
         <v>112</v>
       </c>
       <c r="E102" s="5" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="F102" s="5"/>
-      <c r="G102" s="2" t="s">
-        <v>323</v>
-      </c>
-      <c r="H102" s="2"/>
-      <c r="I102" s="2" t="s">
-        <v>361</v>
-      </c>
-      <c r="J102" s="2" t="s">
-        <v>408</v>
-      </c>
-      <c r="K102" s="2" t="s">
-        <v>370</v>
+      <c r="G102" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="H102" s="6"/>
+      <c r="I102" s="6" t="s">
+        <v>358</v>
+      </c>
+      <c r="J102" s="6" t="s">
+        <v>405</v>
+      </c>
+      <c r="K102" s="6" t="s">
+        <v>367</v>
       </c>
       <c r="L102" s="2"/>
-      <c r="M102" s="14" t="s">
-        <v>593</v>
-      </c>
-      <c r="N102" s="2" t="s">
-        <v>512</v>
-      </c>
-    </row>
-    <row r="103" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="M102" s="12" t="s">
+        <v>590</v>
+      </c>
+      <c r="N102" s="14" t="s">
+        <v>611</v>
+      </c>
+      <c r="O102" s="14" t="s">
+        <v>611</v>
+      </c>
+      <c r="P102" s="14" t="s">
+        <v>611</v>
+      </c>
+      <c r="Q102" s="6" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="103" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A103" s="4" t="s">
         <v>115</v>
       </c>
       <c r="B103" s="5" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C103" s="5" t="s">
         <v>173</v>
@@ -6334,7 +7610,7 @@
         <v>4</v>
       </c>
       <c r="E103" s="5" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F103" s="5" t="s">
         <v>6</v>
@@ -6344,20 +7620,29 @@
       <c r="I103" s="5"/>
       <c r="J103" s="5"/>
       <c r="K103" s="5" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="L103" s="5"/>
       <c r="M103" s="5"/>
-      <c r="N103" s="5" t="s">
-        <v>506</v>
-      </c>
-    </row>
-    <row r="104" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N103" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="O103" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="P103" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="Q103" s="5" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="104" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A104" s="4" t="s">
         <v>115</v>
       </c>
       <c r="B104" s="5" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C104" s="5" t="s">
         <v>174</v>
@@ -6366,30 +7651,39 @@
         <v>112</v>
       </c>
       <c r="E104" s="5" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="F104" s="5" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="G104" s="5"/>
       <c r="H104" s="5"/>
       <c r="I104" s="5"/>
       <c r="J104" s="5"/>
       <c r="K104" s="5" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="L104" s="5"/>
       <c r="M104" s="5"/>
-      <c r="N104" s="5" t="s">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="105" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N104" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="O104" s="14" t="s">
+        <v>611</v>
+      </c>
+      <c r="P104" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="Q104" s="5" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="105" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A105" s="4" t="s">
         <v>115</v>
       </c>
       <c r="B105" s="5" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C105" s="5" t="s">
         <v>175</v>
@@ -6398,7 +7692,7 @@
         <v>4</v>
       </c>
       <c r="E105" s="5" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F105" s="5" t="s">
         <v>6</v>
@@ -6408,20 +7702,29 @@
       <c r="I105" s="5"/>
       <c r="J105" s="5"/>
       <c r="K105" s="5" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="L105" s="5"/>
       <c r="M105" s="5"/>
-      <c r="N105" s="5" t="s">
-        <v>510</v>
-      </c>
-    </row>
-    <row r="106" spans="1:14" ht="81" x14ac:dyDescent="0.3">
+      <c r="N105" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="O105" s="14" t="s">
+        <v>611</v>
+      </c>
+      <c r="P105" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="Q105" s="5" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="106" spans="1:17" ht="81" x14ac:dyDescent="0.3">
       <c r="A106" s="4" t="s">
         <v>115</v>
       </c>
       <c r="B106" s="5" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C106" s="5" t="s">
         <v>176</v>
@@ -6430,32 +7733,41 @@
         <v>112</v>
       </c>
       <c r="E106" s="5" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="F106" s="5" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="G106" s="5"/>
       <c r="H106" s="5"/>
       <c r="I106" s="5"/>
       <c r="J106" s="5"/>
       <c r="K106" s="5" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="L106" s="5"/>
-      <c r="M106" s="12" t="s">
-        <v>592</v>
-      </c>
-      <c r="N106" s="5" t="s">
-        <v>508</v>
-      </c>
-    </row>
-    <row r="107" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="M106" s="10" t="s">
+        <v>589</v>
+      </c>
+      <c r="N106" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="O106" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="P106" s="14" t="s">
+        <v>611</v>
+      </c>
+      <c r="Q106" s="5" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="107" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A107" s="4" t="s">
         <v>115</v>
       </c>
       <c r="B107" s="5" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="C107" s="5" t="s">
         <v>177</v>
@@ -6464,38 +7776,47 @@
         <v>4</v>
       </c>
       <c r="E107" s="5" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F107" s="5" t="s">
         <v>6</v>
       </c>
       <c r="G107" s="5" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="H107" s="5" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="I107" s="5" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="J107" s="5" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="K107" s="5" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="L107" s="5"/>
       <c r="M107" s="5"/>
-      <c r="N107" s="5" t="s">
-        <v>515</v>
-      </c>
-    </row>
-    <row r="108" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N107" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="O107" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="P107" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="Q107" s="5" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="108" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A108" s="4" t="s">
         <v>115</v>
       </c>
       <c r="B108" s="5" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C108" s="5" t="s">
         <v>178</v>
@@ -6504,7 +7825,7 @@
         <v>4</v>
       </c>
       <c r="E108" s="5" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F108" s="5" t="s">
         <v>6</v>
@@ -6514,20 +7835,29 @@
       <c r="I108" s="5"/>
       <c r="J108" s="5"/>
       <c r="K108" s="5" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="L108" s="5"/>
       <c r="M108" s="5"/>
-      <c r="N108" s="5" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="109" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N108" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="O108" s="14" t="s">
+        <v>612</v>
+      </c>
+      <c r="P108" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="Q108" s="5" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="109" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A109" s="4" t="s">
         <v>115</v>
       </c>
       <c r="B109" s="5" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C109" s="5" t="s">
         <v>179</v>
@@ -6536,32 +7866,41 @@
         <v>112</v>
       </c>
       <c r="E109" s="5" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="F109" s="5"/>
-      <c r="G109" s="2" t="s">
-        <v>323</v>
-      </c>
-      <c r="H109" s="2"/>
-      <c r="I109" s="2" t="s">
-        <v>361</v>
-      </c>
-      <c r="J109" s="2" t="s">
-        <v>408</v>
-      </c>
-      <c r="K109" s="2"/>
+      <c r="G109" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="H109" s="6"/>
+      <c r="I109" s="6" t="s">
+        <v>358</v>
+      </c>
+      <c r="J109" s="6" t="s">
+        <v>405</v>
+      </c>
+      <c r="K109" s="6"/>
       <c r="L109" s="2"/>
       <c r="M109" s="2"/>
-      <c r="N109" s="2" t="s">
-        <v>509</v>
-      </c>
-    </row>
-    <row r="110" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N109" s="14" t="s">
+        <v>611</v>
+      </c>
+      <c r="O109" s="14" t="s">
+        <v>611</v>
+      </c>
+      <c r="P109" s="14" t="s">
+        <v>611</v>
+      </c>
+      <c r="Q109" s="6" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="110" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A110" s="4" t="s">
         <v>115</v>
       </c>
       <c r="B110" s="5" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C110" s="5" t="s">
         <v>180</v>
@@ -6570,30 +7909,39 @@
         <v>112</v>
       </c>
       <c r="E110" s="5" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="F110" s="5" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="G110" s="5"/>
       <c r="H110" s="5"/>
       <c r="I110" s="5"/>
       <c r="J110" s="5"/>
       <c r="K110" s="5" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="L110" s="5"/>
       <c r="M110" s="5"/>
-      <c r="N110" s="5" t="s">
-        <v>511</v>
-      </c>
-    </row>
-    <row r="111" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N110" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="O110" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="P110" s="14" t="s">
+        <v>611</v>
+      </c>
+      <c r="Q110" s="5" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="111" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A111" s="4" t="s">
         <v>102</v>
       </c>
       <c r="B111" s="5" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C111" s="5" t="s">
         <v>181</v>
@@ -6602,7 +7950,7 @@
         <v>4</v>
       </c>
       <c r="E111" s="5" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F111" s="5" t="s">
         <v>6</v>
@@ -6612,15 +7960,24 @@
       <c r="I111" s="5"/>
       <c r="J111" s="5"/>
       <c r="K111" s="5" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="L111" s="5"/>
       <c r="M111" s="5"/>
-      <c r="N111" s="5" t="s">
-        <v>516</v>
-      </c>
-    </row>
-    <row r="112" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N111" s="14" t="s">
+        <v>611</v>
+      </c>
+      <c r="O111" s="14" t="s">
+        <v>611</v>
+      </c>
+      <c r="P111" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="Q111" s="5" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="112" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A112" s="4" t="s">
         <v>102</v>
       </c>
@@ -6634,30 +7991,39 @@
         <v>112</v>
       </c>
       <c r="E112" s="5" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="F112" s="5" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="G112" s="5"/>
       <c r="H112" s="5"/>
       <c r="I112" s="5"/>
       <c r="J112" s="5"/>
       <c r="K112" s="5" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="L112" s="5"/>
       <c r="M112" s="5"/>
-      <c r="N112" s="5" t="s">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="113" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N112" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="O112" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="P112" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="Q112" s="5" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="113" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A113" s="4" t="s">
         <v>102</v>
       </c>
       <c r="B113" s="5" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C113" s="5" t="s">
         <v>183</v>
@@ -6666,30 +8032,39 @@
         <v>4</v>
       </c>
       <c r="E113" s="5" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F113" s="5" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="G113" s="5"/>
       <c r="H113" s="5"/>
       <c r="I113" s="5"/>
       <c r="J113" s="5"/>
       <c r="K113" s="5" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="L113" s="5"/>
       <c r="M113" s="5"/>
-      <c r="N113" s="5" t="s">
-        <v>516</v>
-      </c>
-    </row>
-    <row r="114" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N113" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="O113" s="14" t="s">
+        <v>611</v>
+      </c>
+      <c r="P113" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="Q113" s="5" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="114" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A114" s="4" t="s">
         <v>102</v>
       </c>
       <c r="B114" s="5" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C114" s="5" t="s">
         <v>184</v>
@@ -6698,30 +8073,39 @@
         <v>4</v>
       </c>
       <c r="E114" s="5" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F114" s="5" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="G114" s="5"/>
       <c r="H114" s="5"/>
       <c r="I114" s="5"/>
       <c r="J114" s="5"/>
       <c r="K114" s="5" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="L114" s="5"/>
       <c r="M114" s="5"/>
-      <c r="N114" s="5" t="s">
-        <v>521</v>
-      </c>
-    </row>
-    <row r="115" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N114" s="14" t="s">
+        <v>609</v>
+      </c>
+      <c r="O114" s="14" t="s">
+        <v>609</v>
+      </c>
+      <c r="P114" s="14" t="s">
+        <v>609</v>
+      </c>
+      <c r="Q114" s="5" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="115" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A115" s="4" t="s">
         <v>102</v>
       </c>
       <c r="B115" s="5" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C115" s="5" t="s">
         <v>185</v>
@@ -6730,30 +8114,39 @@
         <v>4</v>
       </c>
       <c r="E115" s="5" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F115" s="5" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="G115" s="5"/>
       <c r="H115" s="5"/>
       <c r="I115" s="5"/>
       <c r="J115" s="5"/>
       <c r="K115" s="5" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="L115" s="5"/>
       <c r="M115" s="5"/>
-      <c r="N115" s="5" t="s">
-        <v>520</v>
-      </c>
-    </row>
-    <row r="116" spans="1:14" ht="94.5" x14ac:dyDescent="0.3">
+      <c r="N115" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="O115" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="P115" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="Q115" s="5" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="116" spans="1:17" ht="94.5" x14ac:dyDescent="0.3">
       <c r="A116" s="4" t="s">
         <v>102</v>
       </c>
       <c r="B116" s="5" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C116" s="5" t="s">
         <v>186</v>
@@ -6762,32 +8155,41 @@
         <v>4</v>
       </c>
       <c r="E116" s="5" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F116" s="5" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="G116" s="5"/>
       <c r="H116" s="5"/>
       <c r="I116" s="5"/>
       <c r="J116" s="5"/>
       <c r="K116" s="5" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="L116" s="5"/>
-      <c r="M116" s="12" t="s">
-        <v>597</v>
-      </c>
-      <c r="N116" s="5" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="117" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="M116" s="10" t="s">
+        <v>594</v>
+      </c>
+      <c r="N116" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="O116" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="P116" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="Q116" s="5" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="117" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A117" s="4" t="s">
         <v>102</v>
       </c>
       <c r="B117" s="5" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C117" s="5" t="s">
         <v>187</v>
@@ -6796,7 +8198,7 @@
         <v>4</v>
       </c>
       <c r="E117" s="5" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F117" s="5" t="s">
         <v>6</v>
@@ -6806,15 +8208,24 @@
       <c r="I117" s="5"/>
       <c r="J117" s="5"/>
       <c r="K117" s="5" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="L117" s="5"/>
       <c r="M117" s="5"/>
-      <c r="N117" s="5" t="s">
-        <v>517</v>
-      </c>
-    </row>
-    <row r="118" spans="1:14" ht="94.5" x14ac:dyDescent="0.3">
+      <c r="N117" s="14" t="s">
+        <v>611</v>
+      </c>
+      <c r="O117" s="14" t="s">
+        <v>611</v>
+      </c>
+      <c r="P117" s="14" t="s">
+        <v>611</v>
+      </c>
+      <c r="Q117" s="5" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="118" spans="1:17" ht="94.5" x14ac:dyDescent="0.3">
       <c r="A118" s="4" t="s">
         <v>102</v>
       </c>
@@ -6828,32 +8239,41 @@
         <v>112</v>
       </c>
       <c r="E118" s="5" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="F118" s="5" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="G118" s="5"/>
       <c r="H118" s="5"/>
       <c r="I118" s="5"/>
       <c r="J118" s="5"/>
       <c r="K118" s="5" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="L118" s="5"/>
-      <c r="M118" s="12" t="s">
-        <v>595</v>
-      </c>
-      <c r="N118" s="5" t="s">
-        <v>518</v>
-      </c>
-    </row>
-    <row r="119" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="M118" s="10" t="s">
+        <v>592</v>
+      </c>
+      <c r="N118" s="14" t="s">
+        <v>609</v>
+      </c>
+      <c r="O118" s="14" t="s">
+        <v>609</v>
+      </c>
+      <c r="P118" s="13" t="s">
+        <v>611</v>
+      </c>
+      <c r="Q118" s="5" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="119" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A119" s="4" t="s">
         <v>116</v>
       </c>
       <c r="B119" s="5" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C119" s="5" t="s">
         <v>189</v>
@@ -6862,30 +8282,39 @@
         <v>112</v>
       </c>
       <c r="E119" s="5" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="F119" s="5" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="G119" s="5"/>
       <c r="H119" s="5"/>
       <c r="I119" s="5"/>
       <c r="J119" s="5"/>
       <c r="K119" s="5" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="L119" s="5"/>
       <c r="M119" s="5"/>
-      <c r="N119" s="5" t="s">
-        <v>534</v>
-      </c>
-    </row>
-    <row r="120" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N119" s="13" t="s">
+        <v>611</v>
+      </c>
+      <c r="O119" s="13" t="s">
+        <v>611</v>
+      </c>
+      <c r="P119" s="14" t="s">
+        <v>609</v>
+      </c>
+      <c r="Q119" s="5" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="120" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A120" s="4" t="s">
         <v>116</v>
       </c>
       <c r="B120" s="5" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C120" s="5" t="s">
         <v>190</v>
@@ -6894,30 +8323,39 @@
         <v>112</v>
       </c>
       <c r="E120" s="5" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="F120" s="5" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="G120" s="5"/>
       <c r="H120" s="5"/>
       <c r="I120" s="5"/>
       <c r="J120" s="5"/>
       <c r="K120" s="5" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="L120" s="5"/>
       <c r="M120" s="5"/>
-      <c r="N120" s="5" t="s">
-        <v>533</v>
-      </c>
-    </row>
-    <row r="121" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N120" s="13" t="s">
+        <v>611</v>
+      </c>
+      <c r="O120" s="13" t="s">
+        <v>611</v>
+      </c>
+      <c r="P120" s="14" t="s">
+        <v>609</v>
+      </c>
+      <c r="Q120" s="5" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="121" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A121" s="4" t="s">
         <v>116</v>
       </c>
       <c r="B121" s="5" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C121" s="5" t="s">
         <v>191</v>
@@ -6926,7 +8364,7 @@
         <v>4</v>
       </c>
       <c r="E121" s="5" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F121" s="5" t="s">
         <v>6</v>
@@ -6936,20 +8374,29 @@
       <c r="I121" s="5"/>
       <c r="J121" s="5"/>
       <c r="K121" s="5" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="L121" s="5"/>
       <c r="M121" s="5"/>
-      <c r="N121" s="5" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="122" spans="1:14" ht="135" x14ac:dyDescent="0.3">
+      <c r="N121" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="O121" s="14" t="s">
+        <v>611</v>
+      </c>
+      <c r="P121" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="Q121" s="5" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="122" spans="1:17" ht="135" x14ac:dyDescent="0.3">
       <c r="A122" s="4" t="s">
         <v>116</v>
       </c>
       <c r="B122" s="5" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C122" s="5" t="s">
         <v>192</v>
@@ -6958,32 +8405,41 @@
         <v>4</v>
       </c>
       <c r="E122" s="5" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F122" s="5" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="G122" s="5"/>
       <c r="H122" s="5"/>
       <c r="I122" s="5"/>
       <c r="J122" s="5"/>
       <c r="K122" s="5" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="L122" s="5"/>
-      <c r="M122" s="12" t="s">
-        <v>599</v>
-      </c>
-      <c r="N122" s="5" t="s">
-        <v>526</v>
-      </c>
-    </row>
-    <row r="123" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="M122" s="10" t="s">
+        <v>596</v>
+      </c>
+      <c r="N122" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="O122" s="14" t="s">
+        <v>611</v>
+      </c>
+      <c r="P122" s="14" t="s">
+        <v>611</v>
+      </c>
+      <c r="Q122" s="5" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="123" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A123" s="4" t="s">
         <v>116</v>
       </c>
       <c r="B123" s="5" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C123" s="5" t="s">
         <v>193</v>
@@ -6992,25 +8448,34 @@
         <v>4</v>
       </c>
       <c r="E123" s="5" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F123" s="5" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="G123" s="5"/>
       <c r="H123" s="5"/>
       <c r="I123" s="5"/>
       <c r="J123" s="5"/>
       <c r="K123" s="5" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="L123" s="5"/>
       <c r="M123" s="5"/>
-      <c r="N123" s="5" t="s">
-        <v>529</v>
-      </c>
-    </row>
-    <row r="124" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N123" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="O123" s="14" t="s">
+        <v>611</v>
+      </c>
+      <c r="P123" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="Q123" s="5" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="124" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A124" s="4" t="s">
         <v>116</v>
       </c>
@@ -7024,7 +8489,7 @@
         <v>4</v>
       </c>
       <c r="E124" s="5" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F124" s="5" t="s">
         <v>6</v>
@@ -7034,20 +8499,29 @@
       <c r="I124" s="5"/>
       <c r="J124" s="5"/>
       <c r="K124" s="5" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="L124" s="5"/>
       <c r="M124" s="5"/>
-      <c r="N124" s="5" t="s">
-        <v>530</v>
-      </c>
-    </row>
-    <row r="125" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N124" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="O124" s="14" t="s">
+        <v>611</v>
+      </c>
+      <c r="P124" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="Q124" s="5" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="125" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A125" s="4" t="s">
         <v>116</v>
       </c>
       <c r="B125" s="5" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C125" s="5" t="s">
         <v>195</v>
@@ -7056,7 +8530,7 @@
         <v>4</v>
       </c>
       <c r="E125" s="5" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F125" s="5" t="s">
         <v>6</v>
@@ -7066,20 +8540,29 @@
       <c r="I125" s="5"/>
       <c r="J125" s="5"/>
       <c r="K125" s="5" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="L125" s="5"/>
       <c r="M125" s="5"/>
-      <c r="N125" s="5" t="s">
-        <v>527</v>
-      </c>
-    </row>
-    <row r="126" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N125" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="O125" s="14" t="s">
+        <v>611</v>
+      </c>
+      <c r="P125" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="Q125" s="5" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="126" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A126" s="4" t="s">
         <v>116</v>
       </c>
       <c r="B126" s="5" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C126" s="5" t="s">
         <v>196</v>
@@ -7088,30 +8571,39 @@
         <v>112</v>
       </c>
       <c r="E126" s="5" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="F126" s="5" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="G126" s="5"/>
       <c r="H126" s="5"/>
       <c r="I126" s="5"/>
       <c r="J126" s="5"/>
       <c r="K126" s="5" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="L126" s="5"/>
       <c r="M126" s="5"/>
-      <c r="N126" s="5" t="s">
-        <v>524</v>
-      </c>
-    </row>
-    <row r="127" spans="1:14" ht="40.5" x14ac:dyDescent="0.3">
+      <c r="N126" s="14" t="s">
+        <v>609</v>
+      </c>
+      <c r="O126" s="13" t="s">
+        <v>611</v>
+      </c>
+      <c r="P126" s="13" t="s">
+        <v>611</v>
+      </c>
+      <c r="Q126" s="5" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="127" spans="1:17" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A127" s="4" t="s">
         <v>116</v>
       </c>
       <c r="B127" s="5" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C127" s="5" t="s">
         <v>197</v>
@@ -7120,7 +8612,7 @@
         <v>4</v>
       </c>
       <c r="E127" s="5" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F127" s="5" t="s">
         <v>6</v>
@@ -7130,22 +8622,31 @@
       <c r="I127" s="5"/>
       <c r="J127" s="5"/>
       <c r="K127" s="5" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="L127" s="5"/>
-      <c r="M127" s="12" t="s">
-        <v>598</v>
-      </c>
-      <c r="N127" s="5" t="s">
-        <v>528</v>
-      </c>
-    </row>
-    <row r="128" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="M127" s="10" t="s">
+        <v>595</v>
+      </c>
+      <c r="N127" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="O127" s="14" t="s">
+        <v>611</v>
+      </c>
+      <c r="P127" s="14" t="s">
+        <v>611</v>
+      </c>
+      <c r="Q127" s="5" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="128" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A128" s="4" t="s">
         <v>116</v>
       </c>
       <c r="B128" s="5" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C128" s="5" t="s">
         <v>198</v>
@@ -7154,7 +8655,7 @@
         <v>4</v>
       </c>
       <c r="E128" s="5" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F128" s="5" t="s">
         <v>6</v>
@@ -7164,20 +8665,29 @@
       <c r="I128" s="5"/>
       <c r="J128" s="5"/>
       <c r="K128" s="5" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="L128" s="5"/>
       <c r="M128" s="5"/>
-      <c r="N128" s="5" t="s">
-        <v>531</v>
-      </c>
-    </row>
-    <row r="129" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N128" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="O128" s="14" t="s">
+        <v>612</v>
+      </c>
+      <c r="P128" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="Q128" s="5" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="129" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A129" s="4" t="s">
         <v>116</v>
       </c>
       <c r="B129" s="5" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C129" s="5" t="s">
         <v>199</v>
@@ -7186,7 +8696,7 @@
         <v>4</v>
       </c>
       <c r="E129" s="5" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F129" s="5" t="s">
         <v>6</v>
@@ -7196,20 +8706,29 @@
       <c r="I129" s="5"/>
       <c r="J129" s="5"/>
       <c r="K129" s="5" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="L129" s="5"/>
       <c r="M129" s="5"/>
-      <c r="N129" s="5" t="s">
-        <v>525</v>
-      </c>
-    </row>
-    <row r="130" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N129" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="O129" s="14" t="s">
+        <v>611</v>
+      </c>
+      <c r="P129" s="14" t="s">
+        <v>611</v>
+      </c>
+      <c r="Q129" s="5" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="130" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A130" s="4" t="s">
         <v>116</v>
       </c>
       <c r="B130" s="5" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C130" s="5" t="s">
         <v>200</v>
@@ -7218,7 +8737,7 @@
         <v>4</v>
       </c>
       <c r="E130" s="5" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F130" s="5" t="s">
         <v>6</v>
@@ -7228,20 +8747,29 @@
       <c r="I130" s="5"/>
       <c r="J130" s="5"/>
       <c r="K130" s="5" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="L130" s="5"/>
       <c r="M130" s="5"/>
-      <c r="N130" s="5" t="s">
-        <v>532</v>
-      </c>
-    </row>
-    <row r="131" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N130" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="O130" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="P130" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="Q130" s="5" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="131" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A131" s="4" t="s">
         <v>117</v>
       </c>
       <c r="B131" s="5" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C131" s="5" t="s">
         <v>201</v>
@@ -7250,30 +8778,39 @@
         <v>112</v>
       </c>
       <c r="E131" s="5" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="F131" s="5" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="G131" s="5"/>
       <c r="H131" s="5"/>
       <c r="I131" s="5"/>
       <c r="J131" s="5"/>
       <c r="K131" s="5" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="L131" s="5"/>
       <c r="M131" s="5"/>
-      <c r="N131" s="5" t="s">
-        <v>552</v>
-      </c>
-    </row>
-    <row r="132" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N131" s="14" t="s">
+        <v>609</v>
+      </c>
+      <c r="O131" s="13" t="s">
+        <v>611</v>
+      </c>
+      <c r="P131" s="13" t="s">
+        <v>611</v>
+      </c>
+      <c r="Q131" s="5" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="132" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A132" s="4" t="s">
         <v>117</v>
       </c>
       <c r="B132" s="5" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C132" s="5" t="s">
         <v>202</v>
@@ -7282,7 +8819,7 @@
         <v>4</v>
       </c>
       <c r="E132" s="5" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F132" s="5" t="s">
         <v>6</v>
@@ -7292,20 +8829,29 @@
       <c r="I132" s="5"/>
       <c r="J132" s="5"/>
       <c r="K132" s="5" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="L132" s="5"/>
       <c r="M132" s="5"/>
-      <c r="N132" s="5" t="s">
-        <v>541</v>
-      </c>
-    </row>
-    <row r="133" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N132" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="O132" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="P132" s="14" t="s">
+        <v>611</v>
+      </c>
+      <c r="Q132" s="5" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="133" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A133" s="4" t="s">
         <v>117</v>
       </c>
       <c r="B133" s="5" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C133" s="5" t="s">
         <v>203</v>
@@ -7314,30 +8860,39 @@
         <v>112</v>
       </c>
       <c r="E133" s="5" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="F133" s="5" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="G133" s="5"/>
       <c r="H133" s="5"/>
       <c r="I133" s="5"/>
       <c r="J133" s="5"/>
       <c r="K133" s="5" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="L133" s="5"/>
       <c r="M133" s="5"/>
-      <c r="N133" s="5" t="s">
-        <v>548</v>
-      </c>
-    </row>
-    <row r="134" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N133" s="14" t="s">
+        <v>609</v>
+      </c>
+      <c r="O133" s="14" t="s">
+        <v>609</v>
+      </c>
+      <c r="P133" s="14" t="s">
+        <v>609</v>
+      </c>
+      <c r="Q133" s="5" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="134" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A134" s="4" t="s">
         <v>117</v>
       </c>
       <c r="B134" s="5" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C134" s="5" t="s">
         <v>204</v>
@@ -7346,7 +8901,7 @@
         <v>4</v>
       </c>
       <c r="E134" s="5" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F134" s="5" t="s">
         <v>6</v>
@@ -7356,15 +8911,24 @@
       <c r="I134" s="5"/>
       <c r="J134" s="5"/>
       <c r="K134" s="5" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="L134" s="5"/>
       <c r="M134" s="5"/>
-      <c r="N134" s="5" t="s">
-        <v>536</v>
-      </c>
-    </row>
-    <row r="135" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N134" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="O134" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="P134" s="14" t="s">
+        <v>611</v>
+      </c>
+      <c r="Q134" s="5" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="135" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A135" s="4" t="s">
         <v>117</v>
       </c>
@@ -7378,30 +8942,39 @@
         <v>112</v>
       </c>
       <c r="E135" s="5" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="F135" s="5" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="G135" s="5"/>
       <c r="H135" s="5"/>
       <c r="I135" s="5"/>
       <c r="J135" s="5"/>
       <c r="K135" s="5" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="L135" s="5"/>
       <c r="M135" s="5"/>
-      <c r="N135" s="5" t="s">
-        <v>545</v>
-      </c>
-    </row>
-    <row r="136" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N135" s="14" t="s">
+        <v>609</v>
+      </c>
+      <c r="O135" s="14" t="s">
+        <v>609</v>
+      </c>
+      <c r="P135" s="13" t="s">
+        <v>611</v>
+      </c>
+      <c r="Q135" s="5" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="136" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A136" s="4" t="s">
         <v>117</v>
       </c>
       <c r="B136" s="5" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C136" s="5" t="s">
         <v>206</v>
@@ -7410,7 +8983,7 @@
         <v>4</v>
       </c>
       <c r="E136" s="5" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F136" s="5" t="s">
         <v>6</v>
@@ -7420,20 +8993,29 @@
       <c r="I136" s="5"/>
       <c r="J136" s="5"/>
       <c r="K136" s="5" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="L136" s="5"/>
       <c r="M136" s="5"/>
-      <c r="N136" s="5" t="s">
-        <v>540</v>
-      </c>
-    </row>
-    <row r="137" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N136" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="O136" s="14" t="s">
+        <v>611</v>
+      </c>
+      <c r="P136" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="Q136" s="5" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="137" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A137" s="4" t="s">
         <v>117</v>
       </c>
       <c r="B137" s="5" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C137" s="5" t="s">
         <v>207</v>
@@ -7442,7 +9024,7 @@
         <v>4</v>
       </c>
       <c r="E137" s="5" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F137" s="5" t="s">
         <v>6</v>
@@ -7452,15 +9034,24 @@
       <c r="I137" s="5"/>
       <c r="J137" s="5"/>
       <c r="K137" s="5" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="L137" s="5"/>
       <c r="M137" s="5"/>
-      <c r="N137" s="5" t="s">
-        <v>553</v>
-      </c>
-    </row>
-    <row r="138" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N137" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="O137" s="14" t="s">
+        <v>611</v>
+      </c>
+      <c r="P137" s="14" t="s">
+        <v>611</v>
+      </c>
+      <c r="Q137" s="5" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="138" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A138" s="4" t="s">
         <v>117</v>
       </c>
@@ -7474,30 +9065,39 @@
         <v>4</v>
       </c>
       <c r="E138" s="5" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F138" s="5" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="G138" s="5"/>
       <c r="H138" s="5"/>
       <c r="I138" s="5"/>
       <c r="J138" s="5"/>
       <c r="K138" s="5" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="L138" s="5"/>
       <c r="M138" s="5"/>
-      <c r="N138" s="5" t="s">
-        <v>538</v>
-      </c>
-    </row>
-    <row r="139" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N138" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="O138" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="P138" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="Q138" s="5" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="139" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A139" s="4" t="s">
         <v>117</v>
       </c>
       <c r="B139" s="5" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C139" s="5" t="s">
         <v>209</v>
@@ -7506,30 +9106,39 @@
         <v>112</v>
       </c>
       <c r="E139" s="5" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="F139" s="5" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="G139" s="5"/>
       <c r="H139" s="5"/>
       <c r="I139" s="5"/>
       <c r="J139" s="5"/>
       <c r="K139" s="5" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="L139" s="5"/>
       <c r="M139" s="5"/>
-      <c r="N139" s="5" t="s">
-        <v>543</v>
-      </c>
-    </row>
-    <row r="140" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N139" s="14" t="s">
+        <v>609</v>
+      </c>
+      <c r="O139" s="14" t="s">
+        <v>609</v>
+      </c>
+      <c r="P139" s="14" t="s">
+        <v>609</v>
+      </c>
+      <c r="Q139" s="5" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="140" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A140" s="4" t="s">
         <v>117</v>
       </c>
       <c r="B140" s="5" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C140" s="5" t="s">
         <v>210</v>
@@ -7538,7 +9147,7 @@
         <v>4</v>
       </c>
       <c r="E140" s="5" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F140" s="5" t="s">
         <v>6</v>
@@ -7548,20 +9157,29 @@
       <c r="I140" s="5"/>
       <c r="J140" s="5"/>
       <c r="K140" s="5" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="L140" s="5"/>
       <c r="M140" s="5"/>
-      <c r="N140" s="5" t="s">
-        <v>537</v>
-      </c>
-    </row>
-    <row r="141" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N140" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="O140" s="14" t="s">
+        <v>611</v>
+      </c>
+      <c r="P140" s="14" t="s">
+        <v>611</v>
+      </c>
+      <c r="Q140" s="5" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="141" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A141" s="4" t="s">
         <v>117</v>
       </c>
       <c r="B141" s="5" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C141" s="5" t="s">
         <v>211</v>
@@ -7570,25 +9188,34 @@
         <v>4</v>
       </c>
       <c r="E141" s="5" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F141" s="5" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="G141" s="5"/>
       <c r="H141" s="5"/>
       <c r="I141" s="5"/>
       <c r="J141" s="5"/>
       <c r="K141" s="5" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="L141" s="5"/>
       <c r="M141" s="5"/>
-      <c r="N141" s="5" t="s">
-        <v>546</v>
-      </c>
-    </row>
-    <row r="142" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N141" s="14" t="s">
+        <v>611</v>
+      </c>
+      <c r="O141" s="14" t="s">
+        <v>612</v>
+      </c>
+      <c r="P141" s="14" t="s">
+        <v>611</v>
+      </c>
+      <c r="Q141" s="5" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="142" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A142" s="4" t="s">
         <v>117</v>
       </c>
@@ -7602,30 +9229,39 @@
         <v>112</v>
       </c>
       <c r="E142" s="5" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="F142" s="5" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="G142" s="5"/>
       <c r="H142" s="5"/>
       <c r="I142" s="5"/>
       <c r="J142" s="5"/>
       <c r="K142" s="5" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="L142" s="5"/>
       <c r="M142" s="5"/>
-      <c r="N142" s="5" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="143" spans="1:14" ht="81" x14ac:dyDescent="0.3">
+      <c r="N142" s="13" t="s">
+        <v>611</v>
+      </c>
+      <c r="O142" s="14" t="s">
+        <v>609</v>
+      </c>
+      <c r="P142" s="13" t="s">
+        <v>611</v>
+      </c>
+      <c r="Q142" s="5" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="143" spans="1:17" ht="81" x14ac:dyDescent="0.3">
       <c r="A143" s="4" t="s">
         <v>117</v>
       </c>
       <c r="B143" s="5" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C143" s="5" t="s">
         <v>213</v>
@@ -7634,32 +9270,41 @@
         <v>112</v>
       </c>
       <c r="E143" s="5" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="F143" s="5" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="G143" s="5"/>
       <c r="H143" s="5"/>
       <c r="I143" s="5"/>
       <c r="J143" s="5"/>
       <c r="K143" s="5" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="L143" s="5"/>
-      <c r="M143" s="12" t="s">
-        <v>600</v>
-      </c>
-      <c r="N143" s="5" t="s">
-        <v>539</v>
-      </c>
-    </row>
-    <row r="144" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="M143" s="10" t="s">
+        <v>597</v>
+      </c>
+      <c r="N143" s="13" t="s">
+        <v>611</v>
+      </c>
+      <c r="O143" s="14" t="s">
+        <v>609</v>
+      </c>
+      <c r="P143" s="14" t="s">
+        <v>609</v>
+      </c>
+      <c r="Q143" s="5" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="144" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A144" s="4" t="s">
         <v>117</v>
       </c>
       <c r="B144" s="5" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C144" s="5" t="s">
         <v>214</v>
@@ -7668,25 +9313,34 @@
         <v>112</v>
       </c>
       <c r="E144" s="5" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="F144" s="5" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="G144" s="5"/>
       <c r="H144" s="5"/>
       <c r="I144" s="5"/>
       <c r="J144" s="5"/>
       <c r="K144" s="5" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="L144" s="5"/>
       <c r="M144" s="5"/>
-      <c r="N144" s="5" t="s">
-        <v>549</v>
-      </c>
-    </row>
-    <row r="145" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N144" s="14" t="s">
+        <v>609</v>
+      </c>
+      <c r="O144" s="14" t="s">
+        <v>609</v>
+      </c>
+      <c r="P144" s="14" t="s">
+        <v>609</v>
+      </c>
+      <c r="Q144" s="5" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="145" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A145" s="4" t="s">
         <v>117</v>
       </c>
@@ -7700,7 +9354,7 @@
         <v>4</v>
       </c>
       <c r="E145" s="5" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F145" s="5" t="s">
         <v>6</v>
@@ -7710,20 +9364,29 @@
       <c r="I145" s="5"/>
       <c r="J145" s="5"/>
       <c r="K145" s="5" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="L145" s="5"/>
       <c r="M145" s="5"/>
-      <c r="N145" s="5" t="s">
-        <v>535</v>
-      </c>
-    </row>
-    <row r="146" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N145" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="O145" s="14" t="s">
+        <v>611</v>
+      </c>
+      <c r="P145" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="Q145" s="5" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="146" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A146" s="4" t="s">
         <v>117</v>
       </c>
       <c r="B146" s="5" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C146" s="5" t="s">
         <v>216</v>
@@ -7732,25 +9395,34 @@
         <v>112</v>
       </c>
       <c r="E146" s="5" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="F146" s="5" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="G146" s="5"/>
       <c r="H146" s="5"/>
       <c r="I146" s="5"/>
       <c r="J146" s="5"/>
       <c r="K146" s="5" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="L146" s="5"/>
       <c r="M146" s="5"/>
-      <c r="N146" s="5" t="s">
-        <v>537</v>
-      </c>
-    </row>
-    <row r="147" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N146" s="14" t="s">
+        <v>609</v>
+      </c>
+      <c r="O146" s="14" t="s">
+        <v>609</v>
+      </c>
+      <c r="P146" s="13" t="s">
+        <v>611</v>
+      </c>
+      <c r="Q146" s="5" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="147" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A147" s="4" t="s">
         <v>117</v>
       </c>
@@ -7764,7 +9436,7 @@
         <v>4</v>
       </c>
       <c r="E147" s="5" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F147" s="5" t="s">
         <v>6</v>
@@ -7774,20 +9446,29 @@
       <c r="I147" s="5"/>
       <c r="J147" s="5"/>
       <c r="K147" s="5" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="L147" s="5"/>
       <c r="M147" s="5"/>
-      <c r="N147" s="5" t="s">
-        <v>550</v>
-      </c>
-    </row>
-    <row r="148" spans="1:14" ht="135" x14ac:dyDescent="0.3">
+      <c r="N147" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="O147" s="14" t="s">
+        <v>611</v>
+      </c>
+      <c r="P147" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="Q147" s="5" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="148" spans="1:17" ht="135" x14ac:dyDescent="0.3">
       <c r="A148" s="4" t="s">
         <v>117</v>
       </c>
       <c r="B148" s="5" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C148" s="5" t="s">
         <v>218</v>
@@ -7796,7 +9477,7 @@
         <v>4</v>
       </c>
       <c r="E148" s="5" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F148" s="5" t="s">
         <v>6</v>
@@ -7806,22 +9487,31 @@
       <c r="I148" s="5"/>
       <c r="J148" s="5"/>
       <c r="K148" s="5" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="L148" s="5"/>
-      <c r="M148" s="12" t="s">
-        <v>601</v>
-      </c>
-      <c r="N148" s="5" t="s">
-        <v>551</v>
-      </c>
-    </row>
-    <row r="149" spans="1:14" ht="148.5" x14ac:dyDescent="0.3">
+      <c r="M148" s="10" t="s">
+        <v>598</v>
+      </c>
+      <c r="N148" s="14" t="s">
+        <v>612</v>
+      </c>
+      <c r="O148" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="P148" s="14" t="s">
+        <v>611</v>
+      </c>
+      <c r="Q148" s="5" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="149" spans="1:17" ht="148.5" x14ac:dyDescent="0.3">
       <c r="A149" s="4" t="s">
         <v>117</v>
       </c>
       <c r="B149" s="5" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C149" s="5" t="s">
         <v>219</v>
@@ -7830,7 +9520,7 @@
         <v>4</v>
       </c>
       <c r="E149" s="5" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F149" s="5" t="s">
         <v>6</v>
@@ -7840,22 +9530,31 @@
       <c r="I149" s="5"/>
       <c r="J149" s="5"/>
       <c r="K149" s="5" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="L149" s="5"/>
-      <c r="M149" s="12" t="s">
-        <v>602</v>
-      </c>
-      <c r="N149" s="5" t="s">
-        <v>544</v>
-      </c>
-    </row>
-    <row r="150" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="M149" s="10" t="s">
+        <v>599</v>
+      </c>
+      <c r="N149" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="O149" s="14" t="s">
+        <v>612</v>
+      </c>
+      <c r="P149" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="Q149" s="5" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="150" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A150" s="4" t="s">
         <v>117</v>
       </c>
       <c r="B150" s="5" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C150" s="5" t="s">
         <v>220</v>
@@ -7864,30 +9563,39 @@
         <v>4</v>
       </c>
       <c r="E150" s="5" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F150" s="5" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="G150" s="5"/>
       <c r="H150" s="5"/>
       <c r="I150" s="5"/>
       <c r="J150" s="5"/>
       <c r="K150" s="5" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="L150" s="5"/>
       <c r="M150" s="5"/>
-      <c r="N150" s="5" t="s">
-        <v>553</v>
-      </c>
-    </row>
-    <row r="151" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N150" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="O150" s="14" t="s">
+        <v>611</v>
+      </c>
+      <c r="P150" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="Q150" s="5" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="151" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A151" s="4" t="s">
         <v>117</v>
       </c>
       <c r="B151" s="5" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="C151" s="5" t="s">
         <v>221</v>
@@ -7896,7 +9604,7 @@
         <v>4</v>
       </c>
       <c r="E151" s="5" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F151" s="5" t="s">
         <v>6</v>
@@ -7906,20 +9614,29 @@
       <c r="I151" s="5"/>
       <c r="J151" s="5"/>
       <c r="K151" s="5" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="L151" s="5"/>
       <c r="M151" s="5"/>
-      <c r="N151" s="5" t="s">
-        <v>542</v>
-      </c>
-    </row>
-    <row r="152" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N151" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="O151" s="14" t="s">
+        <v>612</v>
+      </c>
+      <c r="P151" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="Q151" s="5" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="152" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A152" s="4" t="s">
         <v>118</v>
       </c>
       <c r="B152" s="5" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C152" s="5" t="s">
         <v>222</v>
@@ -7928,30 +9645,39 @@
         <v>4</v>
       </c>
       <c r="E152" s="5" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F152" s="5" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="G152" s="5"/>
       <c r="H152" s="5"/>
       <c r="I152" s="5"/>
       <c r="J152" s="5"/>
       <c r="K152" s="5" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="L152" s="5"/>
       <c r="M152" s="5"/>
-      <c r="N152" s="5" t="s">
-        <v>555</v>
-      </c>
-    </row>
-    <row r="153" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N152" s="14" t="s">
+        <v>612</v>
+      </c>
+      <c r="O152" s="14" t="s">
+        <v>611</v>
+      </c>
+      <c r="P152" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="Q152" s="5" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="153" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A153" s="4" t="s">
         <v>118</v>
       </c>
       <c r="B153" s="5" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C153" s="5" t="s">
         <v>223</v>
@@ -7960,7 +9686,7 @@
         <v>4</v>
       </c>
       <c r="E153" s="5" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F153" s="5" t="s">
         <v>6</v>
@@ -7970,61 +9696,79 @@
       <c r="I153" s="5"/>
       <c r="J153" s="5"/>
       <c r="K153" s="5" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="L153" s="5"/>
       <c r="M153" s="5"/>
-      <c r="N153" s="5" t="s">
-        <v>556</v>
-      </c>
-    </row>
-    <row r="154" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N153" s="13" t="s">
+        <v>611</v>
+      </c>
+      <c r="O153" s="13" t="s">
+        <v>611</v>
+      </c>
+      <c r="P153" s="14" t="s">
+        <v>609</v>
+      </c>
+      <c r="Q153" s="5" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="154" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A154" s="4" t="s">
         <v>118</v>
       </c>
       <c r="B154" s="5" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C154" s="5" t="s">
-        <v>224</v>
+        <v>614</v>
       </c>
       <c r="D154" s="5" t="s">
         <v>4</v>
       </c>
       <c r="E154" s="5" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F154" s="5" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="G154" s="5"/>
       <c r="H154" s="5"/>
       <c r="I154" s="5"/>
       <c r="J154" s="5"/>
       <c r="K154" s="5" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="L154" s="5"/>
       <c r="M154" s="5"/>
-      <c r="N154" s="5" t="s">
-        <v>557</v>
-      </c>
-    </row>
-    <row r="155" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N154" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="O154" s="14" t="s">
+        <v>611</v>
+      </c>
+      <c r="P154" s="14" t="s">
+        <v>611</v>
+      </c>
+      <c r="Q154" s="5" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="155" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A155" s="4" t="s">
         <v>118</v>
       </c>
       <c r="B155" s="5" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C155" s="5" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D155" s="5" t="s">
         <v>4</v>
       </c>
       <c r="E155" s="5" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F155" s="5" t="s">
         <v>6</v>
@@ -8034,29 +9778,38 @@
       <c r="I155" s="5"/>
       <c r="J155" s="5"/>
       <c r="K155" s="5" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="L155" s="5"/>
       <c r="M155" s="5"/>
-      <c r="N155" s="5" t="s">
-        <v>559</v>
-      </c>
-    </row>
-    <row r="156" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N155" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="O155" s="14" t="s">
+        <v>611</v>
+      </c>
+      <c r="P155" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="Q155" s="5" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="156" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A156" s="4" t="s">
         <v>118</v>
       </c>
       <c r="B156" s="5" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C156" s="5" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D156" s="5" t="s">
         <v>4</v>
       </c>
       <c r="E156" s="5" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F156" s="5" t="s">
         <v>6</v>
@@ -8066,61 +9819,79 @@
       <c r="I156" s="5"/>
       <c r="J156" s="5"/>
       <c r="K156" s="5" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="L156" s="5"/>
       <c r="M156" s="5"/>
-      <c r="N156" s="5" t="s">
-        <v>554</v>
-      </c>
-    </row>
-    <row r="157" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N156" s="13" t="s">
+        <v>611</v>
+      </c>
+      <c r="O156" s="13" t="s">
+        <v>611</v>
+      </c>
+      <c r="P156" s="13" t="s">
+        <v>611</v>
+      </c>
+      <c r="Q156" s="5" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="157" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A157" s="4" t="s">
         <v>118</v>
       </c>
       <c r="B157" s="5" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C157" s="5" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D157" s="5" t="s">
         <v>112</v>
       </c>
       <c r="E157" s="5" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="F157" s="5" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="G157" s="5"/>
       <c r="H157" s="5"/>
       <c r="I157" s="5"/>
       <c r="J157" s="5"/>
       <c r="K157" s="5" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="L157" s="5"/>
       <c r="M157" s="5"/>
-      <c r="N157" s="5" t="s">
-        <v>563</v>
-      </c>
-    </row>
-    <row r="158" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N157" s="13" t="s">
+        <v>611</v>
+      </c>
+      <c r="O157" s="13" t="s">
+        <v>611</v>
+      </c>
+      <c r="P157" s="14" t="s">
+        <v>609</v>
+      </c>
+      <c r="Q157" s="5" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="158" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A158" s="4" t="s">
         <v>118</v>
       </c>
       <c r="B158" s="5" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C158" s="5" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D158" s="5" t="s">
         <v>4</v>
       </c>
       <c r="E158" s="5" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F158" s="5" t="s">
         <v>6</v>
@@ -8130,29 +9901,38 @@
       <c r="I158" s="5"/>
       <c r="J158" s="5"/>
       <c r="K158" s="5" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="L158" s="5"/>
       <c r="M158" s="5"/>
-      <c r="N158" s="5" t="s">
-        <v>564</v>
-      </c>
-    </row>
-    <row r="159" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N158" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="O158" s="14" t="s">
+        <v>611</v>
+      </c>
+      <c r="P158" s="14" t="s">
+        <v>611</v>
+      </c>
+      <c r="Q158" s="5" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="159" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A159" s="4" t="s">
         <v>118</v>
       </c>
       <c r="B159" s="5" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C159" s="5" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D159" s="5" t="s">
         <v>4</v>
       </c>
       <c r="E159" s="5" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F159" s="5" t="s">
         <v>6</v>
@@ -8162,29 +9942,38 @@
       <c r="I159" s="5"/>
       <c r="J159" s="5"/>
       <c r="K159" s="5" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="L159" s="5"/>
       <c r="M159" s="5"/>
-      <c r="N159" s="5" t="s">
-        <v>566</v>
-      </c>
-    </row>
-    <row r="160" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N159" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="O159" s="14" t="s">
+        <v>611</v>
+      </c>
+      <c r="P159" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="Q159" s="5" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="160" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A160" s="4" t="s">
         <v>118</v>
       </c>
       <c r="B160" s="5" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C160" s="5" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D160" s="5" t="s">
         <v>4</v>
       </c>
       <c r="E160" s="5" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F160" s="5" t="s">
         <v>6</v>
@@ -8194,29 +9983,38 @@
       <c r="I160" s="5"/>
       <c r="J160" s="5"/>
       <c r="K160" s="5" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="L160" s="5"/>
       <c r="M160" s="5"/>
-      <c r="N160" s="5" t="s">
-        <v>562</v>
-      </c>
-    </row>
-    <row r="161" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N160" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="O160" s="14" t="s">
+        <v>612</v>
+      </c>
+      <c r="P160" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="Q160" s="5" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="161" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A161" s="4" t="s">
         <v>118</v>
       </c>
       <c r="B161" s="5" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C161" s="5" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D161" s="5" t="s">
         <v>4</v>
       </c>
       <c r="E161" s="5" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F161" s="5" t="s">
         <v>6</v>
@@ -8226,29 +10024,38 @@
       <c r="I161" s="5"/>
       <c r="J161" s="5"/>
       <c r="K161" s="5" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="L161" s="5"/>
       <c r="M161" s="5"/>
-      <c r="N161" s="5" t="s">
-        <v>569</v>
-      </c>
-    </row>
-    <row r="162" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N161" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="O161" s="14" t="s">
+        <v>611</v>
+      </c>
+      <c r="P161" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="Q161" s="5" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="162" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A162" s="4" t="s">
         <v>118</v>
       </c>
       <c r="B162" s="5" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C162" s="5" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D162" s="5" t="s">
         <v>4</v>
       </c>
       <c r="E162" s="5" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F162" s="5" t="s">
         <v>6</v>
@@ -8258,29 +10065,38 @@
       <c r="I162" s="5"/>
       <c r="J162" s="5"/>
       <c r="K162" s="5" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="L162" s="5"/>
       <c r="M162" s="5"/>
-      <c r="N162" s="5" t="s">
-        <v>570</v>
-      </c>
-    </row>
-    <row r="163" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N162" s="14" t="s">
+        <v>611</v>
+      </c>
+      <c r="O162" s="14" t="s">
+        <v>611</v>
+      </c>
+      <c r="P162" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="Q162" s="5" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="163" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A163" s="4" t="s">
         <v>118</v>
       </c>
       <c r="B163" s="5" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C163" s="5" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D163" s="5" t="s">
         <v>4</v>
       </c>
       <c r="E163" s="5" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F163" s="5" t="s">
         <v>6</v>
@@ -8290,29 +10106,38 @@
       <c r="I163" s="5"/>
       <c r="J163" s="5"/>
       <c r="K163" s="5" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="L163" s="5"/>
       <c r="M163" s="5"/>
-      <c r="N163" s="5" t="s">
-        <v>572</v>
-      </c>
-    </row>
-    <row r="164" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N163" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="O163" s="14" t="s">
+        <v>612</v>
+      </c>
+      <c r="P163" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="Q163" s="5" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="164" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A164" s="4" t="s">
         <v>118</v>
       </c>
       <c r="B164" s="5" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C164" s="5" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="D164" s="5" t="s">
         <v>4</v>
       </c>
       <c r="E164" s="5" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F164" s="5" t="s">
         <v>6</v>
@@ -8322,29 +10147,38 @@
       <c r="I164" s="5"/>
       <c r="J164" s="5"/>
       <c r="K164" s="5" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="L164" s="5"/>
       <c r="M164" s="5"/>
-      <c r="N164" s="5" t="s">
-        <v>558</v>
-      </c>
-    </row>
-    <row r="165" spans="1:14" ht="40.5" x14ac:dyDescent="0.3">
+      <c r="N164" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="O164" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="P164" s="14" t="s">
+        <v>611</v>
+      </c>
+      <c r="Q164" s="5" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="165" spans="1:17" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A165" s="4" t="s">
         <v>118</v>
       </c>
       <c r="B165" s="5" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C165" s="5" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="D165" s="5" t="s">
         <v>4</v>
       </c>
       <c r="E165" s="5" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F165" s="5" t="s">
         <v>6</v>
@@ -8354,17 +10188,26 @@
       <c r="I165" s="5"/>
       <c r="J165" s="5"/>
       <c r="K165" s="5" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="L165" s="5"/>
-      <c r="M165" s="12" t="s">
-        <v>603</v>
-      </c>
-      <c r="N165" s="5" t="s">
-        <v>571</v>
-      </c>
-    </row>
-    <row r="166" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="M165" s="10" t="s">
+        <v>600</v>
+      </c>
+      <c r="N165" s="14" t="s">
+        <v>611</v>
+      </c>
+      <c r="O165" s="14" t="s">
+        <v>611</v>
+      </c>
+      <c r="P165" s="14" t="s">
+        <v>611</v>
+      </c>
+      <c r="Q165" s="5" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="166" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A166" s="4" t="s">
         <v>118</v>
       </c>
@@ -8372,13 +10215,13 @@
         <v>99</v>
       </c>
       <c r="C166" s="5" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D166" s="5" t="s">
         <v>4</v>
       </c>
       <c r="E166" s="5" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F166" s="5" t="s">
         <v>6</v>
@@ -8388,15 +10231,24 @@
       <c r="I166" s="5"/>
       <c r="J166" s="5"/>
       <c r="K166" s="5" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="L166" s="5"/>
       <c r="M166" s="5"/>
-      <c r="N166" s="5" t="s">
-        <v>560</v>
-      </c>
-    </row>
-    <row r="167" spans="1:14" ht="283.5" x14ac:dyDescent="0.3">
+      <c r="N166" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="O166" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="P166" s="14" t="s">
+        <v>611</v>
+      </c>
+      <c r="Q166" s="5" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="167" spans="1:17" ht="283.5" x14ac:dyDescent="0.3">
       <c r="A167" s="4" t="s">
         <v>118</v>
       </c>
@@ -8410,7 +10262,7 @@
         <v>4</v>
       </c>
       <c r="E167" s="5" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F167" s="5" t="s">
         <v>9</v>
@@ -8420,17 +10272,26 @@
       <c r="I167" s="5"/>
       <c r="J167" s="5"/>
       <c r="K167" s="5" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="L167" s="5"/>
-      <c r="M167" s="12" t="s">
-        <v>604</v>
-      </c>
-      <c r="N167" s="5" t="s">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="168" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="M167" s="10" t="s">
+        <v>601</v>
+      </c>
+      <c r="N167" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="O167" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="P167" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="Q167" s="5" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="168" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A168" s="4" t="s">
         <v>118</v>
       </c>
@@ -8438,13 +10299,13 @@
         <v>99</v>
       </c>
       <c r="C168" s="5" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="D168" s="5" t="s">
         <v>4</v>
       </c>
       <c r="E168" s="5" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F168" s="5" t="s">
         <v>6</v>
@@ -8454,15 +10315,24 @@
       <c r="I168" s="5"/>
       <c r="J168" s="5"/>
       <c r="K168" s="5" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="L168" s="5"/>
       <c r="M168" s="5"/>
-      <c r="N168" s="5" t="s">
-        <v>565</v>
-      </c>
-    </row>
-    <row r="169" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N168" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="O168" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="P168" s="14" t="s">
+        <v>611</v>
+      </c>
+      <c r="Q168" s="5" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="169" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A169" s="4" t="s">
         <v>118</v>
       </c>
@@ -8470,13 +10340,13 @@
         <v>99</v>
       </c>
       <c r="C169" s="5" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="D169" s="5" t="s">
         <v>4</v>
       </c>
       <c r="E169" s="5" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F169" s="5" t="s">
         <v>6</v>
@@ -8486,93 +10356,120 @@
       <c r="I169" s="5"/>
       <c r="J169" s="5"/>
       <c r="K169" s="5" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="L169" s="5"/>
       <c r="M169" s="5"/>
-      <c r="N169" s="5" t="s">
-        <v>568</v>
-      </c>
-    </row>
-    <row r="170" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N169" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="O169" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="P169" s="14" t="s">
+        <v>612</v>
+      </c>
+      <c r="Q169" s="5" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="170" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A170" s="4" t="s">
         <v>118</v>
       </c>
       <c r="B170" s="5" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C170" s="5" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D170" s="5" t="s">
         <v>112</v>
       </c>
       <c r="E170" s="5" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="F170" s="5" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="G170" s="5"/>
       <c r="H170" s="5"/>
       <c r="I170" s="5"/>
       <c r="J170" s="5"/>
       <c r="K170" s="5" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="L170" s="5"/>
       <c r="M170" s="5"/>
-      <c r="N170" s="5" t="s">
-        <v>567</v>
-      </c>
-    </row>
-    <row r="171" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N170" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="O170" s="14" t="s">
+        <v>611</v>
+      </c>
+      <c r="P170" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="Q170" s="5" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="171" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A171" s="4" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B171" s="5" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C171" s="5" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D171" s="5" t="s">
         <v>112</v>
       </c>
       <c r="E171" s="5" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="F171" s="5" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="G171" s="5"/>
       <c r="H171" s="5"/>
       <c r="I171" s="5"/>
       <c r="J171" s="5"/>
       <c r="K171" s="5" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="L171" s="5"/>
       <c r="M171" s="5"/>
-      <c r="N171" s="5" t="s">
-        <v>574</v>
-      </c>
-    </row>
-    <row r="172" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N171" s="13" t="s">
+        <v>611</v>
+      </c>
+      <c r="O171" s="13" t="s">
+        <v>611</v>
+      </c>
+      <c r="P171" s="14" t="s">
+        <v>609</v>
+      </c>
+      <c r="Q171" s="5" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="172" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A172" s="4" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B172" s="5" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C172" s="5" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="D172" s="5" t="s">
         <v>4</v>
       </c>
       <c r="E172" s="5" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F172" s="5" t="s">
         <v>6</v>
@@ -8582,61 +10479,79 @@
       <c r="I172" s="5"/>
       <c r="J172" s="5"/>
       <c r="K172" s="5" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="L172" s="5"/>
       <c r="M172" s="5"/>
-      <c r="N172" s="5" t="s">
-        <v>575</v>
-      </c>
-    </row>
-    <row r="173" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N172" s="14" t="s">
+        <v>611</v>
+      </c>
+      <c r="O172" s="14" t="s">
+        <v>611</v>
+      </c>
+      <c r="P172" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="Q172" s="5" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="173" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A173" s="4" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B173" s="5" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C173" s="5" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D173" s="5" t="s">
         <v>112</v>
       </c>
       <c r="E173" s="5" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="F173" s="5" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="G173" s="5"/>
       <c r="H173" s="5"/>
       <c r="I173" s="5"/>
       <c r="J173" s="5"/>
       <c r="K173" s="5" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="L173" s="5"/>
       <c r="M173" s="5"/>
-      <c r="N173" s="5" t="s">
-        <v>573</v>
-      </c>
-    </row>
-    <row r="174" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N173" s="13" t="s">
+        <v>611</v>
+      </c>
+      <c r="O173" s="13" t="s">
+        <v>611</v>
+      </c>
+      <c r="P173" s="14" t="s">
+        <v>609</v>
+      </c>
+      <c r="Q173" s="5" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="174" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A174" s="4" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B174" s="5" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C174" s="5" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D174" s="5" t="s">
         <v>4</v>
       </c>
       <c r="E174" s="5" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F174" s="5" t="s">
         <v>6</v>
@@ -8646,235 +10561,745 @@
       <c r="I174" s="5"/>
       <c r="J174" s="5"/>
       <c r="K174" s="5" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="L174" s="5"/>
       <c r="M174" s="5"/>
-      <c r="N174" s="5" t="s">
-        <v>576</v>
-      </c>
-    </row>
-    <row r="175" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A175" s="2" t="s">
-        <v>363</v>
-      </c>
-      <c r="B175" s="2" t="s">
-        <v>364</v>
-      </c>
-      <c r="C175" s="2" t="s">
+      <c r="N174" s="14" t="s">
+        <v>611</v>
+      </c>
+      <c r="O174" s="14" t="s">
+        <v>611</v>
+      </c>
+      <c r="P174" s="14" t="s">
+        <v>611</v>
+      </c>
+      <c r="Q174" s="5" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="175" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A175" s="6" t="s">
+        <v>360</v>
+      </c>
+      <c r="B175" s="6" t="s">
+        <v>361</v>
+      </c>
+      <c r="C175" s="6" t="s">
+        <v>331</v>
+      </c>
+      <c r="D175" s="6" t="s">
+        <v>331</v>
+      </c>
+      <c r="E175" s="6" t="s">
+        <v>684</v>
+      </c>
+      <c r="F175" s="6" t="s">
         <v>332</v>
       </c>
-      <c r="D175" s="2" t="s">
-        <v>332</v>
-      </c>
-      <c r="E175" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="F175" s="2" t="s">
+      <c r="G175" s="6"/>
+      <c r="H175" s="6"/>
+      <c r="I175" s="6"/>
+      <c r="J175" s="6"/>
+      <c r="K175" s="6" t="s">
         <v>333</v>
-      </c>
-      <c r="G175" s="2"/>
-      <c r="H175" s="2"/>
-      <c r="I175" s="2"/>
-      <c r="J175" s="2"/>
-      <c r="K175" s="2" t="s">
-        <v>335</v>
       </c>
       <c r="L175" s="2"/>
       <c r="M175" s="2"/>
-      <c r="N175" s="7" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="176" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A176" s="2" t="s">
-        <v>363</v>
-      </c>
-      <c r="B176" s="2" t="s">
-        <v>364</v>
-      </c>
-      <c r="C176" s="2" t="s">
+      <c r="N175" s="16"/>
+      <c r="O175" s="16"/>
+      <c r="P175" s="16"/>
+      <c r="Q175" s="8" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="176" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A176" s="6" t="s">
+        <v>360</v>
+      </c>
+      <c r="B176" s="6" t="s">
+        <v>361</v>
+      </c>
+      <c r="C176" s="6" t="s">
+        <v>643</v>
+      </c>
+      <c r="D176" s="6" t="s">
+        <v>685</v>
+      </c>
+      <c r="E176" s="6" t="s">
+        <v>684</v>
+      </c>
+      <c r="F176" s="6"/>
+      <c r="G176" s="6" t="s">
+        <v>408</v>
+      </c>
+      <c r="H176" s="6"/>
+      <c r="I176" s="6"/>
+      <c r="J176" s="6"/>
+      <c r="K176" s="6" t="s">
         <v>334</v>
-      </c>
-      <c r="D176" s="2" t="s">
-        <v>334</v>
-      </c>
-      <c r="E176" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="F176" s="2"/>
-      <c r="G176" s="2" t="s">
-        <v>411</v>
-      </c>
-      <c r="H176" s="2"/>
-      <c r="I176" s="2"/>
-      <c r="J176" s="2"/>
-      <c r="K176" s="2" t="s">
-        <v>336</v>
       </c>
       <c r="L176" s="2"/>
       <c r="M176" s="2"/>
-      <c r="N176" s="7" t="s">
+      <c r="N176" s="16"/>
+      <c r="O176" s="16"/>
+      <c r="P176" s="16"/>
+      <c r="Q176" s="8" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="177" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A177" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="B177" s="6" t="s">
+        <v>336</v>
+      </c>
+      <c r="C177" s="6" t="s">
+        <v>335</v>
+      </c>
+      <c r="D177" s="6" t="s">
+        <v>687</v>
+      </c>
+      <c r="E177" s="6" t="s">
+        <v>683</v>
+      </c>
+      <c r="F177" s="6" t="s">
+        <v>397</v>
+      </c>
+      <c r="G177" s="7" t="s">
+        <v>337</v>
+      </c>
+      <c r="H177" s="7" t="s">
+        <v>354</v>
+      </c>
+      <c r="I177" s="7"/>
+      <c r="J177" s="7"/>
+      <c r="K177" s="7"/>
+      <c r="L177" s="7"/>
+      <c r="M177" s="7"/>
+      <c r="N177" s="15"/>
+      <c r="O177" s="15"/>
+      <c r="P177" s="15"/>
+      <c r="Q177" s="8" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="178" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A178" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="B178" s="6" t="s">
+        <v>336</v>
+      </c>
+      <c r="C178" s="6" t="s">
+        <v>335</v>
+      </c>
+      <c r="D178" s="6" t="s">
+        <v>687</v>
+      </c>
+      <c r="E178" s="6" t="s">
+        <v>683</v>
+      </c>
+      <c r="F178" s="6" t="s">
+        <v>397</v>
+      </c>
+      <c r="G178" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="H178" s="7" t="s">
+        <v>355</v>
+      </c>
+      <c r="I178" s="7"/>
+      <c r="J178" s="7"/>
+      <c r="K178" s="7"/>
+      <c r="L178" s="7"/>
+      <c r="M178" s="7"/>
+      <c r="N178" s="15"/>
+      <c r="O178" s="15"/>
+      <c r="P178" s="15"/>
+      <c r="Q178" s="8" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="179" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A179" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="B179" s="6" t="s">
+        <v>398</v>
+      </c>
+      <c r="C179" s="6" t="s">
+        <v>342</v>
+      </c>
+      <c r="D179" s="6" t="s">
+        <v>687</v>
+      </c>
+      <c r="E179" s="6" t="s">
+        <v>683</v>
+      </c>
+      <c r="F179" s="6" t="s">
+        <v>574</v>
+      </c>
+      <c r="G179" s="7" t="s">
         <v>343</v>
       </c>
-    </row>
-    <row r="177" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A177" s="8" t="s">
+      <c r="H179" s="7" t="s">
+        <v>356</v>
+      </c>
+      <c r="I179" s="7"/>
+      <c r="J179" s="7"/>
+      <c r="K179" s="6" t="s">
+        <v>333</v>
+      </c>
+      <c r="L179" s="6"/>
+      <c r="M179" s="6"/>
+      <c r="N179" s="16"/>
+      <c r="O179" s="16"/>
+      <c r="P179" s="16"/>
+      <c r="Q179" s="6" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="180" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A180" s="6" t="s">
         <v>118</v>
       </c>
-      <c r="B177" s="8" t="s">
-        <v>338</v>
-      </c>
-      <c r="C177" s="8" t="s">
-        <v>337</v>
-      </c>
-      <c r="D177" s="8" t="s">
-        <v>339</v>
-      </c>
-      <c r="E177" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="F177" s="8" t="s">
-        <v>400</v>
-      </c>
-      <c r="G177" s="9" t="s">
-        <v>340</v>
-      </c>
-      <c r="H177" s="9" t="s">
+      <c r="B180" s="6" t="s">
+        <v>398</v>
+      </c>
+      <c r="C180" s="6" t="s">
+        <v>342</v>
+      </c>
+      <c r="D180" s="6" t="s">
+        <v>687</v>
+      </c>
+      <c r="E180" s="6" t="s">
+        <v>683</v>
+      </c>
+      <c r="F180" s="6" t="s">
+        <v>574</v>
+      </c>
+      <c r="G180" s="7" t="s">
+        <v>344</v>
+      </c>
+      <c r="H180" s="7" t="s">
         <v>357</v>
       </c>
-      <c r="I177" s="9"/>
-      <c r="J177" s="9"/>
-      <c r="K177" s="9"/>
-      <c r="L177" s="9"/>
-      <c r="M177" s="9"/>
-      <c r="N177" s="10" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="178" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A178" s="8" t="s">
+      <c r="I180" s="7"/>
+      <c r="J180" s="7"/>
+      <c r="K180" s="6" t="s">
+        <v>333</v>
+      </c>
+      <c r="L180" s="6"/>
+      <c r="M180" s="6"/>
+      <c r="N180" s="16"/>
+      <c r="O180" s="16"/>
+      <c r="P180" s="16"/>
+      <c r="Q180" s="6" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="181" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A181" s="6" t="s">
         <v>118</v>
       </c>
-      <c r="B178" s="8" t="s">
-        <v>338</v>
-      </c>
-      <c r="C178" s="8" t="s">
-        <v>337</v>
-      </c>
-      <c r="D178" s="8" t="s">
-        <v>339</v>
-      </c>
-      <c r="E178" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="F178" s="8" t="s">
-        <v>400</v>
-      </c>
-      <c r="G178" s="9" t="s">
-        <v>341</v>
-      </c>
-      <c r="H178" s="9" t="s">
-        <v>358</v>
-      </c>
-      <c r="I178" s="9"/>
-      <c r="J178" s="9"/>
-      <c r="K178" s="9"/>
-      <c r="L178" s="9"/>
-      <c r="M178" s="9"/>
-      <c r="N178" s="10" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="179" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A179" s="8" t="s">
+      <c r="B181" s="6" t="s">
+        <v>617</v>
+      </c>
+      <c r="C181" s="6" t="s">
+        <v>616</v>
+      </c>
+      <c r="D181" s="6" t="s">
+        <v>686</v>
+      </c>
+      <c r="E181" s="6" t="s">
+        <v>683</v>
+      </c>
+      <c r="F181" s="7" t="s">
+        <v>645</v>
+      </c>
+      <c r="G181" s="6" t="s">
+        <v>644</v>
+      </c>
+      <c r="H181" s="6"/>
+      <c r="I181" s="6"/>
+      <c r="J181" s="6"/>
+      <c r="K181" s="6"/>
+      <c r="L181" s="2"/>
+      <c r="M181" s="2"/>
+      <c r="N181" s="16"/>
+      <c r="O181" s="16"/>
+      <c r="P181" s="16"/>
+      <c r="Q181" s="6" t="s">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="182" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A182" s="6" t="s">
         <v>118</v>
       </c>
-      <c r="B179" s="8" t="s">
-        <v>401</v>
-      </c>
-      <c r="C179" s="8" t="s">
-        <v>345</v>
-      </c>
-      <c r="D179" s="8" t="s">
-        <v>339</v>
-      </c>
-      <c r="E179" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="F179" s="8" t="s">
-        <v>577</v>
-      </c>
-      <c r="G179" s="9" t="s">
-        <v>346</v>
-      </c>
-      <c r="H179" s="9" t="s">
-        <v>359</v>
-      </c>
-      <c r="I179" s="9"/>
-      <c r="J179" s="9"/>
-      <c r="K179" s="8" t="s">
-        <v>335</v>
-      </c>
-      <c r="L179" s="8"/>
-      <c r="M179" s="8"/>
-      <c r="N179" s="2" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="180" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A180" s="8" t="s">
+      <c r="B182" s="6" t="s">
+        <v>336</v>
+      </c>
+      <c r="C182" s="6" t="s">
+        <v>618</v>
+      </c>
+      <c r="D182" s="6" t="s">
+        <v>686</v>
+      </c>
+      <c r="E182" s="6" t="s">
+        <v>683</v>
+      </c>
+      <c r="F182" s="7" t="s">
+        <v>648</v>
+      </c>
+      <c r="G182" s="6"/>
+      <c r="H182" s="6"/>
+      <c r="I182" s="6"/>
+      <c r="J182" s="6"/>
+      <c r="K182" s="6"/>
+      <c r="L182" s="2"/>
+      <c r="M182" s="2"/>
+      <c r="N182" s="16"/>
+      <c r="O182" s="16"/>
+      <c r="P182" s="16"/>
+      <c r="Q182" s="6" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="183" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A183" s="6" t="s">
+        <v>620</v>
+      </c>
+      <c r="B183" s="6" t="s">
+        <v>619</v>
+      </c>
+      <c r="C183" s="6" t="s">
+        <v>651</v>
+      </c>
+      <c r="D183" s="6" t="s">
+        <v>686</v>
+      </c>
+      <c r="E183" s="6" t="s">
+        <v>683</v>
+      </c>
+      <c r="F183" s="6" t="s">
+        <v>650</v>
+      </c>
+      <c r="G183" s="6"/>
+      <c r="H183" s="6"/>
+      <c r="I183" s="6"/>
+      <c r="J183" s="6"/>
+      <c r="K183" s="6"/>
+      <c r="L183" s="2"/>
+      <c r="M183" s="2"/>
+      <c r="N183" s="16"/>
+      <c r="O183" s="16"/>
+      <c r="P183" s="16"/>
+      <c r="Q183" s="6" t="s">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="184" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A184" s="6" t="s">
         <v>118</v>
       </c>
-      <c r="B180" s="8" t="s">
-        <v>401</v>
-      </c>
-      <c r="C180" s="8" t="s">
-        <v>345</v>
-      </c>
-      <c r="D180" s="8" t="s">
-        <v>339</v>
-      </c>
-      <c r="E180" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="F180" s="8" t="s">
-        <v>577</v>
-      </c>
-      <c r="G180" s="9" t="s">
-        <v>347</v>
-      </c>
-      <c r="H180" s="9" t="s">
-        <v>360</v>
-      </c>
-      <c r="I180" s="9"/>
-      <c r="J180" s="9"/>
-      <c r="K180" s="8" t="s">
-        <v>335</v>
-      </c>
-      <c r="L180" s="8"/>
-      <c r="M180" s="8"/>
-      <c r="N180" s="2" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="181" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="F181" s="15"/>
-    </row>
-    <row r="182" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="F182" s="15"/>
+      <c r="B184" s="6" t="s">
+        <v>622</v>
+      </c>
+      <c r="C184" s="6" t="s">
+        <v>621</v>
+      </c>
+      <c r="D184" s="6" t="s">
+        <v>686</v>
+      </c>
+      <c r="E184" s="6" t="s">
+        <v>683</v>
+      </c>
+      <c r="F184" s="6" t="s">
+        <v>653</v>
+      </c>
+      <c r="G184" s="6"/>
+      <c r="H184" s="6"/>
+      <c r="I184" s="6"/>
+      <c r="J184" s="6"/>
+      <c r="K184" s="6"/>
+      <c r="L184" s="2"/>
+      <c r="M184" s="2"/>
+      <c r="N184" s="16"/>
+      <c r="O184" s="16"/>
+      <c r="P184" s="16"/>
+      <c r="Q184" s="6" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="185" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A185" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="B185" s="6" t="s">
+        <v>624</v>
+      </c>
+      <c r="C185" s="6" t="s">
+        <v>623</v>
+      </c>
+      <c r="D185" s="6" t="s">
+        <v>686</v>
+      </c>
+      <c r="E185" s="6" t="s">
+        <v>683</v>
+      </c>
+      <c r="F185" s="6" t="s">
+        <v>656</v>
+      </c>
+      <c r="G185" s="6"/>
+      <c r="H185" s="6"/>
+      <c r="I185" s="6"/>
+      <c r="J185" s="6"/>
+      <c r="K185" s="6"/>
+      <c r="L185" s="2"/>
+      <c r="M185" s="2"/>
+      <c r="N185" s="16"/>
+      <c r="O185" s="16"/>
+      <c r="P185" s="16"/>
+      <c r="Q185" s="6" t="s">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="186" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A186" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="B186" s="6" t="s">
+        <v>626</v>
+      </c>
+      <c r="C186" s="6" t="s">
+        <v>625</v>
+      </c>
+      <c r="D186" s="6" t="s">
+        <v>686</v>
+      </c>
+      <c r="E186" s="6" t="s">
+        <v>683</v>
+      </c>
+      <c r="F186" s="6" t="s">
+        <v>657</v>
+      </c>
+      <c r="G186" s="6"/>
+      <c r="H186" s="6"/>
+      <c r="I186" s="6"/>
+      <c r="J186" s="6"/>
+      <c r="K186" s="6"/>
+      <c r="L186" s="2"/>
+      <c r="M186" s="2"/>
+      <c r="N186" s="16"/>
+      <c r="O186" s="16"/>
+      <c r="P186" s="16"/>
+      <c r="Q186" s="6" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="187" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A187" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="B187" s="6" t="s">
+        <v>628</v>
+      </c>
+      <c r="C187" s="6" t="s">
+        <v>627</v>
+      </c>
+      <c r="D187" s="6" t="s">
+        <v>686</v>
+      </c>
+      <c r="E187" s="6" t="s">
+        <v>683</v>
+      </c>
+      <c r="F187" s="6" t="s">
+        <v>658</v>
+      </c>
+      <c r="G187" s="6"/>
+      <c r="H187" s="6"/>
+      <c r="I187" s="6"/>
+      <c r="J187" s="6"/>
+      <c r="K187" s="6" t="s">
+        <v>659</v>
+      </c>
+      <c r="L187" s="2"/>
+      <c r="M187" s="2"/>
+      <c r="N187" s="16"/>
+      <c r="O187" s="16"/>
+      <c r="P187" s="16"/>
+      <c r="Q187" s="6" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="188" spans="1:17" ht="95.25" x14ac:dyDescent="0.3">
+      <c r="A188" s="6" t="s">
+        <v>620</v>
+      </c>
+      <c r="B188" s="6" t="s">
+        <v>631</v>
+      </c>
+      <c r="C188" s="6" t="s">
+        <v>629</v>
+      </c>
+      <c r="D188" s="6" t="s">
+        <v>687</v>
+      </c>
+      <c r="E188" s="6" t="s">
+        <v>683</v>
+      </c>
+      <c r="F188" s="6" t="s">
+        <v>662</v>
+      </c>
+      <c r="G188" s="6"/>
+      <c r="H188" s="6"/>
+      <c r="I188" s="6"/>
+      <c r="J188" s="6"/>
+      <c r="K188" s="6" t="s">
+        <v>663</v>
+      </c>
+      <c r="L188" s="2"/>
+      <c r="M188" s="21" t="s">
+        <v>664</v>
+      </c>
+      <c r="N188" s="16"/>
+      <c r="O188" s="16"/>
+      <c r="P188" s="16"/>
+      <c r="Q188" s="6" t="s">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="189" spans="1:17" ht="162.75" x14ac:dyDescent="0.3">
+      <c r="A189" s="6" t="s">
+        <v>620</v>
+      </c>
+      <c r="B189" s="6" t="s">
+        <v>632</v>
+      </c>
+      <c r="C189" s="6" t="s">
+        <v>630</v>
+      </c>
+      <c r="D189" s="6" t="s">
+        <v>687</v>
+      </c>
+      <c r="E189" s="6" t="s">
+        <v>683</v>
+      </c>
+      <c r="F189" s="6" t="s">
+        <v>665</v>
+      </c>
+      <c r="G189" s="6"/>
+      <c r="H189" s="6"/>
+      <c r="I189" s="6"/>
+      <c r="J189" s="6"/>
+      <c r="K189" s="5" t="s">
+        <v>666</v>
+      </c>
+      <c r="L189" s="2"/>
+      <c r="M189" s="21" t="s">
+        <v>668</v>
+      </c>
+      <c r="N189" s="16"/>
+      <c r="O189" s="16"/>
+      <c r="P189" s="16"/>
+      <c r="Q189" s="6" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="190" spans="1:17" ht="135.75" x14ac:dyDescent="0.3">
+      <c r="A190" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="B190" s="6" t="s">
+        <v>634</v>
+      </c>
+      <c r="C190" s="6" t="s">
+        <v>633</v>
+      </c>
+      <c r="D190" s="6" t="s">
+        <v>687</v>
+      </c>
+      <c r="E190" s="6" t="s">
+        <v>683</v>
+      </c>
+      <c r="F190" s="6" t="s">
+        <v>665</v>
+      </c>
+      <c r="G190" s="6"/>
+      <c r="H190" s="6"/>
+      <c r="I190" s="6"/>
+      <c r="J190" s="6"/>
+      <c r="K190" s="5" t="s">
+        <v>666</v>
+      </c>
+      <c r="L190" s="2"/>
+      <c r="M190" s="21" t="s">
+        <v>670</v>
+      </c>
+      <c r="N190" s="16"/>
+      <c r="O190" s="16"/>
+      <c r="P190" s="16"/>
+      <c r="Q190" s="6" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="191" spans="1:17" ht="149.25" x14ac:dyDescent="0.3">
+      <c r="A191" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="B191" s="6" t="s">
+        <v>636</v>
+      </c>
+      <c r="C191" s="6" t="s">
+        <v>635</v>
+      </c>
+      <c r="D191" s="6" t="s">
+        <v>687</v>
+      </c>
+      <c r="E191" s="6" t="s">
+        <v>683</v>
+      </c>
+      <c r="F191" s="6" t="s">
+        <v>678</v>
+      </c>
+      <c r="G191" s="6"/>
+      <c r="H191" s="6"/>
+      <c r="I191" s="6"/>
+      <c r="J191" s="6"/>
+      <c r="K191" s="6" t="s">
+        <v>663</v>
+      </c>
+      <c r="L191" s="2"/>
+      <c r="M191" s="21" t="s">
+        <v>672</v>
+      </c>
+      <c r="N191" s="16"/>
+      <c r="O191" s="16"/>
+      <c r="P191" s="16"/>
+      <c r="Q191" s="6" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="192" spans="1:17" ht="27" x14ac:dyDescent="0.3">
+      <c r="A192" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="B192" s="6" t="s">
+        <v>639</v>
+      </c>
+      <c r="C192" s="6" t="s">
+        <v>637</v>
+      </c>
+      <c r="D192" s="6" t="s">
+        <v>687</v>
+      </c>
+      <c r="E192" s="6" t="s">
+        <v>683</v>
+      </c>
+      <c r="F192" s="6"/>
+      <c r="G192" s="7" t="s">
+        <v>673</v>
+      </c>
+      <c r="H192" s="6"/>
+      <c r="I192" s="6"/>
+      <c r="J192" s="6"/>
+      <c r="K192" s="6" t="s">
+        <v>674</v>
+      </c>
+      <c r="L192" s="2"/>
+      <c r="M192" s="2"/>
+      <c r="N192" s="16"/>
+      <c r="O192" s="16"/>
+      <c r="P192" s="16"/>
+      <c r="Q192" s="6" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="193" spans="1:17" ht="54.75" x14ac:dyDescent="0.3">
+      <c r="A193" s="6" t="s">
+        <v>620</v>
+      </c>
+      <c r="B193" s="6" t="s">
+        <v>631</v>
+      </c>
+      <c r="C193" s="6" t="s">
+        <v>638</v>
+      </c>
+      <c r="D193" s="6" t="s">
+        <v>687</v>
+      </c>
+      <c r="E193" s="6" t="s">
+        <v>683</v>
+      </c>
+      <c r="F193" s="6" t="s">
+        <v>677</v>
+      </c>
+      <c r="G193" s="6"/>
+      <c r="H193" s="6"/>
+      <c r="I193" s="6"/>
+      <c r="J193" s="6"/>
+      <c r="K193" s="6" t="s">
+        <v>663</v>
+      </c>
+      <c r="L193" s="2"/>
+      <c r="M193" s="21" t="s">
+        <v>679</v>
+      </c>
+      <c r="N193" s="16"/>
+      <c r="O193" s="16"/>
+      <c r="P193" s="16"/>
+      <c r="Q193" s="6" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="194" spans="1:17" ht="27.75" x14ac:dyDescent="0.3">
+      <c r="A194" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="B194" s="6" t="s">
+        <v>641</v>
+      </c>
+      <c r="C194" s="6" t="s">
+        <v>640</v>
+      </c>
+      <c r="D194" s="6" t="s">
+        <v>687</v>
+      </c>
+      <c r="E194" s="6" t="s">
+        <v>683</v>
+      </c>
+      <c r="F194" s="6" t="s">
+        <v>680</v>
+      </c>
+      <c r="G194" s="6"/>
+      <c r="H194" s="6"/>
+      <c r="I194" s="6"/>
+      <c r="J194" s="6"/>
+      <c r="K194" s="6" t="s">
+        <v>682</v>
+      </c>
+      <c r="L194" s="2"/>
+      <c r="M194" s="21" t="s">
+        <v>681</v>
+      </c>
+      <c r="N194" s="16"/>
+      <c r="O194" s="16"/>
+      <c r="P194" s="16"/>
+      <c r="Q194" s="6" t="s">
+        <v>642</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="B1:N180" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
-  <mergeCells count="1">
-    <mergeCell ref="F181:F182"/>
-  </mergeCells>
+  <autoFilter ref="B1:Q180" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="N177" r:id="rId1" xr:uid="{E8A5EE79-38DC-470C-9E4B-60B8DB179166}"/>
-    <hyperlink ref="N175" r:id="rId2" xr:uid="{B514AFC6-F2CC-453E-A7EE-749BE8F59F63}"/>
-    <hyperlink ref="N176" r:id="rId3" xr:uid="{D2C8DCF1-2A86-40FB-A718-5DFF8C67103B}"/>
-    <hyperlink ref="N178" r:id="rId4" xr:uid="{2526EBF2-78DF-4B4D-A609-DDD4E216E820}"/>
+    <hyperlink ref="Q177" r:id="rId1" xr:uid="{E8A5EE79-38DC-470C-9E4B-60B8DB179166}"/>
+    <hyperlink ref="Q175" r:id="rId2" xr:uid="{B514AFC6-F2CC-453E-A7EE-749BE8F59F63}"/>
+    <hyperlink ref="Q176" r:id="rId3" xr:uid="{D2C8DCF1-2A86-40FB-A718-5DFF8C67103B}"/>
+    <hyperlink ref="Q178" r:id="rId4" xr:uid="{2526EBF2-78DF-4B4D-A609-DDD4E216E820}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/app/convert/forest_sample_template.xlsx
+++ b/app/convert/forest_sample_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TAX-JUNGYOON\forest-app\app\convert\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{620D4363-2001-48AF-95C1-8B089E8504AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{728113FC-F1A6-4A93-94FE-9C5D519B380F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="658" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2313" uniqueCount="688">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2331" uniqueCount="715">
   <si>
     <t>시설명</t>
   </si>
@@ -1879,11 +1879,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>어울림(2F)
-(히노끼탕) 2002, 2004</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>5인실 (선미도, 굴업도, 초지도)
 → 전망 좋음
 → 평일 58,000 / 주말 106,000</t>
@@ -2481,6 +2476,163 @@
   </si>
   <si>
     <t>캠핑장</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>본관 203호
+본관 204호
+본관 205호</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>어울림(2F)
+(히노끼탕) 2002, 2004
+6인실 평일 220,000원 / 주말 280,000원</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">지정객실: 201,215,216,217,503,504,716,717,723,727  </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>데크3
+데크7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.foresttrip.go.kr/indvz/main.do?hmpgId=ID02030034</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.foresttrip.go.kr/indvz/main.do?hmpgId=ID02030099</t>
+  </si>
+  <si>
+    <t>https://www.foresttrip.go.kr/indvz/main.do?hmpgId=ID02030036</t>
+  </si>
+  <si>
+    <t>https://www.foresttrip.go.kr/indvz/main.do?hmpgId=ID02030078</t>
+  </si>
+  <si>
+    <t>https://www.foresttrip.go.kr/indvz/main.do?hmpgId=ID02030119</t>
+  </si>
+  <si>
+    <t>https://www.foresttrip.go.kr/indvz/main.do?hmpgId=ID02030094</t>
+  </si>
+  <si>
+    <t>https://www.foresttrip.go.kr/indvz/main.do?hmpgId=ID02030004</t>
+  </si>
+  <si>
+    <t>숲속의집 
+딱따구리(6인실)
+담비(4인실)
+진달래(4인실)
+갈참나무(8인실)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>단풍나무1, 머루1,2, 전나무1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>도민 및 도내 소재 가족친화인증 기업·기관 재직자는 숙박시설의 40퍼센트 범위에서 우선 예약</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>들국화 (15인/72㎡)
+물병자리 (연립동 1층) (3인/22㎡)
+별비별 (12인/56㎡)
+붉은별 (8인/46㎡)
+사자자리 (연립동 2층) (8인/41㎡)
+양자리 (연립동 1층) (4인/21㎡)
+인동초 (15인/72㎡)
+황소자리 (연립동 2층) (4인/21㎡)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>관불산(302) (6인/32㎡)
+월성산(503) (6인/32㎡)
+호태산(505) (6인/32㎡)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>숙박동 꾀꼬리(35㎡, 4인실)
+숙박동 백  송(66㎡, 10인실)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>분기별우선예약대상시설변경
+지역주민우선예약정책참고</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>숲속의집
+5인실 투구꽃, 구절초, 참나리, 괭이밥
+8인실 노루귀
+휴양관
+5인실 201, 204
+8인실 101</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>월별대상객실변동
+홈페이지확인
+A3, D1, 동백동
+A2, B1, 나무꾼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(다음월 선착순)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(6주차 월요일까지 1주일치)
+차량진입불가객실
+잣나무1
+잣나무2
+트리하우스 느티나무1
+트리하우스 느티나무2
+옛집
+비둘기
+참새
+낙엽송1
+낙엽송2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>숲속의 집(2경-금대지리)
+휴양관(202호)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>양산시민 40%우선배정추첨</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">숲속의 집(월봉산)
+휴양관(202호) </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>숲속의집 1001, 1005호, 
+숲속휴양관 201호</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>숲속의 집(숲2호)
+휴양관(105호, 205호)
+야영데크(14~21)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>숲속의집
+1호
+휴양관
+103호
+104호
+203호
+204호
+글램핑
+1동, 2동</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2599,7 +2751,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -2658,12 +2810,29 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
     <cellStyle name="하이퍼링크" xfId="1" builtinId="8"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -2970,12 +3139,13 @@
     <col min="4" max="4" width="9.875" style="18" customWidth="1"/>
     <col min="5" max="5" width="8.25" style="18" customWidth="1"/>
     <col min="6" max="6" width="36.875" style="18" customWidth="1"/>
-    <col min="7" max="7" width="47.25" style="18" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="47.25" style="18" customWidth="1"/>
     <col min="8" max="8" width="28.375" style="18" customWidth="1"/>
     <col min="9" max="9" width="15.25" style="18" customWidth="1"/>
     <col min="10" max="10" width="55.375" style="18" customWidth="1"/>
     <col min="11" max="11" width="36.875" style="18" customWidth="1"/>
-    <col min="12" max="13" width="36.875" style="1" customWidth="1"/>
+    <col min="12" max="12" width="33.375" style="1" customWidth="1"/>
+    <col min="13" max="13" width="36.875" style="1" customWidth="1"/>
     <col min="14" max="16" width="36.875" style="17" customWidth="1"/>
     <col min="17" max="17" width="65.375" style="18" bestFit="1" customWidth="1"/>
   </cols>
@@ -3021,13 +3191,13 @@
         <v>577</v>
       </c>
       <c r="N1" s="16" t="s">
+        <v>604</v>
+      </c>
+      <c r="O1" s="16" t="s">
         <v>605</v>
       </c>
-      <c r="O1" s="16" t="s">
+      <c r="P1" s="16" t="s">
         <v>606</v>
-      </c>
-      <c r="P1" s="16" t="s">
-        <v>607</v>
       </c>
       <c r="Q1" s="6" t="s">
         <v>330</v>
@@ -3050,7 +3220,7 @@
         <v>113</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="G2" s="5" t="s">
         <v>349</v>
@@ -3070,13 +3240,13 @@
       <c r="L2" s="5"/>
       <c r="M2" s="5"/>
       <c r="N2" s="13" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="O2" s="13" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="P2" s="13" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="Q2" s="5" t="s">
         <v>413</v>
@@ -3113,13 +3283,13 @@
       <c r="L3" s="5"/>
       <c r="M3" s="5"/>
       <c r="N3" s="14" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="O3" s="14" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="P3" s="14" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="Q3" s="5" t="s">
         <v>411</v>
@@ -3142,7 +3312,7 @@
         <v>113</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="G4" s="5" t="s">
         <v>349</v>
@@ -3162,13 +3332,13 @@
       <c r="L4" s="5"/>
       <c r="M4" s="5"/>
       <c r="N4" s="13" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="O4" s="13" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="P4" s="13" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="Q4" s="5" t="s">
         <v>410</v>
@@ -3191,7 +3361,7 @@
         <v>113</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="G5" s="5" t="s">
         <v>349</v>
@@ -3211,13 +3381,13 @@
       <c r="L5" s="5"/>
       <c r="M5" s="5"/>
       <c r="N5" s="13" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="O5" s="14" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="P5" s="13" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="Q5" s="5" t="s">
         <v>412</v>
@@ -3240,7 +3410,7 @@
         <v>113</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="G6" s="5" t="s">
         <v>349</v>
@@ -3259,16 +3429,16 @@
       </c>
       <c r="L6" s="5"/>
       <c r="M6" s="11" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="N6" s="13" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="O6" s="13" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="P6" s="13" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="Q6" s="5" t="s">
         <v>409</v>
@@ -3291,7 +3461,7 @@
         <v>113</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="G7" s="5" t="s">
         <v>349</v>
@@ -3311,13 +3481,13 @@
       <c r="L7" s="5"/>
       <c r="M7" s="5"/>
       <c r="N7" s="13" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="O7" s="13" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="P7" s="13" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="Q7" s="5" t="s">
         <v>414</v>
@@ -3340,7 +3510,7 @@
         <v>113</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="G8" s="5" t="s">
         <v>349</v>
@@ -3360,13 +3530,13 @@
       <c r="L8" s="5"/>
       <c r="M8" s="5"/>
       <c r="N8" s="13" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="O8" s="13" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="P8" s="13" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="Q8" s="5" t="s">
         <v>417</v>
@@ -3389,7 +3559,7 @@
         <v>113</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="G9" s="5" t="s">
         <v>349</v>
@@ -3409,13 +3579,13 @@
       <c r="L9" s="5"/>
       <c r="M9" s="5"/>
       <c r="N9" s="13" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="O9" s="13" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="P9" s="13" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="Q9" s="5" t="s">
         <v>416</v>
@@ -3438,7 +3608,7 @@
         <v>113</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="G10" s="5" t="s">
         <v>349</v>
@@ -3458,13 +3628,13 @@
       <c r="L10" s="5"/>
       <c r="M10" s="5"/>
       <c r="N10" s="13" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="O10" s="13" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="P10" s="13" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="Q10" s="5" t="s">
         <v>419</v>
@@ -3487,7 +3657,7 @@
         <v>113</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="G11" s="5" t="s">
         <v>349</v>
@@ -3507,13 +3677,13 @@
       <c r="L11" s="5"/>
       <c r="M11" s="5"/>
       <c r="N11" s="13" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="O11" s="13" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="P11" s="13" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="Q11" s="5" t="s">
         <v>421</v>
@@ -3536,7 +3706,7 @@
         <v>113</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="G12" s="5" t="s">
         <v>349</v>
@@ -3555,16 +3725,16 @@
       </c>
       <c r="L12" s="5"/>
       <c r="M12" s="10" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="N12" s="13" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="O12" s="13" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="P12" s="13" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="Q12" s="5" t="s">
         <v>420</v>
@@ -3587,7 +3757,7 @@
         <v>113</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="G13" s="5" t="s">
         <v>349</v>
@@ -3607,13 +3777,13 @@
       <c r="L13" s="5"/>
       <c r="M13" s="5"/>
       <c r="N13" s="13" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="O13" s="13" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="P13" s="13" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="Q13" s="5" t="s">
         <v>424</v>
@@ -3636,7 +3806,7 @@
         <v>113</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="G14" s="5" t="s">
         <v>349</v>
@@ -3656,13 +3826,13 @@
       <c r="L14" s="5"/>
       <c r="M14" s="5"/>
       <c r="N14" s="13" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="O14" s="13" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="P14" s="13" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="Q14" s="5" t="s">
         <v>415</v>
@@ -3685,7 +3855,7 @@
         <v>113</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="G15" s="5" t="s">
         <v>349</v>
@@ -3705,13 +3875,13 @@
       <c r="L15" s="5"/>
       <c r="M15" s="5"/>
       <c r="N15" s="13" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="O15" s="13" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="P15" s="13" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="Q15" s="5" t="s">
         <v>422</v>
@@ -3734,7 +3904,7 @@
         <v>113</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="G16" s="5" t="s">
         <v>349</v>
@@ -3754,13 +3924,13 @@
       <c r="L16" s="5"/>
       <c r="M16" s="5"/>
       <c r="N16" s="13" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="O16" s="13" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="P16" s="13" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="Q16" s="5" t="s">
         <v>425</v>
@@ -3783,7 +3953,7 @@
         <v>113</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="G17" s="5" t="s">
         <v>349</v>
@@ -3803,13 +3973,13 @@
       <c r="L17" s="5"/>
       <c r="M17" s="5"/>
       <c r="N17" s="13" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="O17" s="13" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="P17" s="13" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="Q17" s="5" t="s">
         <v>418</v>
@@ -3832,7 +4002,7 @@
         <v>113</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="G18" s="5" t="s">
         <v>349</v>
@@ -3852,13 +4022,13 @@
       <c r="L18" s="5"/>
       <c r="M18" s="5"/>
       <c r="N18" s="13" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="O18" s="13" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="P18" s="13" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="Q18" s="5" t="s">
         <v>423</v>
@@ -3881,7 +4051,7 @@
         <v>113</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="G19" s="5" t="s">
         <v>349</v>
@@ -3901,13 +4071,13 @@
       <c r="L19" s="5"/>
       <c r="M19" s="5"/>
       <c r="N19" s="13" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="O19" s="13" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="P19" s="13" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="Q19" s="5" t="s">
         <v>427</v>
@@ -3930,7 +4100,7 @@
         <v>113</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="G20" s="5" t="s">
         <v>349</v>
@@ -3949,16 +4119,16 @@
       </c>
       <c r="L20" s="5"/>
       <c r="M20" s="10" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="N20" s="13" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="O20" s="14" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="P20" s="13" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="Q20" s="5" t="s">
         <v>426</v>
@@ -3981,7 +4151,7 @@
         <v>113</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="G21" s="5" t="s">
         <v>349</v>
@@ -4001,13 +4171,13 @@
       <c r="L21" s="5"/>
       <c r="M21" s="5"/>
       <c r="N21" s="14" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="O21" s="13" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="P21" s="13" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="Q21" s="5" t="s">
         <v>430</v>
@@ -4030,7 +4200,7 @@
         <v>113</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="G22" s="5" t="s">
         <v>349</v>
@@ -4050,13 +4220,13 @@
       <c r="L22" s="5"/>
       <c r="M22" s="5"/>
       <c r="N22" s="13" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="O22" s="13" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="P22" s="13" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="Q22" s="5" t="s">
         <v>429</v>
@@ -4079,7 +4249,7 @@
         <v>113</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="G23" s="5" t="s">
         <v>349</v>
@@ -4099,13 +4269,13 @@
       <c r="L23" s="5"/>
       <c r="M23" s="5"/>
       <c r="N23" s="13" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="O23" s="14" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="P23" s="13" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="Q23" s="5" t="s">
         <v>428</v>
@@ -4128,7 +4298,7 @@
         <v>113</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="G24" s="5" t="s">
         <v>349</v>
@@ -4148,13 +4318,13 @@
       <c r="L24" s="5"/>
       <c r="M24" s="5"/>
       <c r="N24" s="14" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="O24" s="14" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="P24" s="14" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="Q24" s="5" t="s">
         <v>431</v>
@@ -4177,7 +4347,7 @@
         <v>113</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="G25" s="5" t="s">
         <v>349</v>
@@ -4197,13 +4367,13 @@
       <c r="L25" s="5"/>
       <c r="M25" s="5"/>
       <c r="N25" s="13" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="O25" s="13" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="P25" s="13" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="Q25" s="5" t="s">
         <v>432</v>
@@ -4226,7 +4396,7 @@
         <v>113</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="G26" s="5" t="s">
         <v>349</v>
@@ -4246,13 +4416,13 @@
       <c r="L26" s="5"/>
       <c r="M26" s="5"/>
       <c r="N26" s="13" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="O26" s="13" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="P26" s="13" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="Q26" s="5" t="s">
         <v>433</v>
@@ -4275,7 +4445,7 @@
         <v>113</v>
       </c>
       <c r="F27" s="5" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="G27" s="5" t="s">
         <v>349</v>
@@ -4295,13 +4465,13 @@
       <c r="L27" s="5"/>
       <c r="M27" s="5"/>
       <c r="N27" s="13" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="O27" s="14" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="P27" s="13" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="Q27" s="5" t="s">
         <v>434</v>
@@ -4324,7 +4494,7 @@
         <v>113</v>
       </c>
       <c r="F28" s="5" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="G28" s="5" t="s">
         <v>349</v>
@@ -4343,16 +4513,16 @@
       </c>
       <c r="L28" s="5"/>
       <c r="M28" s="10" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="N28" s="13" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="O28" s="13" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="P28" s="13" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="Q28" s="5" t="s">
         <v>437</v>
@@ -4375,7 +4545,7 @@
         <v>113</v>
       </c>
       <c r="F29" s="5" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="G29" s="5" t="s">
         <v>349</v>
@@ -4395,13 +4565,13 @@
       <c r="L29" s="5"/>
       <c r="M29" s="5"/>
       <c r="N29" s="13" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="O29" s="13" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="P29" s="13" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="Q29" s="5" t="s">
         <v>435</v>
@@ -4424,7 +4594,7 @@
         <v>113</v>
       </c>
       <c r="F30" s="5" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="G30" s="5" t="s">
         <v>349</v>
@@ -4444,13 +4614,13 @@
       <c r="L30" s="5"/>
       <c r="M30" s="5"/>
       <c r="N30" s="13" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="O30" s="13" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="P30" s="13" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="Q30" s="5" t="s">
         <v>436</v>
@@ -4473,7 +4643,7 @@
         <v>113</v>
       </c>
       <c r="F31" s="5" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="G31" s="5" t="s">
         <v>349</v>
@@ -4493,13 +4663,13 @@
       <c r="L31" s="5"/>
       <c r="M31" s="5"/>
       <c r="N31" s="13" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="O31" s="13" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="P31" s="13" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="Q31" s="5" t="s">
         <v>439</v>
@@ -4522,7 +4692,7 @@
         <v>113</v>
       </c>
       <c r="F32" s="5" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="G32" s="5" t="s">
         <v>349</v>
@@ -4541,16 +4711,16 @@
       </c>
       <c r="L32" s="5"/>
       <c r="M32" s="10" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="N32" s="13" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="O32" s="13" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="P32" s="13" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="Q32" s="5" t="s">
         <v>438</v>
@@ -4573,7 +4743,7 @@
         <v>113</v>
       </c>
       <c r="F33" s="5" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="G33" s="5" t="s">
         <v>349</v>
@@ -4593,13 +4763,13 @@
       <c r="L33" s="5"/>
       <c r="M33" s="5"/>
       <c r="N33" s="13" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="O33" s="13" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="P33" s="13" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="Q33" s="5" t="s">
         <v>440</v>
@@ -4622,7 +4792,7 @@
         <v>113</v>
       </c>
       <c r="F34" s="5" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="G34" s="5" t="s">
         <v>349</v>
@@ -4642,13 +4812,13 @@
       <c r="L34" s="5"/>
       <c r="M34" s="5"/>
       <c r="N34" s="13" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="O34" s="13" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="P34" s="13" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="Q34" s="5" t="s">
         <v>441</v>
@@ -4671,7 +4841,7 @@
         <v>113</v>
       </c>
       <c r="F35" s="5" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="G35" s="5" t="s">
         <v>349</v>
@@ -4691,13 +4861,13 @@
       <c r="L35" s="5"/>
       <c r="M35" s="5"/>
       <c r="N35" s="13" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="O35" s="13" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="P35" s="13" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="Q35" s="5" t="s">
         <v>443</v>
@@ -4720,7 +4890,7 @@
         <v>113</v>
       </c>
       <c r="F36" s="5" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="G36" s="5" t="s">
         <v>349</v>
@@ -4740,13 +4910,13 @@
       <c r="L36" s="5"/>
       <c r="M36" s="5"/>
       <c r="N36" s="13" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="O36" s="13" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="P36" s="13" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="Q36" s="5" t="s">
         <v>442</v>
@@ -4769,7 +4939,7 @@
         <v>113</v>
       </c>
       <c r="F37" s="5" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="G37" s="5" t="s">
         <v>349</v>
@@ -4789,13 +4959,13 @@
       <c r="L37" s="5"/>
       <c r="M37" s="5"/>
       <c r="N37" s="14" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="O37" s="14" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="P37" s="14" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="Q37" s="5" t="s">
         <v>445</v>
@@ -4818,7 +4988,7 @@
         <v>113</v>
       </c>
       <c r="F38" s="5" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="G38" s="5" t="s">
         <v>349</v>
@@ -4838,13 +5008,13 @@
       <c r="L38" s="5"/>
       <c r="M38" s="5"/>
       <c r="N38" s="13" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="O38" s="13" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="P38" s="14" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="Q38" s="5" t="s">
         <v>446</v>
@@ -4867,7 +5037,7 @@
         <v>113</v>
       </c>
       <c r="F39" s="5" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="G39" s="5" t="s">
         <v>349</v>
@@ -4887,13 +5057,13 @@
       <c r="L39" s="5"/>
       <c r="M39" s="5"/>
       <c r="N39" s="13" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="O39" s="13" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="P39" s="13" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="Q39" s="5" t="s">
         <v>448</v>
@@ -4916,7 +5086,7 @@
         <v>113</v>
       </c>
       <c r="F40" s="5" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="G40" s="5" t="s">
         <v>349</v>
@@ -4936,13 +5106,13 @@
       <c r="L40" s="5"/>
       <c r="M40" s="5"/>
       <c r="N40" s="14" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="O40" s="13" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="P40" s="13" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="Q40" s="5" t="s">
         <v>449</v>
@@ -4965,7 +5135,7 @@
         <v>113</v>
       </c>
       <c r="F41" s="5" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="G41" s="5" t="s">
         <v>349</v>
@@ -4985,13 +5155,13 @@
       <c r="L41" s="5"/>
       <c r="M41" s="5"/>
       <c r="N41" s="14" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="O41" s="13" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="P41" s="13" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="Q41" s="5" t="s">
         <v>444</v>
@@ -5014,7 +5184,7 @@
         <v>113</v>
       </c>
       <c r="F42" s="5" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="G42" s="5" t="s">
         <v>349</v>
@@ -5034,13 +5204,13 @@
       <c r="L42" s="5"/>
       <c r="M42" s="5"/>
       <c r="N42" s="13" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="O42" s="13" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="P42" s="13" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="Q42" s="5" t="s">
         <v>450</v>
@@ -5063,7 +5233,7 @@
         <v>113</v>
       </c>
       <c r="F43" s="5" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="G43" s="5" t="s">
         <v>349</v>
@@ -5083,13 +5253,13 @@
       <c r="L43" s="5"/>
       <c r="M43" s="5"/>
       <c r="N43" s="13" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="O43" s="13" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="P43" s="13" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="Q43" s="5" t="s">
         <v>447</v>
@@ -5112,7 +5282,7 @@
         <v>113</v>
       </c>
       <c r="F44" s="5" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="G44" s="5" t="s">
         <v>349</v>
@@ -5132,13 +5302,13 @@
       <c r="L44" s="5"/>
       <c r="M44" s="5"/>
       <c r="N44" s="13" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="O44" s="13" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="P44" s="13" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="Q44" s="5" t="s">
         <v>452</v>
@@ -5161,7 +5331,7 @@
         <v>113</v>
       </c>
       <c r="F45" s="5" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="G45" s="5" t="s">
         <v>349</v>
@@ -5181,13 +5351,13 @@
       <c r="L45" s="10"/>
       <c r="M45" s="10"/>
       <c r="N45" s="13" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="O45" s="13" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="P45" s="13" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="Q45" s="5" t="s">
         <v>454</v>
@@ -5210,7 +5380,7 @@
         <v>113</v>
       </c>
       <c r="F46" s="5" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="G46" s="5" t="s">
         <v>349</v>
@@ -5230,13 +5400,13 @@
       <c r="L46" s="5"/>
       <c r="M46" s="5"/>
       <c r="N46" s="14" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="O46" s="13" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="P46" s="13" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="Q46" s="5" t="s">
         <v>451</v>
@@ -5259,7 +5429,7 @@
         <v>113</v>
       </c>
       <c r="F47" s="5" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="G47" s="5" t="s">
         <v>349</v>
@@ -5279,13 +5449,13 @@
       <c r="L47" s="5"/>
       <c r="M47" s="5"/>
       <c r="N47" s="13" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="O47" s="14" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="P47" s="13" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="Q47" s="5" t="s">
         <v>453</v>
@@ -5308,7 +5478,7 @@
         <v>113</v>
       </c>
       <c r="F48" s="5" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="G48" s="5" t="s">
         <v>349</v>
@@ -5328,13 +5498,13 @@
       <c r="L48" s="5"/>
       <c r="M48" s="5"/>
       <c r="N48" s="13" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="O48" s="13" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="P48" s="13" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="Q48" s="5" t="s">
         <v>455</v>
@@ -5367,13 +5537,13 @@
       <c r="L49" s="5"/>
       <c r="M49" s="5"/>
       <c r="N49" s="13" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="O49" s="13" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="P49" s="13" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="Q49" s="5" t="s">
         <v>456</v>
@@ -5408,16 +5578,16 @@
       <c r="L50" s="9"/>
       <c r="M50" s="9"/>
       <c r="N50" s="13" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="O50" s="13" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="P50" s="13" t="s">
-        <v>611</v>
-      </c>
-      <c r="Q50" s="20" t="s">
-        <v>470</v>
+        <v>610</v>
+      </c>
+      <c r="Q50" s="8" t="s">
+        <v>692</v>
       </c>
     </row>
     <row r="51" spans="1:17" x14ac:dyDescent="0.3">
@@ -5449,13 +5619,13 @@
       <c r="L51" s="5"/>
       <c r="M51" s="5"/>
       <c r="N51" s="14" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="O51" s="13" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="P51" s="13" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="Q51" s="5" t="s">
         <v>462</v>
@@ -5492,13 +5662,13 @@
       <c r="L52" s="5"/>
       <c r="M52" s="5"/>
       <c r="N52" s="13" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="O52" s="14" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="P52" s="13" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="Q52" s="5" t="s">
         <v>470</v>
@@ -5531,19 +5701,19 @@
         <v>366</v>
       </c>
       <c r="L53" s="5" t="s">
+        <v>601</v>
+      </c>
+      <c r="M53" s="5" t="s">
         <v>602</v>
       </c>
-      <c r="M53" s="5" t="s">
-        <v>603</v>
-      </c>
       <c r="N53" s="14" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="O53" s="14" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="P53" s="14" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="Q53" s="5" t="s">
         <v>463</v>
@@ -5579,16 +5749,16 @@
         <v>576</v>
       </c>
       <c r="M54" s="10" t="s">
-        <v>578</v>
+        <v>688</v>
       </c>
       <c r="N54" s="13" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="O54" s="13" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="P54" s="13" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="Q54" s="5" t="s">
         <v>459</v>
@@ -5625,19 +5795,19 @@
       <c r="L55" s="2"/>
       <c r="M55" s="2"/>
       <c r="N55" s="13" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="O55" s="13" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="P55" s="13" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="Q55" s="6" t="s">
         <v>461</v>
       </c>
     </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:17" ht="27" x14ac:dyDescent="0.3">
       <c r="A56" s="4" t="s">
         <v>114</v>
       </c>
@@ -5663,16 +5833,18 @@
       <c r="K56" s="5" t="s">
         <v>370</v>
       </c>
-      <c r="L56" s="5"/>
+      <c r="L56" s="5" t="s">
+        <v>690</v>
+      </c>
       <c r="M56" s="5"/>
       <c r="N56" s="13" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="O56" s="13" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="P56" s="13" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="Q56" s="5" t="s">
         <v>464</v>
@@ -5707,13 +5879,13 @@
       <c r="L57" s="5"/>
       <c r="M57" s="5"/>
       <c r="N57" s="14" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="O57" s="14" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="P57" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="Q57" s="5" t="s">
         <v>465</v>
@@ -5748,19 +5920,19 @@
       <c r="L58" s="5"/>
       <c r="M58" s="5"/>
       <c r="N58" s="14" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="O58" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="P58" s="14" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="Q58" s="5" t="s">
         <v>466</v>
       </c>
     </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:17" ht="67.5" x14ac:dyDescent="0.3">
       <c r="A59" s="4" t="s">
         <v>114</v>
       </c>
@@ -5786,16 +5958,18 @@
       <c r="K59" s="5" t="s">
         <v>370</v>
       </c>
-      <c r="L59" s="5"/>
+      <c r="L59" s="5" t="s">
+        <v>698</v>
+      </c>
       <c r="M59" s="5"/>
       <c r="N59" s="14" t="s">
+        <v>610</v>
+      </c>
+      <c r="O59" s="14" t="s">
         <v>611</v>
       </c>
-      <c r="O59" s="14" t="s">
-        <v>612</v>
-      </c>
       <c r="P59" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="Q59" s="5" t="s">
         <v>457</v>
@@ -5830,13 +6004,13 @@
       <c r="L60" s="5"/>
       <c r="M60" s="5"/>
       <c r="N60" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="O60" s="14" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="P60" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="Q60" s="5" t="s">
         <v>458</v>
@@ -5873,13 +6047,13 @@
       <c r="L61" s="5"/>
       <c r="M61" s="5"/>
       <c r="N61" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="O61" s="14" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="P61" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="Q61" s="5" t="s">
         <v>467</v>
@@ -5916,13 +6090,13 @@
       <c r="L62" s="5"/>
       <c r="M62" s="5"/>
       <c r="N62" s="14" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="O62" s="14" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="P62" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="Q62" s="5" t="s">
         <v>468</v>
@@ -5957,13 +6131,13 @@
       <c r="L63" s="5"/>
       <c r="M63" s="5"/>
       <c r="N63" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="O63" s="14" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="P63" s="14" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="Q63" s="5" t="s">
         <v>469</v>
@@ -5998,13 +6172,13 @@
       <c r="L64" s="5"/>
       <c r="M64" s="5"/>
       <c r="N64" s="14" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="O64" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="P64" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="Q64" s="5" t="s">
         <v>460</v>
@@ -6039,13 +6213,13 @@
       <c r="L65" s="5"/>
       <c r="M65" s="5"/>
       <c r="N65" s="14" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="O65" s="14" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="P65" s="14" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="Q65" s="5" t="s">
         <v>477</v>
@@ -6079,16 +6253,16 @@
       </c>
       <c r="L66" s="5"/>
       <c r="M66" s="10" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="N66" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="O66" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="P66" s="14" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="Q66" s="5" t="s">
         <v>474</v>
@@ -6123,13 +6297,13 @@
       <c r="L67" s="5"/>
       <c r="M67" s="5"/>
       <c r="N67" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="O67" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="P67" s="14" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="Q67" s="5" t="s">
         <v>475</v>
@@ -6164,13 +6338,13 @@
       <c r="L68" s="5"/>
       <c r="M68" s="5"/>
       <c r="N68" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="O68" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="P68" s="14" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="Q68" s="5" t="s">
         <v>476</v>
@@ -6205,13 +6379,13 @@
       <c r="L69" s="5"/>
       <c r="M69" s="5"/>
       <c r="N69" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="O69" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="P69" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="Q69" s="5" t="s">
         <v>481</v>
@@ -6245,16 +6419,16 @@
       </c>
       <c r="L70" s="5"/>
       <c r="M70" s="10" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="N70" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="O70" s="14" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="P70" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="Q70" s="5" t="s">
         <v>473</v>
@@ -6289,13 +6463,13 @@
       <c r="L71" s="5"/>
       <c r="M71" s="5"/>
       <c r="N71" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="O71" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="P71" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="Q71" s="5" t="s">
         <v>482</v>
@@ -6330,13 +6504,13 @@
       <c r="L72" s="5"/>
       <c r="M72" s="5"/>
       <c r="N72" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="O72" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="P72" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="Q72" s="5" t="s">
         <v>479</v>
@@ -6371,13 +6545,13 @@
       <c r="L73" s="5"/>
       <c r="M73" s="5"/>
       <c r="N73" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="O73" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="P73" s="14" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="Q73" s="5" t="s">
         <v>472</v>
@@ -6412,13 +6586,13 @@
       <c r="L74" s="5"/>
       <c r="M74" s="5"/>
       <c r="N74" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="O74" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="P74" s="14" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="Q74" s="5" t="s">
         <v>478</v>
@@ -6453,13 +6627,13 @@
       <c r="L75" s="5"/>
       <c r="M75" s="5"/>
       <c r="N75" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="O75" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="P75" s="14" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="Q75" s="5" t="s">
         <v>480</v>
@@ -6494,16 +6668,16 @@
       <c r="L76" s="5"/>
       <c r="M76" s="5"/>
       <c r="N76" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="O76" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="P76" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="Q76" s="5" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
     </row>
     <row r="77" spans="1:17" x14ac:dyDescent="0.3">
@@ -6535,13 +6709,13 @@
       <c r="L77" s="5"/>
       <c r="M77" s="5"/>
       <c r="N77" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="O77" s="14" t="s">
+        <v>610</v>
+      </c>
+      <c r="P77" s="14" t="s">
         <v>611</v>
-      </c>
-      <c r="P77" s="14" t="s">
-        <v>612</v>
       </c>
       <c r="Q77" s="5" t="s">
         <v>483</v>
@@ -6576,13 +6750,13 @@
       <c r="L78" s="5"/>
       <c r="M78" s="5"/>
       <c r="N78" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="O78" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="P78" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="Q78" s="5" t="s">
         <v>471</v>
@@ -6616,22 +6790,22 @@
       </c>
       <c r="L79" s="5"/>
       <c r="M79" s="10" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="N79" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="O79" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="P79" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="Q79" s="5" t="s">
         <v>491</v>
       </c>
     </row>
-    <row r="80" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:17" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A80" s="4" t="s">
         <v>101</v>
       </c>
@@ -6657,16 +6831,18 @@
       <c r="K80" s="5" t="s">
         <v>372</v>
       </c>
-      <c r="L80" s="5"/>
+      <c r="L80" s="5" t="s">
+        <v>700</v>
+      </c>
       <c r="M80" s="5"/>
       <c r="N80" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="O80" s="14" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="P80" s="14" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="Q80" s="5" t="s">
         <v>498</v>
@@ -6701,13 +6877,13 @@
       <c r="L81" s="5"/>
       <c r="M81" s="5"/>
       <c r="N81" s="14" t="s">
+        <v>610</v>
+      </c>
+      <c r="O81" s="14" t="s">
         <v>611</v>
       </c>
-      <c r="O81" s="14" t="s">
-        <v>612</v>
-      </c>
       <c r="P81" s="14" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="Q81" s="5" t="s">
         <v>492</v>
@@ -6742,13 +6918,13 @@
       <c r="L82" s="5"/>
       <c r="M82" s="5"/>
       <c r="N82" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="O82" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="P82" s="14" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="Q82" s="5" t="s">
         <v>493</v>
@@ -6783,13 +6959,13 @@
       <c r="L83" s="5"/>
       <c r="M83" s="5"/>
       <c r="N83" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="O83" s="14" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="P83" s="14" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="Q83" s="5" t="s">
         <v>494</v>
@@ -6823,16 +6999,16 @@
       </c>
       <c r="L84" s="5"/>
       <c r="M84" s="10" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="N84" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="O84" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="P84" s="14" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="Q84" s="5" t="s">
         <v>499</v>
@@ -6867,13 +7043,13 @@
       <c r="L85" s="5"/>
       <c r="M85" s="5"/>
       <c r="N85" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="O85" s="14" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="P85" s="14" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="Q85" s="5" t="s">
         <v>486</v>
@@ -6905,19 +7081,21 @@
       <c r="K86" s="5" t="s">
         <v>372</v>
       </c>
-      <c r="L86" s="5"/>
+      <c r="L86" s="5" t="s">
+        <v>699</v>
+      </c>
       <c r="M86" s="5"/>
       <c r="N86" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="O86" s="14" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="P86" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="Q86" s="5" t="s">
-        <v>497</v>
+        <v>693</v>
       </c>
     </row>
     <row r="87" spans="1:17" x14ac:dyDescent="0.3">
@@ -6949,13 +7127,13 @@
       <c r="L87" s="5"/>
       <c r="M87" s="5"/>
       <c r="N87" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="O87" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="P87" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="Q87" s="5" t="s">
         <v>488</v>
@@ -6990,13 +7168,13 @@
       <c r="L88" s="5"/>
       <c r="M88" s="5"/>
       <c r="N88" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="O88" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="P88" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="Q88" s="5" t="s">
         <v>495</v>
@@ -7031,13 +7209,13 @@
       <c r="L89" s="5"/>
       <c r="M89" s="5"/>
       <c r="N89" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="O89" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="P89" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="Q89" s="5" t="s">
         <v>487</v>
@@ -7072,19 +7250,19 @@
       <c r="L90" s="5"/>
       <c r="M90" s="5"/>
       <c r="N90" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="O90" s="14" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="P90" s="14" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="Q90" s="5" t="s">
         <v>496</v>
       </c>
     </row>
-    <row r="91" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:17" ht="108" x14ac:dyDescent="0.3">
       <c r="A91" s="4" t="s">
         <v>101</v>
       </c>
@@ -7110,16 +7288,18 @@
       <c r="K91" s="5" t="s">
         <v>372</v>
       </c>
-      <c r="L91" s="5"/>
+      <c r="L91" s="5" t="s">
+        <v>701</v>
+      </c>
       <c r="M91" s="5"/>
       <c r="N91" s="14" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="O91" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="P91" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="Q91" s="5" t="s">
         <v>500</v>
@@ -7153,16 +7333,16 @@
       </c>
       <c r="L92" s="5"/>
       <c r="M92" s="10" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="N92" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="O92" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="P92" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="Q92" s="5" t="s">
         <v>490</v>
@@ -7205,13 +7385,13 @@
       <c r="L93" s="2"/>
       <c r="M93" s="2"/>
       <c r="N93" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="O93" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="P93" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="Q93" s="6" t="s">
         <v>497</v>
@@ -7245,16 +7425,16 @@
       </c>
       <c r="L94" s="5"/>
       <c r="M94" s="10" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="N94" s="14" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="O94" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="P94" s="14" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="Q94" s="5" t="s">
         <v>484</v>
@@ -7289,13 +7469,13 @@
       <c r="L95" s="5"/>
       <c r="M95" s="5"/>
       <c r="N95" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="O95" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="P95" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="Q95" s="5" t="s">
         <v>485</v>
@@ -7330,19 +7510,19 @@
       <c r="L96" s="5"/>
       <c r="M96" s="5"/>
       <c r="N96" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="O96" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="P96" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="Q96" s="5" t="s">
         <v>489</v>
       </c>
     </row>
-    <row r="97" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:17" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A97" s="4" t="s">
         <v>115</v>
       </c>
@@ -7368,16 +7548,18 @@
       <c r="K97" s="5" t="s">
         <v>372</v>
       </c>
-      <c r="L97" s="5"/>
+      <c r="L97" s="5" t="s">
+        <v>702</v>
+      </c>
       <c r="M97" s="5"/>
       <c r="N97" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="O97" s="14" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="P97" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="Q97" s="5" t="s">
         <v>501</v>
@@ -7412,13 +7594,13 @@
       <c r="L98" s="5"/>
       <c r="M98" s="5"/>
       <c r="N98" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="O98" s="14" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="P98" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="Q98" s="5" t="s">
         <v>502</v>
@@ -7453,16 +7635,16 @@
       <c r="L99" s="5"/>
       <c r="M99" s="5"/>
       <c r="N99" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="O99" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="P99" s="14" t="s">
-        <v>608</v>
-      </c>
-      <c r="Q99" s="5" t="s">
-        <v>506</v>
+        <v>607</v>
+      </c>
+      <c r="Q99" s="23" t="s">
+        <v>691</v>
       </c>
     </row>
     <row r="100" spans="1:17" ht="94.5" x14ac:dyDescent="0.3">
@@ -7493,16 +7675,16 @@
       </c>
       <c r="L100" s="5"/>
       <c r="M100" s="10" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="N100" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="O100" s="14" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="P100" s="14" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="Q100" s="5" t="s">
         <v>504</v>
@@ -7537,16 +7719,16 @@
       <c r="L101" s="5"/>
       <c r="M101" s="5"/>
       <c r="N101" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="O101" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="P101" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="Q101" s="5" t="s">
-        <v>505</v>
+        <v>694</v>
       </c>
     </row>
     <row r="102" spans="1:17" ht="95.25" x14ac:dyDescent="0.3">
@@ -7581,22 +7763,22 @@
       </c>
       <c r="L102" s="2"/>
       <c r="M102" s="12" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="N102" s="14" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="O102" s="14" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="P102" s="14" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="Q102" s="6" t="s">
         <v>509</v>
       </c>
     </row>
-    <row r="103" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:17" ht="27" x14ac:dyDescent="0.3">
       <c r="A103" s="4" t="s">
         <v>115</v>
       </c>
@@ -7622,16 +7804,18 @@
       <c r="K103" s="5" t="s">
         <v>372</v>
       </c>
-      <c r="L103" s="5"/>
+      <c r="L103" s="5" t="s">
+        <v>703</v>
+      </c>
       <c r="M103" s="5"/>
       <c r="N103" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="O103" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="P103" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="Q103" s="5" t="s">
         <v>503</v>
@@ -7666,19 +7850,19 @@
       <c r="L104" s="5"/>
       <c r="M104" s="5"/>
       <c r="N104" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="O104" s="14" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="P104" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="Q104" s="5" t="s">
         <v>510</v>
       </c>
     </row>
-    <row r="105" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:17" ht="27" x14ac:dyDescent="0.3">
       <c r="A105" s="4" t="s">
         <v>115</v>
       </c>
@@ -7704,16 +7888,18 @@
       <c r="K105" s="5" t="s">
         <v>372</v>
       </c>
-      <c r="L105" s="5"/>
+      <c r="L105" s="5" t="s">
+        <v>704</v>
+      </c>
       <c r="M105" s="5"/>
       <c r="N105" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="O105" s="14" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="P105" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="Q105" s="5" t="s">
         <v>507</v>
@@ -7747,22 +7933,22 @@
       </c>
       <c r="L106" s="5"/>
       <c r="M106" s="10" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="N106" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="O106" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="P106" s="14" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="Q106" s="5" t="s">
         <v>505</v>
       </c>
     </row>
-    <row r="107" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:17" ht="81" x14ac:dyDescent="0.3">
       <c r="A107" s="4" t="s">
         <v>115</v>
       </c>
@@ -7796,16 +7982,18 @@
       <c r="K107" s="5" t="s">
         <v>372</v>
       </c>
-      <c r="L107" s="5"/>
+      <c r="L107" s="5" t="s">
+        <v>705</v>
+      </c>
       <c r="M107" s="5"/>
       <c r="N107" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="O107" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="P107" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="Q107" s="5" t="s">
         <v>512</v>
@@ -7840,13 +8028,13 @@
       <c r="L108" s="5"/>
       <c r="M108" s="5"/>
       <c r="N108" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="O108" s="14" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="P108" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="Q108" s="5" t="s">
         <v>511</v>
@@ -7883,13 +8071,13 @@
       <c r="L109" s="2"/>
       <c r="M109" s="2"/>
       <c r="N109" s="14" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="O109" s="14" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="P109" s="14" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="Q109" s="6" t="s">
         <v>506</v>
@@ -7924,13 +8112,13 @@
       <c r="L110" s="5"/>
       <c r="M110" s="5"/>
       <c r="N110" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="O110" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="P110" s="14" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="Q110" s="5" t="s">
         <v>508</v>
@@ -7965,16 +8153,16 @@
       <c r="L111" s="5"/>
       <c r="M111" s="5"/>
       <c r="N111" s="14" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="O111" s="14" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="P111" s="14" t="s">
-        <v>608</v>
-      </c>
-      <c r="Q111" s="5" t="s">
-        <v>513</v>
+        <v>607</v>
+      </c>
+      <c r="Q111" s="23" t="s">
+        <v>695</v>
       </c>
     </row>
     <row r="112" spans="1:17" x14ac:dyDescent="0.3">
@@ -8006,19 +8194,19 @@
       <c r="L112" s="5"/>
       <c r="M112" s="5"/>
       <c r="N112" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="O112" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="P112" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="Q112" s="5" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="113" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:17" ht="27" x14ac:dyDescent="0.3">
       <c r="A113" s="4" t="s">
         <v>102</v>
       </c>
@@ -8044,22 +8232,24 @@
       <c r="K113" s="5" t="s">
         <v>381</v>
       </c>
-      <c r="L113" s="5"/>
+      <c r="L113" s="22" t="s">
+        <v>689</v>
+      </c>
       <c r="M113" s="5"/>
       <c r="N113" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="O113" s="14" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="P113" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="Q113" s="5" t="s">
         <v>513</v>
       </c>
     </row>
-    <row r="114" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:17" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A114" s="4" t="s">
         <v>102</v>
       </c>
@@ -8085,16 +8275,18 @@
       <c r="K114" s="5" t="s">
         <v>370</v>
       </c>
-      <c r="L114" s="5"/>
+      <c r="L114" s="5" t="s">
+        <v>687</v>
+      </c>
       <c r="M114" s="5"/>
       <c r="N114" s="14" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="O114" s="14" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="P114" s="14" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="Q114" s="5" t="s">
         <v>518</v>
@@ -8129,13 +8321,13 @@
       <c r="L115" s="5"/>
       <c r="M115" s="5"/>
       <c r="N115" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="O115" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="P115" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="Q115" s="5" t="s">
         <v>517</v>
@@ -8169,16 +8361,16 @@
       </c>
       <c r="L116" s="5"/>
       <c r="M116" s="10" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="N116" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="O116" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="P116" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="Q116" s="5" t="s">
         <v>519</v>
@@ -8213,13 +8405,13 @@
       <c r="L117" s="5"/>
       <c r="M117" s="5"/>
       <c r="N117" s="14" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="O117" s="14" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="P117" s="14" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="Q117" s="5" t="s">
         <v>514</v>
@@ -8253,16 +8445,16 @@
       </c>
       <c r="L118" s="5"/>
       <c r="M118" s="10" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="N118" s="14" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="O118" s="14" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="P118" s="13" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="Q118" s="5" t="s">
         <v>515</v>
@@ -8297,13 +8489,13 @@
       <c r="L119" s="5"/>
       <c r="M119" s="5"/>
       <c r="N119" s="13" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="O119" s="13" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="P119" s="14" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="Q119" s="5" t="s">
         <v>531</v>
@@ -8338,13 +8530,13 @@
       <c r="L120" s="5"/>
       <c r="M120" s="5"/>
       <c r="N120" s="13" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="O120" s="13" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="P120" s="14" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="Q120" s="5" t="s">
         <v>530</v>
@@ -8379,13 +8571,13 @@
       <c r="L121" s="5"/>
       <c r="M121" s="5"/>
       <c r="N121" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="O121" s="14" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="P121" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="Q121" s="5" t="s">
         <v>520</v>
@@ -8419,16 +8611,16 @@
       </c>
       <c r="L122" s="5"/>
       <c r="M122" s="10" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="N122" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="O122" s="14" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="P122" s="14" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="Q122" s="5" t="s">
         <v>523</v>
@@ -8463,13 +8655,13 @@
       <c r="L123" s="5"/>
       <c r="M123" s="5"/>
       <c r="N123" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="O123" s="14" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="P123" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="Q123" s="5" t="s">
         <v>526</v>
@@ -8504,13 +8696,13 @@
       <c r="L124" s="5"/>
       <c r="M124" s="5"/>
       <c r="N124" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="O124" s="14" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="P124" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="Q124" s="5" t="s">
         <v>527</v>
@@ -8545,13 +8737,13 @@
       <c r="L125" s="5"/>
       <c r="M125" s="5"/>
       <c r="N125" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="O125" s="14" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="P125" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="Q125" s="5" t="s">
         <v>524</v>
@@ -8586,13 +8778,13 @@
       <c r="L126" s="5"/>
       <c r="M126" s="5"/>
       <c r="N126" s="14" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="O126" s="13" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="P126" s="13" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="Q126" s="5" t="s">
         <v>521</v>
@@ -8626,22 +8818,22 @@
       </c>
       <c r="L127" s="5"/>
       <c r="M127" s="10" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="N127" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="O127" s="14" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="P127" s="14" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="Q127" s="5" t="s">
         <v>525</v>
       </c>
     </row>
-    <row r="128" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:17" ht="54" x14ac:dyDescent="0.3">
       <c r="A128" s="4" t="s">
         <v>116</v>
       </c>
@@ -8667,16 +8859,18 @@
       <c r="K128" s="5" t="s">
         <v>372</v>
       </c>
-      <c r="L128" s="5"/>
+      <c r="L128" s="5" t="s">
+        <v>706</v>
+      </c>
       <c r="M128" s="5"/>
       <c r="N128" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="O128" s="14" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="P128" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="Q128" s="5" t="s">
         <v>528</v>
@@ -8711,13 +8905,13 @@
       <c r="L129" s="5"/>
       <c r="M129" s="5"/>
       <c r="N129" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="O129" s="14" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="P129" s="14" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="Q129" s="5" t="s">
         <v>522</v>
@@ -8752,13 +8946,13 @@
       <c r="L130" s="5"/>
       <c r="M130" s="5"/>
       <c r="N130" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="O130" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="P130" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="Q130" s="5" t="s">
         <v>529</v>
@@ -8793,13 +8987,13 @@
       <c r="L131" s="5"/>
       <c r="M131" s="5"/>
       <c r="N131" s="14" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="O131" s="13" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="P131" s="13" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="Q131" s="5" t="s">
         <v>549</v>
@@ -8834,13 +9028,13 @@
       <c r="L132" s="5"/>
       <c r="M132" s="5"/>
       <c r="N132" s="14" t="s">
-        <v>608</v>
-      </c>
-      <c r="O132" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
+      </c>
+      <c r="O132" s="13" t="s">
+        <v>610</v>
       </c>
       <c r="P132" s="14" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="Q132" s="5" t="s">
         <v>538</v>
@@ -8875,13 +9069,13 @@
       <c r="L133" s="5"/>
       <c r="M133" s="5"/>
       <c r="N133" s="14" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="O133" s="14" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="P133" s="14" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="Q133" s="5" t="s">
         <v>545</v>
@@ -8916,13 +9110,13 @@
       <c r="L134" s="5"/>
       <c r="M134" s="5"/>
       <c r="N134" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="O134" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="P134" s="14" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="Q134" s="5" t="s">
         <v>533</v>
@@ -8957,13 +9151,13 @@
       <c r="L135" s="5"/>
       <c r="M135" s="5"/>
       <c r="N135" s="14" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="O135" s="14" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="P135" s="13" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="Q135" s="5" t="s">
         <v>542</v>
@@ -8998,13 +9192,13 @@
       <c r="L136" s="5"/>
       <c r="M136" s="5"/>
       <c r="N136" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="O136" s="14" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="P136" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="Q136" s="5" t="s">
         <v>537</v>
@@ -9039,16 +9233,16 @@
       <c r="L137" s="5"/>
       <c r="M137" s="5"/>
       <c r="N137" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="O137" s="14" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="P137" s="14" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="Q137" s="5" t="s">
-        <v>550</v>
+        <v>696</v>
       </c>
     </row>
     <row r="138" spans="1:17" x14ac:dyDescent="0.3">
@@ -9080,13 +9274,13 @@
       <c r="L138" s="5"/>
       <c r="M138" s="5"/>
       <c r="N138" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="O138" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="P138" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="Q138" s="5" t="s">
         <v>535</v>
@@ -9121,13 +9315,13 @@
       <c r="L139" s="5"/>
       <c r="M139" s="5"/>
       <c r="N139" s="14" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="O139" s="14" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="P139" s="14" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="Q139" s="5" t="s">
         <v>540</v>
@@ -9162,16 +9356,16 @@
       <c r="L140" s="5"/>
       <c r="M140" s="5"/>
       <c r="N140" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="O140" s="14" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="P140" s="14" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="Q140" s="5" t="s">
-        <v>534</v>
+        <v>697</v>
       </c>
     </row>
     <row r="141" spans="1:17" x14ac:dyDescent="0.3">
@@ -9203,13 +9397,13 @@
       <c r="L141" s="5"/>
       <c r="M141" s="5"/>
       <c r="N141" s="14" t="s">
+        <v>610</v>
+      </c>
+      <c r="O141" s="14" t="s">
         <v>611</v>
       </c>
-      <c r="O141" s="14" t="s">
-        <v>612</v>
-      </c>
       <c r="P141" s="14" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="Q141" s="5" t="s">
         <v>543</v>
@@ -9244,13 +9438,13 @@
       <c r="L142" s="5"/>
       <c r="M142" s="5"/>
       <c r="N142" s="13" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="O142" s="14" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="P142" s="13" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="Q142" s="5" t="s">
         <v>544</v>
@@ -9284,16 +9478,16 @@
       </c>
       <c r="L143" s="5"/>
       <c r="M143" s="10" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="N143" s="13" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="O143" s="14" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="P143" s="14" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="Q143" s="5" t="s">
         <v>536</v>
@@ -9328,19 +9522,19 @@
       <c r="L144" s="5"/>
       <c r="M144" s="5"/>
       <c r="N144" s="14" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="O144" s="14" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="P144" s="14" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="Q144" s="5" t="s">
         <v>546</v>
       </c>
     </row>
-    <row r="145" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:17" ht="148.5" x14ac:dyDescent="0.3">
       <c r="A145" s="4" t="s">
         <v>117</v>
       </c>
@@ -9364,18 +9558,18 @@
       <c r="I145" s="5"/>
       <c r="J145" s="5"/>
       <c r="K145" s="5" t="s">
-        <v>370</v>
+        <v>708</v>
       </c>
       <c r="L145" s="5"/>
       <c r="M145" s="5"/>
       <c r="N145" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="O145" s="14" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="P145" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="Q145" s="5" t="s">
         <v>532</v>
@@ -9405,18 +9599,18 @@
       <c r="I146" s="5"/>
       <c r="J146" s="5"/>
       <c r="K146" s="5" t="s">
-        <v>368</v>
+        <v>707</v>
       </c>
       <c r="L146" s="5"/>
       <c r="M146" s="5"/>
       <c r="N146" s="14" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="O146" s="14" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="P146" s="13" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="Q146" s="5" t="s">
         <v>534</v>
@@ -9451,13 +9645,13 @@
       <c r="L147" s="5"/>
       <c r="M147" s="5"/>
       <c r="N147" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="O147" s="14" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="P147" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="Q147" s="5" t="s">
         <v>547</v>
@@ -9491,16 +9685,16 @@
       </c>
       <c r="L148" s="5"/>
       <c r="M148" s="10" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="N148" s="14" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="O148" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="P148" s="14" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="Q148" s="5" t="s">
         <v>548</v>
@@ -9534,16 +9728,16 @@
       </c>
       <c r="L149" s="5"/>
       <c r="M149" s="10" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="N149" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="O149" s="14" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="P149" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="Q149" s="5" t="s">
         <v>541</v>
@@ -9578,13 +9772,13 @@
       <c r="L150" s="5"/>
       <c r="M150" s="5"/>
       <c r="N150" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="O150" s="14" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="P150" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="Q150" s="5" t="s">
         <v>550</v>
@@ -9619,13 +9813,13 @@
       <c r="L151" s="5"/>
       <c r="M151" s="5"/>
       <c r="N151" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="O151" s="14" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="P151" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="Q151" s="5" t="s">
         <v>539</v>
@@ -9660,13 +9854,13 @@
       <c r="L152" s="5"/>
       <c r="M152" s="5"/>
       <c r="N152" s="14" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="O152" s="14" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="P152" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="Q152" s="5" t="s">
         <v>552</v>
@@ -9701,13 +9895,13 @@
       <c r="L153" s="5"/>
       <c r="M153" s="5"/>
       <c r="N153" s="13" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="O153" s="13" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="P153" s="14" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="Q153" s="5" t="s">
         <v>553</v>
@@ -9721,7 +9915,7 @@
         <v>300</v>
       </c>
       <c r="C154" s="5" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="D154" s="5" t="s">
         <v>4</v>
@@ -9742,13 +9936,13 @@
       <c r="L154" s="5"/>
       <c r="M154" s="5"/>
       <c r="N154" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="O154" s="14" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="P154" s="14" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="Q154" s="5" t="s">
         <v>554</v>
@@ -9783,13 +9977,13 @@
       <c r="L155" s="5"/>
       <c r="M155" s="5"/>
       <c r="N155" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="O155" s="14" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="P155" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="Q155" s="5" t="s">
         <v>556</v>
@@ -9824,13 +10018,13 @@
       <c r="L156" s="5"/>
       <c r="M156" s="5"/>
       <c r="N156" s="13" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="O156" s="13" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="P156" s="13" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="Q156" s="5" t="s">
         <v>551</v>
@@ -9865,13 +10059,13 @@
       <c r="L157" s="5"/>
       <c r="M157" s="5"/>
       <c r="N157" s="13" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="O157" s="13" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="P157" s="14" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="Q157" s="5" t="s">
         <v>560</v>
@@ -9906,19 +10100,19 @@
       <c r="L158" s="5"/>
       <c r="M158" s="5"/>
       <c r="N158" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="O158" s="14" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="P158" s="14" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="Q158" s="5" t="s">
         <v>561</v>
       </c>
     </row>
-    <row r="159" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:17" ht="27" x14ac:dyDescent="0.3">
       <c r="A159" s="4" t="s">
         <v>118</v>
       </c>
@@ -9944,16 +10138,18 @@
       <c r="K159" s="5" t="s">
         <v>372</v>
       </c>
-      <c r="L159" s="5"/>
+      <c r="L159" s="5" t="s">
+        <v>712</v>
+      </c>
       <c r="M159" s="5"/>
       <c r="N159" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="O159" s="14" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="P159" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="Q159" s="5" t="s">
         <v>563</v>
@@ -9985,16 +10181,18 @@
       <c r="K160" s="5" t="s">
         <v>372</v>
       </c>
-      <c r="L160" s="5"/>
+      <c r="L160" s="5" t="s">
+        <v>710</v>
+      </c>
       <c r="M160" s="5"/>
       <c r="N160" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="O160" s="14" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="P160" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="Q160" s="5" t="s">
         <v>559</v>
@@ -10029,19 +10227,19 @@
       <c r="L161" s="5"/>
       <c r="M161" s="5"/>
       <c r="N161" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="O161" s="14" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="P161" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="Q161" s="5" t="s">
         <v>566</v>
       </c>
     </row>
-    <row r="162" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:17" ht="148.5" x14ac:dyDescent="0.3">
       <c r="A162" s="4" t="s">
         <v>118</v>
       </c>
@@ -10067,16 +10265,18 @@
       <c r="K162" s="5" t="s">
         <v>370</v>
       </c>
-      <c r="L162" s="5"/>
+      <c r="L162" s="5" t="s">
+        <v>714</v>
+      </c>
       <c r="M162" s="5"/>
       <c r="N162" s="14" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="O162" s="14" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="P162" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="Q162" s="5" t="s">
         <v>567</v>
@@ -10111,13 +10311,13 @@
       <c r="L163" s="5"/>
       <c r="M163" s="5"/>
       <c r="N163" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="O163" s="14" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="P163" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="Q163" s="5" t="s">
         <v>569</v>
@@ -10152,13 +10352,13 @@
       <c r="L164" s="5"/>
       <c r="M164" s="5"/>
       <c r="N164" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="O164" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="P164" s="14" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="Q164" s="5" t="s">
         <v>555</v>
@@ -10192,22 +10392,22 @@
       </c>
       <c r="L165" s="5"/>
       <c r="M165" s="10" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="N165" s="14" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="O165" s="14" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="P165" s="14" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="Q165" s="5" t="s">
         <v>568</v>
       </c>
     </row>
-    <row r="166" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:17" ht="27" x14ac:dyDescent="0.3">
       <c r="A166" s="4" t="s">
         <v>118</v>
       </c>
@@ -10233,16 +10433,18 @@
       <c r="K166" s="5" t="s">
         <v>376</v>
       </c>
-      <c r="L166" s="5"/>
+      <c r="L166" s="5" t="s">
+        <v>709</v>
+      </c>
       <c r="M166" s="5"/>
       <c r="N166" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="O166" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="P166" s="14" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="Q166" s="5" t="s">
         <v>557</v>
@@ -10276,22 +10478,22 @@
       </c>
       <c r="L167" s="5"/>
       <c r="M167" s="10" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="N167" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="O167" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="P167" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="Q167" s="5" t="s">
         <v>558</v>
       </c>
     </row>
-    <row r="168" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:17" ht="27" x14ac:dyDescent="0.3">
       <c r="A168" s="4" t="s">
         <v>118</v>
       </c>
@@ -10317,22 +10519,24 @@
       <c r="K168" s="5" t="s">
         <v>376</v>
       </c>
-      <c r="L168" s="5"/>
+      <c r="L168" s="5" t="s">
+        <v>711</v>
+      </c>
       <c r="M168" s="5"/>
       <c r="N168" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="O168" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="P168" s="14" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="Q168" s="5" t="s">
         <v>562</v>
       </c>
     </row>
-    <row r="169" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:17" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A169" s="4" t="s">
         <v>118</v>
       </c>
@@ -10358,16 +10562,18 @@
       <c r="K169" s="5" t="s">
         <v>376</v>
       </c>
-      <c r="L169" s="5"/>
+      <c r="L169" s="5" t="s">
+        <v>713</v>
+      </c>
       <c r="M169" s="5"/>
       <c r="N169" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="O169" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="P169" s="14" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="Q169" s="5" t="s">
         <v>565</v>
@@ -10402,13 +10608,13 @@
       <c r="L170" s="5"/>
       <c r="M170" s="5"/>
       <c r="N170" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="O170" s="14" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="P170" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="Q170" s="5" t="s">
         <v>564</v>
@@ -10443,13 +10649,13 @@
       <c r="L171" s="5"/>
       <c r="M171" s="5"/>
       <c r="N171" s="13" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="O171" s="13" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="P171" s="14" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="Q171" s="5" t="s">
         <v>571</v>
@@ -10484,13 +10690,13 @@
       <c r="L172" s="5"/>
       <c r="M172" s="5"/>
       <c r="N172" s="14" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="O172" s="14" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="P172" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="Q172" s="5" t="s">
         <v>572</v>
@@ -10525,13 +10731,13 @@
       <c r="L173" s="5"/>
       <c r="M173" s="5"/>
       <c r="N173" s="13" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="O173" s="13" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="P173" s="14" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="Q173" s="5" t="s">
         <v>570</v>
@@ -10566,13 +10772,13 @@
       <c r="L174" s="5"/>
       <c r="M174" s="5"/>
       <c r="N174" s="14" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="O174" s="14" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="P174" s="14" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="Q174" s="5" t="s">
         <v>573</v>
@@ -10592,7 +10798,7 @@
         <v>331</v>
       </c>
       <c r="E175" s="6" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="F175" s="6" t="s">
         <v>332</v>
@@ -10621,13 +10827,13 @@
         <v>361</v>
       </c>
       <c r="C176" s="6" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="D176" s="6" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="E176" s="6" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="F176" s="6"/>
       <c r="G176" s="6" t="s">
@@ -10659,10 +10865,10 @@
         <v>335</v>
       </c>
       <c r="D177" s="6" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="E177" s="6" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="F177" s="6" t="s">
         <v>397</v>
@@ -10696,10 +10902,10 @@
         <v>335</v>
       </c>
       <c r="D178" s="6" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="E178" s="6" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="F178" s="6" t="s">
         <v>397</v>
@@ -10733,10 +10939,10 @@
         <v>342</v>
       </c>
       <c r="D179" s="6" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="E179" s="6" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="F179" s="6" t="s">
         <v>574</v>
@@ -10772,10 +10978,10 @@
         <v>342</v>
       </c>
       <c r="D180" s="6" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="E180" s="6" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="F180" s="6" t="s">
         <v>574</v>
@@ -10805,22 +11011,22 @@
         <v>118</v>
       </c>
       <c r="B181" s="6" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="C181" s="6" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="D181" s="6" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="E181" s="6" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="F181" s="7" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="G181" s="6" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="H181" s="6"/>
       <c r="I181" s="6"/>
@@ -10832,7 +11038,7 @@
       <c r="O181" s="16"/>
       <c r="P181" s="16"/>
       <c r="Q181" s="6" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="182" spans="1:17" x14ac:dyDescent="0.3">
@@ -10843,16 +11049,16 @@
         <v>336</v>
       </c>
       <c r="C182" s="6" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="D182" s="6" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="E182" s="6" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="F182" s="7" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="G182" s="6"/>
       <c r="H182" s="6"/>
@@ -10865,27 +11071,27 @@
       <c r="O182" s="16"/>
       <c r="P182" s="16"/>
       <c r="Q182" s="6" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
     </row>
     <row r="183" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A183" s="6" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="B183" s="6" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="C183" s="6" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="D183" s="6" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="E183" s="6" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="F183" s="6" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="G183" s="6"/>
       <c r="H183" s="6"/>
@@ -10898,7 +11104,7 @@
       <c r="O183" s="16"/>
       <c r="P183" s="16"/>
       <c r="Q183" s="6" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
     </row>
     <row r="184" spans="1:17" x14ac:dyDescent="0.3">
@@ -10906,19 +11112,19 @@
         <v>118</v>
       </c>
       <c r="B184" s="6" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="C184" s="6" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="D184" s="6" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="E184" s="6" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="F184" s="6" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="G184" s="6"/>
       <c r="H184" s="6"/>
@@ -10931,7 +11137,7 @@
       <c r="O184" s="16"/>
       <c r="P184" s="16"/>
       <c r="Q184" s="6" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
     </row>
     <row r="185" spans="1:17" x14ac:dyDescent="0.3">
@@ -10939,19 +11145,19 @@
         <v>116</v>
       </c>
       <c r="B185" s="6" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="C185" s="6" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="D185" s="6" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="E185" s="6" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="F185" s="6" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="G185" s="6"/>
       <c r="H185" s="6"/>
@@ -10964,7 +11170,7 @@
       <c r="O185" s="16"/>
       <c r="P185" s="16"/>
       <c r="Q185" s="6" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="186" spans="1:17" x14ac:dyDescent="0.3">
@@ -10972,19 +11178,19 @@
         <v>118</v>
       </c>
       <c r="B186" s="6" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="C186" s="6" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="D186" s="6" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="E186" s="6" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="F186" s="6" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="G186" s="6"/>
       <c r="H186" s="6"/>
@@ -10997,7 +11203,7 @@
       <c r="O186" s="16"/>
       <c r="P186" s="16"/>
       <c r="Q186" s="6" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
     </row>
     <row r="187" spans="1:17" x14ac:dyDescent="0.3">
@@ -11005,26 +11211,26 @@
         <v>116</v>
       </c>
       <c r="B187" s="6" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="C187" s="6" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="D187" s="6" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="E187" s="6" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="F187" s="6" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="G187" s="6"/>
       <c r="H187" s="6"/>
       <c r="I187" s="6"/>
       <c r="J187" s="6"/>
       <c r="K187" s="6" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="L187" s="2"/>
       <c r="M187" s="2"/>
@@ -11032,81 +11238,81 @@
       <c r="O187" s="16"/>
       <c r="P187" s="16"/>
       <c r="Q187" s="6" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="188" spans="1:17" ht="95.25" x14ac:dyDescent="0.3">
       <c r="A188" s="6" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="B188" s="6" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="C188" s="6" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="D188" s="6" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="E188" s="6" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="F188" s="6" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="G188" s="6"/>
       <c r="H188" s="6"/>
       <c r="I188" s="6"/>
       <c r="J188" s="6"/>
       <c r="K188" s="6" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="L188" s="2"/>
       <c r="M188" s="21" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="N188" s="16"/>
       <c r="O188" s="16"/>
       <c r="P188" s="16"/>
       <c r="Q188" s="6" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
     </row>
     <row r="189" spans="1:17" ht="162.75" x14ac:dyDescent="0.3">
       <c r="A189" s="6" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="B189" s="6" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="C189" s="6" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="D189" s="6" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="E189" s="6" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="F189" s="6" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="G189" s="6"/>
       <c r="H189" s="6"/>
       <c r="I189" s="6"/>
       <c r="J189" s="6"/>
       <c r="K189" s="5" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="L189" s="2"/>
       <c r="M189" s="21" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="N189" s="16"/>
       <c r="O189" s="16"/>
       <c r="P189" s="16"/>
       <c r="Q189" s="6" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
     </row>
     <row r="190" spans="1:17" ht="135.75" x14ac:dyDescent="0.3">
@@ -11114,36 +11320,36 @@
         <v>117</v>
       </c>
       <c r="B190" s="6" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="C190" s="6" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="D190" s="6" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="E190" s="6" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="F190" s="6" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="G190" s="6"/>
       <c r="H190" s="6"/>
       <c r="I190" s="6"/>
       <c r="J190" s="6"/>
       <c r="K190" s="5" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="L190" s="2"/>
       <c r="M190" s="21" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="N190" s="16"/>
       <c r="O190" s="16"/>
       <c r="P190" s="16"/>
       <c r="Q190" s="6" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="191" spans="1:17" ht="149.25" x14ac:dyDescent="0.3">
@@ -11151,36 +11357,36 @@
         <v>117</v>
       </c>
       <c r="B191" s="6" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="C191" s="6" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="D191" s="6" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="E191" s="6" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="F191" s="6" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="G191" s="6"/>
       <c r="H191" s="6"/>
       <c r="I191" s="6"/>
       <c r="J191" s="6"/>
       <c r="K191" s="6" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="L191" s="2"/>
       <c r="M191" s="21" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="N191" s="16"/>
       <c r="O191" s="16"/>
       <c r="P191" s="16"/>
       <c r="Q191" s="6" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
     </row>
     <row r="192" spans="1:17" ht="27" x14ac:dyDescent="0.3">
@@ -11188,26 +11394,26 @@
         <v>118</v>
       </c>
       <c r="B192" s="6" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="C192" s="6" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="D192" s="6" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="E192" s="6" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="F192" s="6"/>
       <c r="G192" s="7" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="H192" s="6"/>
       <c r="I192" s="6"/>
       <c r="J192" s="6"/>
       <c r="K192" s="6" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="L192" s="2"/>
       <c r="M192" s="2"/>
@@ -11215,44 +11421,44 @@
       <c r="O192" s="16"/>
       <c r="P192" s="16"/>
       <c r="Q192" s="6" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
     </row>
     <row r="193" spans="1:17" ht="54.75" x14ac:dyDescent="0.3">
       <c r="A193" s="6" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="B193" s="6" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="C193" s="6" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="D193" s="6" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="E193" s="6" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="F193" s="6" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="G193" s="6"/>
       <c r="H193" s="6"/>
       <c r="I193" s="6"/>
       <c r="J193" s="6"/>
       <c r="K193" s="6" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="L193" s="2"/>
       <c r="M193" s="21" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="N193" s="16"/>
       <c r="O193" s="16"/>
       <c r="P193" s="16"/>
       <c r="Q193" s="6" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
     </row>
     <row r="194" spans="1:17" ht="27.75" x14ac:dyDescent="0.3">
@@ -11260,46 +11466,50 @@
         <v>117</v>
       </c>
       <c r="B194" s="6" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="C194" s="6" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="D194" s="6" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="E194" s="6" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="F194" s="6" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="G194" s="6"/>
       <c r="H194" s="6"/>
       <c r="I194" s="6"/>
       <c r="J194" s="6"/>
       <c r="K194" s="6" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="L194" s="2"/>
       <c r="M194" s="21" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="N194" s="16"/>
       <c r="O194" s="16"/>
       <c r="P194" s="16"/>
       <c r="Q194" s="6" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="B1:Q180" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="1" type="noConversion"/>
+  <conditionalFormatting sqref="Q2:Q174">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
   <hyperlinks>
     <hyperlink ref="Q177" r:id="rId1" xr:uid="{E8A5EE79-38DC-470C-9E4B-60B8DB179166}"/>
     <hyperlink ref="Q175" r:id="rId2" xr:uid="{B514AFC6-F2CC-453E-A7EE-749BE8F59F63}"/>
     <hyperlink ref="Q176" r:id="rId3" xr:uid="{D2C8DCF1-2A86-40FB-A718-5DFF8C67103B}"/>
     <hyperlink ref="Q178" r:id="rId4" xr:uid="{2526EBF2-78DF-4B4D-A609-DDD4E216E820}"/>
+    <hyperlink ref="Q99" r:id="rId5" xr:uid="{05B60FA0-37BF-4BDF-A54A-C6015B78419C}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/app/convert/forest_sample_template.xlsx
+++ b/app/convert/forest_sample_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TAX-JUNGYOON\forest-app\app\convert\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{728113FC-F1A6-4A93-94FE-9C5D519B380F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20652DA7-3199-4A56-950A-3033D23376CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="658" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2331" uniqueCount="715">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4664" uniqueCount="716">
   <si>
     <t>시설명</t>
   </si>
@@ -2633,6 +2633,11 @@
 204호
 글램핑
 1동, 2동</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>매월1일 08시(지역주민선착순)
+매월1일 09시(선착순전환)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2751,7 +2756,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -2809,9 +2814,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -7643,7 +7645,7 @@
       <c r="P99" s="14" t="s">
         <v>607</v>
       </c>
-      <c r="Q99" s="23" t="s">
+      <c r="Q99" s="22" t="s">
         <v>691</v>
       </c>
     </row>
@@ -7931,7 +7933,9 @@
       <c r="K106" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="L106" s="5"/>
+      <c r="L106" s="5" t="s">
+        <v>715</v>
+      </c>
       <c r="M106" s="10" t="s">
         <v>588</v>
       </c>
@@ -8161,7 +8165,7 @@
       <c r="P111" s="14" t="s">
         <v>607</v>
       </c>
-      <c r="Q111" s="23" t="s">
+      <c r="Q111" s="22" t="s">
         <v>695</v>
       </c>
     </row>
@@ -8232,7 +8236,7 @@
       <c r="K113" s="5" t="s">
         <v>381</v>
       </c>
-      <c r="L113" s="22" t="s">
+      <c r="L113" s="5" t="s">
         <v>689</v>
       </c>
       <c r="M113" s="5"/>

--- a/app/convert/forest_sample_template.xlsx
+++ b/app/convert/forest_sample_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TAX-JUNGYOON\forest-app\app\convert\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20652DA7-3199-4A56-950A-3033D23376CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2ADC7A58-42DF-4599-8893-3039937187E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="658" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4664" uniqueCount="716">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2332" uniqueCount="716">
   <si>
     <t>시설명</t>
   </si>
@@ -1971,14 +1971,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>6인실
-→ 단풍나무, 때죽나무
-→ 평일 75,000 / 주말 134,000
-주의
-→ 지역주민 우선배정 여부 확인 필요</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>4인실
 → 파도채 1~4호, 솔향채 1,3,5호
 → 평일 58,000 / 주말 106,000
@@ -2636,8 +2628,15 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>6인실
+→ 단풍나무, 때죽나무
+→ 평일 75,000 / 주말 134,000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>매월1일 08시(지역주민선착순)
-매월1일 09시(선착순전환)</t>
+매월1일 09시(선착순전환)
+지역주민 우선배정 객실(공지사항)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3193,13 +3192,13 @@
         <v>577</v>
       </c>
       <c r="N1" s="16" t="s">
+        <v>603</v>
+      </c>
+      <c r="O1" s="16" t="s">
         <v>604</v>
       </c>
-      <c r="O1" s="16" t="s">
+      <c r="P1" s="16" t="s">
         <v>605</v>
-      </c>
-      <c r="P1" s="16" t="s">
-        <v>606</v>
       </c>
       <c r="Q1" s="6" t="s">
         <v>330</v>
@@ -3222,7 +3221,7 @@
         <v>113</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="G2" s="5" t="s">
         <v>349</v>
@@ -3242,13 +3241,13 @@
       <c r="L2" s="5"/>
       <c r="M2" s="5"/>
       <c r="N2" s="13" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="O2" s="13" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="P2" s="13" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="Q2" s="5" t="s">
         <v>413</v>
@@ -3285,13 +3284,13 @@
       <c r="L3" s="5"/>
       <c r="M3" s="5"/>
       <c r="N3" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="O3" s="14" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="P3" s="14" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="Q3" s="5" t="s">
         <v>411</v>
@@ -3314,7 +3313,7 @@
         <v>113</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="G4" s="5" t="s">
         <v>349</v>
@@ -3334,13 +3333,13 @@
       <c r="L4" s="5"/>
       <c r="M4" s="5"/>
       <c r="N4" s="13" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="O4" s="13" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="P4" s="13" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="Q4" s="5" t="s">
         <v>410</v>
@@ -3363,7 +3362,7 @@
         <v>113</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="G5" s="5" t="s">
         <v>349</v>
@@ -3383,13 +3382,13 @@
       <c r="L5" s="5"/>
       <c r="M5" s="5"/>
       <c r="N5" s="13" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="O5" s="14" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="P5" s="13" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="Q5" s="5" t="s">
         <v>412</v>
@@ -3412,7 +3411,7 @@
         <v>113</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="G6" s="5" t="s">
         <v>349</v>
@@ -3434,13 +3433,13 @@
         <v>578</v>
       </c>
       <c r="N6" s="13" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="O6" s="13" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="P6" s="13" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="Q6" s="5" t="s">
         <v>409</v>
@@ -3463,7 +3462,7 @@
         <v>113</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="G7" s="5" t="s">
         <v>349</v>
@@ -3483,13 +3482,13 @@
       <c r="L7" s="5"/>
       <c r="M7" s="5"/>
       <c r="N7" s="13" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="O7" s="13" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="P7" s="13" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="Q7" s="5" t="s">
         <v>414</v>
@@ -3512,7 +3511,7 @@
         <v>113</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="G8" s="5" t="s">
         <v>349</v>
@@ -3532,13 +3531,13 @@
       <c r="L8" s="5"/>
       <c r="M8" s="5"/>
       <c r="N8" s="13" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="O8" s="13" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="P8" s="13" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="Q8" s="5" t="s">
         <v>417</v>
@@ -3561,7 +3560,7 @@
         <v>113</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="G9" s="5" t="s">
         <v>349</v>
@@ -3581,13 +3580,13 @@
       <c r="L9" s="5"/>
       <c r="M9" s="5"/>
       <c r="N9" s="13" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="O9" s="13" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="P9" s="13" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="Q9" s="5" t="s">
         <v>416</v>
@@ -3610,7 +3609,7 @@
         <v>113</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="G10" s="5" t="s">
         <v>349</v>
@@ -3630,13 +3629,13 @@
       <c r="L10" s="5"/>
       <c r="M10" s="5"/>
       <c r="N10" s="13" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="O10" s="13" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="P10" s="13" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="Q10" s="5" t="s">
         <v>419</v>
@@ -3659,7 +3658,7 @@
         <v>113</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="G11" s="5" t="s">
         <v>349</v>
@@ -3679,13 +3678,13 @@
       <c r="L11" s="5"/>
       <c r="M11" s="5"/>
       <c r="N11" s="13" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="O11" s="13" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="P11" s="13" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="Q11" s="5" t="s">
         <v>421</v>
@@ -3708,7 +3707,7 @@
         <v>113</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="G12" s="5" t="s">
         <v>349</v>
@@ -3730,13 +3729,13 @@
         <v>582</v>
       </c>
       <c r="N12" s="13" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="O12" s="13" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="P12" s="13" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="Q12" s="5" t="s">
         <v>420</v>
@@ -3759,7 +3758,7 @@
         <v>113</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="G13" s="5" t="s">
         <v>349</v>
@@ -3779,13 +3778,13 @@
       <c r="L13" s="5"/>
       <c r="M13" s="5"/>
       <c r="N13" s="13" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="O13" s="13" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="P13" s="13" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="Q13" s="5" t="s">
         <v>424</v>
@@ -3808,7 +3807,7 @@
         <v>113</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="G14" s="5" t="s">
         <v>349</v>
@@ -3828,13 +3827,13 @@
       <c r="L14" s="5"/>
       <c r="M14" s="5"/>
       <c r="N14" s="13" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="O14" s="13" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="P14" s="13" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="Q14" s="5" t="s">
         <v>415</v>
@@ -3857,7 +3856,7 @@
         <v>113</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="G15" s="5" t="s">
         <v>349</v>
@@ -3877,13 +3876,13 @@
       <c r="L15" s="5"/>
       <c r="M15" s="5"/>
       <c r="N15" s="13" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="O15" s="13" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="P15" s="13" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="Q15" s="5" t="s">
         <v>422</v>
@@ -3906,7 +3905,7 @@
         <v>113</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="G16" s="5" t="s">
         <v>349</v>
@@ -3926,13 +3925,13 @@
       <c r="L16" s="5"/>
       <c r="M16" s="5"/>
       <c r="N16" s="13" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="O16" s="13" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="P16" s="13" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="Q16" s="5" t="s">
         <v>425</v>
@@ -3955,7 +3954,7 @@
         <v>113</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="G17" s="5" t="s">
         <v>349</v>
@@ -3975,13 +3974,13 @@
       <c r="L17" s="5"/>
       <c r="M17" s="5"/>
       <c r="N17" s="13" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="O17" s="13" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="P17" s="13" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="Q17" s="5" t="s">
         <v>418</v>
@@ -4004,7 +4003,7 @@
         <v>113</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="G18" s="5" t="s">
         <v>349</v>
@@ -4024,13 +4023,13 @@
       <c r="L18" s="5"/>
       <c r="M18" s="5"/>
       <c r="N18" s="13" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="O18" s="13" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="P18" s="13" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="Q18" s="5" t="s">
         <v>423</v>
@@ -4053,7 +4052,7 @@
         <v>113</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="G19" s="5" t="s">
         <v>349</v>
@@ -4073,13 +4072,13 @@
       <c r="L19" s="5"/>
       <c r="M19" s="5"/>
       <c r="N19" s="13" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="O19" s="13" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="P19" s="13" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="Q19" s="5" t="s">
         <v>427</v>
@@ -4102,7 +4101,7 @@
         <v>113</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="G20" s="5" t="s">
         <v>349</v>
@@ -4124,13 +4123,13 @@
         <v>581</v>
       </c>
       <c r="N20" s="13" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="O20" s="14" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="P20" s="13" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="Q20" s="5" t="s">
         <v>426</v>
@@ -4153,7 +4152,7 @@
         <v>113</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="G21" s="5" t="s">
         <v>349</v>
@@ -4173,13 +4172,13 @@
       <c r="L21" s="5"/>
       <c r="M21" s="5"/>
       <c r="N21" s="14" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="O21" s="13" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="P21" s="13" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="Q21" s="5" t="s">
         <v>430</v>
@@ -4202,7 +4201,7 @@
         <v>113</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="G22" s="5" t="s">
         <v>349</v>
@@ -4222,13 +4221,13 @@
       <c r="L22" s="5"/>
       <c r="M22" s="5"/>
       <c r="N22" s="13" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="O22" s="13" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="P22" s="13" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="Q22" s="5" t="s">
         <v>429</v>
@@ -4251,7 +4250,7 @@
         <v>113</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="G23" s="5" t="s">
         <v>349</v>
@@ -4271,13 +4270,13 @@
       <c r="L23" s="5"/>
       <c r="M23" s="5"/>
       <c r="N23" s="13" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="O23" s="14" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="P23" s="13" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="Q23" s="5" t="s">
         <v>428</v>
@@ -4300,7 +4299,7 @@
         <v>113</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="G24" s="5" t="s">
         <v>349</v>
@@ -4320,13 +4319,13 @@
       <c r="L24" s="5"/>
       <c r="M24" s="5"/>
       <c r="N24" s="14" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="O24" s="14" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="P24" s="14" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="Q24" s="5" t="s">
         <v>431</v>
@@ -4349,7 +4348,7 @@
         <v>113</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="G25" s="5" t="s">
         <v>349</v>
@@ -4369,13 +4368,13 @@
       <c r="L25" s="5"/>
       <c r="M25" s="5"/>
       <c r="N25" s="13" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="O25" s="13" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="P25" s="13" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="Q25" s="5" t="s">
         <v>432</v>
@@ -4398,7 +4397,7 @@
         <v>113</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="G26" s="5" t="s">
         <v>349</v>
@@ -4418,13 +4417,13 @@
       <c r="L26" s="5"/>
       <c r="M26" s="5"/>
       <c r="N26" s="13" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="O26" s="13" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="P26" s="13" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="Q26" s="5" t="s">
         <v>433</v>
@@ -4447,7 +4446,7 @@
         <v>113</v>
       </c>
       <c r="F27" s="5" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="G27" s="5" t="s">
         <v>349</v>
@@ -4467,13 +4466,13 @@
       <c r="L27" s="5"/>
       <c r="M27" s="5"/>
       <c r="N27" s="13" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="O27" s="14" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="P27" s="13" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="Q27" s="5" t="s">
         <v>434</v>
@@ -4496,7 +4495,7 @@
         <v>113</v>
       </c>
       <c r="F28" s="5" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="G28" s="5" t="s">
         <v>349</v>
@@ -4515,16 +4514,16 @@
       </c>
       <c r="L28" s="5"/>
       <c r="M28" s="10" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="N28" s="13" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="O28" s="13" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="P28" s="13" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="Q28" s="5" t="s">
         <v>437</v>
@@ -4547,7 +4546,7 @@
         <v>113</v>
       </c>
       <c r="F29" s="5" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="G29" s="5" t="s">
         <v>349</v>
@@ -4567,13 +4566,13 @@
       <c r="L29" s="5"/>
       <c r="M29" s="5"/>
       <c r="N29" s="13" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="O29" s="13" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="P29" s="13" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="Q29" s="5" t="s">
         <v>435</v>
@@ -4596,7 +4595,7 @@
         <v>113</v>
       </c>
       <c r="F30" s="5" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="G30" s="5" t="s">
         <v>349</v>
@@ -4616,13 +4615,13 @@
       <c r="L30" s="5"/>
       <c r="M30" s="5"/>
       <c r="N30" s="13" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="O30" s="13" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="P30" s="13" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="Q30" s="5" t="s">
         <v>436</v>
@@ -4645,7 +4644,7 @@
         <v>113</v>
       </c>
       <c r="F31" s="5" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="G31" s="5" t="s">
         <v>349</v>
@@ -4665,13 +4664,13 @@
       <c r="L31" s="5"/>
       <c r="M31" s="5"/>
       <c r="N31" s="13" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="O31" s="13" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="P31" s="13" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="Q31" s="5" t="s">
         <v>439</v>
@@ -4694,7 +4693,7 @@
         <v>113</v>
       </c>
       <c r="F32" s="5" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="G32" s="5" t="s">
         <v>349</v>
@@ -4713,16 +4712,16 @@
       </c>
       <c r="L32" s="5"/>
       <c r="M32" s="10" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="N32" s="13" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="O32" s="13" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="P32" s="13" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="Q32" s="5" t="s">
         <v>438</v>
@@ -4745,7 +4744,7 @@
         <v>113</v>
       </c>
       <c r="F33" s="5" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="G33" s="5" t="s">
         <v>349</v>
@@ -4765,13 +4764,13 @@
       <c r="L33" s="5"/>
       <c r="M33" s="5"/>
       <c r="N33" s="13" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="O33" s="13" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="P33" s="13" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="Q33" s="5" t="s">
         <v>440</v>
@@ -4794,7 +4793,7 @@
         <v>113</v>
       </c>
       <c r="F34" s="5" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="G34" s="5" t="s">
         <v>349</v>
@@ -4814,13 +4813,13 @@
       <c r="L34" s="5"/>
       <c r="M34" s="5"/>
       <c r="N34" s="13" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="O34" s="13" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="P34" s="13" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="Q34" s="5" t="s">
         <v>441</v>
@@ -4843,7 +4842,7 @@
         <v>113</v>
       </c>
       <c r="F35" s="5" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="G35" s="5" t="s">
         <v>349</v>
@@ -4863,13 +4862,13 @@
       <c r="L35" s="5"/>
       <c r="M35" s="5"/>
       <c r="N35" s="13" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="O35" s="13" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="P35" s="13" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="Q35" s="5" t="s">
         <v>443</v>
@@ -4892,7 +4891,7 @@
         <v>113</v>
       </c>
       <c r="F36" s="5" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="G36" s="5" t="s">
         <v>349</v>
@@ -4912,13 +4911,13 @@
       <c r="L36" s="5"/>
       <c r="M36" s="5"/>
       <c r="N36" s="13" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="O36" s="13" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="P36" s="13" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="Q36" s="5" t="s">
         <v>442</v>
@@ -4941,7 +4940,7 @@
         <v>113</v>
       </c>
       <c r="F37" s="5" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="G37" s="5" t="s">
         <v>349</v>
@@ -4961,13 +4960,13 @@
       <c r="L37" s="5"/>
       <c r="M37" s="5"/>
       <c r="N37" s="14" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="O37" s="14" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="P37" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="Q37" s="5" t="s">
         <v>445</v>
@@ -4990,7 +4989,7 @@
         <v>113</v>
       </c>
       <c r="F38" s="5" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="G38" s="5" t="s">
         <v>349</v>
@@ -5010,13 +5009,13 @@
       <c r="L38" s="5"/>
       <c r="M38" s="5"/>
       <c r="N38" s="13" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="O38" s="13" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="P38" s="14" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="Q38" s="5" t="s">
         <v>446</v>
@@ -5039,7 +5038,7 @@
         <v>113</v>
       </c>
       <c r="F39" s="5" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="G39" s="5" t="s">
         <v>349</v>
@@ -5059,13 +5058,13 @@
       <c r="L39" s="5"/>
       <c r="M39" s="5"/>
       <c r="N39" s="13" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="O39" s="13" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="P39" s="13" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="Q39" s="5" t="s">
         <v>448</v>
@@ -5088,7 +5087,7 @@
         <v>113</v>
       </c>
       <c r="F40" s="5" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="G40" s="5" t="s">
         <v>349</v>
@@ -5108,13 +5107,13 @@
       <c r="L40" s="5"/>
       <c r="M40" s="5"/>
       <c r="N40" s="14" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="O40" s="13" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="P40" s="13" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="Q40" s="5" t="s">
         <v>449</v>
@@ -5137,7 +5136,7 @@
         <v>113</v>
       </c>
       <c r="F41" s="5" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="G41" s="5" t="s">
         <v>349</v>
@@ -5157,13 +5156,13 @@
       <c r="L41" s="5"/>
       <c r="M41" s="5"/>
       <c r="N41" s="14" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="O41" s="13" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="P41" s="13" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="Q41" s="5" t="s">
         <v>444</v>
@@ -5186,7 +5185,7 @@
         <v>113</v>
       </c>
       <c r="F42" s="5" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="G42" s="5" t="s">
         <v>349</v>
@@ -5206,13 +5205,13 @@
       <c r="L42" s="5"/>
       <c r="M42" s="5"/>
       <c r="N42" s="13" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="O42" s="13" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="P42" s="13" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="Q42" s="5" t="s">
         <v>450</v>
@@ -5235,7 +5234,7 @@
         <v>113</v>
       </c>
       <c r="F43" s="5" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="G43" s="5" t="s">
         <v>349</v>
@@ -5255,13 +5254,13 @@
       <c r="L43" s="5"/>
       <c r="M43" s="5"/>
       <c r="N43" s="13" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="O43" s="13" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="P43" s="13" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="Q43" s="5" t="s">
         <v>447</v>
@@ -5284,7 +5283,7 @@
         <v>113</v>
       </c>
       <c r="F44" s="5" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="G44" s="5" t="s">
         <v>349</v>
@@ -5304,13 +5303,13 @@
       <c r="L44" s="5"/>
       <c r="M44" s="5"/>
       <c r="N44" s="13" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="O44" s="13" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="P44" s="13" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="Q44" s="5" t="s">
         <v>452</v>
@@ -5333,7 +5332,7 @@
         <v>113</v>
       </c>
       <c r="F45" s="5" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="G45" s="5" t="s">
         <v>349</v>
@@ -5353,13 +5352,13 @@
       <c r="L45" s="10"/>
       <c r="M45" s="10"/>
       <c r="N45" s="13" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="O45" s="13" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="P45" s="13" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="Q45" s="5" t="s">
         <v>454</v>
@@ -5382,7 +5381,7 @@
         <v>113</v>
       </c>
       <c r="F46" s="5" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="G46" s="5" t="s">
         <v>349</v>
@@ -5402,13 +5401,13 @@
       <c r="L46" s="5"/>
       <c r="M46" s="5"/>
       <c r="N46" s="14" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="O46" s="13" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="P46" s="13" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="Q46" s="5" t="s">
         <v>451</v>
@@ -5431,7 +5430,7 @@
         <v>113</v>
       </c>
       <c r="F47" s="5" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="G47" s="5" t="s">
         <v>349</v>
@@ -5451,13 +5450,13 @@
       <c r="L47" s="5"/>
       <c r="M47" s="5"/>
       <c r="N47" s="13" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="O47" s="14" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="P47" s="13" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="Q47" s="5" t="s">
         <v>453</v>
@@ -5480,7 +5479,7 @@
         <v>113</v>
       </c>
       <c r="F48" s="5" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="G48" s="5" t="s">
         <v>349</v>
@@ -5500,13 +5499,13 @@
       <c r="L48" s="5"/>
       <c r="M48" s="5"/>
       <c r="N48" s="13" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="O48" s="13" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="P48" s="13" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="Q48" s="5" t="s">
         <v>455</v>
@@ -5539,13 +5538,13 @@
       <c r="L49" s="5"/>
       <c r="M49" s="5"/>
       <c r="N49" s="13" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="O49" s="13" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="P49" s="13" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="Q49" s="5" t="s">
         <v>456</v>
@@ -5580,16 +5579,16 @@
       <c r="L50" s="9"/>
       <c r="M50" s="9"/>
       <c r="N50" s="13" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="O50" s="13" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="P50" s="13" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="Q50" s="8" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
     </row>
     <row r="51" spans="1:17" x14ac:dyDescent="0.3">
@@ -5621,13 +5620,13 @@
       <c r="L51" s="5"/>
       <c r="M51" s="5"/>
       <c r="N51" s="14" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="O51" s="13" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="P51" s="13" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="Q51" s="5" t="s">
         <v>462</v>
@@ -5664,13 +5663,13 @@
       <c r="L52" s="5"/>
       <c r="M52" s="5"/>
       <c r="N52" s="13" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="O52" s="14" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="P52" s="13" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="Q52" s="5" t="s">
         <v>470</v>
@@ -5703,19 +5702,19 @@
         <v>366</v>
       </c>
       <c r="L53" s="5" t="s">
+        <v>600</v>
+      </c>
+      <c r="M53" s="5" t="s">
         <v>601</v>
       </c>
-      <c r="M53" s="5" t="s">
-        <v>602</v>
-      </c>
       <c r="N53" s="14" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="O53" s="14" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="P53" s="14" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="Q53" s="5" t="s">
         <v>463</v>
@@ -5751,16 +5750,16 @@
         <v>576</v>
       </c>
       <c r="M54" s="10" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="N54" s="13" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="O54" s="13" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="P54" s="13" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="Q54" s="5" t="s">
         <v>459</v>
@@ -5797,13 +5796,13 @@
       <c r="L55" s="2"/>
       <c r="M55" s="2"/>
       <c r="N55" s="13" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="O55" s="13" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="P55" s="13" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="Q55" s="6" t="s">
         <v>461</v>
@@ -5836,17 +5835,17 @@
         <v>370</v>
       </c>
       <c r="L56" s="5" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="M56" s="5"/>
       <c r="N56" s="13" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="O56" s="13" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="P56" s="13" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="Q56" s="5" t="s">
         <v>464</v>
@@ -5881,13 +5880,13 @@
       <c r="L57" s="5"/>
       <c r="M57" s="5"/>
       <c r="N57" s="14" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="O57" s="14" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="P57" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="Q57" s="5" t="s">
         <v>465</v>
@@ -5922,13 +5921,13 @@
       <c r="L58" s="5"/>
       <c r="M58" s="5"/>
       <c r="N58" s="14" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="O58" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="P58" s="14" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="Q58" s="5" t="s">
         <v>466</v>
@@ -5961,17 +5960,17 @@
         <v>370</v>
       </c>
       <c r="L59" s="5" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="M59" s="5"/>
       <c r="N59" s="14" t="s">
+        <v>609</v>
+      </c>
+      <c r="O59" s="14" t="s">
         <v>610</v>
       </c>
-      <c r="O59" s="14" t="s">
-        <v>611</v>
-      </c>
       <c r="P59" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="Q59" s="5" t="s">
         <v>457</v>
@@ -6006,13 +6005,13 @@
       <c r="L60" s="5"/>
       <c r="M60" s="5"/>
       <c r="N60" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="O60" s="14" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="P60" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="Q60" s="5" t="s">
         <v>458</v>
@@ -6049,13 +6048,13 @@
       <c r="L61" s="5"/>
       <c r="M61" s="5"/>
       <c r="N61" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="O61" s="14" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="P61" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="Q61" s="5" t="s">
         <v>467</v>
@@ -6092,13 +6091,13 @@
       <c r="L62" s="5"/>
       <c r="M62" s="5"/>
       <c r="N62" s="14" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="O62" s="14" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="P62" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="Q62" s="5" t="s">
         <v>468</v>
@@ -6133,13 +6132,13 @@
       <c r="L63" s="5"/>
       <c r="M63" s="5"/>
       <c r="N63" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="O63" s="14" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="P63" s="14" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="Q63" s="5" t="s">
         <v>469</v>
@@ -6174,13 +6173,13 @@
       <c r="L64" s="5"/>
       <c r="M64" s="5"/>
       <c r="N64" s="14" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="O64" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="P64" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="Q64" s="5" t="s">
         <v>460</v>
@@ -6215,13 +6214,13 @@
       <c r="L65" s="5"/>
       <c r="M65" s="5"/>
       <c r="N65" s="14" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="O65" s="14" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="P65" s="14" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="Q65" s="5" t="s">
         <v>477</v>
@@ -6258,13 +6257,13 @@
         <v>579</v>
       </c>
       <c r="N66" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="O66" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="P66" s="14" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="Q66" s="5" t="s">
         <v>474</v>
@@ -6299,13 +6298,13 @@
       <c r="L67" s="5"/>
       <c r="M67" s="5"/>
       <c r="N67" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="O67" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="P67" s="14" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="Q67" s="5" t="s">
         <v>475</v>
@@ -6340,13 +6339,13 @@
       <c r="L68" s="5"/>
       <c r="M68" s="5"/>
       <c r="N68" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="O68" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="P68" s="14" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="Q68" s="5" t="s">
         <v>476</v>
@@ -6381,13 +6380,13 @@
       <c r="L69" s="5"/>
       <c r="M69" s="5"/>
       <c r="N69" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="O69" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="P69" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="Q69" s="5" t="s">
         <v>481</v>
@@ -6424,13 +6423,13 @@
         <v>580</v>
       </c>
       <c r="N70" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="O70" s="14" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="P70" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="Q70" s="5" t="s">
         <v>473</v>
@@ -6465,13 +6464,13 @@
       <c r="L71" s="5"/>
       <c r="M71" s="5"/>
       <c r="N71" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="O71" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="P71" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="Q71" s="5" t="s">
         <v>482</v>
@@ -6506,13 +6505,13 @@
       <c r="L72" s="5"/>
       <c r="M72" s="5"/>
       <c r="N72" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="O72" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="P72" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="Q72" s="5" t="s">
         <v>479</v>
@@ -6547,13 +6546,13 @@
       <c r="L73" s="5"/>
       <c r="M73" s="5"/>
       <c r="N73" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="O73" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="P73" s="14" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="Q73" s="5" t="s">
         <v>472</v>
@@ -6588,13 +6587,13 @@
       <c r="L74" s="5"/>
       <c r="M74" s="5"/>
       <c r="N74" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="O74" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="P74" s="14" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="Q74" s="5" t="s">
         <v>478</v>
@@ -6629,13 +6628,13 @@
       <c r="L75" s="5"/>
       <c r="M75" s="5"/>
       <c r="N75" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="O75" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="P75" s="14" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="Q75" s="5" t="s">
         <v>480</v>
@@ -6670,16 +6669,16 @@
       <c r="L76" s="5"/>
       <c r="M76" s="5"/>
       <c r="N76" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="O76" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="P76" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="Q76" s="5" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="77" spans="1:17" x14ac:dyDescent="0.3">
@@ -6711,13 +6710,13 @@
       <c r="L77" s="5"/>
       <c r="M77" s="5"/>
       <c r="N77" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="O77" s="14" t="s">
+        <v>609</v>
+      </c>
+      <c r="P77" s="14" t="s">
         <v>610</v>
-      </c>
-      <c r="P77" s="14" t="s">
-        <v>611</v>
       </c>
       <c r="Q77" s="5" t="s">
         <v>483</v>
@@ -6752,13 +6751,13 @@
       <c r="L78" s="5"/>
       <c r="M78" s="5"/>
       <c r="N78" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="O78" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="P78" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="Q78" s="5" t="s">
         <v>471</v>
@@ -6795,13 +6794,13 @@
         <v>586</v>
       </c>
       <c r="N79" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="O79" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="P79" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="Q79" s="5" t="s">
         <v>491</v>
@@ -6834,17 +6833,17 @@
         <v>372</v>
       </c>
       <c r="L80" s="5" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="M80" s="5"/>
       <c r="N80" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="O80" s="14" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="P80" s="14" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="Q80" s="5" t="s">
         <v>498</v>
@@ -6879,13 +6878,13 @@
       <c r="L81" s="5"/>
       <c r="M81" s="5"/>
       <c r="N81" s="14" t="s">
+        <v>609</v>
+      </c>
+      <c r="O81" s="14" t="s">
         <v>610</v>
       </c>
-      <c r="O81" s="14" t="s">
-        <v>611</v>
-      </c>
       <c r="P81" s="14" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="Q81" s="5" t="s">
         <v>492</v>
@@ -6920,13 +6919,13 @@
       <c r="L82" s="5"/>
       <c r="M82" s="5"/>
       <c r="N82" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="O82" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="P82" s="14" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="Q82" s="5" t="s">
         <v>493</v>
@@ -6961,13 +6960,13 @@
       <c r="L83" s="5"/>
       <c r="M83" s="5"/>
       <c r="N83" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="O83" s="14" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="P83" s="14" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="Q83" s="5" t="s">
         <v>494</v>
@@ -7004,13 +7003,13 @@
         <v>585</v>
       </c>
       <c r="N84" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="O84" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="P84" s="14" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="Q84" s="5" t="s">
         <v>499</v>
@@ -7045,13 +7044,13 @@
       <c r="L85" s="5"/>
       <c r="M85" s="5"/>
       <c r="N85" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="O85" s="14" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="P85" s="14" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="Q85" s="5" t="s">
         <v>486</v>
@@ -7084,20 +7083,20 @@
         <v>372</v>
       </c>
       <c r="L86" s="5" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="M86" s="5"/>
       <c r="N86" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="O86" s="14" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="P86" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="Q86" s="5" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
     </row>
     <row r="87" spans="1:17" x14ac:dyDescent="0.3">
@@ -7129,13 +7128,13 @@
       <c r="L87" s="5"/>
       <c r="M87" s="5"/>
       <c r="N87" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="O87" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="P87" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="Q87" s="5" t="s">
         <v>488</v>
@@ -7170,13 +7169,13 @@
       <c r="L88" s="5"/>
       <c r="M88" s="5"/>
       <c r="N88" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="O88" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="P88" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="Q88" s="5" t="s">
         <v>495</v>
@@ -7211,13 +7210,13 @@
       <c r="L89" s="5"/>
       <c r="M89" s="5"/>
       <c r="N89" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="O89" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="P89" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="Q89" s="5" t="s">
         <v>487</v>
@@ -7252,13 +7251,13 @@
       <c r="L90" s="5"/>
       <c r="M90" s="5"/>
       <c r="N90" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="O90" s="14" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="P90" s="14" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="Q90" s="5" t="s">
         <v>496</v>
@@ -7291,17 +7290,17 @@
         <v>372</v>
       </c>
       <c r="L91" s="5" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="M91" s="5"/>
       <c r="N91" s="14" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="O91" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="P91" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="Q91" s="5" t="s">
         <v>500</v>
@@ -7338,13 +7337,13 @@
         <v>584</v>
       </c>
       <c r="N92" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="O92" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="P92" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="Q92" s="5" t="s">
         <v>490</v>
@@ -7387,13 +7386,13 @@
       <c r="L93" s="2"/>
       <c r="M93" s="2"/>
       <c r="N93" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="O93" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="P93" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="Q93" s="6" t="s">
         <v>497</v>
@@ -7430,13 +7429,13 @@
         <v>583</v>
       </c>
       <c r="N94" s="14" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="O94" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="P94" s="14" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="Q94" s="5" t="s">
         <v>484</v>
@@ -7471,13 +7470,13 @@
       <c r="L95" s="5"/>
       <c r="M95" s="5"/>
       <c r="N95" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="O95" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="P95" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="Q95" s="5" t="s">
         <v>485</v>
@@ -7512,13 +7511,13 @@
       <c r="L96" s="5"/>
       <c r="M96" s="5"/>
       <c r="N96" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="O96" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="P96" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="Q96" s="5" t="s">
         <v>489</v>
@@ -7551,17 +7550,17 @@
         <v>372</v>
       </c>
       <c r="L97" s="5" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="M97" s="5"/>
       <c r="N97" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="O97" s="14" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="P97" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="Q97" s="5" t="s">
         <v>501</v>
@@ -7596,13 +7595,13 @@
       <c r="L98" s="5"/>
       <c r="M98" s="5"/>
       <c r="N98" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="O98" s="14" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="P98" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="Q98" s="5" t="s">
         <v>502</v>
@@ -7637,16 +7636,16 @@
       <c r="L99" s="5"/>
       <c r="M99" s="5"/>
       <c r="N99" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="O99" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="P99" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="Q99" s="22" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
     </row>
     <row r="100" spans="1:17" ht="94.5" x14ac:dyDescent="0.3">
@@ -7680,13 +7679,13 @@
         <v>587</v>
       </c>
       <c r="N100" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="O100" s="14" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="P100" s="14" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="Q100" s="5" t="s">
         <v>504</v>
@@ -7721,16 +7720,16 @@
       <c r="L101" s="5"/>
       <c r="M101" s="5"/>
       <c r="N101" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="O101" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="P101" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="Q101" s="5" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
     </row>
     <row r="102" spans="1:17" ht="95.25" x14ac:dyDescent="0.3">
@@ -7765,16 +7764,16 @@
       </c>
       <c r="L102" s="2"/>
       <c r="M102" s="12" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="N102" s="14" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="O102" s="14" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="P102" s="14" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="Q102" s="6" t="s">
         <v>509</v>
@@ -7807,17 +7806,17 @@
         <v>372</v>
       </c>
       <c r="L103" s="5" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="M103" s="5"/>
       <c r="N103" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="O103" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="P103" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="Q103" s="5" t="s">
         <v>503</v>
@@ -7852,13 +7851,13 @@
       <c r="L104" s="5"/>
       <c r="M104" s="5"/>
       <c r="N104" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="O104" s="14" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="P104" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="Q104" s="5" t="s">
         <v>510</v>
@@ -7891,23 +7890,23 @@
         <v>372</v>
       </c>
       <c r="L105" s="5" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="M105" s="5"/>
       <c r="N105" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="O105" s="14" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="P105" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="Q105" s="5" t="s">
         <v>507</v>
       </c>
     </row>
-    <row r="106" spans="1:17" ht="81" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:17" ht="54" x14ac:dyDescent="0.3">
       <c r="A106" s="4" t="s">
         <v>115</v>
       </c>
@@ -7937,16 +7936,16 @@
         <v>715</v>
       </c>
       <c r="M106" s="10" t="s">
-        <v>588</v>
+        <v>714</v>
       </c>
       <c r="N106" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="O106" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="P106" s="14" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="Q106" s="5" t="s">
         <v>505</v>
@@ -7987,17 +7986,17 @@
         <v>372</v>
       </c>
       <c r="L107" s="5" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="M107" s="5"/>
       <c r="N107" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="O107" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="P107" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="Q107" s="5" t="s">
         <v>512</v>
@@ -8032,13 +8031,13 @@
       <c r="L108" s="5"/>
       <c r="M108" s="5"/>
       <c r="N108" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="O108" s="14" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="P108" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="Q108" s="5" t="s">
         <v>511</v>
@@ -8075,13 +8074,13 @@
       <c r="L109" s="2"/>
       <c r="M109" s="2"/>
       <c r="N109" s="14" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="O109" s="14" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="P109" s="14" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="Q109" s="6" t="s">
         <v>506</v>
@@ -8116,13 +8115,13 @@
       <c r="L110" s="5"/>
       <c r="M110" s="5"/>
       <c r="N110" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="O110" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="P110" s="14" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="Q110" s="5" t="s">
         <v>508</v>
@@ -8157,16 +8156,16 @@
       <c r="L111" s="5"/>
       <c r="M111" s="5"/>
       <c r="N111" s="14" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="O111" s="14" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="P111" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="Q111" s="22" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
     </row>
     <row r="112" spans="1:17" x14ac:dyDescent="0.3">
@@ -8198,13 +8197,13 @@
       <c r="L112" s="5"/>
       <c r="M112" s="5"/>
       <c r="N112" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="O112" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="P112" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="Q112" s="5" t="s">
         <v>516</v>
@@ -8237,17 +8236,17 @@
         <v>381</v>
       </c>
       <c r="L113" s="5" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="M113" s="5"/>
       <c r="N113" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="O113" s="14" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="P113" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="Q113" s="5" t="s">
         <v>513</v>
@@ -8280,17 +8279,17 @@
         <v>370</v>
       </c>
       <c r="L114" s="5" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="M114" s="5"/>
       <c r="N114" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="O114" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="P114" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="Q114" s="5" t="s">
         <v>518</v>
@@ -8325,13 +8324,13 @@
       <c r="L115" s="5"/>
       <c r="M115" s="5"/>
       <c r="N115" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="O115" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="P115" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="Q115" s="5" t="s">
         <v>517</v>
@@ -8365,16 +8364,16 @@
       </c>
       <c r="L116" s="5"/>
       <c r="M116" s="10" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="N116" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="O116" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="P116" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="Q116" s="5" t="s">
         <v>519</v>
@@ -8409,13 +8408,13 @@
       <c r="L117" s="5"/>
       <c r="M117" s="5"/>
       <c r="N117" s="14" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="O117" s="14" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="P117" s="14" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="Q117" s="5" t="s">
         <v>514</v>
@@ -8449,16 +8448,16 @@
       </c>
       <c r="L118" s="5"/>
       <c r="M118" s="10" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="N118" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="O118" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="P118" s="13" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="Q118" s="5" t="s">
         <v>515</v>
@@ -8493,13 +8492,13 @@
       <c r="L119" s="5"/>
       <c r="M119" s="5"/>
       <c r="N119" s="13" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="O119" s="13" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="P119" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="Q119" s="5" t="s">
         <v>531</v>
@@ -8534,13 +8533,13 @@
       <c r="L120" s="5"/>
       <c r="M120" s="5"/>
       <c r="N120" s="13" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="O120" s="13" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="P120" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="Q120" s="5" t="s">
         <v>530</v>
@@ -8575,13 +8574,13 @@
       <c r="L121" s="5"/>
       <c r="M121" s="5"/>
       <c r="N121" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="O121" s="14" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="P121" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="Q121" s="5" t="s">
         <v>520</v>
@@ -8615,16 +8614,16 @@
       </c>
       <c r="L122" s="5"/>
       <c r="M122" s="10" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="N122" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="O122" s="14" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="P122" s="14" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="Q122" s="5" t="s">
         <v>523</v>
@@ -8659,13 +8658,13 @@
       <c r="L123" s="5"/>
       <c r="M123" s="5"/>
       <c r="N123" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="O123" s="14" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="P123" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="Q123" s="5" t="s">
         <v>526</v>
@@ -8700,13 +8699,13 @@
       <c r="L124" s="5"/>
       <c r="M124" s="5"/>
       <c r="N124" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="O124" s="14" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="P124" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="Q124" s="5" t="s">
         <v>527</v>
@@ -8741,13 +8740,13 @@
       <c r="L125" s="5"/>
       <c r="M125" s="5"/>
       <c r="N125" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="O125" s="14" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="P125" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="Q125" s="5" t="s">
         <v>524</v>
@@ -8782,13 +8781,13 @@
       <c r="L126" s="5"/>
       <c r="M126" s="5"/>
       <c r="N126" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="O126" s="13" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="P126" s="13" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="Q126" s="5" t="s">
         <v>521</v>
@@ -8822,16 +8821,16 @@
       </c>
       <c r="L127" s="5"/>
       <c r="M127" s="10" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="N127" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="O127" s="14" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="P127" s="14" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="Q127" s="5" t="s">
         <v>525</v>
@@ -8864,17 +8863,17 @@
         <v>372</v>
       </c>
       <c r="L128" s="5" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="M128" s="5"/>
       <c r="N128" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="O128" s="14" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="P128" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="Q128" s="5" t="s">
         <v>528</v>
@@ -8909,13 +8908,13 @@
       <c r="L129" s="5"/>
       <c r="M129" s="5"/>
       <c r="N129" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="O129" s="14" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="P129" s="14" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="Q129" s="5" t="s">
         <v>522</v>
@@ -8950,13 +8949,13 @@
       <c r="L130" s="5"/>
       <c r="M130" s="5"/>
       <c r="N130" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="O130" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="P130" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="Q130" s="5" t="s">
         <v>529</v>
@@ -8991,13 +8990,13 @@
       <c r="L131" s="5"/>
       <c r="M131" s="5"/>
       <c r="N131" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="O131" s="13" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="P131" s="13" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="Q131" s="5" t="s">
         <v>549</v>
@@ -9032,13 +9031,13 @@
       <c r="L132" s="5"/>
       <c r="M132" s="5"/>
       <c r="N132" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="O132" s="13" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="P132" s="14" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="Q132" s="5" t="s">
         <v>538</v>
@@ -9073,13 +9072,13 @@
       <c r="L133" s="5"/>
       <c r="M133" s="5"/>
       <c r="N133" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="O133" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="P133" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="Q133" s="5" t="s">
         <v>545</v>
@@ -9114,13 +9113,13 @@
       <c r="L134" s="5"/>
       <c r="M134" s="5"/>
       <c r="N134" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="O134" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="P134" s="14" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="Q134" s="5" t="s">
         <v>533</v>
@@ -9155,13 +9154,13 @@
       <c r="L135" s="5"/>
       <c r="M135" s="5"/>
       <c r="N135" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="O135" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="P135" s="13" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="Q135" s="5" t="s">
         <v>542</v>
@@ -9196,13 +9195,13 @@
       <c r="L136" s="5"/>
       <c r="M136" s="5"/>
       <c r="N136" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="O136" s="14" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="P136" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="Q136" s="5" t="s">
         <v>537</v>
@@ -9237,16 +9236,16 @@
       <c r="L137" s="5"/>
       <c r="M137" s="5"/>
       <c r="N137" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="O137" s="14" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="P137" s="14" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="Q137" s="5" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
     </row>
     <row r="138" spans="1:17" x14ac:dyDescent="0.3">
@@ -9278,13 +9277,13 @@
       <c r="L138" s="5"/>
       <c r="M138" s="5"/>
       <c r="N138" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="O138" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="P138" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="Q138" s="5" t="s">
         <v>535</v>
@@ -9319,13 +9318,13 @@
       <c r="L139" s="5"/>
       <c r="M139" s="5"/>
       <c r="N139" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="O139" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="P139" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="Q139" s="5" t="s">
         <v>540</v>
@@ -9360,16 +9359,16 @@
       <c r="L140" s="5"/>
       <c r="M140" s="5"/>
       <c r="N140" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="O140" s="14" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="P140" s="14" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="Q140" s="5" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
     </row>
     <row r="141" spans="1:17" x14ac:dyDescent="0.3">
@@ -9401,13 +9400,13 @@
       <c r="L141" s="5"/>
       <c r="M141" s="5"/>
       <c r="N141" s="14" t="s">
+        <v>609</v>
+      </c>
+      <c r="O141" s="14" t="s">
         <v>610</v>
       </c>
-      <c r="O141" s="14" t="s">
-        <v>611</v>
-      </c>
       <c r="P141" s="14" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="Q141" s="5" t="s">
         <v>543</v>
@@ -9442,13 +9441,13 @@
       <c r="L142" s="5"/>
       <c r="M142" s="5"/>
       <c r="N142" s="13" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="O142" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="P142" s="13" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="Q142" s="5" t="s">
         <v>544</v>
@@ -9482,16 +9481,16 @@
       </c>
       <c r="L143" s="5"/>
       <c r="M143" s="10" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="N143" s="13" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="O143" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="P143" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="Q143" s="5" t="s">
         <v>536</v>
@@ -9526,13 +9525,13 @@
       <c r="L144" s="5"/>
       <c r="M144" s="5"/>
       <c r="N144" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="O144" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="P144" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="Q144" s="5" t="s">
         <v>546</v>
@@ -9562,18 +9561,18 @@
       <c r="I145" s="5"/>
       <c r="J145" s="5"/>
       <c r="K145" s="5" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="L145" s="5"/>
       <c r="M145" s="5"/>
       <c r="N145" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="O145" s="14" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="P145" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="Q145" s="5" t="s">
         <v>532</v>
@@ -9603,18 +9602,18 @@
       <c r="I146" s="5"/>
       <c r="J146" s="5"/>
       <c r="K146" s="5" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="L146" s="5"/>
       <c r="M146" s="5"/>
       <c r="N146" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="O146" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="P146" s="13" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="Q146" s="5" t="s">
         <v>534</v>
@@ -9649,13 +9648,13 @@
       <c r="L147" s="5"/>
       <c r="M147" s="5"/>
       <c r="N147" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="O147" s="14" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="P147" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="Q147" s="5" t="s">
         <v>547</v>
@@ -9689,16 +9688,16 @@
       </c>
       <c r="L148" s="5"/>
       <c r="M148" s="10" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="N148" s="14" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="O148" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="P148" s="14" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="Q148" s="5" t="s">
         <v>548</v>
@@ -9732,16 +9731,16 @@
       </c>
       <c r="L149" s="5"/>
       <c r="M149" s="10" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="N149" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="O149" s="14" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="P149" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="Q149" s="5" t="s">
         <v>541</v>
@@ -9776,13 +9775,13 @@
       <c r="L150" s="5"/>
       <c r="M150" s="5"/>
       <c r="N150" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="O150" s="14" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="P150" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="Q150" s="5" t="s">
         <v>550</v>
@@ -9817,13 +9816,13 @@
       <c r="L151" s="5"/>
       <c r="M151" s="5"/>
       <c r="N151" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="O151" s="14" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="P151" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="Q151" s="5" t="s">
         <v>539</v>
@@ -9858,13 +9857,13 @@
       <c r="L152" s="5"/>
       <c r="M152" s="5"/>
       <c r="N152" s="14" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="O152" s="14" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="P152" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="Q152" s="5" t="s">
         <v>552</v>
@@ -9899,13 +9898,13 @@
       <c r="L153" s="5"/>
       <c r="M153" s="5"/>
       <c r="N153" s="13" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="O153" s="13" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="P153" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="Q153" s="5" t="s">
         <v>553</v>
@@ -9919,7 +9918,7 @@
         <v>300</v>
       </c>
       <c r="C154" s="5" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="D154" s="5" t="s">
         <v>4</v>
@@ -9940,13 +9939,13 @@
       <c r="L154" s="5"/>
       <c r="M154" s="5"/>
       <c r="N154" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="O154" s="14" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="P154" s="14" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="Q154" s="5" t="s">
         <v>554</v>
@@ -9981,13 +9980,13 @@
       <c r="L155" s="5"/>
       <c r="M155" s="5"/>
       <c r="N155" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="O155" s="14" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="P155" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="Q155" s="5" t="s">
         <v>556</v>
@@ -10022,13 +10021,13 @@
       <c r="L156" s="5"/>
       <c r="M156" s="5"/>
       <c r="N156" s="13" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="O156" s="13" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="P156" s="13" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="Q156" s="5" t="s">
         <v>551</v>
@@ -10063,13 +10062,13 @@
       <c r="L157" s="5"/>
       <c r="M157" s="5"/>
       <c r="N157" s="13" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="O157" s="13" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="P157" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="Q157" s="5" t="s">
         <v>560</v>
@@ -10104,13 +10103,13 @@
       <c r="L158" s="5"/>
       <c r="M158" s="5"/>
       <c r="N158" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="O158" s="14" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="P158" s="14" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="Q158" s="5" t="s">
         <v>561</v>
@@ -10143,17 +10142,17 @@
         <v>372</v>
       </c>
       <c r="L159" s="5" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="M159" s="5"/>
       <c r="N159" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="O159" s="14" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="P159" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="Q159" s="5" t="s">
         <v>563</v>
@@ -10186,17 +10185,17 @@
         <v>372</v>
       </c>
       <c r="L160" s="5" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="M160" s="5"/>
       <c r="N160" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="O160" s="14" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="P160" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="Q160" s="5" t="s">
         <v>559</v>
@@ -10231,13 +10230,13 @@
       <c r="L161" s="5"/>
       <c r="M161" s="5"/>
       <c r="N161" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="O161" s="14" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="P161" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="Q161" s="5" t="s">
         <v>566</v>
@@ -10270,17 +10269,17 @@
         <v>370</v>
       </c>
       <c r="L162" s="5" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="M162" s="5"/>
       <c r="N162" s="14" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="O162" s="14" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="P162" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="Q162" s="5" t="s">
         <v>567</v>
@@ -10315,13 +10314,13 @@
       <c r="L163" s="5"/>
       <c r="M163" s="5"/>
       <c r="N163" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="O163" s="14" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="P163" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="Q163" s="5" t="s">
         <v>569</v>
@@ -10356,13 +10355,13 @@
       <c r="L164" s="5"/>
       <c r="M164" s="5"/>
       <c r="N164" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="O164" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="P164" s="14" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="Q164" s="5" t="s">
         <v>555</v>
@@ -10396,16 +10395,16 @@
       </c>
       <c r="L165" s="5"/>
       <c r="M165" s="10" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="N165" s="14" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="O165" s="14" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="P165" s="14" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="Q165" s="5" t="s">
         <v>568</v>
@@ -10438,17 +10437,17 @@
         <v>376</v>
       </c>
       <c r="L166" s="5" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="M166" s="5"/>
       <c r="N166" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="O166" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="P166" s="14" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="Q166" s="5" t="s">
         <v>557</v>
@@ -10482,16 +10481,16 @@
       </c>
       <c r="L167" s="5"/>
       <c r="M167" s="10" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="N167" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="O167" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="P167" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="Q167" s="5" t="s">
         <v>558</v>
@@ -10524,17 +10523,17 @@
         <v>376</v>
       </c>
       <c r="L168" s="5" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="M168" s="5"/>
       <c r="N168" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="O168" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="P168" s="14" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="Q168" s="5" t="s">
         <v>562</v>
@@ -10567,17 +10566,17 @@
         <v>376</v>
       </c>
       <c r="L169" s="5" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="M169" s="5"/>
       <c r="N169" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="O169" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="P169" s="14" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="Q169" s="5" t="s">
         <v>565</v>
@@ -10612,13 +10611,13 @@
       <c r="L170" s="5"/>
       <c r="M170" s="5"/>
       <c r="N170" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="O170" s="14" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="P170" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="Q170" s="5" t="s">
         <v>564</v>
@@ -10653,13 +10652,13 @@
       <c r="L171" s="5"/>
       <c r="M171" s="5"/>
       <c r="N171" s="13" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="O171" s="13" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="P171" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="Q171" s="5" t="s">
         <v>571</v>
@@ -10694,13 +10693,13 @@
       <c r="L172" s="5"/>
       <c r="M172" s="5"/>
       <c r="N172" s="14" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="O172" s="14" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="P172" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="Q172" s="5" t="s">
         <v>572</v>
@@ -10735,13 +10734,13 @@
       <c r="L173" s="5"/>
       <c r="M173" s="5"/>
       <c r="N173" s="13" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="O173" s="13" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="P173" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="Q173" s="5" t="s">
         <v>570</v>
@@ -10776,13 +10775,13 @@
       <c r="L174" s="5"/>
       <c r="M174" s="5"/>
       <c r="N174" s="14" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="O174" s="14" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="P174" s="14" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="Q174" s="5" t="s">
         <v>573</v>
@@ -10802,7 +10801,7 @@
         <v>331</v>
       </c>
       <c r="E175" s="6" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="F175" s="6" t="s">
         <v>332</v>
@@ -10831,13 +10830,13 @@
         <v>361</v>
       </c>
       <c r="C176" s="6" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="D176" s="6" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="E176" s="6" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="F176" s="6"/>
       <c r="G176" s="6" t="s">
@@ -10869,10 +10868,10 @@
         <v>335</v>
       </c>
       <c r="D177" s="6" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="E177" s="6" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="F177" s="6" t="s">
         <v>397</v>
@@ -10906,10 +10905,10 @@
         <v>335</v>
       </c>
       <c r="D178" s="6" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="E178" s="6" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="F178" s="6" t="s">
         <v>397</v>
@@ -10943,10 +10942,10 @@
         <v>342</v>
       </c>
       <c r="D179" s="6" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="E179" s="6" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="F179" s="6" t="s">
         <v>574</v>
@@ -10982,10 +10981,10 @@
         <v>342</v>
       </c>
       <c r="D180" s="6" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="E180" s="6" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="F180" s="6" t="s">
         <v>574</v>
@@ -11015,22 +11014,22 @@
         <v>118</v>
       </c>
       <c r="B181" s="6" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="C181" s="6" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="D181" s="6" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="E181" s="6" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="F181" s="7" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="G181" s="6" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="H181" s="6"/>
       <c r="I181" s="6"/>
@@ -11042,7 +11041,7 @@
       <c r="O181" s="16"/>
       <c r="P181" s="16"/>
       <c r="Q181" s="6" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
     </row>
     <row r="182" spans="1:17" x14ac:dyDescent="0.3">
@@ -11053,16 +11052,16 @@
         <v>336</v>
       </c>
       <c r="C182" s="6" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="D182" s="6" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="E182" s="6" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="F182" s="7" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="G182" s="6"/>
       <c r="H182" s="6"/>
@@ -11075,27 +11074,27 @@
       <c r="O182" s="16"/>
       <c r="P182" s="16"/>
       <c r="Q182" s="6" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
     </row>
     <row r="183" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A183" s="6" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="B183" s="6" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="C183" s="6" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="D183" s="6" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="E183" s="6" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="F183" s="6" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="G183" s="6"/>
       <c r="H183" s="6"/>
@@ -11108,7 +11107,7 @@
       <c r="O183" s="16"/>
       <c r="P183" s="16"/>
       <c r="Q183" s="6" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
     </row>
     <row r="184" spans="1:17" x14ac:dyDescent="0.3">
@@ -11116,19 +11115,19 @@
         <v>118</v>
       </c>
       <c r="B184" s="6" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="C184" s="6" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="D184" s="6" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="E184" s="6" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="F184" s="6" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="G184" s="6"/>
       <c r="H184" s="6"/>
@@ -11141,7 +11140,7 @@
       <c r="O184" s="16"/>
       <c r="P184" s="16"/>
       <c r="Q184" s="6" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
     </row>
     <row r="185" spans="1:17" x14ac:dyDescent="0.3">
@@ -11149,19 +11148,19 @@
         <v>116</v>
       </c>
       <c r="B185" s="6" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="C185" s="6" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="D185" s="6" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="E185" s="6" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="F185" s="6" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="G185" s="6"/>
       <c r="H185" s="6"/>
@@ -11174,7 +11173,7 @@
       <c r="O185" s="16"/>
       <c r="P185" s="16"/>
       <c r="Q185" s="6" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
     </row>
     <row r="186" spans="1:17" x14ac:dyDescent="0.3">
@@ -11182,19 +11181,19 @@
         <v>118</v>
       </c>
       <c r="B186" s="6" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="C186" s="6" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="D186" s="6" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="E186" s="6" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="F186" s="6" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="G186" s="6"/>
       <c r="H186" s="6"/>
@@ -11207,7 +11206,7 @@
       <c r="O186" s="16"/>
       <c r="P186" s="16"/>
       <c r="Q186" s="6" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="187" spans="1:17" x14ac:dyDescent="0.3">
@@ -11215,26 +11214,26 @@
         <v>116</v>
       </c>
       <c r="B187" s="6" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="C187" s="6" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="D187" s="6" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="E187" s="6" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="F187" s="6" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="G187" s="6"/>
       <c r="H187" s="6"/>
       <c r="I187" s="6"/>
       <c r="J187" s="6"/>
       <c r="K187" s="6" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="L187" s="2"/>
       <c r="M187" s="2"/>
@@ -11242,81 +11241,81 @@
       <c r="O187" s="16"/>
       <c r="P187" s="16"/>
       <c r="Q187" s="6" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
     </row>
     <row r="188" spans="1:17" ht="95.25" x14ac:dyDescent="0.3">
       <c r="A188" s="6" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="B188" s="6" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="C188" s="6" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="D188" s="6" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="E188" s="6" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="F188" s="6" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="G188" s="6"/>
       <c r="H188" s="6"/>
       <c r="I188" s="6"/>
       <c r="J188" s="6"/>
       <c r="K188" s="6" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="L188" s="2"/>
       <c r="M188" s="21" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="N188" s="16"/>
       <c r="O188" s="16"/>
       <c r="P188" s="16"/>
       <c r="Q188" s="6" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="189" spans="1:17" ht="162.75" x14ac:dyDescent="0.3">
       <c r="A189" s="6" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="B189" s="6" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="C189" s="6" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="D189" s="6" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="E189" s="6" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="F189" s="6" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="G189" s="6"/>
       <c r="H189" s="6"/>
       <c r="I189" s="6"/>
       <c r="J189" s="6"/>
       <c r="K189" s="5" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="L189" s="2"/>
       <c r="M189" s="21" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="N189" s="16"/>
       <c r="O189" s="16"/>
       <c r="P189" s="16"/>
       <c r="Q189" s="6" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="190" spans="1:17" ht="135.75" x14ac:dyDescent="0.3">
@@ -11324,36 +11323,36 @@
         <v>117</v>
       </c>
       <c r="B190" s="6" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="C190" s="6" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="D190" s="6" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="E190" s="6" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="F190" s="6" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="G190" s="6"/>
       <c r="H190" s="6"/>
       <c r="I190" s="6"/>
       <c r="J190" s="6"/>
       <c r="K190" s="5" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="L190" s="2"/>
       <c r="M190" s="21" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="N190" s="16"/>
       <c r="O190" s="16"/>
       <c r="P190" s="16"/>
       <c r="Q190" s="6" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
     </row>
     <row r="191" spans="1:17" ht="149.25" x14ac:dyDescent="0.3">
@@ -11361,36 +11360,36 @@
         <v>117</v>
       </c>
       <c r="B191" s="6" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="C191" s="6" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="D191" s="6" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="E191" s="6" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="F191" s="6" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="G191" s="6"/>
       <c r="H191" s="6"/>
       <c r="I191" s="6"/>
       <c r="J191" s="6"/>
       <c r="K191" s="6" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="L191" s="2"/>
       <c r="M191" s="21" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="N191" s="16"/>
       <c r="O191" s="16"/>
       <c r="P191" s="16"/>
       <c r="Q191" s="6" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
     </row>
     <row r="192" spans="1:17" ht="27" x14ac:dyDescent="0.3">
@@ -11398,26 +11397,26 @@
         <v>118</v>
       </c>
       <c r="B192" s="6" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="C192" s="6" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="D192" s="6" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="E192" s="6" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="F192" s="6"/>
       <c r="G192" s="7" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="H192" s="6"/>
       <c r="I192" s="6"/>
       <c r="J192" s="6"/>
       <c r="K192" s="6" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="L192" s="2"/>
       <c r="M192" s="2"/>
@@ -11425,44 +11424,44 @@
       <c r="O192" s="16"/>
       <c r="P192" s="16"/>
       <c r="Q192" s="6" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
     </row>
     <row r="193" spans="1:17" ht="54.75" x14ac:dyDescent="0.3">
       <c r="A193" s="6" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="B193" s="6" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="C193" s="6" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="D193" s="6" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="E193" s="6" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="F193" s="6" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="G193" s="6"/>
       <c r="H193" s="6"/>
       <c r="I193" s="6"/>
       <c r="J193" s="6"/>
       <c r="K193" s="6" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="L193" s="2"/>
       <c r="M193" s="21" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="N193" s="16"/>
       <c r="O193" s="16"/>
       <c r="P193" s="16"/>
       <c r="Q193" s="6" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
     </row>
     <row r="194" spans="1:17" ht="27.75" x14ac:dyDescent="0.3">
@@ -11470,36 +11469,36 @@
         <v>117</v>
       </c>
       <c r="B194" s="6" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="C194" s="6" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="D194" s="6" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="E194" s="6" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="F194" s="6" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="G194" s="6"/>
       <c r="H194" s="6"/>
       <c r="I194" s="6"/>
       <c r="J194" s="6"/>
       <c r="K194" s="6" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="L194" s="2"/>
       <c r="M194" s="21" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="N194" s="16"/>
       <c r="O194" s="16"/>
       <c r="P194" s="16"/>
       <c r="Q194" s="6" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
     </row>
   </sheetData>

--- a/app/convert/forest_sample_template.xlsx
+++ b/app/convert/forest_sample_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TAX-JUNGYOON\forest-app\app\convert\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2ADC7A58-42DF-4599-8893-3039937187E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54808EBC-B9F5-45ED-B2AC-7363DEE5A77B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="658" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2616,7 +2616,21 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>숲속의집
+    <t>6인실
+→ 단풍나무, 때죽나무
+→ 평일 75,000 / 주말 134,000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>매월1일 08시(지역주민선착순)
+매월1일 09시(선착순전환)
+지역주민 우선배정 객실(공지사항)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>매달1일오전09시(지역주민선착순)
+매달6일오전09시(대기신청가능)
+숲속의집
 1호
 휴양관
 103호
@@ -2625,18 +2639,6 @@
 204호
 글램핑
 1동, 2동</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>6인실
-→ 단풍나무, 때죽나무
-→ 평일 75,000 / 주말 134,000</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>매월1일 08시(지역주민선착순)
-매월1일 09시(선착순전환)
-지역주민 우선배정 객실(공지사항)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -7933,10 +7935,10 @@
         <v>368</v>
       </c>
       <c r="L106" s="5" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="M106" s="10" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="N106" s="14" t="s">
         <v>606</v>
@@ -10242,7 +10244,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="162" spans="1:17" ht="148.5" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:17" ht="175.5" x14ac:dyDescent="0.3">
       <c r="A162" s="4" t="s">
         <v>118</v>
       </c>
@@ -10269,7 +10271,7 @@
         <v>370</v>
       </c>
       <c r="L162" s="5" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="M162" s="5"/>
       <c r="N162" s="14" t="s">

--- a/app/convert/forest_sample_template.xlsx
+++ b/app/convert/forest_sample_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TAX-JUNGYOON\forest-app\app\convert\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54808EBC-B9F5-45ED-B2AC-7363DEE5A77B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D3E9690-530B-4523-876A-97F93BCE6D1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="658" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2332" uniqueCount="716">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2332" uniqueCount="717">
   <si>
     <t>시설명</t>
   </si>
@@ -2639,6 +2639,10 @@
 204호
 글램핑
 1동, 2동</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>매주 목요일 10시</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -7979,7 +7983,7 @@
         <v>323</v>
       </c>
       <c r="I107" s="5" t="s">
-        <v>407</v>
+        <v>716</v>
       </c>
       <c r="J107" s="5" t="s">
         <v>407</v>

--- a/app/convert/forest_sample_template.xlsx
+++ b/app/convert/forest_sample_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TAX-JUNGYOON\forest-app\app\convert\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D3E9690-530B-4523-876A-97F93BCE6D1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A561CA1-0ED8-45C3-A9FE-219C67DAA6F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="658" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2332" uniqueCount="717">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2333" uniqueCount="718">
   <si>
     <t>시설명</t>
   </si>
@@ -2643,6 +2643,10 @@
   </si>
   <si>
     <t>매주 목요일 10시</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>매달 1일 09:00 ~ 2일 23:59</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -7430,7 +7434,9 @@
       <c r="K94" s="5" t="s">
         <v>374</v>
       </c>
-      <c r="L94" s="5"/>
+      <c r="L94" s="5" t="s">
+        <v>717</v>
+      </c>
       <c r="M94" s="10" t="s">
         <v>583</v>
       </c>

--- a/app/convert/forest_sample_template.xlsx
+++ b/app/convert/forest_sample_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TAX-JUNGYOON\forest-app\app\convert\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A561CA1-0ED8-45C3-A9FE-219C67DAA6F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB20EB22-DFC2-4AAD-91BA-110B7C04FE93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="658" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2333" uniqueCount="718">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4666" uniqueCount="718">
   <si>
     <t>시설명</t>
   </si>
@@ -2646,7 +2646,8 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>매달 1일 09:00 ~ 2일 23:59</t>
+    <t>매월 1일 09:00 ~ 2일 23:59 (지역주민우선예약)
+매월 3일 09:00 (일반예약전환)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>

--- a/app/convert/forest_sample_template.xlsx
+++ b/app/convert/forest_sample_template.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TAX-JUNGYOON\forest-app\app\convert\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB20EB22-DFC2-4AAD-91BA-110B7C04FE93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99472A04-9E51-4B5E-A6F2-DF51971ED33B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="658" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,14 +16,14 @@
     <sheet name="샘플" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">샘플!$B$1:$Q$180</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">샘플!$B$1:$Q$181</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4666" uniqueCount="718">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2348" uniqueCount="728">
   <si>
     <t>시설명</t>
   </si>
@@ -2649,6 +2649,51 @@
     <t>매월 1일 09:00 ~ 2일 23:59 (지역주민우선예약)
 매월 3일 09:00 (일반예약전환)</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>연립동C동(신축) 2022년
+5인실(구조동일)
+평일 58,000원 / 주말 106,000원
+2층 신선봉, 수리봉 추천</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>정감록명당체험마을
+물고기자리4인 평일 126,000원 / 주말 180,000원</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>신축2인실 21호~25호
+평일 48,000원 / 주말 80,000원
+23,24호가 위쪽이라 프라이빗한데 주차장과 거리가 있어 짐나르기 힘듬</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>충북</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>청주시상당구</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>미원별빛자연휴양림</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>자연휴양림</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>공립</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>다음월</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.foresttrip.go.kr/indvz/main.do?hmpgId=ID02030132</t>
   </si>
 </sst>
 </file>
@@ -3142,7 +3187,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q194"/>
+  <dimension ref="A1:Q195"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13" style="18" bestFit="1" customWidth="1"/>
@@ -4146,7 +4191,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:17" ht="54" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
         <v>101</v>
       </c>
@@ -4181,7 +4226,9 @@
         <v>7</v>
       </c>
       <c r="L21" s="5"/>
-      <c r="M21" s="5"/>
+      <c r="M21" s="5" t="s">
+        <v>718</v>
+      </c>
       <c r="N21" s="14" t="s">
         <v>611</v>
       </c>
@@ -6817,7 +6864,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="80" spans="1:17" ht="40.5" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:17" ht="54" x14ac:dyDescent="0.3">
       <c r="A80" s="4" t="s">
         <v>101</v>
       </c>
@@ -6846,7 +6893,9 @@
       <c r="L80" s="5" t="s">
         <v>699</v>
       </c>
-      <c r="M80" s="5"/>
+      <c r="M80" s="5" t="s">
+        <v>720</v>
+      </c>
       <c r="N80" s="14" t="s">
         <v>606</v>
       </c>
@@ -6860,7 +6909,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="81" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:17" ht="27" x14ac:dyDescent="0.3">
       <c r="A81" s="4" t="s">
         <v>101</v>
       </c>
@@ -6887,7 +6936,9 @@
         <v>372</v>
       </c>
       <c r="L81" s="5"/>
-      <c r="M81" s="5"/>
+      <c r="M81" s="5" t="s">
+        <v>719</v>
+      </c>
       <c r="N81" s="14" t="s">
         <v>609</v>
       </c>
@@ -7409,52 +7460,50 @@
         <v>497</v>
       </c>
     </row>
-    <row r="94" spans="1:17" ht="175.5" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A94" s="4" t="s">
-        <v>101</v>
+        <v>721</v>
       </c>
       <c r="B94" s="5" t="s">
-        <v>261</v>
+        <v>722</v>
       </c>
       <c r="C94" s="5" t="s">
-        <v>164</v>
+        <v>723</v>
       </c>
       <c r="D94" s="5" t="s">
-        <v>112</v>
+        <v>724</v>
       </c>
       <c r="E94" s="5" t="s">
-        <v>315</v>
-      </c>
-      <c r="F94" s="5" t="s">
-        <v>393</v>
-      </c>
-      <c r="G94" s="5"/>
-      <c r="H94" s="5"/>
-      <c r="I94" s="5"/>
-      <c r="J94" s="5"/>
-      <c r="K94" s="5" t="s">
-        <v>374</v>
-      </c>
-      <c r="L94" s="5" t="s">
-        <v>717</v>
-      </c>
-      <c r="M94" s="10" t="s">
-        <v>583</v>
-      </c>
-      <c r="N94" s="14" t="s">
-        <v>609</v>
-      </c>
-      <c r="O94" s="14" t="s">
-        <v>606</v>
-      </c>
-      <c r="P94" s="14" t="s">
-        <v>609</v>
-      </c>
-      <c r="Q94" s="5" t="s">
-        <v>484</v>
-      </c>
-    </row>
-    <row r="95" spans="1:17" x14ac:dyDescent="0.3">
+        <v>725</v>
+      </c>
+      <c r="F94" s="6" t="s">
+        <v>358</v>
+      </c>
+      <c r="G94" s="6" t="s">
+        <v>326</v>
+      </c>
+      <c r="H94" s="6" t="s">
+        <v>404</v>
+      </c>
+      <c r="I94" s="6" t="s">
+        <v>358</v>
+      </c>
+      <c r="J94" s="6" t="s">
+        <v>358</v>
+      </c>
+      <c r="K94" s="6" t="s">
+        <v>726</v>
+      </c>
+      <c r="L94" s="2"/>
+      <c r="M94" s="2"/>
+      <c r="N94" s="14"/>
+      <c r="O94" s="14"/>
+      <c r="P94" s="14"/>
+      <c r="Q94" s="6" t="s">
+        <v>727</v>
+      </c>
+    </row>
+    <row r="95" spans="1:17" ht="175.5" x14ac:dyDescent="0.3">
       <c r="A95" s="4" t="s">
         <v>101</v>
       </c>
@@ -7462,7 +7511,7 @@
         <v>261</v>
       </c>
       <c r="C95" s="5" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D95" s="5" t="s">
         <v>112</v>
@@ -7480,19 +7529,23 @@
       <c r="K95" s="5" t="s">
         <v>374</v>
       </c>
-      <c r="L95" s="5"/>
-      <c r="M95" s="5"/>
+      <c r="L95" s="5" t="s">
+        <v>717</v>
+      </c>
+      <c r="M95" s="10" t="s">
+        <v>583</v>
+      </c>
       <c r="N95" s="14" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="O95" s="14" t="s">
         <v>606</v>
       </c>
       <c r="P95" s="14" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="Q95" s="5" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="96" spans="1:17" x14ac:dyDescent="0.3">
@@ -7503,7 +7556,7 @@
         <v>261</v>
       </c>
       <c r="C96" s="5" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D96" s="5" t="s">
         <v>112</v>
@@ -7533,79 +7586,79 @@
         <v>606</v>
       </c>
       <c r="Q96" s="5" t="s">
-        <v>489</v>
-      </c>
-    </row>
-    <row r="97" spans="1:17" ht="40.5" x14ac:dyDescent="0.3">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="97" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A97" s="4" t="s">
-        <v>115</v>
+        <v>101</v>
       </c>
       <c r="B97" s="5" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C97" s="5" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D97" s="5" t="s">
-        <v>4</v>
+        <v>112</v>
       </c>
       <c r="E97" s="5" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="F97" s="5" t="s">
-        <v>6</v>
+        <v>393</v>
       </c>
       <c r="G97" s="5"/>
       <c r="H97" s="5"/>
       <c r="I97" s="5"/>
       <c r="J97" s="5"/>
       <c r="K97" s="5" t="s">
-        <v>372</v>
-      </c>
-      <c r="L97" s="5" t="s">
-        <v>701</v>
-      </c>
+        <v>374</v>
+      </c>
+      <c r="L97" s="5"/>
       <c r="M97" s="5"/>
       <c r="N97" s="14" t="s">
         <v>606</v>
       </c>
       <c r="O97" s="14" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="P97" s="14" t="s">
         <v>606</v>
       </c>
       <c r="Q97" s="5" t="s">
-        <v>501</v>
-      </c>
-    </row>
-    <row r="98" spans="1:17" x14ac:dyDescent="0.3">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="98" spans="1:17" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A98" s="4" t="s">
         <v>115</v>
       </c>
       <c r="B98" s="5" t="s">
-        <v>75</v>
+        <v>262</v>
       </c>
       <c r="C98" s="5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D98" s="5" t="s">
-        <v>112</v>
+        <v>4</v>
       </c>
       <c r="E98" s="5" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F98" s="5" t="s">
-        <v>364</v>
+        <v>6</v>
       </c>
       <c r="G98" s="5"/>
       <c r="H98" s="5"/>
       <c r="I98" s="5"/>
       <c r="J98" s="5"/>
       <c r="K98" s="5" t="s">
-        <v>368</v>
-      </c>
-      <c r="L98" s="5"/>
+        <v>372</v>
+      </c>
+      <c r="L98" s="5" t="s">
+        <v>701</v>
+      </c>
       <c r="M98" s="5"/>
       <c r="N98" s="14" t="s">
         <v>606</v>
@@ -7617,7 +7670,7 @@
         <v>606</v>
       </c>
       <c r="Q98" s="5" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="99" spans="1:17" x14ac:dyDescent="0.3">
@@ -7625,26 +7678,26 @@
         <v>115</v>
       </c>
       <c r="B99" s="5" t="s">
-        <v>263</v>
+        <v>75</v>
       </c>
       <c r="C99" s="5" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D99" s="5" t="s">
-        <v>4</v>
+        <v>112</v>
       </c>
       <c r="E99" s="5" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="F99" s="5" t="s">
-        <v>318</v>
+        <v>364</v>
       </c>
       <c r="G99" s="5"/>
       <c r="H99" s="5"/>
       <c r="I99" s="5"/>
       <c r="J99" s="5"/>
       <c r="K99" s="5" t="s">
-        <v>379</v>
+        <v>368</v>
       </c>
       <c r="L99" s="5"/>
       <c r="M99" s="5"/>
@@ -7652,67 +7705,65 @@
         <v>606</v>
       </c>
       <c r="O99" s="14" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="P99" s="14" t="s">
         <v>606</v>
       </c>
-      <c r="Q99" s="22" t="s">
-        <v>690</v>
-      </c>
-    </row>
-    <row r="100" spans="1:17" ht="94.5" x14ac:dyDescent="0.3">
+      <c r="Q99" s="5" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="100" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A100" s="4" t="s">
         <v>115</v>
       </c>
       <c r="B100" s="5" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C100" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D100" s="5" t="s">
-        <v>112</v>
+        <v>4</v>
       </c>
       <c r="E100" s="5" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F100" s="5" t="s">
-        <v>364</v>
+        <v>318</v>
       </c>
       <c r="G100" s="5"/>
       <c r="H100" s="5"/>
       <c r="I100" s="5"/>
       <c r="J100" s="5"/>
       <c r="K100" s="5" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="L100" s="5"/>
-      <c r="M100" s="10" t="s">
-        <v>587</v>
-      </c>
+      <c r="M100" s="5"/>
       <c r="N100" s="14" t="s">
         <v>606</v>
       </c>
       <c r="O100" s="14" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="P100" s="14" t="s">
-        <v>609</v>
-      </c>
-      <c r="Q100" s="5" t="s">
-        <v>504</v>
-      </c>
-    </row>
-    <row r="101" spans="1:17" x14ac:dyDescent="0.3">
+        <v>606</v>
+      </c>
+      <c r="Q100" s="22" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="101" spans="1:17" ht="94.5" x14ac:dyDescent="0.3">
       <c r="A101" s="4" t="s">
         <v>115</v>
       </c>
       <c r="B101" s="5" t="s">
-        <v>76</v>
+        <v>264</v>
       </c>
       <c r="C101" s="5" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D101" s="5" t="s">
         <v>112</v>
@@ -7731,21 +7782,23 @@
         <v>368</v>
       </c>
       <c r="L101" s="5"/>
-      <c r="M101" s="5"/>
+      <c r="M101" s="10" t="s">
+        <v>587</v>
+      </c>
       <c r="N101" s="14" t="s">
         <v>606</v>
       </c>
       <c r="O101" s="14" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="P101" s="14" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="Q101" s="5" t="s">
-        <v>693</v>
-      </c>
-    </row>
-    <row r="102" spans="1:17" ht="95.25" x14ac:dyDescent="0.3">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="102" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A102" s="4" t="s">
         <v>115</v>
       </c>
@@ -7753,7 +7806,7 @@
         <v>76</v>
       </c>
       <c r="C102" s="5" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D102" s="5" t="s">
         <v>112</v>
@@ -7761,150 +7814,148 @@
       <c r="E102" s="5" t="s">
         <v>315</v>
       </c>
-      <c r="F102" s="5"/>
-      <c r="G102" s="6" t="s">
-        <v>322</v>
-      </c>
-      <c r="H102" s="6"/>
-      <c r="I102" s="6" t="s">
-        <v>358</v>
-      </c>
-      <c r="J102" s="6" t="s">
-        <v>405</v>
-      </c>
-      <c r="K102" s="6" t="s">
-        <v>367</v>
-      </c>
-      <c r="L102" s="2"/>
-      <c r="M102" s="12" t="s">
-        <v>588</v>
-      </c>
+      <c r="F102" s="5" t="s">
+        <v>364</v>
+      </c>
+      <c r="G102" s="5"/>
+      <c r="H102" s="5"/>
+      <c r="I102" s="5"/>
+      <c r="J102" s="5"/>
+      <c r="K102" s="5" t="s">
+        <v>368</v>
+      </c>
+      <c r="L102" s="5"/>
+      <c r="M102" s="5"/>
       <c r="N102" s="14" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="O102" s="14" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="P102" s="14" t="s">
-        <v>609</v>
-      </c>
-      <c r="Q102" s="6" t="s">
-        <v>509</v>
-      </c>
-    </row>
-    <row r="103" spans="1:17" ht="27" x14ac:dyDescent="0.3">
+        <v>606</v>
+      </c>
+      <c r="Q102" s="5" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="103" spans="1:17" ht="95.25" x14ac:dyDescent="0.3">
       <c r="A103" s="4" t="s">
         <v>115</v>
       </c>
       <c r="B103" s="5" t="s">
-        <v>265</v>
+        <v>76</v>
       </c>
       <c r="C103" s="5" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D103" s="5" t="s">
-        <v>4</v>
+        <v>112</v>
       </c>
       <c r="E103" s="5" t="s">
-        <v>314</v>
-      </c>
-      <c r="F103" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="G103" s="5"/>
-      <c r="H103" s="5"/>
-      <c r="I103" s="5"/>
-      <c r="J103" s="5"/>
-      <c r="K103" s="5" t="s">
-        <v>372</v>
-      </c>
-      <c r="L103" s="5" t="s">
-        <v>702</v>
-      </c>
-      <c r="M103" s="5"/>
+        <v>315</v>
+      </c>
+      <c r="F103" s="5"/>
+      <c r="G103" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="H103" s="6"/>
+      <c r="I103" s="6" t="s">
+        <v>358</v>
+      </c>
+      <c r="J103" s="6" t="s">
+        <v>405</v>
+      </c>
+      <c r="K103" s="6" t="s">
+        <v>367</v>
+      </c>
+      <c r="L103" s="2"/>
+      <c r="M103" s="12" t="s">
+        <v>588</v>
+      </c>
       <c r="N103" s="14" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="O103" s="14" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="P103" s="14" t="s">
-        <v>606</v>
-      </c>
-      <c r="Q103" s="5" t="s">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="104" spans="1:17" x14ac:dyDescent="0.3">
+        <v>609</v>
+      </c>
+      <c r="Q103" s="6" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="104" spans="1:17" ht="27" x14ac:dyDescent="0.3">
       <c r="A104" s="4" t="s">
         <v>115</v>
       </c>
       <c r="B104" s="5" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C104" s="5" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D104" s="5" t="s">
-        <v>112</v>
+        <v>4</v>
       </c>
       <c r="E104" s="5" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F104" s="5" t="s">
-        <v>364</v>
+        <v>6</v>
       </c>
       <c r="G104" s="5"/>
       <c r="H104" s="5"/>
       <c r="I104" s="5"/>
       <c r="J104" s="5"/>
       <c r="K104" s="5" t="s">
-        <v>368</v>
-      </c>
-      <c r="L104" s="5"/>
+        <v>372</v>
+      </c>
+      <c r="L104" s="5" t="s">
+        <v>702</v>
+      </c>
       <c r="M104" s="5"/>
       <c r="N104" s="14" t="s">
         <v>606</v>
       </c>
       <c r="O104" s="14" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="P104" s="14" t="s">
         <v>606</v>
       </c>
       <c r="Q104" s="5" t="s">
-        <v>510</v>
-      </c>
-    </row>
-    <row r="105" spans="1:17" ht="27" x14ac:dyDescent="0.3">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="105" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A105" s="4" t="s">
         <v>115</v>
       </c>
       <c r="B105" s="5" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C105" s="5" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D105" s="5" t="s">
-        <v>4</v>
+        <v>112</v>
       </c>
       <c r="E105" s="5" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="F105" s="5" t="s">
-        <v>6</v>
+        <v>364</v>
       </c>
       <c r="G105" s="5"/>
       <c r="H105" s="5"/>
       <c r="I105" s="5"/>
       <c r="J105" s="5"/>
       <c r="K105" s="5" t="s">
-        <v>372</v>
-      </c>
-      <c r="L105" s="5" t="s">
-        <v>703</v>
-      </c>
+        <v>368</v>
+      </c>
+      <c r="L105" s="5"/>
       <c r="M105" s="5"/>
       <c r="N105" s="14" t="s">
         <v>606</v>
@@ -7916,92 +7967,84 @@
         <v>606</v>
       </c>
       <c r="Q105" s="5" t="s">
-        <v>507</v>
-      </c>
-    </row>
-    <row r="106" spans="1:17" ht="54" x14ac:dyDescent="0.3">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="106" spans="1:17" ht="27" x14ac:dyDescent="0.3">
       <c r="A106" s="4" t="s">
         <v>115</v>
       </c>
       <c r="B106" s="5" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C106" s="5" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D106" s="5" t="s">
-        <v>112</v>
+        <v>4</v>
       </c>
       <c r="E106" s="5" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F106" s="5" t="s">
-        <v>364</v>
+        <v>6</v>
       </c>
       <c r="G106" s="5"/>
       <c r="H106" s="5"/>
       <c r="I106" s="5"/>
       <c r="J106" s="5"/>
       <c r="K106" s="5" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="L106" s="5" t="s">
-        <v>714</v>
-      </c>
-      <c r="M106" s="10" t="s">
-        <v>713</v>
-      </c>
+        <v>703</v>
+      </c>
+      <c r="M106" s="5"/>
       <c r="N106" s="14" t="s">
         <v>606</v>
       </c>
       <c r="O106" s="14" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="P106" s="14" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="Q106" s="5" t="s">
-        <v>505</v>
-      </c>
-    </row>
-    <row r="107" spans="1:17" ht="81" x14ac:dyDescent="0.3">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="107" spans="1:17" ht="54" x14ac:dyDescent="0.3">
       <c r="A107" s="4" t="s">
         <v>115</v>
       </c>
       <c r="B107" s="5" t="s">
-        <v>394</v>
+        <v>268</v>
       </c>
       <c r="C107" s="5" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D107" s="5" t="s">
-        <v>4</v>
+        <v>112</v>
       </c>
       <c r="E107" s="5" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="F107" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="G107" s="5" t="s">
-        <v>406</v>
-      </c>
-      <c r="H107" s="5" t="s">
-        <v>323</v>
-      </c>
-      <c r="I107" s="5" t="s">
-        <v>716</v>
-      </c>
-      <c r="J107" s="5" t="s">
-        <v>407</v>
-      </c>
+        <v>364</v>
+      </c>
+      <c r="G107" s="5"/>
+      <c r="H107" s="5"/>
+      <c r="I107" s="5"/>
+      <c r="J107" s="5"/>
       <c r="K107" s="5" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="L107" s="5" t="s">
-        <v>704</v>
-      </c>
-      <c r="M107" s="5"/>
+        <v>714</v>
+      </c>
+      <c r="M107" s="10" t="s">
+        <v>713</v>
+      </c>
       <c r="N107" s="14" t="s">
         <v>606</v>
       </c>
@@ -8009,21 +8052,21 @@
         <v>606</v>
       </c>
       <c r="P107" s="14" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="Q107" s="5" t="s">
-        <v>512</v>
-      </c>
-    </row>
-    <row r="108" spans="1:17" x14ac:dyDescent="0.3">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="108" spans="1:17" ht="81" x14ac:dyDescent="0.3">
       <c r="A108" s="4" t="s">
         <v>115</v>
       </c>
       <c r="B108" s="5" t="s">
-        <v>269</v>
+        <v>394</v>
       </c>
       <c r="C108" s="5" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D108" s="5" t="s">
         <v>4</v>
@@ -8034,26 +8077,36 @@
       <c r="F108" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="G108" s="5"/>
-      <c r="H108" s="5"/>
-      <c r="I108" s="5"/>
-      <c r="J108" s="5"/>
+      <c r="G108" s="5" t="s">
+        <v>406</v>
+      </c>
+      <c r="H108" s="5" t="s">
+        <v>323</v>
+      </c>
+      <c r="I108" s="5" t="s">
+        <v>716</v>
+      </c>
+      <c r="J108" s="5" t="s">
+        <v>407</v>
+      </c>
       <c r="K108" s="5" t="s">
         <v>372</v>
       </c>
-      <c r="L108" s="5"/>
+      <c r="L108" s="5" t="s">
+        <v>704</v>
+      </c>
       <c r="M108" s="5"/>
       <c r="N108" s="14" t="s">
         <v>606</v>
       </c>
       <c r="O108" s="14" t="s">
-        <v>610</v>
+        <v>606</v>
       </c>
       <c r="P108" s="14" t="s">
         <v>606</v>
       </c>
       <c r="Q108" s="5" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="109" spans="1:17" x14ac:dyDescent="0.3">
@@ -8061,42 +8114,40 @@
         <v>115</v>
       </c>
       <c r="B109" s="5" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C109" s="5" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D109" s="5" t="s">
-        <v>112</v>
+        <v>4</v>
       </c>
       <c r="E109" s="5" t="s">
-        <v>315</v>
-      </c>
-      <c r="F109" s="5"/>
-      <c r="G109" s="6" t="s">
-        <v>322</v>
-      </c>
-      <c r="H109" s="6"/>
-      <c r="I109" s="6" t="s">
-        <v>358</v>
-      </c>
-      <c r="J109" s="6" t="s">
-        <v>405</v>
-      </c>
-      <c r="K109" s="6"/>
-      <c r="L109" s="2"/>
-      <c r="M109" s="2"/>
+        <v>314</v>
+      </c>
+      <c r="F109" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="G109" s="5"/>
+      <c r="H109" s="5"/>
+      <c r="I109" s="5"/>
+      <c r="J109" s="5"/>
+      <c r="K109" s="5" t="s">
+        <v>372</v>
+      </c>
+      <c r="L109" s="5"/>
+      <c r="M109" s="5"/>
       <c r="N109" s="14" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="O109" s="14" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="P109" s="14" t="s">
-        <v>609</v>
-      </c>
-      <c r="Q109" s="6" t="s">
-        <v>506</v>
+        <v>606</v>
+      </c>
+      <c r="Q109" s="5" t="s">
+        <v>511</v>
       </c>
     </row>
     <row r="110" spans="1:17" x14ac:dyDescent="0.3">
@@ -8104,10 +8155,10 @@
         <v>115</v>
       </c>
       <c r="B110" s="5" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C110" s="5" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D110" s="5" t="s">
         <v>112</v>
@@ -8115,70 +8166,72 @@
       <c r="E110" s="5" t="s">
         <v>315</v>
       </c>
-      <c r="F110" s="5" t="s">
-        <v>364</v>
-      </c>
-      <c r="G110" s="5"/>
-      <c r="H110" s="5"/>
-      <c r="I110" s="5"/>
-      <c r="J110" s="5"/>
-      <c r="K110" s="5" t="s">
-        <v>368</v>
-      </c>
-      <c r="L110" s="5"/>
-      <c r="M110" s="5"/>
+      <c r="F110" s="5"/>
+      <c r="G110" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="H110" s="6"/>
+      <c r="I110" s="6" t="s">
+        <v>358</v>
+      </c>
+      <c r="J110" s="6" t="s">
+        <v>405</v>
+      </c>
+      <c r="K110" s="6"/>
+      <c r="L110" s="2"/>
+      <c r="M110" s="2"/>
       <c r="N110" s="14" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="O110" s="14" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="P110" s="14" t="s">
         <v>609</v>
       </c>
-      <c r="Q110" s="5" t="s">
-        <v>508</v>
+      <c r="Q110" s="6" t="s">
+        <v>506</v>
       </c>
     </row>
     <row r="111" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A111" s="4" t="s">
-        <v>102</v>
+        <v>115</v>
       </c>
       <c r="B111" s="5" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C111" s="5" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D111" s="5" t="s">
-        <v>4</v>
+        <v>112</v>
       </c>
       <c r="E111" s="5" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="F111" s="5" t="s">
-        <v>6</v>
+        <v>364</v>
       </c>
       <c r="G111" s="5"/>
       <c r="H111" s="5"/>
       <c r="I111" s="5"/>
       <c r="J111" s="5"/>
       <c r="K111" s="5" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="L111" s="5"/>
       <c r="M111" s="5"/>
       <c r="N111" s="14" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="O111" s="14" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="P111" s="14" t="s">
-        <v>606</v>
-      </c>
-      <c r="Q111" s="22" t="s">
-        <v>694</v>
+        <v>609</v>
+      </c>
+      <c r="Q111" s="5" t="s">
+        <v>508</v>
       </c>
     </row>
     <row r="112" spans="1:17" x14ac:dyDescent="0.3">
@@ -8186,94 +8239,92 @@
         <v>102</v>
       </c>
       <c r="B112" s="5" t="s">
-        <v>80</v>
+        <v>272</v>
       </c>
       <c r="C112" s="5" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D112" s="5" t="s">
-        <v>112</v>
+        <v>4</v>
       </c>
       <c r="E112" s="5" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F112" s="5" t="s">
-        <v>364</v>
+        <v>6</v>
       </c>
       <c r="G112" s="5"/>
       <c r="H112" s="5"/>
       <c r="I112" s="5"/>
       <c r="J112" s="5"/>
       <c r="K112" s="5" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="L112" s="5"/>
       <c r="M112" s="5"/>
       <c r="N112" s="14" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="O112" s="14" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="P112" s="14" t="s">
         <v>606</v>
       </c>
-      <c r="Q112" s="5" t="s">
-        <v>516</v>
-      </c>
-    </row>
-    <row r="113" spans="1:17" ht="27" x14ac:dyDescent="0.3">
+      <c r="Q112" s="22" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="113" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A113" s="4" t="s">
         <v>102</v>
       </c>
       <c r="B113" s="5" t="s">
-        <v>273</v>
+        <v>80</v>
       </c>
       <c r="C113" s="5" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D113" s="5" t="s">
-        <v>4</v>
+        <v>112</v>
       </c>
       <c r="E113" s="5" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="F113" s="5" t="s">
-        <v>321</v>
+        <v>364</v>
       </c>
       <c r="G113" s="5"/>
       <c r="H113" s="5"/>
       <c r="I113" s="5"/>
       <c r="J113" s="5"/>
       <c r="K113" s="5" t="s">
-        <v>381</v>
-      </c>
-      <c r="L113" s="5" t="s">
-        <v>688</v>
-      </c>
+        <v>368</v>
+      </c>
+      <c r="L113" s="5"/>
       <c r="M113" s="5"/>
       <c r="N113" s="14" t="s">
         <v>606</v>
       </c>
       <c r="O113" s="14" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="P113" s="14" t="s">
         <v>606</v>
       </c>
       <c r="Q113" s="5" t="s">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="114" spans="1:17" ht="40.5" x14ac:dyDescent="0.3">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="114" spans="1:17" ht="27" x14ac:dyDescent="0.3">
       <c r="A114" s="4" t="s">
         <v>102</v>
       </c>
       <c r="B114" s="5" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C114" s="5" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D114" s="5" t="s">
         <v>4</v>
@@ -8282,41 +8333,41 @@
         <v>314</v>
       </c>
       <c r="F114" s="5" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="G114" s="5"/>
       <c r="H114" s="5"/>
       <c r="I114" s="5"/>
       <c r="J114" s="5"/>
       <c r="K114" s="5" t="s">
-        <v>370</v>
+        <v>381</v>
       </c>
       <c r="L114" s="5" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="M114" s="5"/>
       <c r="N114" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="O114" s="14" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="P114" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="Q114" s="5" t="s">
-        <v>518</v>
-      </c>
-    </row>
-    <row r="115" spans="1:17" x14ac:dyDescent="0.3">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="115" spans="1:17" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A115" s="4" t="s">
         <v>102</v>
       </c>
       <c r="B115" s="5" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C115" s="5" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D115" s="5" t="s">
         <v>4</v>
@@ -8325,31 +8376,33 @@
         <v>314</v>
       </c>
       <c r="F115" s="5" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="G115" s="5"/>
       <c r="H115" s="5"/>
       <c r="I115" s="5"/>
       <c r="J115" s="5"/>
       <c r="K115" s="5" t="s">
-        <v>381</v>
-      </c>
-      <c r="L115" s="5"/>
+        <v>370</v>
+      </c>
+      <c r="L115" s="5" t="s">
+        <v>686</v>
+      </c>
       <c r="M115" s="5"/>
       <c r="N115" s="14" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="O115" s="14" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="P115" s="14" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="Q115" s="5" t="s">
-        <v>517</v>
-      </c>
-    </row>
-    <row r="116" spans="1:17" ht="94.5" x14ac:dyDescent="0.3">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="116" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A116" s="4" t="s">
         <v>102</v>
       </c>
@@ -8357,7 +8410,7 @@
         <v>275</v>
       </c>
       <c r="C116" s="5" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D116" s="5" t="s">
         <v>4</v>
@@ -8376,9 +8429,7 @@
         <v>381</v>
       </c>
       <c r="L116" s="5"/>
-      <c r="M116" s="10" t="s">
-        <v>592</v>
-      </c>
+      <c r="M116" s="5"/>
       <c r="N116" s="14" t="s">
         <v>606</v>
       </c>
@@ -8389,18 +8440,18 @@
         <v>606</v>
       </c>
       <c r="Q116" s="5" t="s">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="117" spans="1:17" x14ac:dyDescent="0.3">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="117" spans="1:17" ht="94.5" x14ac:dyDescent="0.3">
       <c r="A117" s="4" t="s">
         <v>102</v>
       </c>
       <c r="B117" s="5" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C117" s="5" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D117" s="5" t="s">
         <v>4</v>
@@ -8409,82 +8460,82 @@
         <v>314</v>
       </c>
       <c r="F117" s="5" t="s">
-        <v>6</v>
+        <v>321</v>
       </c>
       <c r="G117" s="5"/>
       <c r="H117" s="5"/>
       <c r="I117" s="5"/>
       <c r="J117" s="5"/>
       <c r="K117" s="5" t="s">
-        <v>372</v>
+        <v>381</v>
       </c>
       <c r="L117" s="5"/>
-      <c r="M117" s="5"/>
+      <c r="M117" s="10" t="s">
+        <v>592</v>
+      </c>
       <c r="N117" s="14" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="O117" s="14" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="P117" s="14" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="Q117" s="5" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="118" spans="1:17" ht="94.5" x14ac:dyDescent="0.3">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="118" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A118" s="4" t="s">
         <v>102</v>
       </c>
       <c r="B118" s="5" t="s">
-        <v>83</v>
+        <v>276</v>
       </c>
       <c r="C118" s="5" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D118" s="5" t="s">
-        <v>112</v>
+        <v>4</v>
       </c>
       <c r="E118" s="5" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F118" s="5" t="s">
-        <v>364</v>
+        <v>6</v>
       </c>
       <c r="G118" s="5"/>
       <c r="H118" s="5"/>
       <c r="I118" s="5"/>
       <c r="J118" s="5"/>
       <c r="K118" s="5" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="L118" s="5"/>
-      <c r="M118" s="10" t="s">
-        <v>590</v>
-      </c>
+      <c r="M118" s="5"/>
       <c r="N118" s="14" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="O118" s="14" t="s">
-        <v>607</v>
-      </c>
-      <c r="P118" s="13" t="s">
+        <v>609</v>
+      </c>
+      <c r="P118" s="14" t="s">
         <v>609</v>
       </c>
       <c r="Q118" s="5" t="s">
-        <v>515</v>
-      </c>
-    </row>
-    <row r="119" spans="1:17" x14ac:dyDescent="0.3">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="119" spans="1:17" ht="94.5" x14ac:dyDescent="0.3">
       <c r="A119" s="4" t="s">
-        <v>116</v>
+        <v>102</v>
       </c>
       <c r="B119" s="5" t="s">
-        <v>277</v>
+        <v>83</v>
       </c>
       <c r="C119" s="5" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D119" s="5" t="s">
         <v>112</v>
@@ -8503,18 +8554,20 @@
         <v>368</v>
       </c>
       <c r="L119" s="5"/>
-      <c r="M119" s="5"/>
-      <c r="N119" s="13" t="s">
-        <v>609</v>
-      </c>
-      <c r="O119" s="13" t="s">
-        <v>609</v>
-      </c>
-      <c r="P119" s="14" t="s">
-        <v>607</v>
+      <c r="M119" s="10" t="s">
+        <v>590</v>
+      </c>
+      <c r="N119" s="14" t="s">
+        <v>607</v>
+      </c>
+      <c r="O119" s="14" t="s">
+        <v>607</v>
+      </c>
+      <c r="P119" s="13" t="s">
+        <v>609</v>
       </c>
       <c r="Q119" s="5" t="s">
-        <v>531</v>
+        <v>515</v>
       </c>
     </row>
     <row r="120" spans="1:17" x14ac:dyDescent="0.3">
@@ -8522,10 +8575,10 @@
         <v>116</v>
       </c>
       <c r="B120" s="5" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C120" s="5" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D120" s="5" t="s">
         <v>112</v>
@@ -8555,7 +8608,7 @@
         <v>607</v>
       </c>
       <c r="Q120" s="5" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
     </row>
     <row r="121" spans="1:17" x14ac:dyDescent="0.3">
@@ -8563,51 +8616,51 @@
         <v>116</v>
       </c>
       <c r="B121" s="5" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C121" s="5" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D121" s="5" t="s">
-        <v>4</v>
+        <v>112</v>
       </c>
       <c r="E121" s="5" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="F121" s="5" t="s">
-        <v>6</v>
+        <v>364</v>
       </c>
       <c r="G121" s="5"/>
       <c r="H121" s="5"/>
       <c r="I121" s="5"/>
       <c r="J121" s="5"/>
       <c r="K121" s="5" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="L121" s="5"/>
       <c r="M121" s="5"/>
-      <c r="N121" s="14" t="s">
-        <v>606</v>
-      </c>
-      <c r="O121" s="14" t="s">
+      <c r="N121" s="13" t="s">
+        <v>609</v>
+      </c>
+      <c r="O121" s="13" t="s">
         <v>609</v>
       </c>
       <c r="P121" s="14" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="Q121" s="5" t="s">
-        <v>520</v>
-      </c>
-    </row>
-    <row r="122" spans="1:17" ht="135" x14ac:dyDescent="0.3">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="122" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A122" s="4" t="s">
         <v>116</v>
       </c>
       <c r="B122" s="5" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C122" s="5" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D122" s="5" t="s">
         <v>4</v>
@@ -8616,19 +8669,17 @@
         <v>314</v>
       </c>
       <c r="F122" s="5" t="s">
-        <v>317</v>
+        <v>6</v>
       </c>
       <c r="G122" s="5"/>
       <c r="H122" s="5"/>
       <c r="I122" s="5"/>
       <c r="J122" s="5"/>
       <c r="K122" s="5" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="L122" s="5"/>
-      <c r="M122" s="10" t="s">
-        <v>594</v>
-      </c>
+      <c r="M122" s="5"/>
       <c r="N122" s="14" t="s">
         <v>606</v>
       </c>
@@ -8636,21 +8687,21 @@
         <v>609</v>
       </c>
       <c r="P122" s="14" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="Q122" s="5" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="123" spans="1:17" x14ac:dyDescent="0.3">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="123" spans="1:17" ht="135" x14ac:dyDescent="0.3">
       <c r="A123" s="4" t="s">
         <v>116</v>
       </c>
       <c r="B123" s="5" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C123" s="5" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D123" s="5" t="s">
         <v>4</v>
@@ -8659,17 +8710,19 @@
         <v>314</v>
       </c>
       <c r="F123" s="5" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="G123" s="5"/>
       <c r="H123" s="5"/>
       <c r="I123" s="5"/>
       <c r="J123" s="5"/>
       <c r="K123" s="5" t="s">
-        <v>376</v>
+        <v>370</v>
       </c>
       <c r="L123" s="5"/>
-      <c r="M123" s="5"/>
+      <c r="M123" s="10" t="s">
+        <v>594</v>
+      </c>
       <c r="N123" s="14" t="s">
         <v>606</v>
       </c>
@@ -8677,10 +8730,10 @@
         <v>609</v>
       </c>
       <c r="P123" s="14" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="Q123" s="5" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
     </row>
     <row r="124" spans="1:17" x14ac:dyDescent="0.3">
@@ -8688,10 +8741,10 @@
         <v>116</v>
       </c>
       <c r="B124" s="5" t="s">
-        <v>84</v>
+        <v>281</v>
       </c>
       <c r="C124" s="5" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D124" s="5" t="s">
         <v>4</v>
@@ -8700,14 +8753,14 @@
         <v>314</v>
       </c>
       <c r="F124" s="5" t="s">
-        <v>6</v>
+        <v>318</v>
       </c>
       <c r="G124" s="5"/>
       <c r="H124" s="5"/>
       <c r="I124" s="5"/>
       <c r="J124" s="5"/>
       <c r="K124" s="5" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="L124" s="5"/>
       <c r="M124" s="5"/>
@@ -8721,7 +8774,7 @@
         <v>606</v>
       </c>
       <c r="Q124" s="5" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
     </row>
     <row r="125" spans="1:17" x14ac:dyDescent="0.3">
@@ -8729,10 +8782,10 @@
         <v>116</v>
       </c>
       <c r="B125" s="5" t="s">
-        <v>282</v>
+        <v>84</v>
       </c>
       <c r="C125" s="5" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D125" s="5" t="s">
         <v>4</v>
@@ -8748,7 +8801,7 @@
       <c r="I125" s="5"/>
       <c r="J125" s="5"/>
       <c r="K125" s="5" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="L125" s="5"/>
       <c r="M125" s="5"/>
@@ -8762,7 +8815,7 @@
         <v>606</v>
       </c>
       <c r="Q125" s="5" t="s">
-        <v>524</v>
+        <v>527</v>
       </c>
     </row>
     <row r="126" spans="1:17" x14ac:dyDescent="0.3">
@@ -8770,94 +8823,92 @@
         <v>116</v>
       </c>
       <c r="B126" s="5" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C126" s="5" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D126" s="5" t="s">
-        <v>112</v>
+        <v>4</v>
       </c>
       <c r="E126" s="5" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F126" s="5" t="s">
-        <v>364</v>
+        <v>6</v>
       </c>
       <c r="G126" s="5"/>
       <c r="H126" s="5"/>
       <c r="I126" s="5"/>
       <c r="J126" s="5"/>
       <c r="K126" s="5" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="L126" s="5"/>
       <c r="M126" s="5"/>
       <c r="N126" s="14" t="s">
-        <v>607</v>
-      </c>
-      <c r="O126" s="13" t="s">
-        <v>609</v>
-      </c>
-      <c r="P126" s="13" t="s">
-        <v>609</v>
+        <v>606</v>
+      </c>
+      <c r="O126" s="14" t="s">
+        <v>609</v>
+      </c>
+      <c r="P126" s="14" t="s">
+        <v>606</v>
       </c>
       <c r="Q126" s="5" t="s">
-        <v>521</v>
-      </c>
-    </row>
-    <row r="127" spans="1:17" ht="40.5" x14ac:dyDescent="0.3">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="127" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A127" s="4" t="s">
         <v>116</v>
       </c>
       <c r="B127" s="5" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C127" s="5" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D127" s="5" t="s">
-        <v>4</v>
+        <v>112</v>
       </c>
       <c r="E127" s="5" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="F127" s="5" t="s">
-        <v>6</v>
+        <v>364</v>
       </c>
       <c r="G127" s="5"/>
       <c r="H127" s="5"/>
       <c r="I127" s="5"/>
       <c r="J127" s="5"/>
       <c r="K127" s="5" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="L127" s="5"/>
-      <c r="M127" s="10" t="s">
-        <v>593</v>
-      </c>
+      <c r="M127" s="5"/>
       <c r="N127" s="14" t="s">
-        <v>606</v>
-      </c>
-      <c r="O127" s="14" t="s">
-        <v>609</v>
-      </c>
-      <c r="P127" s="14" t="s">
+        <v>607</v>
+      </c>
+      <c r="O127" s="13" t="s">
+        <v>609</v>
+      </c>
+      <c r="P127" s="13" t="s">
         <v>609</v>
       </c>
       <c r="Q127" s="5" t="s">
-        <v>525</v>
-      </c>
-    </row>
-    <row r="128" spans="1:17" ht="54" x14ac:dyDescent="0.3">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="128" spans="1:17" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A128" s="4" t="s">
         <v>116</v>
       </c>
       <c r="B128" s="5" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C128" s="5" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D128" s="5" t="s">
         <v>4</v>
@@ -8873,34 +8924,34 @@
       <c r="I128" s="5"/>
       <c r="J128" s="5"/>
       <c r="K128" s="5" t="s">
-        <v>372</v>
-      </c>
-      <c r="L128" s="5" t="s">
-        <v>705</v>
-      </c>
-      <c r="M128" s="5"/>
+        <v>370</v>
+      </c>
+      <c r="L128" s="5"/>
+      <c r="M128" s="10" t="s">
+        <v>593</v>
+      </c>
       <c r="N128" s="14" t="s">
         <v>606</v>
       </c>
       <c r="O128" s="14" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="P128" s="14" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="Q128" s="5" t="s">
-        <v>528</v>
-      </c>
-    </row>
-    <row r="129" spans="1:17" x14ac:dyDescent="0.3">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="129" spans="1:17" ht="54" x14ac:dyDescent="0.3">
       <c r="A129" s="4" t="s">
         <v>116</v>
       </c>
       <c r="B129" s="5" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C129" s="5" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D129" s="5" t="s">
         <v>4</v>
@@ -8918,19 +8969,21 @@
       <c r="K129" s="5" t="s">
         <v>372</v>
       </c>
-      <c r="L129" s="5"/>
+      <c r="L129" s="5" t="s">
+        <v>705</v>
+      </c>
       <c r="M129" s="5"/>
       <c r="N129" s="14" t="s">
         <v>606</v>
       </c>
       <c r="O129" s="14" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="P129" s="14" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="Q129" s="5" t="s">
-        <v>522</v>
+        <v>528</v>
       </c>
     </row>
     <row r="130" spans="1:17" x14ac:dyDescent="0.3">
@@ -8941,7 +8994,7 @@
         <v>286</v>
       </c>
       <c r="C130" s="5" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D130" s="5" t="s">
         <v>4</v>
@@ -8965,54 +9018,54 @@
         <v>606</v>
       </c>
       <c r="O130" s="14" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="P130" s="14" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="Q130" s="5" t="s">
-        <v>529</v>
+        <v>522</v>
       </c>
     </row>
     <row r="131" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A131" s="4" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B131" s="5" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C131" s="5" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D131" s="5" t="s">
-        <v>112</v>
+        <v>4</v>
       </c>
       <c r="E131" s="5" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F131" s="5" t="s">
-        <v>364</v>
+        <v>6</v>
       </c>
       <c r="G131" s="5"/>
       <c r="H131" s="5"/>
       <c r="I131" s="5"/>
       <c r="J131" s="5"/>
       <c r="K131" s="5" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="L131" s="5"/>
       <c r="M131" s="5"/>
       <c r="N131" s="14" t="s">
-        <v>607</v>
-      </c>
-      <c r="O131" s="13" t="s">
-        <v>609</v>
-      </c>
-      <c r="P131" s="13" t="s">
-        <v>609</v>
+        <v>606</v>
+      </c>
+      <c r="O131" s="14" t="s">
+        <v>606</v>
+      </c>
+      <c r="P131" s="14" t="s">
+        <v>606</v>
       </c>
       <c r="Q131" s="5" t="s">
-        <v>549</v>
+        <v>529</v>
       </c>
     </row>
     <row r="132" spans="1:17" x14ac:dyDescent="0.3">
@@ -9020,40 +9073,40 @@
         <v>117</v>
       </c>
       <c r="B132" s="5" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C132" s="5" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D132" s="5" t="s">
-        <v>4</v>
+        <v>112</v>
       </c>
       <c r="E132" s="5" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="F132" s="5" t="s">
-        <v>6</v>
+        <v>364</v>
       </c>
       <c r="G132" s="5"/>
       <c r="H132" s="5"/>
       <c r="I132" s="5"/>
       <c r="J132" s="5"/>
       <c r="K132" s="5" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="L132" s="5"/>
       <c r="M132" s="5"/>
       <c r="N132" s="14" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="O132" s="13" t="s">
         <v>609</v>
       </c>
-      <c r="P132" s="14" t="s">
+      <c r="P132" s="13" t="s">
         <v>609</v>
       </c>
       <c r="Q132" s="5" t="s">
-        <v>538</v>
+        <v>549</v>
       </c>
     </row>
     <row r="133" spans="1:17" x14ac:dyDescent="0.3">
@@ -9061,40 +9114,40 @@
         <v>117</v>
       </c>
       <c r="B133" s="5" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C133" s="5" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D133" s="5" t="s">
-        <v>112</v>
+        <v>4</v>
       </c>
       <c r="E133" s="5" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F133" s="5" t="s">
-        <v>364</v>
+        <v>6</v>
       </c>
       <c r="G133" s="5"/>
       <c r="H133" s="5"/>
       <c r="I133" s="5"/>
       <c r="J133" s="5"/>
       <c r="K133" s="5" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="L133" s="5"/>
       <c r="M133" s="5"/>
       <c r="N133" s="14" t="s">
-        <v>607</v>
-      </c>
-      <c r="O133" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
+      </c>
+      <c r="O133" s="13" t="s">
+        <v>609</v>
       </c>
       <c r="P133" s="14" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="Q133" s="5" t="s">
-        <v>545</v>
+        <v>538</v>
       </c>
     </row>
     <row r="134" spans="1:17" x14ac:dyDescent="0.3">
@@ -9102,40 +9155,40 @@
         <v>117</v>
       </c>
       <c r="B134" s="5" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C134" s="5" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D134" s="5" t="s">
-        <v>4</v>
+        <v>112</v>
       </c>
       <c r="E134" s="5" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="F134" s="5" t="s">
-        <v>6</v>
+        <v>364</v>
       </c>
       <c r="G134" s="5"/>
       <c r="H134" s="5"/>
       <c r="I134" s="5"/>
       <c r="J134" s="5"/>
       <c r="K134" s="5" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="L134" s="5"/>
       <c r="M134" s="5"/>
       <c r="N134" s="14" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="O134" s="14" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="P134" s="14" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="Q134" s="5" t="s">
-        <v>533</v>
+        <v>545</v>
       </c>
     </row>
     <row r="135" spans="1:17" x14ac:dyDescent="0.3">
@@ -9143,40 +9196,40 @@
         <v>117</v>
       </c>
       <c r="B135" s="5" t="s">
-        <v>88</v>
+        <v>290</v>
       </c>
       <c r="C135" s="5" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D135" s="5" t="s">
-        <v>112</v>
+        <v>4</v>
       </c>
       <c r="E135" s="5" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F135" s="5" t="s">
-        <v>364</v>
+        <v>6</v>
       </c>
       <c r="G135" s="5"/>
       <c r="H135" s="5"/>
       <c r="I135" s="5"/>
       <c r="J135" s="5"/>
       <c r="K135" s="5" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="L135" s="5"/>
       <c r="M135" s="5"/>
       <c r="N135" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="O135" s="14" t="s">
-        <v>607</v>
-      </c>
-      <c r="P135" s="13" t="s">
+        <v>606</v>
+      </c>
+      <c r="P135" s="14" t="s">
         <v>609</v>
       </c>
       <c r="Q135" s="5" t="s">
-        <v>542</v>
+        <v>533</v>
       </c>
     </row>
     <row r="136" spans="1:17" x14ac:dyDescent="0.3">
@@ -9184,40 +9237,40 @@
         <v>117</v>
       </c>
       <c r="B136" s="5" t="s">
-        <v>291</v>
+        <v>88</v>
       </c>
       <c r="C136" s="5" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D136" s="5" t="s">
-        <v>4</v>
+        <v>112</v>
       </c>
       <c r="E136" s="5" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="F136" s="5" t="s">
-        <v>6</v>
+        <v>364</v>
       </c>
       <c r="G136" s="5"/>
       <c r="H136" s="5"/>
       <c r="I136" s="5"/>
       <c r="J136" s="5"/>
       <c r="K136" s="5" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="L136" s="5"/>
       <c r="M136" s="5"/>
       <c r="N136" s="14" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="O136" s="14" t="s">
-        <v>609</v>
-      </c>
-      <c r="P136" s="14" t="s">
-        <v>606</v>
+        <v>607</v>
+      </c>
+      <c r="P136" s="13" t="s">
+        <v>609</v>
       </c>
       <c r="Q136" s="5" t="s">
-        <v>537</v>
+        <v>542</v>
       </c>
     </row>
     <row r="137" spans="1:17" x14ac:dyDescent="0.3">
@@ -9228,7 +9281,7 @@
         <v>291</v>
       </c>
       <c r="C137" s="5" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D137" s="5" t="s">
         <v>4</v>
@@ -9255,10 +9308,10 @@
         <v>609</v>
       </c>
       <c r="P137" s="14" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="Q137" s="5" t="s">
-        <v>695</v>
+        <v>537</v>
       </c>
     </row>
     <row r="138" spans="1:17" x14ac:dyDescent="0.3">
@@ -9266,10 +9319,10 @@
         <v>117</v>
       </c>
       <c r="B138" s="5" t="s">
-        <v>90</v>
+        <v>291</v>
       </c>
       <c r="C138" s="5" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D138" s="5" t="s">
         <v>4</v>
@@ -9278,14 +9331,14 @@
         <v>314</v>
       </c>
       <c r="F138" s="5" t="s">
-        <v>317</v>
+        <v>6</v>
       </c>
       <c r="G138" s="5"/>
       <c r="H138" s="5"/>
       <c r="I138" s="5"/>
       <c r="J138" s="5"/>
       <c r="K138" s="5" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="L138" s="5"/>
       <c r="M138" s="5"/>
@@ -9293,13 +9346,13 @@
         <v>606</v>
       </c>
       <c r="O138" s="14" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="P138" s="14" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="Q138" s="5" t="s">
-        <v>535</v>
+        <v>695</v>
       </c>
     </row>
     <row r="139" spans="1:17" x14ac:dyDescent="0.3">
@@ -9307,40 +9360,40 @@
         <v>117</v>
       </c>
       <c r="B139" s="5" t="s">
-        <v>292</v>
+        <v>90</v>
       </c>
       <c r="C139" s="5" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="D139" s="5" t="s">
-        <v>112</v>
+        <v>4</v>
       </c>
       <c r="E139" s="5" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F139" s="5" t="s">
-        <v>364</v>
+        <v>317</v>
       </c>
       <c r="G139" s="5"/>
       <c r="H139" s="5"/>
       <c r="I139" s="5"/>
       <c r="J139" s="5"/>
       <c r="K139" s="5" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="L139" s="5"/>
       <c r="M139" s="5"/>
       <c r="N139" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="O139" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="P139" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="Q139" s="5" t="s">
-        <v>540</v>
+        <v>535</v>
       </c>
     </row>
     <row r="140" spans="1:17" x14ac:dyDescent="0.3">
@@ -9348,40 +9401,40 @@
         <v>117</v>
       </c>
       <c r="B140" s="5" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C140" s="5" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D140" s="5" t="s">
-        <v>4</v>
+        <v>112</v>
       </c>
       <c r="E140" s="5" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="F140" s="5" t="s">
-        <v>6</v>
+        <v>364</v>
       </c>
       <c r="G140" s="5"/>
       <c r="H140" s="5"/>
       <c r="I140" s="5"/>
       <c r="J140" s="5"/>
       <c r="K140" s="5" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="L140" s="5"/>
       <c r="M140" s="5"/>
       <c r="N140" s="14" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="O140" s="14" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="P140" s="14" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="Q140" s="5" t="s">
-        <v>696</v>
+        <v>540</v>
       </c>
     </row>
     <row r="141" spans="1:17" x14ac:dyDescent="0.3">
@@ -9389,10 +9442,10 @@
         <v>117</v>
       </c>
       <c r="B141" s="5" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C141" s="5" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D141" s="5" t="s">
         <v>4</v>
@@ -9401,7 +9454,7 @@
         <v>314</v>
       </c>
       <c r="F141" s="5" t="s">
-        <v>318</v>
+        <v>6</v>
       </c>
       <c r="G141" s="5"/>
       <c r="H141" s="5"/>
@@ -9413,16 +9466,16 @@
       <c r="L141" s="5"/>
       <c r="M141" s="5"/>
       <c r="N141" s="14" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="O141" s="14" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="P141" s="14" t="s">
         <v>609</v>
       </c>
       <c r="Q141" s="5" t="s">
-        <v>543</v>
+        <v>696</v>
       </c>
     </row>
     <row r="142" spans="1:17" x14ac:dyDescent="0.3">
@@ -9430,51 +9483,51 @@
         <v>117</v>
       </c>
       <c r="B142" s="5" t="s">
-        <v>92</v>
+        <v>294</v>
       </c>
       <c r="C142" s="5" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D142" s="5" t="s">
-        <v>112</v>
+        <v>4</v>
       </c>
       <c r="E142" s="5" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F142" s="5" t="s">
-        <v>391</v>
+        <v>318</v>
       </c>
       <c r="G142" s="5"/>
       <c r="H142" s="5"/>
       <c r="I142" s="5"/>
       <c r="J142" s="5"/>
       <c r="K142" s="5" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="L142" s="5"/>
       <c r="M142" s="5"/>
-      <c r="N142" s="13" t="s">
+      <c r="N142" s="14" t="s">
         <v>609</v>
       </c>
       <c r="O142" s="14" t="s">
-        <v>607</v>
-      </c>
-      <c r="P142" s="13" t="s">
+        <v>610</v>
+      </c>
+      <c r="P142" s="14" t="s">
         <v>609</v>
       </c>
       <c r="Q142" s="5" t="s">
-        <v>544</v>
-      </c>
-    </row>
-    <row r="143" spans="1:17" ht="81" x14ac:dyDescent="0.3">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="143" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A143" s="4" t="s">
         <v>117</v>
       </c>
       <c r="B143" s="5" t="s">
-        <v>295</v>
+        <v>92</v>
       </c>
       <c r="C143" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D143" s="5" t="s">
         <v>112</v>
@@ -9483,7 +9536,7 @@
         <v>315</v>
       </c>
       <c r="F143" s="5" t="s">
-        <v>364</v>
+        <v>391</v>
       </c>
       <c r="G143" s="5"/>
       <c r="H143" s="5"/>
@@ -9493,23 +9546,21 @@
         <v>368</v>
       </c>
       <c r="L143" s="5"/>
-      <c r="M143" s="10" t="s">
-        <v>595</v>
-      </c>
+      <c r="M143" s="5"/>
       <c r="N143" s="13" t="s">
         <v>609</v>
       </c>
       <c r="O143" s="14" t="s">
         <v>607</v>
       </c>
-      <c r="P143" s="14" t="s">
-        <v>607</v>
+      <c r="P143" s="13" t="s">
+        <v>609</v>
       </c>
       <c r="Q143" s="5" t="s">
-        <v>536</v>
-      </c>
-    </row>
-    <row r="144" spans="1:17" x14ac:dyDescent="0.3">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="144" spans="1:17" ht="81" x14ac:dyDescent="0.3">
       <c r="A144" s="4" t="s">
         <v>117</v>
       </c>
@@ -9517,7 +9568,7 @@
         <v>295</v>
       </c>
       <c r="C144" s="5" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="D144" s="5" t="s">
         <v>112</v>
@@ -9526,19 +9577,21 @@
         <v>315</v>
       </c>
       <c r="F144" s="5" t="s">
-        <v>324</v>
+        <v>364</v>
       </c>
       <c r="G144" s="5"/>
       <c r="H144" s="5"/>
       <c r="I144" s="5"/>
       <c r="J144" s="5"/>
       <c r="K144" s="5" t="s">
-        <v>375</v>
+        <v>368</v>
       </c>
       <c r="L144" s="5"/>
-      <c r="M144" s="5"/>
-      <c r="N144" s="14" t="s">
-        <v>607</v>
+      <c r="M144" s="10" t="s">
+        <v>595</v>
+      </c>
+      <c r="N144" s="13" t="s">
+        <v>609</v>
       </c>
       <c r="O144" s="14" t="s">
         <v>607</v>
@@ -9547,89 +9600,89 @@
         <v>607</v>
       </c>
       <c r="Q144" s="5" t="s">
-        <v>546</v>
-      </c>
-    </row>
-    <row r="145" spans="1:17" ht="148.5" x14ac:dyDescent="0.3">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="145" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A145" s="4" t="s">
         <v>117</v>
       </c>
       <c r="B145" s="5" t="s">
-        <v>93</v>
+        <v>295</v>
       </c>
       <c r="C145" s="5" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D145" s="5" t="s">
-        <v>4</v>
+        <v>112</v>
       </c>
       <c r="E145" s="5" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="F145" s="5" t="s">
-        <v>6</v>
+        <v>324</v>
       </c>
       <c r="G145" s="5"/>
       <c r="H145" s="5"/>
       <c r="I145" s="5"/>
       <c r="J145" s="5"/>
       <c r="K145" s="5" t="s">
-        <v>707</v>
+        <v>375</v>
       </c>
       <c r="L145" s="5"/>
       <c r="M145" s="5"/>
       <c r="N145" s="14" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="O145" s="14" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="P145" s="14" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="Q145" s="5" t="s">
-        <v>532</v>
-      </c>
-    </row>
-    <row r="146" spans="1:17" x14ac:dyDescent="0.3">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="146" spans="1:17" ht="148.5" x14ac:dyDescent="0.3">
       <c r="A146" s="4" t="s">
         <v>117</v>
       </c>
       <c r="B146" s="5" t="s">
-        <v>296</v>
+        <v>93</v>
       </c>
       <c r="C146" s="5" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D146" s="5" t="s">
-        <v>112</v>
+        <v>4</v>
       </c>
       <c r="E146" s="5" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F146" s="5" t="s">
-        <v>364</v>
+        <v>6</v>
       </c>
       <c r="G146" s="5"/>
       <c r="H146" s="5"/>
       <c r="I146" s="5"/>
       <c r="J146" s="5"/>
       <c r="K146" s="5" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="L146" s="5"/>
       <c r="M146" s="5"/>
       <c r="N146" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="O146" s="14" t="s">
-        <v>607</v>
-      </c>
-      <c r="P146" s="13" t="s">
-        <v>609</v>
+        <v>609</v>
+      </c>
+      <c r="P146" s="14" t="s">
+        <v>606</v>
       </c>
       <c r="Q146" s="5" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
     </row>
     <row r="147" spans="1:17" x14ac:dyDescent="0.3">
@@ -9637,51 +9690,51 @@
         <v>117</v>
       </c>
       <c r="B147" s="5" t="s">
-        <v>94</v>
+        <v>296</v>
       </c>
       <c r="C147" s="5" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D147" s="5" t="s">
-        <v>4</v>
+        <v>112</v>
       </c>
       <c r="E147" s="5" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="F147" s="5" t="s">
-        <v>6</v>
+        <v>364</v>
       </c>
       <c r="G147" s="5"/>
       <c r="H147" s="5"/>
       <c r="I147" s="5"/>
       <c r="J147" s="5"/>
       <c r="K147" s="5" t="s">
-        <v>372</v>
+        <v>706</v>
       </c>
       <c r="L147" s="5"/>
       <c r="M147" s="5"/>
       <c r="N147" s="14" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="O147" s="14" t="s">
-        <v>609</v>
-      </c>
-      <c r="P147" s="14" t="s">
-        <v>606</v>
+        <v>607</v>
+      </c>
+      <c r="P147" s="13" t="s">
+        <v>609</v>
       </c>
       <c r="Q147" s="5" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="148" spans="1:17" ht="135" x14ac:dyDescent="0.3">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="148" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A148" s="4" t="s">
         <v>117</v>
       </c>
       <c r="B148" s="5" t="s">
-        <v>297</v>
+        <v>94</v>
       </c>
       <c r="C148" s="5" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D148" s="5" t="s">
         <v>4</v>
@@ -9700,31 +9753,29 @@
         <v>372</v>
       </c>
       <c r="L148" s="5"/>
-      <c r="M148" s="10" t="s">
-        <v>596</v>
-      </c>
+      <c r="M148" s="5"/>
       <c r="N148" s="14" t="s">
-        <v>610</v>
+        <v>606</v>
       </c>
       <c r="O148" s="14" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="P148" s="14" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="Q148" s="5" t="s">
-        <v>548</v>
-      </c>
-    </row>
-    <row r="149" spans="1:17" ht="148.5" x14ac:dyDescent="0.3">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="149" spans="1:17" ht="135" x14ac:dyDescent="0.3">
       <c r="A149" s="4" t="s">
         <v>117</v>
       </c>
       <c r="B149" s="5" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C149" s="5" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D149" s="5" t="s">
         <v>4</v>
@@ -9744,22 +9795,22 @@
       </c>
       <c r="L149" s="5"/>
       <c r="M149" s="10" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="N149" s="14" t="s">
-        <v>606</v>
+        <v>610</v>
       </c>
       <c r="O149" s="14" t="s">
-        <v>610</v>
+        <v>606</v>
       </c>
       <c r="P149" s="14" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="Q149" s="5" t="s">
-        <v>541</v>
-      </c>
-    </row>
-    <row r="150" spans="1:17" x14ac:dyDescent="0.3">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="150" spans="1:17" ht="148.5" x14ac:dyDescent="0.3">
       <c r="A150" s="4" t="s">
         <v>117</v>
       </c>
@@ -9767,7 +9818,7 @@
         <v>298</v>
       </c>
       <c r="C150" s="5" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D150" s="5" t="s">
         <v>4</v>
@@ -9776,28 +9827,30 @@
         <v>314</v>
       </c>
       <c r="F150" s="5" t="s">
-        <v>318</v>
+        <v>6</v>
       </c>
       <c r="G150" s="5"/>
       <c r="H150" s="5"/>
       <c r="I150" s="5"/>
       <c r="J150" s="5"/>
       <c r="K150" s="5" t="s">
-        <v>380</v>
+        <v>372</v>
       </c>
       <c r="L150" s="5"/>
-      <c r="M150" s="5"/>
+      <c r="M150" s="10" t="s">
+        <v>597</v>
+      </c>
       <c r="N150" s="14" t="s">
         <v>606</v>
       </c>
       <c r="O150" s="14" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="P150" s="14" t="s">
         <v>606</v>
       </c>
       <c r="Q150" s="5" t="s">
-        <v>550</v>
+        <v>541</v>
       </c>
     </row>
     <row r="151" spans="1:17" x14ac:dyDescent="0.3">
@@ -9805,10 +9858,10 @@
         <v>117</v>
       </c>
       <c r="B151" s="5" t="s">
-        <v>395</v>
+        <v>298</v>
       </c>
       <c r="C151" s="5" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D151" s="5" t="s">
         <v>4</v>
@@ -9817,14 +9870,14 @@
         <v>314</v>
       </c>
       <c r="F151" s="5" t="s">
-        <v>6</v>
+        <v>318</v>
       </c>
       <c r="G151" s="5"/>
       <c r="H151" s="5"/>
       <c r="I151" s="5"/>
       <c r="J151" s="5"/>
       <c r="K151" s="5" t="s">
-        <v>372</v>
+        <v>380</v>
       </c>
       <c r="L151" s="5"/>
       <c r="M151" s="5"/>
@@ -9832,24 +9885,24 @@
         <v>606</v>
       </c>
       <c r="O151" s="14" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="P151" s="14" t="s">
         <v>606</v>
       </c>
       <c r="Q151" s="5" t="s">
-        <v>539</v>
+        <v>550</v>
       </c>
     </row>
     <row r="152" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A152" s="4" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B152" s="5" t="s">
-        <v>299</v>
+        <v>395</v>
       </c>
       <c r="C152" s="5" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D152" s="5" t="s">
         <v>4</v>
@@ -9858,7 +9911,7 @@
         <v>314</v>
       </c>
       <c r="F152" s="5" t="s">
-        <v>320</v>
+        <v>6</v>
       </c>
       <c r="G152" s="5"/>
       <c r="H152" s="5"/>
@@ -9870,16 +9923,16 @@
       <c r="L152" s="5"/>
       <c r="M152" s="5"/>
       <c r="N152" s="14" t="s">
+        <v>606</v>
+      </c>
+      <c r="O152" s="14" t="s">
         <v>610</v>
       </c>
-      <c r="O152" s="14" t="s">
-        <v>609</v>
-      </c>
       <c r="P152" s="14" t="s">
         <v>606</v>
       </c>
       <c r="Q152" s="5" t="s">
-        <v>552</v>
+        <v>539</v>
       </c>
     </row>
     <row r="153" spans="1:17" x14ac:dyDescent="0.3">
@@ -9887,10 +9940,10 @@
         <v>118</v>
       </c>
       <c r="B153" s="5" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C153" s="5" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D153" s="5" t="s">
         <v>4</v>
@@ -9899,7 +9952,7 @@
         <v>314</v>
       </c>
       <c r="F153" s="5" t="s">
-        <v>6</v>
+        <v>320</v>
       </c>
       <c r="G153" s="5"/>
       <c r="H153" s="5"/>
@@ -9910,17 +9963,17 @@
       </c>
       <c r="L153" s="5"/>
       <c r="M153" s="5"/>
-      <c r="N153" s="13" t="s">
-        <v>609</v>
-      </c>
-      <c r="O153" s="13" t="s">
+      <c r="N153" s="14" t="s">
+        <v>610</v>
+      </c>
+      <c r="O153" s="14" t="s">
         <v>609</v>
       </c>
       <c r="P153" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="Q153" s="5" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
     </row>
     <row r="154" spans="1:17" x14ac:dyDescent="0.3">
@@ -9931,7 +9984,7 @@
         <v>300</v>
       </c>
       <c r="C154" s="5" t="s">
-        <v>612</v>
+        <v>223</v>
       </c>
       <c r="D154" s="5" t="s">
         <v>4</v>
@@ -9940,28 +9993,28 @@
         <v>314</v>
       </c>
       <c r="F154" s="5" t="s">
-        <v>396</v>
+        <v>6</v>
       </c>
       <c r="G154" s="5"/>
       <c r="H154" s="5"/>
       <c r="I154" s="5"/>
       <c r="J154" s="5"/>
       <c r="K154" s="5" t="s">
-        <v>383</v>
+        <v>372</v>
       </c>
       <c r="L154" s="5"/>
       <c r="M154" s="5"/>
-      <c r="N154" s="14" t="s">
-        <v>606</v>
-      </c>
-      <c r="O154" s="14" t="s">
+      <c r="N154" s="13" t="s">
+        <v>609</v>
+      </c>
+      <c r="O154" s="13" t="s">
         <v>609</v>
       </c>
       <c r="P154" s="14" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="Q154" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
     <row r="155" spans="1:17" x14ac:dyDescent="0.3">
@@ -9972,7 +10025,7 @@
         <v>300</v>
       </c>
       <c r="C155" s="5" t="s">
-        <v>224</v>
+        <v>612</v>
       </c>
       <c r="D155" s="5" t="s">
         <v>4</v>
@@ -9981,14 +10034,14 @@
         <v>314</v>
       </c>
       <c r="F155" s="5" t="s">
-        <v>6</v>
+        <v>396</v>
       </c>
       <c r="G155" s="5"/>
       <c r="H155" s="5"/>
       <c r="I155" s="5"/>
       <c r="J155" s="5"/>
       <c r="K155" s="5" t="s">
-        <v>372</v>
+        <v>383</v>
       </c>
       <c r="L155" s="5"/>
       <c r="M155" s="5"/>
@@ -9999,10 +10052,10 @@
         <v>609</v>
       </c>
       <c r="P155" s="14" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="Q155" s="5" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
     </row>
     <row r="156" spans="1:17" x14ac:dyDescent="0.3">
@@ -10010,10 +10063,10 @@
         <v>118</v>
       </c>
       <c r="B156" s="5" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C156" s="5" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D156" s="5" t="s">
         <v>4</v>
@@ -10033,17 +10086,17 @@
       </c>
       <c r="L156" s="5"/>
       <c r="M156" s="5"/>
-      <c r="N156" s="13" t="s">
-        <v>609</v>
-      </c>
-      <c r="O156" s="13" t="s">
-        <v>609</v>
-      </c>
-      <c r="P156" s="13" t="s">
-        <v>609</v>
+      <c r="N156" s="14" t="s">
+        <v>606</v>
+      </c>
+      <c r="O156" s="14" t="s">
+        <v>609</v>
+      </c>
+      <c r="P156" s="14" t="s">
+        <v>606</v>
       </c>
       <c r="Q156" s="5" t="s">
-        <v>551</v>
+        <v>556</v>
       </c>
     </row>
     <row r="157" spans="1:17" x14ac:dyDescent="0.3">
@@ -10051,26 +10104,26 @@
         <v>118</v>
       </c>
       <c r="B157" s="5" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C157" s="5" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D157" s="5" t="s">
-        <v>112</v>
+        <v>4</v>
       </c>
       <c r="E157" s="5" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F157" s="5" t="s">
-        <v>364</v>
+        <v>6</v>
       </c>
       <c r="G157" s="5"/>
       <c r="H157" s="5"/>
       <c r="I157" s="5"/>
       <c r="J157" s="5"/>
       <c r="K157" s="5" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="L157" s="5"/>
       <c r="M157" s="5"/>
@@ -10080,63 +10133,63 @@
       <c r="O157" s="13" t="s">
         <v>609</v>
       </c>
-      <c r="P157" s="14" t="s">
-        <v>607</v>
+      <c r="P157" s="13" t="s">
+        <v>609</v>
       </c>
       <c r="Q157" s="5" t="s">
-        <v>560</v>
-      </c>
-    </row>
-    <row r="158" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="158" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A158" s="4" t="s">
         <v>118</v>
       </c>
       <c r="B158" s="5" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C158" s="5" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D158" s="5" t="s">
-        <v>4</v>
+        <v>112</v>
       </c>
       <c r="E158" s="5" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="F158" s="5" t="s">
-        <v>6</v>
+        <v>364</v>
       </c>
       <c r="G158" s="5"/>
       <c r="H158" s="5"/>
       <c r="I158" s="5"/>
       <c r="J158" s="5"/>
       <c r="K158" s="5" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="L158" s="5"/>
       <c r="M158" s="5"/>
-      <c r="N158" s="14" t="s">
-        <v>606</v>
-      </c>
-      <c r="O158" s="14" t="s">
+      <c r="N158" s="13" t="s">
+        <v>609</v>
+      </c>
+      <c r="O158" s="13" t="s">
         <v>609</v>
       </c>
       <c r="P158" s="14" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="Q158" s="5" t="s">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="159" spans="1:17" ht="27" x14ac:dyDescent="0.3">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="159" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A159" s="4" t="s">
         <v>118</v>
       </c>
       <c r="B159" s="5" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C159" s="5" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D159" s="5" t="s">
         <v>4</v>
@@ -10152,11 +10205,9 @@
       <c r="I159" s="5"/>
       <c r="J159" s="5"/>
       <c r="K159" s="5" t="s">
-        <v>372</v>
-      </c>
-      <c r="L159" s="5" t="s">
-        <v>711</v>
-      </c>
+        <v>370</v>
+      </c>
+      <c r="L159" s="5"/>
       <c r="M159" s="5"/>
       <c r="N159" s="14" t="s">
         <v>606</v>
@@ -10165,21 +10216,21 @@
         <v>609</v>
       </c>
       <c r="P159" s="14" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="Q159" s="5" t="s">
-        <v>563</v>
-      </c>
-    </row>
-    <row r="160" spans="1:17" x14ac:dyDescent="0.3">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="160" spans="1:17" ht="27" x14ac:dyDescent="0.3">
       <c r="A160" s="4" t="s">
         <v>118</v>
       </c>
       <c r="B160" s="5" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C160" s="5" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D160" s="5" t="s">
         <v>4</v>
@@ -10198,20 +10249,20 @@
         <v>372</v>
       </c>
       <c r="L160" s="5" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="M160" s="5"/>
       <c r="N160" s="14" t="s">
         <v>606</v>
       </c>
       <c r="O160" s="14" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="P160" s="14" t="s">
         <v>606</v>
       </c>
       <c r="Q160" s="5" t="s">
-        <v>559</v>
+        <v>563</v>
       </c>
     </row>
     <row r="161" spans="1:17" x14ac:dyDescent="0.3">
@@ -10219,10 +10270,10 @@
         <v>118</v>
       </c>
       <c r="B161" s="5" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C161" s="5" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D161" s="5" t="s">
         <v>4</v>
@@ -10238,32 +10289,34 @@
       <c r="I161" s="5"/>
       <c r="J161" s="5"/>
       <c r="K161" s="5" t="s">
-        <v>377</v>
-      </c>
-      <c r="L161" s="5"/>
+        <v>372</v>
+      </c>
+      <c r="L161" s="5" t="s">
+        <v>709</v>
+      </c>
       <c r="M161" s="5"/>
       <c r="N161" s="14" t="s">
         <v>606</v>
       </c>
       <c r="O161" s="14" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="P161" s="14" t="s">
         <v>606</v>
       </c>
       <c r="Q161" s="5" t="s">
-        <v>566</v>
-      </c>
-    </row>
-    <row r="162" spans="1:17" ht="175.5" x14ac:dyDescent="0.3">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="162" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A162" s="4" t="s">
         <v>118</v>
       </c>
       <c r="B162" s="5" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C162" s="5" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D162" s="5" t="s">
         <v>4</v>
@@ -10279,14 +10332,12 @@
       <c r="I162" s="5"/>
       <c r="J162" s="5"/>
       <c r="K162" s="5" t="s">
-        <v>370</v>
-      </c>
-      <c r="L162" s="5" t="s">
-        <v>715</v>
-      </c>
+        <v>377</v>
+      </c>
+      <c r="L162" s="5"/>
       <c r="M162" s="5"/>
       <c r="N162" s="14" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="O162" s="14" t="s">
         <v>609</v>
@@ -10295,18 +10346,18 @@
         <v>606</v>
       </c>
       <c r="Q162" s="5" t="s">
-        <v>567</v>
-      </c>
-    </row>
-    <row r="163" spans="1:17" x14ac:dyDescent="0.3">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="163" spans="1:17" ht="175.5" x14ac:dyDescent="0.3">
       <c r="A163" s="4" t="s">
         <v>118</v>
       </c>
       <c r="B163" s="5" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C163" s="5" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D163" s="5" t="s">
         <v>4</v>
@@ -10322,21 +10373,23 @@
       <c r="I163" s="5"/>
       <c r="J163" s="5"/>
       <c r="K163" s="5" t="s">
-        <v>372</v>
-      </c>
-      <c r="L163" s="5"/>
+        <v>370</v>
+      </c>
+      <c r="L163" s="5" t="s">
+        <v>715</v>
+      </c>
       <c r="M163" s="5"/>
       <c r="N163" s="14" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="O163" s="14" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="P163" s="14" t="s">
         <v>606</v>
       </c>
       <c r="Q163" s="5" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
     </row>
     <row r="164" spans="1:17" x14ac:dyDescent="0.3">
@@ -10344,10 +10397,10 @@
         <v>118</v>
       </c>
       <c r="B164" s="5" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C164" s="5" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D164" s="5" t="s">
         <v>4</v>
@@ -10363,7 +10416,7 @@
       <c r="I164" s="5"/>
       <c r="J164" s="5"/>
       <c r="K164" s="5" t="s">
-        <v>377</v>
+        <v>372</v>
       </c>
       <c r="L164" s="5"/>
       <c r="M164" s="5"/>
@@ -10371,16 +10424,16 @@
         <v>606</v>
       </c>
       <c r="O164" s="14" t="s">
-        <v>606</v>
+        <v>610</v>
       </c>
       <c r="P164" s="14" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="Q164" s="5" t="s">
-        <v>555</v>
-      </c>
-    </row>
-    <row r="165" spans="1:17" ht="40.5" x14ac:dyDescent="0.3">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="165" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A165" s="4" t="s">
         <v>118</v>
       </c>
@@ -10388,7 +10441,7 @@
         <v>309</v>
       </c>
       <c r="C165" s="5" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="D165" s="5" t="s">
         <v>4</v>
@@ -10407,31 +10460,29 @@
         <v>377</v>
       </c>
       <c r="L165" s="5"/>
-      <c r="M165" s="10" t="s">
-        <v>598</v>
-      </c>
+      <c r="M165" s="5"/>
       <c r="N165" s="14" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="O165" s="14" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="P165" s="14" t="s">
         <v>609</v>
       </c>
       <c r="Q165" s="5" t="s">
-        <v>568</v>
-      </c>
-    </row>
-    <row r="166" spans="1:17" ht="27" x14ac:dyDescent="0.3">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="166" spans="1:17" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A166" s="4" t="s">
         <v>118</v>
       </c>
       <c r="B166" s="5" t="s">
-        <v>99</v>
+        <v>309</v>
       </c>
       <c r="C166" s="5" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="D166" s="5" t="s">
         <v>4</v>
@@ -10447,26 +10498,26 @@
       <c r="I166" s="5"/>
       <c r="J166" s="5"/>
       <c r="K166" s="5" t="s">
-        <v>376</v>
-      </c>
-      <c r="L166" s="5" t="s">
-        <v>708</v>
-      </c>
-      <c r="M166" s="5"/>
+        <v>377</v>
+      </c>
+      <c r="L166" s="5"/>
+      <c r="M166" s="10" t="s">
+        <v>598</v>
+      </c>
       <c r="N166" s="14" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="O166" s="14" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="P166" s="14" t="s">
         <v>609</v>
       </c>
       <c r="Q166" s="5" t="s">
-        <v>557</v>
-      </c>
-    </row>
-    <row r="167" spans="1:17" ht="283.5" x14ac:dyDescent="0.3">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="167" spans="1:17" ht="27" x14ac:dyDescent="0.3">
       <c r="A167" s="4" t="s">
         <v>118</v>
       </c>
@@ -10474,7 +10525,7 @@
         <v>99</v>
       </c>
       <c r="C167" s="5" t="s">
-        <v>8</v>
+        <v>235</v>
       </c>
       <c r="D167" s="5" t="s">
         <v>4</v>
@@ -10483,19 +10534,19 @@
         <v>314</v>
       </c>
       <c r="F167" s="5" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G167" s="5"/>
       <c r="H167" s="5"/>
       <c r="I167" s="5"/>
       <c r="J167" s="5"/>
       <c r="K167" s="5" t="s">
-        <v>382</v>
-      </c>
-      <c r="L167" s="5"/>
-      <c r="M167" s="10" t="s">
-        <v>599</v>
-      </c>
+        <v>376</v>
+      </c>
+      <c r="L167" s="5" t="s">
+        <v>708</v>
+      </c>
+      <c r="M167" s="5"/>
       <c r="N167" s="14" t="s">
         <v>606</v>
       </c>
@@ -10503,13 +10554,13 @@
         <v>606</v>
       </c>
       <c r="P167" s="14" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="Q167" s="5" t="s">
-        <v>558</v>
-      </c>
-    </row>
-    <row r="168" spans="1:17" ht="27" x14ac:dyDescent="0.3">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="168" spans="1:17" ht="283.5" x14ac:dyDescent="0.3">
       <c r="A168" s="4" t="s">
         <v>118</v>
       </c>
@@ -10517,7 +10568,7 @@
         <v>99</v>
       </c>
       <c r="C168" s="5" t="s">
-        <v>236</v>
+        <v>8</v>
       </c>
       <c r="D168" s="5" t="s">
         <v>4</v>
@@ -10526,19 +10577,19 @@
         <v>314</v>
       </c>
       <c r="F168" s="5" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G168" s="5"/>
       <c r="H168" s="5"/>
       <c r="I168" s="5"/>
       <c r="J168" s="5"/>
       <c r="K168" s="5" t="s">
-        <v>376</v>
-      </c>
-      <c r="L168" s="5" t="s">
-        <v>710</v>
-      </c>
-      <c r="M168" s="5"/>
+        <v>382</v>
+      </c>
+      <c r="L168" s="5"/>
+      <c r="M168" s="10" t="s">
+        <v>599</v>
+      </c>
       <c r="N168" s="14" t="s">
         <v>606</v>
       </c>
@@ -10546,13 +10597,13 @@
         <v>606</v>
       </c>
       <c r="P168" s="14" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="Q168" s="5" t="s">
-        <v>562</v>
-      </c>
-    </row>
-    <row r="169" spans="1:17" ht="40.5" x14ac:dyDescent="0.3">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="169" spans="1:17" ht="27" x14ac:dyDescent="0.3">
       <c r="A169" s="4" t="s">
         <v>118</v>
       </c>
@@ -10560,7 +10611,7 @@
         <v>99</v>
       </c>
       <c r="C169" s="5" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="D169" s="5" t="s">
         <v>4</v>
@@ -10579,7 +10630,7 @@
         <v>376</v>
       </c>
       <c r="L169" s="5" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
       <c r="M169" s="5"/>
       <c r="N169" s="14" t="s">
@@ -10589,62 +10640,64 @@
         <v>606</v>
       </c>
       <c r="P169" s="14" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="Q169" s="5" t="s">
-        <v>565</v>
-      </c>
-    </row>
-    <row r="170" spans="1:17" x14ac:dyDescent="0.3">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="170" spans="1:17" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A170" s="4" t="s">
         <v>118</v>
       </c>
       <c r="B170" s="5" t="s">
-        <v>310</v>
+        <v>99</v>
       </c>
       <c r="C170" s="5" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="D170" s="5" t="s">
-        <v>112</v>
+        <v>4</v>
       </c>
       <c r="E170" s="5" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F170" s="5" t="s">
-        <v>364</v>
+        <v>6</v>
       </c>
       <c r="G170" s="5"/>
       <c r="H170" s="5"/>
       <c r="I170" s="5"/>
       <c r="J170" s="5"/>
       <c r="K170" s="5" t="s">
-        <v>368</v>
-      </c>
-      <c r="L170" s="5"/>
+        <v>376</v>
+      </c>
+      <c r="L170" s="5" t="s">
+        <v>712</v>
+      </c>
       <c r="M170" s="5"/>
       <c r="N170" s="14" t="s">
         <v>606</v>
       </c>
       <c r="O170" s="14" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="P170" s="14" t="s">
-        <v>606</v>
+        <v>610</v>
       </c>
       <c r="Q170" s="5" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
     </row>
     <row r="171" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A171" s="4" t="s">
-        <v>313</v>
+        <v>118</v>
       </c>
       <c r="B171" s="5" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C171" s="5" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D171" s="5" t="s">
         <v>112</v>
@@ -10664,17 +10717,17 @@
       </c>
       <c r="L171" s="5"/>
       <c r="M171" s="5"/>
-      <c r="N171" s="13" t="s">
-        <v>609</v>
-      </c>
-      <c r="O171" s="13" t="s">
+      <c r="N171" s="14" t="s">
+        <v>606</v>
+      </c>
+      <c r="O171" s="14" t="s">
         <v>609</v>
       </c>
       <c r="P171" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="Q171" s="5" t="s">
-        <v>571</v>
+        <v>564</v>
       </c>
     </row>
     <row r="172" spans="1:17" x14ac:dyDescent="0.3">
@@ -10685,37 +10738,37 @@
         <v>311</v>
       </c>
       <c r="C172" s="5" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D172" s="5" t="s">
-        <v>4</v>
+        <v>112</v>
       </c>
       <c r="E172" s="5" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="F172" s="5" t="s">
-        <v>6</v>
+        <v>364</v>
       </c>
       <c r="G172" s="5"/>
       <c r="H172" s="5"/>
       <c r="I172" s="5"/>
       <c r="J172" s="5"/>
       <c r="K172" s="5" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="L172" s="5"/>
       <c r="M172" s="5"/>
-      <c r="N172" s="14" t="s">
-        <v>609</v>
-      </c>
-      <c r="O172" s="14" t="s">
+      <c r="N172" s="13" t="s">
+        <v>609</v>
+      </c>
+      <c r="O172" s="13" t="s">
         <v>609</v>
       </c>
       <c r="P172" s="14" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="Q172" s="5" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
     </row>
     <row r="173" spans="1:17" x14ac:dyDescent="0.3">
@@ -10723,40 +10776,40 @@
         <v>313</v>
       </c>
       <c r="B173" s="5" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C173" s="5" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="D173" s="5" t="s">
-        <v>112</v>
+        <v>4</v>
       </c>
       <c r="E173" s="5" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F173" s="5" t="s">
-        <v>364</v>
+        <v>6</v>
       </c>
       <c r="G173" s="5"/>
       <c r="H173" s="5"/>
       <c r="I173" s="5"/>
       <c r="J173" s="5"/>
       <c r="K173" s="5" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="L173" s="5"/>
       <c r="M173" s="5"/>
-      <c r="N173" s="13" t="s">
-        <v>609</v>
-      </c>
-      <c r="O173" s="13" t="s">
+      <c r="N173" s="14" t="s">
+        <v>609</v>
+      </c>
+      <c r="O173" s="14" t="s">
         <v>609</v>
       </c>
       <c r="P173" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="Q173" s="5" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
     </row>
     <row r="174" spans="1:17" x14ac:dyDescent="0.3">
@@ -10767,75 +10820,81 @@
         <v>312</v>
       </c>
       <c r="C174" s="5" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D174" s="5" t="s">
-        <v>4</v>
+        <v>112</v>
       </c>
       <c r="E174" s="5" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="F174" s="5" t="s">
-        <v>6</v>
+        <v>364</v>
       </c>
       <c r="G174" s="5"/>
       <c r="H174" s="5"/>
       <c r="I174" s="5"/>
       <c r="J174" s="5"/>
       <c r="K174" s="5" t="s">
-        <v>378</v>
+        <v>368</v>
       </c>
       <c r="L174" s="5"/>
       <c r="M174" s="5"/>
-      <c r="N174" s="14" t="s">
-        <v>609</v>
-      </c>
-      <c r="O174" s="14" t="s">
+      <c r="N174" s="13" t="s">
+        <v>609</v>
+      </c>
+      <c r="O174" s="13" t="s">
         <v>609</v>
       </c>
       <c r="P174" s="14" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="Q174" s="5" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="175" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A175" s="4" t="s">
+        <v>313</v>
+      </c>
+      <c r="B175" s="5" t="s">
+        <v>312</v>
+      </c>
+      <c r="C175" s="5" t="s">
+        <v>242</v>
+      </c>
+      <c r="D175" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E175" s="5" t="s">
+        <v>314</v>
+      </c>
+      <c r="F175" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="G175" s="5"/>
+      <c r="H175" s="5"/>
+      <c r="I175" s="5"/>
+      <c r="J175" s="5"/>
+      <c r="K175" s="5" t="s">
+        <v>378</v>
+      </c>
+      <c r="L175" s="5"/>
+      <c r="M175" s="5"/>
+      <c r="N175" s="14" t="s">
+        <v>609</v>
+      </c>
+      <c r="O175" s="14" t="s">
+        <v>609</v>
+      </c>
+      <c r="P175" s="14" t="s">
+        <v>609</v>
+      </c>
+      <c r="Q175" s="5" t="s">
         <v>573</v>
       </c>
     </row>
-    <row r="175" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A175" s="6" t="s">
-        <v>360</v>
-      </c>
-      <c r="B175" s="6" t="s">
-        <v>361</v>
-      </c>
-      <c r="C175" s="6" t="s">
-        <v>331</v>
-      </c>
-      <c r="D175" s="6" t="s">
-        <v>331</v>
-      </c>
-      <c r="E175" s="6" t="s">
-        <v>682</v>
-      </c>
-      <c r="F175" s="6" t="s">
-        <v>332</v>
-      </c>
-      <c r="G175" s="6"/>
-      <c r="H175" s="6"/>
-      <c r="I175" s="6"/>
-      <c r="J175" s="6"/>
-      <c r="K175" s="6" t="s">
-        <v>333</v>
-      </c>
-      <c r="L175" s="2"/>
-      <c r="M175" s="2"/>
-      <c r="N175" s="16"/>
-      <c r="O175" s="16"/>
-      <c r="P175" s="16"/>
-      <c r="Q175" s="8" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="176" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A176" s="6" t="s">
         <v>360</v>
       </c>
@@ -10843,23 +10902,23 @@
         <v>361</v>
       </c>
       <c r="C176" s="6" t="s">
-        <v>641</v>
+        <v>331</v>
       </c>
       <c r="D176" s="6" t="s">
-        <v>683</v>
+        <v>331</v>
       </c>
       <c r="E176" s="6" t="s">
         <v>682</v>
       </c>
-      <c r="F176" s="6"/>
-      <c r="G176" s="6" t="s">
-        <v>408</v>
-      </c>
+      <c r="F176" s="6" t="s">
+        <v>332</v>
+      </c>
+      <c r="G176" s="6"/>
       <c r="H176" s="6"/>
       <c r="I176" s="6"/>
       <c r="J176" s="6"/>
       <c r="K176" s="6" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="L176" s="2"/>
       <c r="M176" s="2"/>
@@ -10872,39 +10931,37 @@
     </row>
     <row r="177" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A177" s="6" t="s">
-        <v>118</v>
+        <v>360</v>
       </c>
       <c r="B177" s="6" t="s">
-        <v>336</v>
+        <v>361</v>
       </c>
       <c r="C177" s="6" t="s">
-        <v>335</v>
+        <v>641</v>
       </c>
       <c r="D177" s="6" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="E177" s="6" t="s">
-        <v>681</v>
-      </c>
-      <c r="F177" s="6" t="s">
-        <v>397</v>
-      </c>
-      <c r="G177" s="7" t="s">
-        <v>337</v>
-      </c>
-      <c r="H177" s="7" t="s">
-        <v>354</v>
-      </c>
-      <c r="I177" s="7"/>
-      <c r="J177" s="7"/>
-      <c r="K177" s="7"/>
-      <c r="L177" s="7"/>
-      <c r="M177" s="7"/>
-      <c r="N177" s="15"/>
-      <c r="O177" s="15"/>
-      <c r="P177" s="15"/>
+        <v>682</v>
+      </c>
+      <c r="F177" s="6"/>
+      <c r="G177" s="6" t="s">
+        <v>408</v>
+      </c>
+      <c r="H177" s="6"/>
+      <c r="I177" s="6"/>
+      <c r="J177" s="6"/>
+      <c r="K177" s="6" t="s">
+        <v>334</v>
+      </c>
+      <c r="L177" s="2"/>
+      <c r="M177" s="2"/>
+      <c r="N177" s="16"/>
+      <c r="O177" s="16"/>
+      <c r="P177" s="16"/>
       <c r="Q177" s="8" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="178" spans="1:17" x14ac:dyDescent="0.3">
@@ -10927,10 +10984,10 @@
         <v>397</v>
       </c>
       <c r="G178" s="7" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="H178" s="7" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="I178" s="7"/>
       <c r="J178" s="7"/>
@@ -10949,10 +11006,10 @@
         <v>118</v>
       </c>
       <c r="B179" s="6" t="s">
-        <v>398</v>
+        <v>336</v>
       </c>
       <c r="C179" s="6" t="s">
-        <v>342</v>
+        <v>335</v>
       </c>
       <c r="D179" s="6" t="s">
         <v>685</v>
@@ -10961,26 +11018,24 @@
         <v>681</v>
       </c>
       <c r="F179" s="6" t="s">
-        <v>574</v>
+        <v>397</v>
       </c>
       <c r="G179" s="7" t="s">
-        <v>343</v>
+        <v>338</v>
       </c>
       <c r="H179" s="7" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="I179" s="7"/>
       <c r="J179" s="7"/>
-      <c r="K179" s="6" t="s">
-        <v>333</v>
-      </c>
-      <c r="L179" s="6"/>
-      <c r="M179" s="6"/>
-      <c r="N179" s="16"/>
-      <c r="O179" s="16"/>
-      <c r="P179" s="16"/>
-      <c r="Q179" s="6" t="s">
-        <v>341</v>
+      <c r="K179" s="7"/>
+      <c r="L179" s="7"/>
+      <c r="M179" s="7"/>
+      <c r="N179" s="15"/>
+      <c r="O179" s="15"/>
+      <c r="P179" s="15"/>
+      <c r="Q179" s="8" t="s">
+        <v>339</v>
       </c>
     </row>
     <row r="180" spans="1:17" x14ac:dyDescent="0.3">
@@ -11003,10 +11058,10 @@
         <v>574</v>
       </c>
       <c r="G180" s="7" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="H180" s="7" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="I180" s="7"/>
       <c r="J180" s="7"/>
@@ -11027,34 +11082,38 @@
         <v>118</v>
       </c>
       <c r="B181" s="6" t="s">
-        <v>615</v>
+        <v>398</v>
       </c>
       <c r="C181" s="6" t="s">
-        <v>614</v>
+        <v>342</v>
       </c>
       <c r="D181" s="6" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="E181" s="6" t="s">
         <v>681</v>
       </c>
-      <c r="F181" s="7" t="s">
-        <v>643</v>
-      </c>
-      <c r="G181" s="6" t="s">
-        <v>642</v>
-      </c>
-      <c r="H181" s="6"/>
-      <c r="I181" s="6"/>
-      <c r="J181" s="6"/>
-      <c r="K181" s="6"/>
-      <c r="L181" s="2"/>
-      <c r="M181" s="2"/>
+      <c r="F181" s="6" t="s">
+        <v>574</v>
+      </c>
+      <c r="G181" s="7" t="s">
+        <v>344</v>
+      </c>
+      <c r="H181" s="7" t="s">
+        <v>357</v>
+      </c>
+      <c r="I181" s="7"/>
+      <c r="J181" s="7"/>
+      <c r="K181" s="6" t="s">
+        <v>333</v>
+      </c>
+      <c r="L181" s="6"/>
+      <c r="M181" s="6"/>
       <c r="N181" s="16"/>
       <c r="O181" s="16"/>
       <c r="P181" s="16"/>
       <c r="Q181" s="6" t="s">
-        <v>645</v>
+        <v>341</v>
       </c>
     </row>
     <row r="182" spans="1:17" x14ac:dyDescent="0.3">
@@ -11062,10 +11121,10 @@
         <v>118</v>
       </c>
       <c r="B182" s="6" t="s">
-        <v>336</v>
+        <v>615</v>
       </c>
       <c r="C182" s="6" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="D182" s="6" t="s">
         <v>684</v>
@@ -11074,9 +11133,11 @@
         <v>681</v>
       </c>
       <c r="F182" s="7" t="s">
-        <v>646</v>
-      </c>
-      <c r="G182" s="6"/>
+        <v>643</v>
+      </c>
+      <c r="G182" s="6" t="s">
+        <v>642</v>
+      </c>
       <c r="H182" s="6"/>
       <c r="I182" s="6"/>
       <c r="J182" s="6"/>
@@ -11087,18 +11148,18 @@
       <c r="O182" s="16"/>
       <c r="P182" s="16"/>
       <c r="Q182" s="6" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
     </row>
     <row r="183" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A183" s="6" t="s">
-        <v>618</v>
+        <v>118</v>
       </c>
       <c r="B183" s="6" t="s">
-        <v>617</v>
+        <v>336</v>
       </c>
       <c r="C183" s="6" t="s">
-        <v>649</v>
+        <v>616</v>
       </c>
       <c r="D183" s="6" t="s">
         <v>684</v>
@@ -11106,8 +11167,8 @@
       <c r="E183" s="6" t="s">
         <v>681</v>
       </c>
-      <c r="F183" s="6" t="s">
-        <v>648</v>
+      <c r="F183" s="7" t="s">
+        <v>646</v>
       </c>
       <c r="G183" s="6"/>
       <c r="H183" s="6"/>
@@ -11120,18 +11181,18 @@
       <c r="O183" s="16"/>
       <c r="P183" s="16"/>
       <c r="Q183" s="6" t="s">
-        <v>647</v>
+        <v>644</v>
       </c>
     </row>
     <row r="184" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A184" s="6" t="s">
-        <v>118</v>
+        <v>618</v>
       </c>
       <c r="B184" s="6" t="s">
-        <v>620</v>
+        <v>617</v>
       </c>
       <c r="C184" s="6" t="s">
-        <v>619</v>
+        <v>649</v>
       </c>
       <c r="D184" s="6" t="s">
         <v>684</v>
@@ -11140,7 +11201,7 @@
         <v>681</v>
       </c>
       <c r="F184" s="6" t="s">
-        <v>651</v>
+        <v>648</v>
       </c>
       <c r="G184" s="6"/>
       <c r="H184" s="6"/>
@@ -11153,18 +11214,18 @@
       <c r="O184" s="16"/>
       <c r="P184" s="16"/>
       <c r="Q184" s="6" t="s">
-        <v>650</v>
+        <v>647</v>
       </c>
     </row>
     <row r="185" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A185" s="6" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B185" s="6" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="C185" s="6" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="D185" s="6" t="s">
         <v>684</v>
@@ -11173,7 +11234,7 @@
         <v>681</v>
       </c>
       <c r="F185" s="6" t="s">
-        <v>654</v>
+        <v>651</v>
       </c>
       <c r="G185" s="6"/>
       <c r="H185" s="6"/>
@@ -11186,18 +11247,18 @@
       <c r="O185" s="16"/>
       <c r="P185" s="16"/>
       <c r="Q185" s="6" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
     </row>
     <row r="186" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A186" s="6" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B186" s="6" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="C186" s="6" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="D186" s="6" t="s">
         <v>684</v>
@@ -11206,7 +11267,7 @@
         <v>681</v>
       </c>
       <c r="F186" s="6" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="G186" s="6"/>
       <c r="H186" s="6"/>
@@ -11219,18 +11280,18 @@
       <c r="O186" s="16"/>
       <c r="P186" s="16"/>
       <c r="Q186" s="6" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
     </row>
     <row r="187" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A187" s="6" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B187" s="6" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="C187" s="6" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="D187" s="6" t="s">
         <v>684</v>
@@ -11239,70 +11300,66 @@
         <v>681</v>
       </c>
       <c r="F187" s="6" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="G187" s="6"/>
       <c r="H187" s="6"/>
       <c r="I187" s="6"/>
       <c r="J187" s="6"/>
-      <c r="K187" s="6" t="s">
-        <v>657</v>
-      </c>
+      <c r="K187" s="6"/>
       <c r="L187" s="2"/>
       <c r="M187" s="2"/>
       <c r="N187" s="16"/>
       <c r="O187" s="16"/>
       <c r="P187" s="16"/>
       <c r="Q187" s="6" t="s">
-        <v>658</v>
-      </c>
-    </row>
-    <row r="188" spans="1:17" ht="95.25" x14ac:dyDescent="0.3">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="188" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A188" s="6" t="s">
-        <v>618</v>
+        <v>116</v>
       </c>
       <c r="B188" s="6" t="s">
-        <v>629</v>
+        <v>626</v>
       </c>
       <c r="C188" s="6" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="D188" s="6" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="E188" s="6" t="s">
         <v>681</v>
       </c>
       <c r="F188" s="6" t="s">
-        <v>660</v>
+        <v>656</v>
       </c>
       <c r="G188" s="6"/>
       <c r="H188" s="6"/>
       <c r="I188" s="6"/>
       <c r="J188" s="6"/>
       <c r="K188" s="6" t="s">
-        <v>661</v>
+        <v>657</v>
       </c>
       <c r="L188" s="2"/>
-      <c r="M188" s="21" t="s">
-        <v>662</v>
-      </c>
+      <c r="M188" s="2"/>
       <c r="N188" s="16"/>
       <c r="O188" s="16"/>
       <c r="P188" s="16"/>
       <c r="Q188" s="6" t="s">
-        <v>659</v>
-      </c>
-    </row>
-    <row r="189" spans="1:17" ht="162.75" x14ac:dyDescent="0.3">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="189" spans="1:17" ht="95.25" x14ac:dyDescent="0.3">
       <c r="A189" s="6" t="s">
         <v>618</v>
       </c>
       <c r="B189" s="6" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="C189" s="6" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="D189" s="6" t="s">
         <v>685</v>
@@ -11311,35 +11368,35 @@
         <v>681</v>
       </c>
       <c r="F189" s="6" t="s">
-        <v>663</v>
+        <v>660</v>
       </c>
       <c r="G189" s="6"/>
       <c r="H189" s="6"/>
       <c r="I189" s="6"/>
       <c r="J189" s="6"/>
-      <c r="K189" s="5" t="s">
-        <v>664</v>
+      <c r="K189" s="6" t="s">
+        <v>661</v>
       </c>
       <c r="L189" s="2"/>
       <c r="M189" s="21" t="s">
-        <v>666</v>
+        <v>662</v>
       </c>
       <c r="N189" s="16"/>
       <c r="O189" s="16"/>
       <c r="P189" s="16"/>
       <c r="Q189" s="6" t="s">
-        <v>665</v>
-      </c>
-    </row>
-    <row r="190" spans="1:17" ht="135.75" x14ac:dyDescent="0.3">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="190" spans="1:17" ht="162.75" x14ac:dyDescent="0.3">
       <c r="A190" s="6" t="s">
-        <v>117</v>
+        <v>618</v>
       </c>
       <c r="B190" s="6" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="C190" s="6" t="s">
-        <v>631</v>
+        <v>628</v>
       </c>
       <c r="D190" s="6" t="s">
         <v>685</v>
@@ -11359,24 +11416,24 @@
       </c>
       <c r="L190" s="2"/>
       <c r="M190" s="21" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="N190" s="16"/>
       <c r="O190" s="16"/>
       <c r="P190" s="16"/>
       <c r="Q190" s="6" t="s">
-        <v>667</v>
-      </c>
-    </row>
-    <row r="191" spans="1:17" ht="149.25" x14ac:dyDescent="0.3">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="191" spans="1:17" ht="135.75" x14ac:dyDescent="0.3">
       <c r="A191" s="6" t="s">
         <v>117</v>
       </c>
       <c r="B191" s="6" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="C191" s="6" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="D191" s="6" t="s">
         <v>685</v>
@@ -11385,35 +11442,35 @@
         <v>681</v>
       </c>
       <c r="F191" s="6" t="s">
-        <v>676</v>
+        <v>663</v>
       </c>
       <c r="G191" s="6"/>
       <c r="H191" s="6"/>
       <c r="I191" s="6"/>
       <c r="J191" s="6"/>
-      <c r="K191" s="6" t="s">
-        <v>661</v>
+      <c r="K191" s="5" t="s">
+        <v>664</v>
       </c>
       <c r="L191" s="2"/>
       <c r="M191" s="21" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="N191" s="16"/>
       <c r="O191" s="16"/>
       <c r="P191" s="16"/>
       <c r="Q191" s="6" t="s">
-        <v>669</v>
-      </c>
-    </row>
-    <row r="192" spans="1:17" ht="27" x14ac:dyDescent="0.3">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="192" spans="1:17" ht="149.25" x14ac:dyDescent="0.3">
       <c r="A192" s="6" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B192" s="6" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="C192" s="6" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="D192" s="6" t="s">
         <v>685</v>
@@ -11421,34 +11478,36 @@
       <c r="E192" s="6" t="s">
         <v>681</v>
       </c>
-      <c r="F192" s="6"/>
-      <c r="G192" s="7" t="s">
-        <v>671</v>
-      </c>
+      <c r="F192" s="6" t="s">
+        <v>676</v>
+      </c>
+      <c r="G192" s="6"/>
       <c r="H192" s="6"/>
       <c r="I192" s="6"/>
       <c r="J192" s="6"/>
       <c r="K192" s="6" t="s">
-        <v>672</v>
+        <v>661</v>
       </c>
       <c r="L192" s="2"/>
-      <c r="M192" s="2"/>
+      <c r="M192" s="21" t="s">
+        <v>670</v>
+      </c>
       <c r="N192" s="16"/>
       <c r="O192" s="16"/>
       <c r="P192" s="16"/>
       <c r="Q192" s="6" t="s">
-        <v>673</v>
-      </c>
-    </row>
-    <row r="193" spans="1:17" ht="54.75" x14ac:dyDescent="0.3">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="193" spans="1:17" ht="27" x14ac:dyDescent="0.3">
       <c r="A193" s="6" t="s">
-        <v>618</v>
+        <v>118</v>
       </c>
       <c r="B193" s="6" t="s">
-        <v>629</v>
+        <v>637</v>
       </c>
       <c r="C193" s="6" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="D193" s="6" t="s">
         <v>685</v>
@@ -11456,36 +11515,34 @@
       <c r="E193" s="6" t="s">
         <v>681</v>
       </c>
-      <c r="F193" s="6" t="s">
-        <v>675</v>
-      </c>
-      <c r="G193" s="6"/>
+      <c r="F193" s="6"/>
+      <c r="G193" s="7" t="s">
+        <v>671</v>
+      </c>
       <c r="H193" s="6"/>
       <c r="I193" s="6"/>
       <c r="J193" s="6"/>
       <c r="K193" s="6" t="s">
-        <v>661</v>
+        <v>672</v>
       </c>
       <c r="L193" s="2"/>
-      <c r="M193" s="21" t="s">
-        <v>677</v>
-      </c>
+      <c r="M193" s="2"/>
       <c r="N193" s="16"/>
       <c r="O193" s="16"/>
       <c r="P193" s="16"/>
       <c r="Q193" s="6" t="s">
-        <v>674</v>
-      </c>
-    </row>
-    <row r="194" spans="1:17" ht="27.75" x14ac:dyDescent="0.3">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="194" spans="1:17" ht="54.75" x14ac:dyDescent="0.3">
       <c r="A194" s="6" t="s">
-        <v>117</v>
+        <v>618</v>
       </c>
       <c r="B194" s="6" t="s">
-        <v>639</v>
+        <v>629</v>
       </c>
       <c r="C194" s="6" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="D194" s="6" t="s">
         <v>685</v>
@@ -11494,38 +11551,75 @@
         <v>681</v>
       </c>
       <c r="F194" s="6" t="s">
-        <v>678</v>
+        <v>675</v>
       </c>
       <c r="G194" s="6"/>
       <c r="H194" s="6"/>
       <c r="I194" s="6"/>
       <c r="J194" s="6"/>
       <c r="K194" s="6" t="s">
-        <v>680</v>
+        <v>661</v>
       </c>
       <c r="L194" s="2"/>
       <c r="M194" s="21" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="N194" s="16"/>
       <c r="O194" s="16"/>
       <c r="P194" s="16"/>
       <c r="Q194" s="6" t="s">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="195" spans="1:17" ht="27.75" x14ac:dyDescent="0.3">
+      <c r="A195" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="B195" s="6" t="s">
+        <v>639</v>
+      </c>
+      <c r="C195" s="6" t="s">
+        <v>638</v>
+      </c>
+      <c r="D195" s="6" t="s">
+        <v>685</v>
+      </c>
+      <c r="E195" s="6" t="s">
+        <v>681</v>
+      </c>
+      <c r="F195" s="6" t="s">
+        <v>678</v>
+      </c>
+      <c r="G195" s="6"/>
+      <c r="H195" s="6"/>
+      <c r="I195" s="6"/>
+      <c r="J195" s="6"/>
+      <c r="K195" s="6" t="s">
+        <v>680</v>
+      </c>
+      <c r="L195" s="2"/>
+      <c r="M195" s="21" t="s">
+        <v>679</v>
+      </c>
+      <c r="N195" s="16"/>
+      <c r="O195" s="16"/>
+      <c r="P195" s="16"/>
+      <c r="Q195" s="6" t="s">
         <v>640</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="B1:Q180" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="B1:Q181" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="Q2:Q174">
+  <conditionalFormatting sqref="Q2:Q175">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <hyperlinks>
-    <hyperlink ref="Q177" r:id="rId1" xr:uid="{E8A5EE79-38DC-470C-9E4B-60B8DB179166}"/>
-    <hyperlink ref="Q175" r:id="rId2" xr:uid="{B514AFC6-F2CC-453E-A7EE-749BE8F59F63}"/>
-    <hyperlink ref="Q176" r:id="rId3" xr:uid="{D2C8DCF1-2A86-40FB-A718-5DFF8C67103B}"/>
-    <hyperlink ref="Q178" r:id="rId4" xr:uid="{2526EBF2-78DF-4B4D-A609-DDD4E216E820}"/>
-    <hyperlink ref="Q99" r:id="rId5" xr:uid="{05B60FA0-37BF-4BDF-A54A-C6015B78419C}"/>
+    <hyperlink ref="Q178" r:id="rId1" xr:uid="{E8A5EE79-38DC-470C-9E4B-60B8DB179166}"/>
+    <hyperlink ref="Q176" r:id="rId2" xr:uid="{B514AFC6-F2CC-453E-A7EE-749BE8F59F63}"/>
+    <hyperlink ref="Q177" r:id="rId3" xr:uid="{D2C8DCF1-2A86-40FB-A718-5DFF8C67103B}"/>
+    <hyperlink ref="Q179" r:id="rId4" xr:uid="{2526EBF2-78DF-4B4D-A609-DDD4E216E820}"/>
+    <hyperlink ref="Q100" r:id="rId5" xr:uid="{05B60FA0-37BF-4BDF-A54A-C6015B78419C}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/app/convert/forest_sample_template.xlsx
+++ b/app/convert/forest_sample_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TAX-JUNGYOON\forest-app\app\convert\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99472A04-9E51-4B5E-A6F2-DF51971ED33B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3F32918-A6E2-4D10-AF4E-296ECE16E826}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="658" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2348" uniqueCount="728">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2349" uniqueCount="729">
   <si>
     <t>시설명</t>
   </si>
@@ -2694,6 +2694,10 @@
   </si>
   <si>
     <t>https://www.foresttrip.go.kr/indvz/main.do?hmpgId=ID02030132</t>
+  </si>
+  <si>
+    <t>2026.07월중 정식오픈 예정</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -7494,7 +7498,9 @@
       <c r="K94" s="6" t="s">
         <v>726</v>
       </c>
-      <c r="L94" s="2"/>
+      <c r="L94" s="2" t="s">
+        <v>728</v>
+      </c>
       <c r="M94" s="2"/>
       <c r="N94" s="14"/>
       <c r="O94" s="14"/>

--- a/app/convert/forest_sample_template.xlsx
+++ b/app/convert/forest_sample_template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TAX-JUNGYOON\forest-app\app\convert\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3F32918-A6E2-4D10-AF4E-296ECE16E826}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C24A310-082F-4BDD-AE66-A97940AA0921}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="658" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="658" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="샘플" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2349" uniqueCount="729">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2350" uniqueCount="730">
   <si>
     <t>시설명</t>
   </si>
@@ -2697,6 +2697,20 @@
   </si>
   <si>
     <t>2026.07월중 정식오픈 예정</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>경상남도도민우선예약정책
+매월1일 09시~ 5일 18시
+숲속의 집(1호, 4호, 5호, 10호)
+산림문화휴양관(201호, 202호, 203호, 204호, 205호)
+숲속수련장(2호, 3호)
+반려견 동반 휴양림
+[산림문화휴양관] 반려견 동반객실 1호, 2호 (2객실)
+바우처우선예약정책
+숲속의집 6호 금원암(6인실)
+산림문화휴양관 206호(5인실)
+숲속수련장 6호(19인실)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -10064,7 +10078,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="156" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:17" ht="202.5" x14ac:dyDescent="0.3">
       <c r="A156" s="4" t="s">
         <v>118</v>
       </c>
@@ -10090,7 +10104,9 @@
       <c r="K156" s="5" t="s">
         <v>372</v>
       </c>
-      <c r="L156" s="5"/>
+      <c r="L156" s="5" t="s">
+        <v>729</v>
+      </c>
       <c r="M156" s="5"/>
       <c r="N156" s="14" t="s">
         <v>606</v>

--- a/app/convert/forest_sample_template.xlsx
+++ b/app/convert/forest_sample_template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TAX-JUNGYOON\forest-app\app\convert\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C24A310-082F-4BDD-AE66-A97940AA0921}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D2460BB-CFAB-446B-BE91-C5E838106134}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="658" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-14490" yWindow="210" windowWidth="14160" windowHeight="15120" tabRatio="658" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="샘플" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2350" uniqueCount="730">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4702" uniqueCount="731">
   <si>
     <t>시설명</t>
   </si>
@@ -2711,6 +2711,20 @@
 숲속의집 6호 금원암(6인실)
 산림문화휴양관 206호(5인실)
 숲속수련장 6호(19인실)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>지역주민우선예약
+산림휴양관A 1~2호
+산림휴양관B 1호
+숲속의집A 1~2호
+숲속의집B 1~3호
+숲속의집D 1~2호
+오토캠핑A 1~4호
+오토캠핑B 1~8호
+바우처우선예약
+숲속의집 A 103호
+휴양관 A 103호</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -6468,7 +6482,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="70" spans="1:17" ht="121.5" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:17" ht="162" x14ac:dyDescent="0.3">
       <c r="A70" s="4" t="s">
         <v>3</v>
       </c>
@@ -6494,7 +6508,9 @@
       <c r="K70" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="L70" s="5"/>
+      <c r="L70" s="5" t="s">
+        <v>730</v>
+      </c>
       <c r="M70" s="10" t="s">
         <v>580</v>
       </c>

--- a/app/convert/forest_sample_template.xlsx
+++ b/app/convert/forest_sample_template.xlsx
@@ -8,22 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TAX-JUNGYOON\forest-app\app\convert\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D2460BB-CFAB-446B-BE91-C5E838106134}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7913A58-A22F-4036-94F2-75BE4A0387B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-14490" yWindow="210" windowWidth="14160" windowHeight="15120" tabRatio="658" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="658" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="샘플" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">샘플!$B$1:$Q$181</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">샘플!$B$1:$Q$182</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4702" uniqueCount="731">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2364" uniqueCount="736">
   <si>
     <t>시설명</t>
   </si>
@@ -2726,6 +2726,28 @@
 숲속의집 A 103호
 휴양관 A 103호</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>성수기 지역주민우선예약
+[숲속의집]군자산 (6인/40㎡)에어컨
+[숲속의집]도토리나무 (8인/42㎡)에어컨
+[숲속의집]왕소나무 (14인/70㎡)에어컨</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>강원</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>진부령자연휴양림</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>고성군</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.foresttrip.go.kr/indvz/main.do?hmpgId=0306</t>
   </si>
 </sst>
 </file>
@@ -3219,7 +3241,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q195"/>
+  <dimension ref="A1:Q196"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13" style="18" bestFit="1" customWidth="1"/>
@@ -4223,15 +4245,15 @@
         <v>426</v>
       </c>
     </row>
-    <row r="21" spans="1:17" ht="54" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
-        <v>101</v>
+        <v>732</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>73</v>
+        <v>734</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>28</v>
+        <v>733</v>
       </c>
       <c r="D21" s="5" t="s">
         <v>112</v>
@@ -4258,31 +4280,23 @@
         <v>7</v>
       </c>
       <c r="L21" s="5"/>
-      <c r="M21" s="5" t="s">
-        <v>718</v>
-      </c>
-      <c r="N21" s="14" t="s">
-        <v>611</v>
-      </c>
-      <c r="O21" s="13" t="s">
-        <v>607</v>
-      </c>
-      <c r="P21" s="13" t="s">
-        <v>607</v>
-      </c>
+      <c r="M21" s="10"/>
+      <c r="N21" s="13"/>
+      <c r="O21" s="14"/>
+      <c r="P21" s="13"/>
       <c r="Q21" s="5" t="s">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="22" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17" ht="54" x14ac:dyDescent="0.3">
       <c r="A22" s="4" t="s">
         <v>101</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D22" s="5" t="s">
         <v>112</v>
@@ -4309,29 +4323,31 @@
         <v>7</v>
       </c>
       <c r="L22" s="5"/>
-      <c r="M22" s="5"/>
-      <c r="N22" s="13" t="s">
-        <v>609</v>
+      <c r="M22" s="5" t="s">
+        <v>718</v>
+      </c>
+      <c r="N22" s="14" t="s">
+        <v>611</v>
       </c>
       <c r="O22" s="13" t="s">
         <v>607</v>
       </c>
       <c r="P22" s="13" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="Q22" s="5" t="s">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.3">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="23" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
         <v>101</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>385</v>
+        <v>74</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D23" s="5" t="s">
         <v>112</v>
@@ -4362,25 +4378,25 @@
       <c r="N23" s="13" t="s">
         <v>609</v>
       </c>
-      <c r="O23" s="14" t="s">
-        <v>611</v>
+      <c r="O23" s="13" t="s">
+        <v>607</v>
       </c>
       <c r="P23" s="13" t="s">
         <v>609</v>
       </c>
       <c r="Q23" s="5" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A24" s="4" t="s">
-        <v>115</v>
+        <v>101</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>75</v>
+        <v>385</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D24" s="5" t="s">
         <v>112</v>
@@ -4395,7 +4411,7 @@
         <v>349</v>
       </c>
       <c r="H24" s="5" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="I24" s="5" t="s">
         <v>352</v>
@@ -4408,17 +4424,17 @@
       </c>
       <c r="L24" s="5"/>
       <c r="M24" s="5"/>
-      <c r="N24" s="14" t="s">
+      <c r="N24" s="13" t="s">
         <v>609</v>
       </c>
       <c r="O24" s="14" t="s">
-        <v>609</v>
-      </c>
-      <c r="P24" s="14" t="s">
+        <v>611</v>
+      </c>
+      <c r="P24" s="13" t="s">
         <v>609</v>
       </c>
       <c r="Q24" s="5" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.3">
@@ -4426,10 +4442,10 @@
         <v>115</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D25" s="5" t="s">
         <v>112</v>
@@ -4444,7 +4460,7 @@
         <v>349</v>
       </c>
       <c r="H25" s="5" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="I25" s="5" t="s">
         <v>352</v>
@@ -4457,17 +4473,17 @@
       </c>
       <c r="L25" s="5"/>
       <c r="M25" s="5"/>
-      <c r="N25" s="13" t="s">
-        <v>609</v>
-      </c>
-      <c r="O25" s="13" t="s">
-        <v>607</v>
-      </c>
-      <c r="P25" s="13" t="s">
-        <v>607</v>
+      <c r="N25" s="14" t="s">
+        <v>609</v>
+      </c>
+      <c r="O25" s="14" t="s">
+        <v>609</v>
+      </c>
+      <c r="P25" s="14" t="s">
+        <v>609</v>
       </c>
       <c r="Q25" s="5" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.3">
@@ -4475,10 +4491,10 @@
         <v>115</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D26" s="5" t="s">
         <v>112</v>
@@ -4507,7 +4523,7 @@
       <c r="L26" s="5"/>
       <c r="M26" s="5"/>
       <c r="N26" s="13" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="O26" s="13" t="s">
         <v>607</v>
@@ -4516,7 +4532,7 @@
         <v>607</v>
       </c>
       <c r="Q26" s="5" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.3">
@@ -4524,10 +4540,10 @@
         <v>115</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D27" s="5" t="s">
         <v>112</v>
@@ -4556,27 +4572,27 @@
       <c r="L27" s="5"/>
       <c r="M27" s="5"/>
       <c r="N27" s="13" t="s">
-        <v>609</v>
-      </c>
-      <c r="O27" s="14" t="s">
-        <v>611</v>
+        <v>607</v>
+      </c>
+      <c r="O27" s="13" t="s">
+        <v>607</v>
       </c>
       <c r="P27" s="13" t="s">
         <v>607</v>
       </c>
       <c r="Q27" s="5" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="28" spans="1:17" ht="148.5" x14ac:dyDescent="0.3">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="28" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A28" s="4" t="s">
-        <v>102</v>
+        <v>115</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D28" s="5" t="s">
         <v>112</v>
@@ -4603,31 +4619,29 @@
         <v>7</v>
       </c>
       <c r="L28" s="5"/>
-      <c r="M28" s="10" t="s">
-        <v>589</v>
-      </c>
+      <c r="M28" s="5"/>
       <c r="N28" s="13" t="s">
-        <v>607</v>
-      </c>
-      <c r="O28" s="13" t="s">
-        <v>609</v>
+        <v>609</v>
+      </c>
+      <c r="O28" s="14" t="s">
+        <v>611</v>
       </c>
       <c r="P28" s="13" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="Q28" s="5" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.3">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="29" spans="1:17" ht="148.5" x14ac:dyDescent="0.3">
       <c r="A29" s="4" t="s">
         <v>102</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D29" s="5" t="s">
         <v>112</v>
@@ -4654,18 +4668,20 @@
         <v>7</v>
       </c>
       <c r="L29" s="5"/>
-      <c r="M29" s="5"/>
+      <c r="M29" s="10" t="s">
+        <v>589</v>
+      </c>
       <c r="N29" s="13" t="s">
         <v>607</v>
       </c>
       <c r="O29" s="13" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="P29" s="13" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="Q29" s="5" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.3">
@@ -4673,10 +4689,10 @@
         <v>102</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D30" s="5" t="s">
         <v>112</v>
@@ -4708,13 +4724,13 @@
         <v>607</v>
       </c>
       <c r="O30" s="13" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="P30" s="13" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="Q30" s="5" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.3">
@@ -4722,10 +4738,10 @@
         <v>102</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D31" s="5" t="s">
         <v>112</v>
@@ -4754,27 +4770,27 @@
       <c r="L31" s="5"/>
       <c r="M31" s="5"/>
       <c r="N31" s="13" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="O31" s="13" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="P31" s="13" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="Q31" s="5" t="s">
-        <v>439</v>
-      </c>
-    </row>
-    <row r="32" spans="1:17" ht="81" x14ac:dyDescent="0.3">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="32" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A32" s="4" t="s">
         <v>102</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D32" s="5" t="s">
         <v>112</v>
@@ -4801,11 +4817,9 @@
         <v>7</v>
       </c>
       <c r="L32" s="5"/>
-      <c r="M32" s="10" t="s">
-        <v>591</v>
-      </c>
+      <c r="M32" s="5"/>
       <c r="N32" s="13" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="O32" s="13" t="s">
         <v>607</v>
@@ -4814,18 +4828,18 @@
         <v>607</v>
       </c>
       <c r="Q32" s="5" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.3">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="33" spans="1:17" ht="81" x14ac:dyDescent="0.3">
       <c r="A33" s="4" t="s">
-        <v>116</v>
+        <v>102</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D33" s="5" t="s">
         <v>112</v>
@@ -4852,7 +4866,9 @@
         <v>7</v>
       </c>
       <c r="L33" s="5"/>
-      <c r="M33" s="5"/>
+      <c r="M33" s="10" t="s">
+        <v>591</v>
+      </c>
       <c r="N33" s="13" t="s">
         <v>607</v>
       </c>
@@ -4863,7 +4879,7 @@
         <v>607</v>
       </c>
       <c r="Q33" s="5" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
     </row>
     <row r="34" spans="1:17" x14ac:dyDescent="0.3">
@@ -4871,10 +4887,10 @@
         <v>116</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D34" s="5" t="s">
         <v>112</v>
@@ -4903,16 +4919,16 @@
       <c r="L34" s="5"/>
       <c r="M34" s="5"/>
       <c r="N34" s="13" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="O34" s="13" t="s">
         <v>607</v>
       </c>
       <c r="P34" s="13" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="Q34" s="5" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="35" spans="1:17" x14ac:dyDescent="0.3">
@@ -4920,10 +4936,10 @@
         <v>116</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D35" s="5" t="s">
         <v>112</v>
@@ -4958,10 +4974,10 @@
         <v>607</v>
       </c>
       <c r="P35" s="13" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="Q35" s="5" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.3">
@@ -4969,10 +4985,10 @@
         <v>116</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D36" s="5" t="s">
         <v>112</v>
@@ -4987,7 +5003,7 @@
         <v>349</v>
       </c>
       <c r="H36" s="5" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="I36" s="5" t="s">
         <v>352</v>
@@ -5004,24 +5020,24 @@
         <v>609</v>
       </c>
       <c r="O36" s="13" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="P36" s="13" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="Q36" s="5" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A37" s="4" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D37" s="5" t="s">
         <v>112</v>
@@ -5036,7 +5052,7 @@
         <v>349</v>
       </c>
       <c r="H37" s="5" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="I37" s="5" t="s">
         <v>352</v>
@@ -5049,17 +5065,17 @@
       </c>
       <c r="L37" s="5"/>
       <c r="M37" s="5"/>
-      <c r="N37" s="14" t="s">
-        <v>609</v>
-      </c>
-      <c r="O37" s="14" t="s">
-        <v>609</v>
-      </c>
-      <c r="P37" s="14" t="s">
-        <v>607</v>
+      <c r="N37" s="13" t="s">
+        <v>609</v>
+      </c>
+      <c r="O37" s="13" t="s">
+        <v>609</v>
+      </c>
+      <c r="P37" s="13" t="s">
+        <v>609</v>
       </c>
       <c r="Q37" s="5" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.3">
@@ -5067,10 +5083,10 @@
         <v>117</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D38" s="5" t="s">
         <v>112</v>
@@ -5085,7 +5101,7 @@
         <v>349</v>
       </c>
       <c r="H38" s="5" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="I38" s="5" t="s">
         <v>352</v>
@@ -5098,17 +5114,17 @@
       </c>
       <c r="L38" s="5"/>
       <c r="M38" s="5"/>
-      <c r="N38" s="13" t="s">
-        <v>607</v>
-      </c>
-      <c r="O38" s="13" t="s">
-        <v>607</v>
+      <c r="N38" s="14" t="s">
+        <v>609</v>
+      </c>
+      <c r="O38" s="14" t="s">
+        <v>609</v>
       </c>
       <c r="P38" s="14" t="s">
-        <v>611</v>
+        <v>607</v>
       </c>
       <c r="Q38" s="5" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.3">
@@ -5116,10 +5132,10 @@
         <v>117</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D39" s="5" t="s">
         <v>112</v>
@@ -5134,7 +5150,7 @@
         <v>349</v>
       </c>
       <c r="H39" s="5" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="I39" s="5" t="s">
         <v>352</v>
@@ -5148,16 +5164,16 @@
       <c r="L39" s="5"/>
       <c r="M39" s="5"/>
       <c r="N39" s="13" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="O39" s="13" t="s">
         <v>607</v>
       </c>
-      <c r="P39" s="13" t="s">
-        <v>607</v>
+      <c r="P39" s="14" t="s">
+        <v>611</v>
       </c>
       <c r="Q39" s="5" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.3">
@@ -5165,10 +5181,10 @@
         <v>117</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D40" s="5" t="s">
         <v>112</v>
@@ -5183,7 +5199,7 @@
         <v>349</v>
       </c>
       <c r="H40" s="5" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="I40" s="5" t="s">
         <v>352</v>
@@ -5196,8 +5212,8 @@
       </c>
       <c r="L40" s="5"/>
       <c r="M40" s="5"/>
-      <c r="N40" s="14" t="s">
-        <v>611</v>
+      <c r="N40" s="13" t="s">
+        <v>609</v>
       </c>
       <c r="O40" s="13" t="s">
         <v>607</v>
@@ -5206,7 +5222,7 @@
         <v>607</v>
       </c>
       <c r="Q40" s="5" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.3">
@@ -5214,10 +5230,10 @@
         <v>117</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D41" s="5" t="s">
         <v>112</v>
@@ -5232,7 +5248,7 @@
         <v>349</v>
       </c>
       <c r="H41" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I41" s="5" t="s">
         <v>352</v>
@@ -5255,7 +5271,7 @@
         <v>607</v>
       </c>
       <c r="Q41" s="5" t="s">
-        <v>444</v>
+        <v>449</v>
       </c>
     </row>
     <row r="42" spans="1:17" x14ac:dyDescent="0.3">
@@ -5263,10 +5279,10 @@
         <v>117</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D42" s="5" t="s">
         <v>112</v>
@@ -5281,7 +5297,7 @@
         <v>349</v>
       </c>
       <c r="H42" s="5" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I42" s="5" t="s">
         <v>352</v>
@@ -5294,8 +5310,8 @@
       </c>
       <c r="L42" s="5"/>
       <c r="M42" s="5"/>
-      <c r="N42" s="13" t="s">
-        <v>607</v>
+      <c r="N42" s="14" t="s">
+        <v>611</v>
       </c>
       <c r="O42" s="13" t="s">
         <v>607</v>
@@ -5304,7 +5320,7 @@
         <v>607</v>
       </c>
       <c r="Q42" s="5" t="s">
-        <v>450</v>
+        <v>444</v>
       </c>
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.3">
@@ -5312,10 +5328,10 @@
         <v>117</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D43" s="5" t="s">
         <v>112</v>
@@ -5353,18 +5369,18 @@
         <v>607</v>
       </c>
       <c r="Q43" s="5" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A44" s="4" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D44" s="5" t="s">
         <v>112</v>
@@ -5379,7 +5395,7 @@
         <v>349</v>
       </c>
       <c r="H44" s="5" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="I44" s="5" t="s">
         <v>352</v>
@@ -5393,16 +5409,16 @@
       <c r="L44" s="5"/>
       <c r="M44" s="5"/>
       <c r="N44" s="13" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="O44" s="13" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="P44" s="13" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="Q44" s="5" t="s">
-        <v>452</v>
+        <v>447</v>
       </c>
     </row>
     <row r="45" spans="1:17" x14ac:dyDescent="0.3">
@@ -5410,10 +5426,10 @@
         <v>118</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D45" s="5" t="s">
         <v>112</v>
@@ -5439,8 +5455,8 @@
       <c r="K45" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="L45" s="10"/>
-      <c r="M45" s="10"/>
+      <c r="L45" s="5"/>
+      <c r="M45" s="5"/>
       <c r="N45" s="13" t="s">
         <v>609</v>
       </c>
@@ -5451,7 +5467,7 @@
         <v>609</v>
       </c>
       <c r="Q45" s="5" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
     </row>
     <row r="46" spans="1:17" x14ac:dyDescent="0.3">
@@ -5459,10 +5475,10 @@
         <v>118</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D46" s="5" t="s">
         <v>112</v>
@@ -5477,7 +5493,7 @@
         <v>349</v>
       </c>
       <c r="H46" s="5" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="I46" s="5" t="s">
         <v>352</v>
@@ -5488,19 +5504,19 @@
       <c r="K46" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="L46" s="5"/>
-      <c r="M46" s="5"/>
-      <c r="N46" s="14" t="s">
-        <v>611</v>
+      <c r="L46" s="10"/>
+      <c r="M46" s="10"/>
+      <c r="N46" s="13" t="s">
+        <v>609</v>
       </c>
       <c r="O46" s="13" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="P46" s="13" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="Q46" s="5" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
     </row>
     <row r="47" spans="1:17" x14ac:dyDescent="0.3">
@@ -5508,10 +5524,10 @@
         <v>118</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D47" s="5" t="s">
         <v>112</v>
@@ -5539,17 +5555,17 @@
       </c>
       <c r="L47" s="5"/>
       <c r="M47" s="5"/>
-      <c r="N47" s="13" t="s">
-        <v>607</v>
-      </c>
-      <c r="O47" s="14" t="s">
+      <c r="N47" s="14" t="s">
         <v>611</v>
       </c>
+      <c r="O47" s="13" t="s">
+        <v>607</v>
+      </c>
       <c r="P47" s="13" t="s">
         <v>607</v>
       </c>
       <c r="Q47" s="5" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.3">
@@ -5557,10 +5573,10 @@
         <v>118</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D48" s="5" t="s">
         <v>112</v>
@@ -5591,53 +5607,63 @@
       <c r="N48" s="13" t="s">
         <v>607</v>
       </c>
-      <c r="O48" s="13" t="s">
-        <v>609</v>
+      <c r="O48" s="14" t="s">
+        <v>611</v>
       </c>
       <c r="P48" s="13" t="s">
         <v>607</v>
       </c>
       <c r="Q48" s="5" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
     </row>
     <row r="49" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A49" s="4" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>56</v>
+        <v>99</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>119</v>
+        <v>55</v>
       </c>
       <c r="D49" s="5" t="s">
         <v>112</v>
       </c>
       <c r="E49" s="5" t="s">
-        <v>315</v>
-      </c>
-      <c r="F49" s="5"/>
+        <v>113</v>
+      </c>
+      <c r="F49" s="5" t="s">
+        <v>602</v>
+      </c>
       <c r="G49" s="5" t="s">
-        <v>316</v>
-      </c>
-      <c r="H49" s="5"/>
-      <c r="I49" s="5"/>
-      <c r="J49" s="5"/>
-      <c r="K49" s="5"/>
+        <v>349</v>
+      </c>
+      <c r="H49" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="I49" s="5" t="s">
+        <v>352</v>
+      </c>
+      <c r="J49" s="5" t="s">
+        <v>353</v>
+      </c>
+      <c r="K49" s="5" t="s">
+        <v>7</v>
+      </c>
       <c r="L49" s="5"/>
       <c r="M49" s="5"/>
       <c r="N49" s="13" t="s">
         <v>607</v>
       </c>
       <c r="O49" s="13" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="P49" s="13" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="Q49" s="5" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="50" spans="1:17" x14ac:dyDescent="0.3">
@@ -5648,7 +5674,7 @@
         <v>56</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D50" s="5" t="s">
         <v>112</v>
@@ -5656,18 +5682,16 @@
       <c r="E50" s="5" t="s">
         <v>315</v>
       </c>
-      <c r="F50" s="20" t="s">
-        <v>363</v>
-      </c>
-      <c r="G50" s="20"/>
-      <c r="H50" s="20"/>
-      <c r="I50" s="20"/>
-      <c r="J50" s="20"/>
-      <c r="K50" s="19" t="s">
-        <v>367</v>
-      </c>
-      <c r="L50" s="9"/>
-      <c r="M50" s="9"/>
+      <c r="F50" s="5"/>
+      <c r="G50" s="5" t="s">
+        <v>316</v>
+      </c>
+      <c r="H50" s="5"/>
+      <c r="I50" s="5"/>
+      <c r="J50" s="5"/>
+      <c r="K50" s="5"/>
+      <c r="L50" s="5"/>
+      <c r="M50" s="5"/>
       <c r="N50" s="13" t="s">
         <v>607</v>
       </c>
@@ -5677,8 +5701,8 @@
       <c r="P50" s="13" t="s">
         <v>609</v>
       </c>
-      <c r="Q50" s="8" t="s">
-        <v>691</v>
+      <c r="Q50" s="5" t="s">
+        <v>456</v>
       </c>
     </row>
     <row r="51" spans="1:17" x14ac:dyDescent="0.3">
@@ -5686,10 +5710,10 @@
         <v>114</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>243</v>
+        <v>56</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D51" s="5" t="s">
         <v>112</v>
@@ -5697,20 +5721,20 @@
       <c r="E51" s="5" t="s">
         <v>315</v>
       </c>
-      <c r="F51" s="5" t="s">
-        <v>365</v>
-      </c>
-      <c r="G51" s="5"/>
-      <c r="H51" s="5"/>
-      <c r="I51" s="5"/>
-      <c r="J51" s="5"/>
-      <c r="K51" s="5" t="s">
-        <v>369</v>
-      </c>
-      <c r="L51" s="5"/>
-      <c r="M51" s="5"/>
-      <c r="N51" s="14" t="s">
-        <v>611</v>
+      <c r="F51" s="20" t="s">
+        <v>363</v>
+      </c>
+      <c r="G51" s="20"/>
+      <c r="H51" s="20"/>
+      <c r="I51" s="20"/>
+      <c r="J51" s="20"/>
+      <c r="K51" s="19" t="s">
+        <v>367</v>
+      </c>
+      <c r="L51" s="9"/>
+      <c r="M51" s="9"/>
+      <c r="N51" s="13" t="s">
+        <v>607</v>
       </c>
       <c r="O51" s="13" t="s">
         <v>607</v>
@@ -5718,8 +5742,8 @@
       <c r="P51" s="13" t="s">
         <v>609</v>
       </c>
-      <c r="Q51" s="5" t="s">
-        <v>462</v>
+      <c r="Q51" s="8" t="s">
+        <v>691</v>
       </c>
     </row>
     <row r="52" spans="1:17" x14ac:dyDescent="0.3">
@@ -5727,10 +5751,10 @@
         <v>114</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D52" s="5" t="s">
         <v>112</v>
@@ -5738,42 +5762,40 @@
       <c r="E52" s="5" t="s">
         <v>315</v>
       </c>
-      <c r="F52" s="5"/>
-      <c r="G52" s="5" t="s">
-        <v>316</v>
-      </c>
+      <c r="F52" s="5" t="s">
+        <v>365</v>
+      </c>
+      <c r="G52" s="5"/>
       <c r="H52" s="5"/>
-      <c r="I52" s="5" t="s">
-        <v>358</v>
-      </c>
-      <c r="J52" s="5" t="s">
-        <v>359</v>
-      </c>
-      <c r="K52" s="5"/>
+      <c r="I52" s="5"/>
+      <c r="J52" s="5"/>
+      <c r="K52" s="5" t="s">
+        <v>369</v>
+      </c>
       <c r="L52" s="5"/>
       <c r="M52" s="5"/>
-      <c r="N52" s="13" t="s">
-        <v>607</v>
-      </c>
-      <c r="O52" s="14" t="s">
+      <c r="N52" s="14" t="s">
         <v>611</v>
       </c>
+      <c r="O52" s="13" t="s">
+        <v>607</v>
+      </c>
       <c r="P52" s="13" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="Q52" s="5" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="53" spans="1:17" ht="162" x14ac:dyDescent="0.3">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="53" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A53" s="4" t="s">
         <v>114</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D53" s="5" t="s">
         <v>112</v>
@@ -5781,110 +5803,110 @@
       <c r="E53" s="5" t="s">
         <v>315</v>
       </c>
-      <c r="F53" s="5" t="s">
-        <v>386</v>
-      </c>
-      <c r="G53" s="5"/>
+      <c r="F53" s="5"/>
+      <c r="G53" s="5" t="s">
+        <v>316</v>
+      </c>
       <c r="H53" s="5"/>
-      <c r="I53" s="5"/>
-      <c r="J53" s="5"/>
-      <c r="K53" s="5" t="s">
-        <v>366</v>
-      </c>
-      <c r="L53" s="5" t="s">
-        <v>600</v>
-      </c>
-      <c r="M53" s="5" t="s">
-        <v>601</v>
-      </c>
-      <c r="N53" s="14" t="s">
-        <v>608</v>
+      <c r="I53" s="5" t="s">
+        <v>358</v>
+      </c>
+      <c r="J53" s="5" t="s">
+        <v>359</v>
+      </c>
+      <c r="K53" s="5"/>
+      <c r="L53" s="5"/>
+      <c r="M53" s="5"/>
+      <c r="N53" s="13" t="s">
+        <v>607</v>
       </c>
       <c r="O53" s="14" t="s">
-        <v>608</v>
-      </c>
-      <c r="P53" s="14" t="s">
-        <v>608</v>
+        <v>611</v>
+      </c>
+      <c r="P53" s="13" t="s">
+        <v>607</v>
       </c>
       <c r="Q53" s="5" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="54" spans="1:17" ht="148.5" x14ac:dyDescent="0.3">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="54" spans="1:17" ht="162" x14ac:dyDescent="0.3">
       <c r="A54" s="4" t="s">
         <v>114</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D54" s="5" t="s">
-        <v>4</v>
+        <v>112</v>
       </c>
       <c r="E54" s="5" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="F54" s="5" t="s">
-        <v>317</v>
+        <v>386</v>
       </c>
       <c r="G54" s="5"/>
       <c r="H54" s="5"/>
       <c r="I54" s="5"/>
       <c r="J54" s="5"/>
       <c r="K54" s="5" t="s">
-        <v>370</v>
-      </c>
-      <c r="L54" s="10" t="s">
-        <v>576</v>
-      </c>
-      <c r="M54" s="10" t="s">
-        <v>687</v>
-      </c>
-      <c r="N54" s="13" t="s">
-        <v>607</v>
-      </c>
-      <c r="O54" s="13" t="s">
-        <v>607</v>
-      </c>
-      <c r="P54" s="13" t="s">
-        <v>607</v>
+        <v>366</v>
+      </c>
+      <c r="L54" s="5" t="s">
+        <v>600</v>
+      </c>
+      <c r="M54" s="5" t="s">
+        <v>601</v>
+      </c>
+      <c r="N54" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="O54" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="P54" s="14" t="s">
+        <v>608</v>
       </c>
       <c r="Q54" s="5" t="s">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.3">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="55" spans="1:17" ht="148.5" x14ac:dyDescent="0.3">
       <c r="A55" s="4" t="s">
         <v>114</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D55" s="5" t="s">
-        <v>112</v>
+        <v>4</v>
       </c>
       <c r="E55" s="5" t="s">
-        <v>315</v>
-      </c>
-      <c r="F55" s="5"/>
-      <c r="G55" s="6" t="s">
-        <v>362</v>
-      </c>
-      <c r="H55" s="6"/>
-      <c r="I55" s="6" t="s">
-        <v>399</v>
-      </c>
-      <c r="J55" s="6" t="s">
-        <v>400</v>
-      </c>
-      <c r="K55" s="6"/>
-      <c r="L55" s="2"/>
-      <c r="M55" s="2"/>
+        <v>314</v>
+      </c>
+      <c r="F55" s="5" t="s">
+        <v>317</v>
+      </c>
+      <c r="G55" s="5"/>
+      <c r="H55" s="5"/>
+      <c r="I55" s="5"/>
+      <c r="J55" s="5"/>
+      <c r="K55" s="5" t="s">
+        <v>370</v>
+      </c>
+      <c r="L55" s="10" t="s">
+        <v>576</v>
+      </c>
+      <c r="M55" s="10" t="s">
+        <v>687</v>
+      </c>
       <c r="N55" s="13" t="s">
         <v>607</v>
       </c>
@@ -5894,40 +5916,40 @@
       <c r="P55" s="13" t="s">
         <v>607</v>
       </c>
-      <c r="Q55" s="6" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="56" spans="1:17" ht="27" x14ac:dyDescent="0.3">
+      <c r="Q55" s="5" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="56" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A56" s="4" t="s">
         <v>114</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>57</v>
+        <v>247</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D56" s="5" t="s">
-        <v>4</v>
+        <v>112</v>
       </c>
       <c r="E56" s="5" t="s">
-        <v>314</v>
-      </c>
-      <c r="F56" s="5" t="s">
-        <v>319</v>
-      </c>
-      <c r="G56" s="5"/>
-      <c r="H56" s="5"/>
-      <c r="I56" s="5"/>
-      <c r="J56" s="5"/>
-      <c r="K56" s="5" t="s">
-        <v>370</v>
-      </c>
-      <c r="L56" s="5" t="s">
-        <v>689</v>
-      </c>
-      <c r="M56" s="5"/>
+        <v>315</v>
+      </c>
+      <c r="F56" s="5"/>
+      <c r="G56" s="6" t="s">
+        <v>362</v>
+      </c>
+      <c r="H56" s="6"/>
+      <c r="I56" s="6" t="s">
+        <v>399</v>
+      </c>
+      <c r="J56" s="6" t="s">
+        <v>400</v>
+      </c>
+      <c r="K56" s="6"/>
+      <c r="L56" s="2"/>
+      <c r="M56" s="2"/>
       <c r="N56" s="13" t="s">
         <v>607</v>
       </c>
@@ -5937,19 +5959,19 @@
       <c r="P56" s="13" t="s">
         <v>607</v>
       </c>
-      <c r="Q56" s="5" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="57" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="Q56" s="6" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="57" spans="1:17" ht="27" x14ac:dyDescent="0.3">
       <c r="A57" s="4" t="s">
         <v>114</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D57" s="5" t="s">
         <v>4</v>
@@ -5958,31 +5980,33 @@
         <v>314</v>
       </c>
       <c r="F57" s="5" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="G57" s="5"/>
       <c r="H57" s="5"/>
       <c r="I57" s="5"/>
       <c r="J57" s="5"/>
       <c r="K57" s="5" t="s">
-        <v>371</v>
-      </c>
-      <c r="L57" s="5"/>
+        <v>370</v>
+      </c>
+      <c r="L57" s="5" t="s">
+        <v>689</v>
+      </c>
       <c r="M57" s="5"/>
-      <c r="N57" s="14" t="s">
-        <v>608</v>
-      </c>
-      <c r="O57" s="14" t="s">
-        <v>610</v>
-      </c>
-      <c r="P57" s="14" t="s">
-        <v>606</v>
+      <c r="N57" s="13" t="s">
+        <v>607</v>
+      </c>
+      <c r="O57" s="13" t="s">
+        <v>607</v>
+      </c>
+      <c r="P57" s="13" t="s">
+        <v>607</v>
       </c>
       <c r="Q57" s="5" t="s">
-        <v>465</v>
-      </c>
-    </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.3">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="58" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="4" t="s">
         <v>114</v>
       </c>
@@ -5990,7 +6014,7 @@
         <v>58</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D58" s="5" t="s">
         <v>4</v>
@@ -6011,27 +6035,27 @@
       <c r="L58" s="5"/>
       <c r="M58" s="5"/>
       <c r="N58" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="O58" s="14" t="s">
         <v>610</v>
       </c>
-      <c r="O58" s="14" t="s">
-        <v>606</v>
-      </c>
       <c r="P58" s="14" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="Q58" s="5" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="59" spans="1:17" ht="67.5" x14ac:dyDescent="0.3">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="59" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A59" s="4" t="s">
         <v>114</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>248</v>
+        <v>58</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D59" s="5" t="s">
         <v>4</v>
@@ -6040,71 +6064,71 @@
         <v>314</v>
       </c>
       <c r="F59" s="5" t="s">
-        <v>6</v>
+        <v>318</v>
       </c>
       <c r="G59" s="5"/>
       <c r="H59" s="5"/>
       <c r="I59" s="5"/>
       <c r="J59" s="5"/>
       <c r="K59" s="5" t="s">
-        <v>370</v>
-      </c>
-      <c r="L59" s="5" t="s">
-        <v>697</v>
-      </c>
+        <v>371</v>
+      </c>
+      <c r="L59" s="5"/>
       <c r="M59" s="5"/>
       <c r="N59" s="14" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="O59" s="14" t="s">
-        <v>610</v>
+        <v>606</v>
       </c>
       <c r="P59" s="14" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="Q59" s="5" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.3">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="60" spans="1:17" ht="67.5" x14ac:dyDescent="0.3">
       <c r="A60" s="4" t="s">
         <v>114</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D60" s="5" t="s">
-        <v>112</v>
+        <v>4</v>
       </c>
       <c r="E60" s="5" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F60" s="5" t="s">
-        <v>364</v>
+        <v>6</v>
       </c>
       <c r="G60" s="5"/>
       <c r="H60" s="5"/>
       <c r="I60" s="5"/>
       <c r="J60" s="5"/>
       <c r="K60" s="5" t="s">
-        <v>368</v>
-      </c>
-      <c r="L60" s="5"/>
+        <v>370</v>
+      </c>
+      <c r="L60" s="5" t="s">
+        <v>697</v>
+      </c>
       <c r="M60" s="5"/>
       <c r="N60" s="14" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="O60" s="14" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="P60" s="14" t="s">
         <v>606</v>
       </c>
       <c r="Q60" s="5" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="61" spans="1:17" x14ac:dyDescent="0.3">
@@ -6112,10 +6136,10 @@
         <v>114</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>387</v>
+        <v>249</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D61" s="5" t="s">
         <v>112</v>
@@ -6123,31 +6147,29 @@
       <c r="E61" s="5" t="s">
         <v>315</v>
       </c>
-      <c r="F61" s="5"/>
-      <c r="G61" s="5" t="s">
-        <v>327</v>
-      </c>
+      <c r="F61" s="5" t="s">
+        <v>364</v>
+      </c>
+      <c r="G61" s="5"/>
       <c r="H61" s="5"/>
-      <c r="I61" s="5" t="s">
-        <v>401</v>
-      </c>
-      <c r="J61" s="5" t="s">
-        <v>401</v>
-      </c>
-      <c r="K61" s="5"/>
+      <c r="I61" s="5"/>
+      <c r="J61" s="5"/>
+      <c r="K61" s="5" t="s">
+        <v>368</v>
+      </c>
       <c r="L61" s="5"/>
       <c r="M61" s="5"/>
       <c r="N61" s="14" t="s">
         <v>606</v>
       </c>
       <c r="O61" s="14" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="P61" s="14" t="s">
         <v>606</v>
       </c>
       <c r="Q61" s="5" t="s">
-        <v>467</v>
+        <v>458</v>
       </c>
     </row>
     <row r="62" spans="1:17" x14ac:dyDescent="0.3">
@@ -6155,10 +6177,10 @@
         <v>114</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>250</v>
+        <v>387</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D62" s="5" t="s">
         <v>112</v>
@@ -6168,29 +6190,29 @@
       </c>
       <c r="F62" s="5"/>
       <c r="G62" s="5" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H62" s="5"/>
       <c r="I62" s="5" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="J62" s="5" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="K62" s="5"/>
       <c r="L62" s="5"/>
       <c r="M62" s="5"/>
       <c r="N62" s="14" t="s">
+        <v>606</v>
+      </c>
+      <c r="O62" s="14" t="s">
         <v>610</v>
       </c>
-      <c r="O62" s="14" t="s">
-        <v>609</v>
-      </c>
       <c r="P62" s="14" t="s">
         <v>606</v>
       </c>
       <c r="Q62" s="5" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="63" spans="1:17" x14ac:dyDescent="0.3">
@@ -6198,40 +6220,42 @@
         <v>114</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>60</v>
+        <v>250</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D63" s="5" t="s">
-        <v>4</v>
+        <v>112</v>
       </c>
       <c r="E63" s="5" t="s">
-        <v>314</v>
-      </c>
-      <c r="F63" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="G63" s="5"/>
+        <v>315</v>
+      </c>
+      <c r="F63" s="5"/>
+      <c r="G63" s="5" t="s">
+        <v>328</v>
+      </c>
       <c r="H63" s="5"/>
-      <c r="I63" s="5"/>
-      <c r="J63" s="5"/>
-      <c r="K63" s="5" t="s">
-        <v>370</v>
-      </c>
+      <c r="I63" s="5" t="s">
+        <v>402</v>
+      </c>
+      <c r="J63" s="5" t="s">
+        <v>403</v>
+      </c>
+      <c r="K63" s="5"/>
       <c r="L63" s="5"/>
       <c r="M63" s="5"/>
       <c r="N63" s="14" t="s">
-        <v>606</v>
+        <v>610</v>
       </c>
       <c r="O63" s="14" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="P63" s="14" t="s">
-        <v>610</v>
+        <v>606</v>
       </c>
       <c r="Q63" s="5" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
     </row>
     <row r="64" spans="1:17" x14ac:dyDescent="0.3">
@@ -6239,51 +6263,51 @@
         <v>114</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>388</v>
+        <v>60</v>
       </c>
       <c r="C64" s="5" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D64" s="5" t="s">
-        <v>112</v>
+        <v>4</v>
       </c>
       <c r="E64" s="5" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F64" s="5" t="s">
-        <v>364</v>
+        <v>6</v>
       </c>
       <c r="G64" s="5"/>
       <c r="H64" s="5"/>
       <c r="I64" s="5"/>
       <c r="J64" s="5"/>
       <c r="K64" s="5" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="L64" s="5"/>
       <c r="M64" s="5"/>
       <c r="N64" s="14" t="s">
+        <v>606</v>
+      </c>
+      <c r="O64" s="14" t="s">
         <v>610</v>
       </c>
-      <c r="O64" s="14" t="s">
-        <v>606</v>
-      </c>
       <c r="P64" s="14" t="s">
-        <v>606</v>
+        <v>610</v>
       </c>
       <c r="Q64" s="5" t="s">
-        <v>460</v>
+        <v>469</v>
       </c>
     </row>
     <row r="65" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A65" s="4" t="s">
-        <v>3</v>
+        <v>114</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>61</v>
+        <v>388</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D65" s="5" t="s">
         <v>112</v>
@@ -6304,27 +6328,27 @@
       <c r="L65" s="5"/>
       <c r="M65" s="5"/>
       <c r="N65" s="14" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="O65" s="14" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="P65" s="14" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="Q65" s="5" t="s">
-        <v>477</v>
-      </c>
-    </row>
-    <row r="66" spans="1:17" ht="162" x14ac:dyDescent="0.3">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="66" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A66" s="4" t="s">
         <v>3</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>251</v>
+        <v>61</v>
       </c>
       <c r="C66" s="5" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D66" s="5" t="s">
         <v>112</v>
@@ -6343,50 +6367,50 @@
         <v>368</v>
       </c>
       <c r="L66" s="5"/>
-      <c r="M66" s="10" t="s">
-        <v>579</v>
-      </c>
+      <c r="M66" s="5"/>
       <c r="N66" s="14" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="O66" s="14" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="P66" s="14" t="s">
         <v>609</v>
       </c>
       <c r="Q66" s="5" t="s">
-        <v>474</v>
-      </c>
-    </row>
-    <row r="67" spans="1:17" x14ac:dyDescent="0.3">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="67" spans="1:17" ht="162" x14ac:dyDescent="0.3">
       <c r="A67" s="4" t="s">
         <v>3</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>63</v>
+        <v>251</v>
       </c>
       <c r="C67" s="5" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D67" s="5" t="s">
-        <v>4</v>
+        <v>112</v>
       </c>
       <c r="E67" s="5" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="F67" s="5" t="s">
-        <v>6</v>
+        <v>364</v>
       </c>
       <c r="G67" s="5"/>
       <c r="H67" s="5"/>
       <c r="I67" s="5"/>
       <c r="J67" s="5"/>
       <c r="K67" s="5" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="L67" s="5"/>
-      <c r="M67" s="5"/>
+      <c r="M67" s="10" t="s">
+        <v>579</v>
+      </c>
       <c r="N67" s="14" t="s">
         <v>606</v>
       </c>
@@ -6397,7 +6421,7 @@
         <v>609</v>
       </c>
       <c r="Q67" s="5" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
     </row>
     <row r="68" spans="1:17" x14ac:dyDescent="0.3">
@@ -6405,26 +6429,26 @@
         <v>3</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>252</v>
+        <v>63</v>
       </c>
       <c r="C68" s="5" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D68" s="5" t="s">
-        <v>112</v>
+        <v>4</v>
       </c>
       <c r="E68" s="5" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F68" s="5" t="s">
-        <v>364</v>
+        <v>6</v>
       </c>
       <c r="G68" s="5"/>
       <c r="H68" s="5"/>
       <c r="I68" s="5"/>
       <c r="J68" s="5"/>
       <c r="K68" s="5" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="L68" s="5"/>
       <c r="M68" s="5"/>
@@ -6438,7 +6462,7 @@
         <v>609</v>
       </c>
       <c r="Q68" s="5" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
     </row>
     <row r="69" spans="1:17" x14ac:dyDescent="0.3">
@@ -6446,10 +6470,10 @@
         <v>3</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>64</v>
+        <v>252</v>
       </c>
       <c r="C69" s="5" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D69" s="5" t="s">
         <v>112</v>
@@ -6476,21 +6500,21 @@
         <v>606</v>
       </c>
       <c r="P69" s="14" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="Q69" s="5" t="s">
-        <v>481</v>
-      </c>
-    </row>
-    <row r="70" spans="1:17" ht="162" x14ac:dyDescent="0.3">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="70" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A70" s="4" t="s">
         <v>3</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C70" s="5" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D70" s="5" t="s">
         <v>112</v>
@@ -6499,7 +6523,7 @@
         <v>315</v>
       </c>
       <c r="F70" s="5" t="s">
-        <v>389</v>
+        <v>364</v>
       </c>
       <c r="G70" s="5"/>
       <c r="H70" s="5"/>
@@ -6508,26 +6532,22 @@
       <c r="K70" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="L70" s="5" t="s">
-        <v>730</v>
-      </c>
-      <c r="M70" s="10" t="s">
-        <v>580</v>
-      </c>
+      <c r="L70" s="5"/>
+      <c r="M70" s="5"/>
       <c r="N70" s="14" t="s">
         <v>606</v>
       </c>
       <c r="O70" s="14" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="P70" s="14" t="s">
         <v>606</v>
       </c>
       <c r="Q70" s="5" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="71" spans="1:17" x14ac:dyDescent="0.3">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="71" spans="1:17" ht="162" x14ac:dyDescent="0.3">
       <c r="A71" s="4" t="s">
         <v>3</v>
       </c>
@@ -6535,7 +6555,7 @@
         <v>65</v>
       </c>
       <c r="C71" s="5" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D71" s="5" t="s">
         <v>112</v>
@@ -6553,46 +6573,50 @@
       <c r="K71" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="L71" s="5"/>
-      <c r="M71" s="5"/>
+      <c r="L71" s="5" t="s">
+        <v>730</v>
+      </c>
+      <c r="M71" s="10" t="s">
+        <v>580</v>
+      </c>
       <c r="N71" s="14" t="s">
         <v>606</v>
       </c>
       <c r="O71" s="14" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="P71" s="14" t="s">
         <v>606</v>
       </c>
       <c r="Q71" s="5" t="s">
-        <v>482</v>
-      </c>
-    </row>
-    <row r="72" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="72" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A72" s="4" t="s">
         <v>3</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C72" s="5" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D72" s="5" t="s">
-        <v>4</v>
+        <v>112</v>
       </c>
       <c r="E72" s="5" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="F72" s="5" t="s">
-        <v>6</v>
+        <v>389</v>
       </c>
       <c r="G72" s="5"/>
       <c r="H72" s="5"/>
       <c r="I72" s="5"/>
       <c r="J72" s="5"/>
       <c r="K72" s="5" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="L72" s="5"/>
       <c r="M72" s="5"/>
@@ -6606,34 +6630,34 @@
         <v>606</v>
       </c>
       <c r="Q72" s="5" t="s">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="73" spans="1:17" x14ac:dyDescent="0.3">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="73" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="4" t="s">
         <v>3</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C73" s="5" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D73" s="5" t="s">
-        <v>112</v>
+        <v>4</v>
       </c>
       <c r="E73" s="5" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F73" s="5" t="s">
-        <v>364</v>
+        <v>6</v>
       </c>
       <c r="G73" s="5"/>
       <c r="H73" s="5"/>
       <c r="I73" s="5"/>
       <c r="J73" s="5"/>
       <c r="K73" s="5" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="L73" s="5"/>
       <c r="M73" s="5"/>
@@ -6644,10 +6668,10 @@
         <v>606</v>
       </c>
       <c r="P73" s="14" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="Q73" s="5" t="s">
-        <v>472</v>
+        <v>479</v>
       </c>
     </row>
     <row r="74" spans="1:17" x14ac:dyDescent="0.3">
@@ -6658,7 +6682,7 @@
         <v>68</v>
       </c>
       <c r="C74" s="5" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D74" s="5" t="s">
         <v>112</v>
@@ -6688,7 +6712,7 @@
         <v>609</v>
       </c>
       <c r="Q74" s="5" t="s">
-        <v>478</v>
+        <v>472</v>
       </c>
     </row>
     <row r="75" spans="1:17" x14ac:dyDescent="0.3">
@@ -6699,23 +6723,23 @@
         <v>68</v>
       </c>
       <c r="C75" s="5" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D75" s="5" t="s">
-        <v>4</v>
+        <v>112</v>
       </c>
       <c r="E75" s="5" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="F75" s="5" t="s">
-        <v>390</v>
+        <v>364</v>
       </c>
       <c r="G75" s="5"/>
       <c r="H75" s="5"/>
       <c r="I75" s="5"/>
       <c r="J75" s="5"/>
       <c r="K75" s="5" t="s">
-        <v>384</v>
+        <v>368</v>
       </c>
       <c r="L75" s="5"/>
       <c r="M75" s="5"/>
@@ -6729,7 +6753,7 @@
         <v>609</v>
       </c>
       <c r="Q75" s="5" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
     </row>
     <row r="76" spans="1:17" x14ac:dyDescent="0.3">
@@ -6737,26 +6761,26 @@
         <v>3</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>253</v>
+        <v>68</v>
       </c>
       <c r="C76" s="5" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D76" s="5" t="s">
-        <v>112</v>
+        <v>4</v>
       </c>
       <c r="E76" s="5" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F76" s="5" t="s">
-        <v>364</v>
+        <v>390</v>
       </c>
       <c r="G76" s="5"/>
       <c r="H76" s="5"/>
       <c r="I76" s="5"/>
       <c r="J76" s="5"/>
       <c r="K76" s="5" t="s">
-        <v>368</v>
+        <v>384</v>
       </c>
       <c r="L76" s="5"/>
       <c r="M76" s="5"/>
@@ -6767,10 +6791,10 @@
         <v>606</v>
       </c>
       <c r="P76" s="14" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="Q76" s="5" t="s">
-        <v>613</v>
+        <v>480</v>
       </c>
     </row>
     <row r="77" spans="1:17" x14ac:dyDescent="0.3">
@@ -6778,26 +6802,26 @@
         <v>3</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>69</v>
+        <v>253</v>
       </c>
       <c r="C77" s="5" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D77" s="5" t="s">
-        <v>4</v>
+        <v>112</v>
       </c>
       <c r="E77" s="5" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="F77" s="5" t="s">
-        <v>6</v>
+        <v>364</v>
       </c>
       <c r="G77" s="5"/>
       <c r="H77" s="5"/>
       <c r="I77" s="5"/>
       <c r="J77" s="5"/>
       <c r="K77" s="5" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="L77" s="5"/>
       <c r="M77" s="5"/>
@@ -6805,13 +6829,13 @@
         <v>606</v>
       </c>
       <c r="O77" s="14" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="P77" s="14" t="s">
-        <v>610</v>
+        <v>606</v>
       </c>
       <c r="Q77" s="5" t="s">
-        <v>483</v>
+        <v>613</v>
       </c>
     </row>
     <row r="78" spans="1:17" x14ac:dyDescent="0.3">
@@ -6819,10 +6843,10 @@
         <v>3</v>
       </c>
       <c r="B78" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C78" s="5" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D78" s="5" t="s">
         <v>4</v>
@@ -6846,45 +6870,43 @@
         <v>606</v>
       </c>
       <c r="O78" s="14" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="P78" s="14" t="s">
-        <v>606</v>
+        <v>610</v>
       </c>
       <c r="Q78" s="5" t="s">
-        <v>471</v>
-      </c>
-    </row>
-    <row r="79" spans="1:17" ht="94.5" x14ac:dyDescent="0.3">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="79" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A79" s="4" t="s">
-        <v>101</v>
+        <v>3</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>254</v>
+        <v>70</v>
       </c>
       <c r="C79" s="5" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D79" s="5" t="s">
-        <v>112</v>
+        <v>4</v>
       </c>
       <c r="E79" s="5" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F79" s="5" t="s">
-        <v>391</v>
+        <v>6</v>
       </c>
       <c r="G79" s="5"/>
       <c r="H79" s="5"/>
       <c r="I79" s="5"/>
       <c r="J79" s="5"/>
       <c r="K79" s="5" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="L79" s="5"/>
-      <c r="M79" s="10" t="s">
-        <v>586</v>
-      </c>
+      <c r="M79" s="5"/>
       <c r="N79" s="14" t="s">
         <v>606</v>
       </c>
@@ -6895,10 +6917,10 @@
         <v>606</v>
       </c>
       <c r="Q79" s="5" t="s">
-        <v>491</v>
-      </c>
-    </row>
-    <row r="80" spans="1:17" ht="54" x14ac:dyDescent="0.3">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="80" spans="1:17" ht="94.5" x14ac:dyDescent="0.3">
       <c r="A80" s="4" t="s">
         <v>101</v>
       </c>
@@ -6906,52 +6928,52 @@
         <v>254</v>
       </c>
       <c r="C80" s="5" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D80" s="5" t="s">
-        <v>4</v>
+        <v>112</v>
       </c>
       <c r="E80" s="5" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="F80" s="5" t="s">
-        <v>6</v>
+        <v>391</v>
       </c>
       <c r="G80" s="5"/>
       <c r="H80" s="5"/>
       <c r="I80" s="5"/>
       <c r="J80" s="5"/>
       <c r="K80" s="5" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="L80" s="5" t="s">
-        <v>699</v>
-      </c>
-      <c r="M80" s="5" t="s">
-        <v>720</v>
+        <v>731</v>
+      </c>
+      <c r="M80" s="10" t="s">
+        <v>586</v>
       </c>
       <c r="N80" s="14" t="s">
         <v>606</v>
       </c>
       <c r="O80" s="14" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="P80" s="14" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="Q80" s="5" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="81" spans="1:17" ht="27" x14ac:dyDescent="0.3">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="81" spans="1:17" ht="54" x14ac:dyDescent="0.3">
       <c r="A81" s="4" t="s">
         <v>101</v>
       </c>
       <c r="B81" s="5" t="s">
-        <v>73</v>
+        <v>254</v>
       </c>
       <c r="C81" s="5" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D81" s="5" t="s">
         <v>4</v>
@@ -6969,24 +6991,26 @@
       <c r="K81" s="5" t="s">
         <v>372</v>
       </c>
-      <c r="L81" s="5"/>
+      <c r="L81" s="5" t="s">
+        <v>699</v>
+      </c>
       <c r="M81" s="5" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="N81" s="14" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="O81" s="14" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="P81" s="14" t="s">
         <v>609</v>
       </c>
       <c r="Q81" s="5" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="82" spans="1:17" x14ac:dyDescent="0.3">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="82" spans="1:17" ht="27" x14ac:dyDescent="0.3">
       <c r="A82" s="4" t="s">
         <v>101</v>
       </c>
@@ -6994,7 +7018,7 @@
         <v>73</v>
       </c>
       <c r="C82" s="5" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D82" s="5" t="s">
         <v>4</v>
@@ -7013,18 +7037,20 @@
         <v>372</v>
       </c>
       <c r="L82" s="5"/>
-      <c r="M82" s="5"/>
+      <c r="M82" s="5" t="s">
+        <v>719</v>
+      </c>
       <c r="N82" s="14" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="O82" s="14" t="s">
-        <v>606</v>
+        <v>610</v>
       </c>
       <c r="P82" s="14" t="s">
         <v>609</v>
       </c>
       <c r="Q82" s="5" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
     </row>
     <row r="83" spans="1:17" x14ac:dyDescent="0.3">
@@ -7032,26 +7058,26 @@
         <v>101</v>
       </c>
       <c r="B83" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C83" s="5" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D83" s="5" t="s">
-        <v>112</v>
+        <v>4</v>
       </c>
       <c r="E83" s="5" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F83" s="5" t="s">
-        <v>364</v>
+        <v>6</v>
       </c>
       <c r="G83" s="5"/>
       <c r="H83" s="5"/>
       <c r="I83" s="5"/>
       <c r="J83" s="5"/>
       <c r="K83" s="5" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="L83" s="5"/>
       <c r="M83" s="5"/>
@@ -7059,16 +7085,16 @@
         <v>606</v>
       </c>
       <c r="O83" s="14" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="P83" s="14" t="s">
         <v>609</v>
       </c>
       <c r="Q83" s="5" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="84" spans="1:17" ht="40.5" x14ac:dyDescent="0.3">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="84" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A84" s="4" t="s">
         <v>101</v>
       </c>
@@ -7076,7 +7102,7 @@
         <v>74</v>
       </c>
       <c r="C84" s="5" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D84" s="5" t="s">
         <v>112</v>
@@ -7095,31 +7121,29 @@
         <v>368</v>
       </c>
       <c r="L84" s="5"/>
-      <c r="M84" s="10" t="s">
-        <v>585</v>
-      </c>
+      <c r="M84" s="5"/>
       <c r="N84" s="14" t="s">
         <v>606</v>
       </c>
       <c r="O84" s="14" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="P84" s="14" t="s">
         <v>609</v>
       </c>
       <c r="Q84" s="5" t="s">
-        <v>499</v>
-      </c>
-    </row>
-    <row r="85" spans="1:17" x14ac:dyDescent="0.3">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="85" spans="1:17" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A85" s="4" t="s">
         <v>101</v>
       </c>
       <c r="B85" s="5" t="s">
-        <v>255</v>
+        <v>74</v>
       </c>
       <c r="C85" s="5" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D85" s="5" t="s">
         <v>112</v>
@@ -7138,18 +7162,20 @@
         <v>368</v>
       </c>
       <c r="L85" s="5"/>
-      <c r="M85" s="5"/>
+      <c r="M85" s="10" t="s">
+        <v>585</v>
+      </c>
       <c r="N85" s="14" t="s">
         <v>606</v>
       </c>
       <c r="O85" s="14" t="s">
-        <v>610</v>
+        <v>606</v>
       </c>
       <c r="P85" s="14" t="s">
         <v>609</v>
       </c>
       <c r="Q85" s="5" t="s">
-        <v>486</v>
+        <v>499</v>
       </c>
     </row>
     <row r="86" spans="1:17" x14ac:dyDescent="0.3">
@@ -7157,42 +7183,40 @@
         <v>101</v>
       </c>
       <c r="B86" s="5" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C86" s="5" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D86" s="5" t="s">
-        <v>4</v>
+        <v>112</v>
       </c>
       <c r="E86" s="5" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="F86" s="5" t="s">
-        <v>6</v>
+        <v>364</v>
       </c>
       <c r="G86" s="5"/>
       <c r="H86" s="5"/>
       <c r="I86" s="5"/>
       <c r="J86" s="5"/>
       <c r="K86" s="5" t="s">
-        <v>372</v>
-      </c>
-      <c r="L86" s="5" t="s">
-        <v>698</v>
-      </c>
+        <v>368</v>
+      </c>
+      <c r="L86" s="5"/>
       <c r="M86" s="5"/>
       <c r="N86" s="14" t="s">
         <v>606</v>
       </c>
       <c r="O86" s="14" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="P86" s="14" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="Q86" s="5" t="s">
-        <v>692</v>
+        <v>486</v>
       </c>
     </row>
     <row r="87" spans="1:17" x14ac:dyDescent="0.3">
@@ -7200,40 +7224,42 @@
         <v>101</v>
       </c>
       <c r="B87" s="5" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C87" s="5" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D87" s="5" t="s">
-        <v>112</v>
+        <v>4</v>
       </c>
       <c r="E87" s="5" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F87" s="5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G87" s="5"/>
       <c r="H87" s="5"/>
       <c r="I87" s="5"/>
       <c r="J87" s="5"/>
       <c r="K87" s="5" t="s">
-        <v>374</v>
-      </c>
-      <c r="L87" s="5"/>
+        <v>372</v>
+      </c>
+      <c r="L87" s="5" t="s">
+        <v>698</v>
+      </c>
       <c r="M87" s="5"/>
       <c r="N87" s="14" t="s">
         <v>606</v>
       </c>
       <c r="O87" s="14" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="P87" s="14" t="s">
         <v>606</v>
       </c>
       <c r="Q87" s="5" t="s">
-        <v>488</v>
+        <v>692</v>
       </c>
     </row>
     <row r="88" spans="1:17" x14ac:dyDescent="0.3">
@@ -7244,7 +7270,7 @@
         <v>257</v>
       </c>
       <c r="C88" s="5" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D88" s="5" t="s">
         <v>112</v>
@@ -7253,7 +7279,7 @@
         <v>315</v>
       </c>
       <c r="F88" s="5" t="s">
-        <v>325</v>
+        <v>10</v>
       </c>
       <c r="G88" s="5"/>
       <c r="H88" s="5"/>
@@ -7274,7 +7300,7 @@
         <v>606</v>
       </c>
       <c r="Q88" s="5" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
     </row>
     <row r="89" spans="1:17" x14ac:dyDescent="0.3">
@@ -7282,26 +7308,26 @@
         <v>101</v>
       </c>
       <c r="B89" s="5" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C89" s="5" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D89" s="5" t="s">
-        <v>4</v>
+        <v>112</v>
       </c>
       <c r="E89" s="5" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="F89" s="5" t="s">
-        <v>6</v>
+        <v>325</v>
       </c>
       <c r="G89" s="5"/>
       <c r="H89" s="5"/>
       <c r="I89" s="5"/>
       <c r="J89" s="5"/>
       <c r="K89" s="5" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="L89" s="5"/>
       <c r="M89" s="5"/>
@@ -7315,7 +7341,7 @@
         <v>606</v>
       </c>
       <c r="Q89" s="5" t="s">
-        <v>487</v>
+        <v>495</v>
       </c>
     </row>
     <row r="90" spans="1:17" x14ac:dyDescent="0.3">
@@ -7326,7 +7352,7 @@
         <v>258</v>
       </c>
       <c r="C90" s="5" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D90" s="5" t="s">
         <v>4</v>
@@ -7342,7 +7368,7 @@
       <c r="I90" s="5"/>
       <c r="J90" s="5"/>
       <c r="K90" s="5" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="L90" s="5"/>
       <c r="M90" s="5"/>
@@ -7350,24 +7376,24 @@
         <v>606</v>
       </c>
       <c r="O90" s="14" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="P90" s="14" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="Q90" s="5" t="s">
-        <v>496</v>
-      </c>
-    </row>
-    <row r="91" spans="1:17" ht="108" x14ac:dyDescent="0.3">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="91" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A91" s="4" t="s">
         <v>101</v>
       </c>
       <c r="B91" s="5" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C91" s="5" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D91" s="5" t="s">
         <v>4</v>
@@ -7385,55 +7411,53 @@
       <c r="K91" s="5" t="s">
         <v>372</v>
       </c>
-      <c r="L91" s="5" t="s">
-        <v>700</v>
-      </c>
+      <c r="L91" s="5"/>
       <c r="M91" s="5"/>
       <c r="N91" s="14" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="O91" s="14" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="P91" s="14" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="Q91" s="5" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="92" spans="1:17" ht="40.5" x14ac:dyDescent="0.3">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="92" spans="1:17" ht="108" x14ac:dyDescent="0.3">
       <c r="A92" s="4" t="s">
         <v>101</v>
       </c>
       <c r="B92" s="5" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C92" s="5" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D92" s="5" t="s">
-        <v>112</v>
+        <v>4</v>
       </c>
       <c r="E92" s="5" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F92" s="5" t="s">
-        <v>373</v>
+        <v>6</v>
       </c>
       <c r="G92" s="5"/>
       <c r="H92" s="5"/>
       <c r="I92" s="5"/>
       <c r="J92" s="5"/>
       <c r="K92" s="5" t="s">
-        <v>375</v>
-      </c>
-      <c r="L92" s="5"/>
-      <c r="M92" s="10" t="s">
-        <v>584</v>
-      </c>
+        <v>372</v>
+      </c>
+      <c r="L92" s="5" t="s">
+        <v>700</v>
+      </c>
+      <c r="M92" s="5"/>
       <c r="N92" s="14" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="O92" s="14" t="s">
         <v>606</v>
@@ -7442,18 +7466,18 @@
         <v>606</v>
       </c>
       <c r="Q92" s="5" t="s">
-        <v>490</v>
-      </c>
-    </row>
-    <row r="93" spans="1:17" x14ac:dyDescent="0.3">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="93" spans="1:17" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A93" s="4" t="s">
         <v>101</v>
       </c>
       <c r="B93" s="5" t="s">
-        <v>392</v>
+        <v>260</v>
       </c>
       <c r="C93" s="5" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D93" s="5" t="s">
         <v>112</v>
@@ -7461,26 +7485,20 @@
       <c r="E93" s="5" t="s">
         <v>315</v>
       </c>
-      <c r="F93" s="6" t="s">
-        <v>358</v>
-      </c>
-      <c r="G93" s="6" t="s">
-        <v>326</v>
-      </c>
-      <c r="H93" s="6" t="s">
-        <v>404</v>
-      </c>
-      <c r="I93" s="6" t="s">
-        <v>358</v>
-      </c>
-      <c r="J93" s="6" t="s">
-        <v>358</v>
-      </c>
-      <c r="K93" s="6" t="s">
-        <v>367</v>
-      </c>
-      <c r="L93" s="2"/>
-      <c r="M93" s="2"/>
+      <c r="F93" s="5" t="s">
+        <v>373</v>
+      </c>
+      <c r="G93" s="5"/>
+      <c r="H93" s="5"/>
+      <c r="I93" s="5"/>
+      <c r="J93" s="5"/>
+      <c r="K93" s="5" t="s">
+        <v>375</v>
+      </c>
+      <c r="L93" s="5"/>
+      <c r="M93" s="10" t="s">
+        <v>584</v>
+      </c>
       <c r="N93" s="14" t="s">
         <v>606</v>
       </c>
@@ -7490,25 +7508,25 @@
       <c r="P93" s="14" t="s">
         <v>606</v>
       </c>
-      <c r="Q93" s="6" t="s">
-        <v>497</v>
+      <c r="Q93" s="5" t="s">
+        <v>490</v>
       </c>
     </row>
     <row r="94" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A94" s="4" t="s">
-        <v>721</v>
+        <v>101</v>
       </c>
       <c r="B94" s="5" t="s">
-        <v>722</v>
+        <v>392</v>
       </c>
       <c r="C94" s="5" t="s">
-        <v>723</v>
+        <v>163</v>
       </c>
       <c r="D94" s="5" t="s">
-        <v>724</v>
+        <v>112</v>
       </c>
       <c r="E94" s="5" t="s">
-        <v>725</v>
+        <v>315</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>358</v>
@@ -7526,65 +7544,69 @@
         <v>358</v>
       </c>
       <c r="K94" s="6" t="s">
+        <v>367</v>
+      </c>
+      <c r="L94" s="2"/>
+      <c r="M94" s="2"/>
+      <c r="N94" s="14" t="s">
+        <v>606</v>
+      </c>
+      <c r="O94" s="14" t="s">
+        <v>606</v>
+      </c>
+      <c r="P94" s="14" t="s">
+        <v>606</v>
+      </c>
+      <c r="Q94" s="6" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="95" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A95" s="4" t="s">
+        <v>721</v>
+      </c>
+      <c r="B95" s="5" t="s">
+        <v>722</v>
+      </c>
+      <c r="C95" s="5" t="s">
+        <v>723</v>
+      </c>
+      <c r="D95" s="5" t="s">
+        <v>724</v>
+      </c>
+      <c r="E95" s="5" t="s">
+        <v>725</v>
+      </c>
+      <c r="F95" s="6" t="s">
+        <v>358</v>
+      </c>
+      <c r="G95" s="6" t="s">
+        <v>326</v>
+      </c>
+      <c r="H95" s="6" t="s">
+        <v>404</v>
+      </c>
+      <c r="I95" s="6" t="s">
+        <v>358</v>
+      </c>
+      <c r="J95" s="6" t="s">
+        <v>358</v>
+      </c>
+      <c r="K95" s="6" t="s">
         <v>726</v>
       </c>
-      <c r="L94" s="2" t="s">
+      <c r="L95" s="2" t="s">
         <v>728</v>
       </c>
-      <c r="M94" s="2"/>
-      <c r="N94" s="14"/>
-      <c r="O94" s="14"/>
-      <c r="P94" s="14"/>
-      <c r="Q94" s="6" t="s">
+      <c r="M95" s="2"/>
+      <c r="N95" s="14"/>
+      <c r="O95" s="14"/>
+      <c r="P95" s="14"/>
+      <c r="Q95" s="6" t="s">
         <v>727</v>
       </c>
     </row>
-    <row r="95" spans="1:17" ht="175.5" x14ac:dyDescent="0.3">
-      <c r="A95" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="B95" s="5" t="s">
-        <v>261</v>
-      </c>
-      <c r="C95" s="5" t="s">
-        <v>164</v>
-      </c>
-      <c r="D95" s="5" t="s">
-        <v>112</v>
-      </c>
-      <c r="E95" s="5" t="s">
-        <v>315</v>
-      </c>
-      <c r="F95" s="5" t="s">
-        <v>393</v>
-      </c>
-      <c r="G95" s="5"/>
-      <c r="H95" s="5"/>
-      <c r="I95" s="5"/>
-      <c r="J95" s="5"/>
-      <c r="K95" s="5" t="s">
-        <v>374</v>
-      </c>
-      <c r="L95" s="5" t="s">
-        <v>717</v>
-      </c>
-      <c r="M95" s="10" t="s">
-        <v>583</v>
-      </c>
-      <c r="N95" s="14" t="s">
-        <v>609</v>
-      </c>
-      <c r="O95" s="14" t="s">
-        <v>606</v>
-      </c>
-      <c r="P95" s="14" t="s">
-        <v>609</v>
-      </c>
-      <c r="Q95" s="5" t="s">
-        <v>484</v>
-      </c>
-    </row>
-    <row r="96" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:17" ht="175.5" x14ac:dyDescent="0.3">
       <c r="A96" s="4" t="s">
         <v>101</v>
       </c>
@@ -7592,7 +7614,7 @@
         <v>261</v>
       </c>
       <c r="C96" s="5" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D96" s="5" t="s">
         <v>112</v>
@@ -7610,19 +7632,23 @@
       <c r="K96" s="5" t="s">
         <v>374</v>
       </c>
-      <c r="L96" s="5"/>
-      <c r="M96" s="5"/>
+      <c r="L96" s="5" t="s">
+        <v>717</v>
+      </c>
+      <c r="M96" s="10" t="s">
+        <v>583</v>
+      </c>
       <c r="N96" s="14" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="O96" s="14" t="s">
         <v>606</v>
       </c>
       <c r="P96" s="14" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="Q96" s="5" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="97" spans="1:17" x14ac:dyDescent="0.3">
@@ -7633,7 +7659,7 @@
         <v>261</v>
       </c>
       <c r="C97" s="5" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D97" s="5" t="s">
         <v>112</v>
@@ -7663,79 +7689,79 @@
         <v>606</v>
       </c>
       <c r="Q97" s="5" t="s">
-        <v>489</v>
-      </c>
-    </row>
-    <row r="98" spans="1:17" ht="40.5" x14ac:dyDescent="0.3">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="98" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A98" s="4" t="s">
-        <v>115</v>
+        <v>101</v>
       </c>
       <c r="B98" s="5" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C98" s="5" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D98" s="5" t="s">
-        <v>4</v>
+        <v>112</v>
       </c>
       <c r="E98" s="5" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="F98" s="5" t="s">
-        <v>6</v>
+        <v>393</v>
       </c>
       <c r="G98" s="5"/>
       <c r="H98" s="5"/>
       <c r="I98" s="5"/>
       <c r="J98" s="5"/>
       <c r="K98" s="5" t="s">
-        <v>372</v>
-      </c>
-      <c r="L98" s="5" t="s">
-        <v>701</v>
-      </c>
+        <v>374</v>
+      </c>
+      <c r="L98" s="5"/>
       <c r="M98" s="5"/>
       <c r="N98" s="14" t="s">
         <v>606</v>
       </c>
       <c r="O98" s="14" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="P98" s="14" t="s">
         <v>606</v>
       </c>
       <c r="Q98" s="5" t="s">
-        <v>501</v>
-      </c>
-    </row>
-    <row r="99" spans="1:17" x14ac:dyDescent="0.3">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="99" spans="1:17" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A99" s="4" t="s">
         <v>115</v>
       </c>
       <c r="B99" s="5" t="s">
-        <v>75</v>
+        <v>262</v>
       </c>
       <c r="C99" s="5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D99" s="5" t="s">
-        <v>112</v>
+        <v>4</v>
       </c>
       <c r="E99" s="5" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F99" s="5" t="s">
-        <v>364</v>
+        <v>6</v>
       </c>
       <c r="G99" s="5"/>
       <c r="H99" s="5"/>
       <c r="I99" s="5"/>
       <c r="J99" s="5"/>
       <c r="K99" s="5" t="s">
-        <v>368</v>
-      </c>
-      <c r="L99" s="5"/>
+        <v>372</v>
+      </c>
+      <c r="L99" s="5" t="s">
+        <v>701</v>
+      </c>
       <c r="M99" s="5"/>
       <c r="N99" s="14" t="s">
         <v>606</v>
@@ -7747,7 +7773,7 @@
         <v>606</v>
       </c>
       <c r="Q99" s="5" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="100" spans="1:17" x14ac:dyDescent="0.3">
@@ -7755,26 +7781,26 @@
         <v>115</v>
       </c>
       <c r="B100" s="5" t="s">
-        <v>263</v>
+        <v>75</v>
       </c>
       <c r="C100" s="5" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D100" s="5" t="s">
-        <v>4</v>
+        <v>112</v>
       </c>
       <c r="E100" s="5" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="F100" s="5" t="s">
-        <v>318</v>
+        <v>364</v>
       </c>
       <c r="G100" s="5"/>
       <c r="H100" s="5"/>
       <c r="I100" s="5"/>
       <c r="J100" s="5"/>
       <c r="K100" s="5" t="s">
-        <v>379</v>
+        <v>368</v>
       </c>
       <c r="L100" s="5"/>
       <c r="M100" s="5"/>
@@ -7782,67 +7808,65 @@
         <v>606</v>
       </c>
       <c r="O100" s="14" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="P100" s="14" t="s">
         <v>606</v>
       </c>
-      <c r="Q100" s="22" t="s">
-        <v>690</v>
-      </c>
-    </row>
-    <row r="101" spans="1:17" ht="94.5" x14ac:dyDescent="0.3">
+      <c r="Q100" s="5" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="101" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A101" s="4" t="s">
         <v>115</v>
       </c>
       <c r="B101" s="5" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C101" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D101" s="5" t="s">
-        <v>112</v>
+        <v>4</v>
       </c>
       <c r="E101" s="5" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F101" s="5" t="s">
-        <v>364</v>
+        <v>318</v>
       </c>
       <c r="G101" s="5"/>
       <c r="H101" s="5"/>
       <c r="I101" s="5"/>
       <c r="J101" s="5"/>
       <c r="K101" s="5" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="L101" s="5"/>
-      <c r="M101" s="10" t="s">
-        <v>587</v>
-      </c>
+      <c r="M101" s="5"/>
       <c r="N101" s="14" t="s">
         <v>606</v>
       </c>
       <c r="O101" s="14" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="P101" s="14" t="s">
-        <v>609</v>
-      </c>
-      <c r="Q101" s="5" t="s">
-        <v>504</v>
-      </c>
-    </row>
-    <row r="102" spans="1:17" x14ac:dyDescent="0.3">
+        <v>606</v>
+      </c>
+      <c r="Q101" s="22" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="102" spans="1:17" ht="94.5" x14ac:dyDescent="0.3">
       <c r="A102" s="4" t="s">
         <v>115</v>
       </c>
       <c r="B102" s="5" t="s">
-        <v>76</v>
+        <v>264</v>
       </c>
       <c r="C102" s="5" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D102" s="5" t="s">
         <v>112</v>
@@ -7861,21 +7885,23 @@
         <v>368</v>
       </c>
       <c r="L102" s="5"/>
-      <c r="M102" s="5"/>
+      <c r="M102" s="10" t="s">
+        <v>587</v>
+      </c>
       <c r="N102" s="14" t="s">
         <v>606</v>
       </c>
       <c r="O102" s="14" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="P102" s="14" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="Q102" s="5" t="s">
-        <v>693</v>
-      </c>
-    </row>
-    <row r="103" spans="1:17" ht="95.25" x14ac:dyDescent="0.3">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="103" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A103" s="4" t="s">
         <v>115</v>
       </c>
@@ -7883,7 +7909,7 @@
         <v>76</v>
       </c>
       <c r="C103" s="5" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D103" s="5" t="s">
         <v>112</v>
@@ -7891,150 +7917,148 @@
       <c r="E103" s="5" t="s">
         <v>315</v>
       </c>
-      <c r="F103" s="5"/>
-      <c r="G103" s="6" t="s">
-        <v>322</v>
-      </c>
-      <c r="H103" s="6"/>
-      <c r="I103" s="6" t="s">
-        <v>358</v>
-      </c>
-      <c r="J103" s="6" t="s">
-        <v>405</v>
-      </c>
-      <c r="K103" s="6" t="s">
-        <v>367</v>
-      </c>
-      <c r="L103" s="2"/>
-      <c r="M103" s="12" t="s">
-        <v>588</v>
-      </c>
+      <c r="F103" s="5" t="s">
+        <v>364</v>
+      </c>
+      <c r="G103" s="5"/>
+      <c r="H103" s="5"/>
+      <c r="I103" s="5"/>
+      <c r="J103" s="5"/>
+      <c r="K103" s="5" t="s">
+        <v>368</v>
+      </c>
+      <c r="L103" s="5"/>
+      <c r="M103" s="5"/>
       <c r="N103" s="14" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="O103" s="14" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="P103" s="14" t="s">
-        <v>609</v>
-      </c>
-      <c r="Q103" s="6" t="s">
-        <v>509</v>
-      </c>
-    </row>
-    <row r="104" spans="1:17" ht="27" x14ac:dyDescent="0.3">
+        <v>606</v>
+      </c>
+      <c r="Q103" s="5" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="104" spans="1:17" ht="95.25" x14ac:dyDescent="0.3">
       <c r="A104" s="4" t="s">
         <v>115</v>
       </c>
       <c r="B104" s="5" t="s">
-        <v>265</v>
+        <v>76</v>
       </c>
       <c r="C104" s="5" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D104" s="5" t="s">
-        <v>4</v>
+        <v>112</v>
       </c>
       <c r="E104" s="5" t="s">
-        <v>314</v>
-      </c>
-      <c r="F104" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="G104" s="5"/>
-      <c r="H104" s="5"/>
-      <c r="I104" s="5"/>
-      <c r="J104" s="5"/>
-      <c r="K104" s="5" t="s">
-        <v>372</v>
-      </c>
-      <c r="L104" s="5" t="s">
-        <v>702</v>
-      </c>
-      <c r="M104" s="5"/>
+        <v>315</v>
+      </c>
+      <c r="F104" s="5"/>
+      <c r="G104" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="H104" s="6"/>
+      <c r="I104" s="6" t="s">
+        <v>358</v>
+      </c>
+      <c r="J104" s="6" t="s">
+        <v>405</v>
+      </c>
+      <c r="K104" s="6" t="s">
+        <v>367</v>
+      </c>
+      <c r="L104" s="2"/>
+      <c r="M104" s="12" t="s">
+        <v>588</v>
+      </c>
       <c r="N104" s="14" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="O104" s="14" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="P104" s="14" t="s">
-        <v>606</v>
-      </c>
-      <c r="Q104" s="5" t="s">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="105" spans="1:17" x14ac:dyDescent="0.3">
+        <v>609</v>
+      </c>
+      <c r="Q104" s="6" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="105" spans="1:17" ht="27" x14ac:dyDescent="0.3">
       <c r="A105" s="4" t="s">
         <v>115</v>
       </c>
       <c r="B105" s="5" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C105" s="5" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D105" s="5" t="s">
-        <v>112</v>
+        <v>4</v>
       </c>
       <c r="E105" s="5" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F105" s="5" t="s">
-        <v>364</v>
+        <v>6</v>
       </c>
       <c r="G105" s="5"/>
       <c r="H105" s="5"/>
       <c r="I105" s="5"/>
       <c r="J105" s="5"/>
       <c r="K105" s="5" t="s">
-        <v>368</v>
-      </c>
-      <c r="L105" s="5"/>
+        <v>372</v>
+      </c>
+      <c r="L105" s="5" t="s">
+        <v>702</v>
+      </c>
       <c r="M105" s="5"/>
       <c r="N105" s="14" t="s">
         <v>606</v>
       </c>
       <c r="O105" s="14" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="P105" s="14" t="s">
         <v>606</v>
       </c>
       <c r="Q105" s="5" t="s">
-        <v>510</v>
-      </c>
-    </row>
-    <row r="106" spans="1:17" ht="27" x14ac:dyDescent="0.3">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="106" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A106" s="4" t="s">
         <v>115</v>
       </c>
       <c r="B106" s="5" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C106" s="5" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D106" s="5" t="s">
-        <v>4</v>
+        <v>112</v>
       </c>
       <c r="E106" s="5" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="F106" s="5" t="s">
-        <v>6</v>
+        <v>364</v>
       </c>
       <c r="G106" s="5"/>
       <c r="H106" s="5"/>
       <c r="I106" s="5"/>
       <c r="J106" s="5"/>
       <c r="K106" s="5" t="s">
-        <v>372</v>
-      </c>
-      <c r="L106" s="5" t="s">
-        <v>703</v>
-      </c>
+        <v>368</v>
+      </c>
+      <c r="L106" s="5"/>
       <c r="M106" s="5"/>
       <c r="N106" s="14" t="s">
         <v>606</v>
@@ -8046,92 +8070,84 @@
         <v>606</v>
       </c>
       <c r="Q106" s="5" t="s">
-        <v>507</v>
-      </c>
-    </row>
-    <row r="107" spans="1:17" ht="54" x14ac:dyDescent="0.3">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="107" spans="1:17" ht="27" x14ac:dyDescent="0.3">
       <c r="A107" s="4" t="s">
         <v>115</v>
       </c>
       <c r="B107" s="5" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C107" s="5" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D107" s="5" t="s">
-        <v>112</v>
+        <v>4</v>
       </c>
       <c r="E107" s="5" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F107" s="5" t="s">
-        <v>364</v>
+        <v>6</v>
       </c>
       <c r="G107" s="5"/>
       <c r="H107" s="5"/>
       <c r="I107" s="5"/>
       <c r="J107" s="5"/>
       <c r="K107" s="5" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="L107" s="5" t="s">
-        <v>714</v>
-      </c>
-      <c r="M107" s="10" t="s">
-        <v>713</v>
-      </c>
+        <v>703</v>
+      </c>
+      <c r="M107" s="5"/>
       <c r="N107" s="14" t="s">
         <v>606</v>
       </c>
       <c r="O107" s="14" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="P107" s="14" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="Q107" s="5" t="s">
-        <v>505</v>
-      </c>
-    </row>
-    <row r="108" spans="1:17" ht="81" x14ac:dyDescent="0.3">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="108" spans="1:17" ht="54" x14ac:dyDescent="0.3">
       <c r="A108" s="4" t="s">
         <v>115</v>
       </c>
       <c r="B108" s="5" t="s">
-        <v>394</v>
+        <v>268</v>
       </c>
       <c r="C108" s="5" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D108" s="5" t="s">
-        <v>4</v>
+        <v>112</v>
       </c>
       <c r="E108" s="5" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="F108" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="G108" s="5" t="s">
-        <v>406</v>
-      </c>
-      <c r="H108" s="5" t="s">
-        <v>323</v>
-      </c>
-      <c r="I108" s="5" t="s">
-        <v>716</v>
-      </c>
-      <c r="J108" s="5" t="s">
-        <v>407</v>
-      </c>
+        <v>364</v>
+      </c>
+      <c r="G108" s="5"/>
+      <c r="H108" s="5"/>
+      <c r="I108" s="5"/>
+      <c r="J108" s="5"/>
       <c r="K108" s="5" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="L108" s="5" t="s">
-        <v>704</v>
-      </c>
-      <c r="M108" s="5"/>
+        <v>714</v>
+      </c>
+      <c r="M108" s="10" t="s">
+        <v>713</v>
+      </c>
       <c r="N108" s="14" t="s">
         <v>606</v>
       </c>
@@ -8139,21 +8155,21 @@
         <v>606</v>
       </c>
       <c r="P108" s="14" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="Q108" s="5" t="s">
-        <v>512</v>
-      </c>
-    </row>
-    <row r="109" spans="1:17" x14ac:dyDescent="0.3">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="109" spans="1:17" ht="81" x14ac:dyDescent="0.3">
       <c r="A109" s="4" t="s">
         <v>115</v>
       </c>
       <c r="B109" s="5" t="s">
-        <v>269</v>
+        <v>394</v>
       </c>
       <c r="C109" s="5" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D109" s="5" t="s">
         <v>4</v>
@@ -8164,26 +8180,36 @@
       <c r="F109" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="G109" s="5"/>
-      <c r="H109" s="5"/>
-      <c r="I109" s="5"/>
-      <c r="J109" s="5"/>
+      <c r="G109" s="5" t="s">
+        <v>406</v>
+      </c>
+      <c r="H109" s="5" t="s">
+        <v>323</v>
+      </c>
+      <c r="I109" s="5" t="s">
+        <v>716</v>
+      </c>
+      <c r="J109" s="5" t="s">
+        <v>407</v>
+      </c>
       <c r="K109" s="5" t="s">
         <v>372</v>
       </c>
-      <c r="L109" s="5"/>
+      <c r="L109" s="5" t="s">
+        <v>704</v>
+      </c>
       <c r="M109" s="5"/>
       <c r="N109" s="14" t="s">
         <v>606</v>
       </c>
       <c r="O109" s="14" t="s">
-        <v>610</v>
+        <v>606</v>
       </c>
       <c r="P109" s="14" t="s">
         <v>606</v>
       </c>
       <c r="Q109" s="5" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="110" spans="1:17" x14ac:dyDescent="0.3">
@@ -8191,42 +8217,40 @@
         <v>115</v>
       </c>
       <c r="B110" s="5" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C110" s="5" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D110" s="5" t="s">
-        <v>112</v>
+        <v>4</v>
       </c>
       <c r="E110" s="5" t="s">
-        <v>315</v>
-      </c>
-      <c r="F110" s="5"/>
-      <c r="G110" s="6" t="s">
-        <v>322</v>
-      </c>
-      <c r="H110" s="6"/>
-      <c r="I110" s="6" t="s">
-        <v>358</v>
-      </c>
-      <c r="J110" s="6" t="s">
-        <v>405</v>
-      </c>
-      <c r="K110" s="6"/>
-      <c r="L110" s="2"/>
-      <c r="M110" s="2"/>
+        <v>314</v>
+      </c>
+      <c r="F110" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="G110" s="5"/>
+      <c r="H110" s="5"/>
+      <c r="I110" s="5"/>
+      <c r="J110" s="5"/>
+      <c r="K110" s="5" t="s">
+        <v>372</v>
+      </c>
+      <c r="L110" s="5"/>
+      <c r="M110" s="5"/>
       <c r="N110" s="14" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="O110" s="14" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="P110" s="14" t="s">
-        <v>609</v>
-      </c>
-      <c r="Q110" s="6" t="s">
-        <v>506</v>
+        <v>606</v>
+      </c>
+      <c r="Q110" s="5" t="s">
+        <v>511</v>
       </c>
     </row>
     <row r="111" spans="1:17" x14ac:dyDescent="0.3">
@@ -8234,10 +8258,10 @@
         <v>115</v>
       </c>
       <c r="B111" s="5" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C111" s="5" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D111" s="5" t="s">
         <v>112</v>
@@ -8245,70 +8269,72 @@
       <c r="E111" s="5" t="s">
         <v>315</v>
       </c>
-      <c r="F111" s="5" t="s">
-        <v>364</v>
-      </c>
-      <c r="G111" s="5"/>
-      <c r="H111" s="5"/>
-      <c r="I111" s="5"/>
-      <c r="J111" s="5"/>
-      <c r="K111" s="5" t="s">
-        <v>368</v>
-      </c>
-      <c r="L111" s="5"/>
-      <c r="M111" s="5"/>
+      <c r="F111" s="5"/>
+      <c r="G111" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="H111" s="6"/>
+      <c r="I111" s="6" t="s">
+        <v>358</v>
+      </c>
+      <c r="J111" s="6" t="s">
+        <v>405</v>
+      </c>
+      <c r="K111" s="6"/>
+      <c r="L111" s="2"/>
+      <c r="M111" s="2"/>
       <c r="N111" s="14" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="O111" s="14" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="P111" s="14" t="s">
         <v>609</v>
       </c>
-      <c r="Q111" s="5" t="s">
-        <v>508</v>
+      <c r="Q111" s="6" t="s">
+        <v>506</v>
       </c>
     </row>
     <row r="112" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A112" s="4" t="s">
-        <v>102</v>
+        <v>115</v>
       </c>
       <c r="B112" s="5" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C112" s="5" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D112" s="5" t="s">
-        <v>4</v>
+        <v>112</v>
       </c>
       <c r="E112" s="5" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="F112" s="5" t="s">
-        <v>6</v>
+        <v>364</v>
       </c>
       <c r="G112" s="5"/>
       <c r="H112" s="5"/>
       <c r="I112" s="5"/>
       <c r="J112" s="5"/>
       <c r="K112" s="5" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="L112" s="5"/>
       <c r="M112" s="5"/>
       <c r="N112" s="14" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="O112" s="14" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="P112" s="14" t="s">
-        <v>606</v>
-      </c>
-      <c r="Q112" s="22" t="s">
-        <v>694</v>
+        <v>609</v>
+      </c>
+      <c r="Q112" s="5" t="s">
+        <v>508</v>
       </c>
     </row>
     <row r="113" spans="1:17" x14ac:dyDescent="0.3">
@@ -8316,94 +8342,92 @@
         <v>102</v>
       </c>
       <c r="B113" s="5" t="s">
-        <v>80</v>
+        <v>272</v>
       </c>
       <c r="C113" s="5" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D113" s="5" t="s">
-        <v>112</v>
+        <v>4</v>
       </c>
       <c r="E113" s="5" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F113" s="5" t="s">
-        <v>364</v>
+        <v>6</v>
       </c>
       <c r="G113" s="5"/>
       <c r="H113" s="5"/>
       <c r="I113" s="5"/>
       <c r="J113" s="5"/>
       <c r="K113" s="5" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="L113" s="5"/>
       <c r="M113" s="5"/>
       <c r="N113" s="14" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="O113" s="14" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="P113" s="14" t="s">
         <v>606</v>
       </c>
-      <c r="Q113" s="5" t="s">
-        <v>516</v>
-      </c>
-    </row>
-    <row r="114" spans="1:17" ht="27" x14ac:dyDescent="0.3">
+      <c r="Q113" s="22" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="114" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A114" s="4" t="s">
         <v>102</v>
       </c>
       <c r="B114" s="5" t="s">
-        <v>273</v>
+        <v>80</v>
       </c>
       <c r="C114" s="5" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D114" s="5" t="s">
-        <v>4</v>
+        <v>112</v>
       </c>
       <c r="E114" s="5" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="F114" s="5" t="s">
-        <v>321</v>
+        <v>364</v>
       </c>
       <c r="G114" s="5"/>
       <c r="H114" s="5"/>
       <c r="I114" s="5"/>
       <c r="J114" s="5"/>
       <c r="K114" s="5" t="s">
-        <v>381</v>
-      </c>
-      <c r="L114" s="5" t="s">
-        <v>688</v>
-      </c>
+        <v>368</v>
+      </c>
+      <c r="L114" s="5"/>
       <c r="M114" s="5"/>
       <c r="N114" s="14" t="s">
         <v>606</v>
       </c>
       <c r="O114" s="14" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="P114" s="14" t="s">
         <v>606</v>
       </c>
       <c r="Q114" s="5" t="s">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="115" spans="1:17" ht="40.5" x14ac:dyDescent="0.3">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="115" spans="1:17" ht="27" x14ac:dyDescent="0.3">
       <c r="A115" s="4" t="s">
         <v>102</v>
       </c>
       <c r="B115" s="5" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C115" s="5" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D115" s="5" t="s">
         <v>4</v>
@@ -8412,41 +8436,41 @@
         <v>314</v>
       </c>
       <c r="F115" s="5" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="G115" s="5"/>
       <c r="H115" s="5"/>
       <c r="I115" s="5"/>
       <c r="J115" s="5"/>
       <c r="K115" s="5" t="s">
-        <v>370</v>
+        <v>381</v>
       </c>
       <c r="L115" s="5" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="M115" s="5"/>
       <c r="N115" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="O115" s="14" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="P115" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="Q115" s="5" t="s">
-        <v>518</v>
-      </c>
-    </row>
-    <row r="116" spans="1:17" x14ac:dyDescent="0.3">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="116" spans="1:17" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A116" s="4" t="s">
         <v>102</v>
       </c>
       <c r="B116" s="5" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C116" s="5" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D116" s="5" t="s">
         <v>4</v>
@@ -8455,31 +8479,33 @@
         <v>314</v>
       </c>
       <c r="F116" s="5" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="G116" s="5"/>
       <c r="H116" s="5"/>
       <c r="I116" s="5"/>
       <c r="J116" s="5"/>
       <c r="K116" s="5" t="s">
-        <v>381</v>
-      </c>
-      <c r="L116" s="5"/>
+        <v>370</v>
+      </c>
+      <c r="L116" s="5" t="s">
+        <v>686</v>
+      </c>
       <c r="M116" s="5"/>
       <c r="N116" s="14" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="O116" s="14" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="P116" s="14" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="Q116" s="5" t="s">
-        <v>517</v>
-      </c>
-    </row>
-    <row r="117" spans="1:17" ht="94.5" x14ac:dyDescent="0.3">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="117" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A117" s="4" t="s">
         <v>102</v>
       </c>
@@ -8487,7 +8513,7 @@
         <v>275</v>
       </c>
       <c r="C117" s="5" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D117" s="5" t="s">
         <v>4</v>
@@ -8506,9 +8532,7 @@
         <v>381</v>
       </c>
       <c r="L117" s="5"/>
-      <c r="M117" s="10" t="s">
-        <v>592</v>
-      </c>
+      <c r="M117" s="5"/>
       <c r="N117" s="14" t="s">
         <v>606</v>
       </c>
@@ -8519,18 +8543,18 @@
         <v>606</v>
       </c>
       <c r="Q117" s="5" t="s">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="118" spans="1:17" x14ac:dyDescent="0.3">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="118" spans="1:17" ht="94.5" x14ac:dyDescent="0.3">
       <c r="A118" s="4" t="s">
         <v>102</v>
       </c>
       <c r="B118" s="5" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C118" s="5" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D118" s="5" t="s">
         <v>4</v>
@@ -8539,82 +8563,82 @@
         <v>314</v>
       </c>
       <c r="F118" s="5" t="s">
-        <v>6</v>
+        <v>321</v>
       </c>
       <c r="G118" s="5"/>
       <c r="H118" s="5"/>
       <c r="I118" s="5"/>
       <c r="J118" s="5"/>
       <c r="K118" s="5" t="s">
-        <v>372</v>
+        <v>381</v>
       </c>
       <c r="L118" s="5"/>
-      <c r="M118" s="5"/>
+      <c r="M118" s="10" t="s">
+        <v>592</v>
+      </c>
       <c r="N118" s="14" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="O118" s="14" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="P118" s="14" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="Q118" s="5" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="119" spans="1:17" ht="94.5" x14ac:dyDescent="0.3">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="119" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A119" s="4" t="s">
         <v>102</v>
       </c>
       <c r="B119" s="5" t="s">
-        <v>83</v>
+        <v>276</v>
       </c>
       <c r="C119" s="5" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D119" s="5" t="s">
-        <v>112</v>
+        <v>4</v>
       </c>
       <c r="E119" s="5" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F119" s="5" t="s">
-        <v>364</v>
+        <v>6</v>
       </c>
       <c r="G119" s="5"/>
       <c r="H119" s="5"/>
       <c r="I119" s="5"/>
       <c r="J119" s="5"/>
       <c r="K119" s="5" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="L119" s="5"/>
-      <c r="M119" s="10" t="s">
-        <v>590</v>
-      </c>
+      <c r="M119" s="5"/>
       <c r="N119" s="14" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="O119" s="14" t="s">
-        <v>607</v>
-      </c>
-      <c r="P119" s="13" t="s">
+        <v>609</v>
+      </c>
+      <c r="P119" s="14" t="s">
         <v>609</v>
       </c>
       <c r="Q119" s="5" t="s">
-        <v>515</v>
-      </c>
-    </row>
-    <row r="120" spans="1:17" x14ac:dyDescent="0.3">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="120" spans="1:17" ht="94.5" x14ac:dyDescent="0.3">
       <c r="A120" s="4" t="s">
-        <v>116</v>
+        <v>102</v>
       </c>
       <c r="B120" s="5" t="s">
-        <v>277</v>
+        <v>83</v>
       </c>
       <c r="C120" s="5" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D120" s="5" t="s">
         <v>112</v>
@@ -8633,18 +8657,20 @@
         <v>368</v>
       </c>
       <c r="L120" s="5"/>
-      <c r="M120" s="5"/>
-      <c r="N120" s="13" t="s">
-        <v>609</v>
-      </c>
-      <c r="O120" s="13" t="s">
-        <v>609</v>
-      </c>
-      <c r="P120" s="14" t="s">
-        <v>607</v>
+      <c r="M120" s="10" t="s">
+        <v>590</v>
+      </c>
+      <c r="N120" s="14" t="s">
+        <v>607</v>
+      </c>
+      <c r="O120" s="14" t="s">
+        <v>607</v>
+      </c>
+      <c r="P120" s="13" t="s">
+        <v>609</v>
       </c>
       <c r="Q120" s="5" t="s">
-        <v>531</v>
+        <v>515</v>
       </c>
     </row>
     <row r="121" spans="1:17" x14ac:dyDescent="0.3">
@@ -8652,10 +8678,10 @@
         <v>116</v>
       </c>
       <c r="B121" s="5" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C121" s="5" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D121" s="5" t="s">
         <v>112</v>
@@ -8685,7 +8711,7 @@
         <v>607</v>
       </c>
       <c r="Q121" s="5" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
     </row>
     <row r="122" spans="1:17" x14ac:dyDescent="0.3">
@@ -8693,51 +8719,51 @@
         <v>116</v>
       </c>
       <c r="B122" s="5" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C122" s="5" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D122" s="5" t="s">
-        <v>4</v>
+        <v>112</v>
       </c>
       <c r="E122" s="5" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="F122" s="5" t="s">
-        <v>6</v>
+        <v>364</v>
       </c>
       <c r="G122" s="5"/>
       <c r="H122" s="5"/>
       <c r="I122" s="5"/>
       <c r="J122" s="5"/>
       <c r="K122" s="5" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="L122" s="5"/>
       <c r="M122" s="5"/>
-      <c r="N122" s="14" t="s">
-        <v>606</v>
-      </c>
-      <c r="O122" s="14" t="s">
+      <c r="N122" s="13" t="s">
+        <v>609</v>
+      </c>
+      <c r="O122" s="13" t="s">
         <v>609</v>
       </c>
       <c r="P122" s="14" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="Q122" s="5" t="s">
-        <v>520</v>
-      </c>
-    </row>
-    <row r="123" spans="1:17" ht="135" x14ac:dyDescent="0.3">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="123" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A123" s="4" t="s">
         <v>116</v>
       </c>
       <c r="B123" s="5" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C123" s="5" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D123" s="5" t="s">
         <v>4</v>
@@ -8746,19 +8772,17 @@
         <v>314</v>
       </c>
       <c r="F123" s="5" t="s">
-        <v>317</v>
+        <v>6</v>
       </c>
       <c r="G123" s="5"/>
       <c r="H123" s="5"/>
       <c r="I123" s="5"/>
       <c r="J123" s="5"/>
       <c r="K123" s="5" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="L123" s="5"/>
-      <c r="M123" s="10" t="s">
-        <v>594</v>
-      </c>
+      <c r="M123" s="5"/>
       <c r="N123" s="14" t="s">
         <v>606</v>
       </c>
@@ -8766,21 +8790,21 @@
         <v>609</v>
       </c>
       <c r="P123" s="14" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="Q123" s="5" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="124" spans="1:17" x14ac:dyDescent="0.3">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="124" spans="1:17" ht="135" x14ac:dyDescent="0.3">
       <c r="A124" s="4" t="s">
         <v>116</v>
       </c>
       <c r="B124" s="5" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C124" s="5" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D124" s="5" t="s">
         <v>4</v>
@@ -8789,17 +8813,19 @@
         <v>314</v>
       </c>
       <c r="F124" s="5" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="G124" s="5"/>
       <c r="H124" s="5"/>
       <c r="I124" s="5"/>
       <c r="J124" s="5"/>
       <c r="K124" s="5" t="s">
-        <v>376</v>
+        <v>370</v>
       </c>
       <c r="L124" s="5"/>
-      <c r="M124" s="5"/>
+      <c r="M124" s="10" t="s">
+        <v>594</v>
+      </c>
       <c r="N124" s="14" t="s">
         <v>606</v>
       </c>
@@ -8807,10 +8833,10 @@
         <v>609</v>
       </c>
       <c r="P124" s="14" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="Q124" s="5" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
     </row>
     <row r="125" spans="1:17" x14ac:dyDescent="0.3">
@@ -8818,10 +8844,10 @@
         <v>116</v>
       </c>
       <c r="B125" s="5" t="s">
-        <v>84</v>
+        <v>281</v>
       </c>
       <c r="C125" s="5" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D125" s="5" t="s">
         <v>4</v>
@@ -8830,14 +8856,14 @@
         <v>314</v>
       </c>
       <c r="F125" s="5" t="s">
-        <v>6</v>
+        <v>318</v>
       </c>
       <c r="G125" s="5"/>
       <c r="H125" s="5"/>
       <c r="I125" s="5"/>
       <c r="J125" s="5"/>
       <c r="K125" s="5" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="L125" s="5"/>
       <c r="M125" s="5"/>
@@ -8851,7 +8877,7 @@
         <v>606</v>
       </c>
       <c r="Q125" s="5" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
     </row>
     <row r="126" spans="1:17" x14ac:dyDescent="0.3">
@@ -8859,10 +8885,10 @@
         <v>116</v>
       </c>
       <c r="B126" s="5" t="s">
-        <v>282</v>
+        <v>84</v>
       </c>
       <c r="C126" s="5" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D126" s="5" t="s">
         <v>4</v>
@@ -8878,7 +8904,7 @@
       <c r="I126" s="5"/>
       <c r="J126" s="5"/>
       <c r="K126" s="5" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="L126" s="5"/>
       <c r="M126" s="5"/>
@@ -8892,7 +8918,7 @@
         <v>606</v>
       </c>
       <c r="Q126" s="5" t="s">
-        <v>524</v>
+        <v>527</v>
       </c>
     </row>
     <row r="127" spans="1:17" x14ac:dyDescent="0.3">
@@ -8900,94 +8926,92 @@
         <v>116</v>
       </c>
       <c r="B127" s="5" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C127" s="5" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D127" s="5" t="s">
-        <v>112</v>
+        <v>4</v>
       </c>
       <c r="E127" s="5" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F127" s="5" t="s">
-        <v>364</v>
+        <v>6</v>
       </c>
       <c r="G127" s="5"/>
       <c r="H127" s="5"/>
       <c r="I127" s="5"/>
       <c r="J127" s="5"/>
       <c r="K127" s="5" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="L127" s="5"/>
       <c r="M127" s="5"/>
       <c r="N127" s="14" t="s">
-        <v>607</v>
-      </c>
-      <c r="O127" s="13" t="s">
-        <v>609</v>
-      </c>
-      <c r="P127" s="13" t="s">
-        <v>609</v>
+        <v>606</v>
+      </c>
+      <c r="O127" s="14" t="s">
+        <v>609</v>
+      </c>
+      <c r="P127" s="14" t="s">
+        <v>606</v>
       </c>
       <c r="Q127" s="5" t="s">
-        <v>521</v>
-      </c>
-    </row>
-    <row r="128" spans="1:17" ht="40.5" x14ac:dyDescent="0.3">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="128" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A128" s="4" t="s">
         <v>116</v>
       </c>
       <c r="B128" s="5" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C128" s="5" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D128" s="5" t="s">
-        <v>4</v>
+        <v>112</v>
       </c>
       <c r="E128" s="5" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="F128" s="5" t="s">
-        <v>6</v>
+        <v>364</v>
       </c>
       <c r="G128" s="5"/>
       <c r="H128" s="5"/>
       <c r="I128" s="5"/>
       <c r="J128" s="5"/>
       <c r="K128" s="5" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="L128" s="5"/>
-      <c r="M128" s="10" t="s">
-        <v>593</v>
-      </c>
+      <c r="M128" s="5"/>
       <c r="N128" s="14" t="s">
-        <v>606</v>
-      </c>
-      <c r="O128" s="14" t="s">
-        <v>609</v>
-      </c>
-      <c r="P128" s="14" t="s">
+        <v>607</v>
+      </c>
+      <c r="O128" s="13" t="s">
+        <v>609</v>
+      </c>
+      <c r="P128" s="13" t="s">
         <v>609</v>
       </c>
       <c r="Q128" s="5" t="s">
-        <v>525</v>
-      </c>
-    </row>
-    <row r="129" spans="1:17" ht="54" x14ac:dyDescent="0.3">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="129" spans="1:17" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A129" s="4" t="s">
         <v>116</v>
       </c>
       <c r="B129" s="5" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C129" s="5" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D129" s="5" t="s">
         <v>4</v>
@@ -9003,34 +9027,34 @@
       <c r="I129" s="5"/>
       <c r="J129" s="5"/>
       <c r="K129" s="5" t="s">
-        <v>372</v>
-      </c>
-      <c r="L129" s="5" t="s">
-        <v>705</v>
-      </c>
-      <c r="M129" s="5"/>
+        <v>370</v>
+      </c>
+      <c r="L129" s="5"/>
+      <c r="M129" s="10" t="s">
+        <v>593</v>
+      </c>
       <c r="N129" s="14" t="s">
         <v>606</v>
       </c>
       <c r="O129" s="14" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="P129" s="14" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="Q129" s="5" t="s">
-        <v>528</v>
-      </c>
-    </row>
-    <row r="130" spans="1:17" x14ac:dyDescent="0.3">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="130" spans="1:17" ht="54" x14ac:dyDescent="0.3">
       <c r="A130" s="4" t="s">
         <v>116</v>
       </c>
       <c r="B130" s="5" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C130" s="5" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D130" s="5" t="s">
         <v>4</v>
@@ -9048,19 +9072,21 @@
       <c r="K130" s="5" t="s">
         <v>372</v>
       </c>
-      <c r="L130" s="5"/>
+      <c r="L130" s="5" t="s">
+        <v>705</v>
+      </c>
       <c r="M130" s="5"/>
       <c r="N130" s="14" t="s">
         <v>606</v>
       </c>
       <c r="O130" s="14" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="P130" s="14" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="Q130" s="5" t="s">
-        <v>522</v>
+        <v>528</v>
       </c>
     </row>
     <row r="131" spans="1:17" x14ac:dyDescent="0.3">
@@ -9071,7 +9097,7 @@
         <v>286</v>
       </c>
       <c r="C131" s="5" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D131" s="5" t="s">
         <v>4</v>
@@ -9095,54 +9121,54 @@
         <v>606</v>
       </c>
       <c r="O131" s="14" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="P131" s="14" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="Q131" s="5" t="s">
-        <v>529</v>
+        <v>522</v>
       </c>
     </row>
     <row r="132" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A132" s="4" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B132" s="5" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C132" s="5" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D132" s="5" t="s">
-        <v>112</v>
+        <v>4</v>
       </c>
       <c r="E132" s="5" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F132" s="5" t="s">
-        <v>364</v>
+        <v>6</v>
       </c>
       <c r="G132" s="5"/>
       <c r="H132" s="5"/>
       <c r="I132" s="5"/>
       <c r="J132" s="5"/>
       <c r="K132" s="5" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="L132" s="5"/>
       <c r="M132" s="5"/>
       <c r="N132" s="14" t="s">
-        <v>607</v>
-      </c>
-      <c r="O132" s="13" t="s">
-        <v>609</v>
-      </c>
-      <c r="P132" s="13" t="s">
-        <v>609</v>
+        <v>606</v>
+      </c>
+      <c r="O132" s="14" t="s">
+        <v>606</v>
+      </c>
+      <c r="P132" s="14" t="s">
+        <v>606</v>
       </c>
       <c r="Q132" s="5" t="s">
-        <v>549</v>
+        <v>529</v>
       </c>
     </row>
     <row r="133" spans="1:17" x14ac:dyDescent="0.3">
@@ -9150,40 +9176,40 @@
         <v>117</v>
       </c>
       <c r="B133" s="5" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C133" s="5" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D133" s="5" t="s">
-        <v>4</v>
+        <v>112</v>
       </c>
       <c r="E133" s="5" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="F133" s="5" t="s">
-        <v>6</v>
+        <v>364</v>
       </c>
       <c r="G133" s="5"/>
       <c r="H133" s="5"/>
       <c r="I133" s="5"/>
       <c r="J133" s="5"/>
       <c r="K133" s="5" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="L133" s="5"/>
       <c r="M133" s="5"/>
       <c r="N133" s="14" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="O133" s="13" t="s">
         <v>609</v>
       </c>
-      <c r="P133" s="14" t="s">
+      <c r="P133" s="13" t="s">
         <v>609</v>
       </c>
       <c r="Q133" s="5" t="s">
-        <v>538</v>
+        <v>549</v>
       </c>
     </row>
     <row r="134" spans="1:17" x14ac:dyDescent="0.3">
@@ -9191,40 +9217,40 @@
         <v>117</v>
       </c>
       <c r="B134" s="5" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C134" s="5" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D134" s="5" t="s">
-        <v>112</v>
+        <v>4</v>
       </c>
       <c r="E134" s="5" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F134" s="5" t="s">
-        <v>364</v>
+        <v>6</v>
       </c>
       <c r="G134" s="5"/>
       <c r="H134" s="5"/>
       <c r="I134" s="5"/>
       <c r="J134" s="5"/>
       <c r="K134" s="5" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="L134" s="5"/>
       <c r="M134" s="5"/>
       <c r="N134" s="14" t="s">
-        <v>607</v>
-      </c>
-      <c r="O134" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
+      </c>
+      <c r="O134" s="13" t="s">
+        <v>609</v>
       </c>
       <c r="P134" s="14" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="Q134" s="5" t="s">
-        <v>545</v>
+        <v>538</v>
       </c>
     </row>
     <row r="135" spans="1:17" x14ac:dyDescent="0.3">
@@ -9232,40 +9258,40 @@
         <v>117</v>
       </c>
       <c r="B135" s="5" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C135" s="5" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D135" s="5" t="s">
-        <v>4</v>
+        <v>112</v>
       </c>
       <c r="E135" s="5" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="F135" s="5" t="s">
-        <v>6</v>
+        <v>364</v>
       </c>
       <c r="G135" s="5"/>
       <c r="H135" s="5"/>
       <c r="I135" s="5"/>
       <c r="J135" s="5"/>
       <c r="K135" s="5" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="L135" s="5"/>
       <c r="M135" s="5"/>
       <c r="N135" s="14" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="O135" s="14" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="P135" s="14" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="Q135" s="5" t="s">
-        <v>533</v>
+        <v>545</v>
       </c>
     </row>
     <row r="136" spans="1:17" x14ac:dyDescent="0.3">
@@ -9273,40 +9299,40 @@
         <v>117</v>
       </c>
       <c r="B136" s="5" t="s">
-        <v>88</v>
+        <v>290</v>
       </c>
       <c r="C136" s="5" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D136" s="5" t="s">
-        <v>112</v>
+        <v>4</v>
       </c>
       <c r="E136" s="5" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F136" s="5" t="s">
-        <v>364</v>
+        <v>6</v>
       </c>
       <c r="G136" s="5"/>
       <c r="H136" s="5"/>
       <c r="I136" s="5"/>
       <c r="J136" s="5"/>
       <c r="K136" s="5" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="L136" s="5"/>
       <c r="M136" s="5"/>
       <c r="N136" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="O136" s="14" t="s">
-        <v>607</v>
-      </c>
-      <c r="P136" s="13" t="s">
+        <v>606</v>
+      </c>
+      <c r="P136" s="14" t="s">
         <v>609</v>
       </c>
       <c r="Q136" s="5" t="s">
-        <v>542</v>
+        <v>533</v>
       </c>
     </row>
     <row r="137" spans="1:17" x14ac:dyDescent="0.3">
@@ -9314,40 +9340,40 @@
         <v>117</v>
       </c>
       <c r="B137" s="5" t="s">
-        <v>291</v>
+        <v>88</v>
       </c>
       <c r="C137" s="5" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D137" s="5" t="s">
-        <v>4</v>
+        <v>112</v>
       </c>
       <c r="E137" s="5" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="F137" s="5" t="s">
-        <v>6</v>
+        <v>364</v>
       </c>
       <c r="G137" s="5"/>
       <c r="H137" s="5"/>
       <c r="I137" s="5"/>
       <c r="J137" s="5"/>
       <c r="K137" s="5" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="L137" s="5"/>
       <c r="M137" s="5"/>
       <c r="N137" s="14" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="O137" s="14" t="s">
-        <v>609</v>
-      </c>
-      <c r="P137" s="14" t="s">
-        <v>606</v>
+        <v>607</v>
+      </c>
+      <c r="P137" s="13" t="s">
+        <v>609</v>
       </c>
       <c r="Q137" s="5" t="s">
-        <v>537</v>
+        <v>542</v>
       </c>
     </row>
     <row r="138" spans="1:17" x14ac:dyDescent="0.3">
@@ -9358,7 +9384,7 @@
         <v>291</v>
       </c>
       <c r="C138" s="5" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D138" s="5" t="s">
         <v>4</v>
@@ -9385,10 +9411,10 @@
         <v>609</v>
       </c>
       <c r="P138" s="14" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="Q138" s="5" t="s">
-        <v>695</v>
+        <v>537</v>
       </c>
     </row>
     <row r="139" spans="1:17" x14ac:dyDescent="0.3">
@@ -9396,10 +9422,10 @@
         <v>117</v>
       </c>
       <c r="B139" s="5" t="s">
-        <v>90</v>
+        <v>291</v>
       </c>
       <c r="C139" s="5" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D139" s="5" t="s">
         <v>4</v>
@@ -9408,14 +9434,14 @@
         <v>314</v>
       </c>
       <c r="F139" s="5" t="s">
-        <v>317</v>
+        <v>6</v>
       </c>
       <c r="G139" s="5"/>
       <c r="H139" s="5"/>
       <c r="I139" s="5"/>
       <c r="J139" s="5"/>
       <c r="K139" s="5" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="L139" s="5"/>
       <c r="M139" s="5"/>
@@ -9423,13 +9449,13 @@
         <v>606</v>
       </c>
       <c r="O139" s="14" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="P139" s="14" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="Q139" s="5" t="s">
-        <v>535</v>
+        <v>695</v>
       </c>
     </row>
     <row r="140" spans="1:17" x14ac:dyDescent="0.3">
@@ -9437,40 +9463,40 @@
         <v>117</v>
       </c>
       <c r="B140" s="5" t="s">
-        <v>292</v>
+        <v>90</v>
       </c>
       <c r="C140" s="5" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="D140" s="5" t="s">
-        <v>112</v>
+        <v>4</v>
       </c>
       <c r="E140" s="5" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F140" s="5" t="s">
-        <v>364</v>
+        <v>317</v>
       </c>
       <c r="G140" s="5"/>
       <c r="H140" s="5"/>
       <c r="I140" s="5"/>
       <c r="J140" s="5"/>
       <c r="K140" s="5" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="L140" s="5"/>
       <c r="M140" s="5"/>
       <c r="N140" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="O140" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="P140" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="Q140" s="5" t="s">
-        <v>540</v>
+        <v>535</v>
       </c>
     </row>
     <row r="141" spans="1:17" x14ac:dyDescent="0.3">
@@ -9478,40 +9504,40 @@
         <v>117</v>
       </c>
       <c r="B141" s="5" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C141" s="5" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D141" s="5" t="s">
-        <v>4</v>
+        <v>112</v>
       </c>
       <c r="E141" s="5" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="F141" s="5" t="s">
-        <v>6</v>
+        <v>364</v>
       </c>
       <c r="G141" s="5"/>
       <c r="H141" s="5"/>
       <c r="I141" s="5"/>
       <c r="J141" s="5"/>
       <c r="K141" s="5" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="L141" s="5"/>
       <c r="M141" s="5"/>
       <c r="N141" s="14" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="O141" s="14" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="P141" s="14" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="Q141" s="5" t="s">
-        <v>696</v>
+        <v>540</v>
       </c>
     </row>
     <row r="142" spans="1:17" x14ac:dyDescent="0.3">
@@ -9519,10 +9545,10 @@
         <v>117</v>
       </c>
       <c r="B142" s="5" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C142" s="5" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D142" s="5" t="s">
         <v>4</v>
@@ -9531,7 +9557,7 @@
         <v>314</v>
       </c>
       <c r="F142" s="5" t="s">
-        <v>318</v>
+        <v>6</v>
       </c>
       <c r="G142" s="5"/>
       <c r="H142" s="5"/>
@@ -9543,16 +9569,16 @@
       <c r="L142" s="5"/>
       <c r="M142" s="5"/>
       <c r="N142" s="14" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="O142" s="14" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="P142" s="14" t="s">
         <v>609</v>
       </c>
       <c r="Q142" s="5" t="s">
-        <v>543</v>
+        <v>696</v>
       </c>
     </row>
     <row r="143" spans="1:17" x14ac:dyDescent="0.3">
@@ -9560,51 +9586,51 @@
         <v>117</v>
       </c>
       <c r="B143" s="5" t="s">
-        <v>92</v>
+        <v>294</v>
       </c>
       <c r="C143" s="5" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D143" s="5" t="s">
-        <v>112</v>
+        <v>4</v>
       </c>
       <c r="E143" s="5" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F143" s="5" t="s">
-        <v>391</v>
+        <v>318</v>
       </c>
       <c r="G143" s="5"/>
       <c r="H143" s="5"/>
       <c r="I143" s="5"/>
       <c r="J143" s="5"/>
       <c r="K143" s="5" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="L143" s="5"/>
       <c r="M143" s="5"/>
-      <c r="N143" s="13" t="s">
+      <c r="N143" s="14" t="s">
         <v>609</v>
       </c>
       <c r="O143" s="14" t="s">
-        <v>607</v>
-      </c>
-      <c r="P143" s="13" t="s">
+        <v>610</v>
+      </c>
+      <c r="P143" s="14" t="s">
         <v>609</v>
       </c>
       <c r="Q143" s="5" t="s">
-        <v>544</v>
-      </c>
-    </row>
-    <row r="144" spans="1:17" ht="81" x14ac:dyDescent="0.3">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="144" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A144" s="4" t="s">
         <v>117</v>
       </c>
       <c r="B144" s="5" t="s">
-        <v>295</v>
+        <v>92</v>
       </c>
       <c r="C144" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D144" s="5" t="s">
         <v>112</v>
@@ -9613,7 +9639,7 @@
         <v>315</v>
       </c>
       <c r="F144" s="5" t="s">
-        <v>364</v>
+        <v>391</v>
       </c>
       <c r="G144" s="5"/>
       <c r="H144" s="5"/>
@@ -9623,23 +9649,21 @@
         <v>368</v>
       </c>
       <c r="L144" s="5"/>
-      <c r="M144" s="10" t="s">
-        <v>595</v>
-      </c>
+      <c r="M144" s="5"/>
       <c r="N144" s="13" t="s">
         <v>609</v>
       </c>
       <c r="O144" s="14" t="s">
         <v>607</v>
       </c>
-      <c r="P144" s="14" t="s">
-        <v>607</v>
+      <c r="P144" s="13" t="s">
+        <v>609</v>
       </c>
       <c r="Q144" s="5" t="s">
-        <v>536</v>
-      </c>
-    </row>
-    <row r="145" spans="1:17" x14ac:dyDescent="0.3">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="145" spans="1:17" ht="81" x14ac:dyDescent="0.3">
       <c r="A145" s="4" t="s">
         <v>117</v>
       </c>
@@ -9647,7 +9671,7 @@
         <v>295</v>
       </c>
       <c r="C145" s="5" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="D145" s="5" t="s">
         <v>112</v>
@@ -9656,19 +9680,21 @@
         <v>315</v>
       </c>
       <c r="F145" s="5" t="s">
-        <v>324</v>
+        <v>364</v>
       </c>
       <c r="G145" s="5"/>
       <c r="H145" s="5"/>
       <c r="I145" s="5"/>
       <c r="J145" s="5"/>
       <c r="K145" s="5" t="s">
-        <v>375</v>
+        <v>368</v>
       </c>
       <c r="L145" s="5"/>
-      <c r="M145" s="5"/>
-      <c r="N145" s="14" t="s">
-        <v>607</v>
+      <c r="M145" s="10" t="s">
+        <v>595</v>
+      </c>
+      <c r="N145" s="13" t="s">
+        <v>609</v>
       </c>
       <c r="O145" s="14" t="s">
         <v>607</v>
@@ -9677,89 +9703,89 @@
         <v>607</v>
       </c>
       <c r="Q145" s="5" t="s">
-        <v>546</v>
-      </c>
-    </row>
-    <row r="146" spans="1:17" ht="148.5" x14ac:dyDescent="0.3">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="146" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A146" s="4" t="s">
         <v>117</v>
       </c>
       <c r="B146" s="5" t="s">
-        <v>93</v>
+        <v>295</v>
       </c>
       <c r="C146" s="5" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D146" s="5" t="s">
-        <v>4</v>
+        <v>112</v>
       </c>
       <c r="E146" s="5" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="F146" s="5" t="s">
-        <v>6</v>
+        <v>324</v>
       </c>
       <c r="G146" s="5"/>
       <c r="H146" s="5"/>
       <c r="I146" s="5"/>
       <c r="J146" s="5"/>
       <c r="K146" s="5" t="s">
-        <v>707</v>
+        <v>375</v>
       </c>
       <c r="L146" s="5"/>
       <c r="M146" s="5"/>
       <c r="N146" s="14" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="O146" s="14" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="P146" s="14" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="Q146" s="5" t="s">
-        <v>532</v>
-      </c>
-    </row>
-    <row r="147" spans="1:17" x14ac:dyDescent="0.3">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="147" spans="1:17" ht="148.5" x14ac:dyDescent="0.3">
       <c r="A147" s="4" t="s">
         <v>117</v>
       </c>
       <c r="B147" s="5" t="s">
-        <v>296</v>
+        <v>93</v>
       </c>
       <c r="C147" s="5" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D147" s="5" t="s">
-        <v>112</v>
+        <v>4</v>
       </c>
       <c r="E147" s="5" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F147" s="5" t="s">
-        <v>364</v>
+        <v>6</v>
       </c>
       <c r="G147" s="5"/>
       <c r="H147" s="5"/>
       <c r="I147" s="5"/>
       <c r="J147" s="5"/>
       <c r="K147" s="5" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="L147" s="5"/>
       <c r="M147" s="5"/>
       <c r="N147" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="O147" s="14" t="s">
-        <v>607</v>
-      </c>
-      <c r="P147" s="13" t="s">
-        <v>609</v>
+        <v>609</v>
+      </c>
+      <c r="P147" s="14" t="s">
+        <v>606</v>
       </c>
       <c r="Q147" s="5" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
     </row>
     <row r="148" spans="1:17" x14ac:dyDescent="0.3">
@@ -9767,51 +9793,51 @@
         <v>117</v>
       </c>
       <c r="B148" s="5" t="s">
-        <v>94</v>
+        <v>296</v>
       </c>
       <c r="C148" s="5" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D148" s="5" t="s">
-        <v>4</v>
+        <v>112</v>
       </c>
       <c r="E148" s="5" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="F148" s="5" t="s">
-        <v>6</v>
+        <v>364</v>
       </c>
       <c r="G148" s="5"/>
       <c r="H148" s="5"/>
       <c r="I148" s="5"/>
       <c r="J148" s="5"/>
       <c r="K148" s="5" t="s">
-        <v>372</v>
+        <v>706</v>
       </c>
       <c r="L148" s="5"/>
       <c r="M148" s="5"/>
       <c r="N148" s="14" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="O148" s="14" t="s">
-        <v>609</v>
-      </c>
-      <c r="P148" s="14" t="s">
-        <v>606</v>
+        <v>607</v>
+      </c>
+      <c r="P148" s="13" t="s">
+        <v>609</v>
       </c>
       <c r="Q148" s="5" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="149" spans="1:17" ht="135" x14ac:dyDescent="0.3">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="149" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A149" s="4" t="s">
         <v>117</v>
       </c>
       <c r="B149" s="5" t="s">
-        <v>297</v>
+        <v>94</v>
       </c>
       <c r="C149" s="5" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D149" s="5" t="s">
         <v>4</v>
@@ -9830,31 +9856,29 @@
         <v>372</v>
       </c>
       <c r="L149" s="5"/>
-      <c r="M149" s="10" t="s">
-        <v>596</v>
-      </c>
+      <c r="M149" s="5"/>
       <c r="N149" s="14" t="s">
-        <v>610</v>
+        <v>606</v>
       </c>
       <c r="O149" s="14" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="P149" s="14" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="Q149" s="5" t="s">
-        <v>548</v>
-      </c>
-    </row>
-    <row r="150" spans="1:17" ht="148.5" x14ac:dyDescent="0.3">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="150" spans="1:17" ht="135" x14ac:dyDescent="0.3">
       <c r="A150" s="4" t="s">
         <v>117</v>
       </c>
       <c r="B150" s="5" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C150" s="5" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D150" s="5" t="s">
         <v>4</v>
@@ -9874,22 +9898,22 @@
       </c>
       <c r="L150" s="5"/>
       <c r="M150" s="10" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="N150" s="14" t="s">
-        <v>606</v>
+        <v>610</v>
       </c>
       <c r="O150" s="14" t="s">
-        <v>610</v>
+        <v>606</v>
       </c>
       <c r="P150" s="14" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="Q150" s="5" t="s">
-        <v>541</v>
-      </c>
-    </row>
-    <row r="151" spans="1:17" x14ac:dyDescent="0.3">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="151" spans="1:17" ht="148.5" x14ac:dyDescent="0.3">
       <c r="A151" s="4" t="s">
         <v>117</v>
       </c>
@@ -9897,7 +9921,7 @@
         <v>298</v>
       </c>
       <c r="C151" s="5" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D151" s="5" t="s">
         <v>4</v>
@@ -9906,28 +9930,30 @@
         <v>314</v>
       </c>
       <c r="F151" s="5" t="s">
-        <v>318</v>
+        <v>6</v>
       </c>
       <c r="G151" s="5"/>
       <c r="H151" s="5"/>
       <c r="I151" s="5"/>
       <c r="J151" s="5"/>
       <c r="K151" s="5" t="s">
-        <v>380</v>
+        <v>372</v>
       </c>
       <c r="L151" s="5"/>
-      <c r="M151" s="5"/>
+      <c r="M151" s="10" t="s">
+        <v>597</v>
+      </c>
       <c r="N151" s="14" t="s">
         <v>606</v>
       </c>
       <c r="O151" s="14" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="P151" s="14" t="s">
         <v>606</v>
       </c>
       <c r="Q151" s="5" t="s">
-        <v>550</v>
+        <v>541</v>
       </c>
     </row>
     <row r="152" spans="1:17" x14ac:dyDescent="0.3">
@@ -9935,10 +9961,10 @@
         <v>117</v>
       </c>
       <c r="B152" s="5" t="s">
-        <v>395</v>
+        <v>298</v>
       </c>
       <c r="C152" s="5" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D152" s="5" t="s">
         <v>4</v>
@@ -9947,14 +9973,14 @@
         <v>314</v>
       </c>
       <c r="F152" s="5" t="s">
-        <v>6</v>
+        <v>318</v>
       </c>
       <c r="G152" s="5"/>
       <c r="H152" s="5"/>
       <c r="I152" s="5"/>
       <c r="J152" s="5"/>
       <c r="K152" s="5" t="s">
-        <v>372</v>
+        <v>380</v>
       </c>
       <c r="L152" s="5"/>
       <c r="M152" s="5"/>
@@ -9962,24 +9988,24 @@
         <v>606</v>
       </c>
       <c r="O152" s="14" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="P152" s="14" t="s">
         <v>606</v>
       </c>
       <c r="Q152" s="5" t="s">
-        <v>539</v>
+        <v>550</v>
       </c>
     </row>
     <row r="153" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A153" s="4" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B153" s="5" t="s">
-        <v>299</v>
+        <v>395</v>
       </c>
       <c r="C153" s="5" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D153" s="5" t="s">
         <v>4</v>
@@ -9988,7 +10014,7 @@
         <v>314</v>
       </c>
       <c r="F153" s="5" t="s">
-        <v>320</v>
+        <v>6</v>
       </c>
       <c r="G153" s="5"/>
       <c r="H153" s="5"/>
@@ -10000,16 +10026,16 @@
       <c r="L153" s="5"/>
       <c r="M153" s="5"/>
       <c r="N153" s="14" t="s">
+        <v>606</v>
+      </c>
+      <c r="O153" s="14" t="s">
         <v>610</v>
       </c>
-      <c r="O153" s="14" t="s">
-        <v>609</v>
-      </c>
       <c r="P153" s="14" t="s">
         <v>606</v>
       </c>
       <c r="Q153" s="5" t="s">
-        <v>552</v>
+        <v>539</v>
       </c>
     </row>
     <row r="154" spans="1:17" x14ac:dyDescent="0.3">
@@ -10017,10 +10043,10 @@
         <v>118</v>
       </c>
       <c r="B154" s="5" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C154" s="5" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D154" s="5" t="s">
         <v>4</v>
@@ -10029,7 +10055,7 @@
         <v>314</v>
       </c>
       <c r="F154" s="5" t="s">
-        <v>6</v>
+        <v>320</v>
       </c>
       <c r="G154" s="5"/>
       <c r="H154" s="5"/>
@@ -10040,17 +10066,17 @@
       </c>
       <c r="L154" s="5"/>
       <c r="M154" s="5"/>
-      <c r="N154" s="13" t="s">
-        <v>609</v>
-      </c>
-      <c r="O154" s="13" t="s">
+      <c r="N154" s="14" t="s">
+        <v>610</v>
+      </c>
+      <c r="O154" s="14" t="s">
         <v>609</v>
       </c>
       <c r="P154" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="Q154" s="5" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
     </row>
     <row r="155" spans="1:17" x14ac:dyDescent="0.3">
@@ -10061,7 +10087,7 @@
         <v>300</v>
       </c>
       <c r="C155" s="5" t="s">
-        <v>612</v>
+        <v>223</v>
       </c>
       <c r="D155" s="5" t="s">
         <v>4</v>
@@ -10070,31 +10096,31 @@
         <v>314</v>
       </c>
       <c r="F155" s="5" t="s">
-        <v>396</v>
+        <v>6</v>
       </c>
       <c r="G155" s="5"/>
       <c r="H155" s="5"/>
       <c r="I155" s="5"/>
       <c r="J155" s="5"/>
       <c r="K155" s="5" t="s">
-        <v>383</v>
+        <v>372</v>
       </c>
       <c r="L155" s="5"/>
       <c r="M155" s="5"/>
-      <c r="N155" s="14" t="s">
-        <v>606</v>
-      </c>
-      <c r="O155" s="14" t="s">
+      <c r="N155" s="13" t="s">
+        <v>609</v>
+      </c>
+      <c r="O155" s="13" t="s">
         <v>609</v>
       </c>
       <c r="P155" s="14" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="Q155" s="5" t="s">
-        <v>554</v>
-      </c>
-    </row>
-    <row r="156" spans="1:17" ht="202.5" x14ac:dyDescent="0.3">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="156" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A156" s="4" t="s">
         <v>118</v>
       </c>
@@ -10102,7 +10128,7 @@
         <v>300</v>
       </c>
       <c r="C156" s="5" t="s">
-        <v>224</v>
+        <v>612</v>
       </c>
       <c r="D156" s="5" t="s">
         <v>4</v>
@@ -10111,18 +10137,16 @@
         <v>314</v>
       </c>
       <c r="F156" s="5" t="s">
-        <v>6</v>
+        <v>396</v>
       </c>
       <c r="G156" s="5"/>
       <c r="H156" s="5"/>
       <c r="I156" s="5"/>
       <c r="J156" s="5"/>
       <c r="K156" s="5" t="s">
-        <v>372</v>
-      </c>
-      <c r="L156" s="5" t="s">
-        <v>729</v>
-      </c>
+        <v>383</v>
+      </c>
+      <c r="L156" s="5"/>
       <c r="M156" s="5"/>
       <c r="N156" s="14" t="s">
         <v>606</v>
@@ -10131,21 +10155,21 @@
         <v>609</v>
       </c>
       <c r="P156" s="14" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="Q156" s="5" t="s">
-        <v>556</v>
-      </c>
-    </row>
-    <row r="157" spans="1:17" x14ac:dyDescent="0.3">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="157" spans="1:17" ht="202.5" x14ac:dyDescent="0.3">
       <c r="A157" s="4" t="s">
         <v>118</v>
       </c>
       <c r="B157" s="5" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C157" s="5" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D157" s="5" t="s">
         <v>4</v>
@@ -10163,19 +10187,21 @@
       <c r="K157" s="5" t="s">
         <v>372</v>
       </c>
-      <c r="L157" s="5"/>
+      <c r="L157" s="5" t="s">
+        <v>729</v>
+      </c>
       <c r="M157" s="5"/>
-      <c r="N157" s="13" t="s">
-        <v>609</v>
-      </c>
-      <c r="O157" s="13" t="s">
-        <v>609</v>
-      </c>
-      <c r="P157" s="13" t="s">
-        <v>609</v>
+      <c r="N157" s="14" t="s">
+        <v>606</v>
+      </c>
+      <c r="O157" s="14" t="s">
+        <v>609</v>
+      </c>
+      <c r="P157" s="14" t="s">
+        <v>606</v>
       </c>
       <c r="Q157" s="5" t="s">
-        <v>551</v>
+        <v>556</v>
       </c>
     </row>
     <row r="158" spans="1:17" x14ac:dyDescent="0.3">
@@ -10183,26 +10209,26 @@
         <v>118</v>
       </c>
       <c r="B158" s="5" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C158" s="5" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D158" s="5" t="s">
-        <v>112</v>
+        <v>4</v>
       </c>
       <c r="E158" s="5" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F158" s="5" t="s">
-        <v>364</v>
+        <v>6</v>
       </c>
       <c r="G158" s="5"/>
       <c r="H158" s="5"/>
       <c r="I158" s="5"/>
       <c r="J158" s="5"/>
       <c r="K158" s="5" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="L158" s="5"/>
       <c r="M158" s="5"/>
@@ -10212,63 +10238,63 @@
       <c r="O158" s="13" t="s">
         <v>609</v>
       </c>
-      <c r="P158" s="14" t="s">
-        <v>607</v>
+      <c r="P158" s="13" t="s">
+        <v>609</v>
       </c>
       <c r="Q158" s="5" t="s">
-        <v>560</v>
-      </c>
-    </row>
-    <row r="159" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="159" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A159" s="4" t="s">
         <v>118</v>
       </c>
       <c r="B159" s="5" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C159" s="5" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D159" s="5" t="s">
-        <v>4</v>
+        <v>112</v>
       </c>
       <c r="E159" s="5" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="F159" s="5" t="s">
-        <v>6</v>
+        <v>364</v>
       </c>
       <c r="G159" s="5"/>
       <c r="H159" s="5"/>
       <c r="I159" s="5"/>
       <c r="J159" s="5"/>
       <c r="K159" s="5" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="L159" s="5"/>
       <c r="M159" s="5"/>
-      <c r="N159" s="14" t="s">
-        <v>606</v>
-      </c>
-      <c r="O159" s="14" t="s">
+      <c r="N159" s="13" t="s">
+        <v>609</v>
+      </c>
+      <c r="O159" s="13" t="s">
         <v>609</v>
       </c>
       <c r="P159" s="14" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="Q159" s="5" t="s">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="160" spans="1:17" ht="27" x14ac:dyDescent="0.3">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="160" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A160" s="4" t="s">
         <v>118</v>
       </c>
       <c r="B160" s="5" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C160" s="5" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D160" s="5" t="s">
         <v>4</v>
@@ -10284,11 +10310,9 @@
       <c r="I160" s="5"/>
       <c r="J160" s="5"/>
       <c r="K160" s="5" t="s">
-        <v>372</v>
-      </c>
-      <c r="L160" s="5" t="s">
-        <v>711</v>
-      </c>
+        <v>370</v>
+      </c>
+      <c r="L160" s="5"/>
       <c r="M160" s="5"/>
       <c r="N160" s="14" t="s">
         <v>606</v>
@@ -10297,21 +10321,21 @@
         <v>609</v>
       </c>
       <c r="P160" s="14" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="Q160" s="5" t="s">
-        <v>563</v>
-      </c>
-    </row>
-    <row r="161" spans="1:17" x14ac:dyDescent="0.3">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="161" spans="1:17" ht="27" x14ac:dyDescent="0.3">
       <c r="A161" s="4" t="s">
         <v>118</v>
       </c>
       <c r="B161" s="5" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C161" s="5" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D161" s="5" t="s">
         <v>4</v>
@@ -10330,20 +10354,20 @@
         <v>372</v>
       </c>
       <c r="L161" s="5" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="M161" s="5"/>
       <c r="N161" s="14" t="s">
         <v>606</v>
       </c>
       <c r="O161" s="14" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="P161" s="14" t="s">
         <v>606</v>
       </c>
       <c r="Q161" s="5" t="s">
-        <v>559</v>
+        <v>563</v>
       </c>
     </row>
     <row r="162" spans="1:17" x14ac:dyDescent="0.3">
@@ -10351,10 +10375,10 @@
         <v>118</v>
       </c>
       <c r="B162" s="5" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C162" s="5" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D162" s="5" t="s">
         <v>4</v>
@@ -10370,32 +10394,34 @@
       <c r="I162" s="5"/>
       <c r="J162" s="5"/>
       <c r="K162" s="5" t="s">
-        <v>377</v>
-      </c>
-      <c r="L162" s="5"/>
+        <v>372</v>
+      </c>
+      <c r="L162" s="5" t="s">
+        <v>709</v>
+      </c>
       <c r="M162" s="5"/>
       <c r="N162" s="14" t="s">
         <v>606</v>
       </c>
       <c r="O162" s="14" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="P162" s="14" t="s">
         <v>606</v>
       </c>
       <c r="Q162" s="5" t="s">
-        <v>566</v>
-      </c>
-    </row>
-    <row r="163" spans="1:17" ht="175.5" x14ac:dyDescent="0.3">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="163" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A163" s="4" t="s">
         <v>118</v>
       </c>
       <c r="B163" s="5" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C163" s="5" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D163" s="5" t="s">
         <v>4</v>
@@ -10411,14 +10437,12 @@
       <c r="I163" s="5"/>
       <c r="J163" s="5"/>
       <c r="K163" s="5" t="s">
-        <v>370</v>
-      </c>
-      <c r="L163" s="5" t="s">
-        <v>715</v>
-      </c>
+        <v>377</v>
+      </c>
+      <c r="L163" s="5"/>
       <c r="M163" s="5"/>
       <c r="N163" s="14" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="O163" s="14" t="s">
         <v>609</v>
@@ -10427,18 +10451,18 @@
         <v>606</v>
       </c>
       <c r="Q163" s="5" t="s">
-        <v>567</v>
-      </c>
-    </row>
-    <row r="164" spans="1:17" x14ac:dyDescent="0.3">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="164" spans="1:17" ht="175.5" x14ac:dyDescent="0.3">
       <c r="A164" s="4" t="s">
         <v>118</v>
       </c>
       <c r="B164" s="5" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C164" s="5" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D164" s="5" t="s">
         <v>4</v>
@@ -10454,21 +10478,23 @@
       <c r="I164" s="5"/>
       <c r="J164" s="5"/>
       <c r="K164" s="5" t="s">
-        <v>372</v>
-      </c>
-      <c r="L164" s="5"/>
+        <v>370</v>
+      </c>
+      <c r="L164" s="5" t="s">
+        <v>715</v>
+      </c>
       <c r="M164" s="5"/>
       <c r="N164" s="14" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="O164" s="14" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="P164" s="14" t="s">
         <v>606</v>
       </c>
       <c r="Q164" s="5" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
     </row>
     <row r="165" spans="1:17" x14ac:dyDescent="0.3">
@@ -10476,10 +10502,10 @@
         <v>118</v>
       </c>
       <c r="B165" s="5" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C165" s="5" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D165" s="5" t="s">
         <v>4</v>
@@ -10495,7 +10521,7 @@
       <c r="I165" s="5"/>
       <c r="J165" s="5"/>
       <c r="K165" s="5" t="s">
-        <v>377</v>
+        <v>372</v>
       </c>
       <c r="L165" s="5"/>
       <c r="M165" s="5"/>
@@ -10503,16 +10529,16 @@
         <v>606</v>
       </c>
       <c r="O165" s="14" t="s">
-        <v>606</v>
+        <v>610</v>
       </c>
       <c r="P165" s="14" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="Q165" s="5" t="s">
-        <v>555</v>
-      </c>
-    </row>
-    <row r="166" spans="1:17" ht="40.5" x14ac:dyDescent="0.3">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="166" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A166" s="4" t="s">
         <v>118</v>
       </c>
@@ -10520,7 +10546,7 @@
         <v>309</v>
       </c>
       <c r="C166" s="5" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="D166" s="5" t="s">
         <v>4</v>
@@ -10539,31 +10565,29 @@
         <v>377</v>
       </c>
       <c r="L166" s="5"/>
-      <c r="M166" s="10" t="s">
-        <v>598</v>
-      </c>
+      <c r="M166" s="5"/>
       <c r="N166" s="14" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="O166" s="14" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="P166" s="14" t="s">
         <v>609</v>
       </c>
       <c r="Q166" s="5" t="s">
-        <v>568</v>
-      </c>
-    </row>
-    <row r="167" spans="1:17" ht="27" x14ac:dyDescent="0.3">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="167" spans="1:17" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A167" s="4" t="s">
         <v>118</v>
       </c>
       <c r="B167" s="5" t="s">
-        <v>99</v>
+        <v>309</v>
       </c>
       <c r="C167" s="5" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="D167" s="5" t="s">
         <v>4</v>
@@ -10579,26 +10603,26 @@
       <c r="I167" s="5"/>
       <c r="J167" s="5"/>
       <c r="K167" s="5" t="s">
-        <v>376</v>
-      </c>
-      <c r="L167" s="5" t="s">
-        <v>708</v>
-      </c>
-      <c r="M167" s="5"/>
+        <v>377</v>
+      </c>
+      <c r="L167" s="5"/>
+      <c r="M167" s="10" t="s">
+        <v>598</v>
+      </c>
       <c r="N167" s="14" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="O167" s="14" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="P167" s="14" t="s">
         <v>609</v>
       </c>
       <c r="Q167" s="5" t="s">
-        <v>557</v>
-      </c>
-    </row>
-    <row r="168" spans="1:17" ht="283.5" x14ac:dyDescent="0.3">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="168" spans="1:17" ht="27" x14ac:dyDescent="0.3">
       <c r="A168" s="4" t="s">
         <v>118</v>
       </c>
@@ -10606,7 +10630,7 @@
         <v>99</v>
       </c>
       <c r="C168" s="5" t="s">
-        <v>8</v>
+        <v>235</v>
       </c>
       <c r="D168" s="5" t="s">
         <v>4</v>
@@ -10615,19 +10639,19 @@
         <v>314</v>
       </c>
       <c r="F168" s="5" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G168" s="5"/>
       <c r="H168" s="5"/>
       <c r="I168" s="5"/>
       <c r="J168" s="5"/>
       <c r="K168" s="5" t="s">
-        <v>382</v>
-      </c>
-      <c r="L168" s="5"/>
-      <c r="M168" s="10" t="s">
-        <v>599</v>
-      </c>
+        <v>376</v>
+      </c>
+      <c r="L168" s="5" t="s">
+        <v>708</v>
+      </c>
+      <c r="M168" s="5"/>
       <c r="N168" s="14" t="s">
         <v>606</v>
       </c>
@@ -10635,13 +10659,13 @@
         <v>606</v>
       </c>
       <c r="P168" s="14" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="Q168" s="5" t="s">
-        <v>558</v>
-      </c>
-    </row>
-    <row r="169" spans="1:17" ht="27" x14ac:dyDescent="0.3">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="169" spans="1:17" ht="283.5" x14ac:dyDescent="0.3">
       <c r="A169" s="4" t="s">
         <v>118</v>
       </c>
@@ -10649,7 +10673,7 @@
         <v>99</v>
       </c>
       <c r="C169" s="5" t="s">
-        <v>236</v>
+        <v>8</v>
       </c>
       <c r="D169" s="5" t="s">
         <v>4</v>
@@ -10658,19 +10682,19 @@
         <v>314</v>
       </c>
       <c r="F169" s="5" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G169" s="5"/>
       <c r="H169" s="5"/>
       <c r="I169" s="5"/>
       <c r="J169" s="5"/>
       <c r="K169" s="5" t="s">
-        <v>376</v>
-      </c>
-      <c r="L169" s="5" t="s">
-        <v>710</v>
-      </c>
-      <c r="M169" s="5"/>
+        <v>382</v>
+      </c>
+      <c r="L169" s="5"/>
+      <c r="M169" s="10" t="s">
+        <v>599</v>
+      </c>
       <c r="N169" s="14" t="s">
         <v>606</v>
       </c>
@@ -10678,13 +10702,13 @@
         <v>606</v>
       </c>
       <c r="P169" s="14" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="Q169" s="5" t="s">
-        <v>562</v>
-      </c>
-    </row>
-    <row r="170" spans="1:17" ht="40.5" x14ac:dyDescent="0.3">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="170" spans="1:17" ht="27" x14ac:dyDescent="0.3">
       <c r="A170" s="4" t="s">
         <v>118</v>
       </c>
@@ -10692,7 +10716,7 @@
         <v>99</v>
       </c>
       <c r="C170" s="5" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="D170" s="5" t="s">
         <v>4</v>
@@ -10711,7 +10735,7 @@
         <v>376</v>
       </c>
       <c r="L170" s="5" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
       <c r="M170" s="5"/>
       <c r="N170" s="14" t="s">
@@ -10721,62 +10745,64 @@
         <v>606</v>
       </c>
       <c r="P170" s="14" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="Q170" s="5" t="s">
-        <v>565</v>
-      </c>
-    </row>
-    <row r="171" spans="1:17" x14ac:dyDescent="0.3">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="171" spans="1:17" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A171" s="4" t="s">
         <v>118</v>
       </c>
       <c r="B171" s="5" t="s">
-        <v>310</v>
+        <v>99</v>
       </c>
       <c r="C171" s="5" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="D171" s="5" t="s">
-        <v>112</v>
+        <v>4</v>
       </c>
       <c r="E171" s="5" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F171" s="5" t="s">
-        <v>364</v>
+        <v>6</v>
       </c>
       <c r="G171" s="5"/>
       <c r="H171" s="5"/>
       <c r="I171" s="5"/>
       <c r="J171" s="5"/>
       <c r="K171" s="5" t="s">
-        <v>368</v>
-      </c>
-      <c r="L171" s="5"/>
+        <v>376</v>
+      </c>
+      <c r="L171" s="5" t="s">
+        <v>712</v>
+      </c>
       <c r="M171" s="5"/>
       <c r="N171" s="14" t="s">
         <v>606</v>
       </c>
       <c r="O171" s="14" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="P171" s="14" t="s">
-        <v>606</v>
+        <v>610</v>
       </c>
       <c r="Q171" s="5" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
     </row>
     <row r="172" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A172" s="4" t="s">
-        <v>313</v>
+        <v>118</v>
       </c>
       <c r="B172" s="5" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C172" s="5" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D172" s="5" t="s">
         <v>112</v>
@@ -10796,17 +10822,17 @@
       </c>
       <c r="L172" s="5"/>
       <c r="M172" s="5"/>
-      <c r="N172" s="13" t="s">
-        <v>609</v>
-      </c>
-      <c r="O172" s="13" t="s">
+      <c r="N172" s="14" t="s">
+        <v>606</v>
+      </c>
+      <c r="O172" s="14" t="s">
         <v>609</v>
       </c>
       <c r="P172" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="Q172" s="5" t="s">
-        <v>571</v>
+        <v>564</v>
       </c>
     </row>
     <row r="173" spans="1:17" x14ac:dyDescent="0.3">
@@ -10817,37 +10843,37 @@
         <v>311</v>
       </c>
       <c r="C173" s="5" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D173" s="5" t="s">
-        <v>4</v>
+        <v>112</v>
       </c>
       <c r="E173" s="5" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="F173" s="5" t="s">
-        <v>6</v>
+        <v>364</v>
       </c>
       <c r="G173" s="5"/>
       <c r="H173" s="5"/>
       <c r="I173" s="5"/>
       <c r="J173" s="5"/>
       <c r="K173" s="5" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="L173" s="5"/>
       <c r="M173" s="5"/>
-      <c r="N173" s="14" t="s">
-        <v>609</v>
-      </c>
-      <c r="O173" s="14" t="s">
+      <c r="N173" s="13" t="s">
+        <v>609</v>
+      </c>
+      <c r="O173" s="13" t="s">
         <v>609</v>
       </c>
       <c r="P173" s="14" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="Q173" s="5" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
     </row>
     <row r="174" spans="1:17" x14ac:dyDescent="0.3">
@@ -10855,40 +10881,40 @@
         <v>313</v>
       </c>
       <c r="B174" s="5" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C174" s="5" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="D174" s="5" t="s">
-        <v>112</v>
+        <v>4</v>
       </c>
       <c r="E174" s="5" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F174" s="5" t="s">
-        <v>364</v>
+        <v>6</v>
       </c>
       <c r="G174" s="5"/>
       <c r="H174" s="5"/>
       <c r="I174" s="5"/>
       <c r="J174" s="5"/>
       <c r="K174" s="5" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="L174" s="5"/>
       <c r="M174" s="5"/>
-      <c r="N174" s="13" t="s">
-        <v>609</v>
-      </c>
-      <c r="O174" s="13" t="s">
+      <c r="N174" s="14" t="s">
+        <v>609</v>
+      </c>
+      <c r="O174" s="14" t="s">
         <v>609</v>
       </c>
       <c r="P174" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="Q174" s="5" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
     </row>
     <row r="175" spans="1:17" x14ac:dyDescent="0.3">
@@ -10899,75 +10925,81 @@
         <v>312</v>
       </c>
       <c r="C175" s="5" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D175" s="5" t="s">
-        <v>4</v>
+        <v>112</v>
       </c>
       <c r="E175" s="5" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="F175" s="5" t="s">
-        <v>6</v>
+        <v>364</v>
       </c>
       <c r="G175" s="5"/>
       <c r="H175" s="5"/>
       <c r="I175" s="5"/>
       <c r="J175" s="5"/>
       <c r="K175" s="5" t="s">
-        <v>378</v>
+        <v>368</v>
       </c>
       <c r="L175" s="5"/>
       <c r="M175" s="5"/>
-      <c r="N175" s="14" t="s">
-        <v>609</v>
-      </c>
-      <c r="O175" s="14" t="s">
+      <c r="N175" s="13" t="s">
+        <v>609</v>
+      </c>
+      <c r="O175" s="13" t="s">
         <v>609</v>
       </c>
       <c r="P175" s="14" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="Q175" s="5" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="176" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A176" s="4" t="s">
+        <v>313</v>
+      </c>
+      <c r="B176" s="5" t="s">
+        <v>312</v>
+      </c>
+      <c r="C176" s="5" t="s">
+        <v>242</v>
+      </c>
+      <c r="D176" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E176" s="5" t="s">
+        <v>314</v>
+      </c>
+      <c r="F176" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="G176" s="5"/>
+      <c r="H176" s="5"/>
+      <c r="I176" s="5"/>
+      <c r="J176" s="5"/>
+      <c r="K176" s="5" t="s">
+        <v>378</v>
+      </c>
+      <c r="L176" s="5"/>
+      <c r="M176" s="5"/>
+      <c r="N176" s="14" t="s">
+        <v>609</v>
+      </c>
+      <c r="O176" s="14" t="s">
+        <v>609</v>
+      </c>
+      <c r="P176" s="14" t="s">
+        <v>609</v>
+      </c>
+      <c r="Q176" s="5" t="s">
         <v>573</v>
       </c>
     </row>
-    <row r="176" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A176" s="6" t="s">
-        <v>360</v>
-      </c>
-      <c r="B176" s="6" t="s">
-        <v>361</v>
-      </c>
-      <c r="C176" s="6" t="s">
-        <v>331</v>
-      </c>
-      <c r="D176" s="6" t="s">
-        <v>331</v>
-      </c>
-      <c r="E176" s="6" t="s">
-        <v>682</v>
-      </c>
-      <c r="F176" s="6" t="s">
-        <v>332</v>
-      </c>
-      <c r="G176" s="6"/>
-      <c r="H176" s="6"/>
-      <c r="I176" s="6"/>
-      <c r="J176" s="6"/>
-      <c r="K176" s="6" t="s">
-        <v>333</v>
-      </c>
-      <c r="L176" s="2"/>
-      <c r="M176" s="2"/>
-      <c r="N176" s="16"/>
-      <c r="O176" s="16"/>
-      <c r="P176" s="16"/>
-      <c r="Q176" s="8" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="177" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A177" s="6" t="s">
         <v>360</v>
       </c>
@@ -10975,23 +11007,23 @@
         <v>361</v>
       </c>
       <c r="C177" s="6" t="s">
-        <v>641</v>
+        <v>331</v>
       </c>
       <c r="D177" s="6" t="s">
-        <v>683</v>
+        <v>331</v>
       </c>
       <c r="E177" s="6" t="s">
         <v>682</v>
       </c>
-      <c r="F177" s="6"/>
-      <c r="G177" s="6" t="s">
-        <v>408</v>
-      </c>
+      <c r="F177" s="6" t="s">
+        <v>332</v>
+      </c>
+      <c r="G177" s="6"/>
       <c r="H177" s="6"/>
       <c r="I177" s="6"/>
       <c r="J177" s="6"/>
       <c r="K177" s="6" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="L177" s="2"/>
       <c r="M177" s="2"/>
@@ -11004,39 +11036,37 @@
     </row>
     <row r="178" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A178" s="6" t="s">
-        <v>118</v>
+        <v>360</v>
       </c>
       <c r="B178" s="6" t="s">
-        <v>336</v>
+        <v>361</v>
       </c>
       <c r="C178" s="6" t="s">
-        <v>335</v>
+        <v>641</v>
       </c>
       <c r="D178" s="6" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="E178" s="6" t="s">
-        <v>681</v>
-      </c>
-      <c r="F178" s="6" t="s">
-        <v>397</v>
-      </c>
-      <c r="G178" s="7" t="s">
-        <v>337</v>
-      </c>
-      <c r="H178" s="7" t="s">
-        <v>354</v>
-      </c>
-      <c r="I178" s="7"/>
-      <c r="J178" s="7"/>
-      <c r="K178" s="7"/>
-      <c r="L178" s="7"/>
-      <c r="M178" s="7"/>
-      <c r="N178" s="15"/>
-      <c r="O178" s="15"/>
-      <c r="P178" s="15"/>
+        <v>682</v>
+      </c>
+      <c r="F178" s="6"/>
+      <c r="G178" s="6" t="s">
+        <v>408</v>
+      </c>
+      <c r="H178" s="6"/>
+      <c r="I178" s="6"/>
+      <c r="J178" s="6"/>
+      <c r="K178" s="6" t="s">
+        <v>334</v>
+      </c>
+      <c r="L178" s="2"/>
+      <c r="M178" s="2"/>
+      <c r="N178" s="16"/>
+      <c r="O178" s="16"/>
+      <c r="P178" s="16"/>
       <c r="Q178" s="8" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="179" spans="1:17" x14ac:dyDescent="0.3">
@@ -11059,10 +11089,10 @@
         <v>397</v>
       </c>
       <c r="G179" s="7" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="H179" s="7" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="I179" s="7"/>
       <c r="J179" s="7"/>
@@ -11081,10 +11111,10 @@
         <v>118</v>
       </c>
       <c r="B180" s="6" t="s">
-        <v>398</v>
+        <v>336</v>
       </c>
       <c r="C180" s="6" t="s">
-        <v>342</v>
+        <v>335</v>
       </c>
       <c r="D180" s="6" t="s">
         <v>685</v>
@@ -11093,26 +11123,24 @@
         <v>681</v>
       </c>
       <c r="F180" s="6" t="s">
-        <v>574</v>
+        <v>397</v>
       </c>
       <c r="G180" s="7" t="s">
-        <v>343</v>
+        <v>338</v>
       </c>
       <c r="H180" s="7" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="I180" s="7"/>
       <c r="J180" s="7"/>
-      <c r="K180" s="6" t="s">
-        <v>333</v>
-      </c>
-      <c r="L180" s="6"/>
-      <c r="M180" s="6"/>
-      <c r="N180" s="16"/>
-      <c r="O180" s="16"/>
-      <c r="P180" s="16"/>
-      <c r="Q180" s="6" t="s">
-        <v>341</v>
+      <c r="K180" s="7"/>
+      <c r="L180" s="7"/>
+      <c r="M180" s="7"/>
+      <c r="N180" s="15"/>
+      <c r="O180" s="15"/>
+      <c r="P180" s="15"/>
+      <c r="Q180" s="8" t="s">
+        <v>339</v>
       </c>
     </row>
     <row r="181" spans="1:17" x14ac:dyDescent="0.3">
@@ -11135,10 +11163,10 @@
         <v>574</v>
       </c>
       <c r="G181" s="7" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="H181" s="7" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="I181" s="7"/>
       <c r="J181" s="7"/>
@@ -11159,34 +11187,38 @@
         <v>118</v>
       </c>
       <c r="B182" s="6" t="s">
-        <v>615</v>
+        <v>398</v>
       </c>
       <c r="C182" s="6" t="s">
-        <v>614</v>
+        <v>342</v>
       </c>
       <c r="D182" s="6" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="E182" s="6" t="s">
         <v>681</v>
       </c>
-      <c r="F182" s="7" t="s">
-        <v>643</v>
-      </c>
-      <c r="G182" s="6" t="s">
-        <v>642</v>
-      </c>
-      <c r="H182" s="6"/>
-      <c r="I182" s="6"/>
-      <c r="J182" s="6"/>
-      <c r="K182" s="6"/>
-      <c r="L182" s="2"/>
-      <c r="M182" s="2"/>
+      <c r="F182" s="6" t="s">
+        <v>574</v>
+      </c>
+      <c r="G182" s="7" t="s">
+        <v>344</v>
+      </c>
+      <c r="H182" s="7" t="s">
+        <v>357</v>
+      </c>
+      <c r="I182" s="7"/>
+      <c r="J182" s="7"/>
+      <c r="K182" s="6" t="s">
+        <v>333</v>
+      </c>
+      <c r="L182" s="6"/>
+      <c r="M182" s="6"/>
       <c r="N182" s="16"/>
       <c r="O182" s="16"/>
       <c r="P182" s="16"/>
       <c r="Q182" s="6" t="s">
-        <v>645</v>
+        <v>341</v>
       </c>
     </row>
     <row r="183" spans="1:17" x14ac:dyDescent="0.3">
@@ -11194,10 +11226,10 @@
         <v>118</v>
       </c>
       <c r="B183" s="6" t="s">
-        <v>336</v>
+        <v>615</v>
       </c>
       <c r="C183" s="6" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="D183" s="6" t="s">
         <v>684</v>
@@ -11206,9 +11238,11 @@
         <v>681</v>
       </c>
       <c r="F183" s="7" t="s">
-        <v>646</v>
-      </c>
-      <c r="G183" s="6"/>
+        <v>643</v>
+      </c>
+      <c r="G183" s="6" t="s">
+        <v>642</v>
+      </c>
       <c r="H183" s="6"/>
       <c r="I183" s="6"/>
       <c r="J183" s="6"/>
@@ -11219,18 +11253,18 @@
       <c r="O183" s="16"/>
       <c r="P183" s="16"/>
       <c r="Q183" s="6" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
     </row>
     <row r="184" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A184" s="6" t="s">
-        <v>618</v>
+        <v>118</v>
       </c>
       <c r="B184" s="6" t="s">
-        <v>617</v>
+        <v>336</v>
       </c>
       <c r="C184" s="6" t="s">
-        <v>649</v>
+        <v>616</v>
       </c>
       <c r="D184" s="6" t="s">
         <v>684</v>
@@ -11238,8 +11272,8 @@
       <c r="E184" s="6" t="s">
         <v>681</v>
       </c>
-      <c r="F184" s="6" t="s">
-        <v>648</v>
+      <c r="F184" s="7" t="s">
+        <v>646</v>
       </c>
       <c r="G184" s="6"/>
       <c r="H184" s="6"/>
@@ -11252,18 +11286,18 @@
       <c r="O184" s="16"/>
       <c r="P184" s="16"/>
       <c r="Q184" s="6" t="s">
-        <v>647</v>
+        <v>644</v>
       </c>
     </row>
     <row r="185" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A185" s="6" t="s">
-        <v>118</v>
+        <v>618</v>
       </c>
       <c r="B185" s="6" t="s">
-        <v>620</v>
+        <v>617</v>
       </c>
       <c r="C185" s="6" t="s">
-        <v>619</v>
+        <v>649</v>
       </c>
       <c r="D185" s="6" t="s">
         <v>684</v>
@@ -11272,7 +11306,7 @@
         <v>681</v>
       </c>
       <c r="F185" s="6" t="s">
-        <v>651</v>
+        <v>648</v>
       </c>
       <c r="G185" s="6"/>
       <c r="H185" s="6"/>
@@ -11285,18 +11319,18 @@
       <c r="O185" s="16"/>
       <c r="P185" s="16"/>
       <c r="Q185" s="6" t="s">
-        <v>650</v>
+        <v>647</v>
       </c>
     </row>
     <row r="186" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A186" s="6" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B186" s="6" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="C186" s="6" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="D186" s="6" t="s">
         <v>684</v>
@@ -11305,7 +11339,7 @@
         <v>681</v>
       </c>
       <c r="F186" s="6" t="s">
-        <v>654</v>
+        <v>651</v>
       </c>
       <c r="G186" s="6"/>
       <c r="H186" s="6"/>
@@ -11318,18 +11352,18 @@
       <c r="O186" s="16"/>
       <c r="P186" s="16"/>
       <c r="Q186" s="6" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
     </row>
     <row r="187" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A187" s="6" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B187" s="6" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="C187" s="6" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="D187" s="6" t="s">
         <v>684</v>
@@ -11338,7 +11372,7 @@
         <v>681</v>
       </c>
       <c r="F187" s="6" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="G187" s="6"/>
       <c r="H187" s="6"/>
@@ -11351,18 +11385,18 @@
       <c r="O187" s="16"/>
       <c r="P187" s="16"/>
       <c r="Q187" s="6" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
     </row>
     <row r="188" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A188" s="6" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B188" s="6" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="C188" s="6" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="D188" s="6" t="s">
         <v>684</v>
@@ -11371,70 +11405,66 @@
         <v>681</v>
       </c>
       <c r="F188" s="6" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="G188" s="6"/>
       <c r="H188" s="6"/>
       <c r="I188" s="6"/>
       <c r="J188" s="6"/>
-      <c r="K188" s="6" t="s">
-        <v>657</v>
-      </c>
+      <c r="K188" s="6"/>
       <c r="L188" s="2"/>
       <c r="M188" s="2"/>
       <c r="N188" s="16"/>
       <c r="O188" s="16"/>
       <c r="P188" s="16"/>
       <c r="Q188" s="6" t="s">
-        <v>658</v>
-      </c>
-    </row>
-    <row r="189" spans="1:17" ht="95.25" x14ac:dyDescent="0.3">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="189" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A189" s="6" t="s">
-        <v>618</v>
+        <v>116</v>
       </c>
       <c r="B189" s="6" t="s">
-        <v>629</v>
+        <v>626</v>
       </c>
       <c r="C189" s="6" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="D189" s="6" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="E189" s="6" t="s">
         <v>681</v>
       </c>
       <c r="F189" s="6" t="s">
-        <v>660</v>
+        <v>656</v>
       </c>
       <c r="G189" s="6"/>
       <c r="H189" s="6"/>
       <c r="I189" s="6"/>
       <c r="J189" s="6"/>
       <c r="K189" s="6" t="s">
-        <v>661</v>
+        <v>657</v>
       </c>
       <c r="L189" s="2"/>
-      <c r="M189" s="21" t="s">
-        <v>662</v>
-      </c>
+      <c r="M189" s="2"/>
       <c r="N189" s="16"/>
       <c r="O189" s="16"/>
       <c r="P189" s="16"/>
       <c r="Q189" s="6" t="s">
-        <v>659</v>
-      </c>
-    </row>
-    <row r="190" spans="1:17" ht="162.75" x14ac:dyDescent="0.3">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="190" spans="1:17" ht="95.25" x14ac:dyDescent="0.3">
       <c r="A190" s="6" t="s">
         <v>618</v>
       </c>
       <c r="B190" s="6" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="C190" s="6" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="D190" s="6" t="s">
         <v>685</v>
@@ -11443,35 +11473,35 @@
         <v>681</v>
       </c>
       <c r="F190" s="6" t="s">
-        <v>663</v>
+        <v>660</v>
       </c>
       <c r="G190" s="6"/>
       <c r="H190" s="6"/>
       <c r="I190" s="6"/>
       <c r="J190" s="6"/>
-      <c r="K190" s="5" t="s">
-        <v>664</v>
+      <c r="K190" s="6" t="s">
+        <v>661</v>
       </c>
       <c r="L190" s="2"/>
       <c r="M190" s="21" t="s">
-        <v>666</v>
+        <v>662</v>
       </c>
       <c r="N190" s="16"/>
       <c r="O190" s="16"/>
       <c r="P190" s="16"/>
       <c r="Q190" s="6" t="s">
-        <v>665</v>
-      </c>
-    </row>
-    <row r="191" spans="1:17" ht="135.75" x14ac:dyDescent="0.3">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="191" spans="1:17" ht="162.75" x14ac:dyDescent="0.3">
       <c r="A191" s="6" t="s">
-        <v>117</v>
+        <v>618</v>
       </c>
       <c r="B191" s="6" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="C191" s="6" t="s">
-        <v>631</v>
+        <v>628</v>
       </c>
       <c r="D191" s="6" t="s">
         <v>685</v>
@@ -11491,24 +11521,24 @@
       </c>
       <c r="L191" s="2"/>
       <c r="M191" s="21" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="N191" s="16"/>
       <c r="O191" s="16"/>
       <c r="P191" s="16"/>
       <c r="Q191" s="6" t="s">
-        <v>667</v>
-      </c>
-    </row>
-    <row r="192" spans="1:17" ht="149.25" x14ac:dyDescent="0.3">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="192" spans="1:17" ht="135.75" x14ac:dyDescent="0.3">
       <c r="A192" s="6" t="s">
         <v>117</v>
       </c>
       <c r="B192" s="6" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="C192" s="6" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="D192" s="6" t="s">
         <v>685</v>
@@ -11517,35 +11547,35 @@
         <v>681</v>
       </c>
       <c r="F192" s="6" t="s">
-        <v>676</v>
+        <v>663</v>
       </c>
       <c r="G192" s="6"/>
       <c r="H192" s="6"/>
       <c r="I192" s="6"/>
       <c r="J192" s="6"/>
-      <c r="K192" s="6" t="s">
-        <v>661</v>
+      <c r="K192" s="5" t="s">
+        <v>664</v>
       </c>
       <c r="L192" s="2"/>
       <c r="M192" s="21" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="N192" s="16"/>
       <c r="O192" s="16"/>
       <c r="P192" s="16"/>
       <c r="Q192" s="6" t="s">
-        <v>669</v>
-      </c>
-    </row>
-    <row r="193" spans="1:17" ht="27" x14ac:dyDescent="0.3">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="193" spans="1:17" ht="149.25" x14ac:dyDescent="0.3">
       <c r="A193" s="6" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B193" s="6" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="C193" s="6" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="D193" s="6" t="s">
         <v>685</v>
@@ -11553,34 +11583,36 @@
       <c r="E193" s="6" t="s">
         <v>681</v>
       </c>
-      <c r="F193" s="6"/>
-      <c r="G193" s="7" t="s">
-        <v>671</v>
-      </c>
+      <c r="F193" s="6" t="s">
+        <v>676</v>
+      </c>
+      <c r="G193" s="6"/>
       <c r="H193" s="6"/>
       <c r="I193" s="6"/>
       <c r="J193" s="6"/>
       <c r="K193" s="6" t="s">
-        <v>672</v>
+        <v>661</v>
       </c>
       <c r="L193" s="2"/>
-      <c r="M193" s="2"/>
+      <c r="M193" s="21" t="s">
+        <v>670</v>
+      </c>
       <c r="N193" s="16"/>
       <c r="O193" s="16"/>
       <c r="P193" s="16"/>
       <c r="Q193" s="6" t="s">
-        <v>673</v>
-      </c>
-    </row>
-    <row r="194" spans="1:17" ht="54.75" x14ac:dyDescent="0.3">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="194" spans="1:17" ht="27" x14ac:dyDescent="0.3">
       <c r="A194" s="6" t="s">
-        <v>618</v>
+        <v>118</v>
       </c>
       <c r="B194" s="6" t="s">
-        <v>629</v>
+        <v>637</v>
       </c>
       <c r="C194" s="6" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="D194" s="6" t="s">
         <v>685</v>
@@ -11588,36 +11620,34 @@
       <c r="E194" s="6" t="s">
         <v>681</v>
       </c>
-      <c r="F194" s="6" t="s">
-        <v>675</v>
-      </c>
-      <c r="G194" s="6"/>
+      <c r="F194" s="6"/>
+      <c r="G194" s="7" t="s">
+        <v>671</v>
+      </c>
       <c r="H194" s="6"/>
       <c r="I194" s="6"/>
       <c r="J194" s="6"/>
       <c r="K194" s="6" t="s">
-        <v>661</v>
+        <v>672</v>
       </c>
       <c r="L194" s="2"/>
-      <c r="M194" s="21" t="s">
-        <v>677</v>
-      </c>
+      <c r="M194" s="2"/>
       <c r="N194" s="16"/>
       <c r="O194" s="16"/>
       <c r="P194" s="16"/>
       <c r="Q194" s="6" t="s">
-        <v>674</v>
-      </c>
-    </row>
-    <row r="195" spans="1:17" ht="27.75" x14ac:dyDescent="0.3">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="195" spans="1:17" ht="54.75" x14ac:dyDescent="0.3">
       <c r="A195" s="6" t="s">
-        <v>117</v>
+        <v>618</v>
       </c>
       <c r="B195" s="6" t="s">
-        <v>639</v>
+        <v>629</v>
       </c>
       <c r="C195" s="6" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="D195" s="6" t="s">
         <v>685</v>
@@ -11626,38 +11656,75 @@
         <v>681</v>
       </c>
       <c r="F195" s="6" t="s">
-        <v>678</v>
+        <v>675</v>
       </c>
       <c r="G195" s="6"/>
       <c r="H195" s="6"/>
       <c r="I195" s="6"/>
       <c r="J195" s="6"/>
       <c r="K195" s="6" t="s">
-        <v>680</v>
+        <v>661</v>
       </c>
       <c r="L195" s="2"/>
       <c r="M195" s="21" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="N195" s="16"/>
       <c r="O195" s="16"/>
       <c r="P195" s="16"/>
       <c r="Q195" s="6" t="s">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="196" spans="1:17" ht="27.75" x14ac:dyDescent="0.3">
+      <c r="A196" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="B196" s="6" t="s">
+        <v>639</v>
+      </c>
+      <c r="C196" s="6" t="s">
+        <v>638</v>
+      </c>
+      <c r="D196" s="6" t="s">
+        <v>685</v>
+      </c>
+      <c r="E196" s="6" t="s">
+        <v>681</v>
+      </c>
+      <c r="F196" s="6" t="s">
+        <v>678</v>
+      </c>
+      <c r="G196" s="6"/>
+      <c r="H196" s="6"/>
+      <c r="I196" s="6"/>
+      <c r="J196" s="6"/>
+      <c r="K196" s="6" t="s">
+        <v>680</v>
+      </c>
+      <c r="L196" s="2"/>
+      <c r="M196" s="21" t="s">
+        <v>679</v>
+      </c>
+      <c r="N196" s="16"/>
+      <c r="O196" s="16"/>
+      <c r="P196" s="16"/>
+      <c r="Q196" s="6" t="s">
         <v>640</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="B1:Q181" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="B1:Q182" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="Q2:Q175">
+  <conditionalFormatting sqref="Q2:Q176">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <hyperlinks>
-    <hyperlink ref="Q178" r:id="rId1" xr:uid="{E8A5EE79-38DC-470C-9E4B-60B8DB179166}"/>
-    <hyperlink ref="Q176" r:id="rId2" xr:uid="{B514AFC6-F2CC-453E-A7EE-749BE8F59F63}"/>
-    <hyperlink ref="Q177" r:id="rId3" xr:uid="{D2C8DCF1-2A86-40FB-A718-5DFF8C67103B}"/>
-    <hyperlink ref="Q179" r:id="rId4" xr:uid="{2526EBF2-78DF-4B4D-A609-DDD4E216E820}"/>
-    <hyperlink ref="Q100" r:id="rId5" xr:uid="{05B60FA0-37BF-4BDF-A54A-C6015B78419C}"/>
+    <hyperlink ref="Q179" r:id="rId1" xr:uid="{E8A5EE79-38DC-470C-9E4B-60B8DB179166}"/>
+    <hyperlink ref="Q177" r:id="rId2" xr:uid="{B514AFC6-F2CC-453E-A7EE-749BE8F59F63}"/>
+    <hyperlink ref="Q178" r:id="rId3" xr:uid="{D2C8DCF1-2A86-40FB-A718-5DFF8C67103B}"/>
+    <hyperlink ref="Q180" r:id="rId4" xr:uid="{2526EBF2-78DF-4B4D-A609-DDD4E216E820}"/>
+    <hyperlink ref="Q101" r:id="rId5" xr:uid="{05B60FA0-37BF-4BDF-A54A-C6015B78419C}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/app/convert/forest_sample_template.xlsx
+++ b/app/convert/forest_sample_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TAX-JUNGYOON\forest-app\app\convert\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7913A58-A22F-4036-94F2-75BE4A0387B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DEE253F-BA92-4190-A3D5-807CF4286F5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="658" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,14 +16,14 @@
     <sheet name="샘플" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">샘플!$B$1:$Q$182</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">샘플!$B$1:$R$182</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2364" uniqueCount="736">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2367" uniqueCount="738">
   <si>
     <t>시설명</t>
   </si>
@@ -1859,10 +1859,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>지역주민 우선예약정책</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>숲속의집(복층형) : 02, 05
 숲속의집(단층형) : 06, 08, 10
 산림휴양관(4인실) : 104, 107, 204, 206
@@ -2748,6 +2744,18 @@
   </si>
   <si>
     <t>https://www.foresttrip.go.kr/indvz/main.do?hmpgId=0306</t>
+  </si>
+  <si>
+    <t>지역주민 우선객실</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>지역주민 우선오픈</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>매월 07일 14시</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -3241,7 +3249,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q196"/>
+  <dimension ref="A1:R196"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13" style="18" bestFit="1" customWidth="1"/>
@@ -3253,15 +3261,15 @@
     <col min="7" max="7" width="47.25" style="18" customWidth="1"/>
     <col min="8" max="8" width="28.375" style="18" customWidth="1"/>
     <col min="9" max="9" width="15.25" style="18" customWidth="1"/>
-    <col min="10" max="10" width="55.375" style="18" customWidth="1"/>
-    <col min="11" max="11" width="36.875" style="18" customWidth="1"/>
-    <col min="12" max="12" width="33.375" style="1" customWidth="1"/>
-    <col min="13" max="13" width="36.875" style="1" customWidth="1"/>
-    <col min="14" max="16" width="36.875" style="17" customWidth="1"/>
-    <col min="17" max="17" width="65.375" style="18" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="55.375" style="18" customWidth="1"/>
+    <col min="12" max="12" width="36.875" style="18" customWidth="1"/>
+    <col min="13" max="13" width="33.375" style="1" customWidth="1"/>
+    <col min="14" max="14" width="36.875" style="1" customWidth="1"/>
+    <col min="15" max="17" width="36.875" style="17" customWidth="1"/>
+    <col min="18" max="18" width="65.375" style="18" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
         <v>100</v>
       </c>
@@ -3292,29 +3300,32 @@
       <c r="J1" s="6" t="s">
         <v>351</v>
       </c>
-      <c r="K1" s="16" t="s">
+      <c r="K1" s="6" t="s">
+        <v>736</v>
+      </c>
+      <c r="L1" s="16" t="s">
         <v>329</v>
       </c>
-      <c r="L1" s="3" t="s">
-        <v>575</v>
-      </c>
       <c r="M1" s="3" t="s">
-        <v>577</v>
-      </c>
-      <c r="N1" s="16" t="s">
+        <v>735</v>
+      </c>
+      <c r="N1" s="3" t="s">
+        <v>576</v>
+      </c>
+      <c r="O1" s="16" t="s">
+        <v>602</v>
+      </c>
+      <c r="P1" s="16" t="s">
         <v>603</v>
       </c>
-      <c r="O1" s="16" t="s">
+      <c r="Q1" s="16" t="s">
         <v>604</v>
       </c>
-      <c r="P1" s="16" t="s">
-        <v>605</v>
-      </c>
-      <c r="Q1" s="6" t="s">
+      <c r="R1" s="6" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>114</v>
       </c>
@@ -3331,7 +3342,7 @@
         <v>113</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="G2" s="5" t="s">
         <v>349</v>
@@ -3345,25 +3356,26 @@
       <c r="J2" s="5" t="s">
         <v>353</v>
       </c>
-      <c r="K2" s="5" t="s">
+      <c r="K2" s="5"/>
+      <c r="L2" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="L2" s="5"/>
       <c r="M2" s="5"/>
-      <c r="N2" s="13" t="s">
-        <v>607</v>
-      </c>
+      <c r="N2" s="5"/>
       <c r="O2" s="13" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="P2" s="13" t="s">
-        <v>607</v>
-      </c>
-      <c r="Q2" s="5" t="s">
+        <v>606</v>
+      </c>
+      <c r="Q2" s="13" t="s">
+        <v>606</v>
+      </c>
+      <c r="R2" s="5" t="s">
         <v>413</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>114</v>
       </c>
@@ -3388,25 +3400,26 @@
       </c>
       <c r="I3" s="5"/>
       <c r="J3" s="5"/>
-      <c r="K3" s="5" t="s">
+      <c r="K3" s="5"/>
+      <c r="L3" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="L3" s="5"/>
       <c r="M3" s="5"/>
-      <c r="N3" s="14" t="s">
-        <v>607</v>
-      </c>
+      <c r="N3" s="5"/>
       <c r="O3" s="14" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="P3" s="14" t="s">
-        <v>609</v>
-      </c>
-      <c r="Q3" s="5" t="s">
+        <v>608</v>
+      </c>
+      <c r="Q3" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="R3" s="5" t="s">
         <v>411</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>114</v>
       </c>
@@ -3423,7 +3436,7 @@
         <v>113</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="G4" s="5" t="s">
         <v>349</v>
@@ -3437,25 +3450,26 @@
       <c r="J4" s="5" t="s">
         <v>353</v>
       </c>
-      <c r="K4" s="5" t="s">
+      <c r="K4" s="5"/>
+      <c r="L4" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="L4" s="5"/>
       <c r="M4" s="5"/>
-      <c r="N4" s="13" t="s">
-        <v>607</v>
-      </c>
+      <c r="N4" s="5"/>
       <c r="O4" s="13" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="P4" s="13" t="s">
-        <v>607</v>
-      </c>
-      <c r="Q4" s="5" t="s">
+        <v>608</v>
+      </c>
+      <c r="Q4" s="13" t="s">
+        <v>606</v>
+      </c>
+      <c r="R4" s="5" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
         <v>114</v>
       </c>
@@ -3472,7 +3486,7 @@
         <v>113</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="G5" s="5" t="s">
         <v>349</v>
@@ -3486,25 +3500,26 @@
       <c r="J5" s="5" t="s">
         <v>353</v>
       </c>
-      <c r="K5" s="5" t="s">
+      <c r="K5" s="5"/>
+      <c r="L5" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="L5" s="5"/>
       <c r="M5" s="5"/>
-      <c r="N5" s="13" t="s">
-        <v>607</v>
-      </c>
-      <c r="O5" s="14" t="s">
-        <v>611</v>
-      </c>
-      <c r="P5" s="13" t="s">
-        <v>607</v>
-      </c>
-      <c r="Q5" s="5" t="s">
+      <c r="N5" s="5"/>
+      <c r="O5" s="13" t="s">
+        <v>606</v>
+      </c>
+      <c r="P5" s="14" t="s">
+        <v>610</v>
+      </c>
+      <c r="Q5" s="13" t="s">
+        <v>606</v>
+      </c>
+      <c r="R5" s="5" t="s">
         <v>412</v>
       </c>
     </row>
-    <row r="6" spans="1:17" ht="40.5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
         <v>114</v>
       </c>
@@ -3521,7 +3536,7 @@
         <v>113</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="G6" s="5" t="s">
         <v>349</v>
@@ -3535,27 +3550,28 @@
       <c r="J6" s="5" t="s">
         <v>353</v>
       </c>
-      <c r="K6" s="5" t="s">
+      <c r="K6" s="5"/>
+      <c r="L6" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="L6" s="5"/>
-      <c r="M6" s="11" t="s">
-        <v>578</v>
-      </c>
-      <c r="N6" s="13" t="s">
-        <v>607</v>
+      <c r="M6" s="5"/>
+      <c r="N6" s="11" t="s">
+        <v>577</v>
       </c>
       <c r="O6" s="13" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="P6" s="13" t="s">
-        <v>609</v>
-      </c>
-      <c r="Q6" s="5" t="s">
+        <v>608</v>
+      </c>
+      <c r="Q6" s="13" t="s">
+        <v>608</v>
+      </c>
+      <c r="R6" s="5" t="s">
         <v>409</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
         <v>114</v>
       </c>
@@ -3572,7 +3588,7 @@
         <v>113</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="G7" s="5" t="s">
         <v>349</v>
@@ -3586,25 +3602,26 @@
       <c r="J7" s="5" t="s">
         <v>353</v>
       </c>
-      <c r="K7" s="5" t="s">
+      <c r="K7" s="5"/>
+      <c r="L7" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="L7" s="5"/>
       <c r="M7" s="5"/>
-      <c r="N7" s="13" t="s">
-        <v>609</v>
-      </c>
+      <c r="N7" s="5"/>
       <c r="O7" s="13" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="P7" s="13" t="s">
-        <v>609</v>
-      </c>
-      <c r="Q7" s="5" t="s">
+        <v>606</v>
+      </c>
+      <c r="Q7" s="13" t="s">
+        <v>608</v>
+      </c>
+      <c r="R7" s="5" t="s">
         <v>414</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
         <v>3</v>
       </c>
@@ -3621,7 +3638,7 @@
         <v>113</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="G8" s="5" t="s">
         <v>349</v>
@@ -3635,25 +3652,26 @@
       <c r="J8" s="5" t="s">
         <v>353</v>
       </c>
-      <c r="K8" s="5" t="s">
+      <c r="K8" s="5"/>
+      <c r="L8" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="L8" s="5"/>
       <c r="M8" s="5"/>
-      <c r="N8" s="13" t="s">
-        <v>607</v>
-      </c>
+      <c r="N8" s="5"/>
       <c r="O8" s="13" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="P8" s="13" t="s">
-        <v>607</v>
-      </c>
-      <c r="Q8" s="5" t="s">
+        <v>608</v>
+      </c>
+      <c r="Q8" s="13" t="s">
+        <v>606</v>
+      </c>
+      <c r="R8" s="5" t="s">
         <v>417</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
         <v>3</v>
       </c>
@@ -3670,7 +3688,7 @@
         <v>113</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="G9" s="5" t="s">
         <v>349</v>
@@ -3684,25 +3702,26 @@
       <c r="J9" s="5" t="s">
         <v>353</v>
       </c>
-      <c r="K9" s="5" t="s">
+      <c r="K9" s="5"/>
+      <c r="L9" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="L9" s="5"/>
       <c r="M9" s="5"/>
-      <c r="N9" s="13" t="s">
-        <v>609</v>
-      </c>
+      <c r="N9" s="5"/>
       <c r="O9" s="13" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="P9" s="13" t="s">
-        <v>607</v>
-      </c>
-      <c r="Q9" s="5" t="s">
+        <v>608</v>
+      </c>
+      <c r="Q9" s="13" t="s">
+        <v>606</v>
+      </c>
+      <c r="R9" s="5" t="s">
         <v>416</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
         <v>3</v>
       </c>
@@ -3719,7 +3738,7 @@
         <v>113</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="G10" s="5" t="s">
         <v>349</v>
@@ -3733,25 +3752,26 @@
       <c r="J10" s="5" t="s">
         <v>353</v>
       </c>
-      <c r="K10" s="5" t="s">
+      <c r="K10" s="5"/>
+      <c r="L10" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="L10" s="5"/>
       <c r="M10" s="5"/>
-      <c r="N10" s="13" t="s">
-        <v>607</v>
-      </c>
+      <c r="N10" s="5"/>
       <c r="O10" s="13" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="P10" s="13" t="s">
-        <v>607</v>
-      </c>
-      <c r="Q10" s="5" t="s">
+        <v>608</v>
+      </c>
+      <c r="Q10" s="13" t="s">
+        <v>606</v>
+      </c>
+      <c r="R10" s="5" t="s">
         <v>419</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
         <v>3</v>
       </c>
@@ -3768,7 +3788,7 @@
         <v>113</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="G11" s="5" t="s">
         <v>349</v>
@@ -3782,25 +3802,26 @@
       <c r="J11" s="5" t="s">
         <v>353</v>
       </c>
-      <c r="K11" s="5" t="s">
+      <c r="K11" s="5"/>
+      <c r="L11" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="L11" s="5"/>
       <c r="M11" s="5"/>
-      <c r="N11" s="13" t="s">
-        <v>607</v>
-      </c>
+      <c r="N11" s="5"/>
       <c r="O11" s="13" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="P11" s="13" t="s">
-        <v>609</v>
-      </c>
-      <c r="Q11" s="5" t="s">
+        <v>606</v>
+      </c>
+      <c r="Q11" s="13" t="s">
+        <v>608</v>
+      </c>
+      <c r="R11" s="5" t="s">
         <v>421</v>
       </c>
     </row>
-    <row r="12" spans="1:17" ht="94.5" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" ht="94.5" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
         <v>3</v>
       </c>
@@ -3817,7 +3838,7 @@
         <v>113</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="G12" s="5" t="s">
         <v>349</v>
@@ -3831,27 +3852,28 @@
       <c r="J12" s="5" t="s">
         <v>353</v>
       </c>
-      <c r="K12" s="5" t="s">
+      <c r="K12" s="5"/>
+      <c r="L12" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="L12" s="5"/>
-      <c r="M12" s="10" t="s">
-        <v>582</v>
-      </c>
-      <c r="N12" s="13" t="s">
-        <v>607</v>
+      <c r="M12" s="5"/>
+      <c r="N12" s="10" t="s">
+        <v>581</v>
       </c>
       <c r="O12" s="13" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="P12" s="13" t="s">
-        <v>607</v>
-      </c>
-      <c r="Q12" s="5" t="s">
+        <v>606</v>
+      </c>
+      <c r="Q12" s="13" t="s">
+        <v>606</v>
+      </c>
+      <c r="R12" s="5" t="s">
         <v>420</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
         <v>3</v>
       </c>
@@ -3868,7 +3890,7 @@
         <v>113</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="G13" s="5" t="s">
         <v>349</v>
@@ -3882,25 +3904,26 @@
       <c r="J13" s="5" t="s">
         <v>353</v>
       </c>
-      <c r="K13" s="5" t="s">
+      <c r="K13" s="5"/>
+      <c r="L13" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="L13" s="5"/>
       <c r="M13" s="5"/>
-      <c r="N13" s="13" t="s">
-        <v>607</v>
-      </c>
+      <c r="N13" s="5"/>
       <c r="O13" s="13" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="P13" s="13" t="s">
-        <v>607</v>
-      </c>
-      <c r="Q13" s="5" t="s">
+        <v>608</v>
+      </c>
+      <c r="Q13" s="13" t="s">
+        <v>606</v>
+      </c>
+      <c r="R13" s="5" t="s">
         <v>424</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
         <v>3</v>
       </c>
@@ -3917,7 +3940,7 @@
         <v>113</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="G14" s="5" t="s">
         <v>349</v>
@@ -3931,25 +3954,26 @@
       <c r="J14" s="5" t="s">
         <v>353</v>
       </c>
-      <c r="K14" s="5" t="s">
+      <c r="K14" s="5"/>
+      <c r="L14" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="L14" s="5"/>
       <c r="M14" s="5"/>
-      <c r="N14" s="13" t="s">
-        <v>607</v>
-      </c>
+      <c r="N14" s="5"/>
       <c r="O14" s="13" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="P14" s="13" t="s">
-        <v>607</v>
-      </c>
-      <c r="Q14" s="5" t="s">
+        <v>608</v>
+      </c>
+      <c r="Q14" s="13" t="s">
+        <v>606</v>
+      </c>
+      <c r="R14" s="5" t="s">
         <v>415</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
         <v>3</v>
       </c>
@@ -3966,7 +3990,7 @@
         <v>113</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="G15" s="5" t="s">
         <v>349</v>
@@ -3980,25 +4004,26 @@
       <c r="J15" s="5" t="s">
         <v>353</v>
       </c>
-      <c r="K15" s="5" t="s">
+      <c r="K15" s="5"/>
+      <c r="L15" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="L15" s="5"/>
       <c r="M15" s="5"/>
-      <c r="N15" s="13" t="s">
-        <v>607</v>
-      </c>
+      <c r="N15" s="5"/>
       <c r="O15" s="13" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="P15" s="13" t="s">
-        <v>609</v>
-      </c>
-      <c r="Q15" s="5" t="s">
+        <v>606</v>
+      </c>
+      <c r="Q15" s="13" t="s">
+        <v>608</v>
+      </c>
+      <c r="R15" s="5" t="s">
         <v>422</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
         <v>3</v>
       </c>
@@ -4015,7 +4040,7 @@
         <v>113</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="G16" s="5" t="s">
         <v>349</v>
@@ -4029,25 +4054,26 @@
       <c r="J16" s="5" t="s">
         <v>353</v>
       </c>
-      <c r="K16" s="5" t="s">
+      <c r="K16" s="5"/>
+      <c r="L16" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="L16" s="5"/>
       <c r="M16" s="5"/>
-      <c r="N16" s="13" t="s">
-        <v>607</v>
-      </c>
+      <c r="N16" s="5"/>
       <c r="O16" s="13" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="P16" s="13" t="s">
-        <v>607</v>
-      </c>
-      <c r="Q16" s="5" t="s">
+        <v>606</v>
+      </c>
+      <c r="Q16" s="13" t="s">
+        <v>606</v>
+      </c>
+      <c r="R16" s="5" t="s">
         <v>425</v>
       </c>
     </row>
-    <row r="17" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
         <v>3</v>
       </c>
@@ -4064,7 +4090,7 @@
         <v>113</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="G17" s="5" t="s">
         <v>349</v>
@@ -4078,25 +4104,26 @@
       <c r="J17" s="5" t="s">
         <v>353</v>
       </c>
-      <c r="K17" s="5" t="s">
+      <c r="K17" s="5"/>
+      <c r="L17" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="L17" s="5"/>
       <c r="M17" s="5"/>
-      <c r="N17" s="13" t="s">
-        <v>607</v>
-      </c>
+      <c r="N17" s="5"/>
       <c r="O17" s="13" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="P17" s="13" t="s">
-        <v>607</v>
-      </c>
-      <c r="Q17" s="5" t="s">
+        <v>606</v>
+      </c>
+      <c r="Q17" s="13" t="s">
+        <v>606</v>
+      </c>
+      <c r="R17" s="5" t="s">
         <v>418</v>
       </c>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
         <v>3</v>
       </c>
@@ -4113,7 +4140,7 @@
         <v>113</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="G18" s="5" t="s">
         <v>349</v>
@@ -4127,25 +4154,26 @@
       <c r="J18" s="5" t="s">
         <v>353</v>
       </c>
-      <c r="K18" s="5" t="s">
+      <c r="K18" s="5"/>
+      <c r="L18" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="L18" s="5"/>
       <c r="M18" s="5"/>
-      <c r="N18" s="13" t="s">
-        <v>607</v>
-      </c>
+      <c r="N18" s="5"/>
       <c r="O18" s="13" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="P18" s="13" t="s">
-        <v>607</v>
-      </c>
-      <c r="Q18" s="5" t="s">
+        <v>606</v>
+      </c>
+      <c r="Q18" s="13" t="s">
+        <v>606</v>
+      </c>
+      <c r="R18" s="5" t="s">
         <v>423</v>
       </c>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
         <v>3</v>
       </c>
@@ -4162,7 +4190,7 @@
         <v>113</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="G19" s="5" t="s">
         <v>349</v>
@@ -4176,25 +4204,26 @@
       <c r="J19" s="5" t="s">
         <v>353</v>
       </c>
-      <c r="K19" s="5" t="s">
+      <c r="K19" s="5"/>
+      <c r="L19" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="L19" s="5"/>
       <c r="M19" s="5"/>
-      <c r="N19" s="13" t="s">
-        <v>607</v>
-      </c>
+      <c r="N19" s="5"/>
       <c r="O19" s="13" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="P19" s="13" t="s">
-        <v>607</v>
-      </c>
-      <c r="Q19" s="5" t="s">
+        <v>606</v>
+      </c>
+      <c r="Q19" s="13" t="s">
+        <v>606</v>
+      </c>
+      <c r="R19" s="5" t="s">
         <v>427</v>
       </c>
     </row>
-    <row r="20" spans="1:17" ht="148.5" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" ht="148.5" x14ac:dyDescent="0.3">
       <c r="A20" s="4" t="s">
         <v>3</v>
       </c>
@@ -4211,7 +4240,7 @@
         <v>113</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="G20" s="5" t="s">
         <v>349</v>
@@ -4225,35 +4254,36 @@
       <c r="J20" s="5" t="s">
         <v>353</v>
       </c>
-      <c r="K20" s="5" t="s">
+      <c r="K20" s="5"/>
+      <c r="L20" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="L20" s="5"/>
-      <c r="M20" s="10" t="s">
-        <v>581</v>
-      </c>
-      <c r="N20" s="13" t="s">
-        <v>609</v>
-      </c>
-      <c r="O20" s="14" t="s">
-        <v>611</v>
-      </c>
-      <c r="P20" s="13" t="s">
-        <v>607</v>
-      </c>
-      <c r="Q20" s="5" t="s">
+      <c r="M20" s="5"/>
+      <c r="N20" s="10" t="s">
+        <v>580</v>
+      </c>
+      <c r="O20" s="13" t="s">
+        <v>608</v>
+      </c>
+      <c r="P20" s="14" t="s">
+        <v>610</v>
+      </c>
+      <c r="Q20" s="13" t="s">
+        <v>606</v>
+      </c>
+      <c r="R20" s="5" t="s">
         <v>426</v>
       </c>
     </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
+        <v>731</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>733</v>
+      </c>
+      <c r="C21" s="5" t="s">
         <v>732</v>
-      </c>
-      <c r="B21" s="5" t="s">
-        <v>734</v>
-      </c>
-      <c r="C21" s="5" t="s">
-        <v>733</v>
       </c>
       <c r="D21" s="5" t="s">
         <v>112</v>
@@ -4262,7 +4292,7 @@
         <v>113</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="G21" s="5" t="s">
         <v>349</v>
@@ -4276,19 +4306,20 @@
       <c r="J21" s="5" t="s">
         <v>353</v>
       </c>
-      <c r="K21" s="5" t="s">
+      <c r="K21" s="5"/>
+      <c r="L21" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="L21" s="5"/>
-      <c r="M21" s="10"/>
-      <c r="N21" s="13"/>
-      <c r="O21" s="14"/>
-      <c r="P21" s="13"/>
-      <c r="Q21" s="5" t="s">
-        <v>735</v>
-      </c>
-    </row>
-    <row r="22" spans="1:17" ht="54" x14ac:dyDescent="0.3">
+      <c r="M21" s="5"/>
+      <c r="N21" s="10"/>
+      <c r="O21" s="13"/>
+      <c r="P21" s="14"/>
+      <c r="Q21" s="13"/>
+      <c r="R21" s="5" t="s">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" ht="54" x14ac:dyDescent="0.3">
       <c r="A22" s="4" t="s">
         <v>101</v>
       </c>
@@ -4305,7 +4336,7 @@
         <v>113</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="G22" s="5" t="s">
         <v>349</v>
@@ -4319,27 +4350,28 @@
       <c r="J22" s="5" t="s">
         <v>353</v>
       </c>
-      <c r="K22" s="5" t="s">
+      <c r="K22" s="5"/>
+      <c r="L22" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="L22" s="5"/>
-      <c r="M22" s="5" t="s">
-        <v>718</v>
-      </c>
-      <c r="N22" s="14" t="s">
-        <v>611</v>
-      </c>
-      <c r="O22" s="13" t="s">
-        <v>607</v>
+      <c r="M22" s="5"/>
+      <c r="N22" s="5" t="s">
+        <v>717</v>
+      </c>
+      <c r="O22" s="14" t="s">
+        <v>610</v>
       </c>
       <c r="P22" s="13" t="s">
-        <v>607</v>
-      </c>
-      <c r="Q22" s="5" t="s">
+        <v>606</v>
+      </c>
+      <c r="Q22" s="13" t="s">
+        <v>606</v>
+      </c>
+      <c r="R22" s="5" t="s">
         <v>430</v>
       </c>
     </row>
-    <row r="23" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
         <v>101</v>
       </c>
@@ -4356,7 +4388,7 @@
         <v>113</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="G23" s="5" t="s">
         <v>349</v>
@@ -4370,25 +4402,26 @@
       <c r="J23" s="5" t="s">
         <v>353</v>
       </c>
-      <c r="K23" s="5" t="s">
+      <c r="K23" s="5"/>
+      <c r="L23" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="L23" s="5"/>
       <c r="M23" s="5"/>
-      <c r="N23" s="13" t="s">
-        <v>609</v>
-      </c>
+      <c r="N23" s="5"/>
       <c r="O23" s="13" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="P23" s="13" t="s">
-        <v>609</v>
-      </c>
-      <c r="Q23" s="5" t="s">
+        <v>606</v>
+      </c>
+      <c r="Q23" s="13" t="s">
+        <v>608</v>
+      </c>
+      <c r="R23" s="5" t="s">
         <v>429</v>
       </c>
     </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A24" s="4" t="s">
         <v>101</v>
       </c>
@@ -4405,7 +4438,7 @@
         <v>113</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="G24" s="5" t="s">
         <v>349</v>
@@ -4419,25 +4452,26 @@
       <c r="J24" s="5" t="s">
         <v>353</v>
       </c>
-      <c r="K24" s="5" t="s">
+      <c r="K24" s="5"/>
+      <c r="L24" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="L24" s="5"/>
       <c r="M24" s="5"/>
-      <c r="N24" s="13" t="s">
-        <v>609</v>
-      </c>
-      <c r="O24" s="14" t="s">
-        <v>611</v>
-      </c>
-      <c r="P24" s="13" t="s">
-        <v>609</v>
-      </c>
-      <c r="Q24" s="5" t="s">
+      <c r="N24" s="5"/>
+      <c r="O24" s="13" t="s">
+        <v>608</v>
+      </c>
+      <c r="P24" s="14" t="s">
+        <v>610</v>
+      </c>
+      <c r="Q24" s="13" t="s">
+        <v>608</v>
+      </c>
+      <c r="R24" s="5" t="s">
         <v>428</v>
       </c>
     </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A25" s="4" t="s">
         <v>115</v>
       </c>
@@ -4454,7 +4488,7 @@
         <v>113</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="G25" s="5" t="s">
         <v>349</v>
@@ -4468,25 +4502,26 @@
       <c r="J25" s="5" t="s">
         <v>353</v>
       </c>
-      <c r="K25" s="5" t="s">
+      <c r="K25" s="5"/>
+      <c r="L25" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="L25" s="5"/>
       <c r="M25" s="5"/>
-      <c r="N25" s="14" t="s">
-        <v>609</v>
-      </c>
+      <c r="N25" s="5"/>
       <c r="O25" s="14" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="P25" s="14" t="s">
-        <v>609</v>
-      </c>
-      <c r="Q25" s="5" t="s">
+        <v>608</v>
+      </c>
+      <c r="Q25" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="R25" s="5" t="s">
         <v>431</v>
       </c>
     </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A26" s="4" t="s">
         <v>115</v>
       </c>
@@ -4503,7 +4538,7 @@
         <v>113</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="G26" s="5" t="s">
         <v>349</v>
@@ -4517,25 +4552,26 @@
       <c r="J26" s="5" t="s">
         <v>353</v>
       </c>
-      <c r="K26" s="5" t="s">
+      <c r="K26" s="5"/>
+      <c r="L26" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="L26" s="5"/>
       <c r="M26" s="5"/>
-      <c r="N26" s="13" t="s">
-        <v>609</v>
-      </c>
+      <c r="N26" s="5"/>
       <c r="O26" s="13" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="P26" s="13" t="s">
-        <v>607</v>
-      </c>
-      <c r="Q26" s="5" t="s">
+        <v>606</v>
+      </c>
+      <c r="Q26" s="13" t="s">
+        <v>606</v>
+      </c>
+      <c r="R26" s="5" t="s">
         <v>432</v>
       </c>
     </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A27" s="4" t="s">
         <v>115</v>
       </c>
@@ -4552,7 +4588,7 @@
         <v>113</v>
       </c>
       <c r="F27" s="5" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="G27" s="5" t="s">
         <v>349</v>
@@ -4566,25 +4602,26 @@
       <c r="J27" s="5" t="s">
         <v>353</v>
       </c>
-      <c r="K27" s="5" t="s">
+      <c r="K27" s="5"/>
+      <c r="L27" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="L27" s="5"/>
       <c r="M27" s="5"/>
-      <c r="N27" s="13" t="s">
-        <v>607</v>
-      </c>
+      <c r="N27" s="5"/>
       <c r="O27" s="13" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="P27" s="13" t="s">
-        <v>607</v>
-      </c>
-      <c r="Q27" s="5" t="s">
+        <v>606</v>
+      </c>
+      <c r="Q27" s="13" t="s">
+        <v>606</v>
+      </c>
+      <c r="R27" s="5" t="s">
         <v>433</v>
       </c>
     </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A28" s="4" t="s">
         <v>115</v>
       </c>
@@ -4601,7 +4638,7 @@
         <v>113</v>
       </c>
       <c r="F28" s="5" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="G28" s="5" t="s">
         <v>349</v>
@@ -4615,25 +4652,26 @@
       <c r="J28" s="5" t="s">
         <v>353</v>
       </c>
-      <c r="K28" s="5" t="s">
+      <c r="K28" s="5"/>
+      <c r="L28" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="L28" s="5"/>
       <c r="M28" s="5"/>
-      <c r="N28" s="13" t="s">
-        <v>609</v>
-      </c>
-      <c r="O28" s="14" t="s">
-        <v>611</v>
-      </c>
-      <c r="P28" s="13" t="s">
-        <v>607</v>
-      </c>
-      <c r="Q28" s="5" t="s">
+      <c r="N28" s="5"/>
+      <c r="O28" s="13" t="s">
+        <v>608</v>
+      </c>
+      <c r="P28" s="14" t="s">
+        <v>610</v>
+      </c>
+      <c r="Q28" s="13" t="s">
+        <v>606</v>
+      </c>
+      <c r="R28" s="5" t="s">
         <v>434</v>
       </c>
     </row>
-    <row r="29" spans="1:17" ht="148.5" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" ht="148.5" x14ac:dyDescent="0.3">
       <c r="A29" s="4" t="s">
         <v>102</v>
       </c>
@@ -4650,7 +4688,7 @@
         <v>113</v>
       </c>
       <c r="F29" s="5" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="G29" s="5" t="s">
         <v>349</v>
@@ -4664,27 +4702,28 @@
       <c r="J29" s="5" t="s">
         <v>353</v>
       </c>
-      <c r="K29" s="5" t="s">
+      <c r="K29" s="5"/>
+      <c r="L29" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="L29" s="5"/>
-      <c r="M29" s="10" t="s">
-        <v>589</v>
-      </c>
-      <c r="N29" s="13" t="s">
-        <v>607</v>
+      <c r="M29" s="5"/>
+      <c r="N29" s="10" t="s">
+        <v>588</v>
       </c>
       <c r="O29" s="13" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="P29" s="13" t="s">
-        <v>609</v>
-      </c>
-      <c r="Q29" s="5" t="s">
+        <v>608</v>
+      </c>
+      <c r="Q29" s="13" t="s">
+        <v>608</v>
+      </c>
+      <c r="R29" s="5" t="s">
         <v>437</v>
       </c>
     </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A30" s="4" t="s">
         <v>102</v>
       </c>
@@ -4701,7 +4740,7 @@
         <v>113</v>
       </c>
       <c r="F30" s="5" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="G30" s="5" t="s">
         <v>349</v>
@@ -4715,25 +4754,26 @@
       <c r="J30" s="5" t="s">
         <v>353</v>
       </c>
-      <c r="K30" s="5" t="s">
+      <c r="K30" s="5"/>
+      <c r="L30" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="L30" s="5"/>
       <c r="M30" s="5"/>
-      <c r="N30" s="13" t="s">
-        <v>607</v>
-      </c>
+      <c r="N30" s="5"/>
       <c r="O30" s="13" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="P30" s="13" t="s">
-        <v>607</v>
-      </c>
-      <c r="Q30" s="5" t="s">
+        <v>606</v>
+      </c>
+      <c r="Q30" s="13" t="s">
+        <v>606</v>
+      </c>
+      <c r="R30" s="5" t="s">
         <v>435</v>
       </c>
     </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A31" s="4" t="s">
         <v>102</v>
       </c>
@@ -4750,7 +4790,7 @@
         <v>113</v>
       </c>
       <c r="F31" s="5" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="G31" s="5" t="s">
         <v>349</v>
@@ -4764,25 +4804,26 @@
       <c r="J31" s="5" t="s">
         <v>353</v>
       </c>
-      <c r="K31" s="5" t="s">
+      <c r="K31" s="5"/>
+      <c r="L31" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="L31" s="5"/>
       <c r="M31" s="5"/>
-      <c r="N31" s="13" t="s">
-        <v>607</v>
-      </c>
+      <c r="N31" s="5"/>
       <c r="O31" s="13" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="P31" s="13" t="s">
-        <v>609</v>
-      </c>
-      <c r="Q31" s="5" t="s">
+        <v>608</v>
+      </c>
+      <c r="Q31" s="13" t="s">
+        <v>608</v>
+      </c>
+      <c r="R31" s="5" t="s">
         <v>436</v>
       </c>
     </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A32" s="4" t="s">
         <v>102</v>
       </c>
@@ -4799,7 +4840,7 @@
         <v>113</v>
       </c>
       <c r="F32" s="5" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="G32" s="5" t="s">
         <v>349</v>
@@ -4813,25 +4854,26 @@
       <c r="J32" s="5" t="s">
         <v>353</v>
       </c>
-      <c r="K32" s="5" t="s">
+      <c r="K32" s="5"/>
+      <c r="L32" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="L32" s="5"/>
       <c r="M32" s="5"/>
-      <c r="N32" s="13" t="s">
-        <v>609</v>
-      </c>
+      <c r="N32" s="5"/>
       <c r="O32" s="13" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="P32" s="13" t="s">
-        <v>607</v>
-      </c>
-      <c r="Q32" s="5" t="s">
+        <v>606</v>
+      </c>
+      <c r="Q32" s="13" t="s">
+        <v>606</v>
+      </c>
+      <c r="R32" s="5" t="s">
         <v>439</v>
       </c>
     </row>
-    <row r="33" spans="1:17" ht="81" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:18" ht="81" x14ac:dyDescent="0.3">
       <c r="A33" s="4" t="s">
         <v>102</v>
       </c>
@@ -4848,7 +4890,7 @@
         <v>113</v>
       </c>
       <c r="F33" s="5" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="G33" s="5" t="s">
         <v>349</v>
@@ -4862,27 +4904,28 @@
       <c r="J33" s="5" t="s">
         <v>353</v>
       </c>
-      <c r="K33" s="5" t="s">
+      <c r="K33" s="5"/>
+      <c r="L33" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="L33" s="5"/>
-      <c r="M33" s="10" t="s">
-        <v>591</v>
-      </c>
-      <c r="N33" s="13" t="s">
-        <v>607</v>
+      <c r="M33" s="5"/>
+      <c r="N33" s="10" t="s">
+        <v>590</v>
       </c>
       <c r="O33" s="13" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="P33" s="13" t="s">
-        <v>607</v>
-      </c>
-      <c r="Q33" s="5" t="s">
+        <v>606</v>
+      </c>
+      <c r="Q33" s="13" t="s">
+        <v>606</v>
+      </c>
+      <c r="R33" s="5" t="s">
         <v>438</v>
       </c>
     </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A34" s="4" t="s">
         <v>116</v>
       </c>
@@ -4899,7 +4942,7 @@
         <v>113</v>
       </c>
       <c r="F34" s="5" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="G34" s="5" t="s">
         <v>349</v>
@@ -4913,25 +4956,26 @@
       <c r="J34" s="5" t="s">
         <v>353</v>
       </c>
-      <c r="K34" s="5" t="s">
+      <c r="K34" s="5"/>
+      <c r="L34" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="L34" s="5"/>
       <c r="M34" s="5"/>
-      <c r="N34" s="13" t="s">
-        <v>607</v>
-      </c>
+      <c r="N34" s="5"/>
       <c r="O34" s="13" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="P34" s="13" t="s">
-        <v>607</v>
-      </c>
-      <c r="Q34" s="5" t="s">
+        <v>606</v>
+      </c>
+      <c r="Q34" s="13" t="s">
+        <v>606</v>
+      </c>
+      <c r="R34" s="5" t="s">
         <v>440</v>
       </c>
     </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A35" s="4" t="s">
         <v>116</v>
       </c>
@@ -4948,7 +4992,7 @@
         <v>113</v>
       </c>
       <c r="F35" s="5" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="G35" s="5" t="s">
         <v>349</v>
@@ -4962,25 +5006,26 @@
       <c r="J35" s="5" t="s">
         <v>353</v>
       </c>
-      <c r="K35" s="5" t="s">
+      <c r="K35" s="5"/>
+      <c r="L35" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="L35" s="5"/>
       <c r="M35" s="5"/>
-      <c r="N35" s="13" t="s">
-        <v>609</v>
-      </c>
+      <c r="N35" s="5"/>
       <c r="O35" s="13" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="P35" s="13" t="s">
-        <v>609</v>
-      </c>
-      <c r="Q35" s="5" t="s">
+        <v>606</v>
+      </c>
+      <c r="Q35" s="13" t="s">
+        <v>608</v>
+      </c>
+      <c r="R35" s="5" t="s">
         <v>441</v>
       </c>
     </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A36" s="4" t="s">
         <v>116</v>
       </c>
@@ -4997,7 +5042,7 @@
         <v>113</v>
       </c>
       <c r="F36" s="5" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="G36" s="5" t="s">
         <v>349</v>
@@ -5011,25 +5056,26 @@
       <c r="J36" s="5" t="s">
         <v>353</v>
       </c>
-      <c r="K36" s="5" t="s">
+      <c r="K36" s="5"/>
+      <c r="L36" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="L36" s="5"/>
       <c r="M36" s="5"/>
-      <c r="N36" s="13" t="s">
-        <v>609</v>
-      </c>
+      <c r="N36" s="5"/>
       <c r="O36" s="13" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="P36" s="13" t="s">
-        <v>607</v>
-      </c>
-      <c r="Q36" s="5" t="s">
+        <v>606</v>
+      </c>
+      <c r="Q36" s="13" t="s">
+        <v>606</v>
+      </c>
+      <c r="R36" s="5" t="s">
         <v>443</v>
       </c>
     </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A37" s="4" t="s">
         <v>116</v>
       </c>
@@ -5046,7 +5092,7 @@
         <v>113</v>
       </c>
       <c r="F37" s="5" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="G37" s="5" t="s">
         <v>349</v>
@@ -5060,25 +5106,26 @@
       <c r="J37" s="5" t="s">
         <v>353</v>
       </c>
-      <c r="K37" s="5" t="s">
+      <c r="K37" s="5"/>
+      <c r="L37" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="L37" s="5"/>
       <c r="M37" s="5"/>
-      <c r="N37" s="13" t="s">
-        <v>609</v>
-      </c>
+      <c r="N37" s="5"/>
       <c r="O37" s="13" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="P37" s="13" t="s">
-        <v>609</v>
-      </c>
-      <c r="Q37" s="5" t="s">
+        <v>608</v>
+      </c>
+      <c r="Q37" s="13" t="s">
+        <v>608</v>
+      </c>
+      <c r="R37" s="5" t="s">
         <v>442</v>
       </c>
     </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A38" s="4" t="s">
         <v>117</v>
       </c>
@@ -5095,7 +5142,7 @@
         <v>113</v>
       </c>
       <c r="F38" s="5" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="G38" s="5" t="s">
         <v>349</v>
@@ -5109,25 +5156,26 @@
       <c r="J38" s="5" t="s">
         <v>353</v>
       </c>
-      <c r="K38" s="5" t="s">
+      <c r="K38" s="5"/>
+      <c r="L38" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="L38" s="5"/>
       <c r="M38" s="5"/>
-      <c r="N38" s="14" t="s">
-        <v>609</v>
-      </c>
+      <c r="N38" s="5"/>
       <c r="O38" s="14" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="P38" s="14" t="s">
-        <v>607</v>
-      </c>
-      <c r="Q38" s="5" t="s">
+        <v>608</v>
+      </c>
+      <c r="Q38" s="14" t="s">
+        <v>606</v>
+      </c>
+      <c r="R38" s="5" t="s">
         <v>445</v>
       </c>
     </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A39" s="4" t="s">
         <v>117</v>
       </c>
@@ -5144,7 +5192,7 @@
         <v>113</v>
       </c>
       <c r="F39" s="5" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="G39" s="5" t="s">
         <v>349</v>
@@ -5158,25 +5206,26 @@
       <c r="J39" s="5" t="s">
         <v>353</v>
       </c>
-      <c r="K39" s="5" t="s">
+      <c r="K39" s="5"/>
+      <c r="L39" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="L39" s="5"/>
       <c r="M39" s="5"/>
-      <c r="N39" s="13" t="s">
-        <v>607</v>
-      </c>
+      <c r="N39" s="5"/>
       <c r="O39" s="13" t="s">
-        <v>607</v>
-      </c>
-      <c r="P39" s="14" t="s">
-        <v>611</v>
-      </c>
-      <c r="Q39" s="5" t="s">
+        <v>606</v>
+      </c>
+      <c r="P39" s="13" t="s">
+        <v>606</v>
+      </c>
+      <c r="Q39" s="14" t="s">
+        <v>610</v>
+      </c>
+      <c r="R39" s="5" t="s">
         <v>446</v>
       </c>
     </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A40" s="4" t="s">
         <v>117</v>
       </c>
@@ -5193,7 +5242,7 @@
         <v>113</v>
       </c>
       <c r="F40" s="5" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="G40" s="5" t="s">
         <v>349</v>
@@ -5207,25 +5256,26 @@
       <c r="J40" s="5" t="s">
         <v>353</v>
       </c>
-      <c r="K40" s="5" t="s">
+      <c r="K40" s="5"/>
+      <c r="L40" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="L40" s="5"/>
       <c r="M40" s="5"/>
-      <c r="N40" s="13" t="s">
-        <v>609</v>
-      </c>
+      <c r="N40" s="5"/>
       <c r="O40" s="13" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="P40" s="13" t="s">
-        <v>607</v>
-      </c>
-      <c r="Q40" s="5" t="s">
+        <v>606</v>
+      </c>
+      <c r="Q40" s="13" t="s">
+        <v>606</v>
+      </c>
+      <c r="R40" s="5" t="s">
         <v>448</v>
       </c>
     </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A41" s="4" t="s">
         <v>117</v>
       </c>
@@ -5242,7 +5292,7 @@
         <v>113</v>
       </c>
       <c r="F41" s="5" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="G41" s="5" t="s">
         <v>349</v>
@@ -5256,25 +5306,26 @@
       <c r="J41" s="5" t="s">
         <v>353</v>
       </c>
-      <c r="K41" s="5" t="s">
+      <c r="K41" s="5"/>
+      <c r="L41" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="L41" s="5"/>
       <c r="M41" s="5"/>
-      <c r="N41" s="14" t="s">
-        <v>611</v>
-      </c>
-      <c r="O41" s="13" t="s">
-        <v>607</v>
+      <c r="N41" s="5"/>
+      <c r="O41" s="14" t="s">
+        <v>610</v>
       </c>
       <c r="P41" s="13" t="s">
-        <v>607</v>
-      </c>
-      <c r="Q41" s="5" t="s">
+        <v>606</v>
+      </c>
+      <c r="Q41" s="13" t="s">
+        <v>606</v>
+      </c>
+      <c r="R41" s="5" t="s">
         <v>449</v>
       </c>
     </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A42" s="4" t="s">
         <v>117</v>
       </c>
@@ -5291,7 +5342,7 @@
         <v>113</v>
       </c>
       <c r="F42" s="5" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="G42" s="5" t="s">
         <v>349</v>
@@ -5305,25 +5356,26 @@
       <c r="J42" s="5" t="s">
         <v>353</v>
       </c>
-      <c r="K42" s="5" t="s">
+      <c r="K42" s="5"/>
+      <c r="L42" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="L42" s="5"/>
       <c r="M42" s="5"/>
-      <c r="N42" s="14" t="s">
-        <v>611</v>
-      </c>
-      <c r="O42" s="13" t="s">
-        <v>607</v>
+      <c r="N42" s="5"/>
+      <c r="O42" s="14" t="s">
+        <v>610</v>
       </c>
       <c r="P42" s="13" t="s">
-        <v>607</v>
-      </c>
-      <c r="Q42" s="5" t="s">
+        <v>606</v>
+      </c>
+      <c r="Q42" s="13" t="s">
+        <v>606</v>
+      </c>
+      <c r="R42" s="5" t="s">
         <v>444</v>
       </c>
     </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A43" s="4" t="s">
         <v>117</v>
       </c>
@@ -5340,7 +5392,7 @@
         <v>113</v>
       </c>
       <c r="F43" s="5" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="G43" s="5" t="s">
         <v>349</v>
@@ -5354,25 +5406,26 @@
       <c r="J43" s="5" t="s">
         <v>353</v>
       </c>
-      <c r="K43" s="5" t="s">
+      <c r="K43" s="5"/>
+      <c r="L43" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="L43" s="5"/>
       <c r="M43" s="5"/>
-      <c r="N43" s="13" t="s">
-        <v>607</v>
-      </c>
+      <c r="N43" s="5"/>
       <c r="O43" s="13" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="P43" s="13" t="s">
-        <v>607</v>
-      </c>
-      <c r="Q43" s="5" t="s">
+        <v>606</v>
+      </c>
+      <c r="Q43" s="13" t="s">
+        <v>606</v>
+      </c>
+      <c r="R43" s="5" t="s">
         <v>450</v>
       </c>
     </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A44" s="4" t="s">
         <v>117</v>
       </c>
@@ -5389,7 +5442,7 @@
         <v>113</v>
       </c>
       <c r="F44" s="5" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="G44" s="5" t="s">
         <v>349</v>
@@ -5403,25 +5456,26 @@
       <c r="J44" s="5" t="s">
         <v>353</v>
       </c>
-      <c r="K44" s="5" t="s">
+      <c r="K44" s="5"/>
+      <c r="L44" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="L44" s="5"/>
       <c r="M44" s="5"/>
-      <c r="N44" s="13" t="s">
-        <v>607</v>
-      </c>
+      <c r="N44" s="5"/>
       <c r="O44" s="13" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="P44" s="13" t="s">
-        <v>607</v>
-      </c>
-      <c r="Q44" s="5" t="s">
+        <v>606</v>
+      </c>
+      <c r="Q44" s="13" t="s">
+        <v>606</v>
+      </c>
+      <c r="R44" s="5" t="s">
         <v>447</v>
       </c>
     </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A45" s="4" t="s">
         <v>118</v>
       </c>
@@ -5438,7 +5492,7 @@
         <v>113</v>
       </c>
       <c r="F45" s="5" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="G45" s="5" t="s">
         <v>349</v>
@@ -5452,25 +5506,26 @@
       <c r="J45" s="5" t="s">
         <v>353</v>
       </c>
-      <c r="K45" s="5" t="s">
+      <c r="K45" s="5"/>
+      <c r="L45" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="L45" s="5"/>
       <c r="M45" s="5"/>
-      <c r="N45" s="13" t="s">
-        <v>609</v>
-      </c>
+      <c r="N45" s="5"/>
       <c r="O45" s="13" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="P45" s="13" t="s">
-        <v>609</v>
-      </c>
-      <c r="Q45" s="5" t="s">
+        <v>608</v>
+      </c>
+      <c r="Q45" s="13" t="s">
+        <v>608</v>
+      </c>
+      <c r="R45" s="5" t="s">
         <v>452</v>
       </c>
     </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A46" s="4" t="s">
         <v>118</v>
       </c>
@@ -5487,7 +5542,7 @@
         <v>113</v>
       </c>
       <c r="F46" s="5" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="G46" s="5" t="s">
         <v>349</v>
@@ -5501,25 +5556,26 @@
       <c r="J46" s="5" t="s">
         <v>353</v>
       </c>
-      <c r="K46" s="5" t="s">
+      <c r="K46" s="5"/>
+      <c r="L46" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="L46" s="10"/>
       <c r="M46" s="10"/>
-      <c r="N46" s="13" t="s">
-        <v>609</v>
-      </c>
+      <c r="N46" s="10"/>
       <c r="O46" s="13" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="P46" s="13" t="s">
-        <v>609</v>
-      </c>
-      <c r="Q46" s="5" t="s">
+        <v>608</v>
+      </c>
+      <c r="Q46" s="13" t="s">
+        <v>608</v>
+      </c>
+      <c r="R46" s="5" t="s">
         <v>454</v>
       </c>
     </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A47" s="4" t="s">
         <v>118</v>
       </c>
@@ -5536,7 +5592,7 @@
         <v>113</v>
       </c>
       <c r="F47" s="5" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="G47" s="5" t="s">
         <v>349</v>
@@ -5550,25 +5606,26 @@
       <c r="J47" s="5" t="s">
         <v>353</v>
       </c>
-      <c r="K47" s="5" t="s">
+      <c r="K47" s="5"/>
+      <c r="L47" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="L47" s="5"/>
       <c r="M47" s="5"/>
-      <c r="N47" s="14" t="s">
-        <v>611</v>
-      </c>
-      <c r="O47" s="13" t="s">
-        <v>607</v>
+      <c r="N47" s="5"/>
+      <c r="O47" s="14" t="s">
+        <v>610</v>
       </c>
       <c r="P47" s="13" t="s">
-        <v>607</v>
-      </c>
-      <c r="Q47" s="5" t="s">
+        <v>606</v>
+      </c>
+      <c r="Q47" s="13" t="s">
+        <v>606</v>
+      </c>
+      <c r="R47" s="5" t="s">
         <v>451</v>
       </c>
     </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A48" s="4" t="s">
         <v>118</v>
       </c>
@@ -5585,7 +5642,7 @@
         <v>113</v>
       </c>
       <c r="F48" s="5" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="G48" s="5" t="s">
         <v>349</v>
@@ -5599,25 +5656,26 @@
       <c r="J48" s="5" t="s">
         <v>353</v>
       </c>
-      <c r="K48" s="5" t="s">
+      <c r="K48" s="5"/>
+      <c r="L48" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="L48" s="5"/>
       <c r="M48" s="5"/>
-      <c r="N48" s="13" t="s">
-        <v>607</v>
-      </c>
-      <c r="O48" s="14" t="s">
-        <v>611</v>
-      </c>
-      <c r="P48" s="13" t="s">
-        <v>607</v>
-      </c>
-      <c r="Q48" s="5" t="s">
+      <c r="N48" s="5"/>
+      <c r="O48" s="13" t="s">
+        <v>606</v>
+      </c>
+      <c r="P48" s="14" t="s">
+        <v>610</v>
+      </c>
+      <c r="Q48" s="13" t="s">
+        <v>606</v>
+      </c>
+      <c r="R48" s="5" t="s">
         <v>453</v>
       </c>
     </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A49" s="4" t="s">
         <v>118</v>
       </c>
@@ -5634,7 +5692,7 @@
         <v>113</v>
       </c>
       <c r="F49" s="5" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="G49" s="5" t="s">
         <v>349</v>
@@ -5648,25 +5706,26 @@
       <c r="J49" s="5" t="s">
         <v>353</v>
       </c>
-      <c r="K49" s="5" t="s">
+      <c r="K49" s="5"/>
+      <c r="L49" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="L49" s="5"/>
       <c r="M49" s="5"/>
-      <c r="N49" s="13" t="s">
-        <v>607</v>
-      </c>
+      <c r="N49" s="5"/>
       <c r="O49" s="13" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="P49" s="13" t="s">
-        <v>607</v>
-      </c>
-      <c r="Q49" s="5" t="s">
+        <v>608</v>
+      </c>
+      <c r="Q49" s="13" t="s">
+        <v>606</v>
+      </c>
+      <c r="R49" s="5" t="s">
         <v>455</v>
       </c>
     </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A50" s="4" t="s">
         <v>114</v>
       </c>
@@ -5692,20 +5751,21 @@
       <c r="K50" s="5"/>
       <c r="L50" s="5"/>
       <c r="M50" s="5"/>
-      <c r="N50" s="13" t="s">
-        <v>607</v>
-      </c>
+      <c r="N50" s="5"/>
       <c r="O50" s="13" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="P50" s="13" t="s">
-        <v>609</v>
-      </c>
-      <c r="Q50" s="5" t="s">
+        <v>606</v>
+      </c>
+      <c r="Q50" s="13" t="s">
+        <v>608</v>
+      </c>
+      <c r="R50" s="5" t="s">
         <v>456</v>
       </c>
     </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A51" s="4" t="s">
         <v>114</v>
       </c>
@@ -5728,25 +5788,26 @@
       <c r="H51" s="20"/>
       <c r="I51" s="20"/>
       <c r="J51" s="20"/>
-      <c r="K51" s="19" t="s">
+      <c r="K51" s="20"/>
+      <c r="L51" s="19" t="s">
         <v>367</v>
       </c>
-      <c r="L51" s="9"/>
       <c r="M51" s="9"/>
-      <c r="N51" s="13" t="s">
-        <v>607</v>
-      </c>
+      <c r="N51" s="9"/>
       <c r="O51" s="13" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="P51" s="13" t="s">
-        <v>609</v>
-      </c>
-      <c r="Q51" s="8" t="s">
-        <v>691</v>
-      </c>
-    </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.3">
+        <v>606</v>
+      </c>
+      <c r="Q51" s="13" t="s">
+        <v>608</v>
+      </c>
+      <c r="R51" s="8" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="52" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A52" s="4" t="s">
         <v>114</v>
       </c>
@@ -5769,25 +5830,26 @@
       <c r="H52" s="5"/>
       <c r="I52" s="5"/>
       <c r="J52" s="5"/>
-      <c r="K52" s="5" t="s">
+      <c r="K52" s="5"/>
+      <c r="L52" s="5" t="s">
         <v>369</v>
       </c>
-      <c r="L52" s="5"/>
       <c r="M52" s="5"/>
-      <c r="N52" s="14" t="s">
-        <v>611</v>
-      </c>
-      <c r="O52" s="13" t="s">
-        <v>607</v>
+      <c r="N52" s="5"/>
+      <c r="O52" s="14" t="s">
+        <v>610</v>
       </c>
       <c r="P52" s="13" t="s">
-        <v>609</v>
-      </c>
-      <c r="Q52" s="5" t="s">
+        <v>606</v>
+      </c>
+      <c r="Q52" s="13" t="s">
+        <v>608</v>
+      </c>
+      <c r="R52" s="5" t="s">
         <v>462</v>
       </c>
     </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A53" s="4" t="s">
         <v>114</v>
       </c>
@@ -5817,20 +5879,21 @@
       <c r="K53" s="5"/>
       <c r="L53" s="5"/>
       <c r="M53" s="5"/>
-      <c r="N53" s="13" t="s">
-        <v>607</v>
-      </c>
-      <c r="O53" s="14" t="s">
-        <v>611</v>
-      </c>
-      <c r="P53" s="13" t="s">
-        <v>607</v>
-      </c>
-      <c r="Q53" s="5" t="s">
+      <c r="N53" s="5"/>
+      <c r="O53" s="13" t="s">
+        <v>606</v>
+      </c>
+      <c r="P53" s="14" t="s">
+        <v>610</v>
+      </c>
+      <c r="Q53" s="13" t="s">
+        <v>606</v>
+      </c>
+      <c r="R53" s="5" t="s">
         <v>470</v>
       </c>
     </row>
-    <row r="54" spans="1:17" ht="162" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:18" ht="162" x14ac:dyDescent="0.3">
       <c r="A54" s="4" t="s">
         <v>114</v>
       </c>
@@ -5854,28 +5917,31 @@
       <c r="I54" s="5"/>
       <c r="J54" s="5"/>
       <c r="K54" s="5" t="s">
+        <v>737</v>
+      </c>
+      <c r="L54" s="5" t="s">
         <v>366</v>
       </c>
-      <c r="L54" s="5" t="s">
+      <c r="M54" s="5" t="s">
+        <v>599</v>
+      </c>
+      <c r="N54" s="5" t="s">
         <v>600</v>
       </c>
-      <c r="M54" s="5" t="s">
-        <v>601</v>
-      </c>
-      <c r="N54" s="14" t="s">
-        <v>608</v>
-      </c>
       <c r="O54" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="P54" s="14" t="s">
-        <v>608</v>
-      </c>
-      <c r="Q54" s="5" t="s">
+        <v>607</v>
+      </c>
+      <c r="Q54" s="14" t="s">
+        <v>607</v>
+      </c>
+      <c r="R54" s="5" t="s">
         <v>463</v>
       </c>
     </row>
-    <row r="55" spans="1:17" ht="148.5" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:18" ht="148.5" x14ac:dyDescent="0.3">
       <c r="A55" s="4" t="s">
         <v>114</v>
       </c>
@@ -5898,29 +5964,30 @@
       <c r="H55" s="5"/>
       <c r="I55" s="5"/>
       <c r="J55" s="5"/>
-      <c r="K55" s="5" t="s">
+      <c r="K55" s="5"/>
+      <c r="L55" s="5" t="s">
         <v>370</v>
       </c>
-      <c r="L55" s="10" t="s">
-        <v>576</v>
-      </c>
       <c r="M55" s="10" t="s">
-        <v>687</v>
-      </c>
-      <c r="N55" s="13" t="s">
-        <v>607</v>
+        <v>575</v>
+      </c>
+      <c r="N55" s="10" t="s">
+        <v>686</v>
       </c>
       <c r="O55" s="13" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="P55" s="13" t="s">
-        <v>607</v>
-      </c>
-      <c r="Q55" s="5" t="s">
+        <v>606</v>
+      </c>
+      <c r="Q55" s="13" t="s">
+        <v>606</v>
+      </c>
+      <c r="R55" s="5" t="s">
         <v>459</v>
       </c>
     </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A56" s="4" t="s">
         <v>114</v>
       </c>
@@ -5948,22 +6015,23 @@
         <v>400</v>
       </c>
       <c r="K56" s="6"/>
-      <c r="L56" s="2"/>
+      <c r="L56" s="6"/>
       <c r="M56" s="2"/>
-      <c r="N56" s="13" t="s">
-        <v>607</v>
-      </c>
+      <c r="N56" s="2"/>
       <c r="O56" s="13" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="P56" s="13" t="s">
-        <v>607</v>
-      </c>
-      <c r="Q56" s="6" t="s">
+        <v>606</v>
+      </c>
+      <c r="Q56" s="13" t="s">
+        <v>606</v>
+      </c>
+      <c r="R56" s="6" t="s">
         <v>461</v>
       </c>
     </row>
-    <row r="57" spans="1:17" ht="27" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:18" ht="27" x14ac:dyDescent="0.3">
       <c r="A57" s="4" t="s">
         <v>114</v>
       </c>
@@ -5986,27 +6054,28 @@
       <c r="H57" s="5"/>
       <c r="I57" s="5"/>
       <c r="J57" s="5"/>
-      <c r="K57" s="5" t="s">
+      <c r="K57" s="5"/>
+      <c r="L57" s="5" t="s">
         <v>370</v>
       </c>
-      <c r="L57" s="5" t="s">
-        <v>689</v>
-      </c>
-      <c r="M57" s="5"/>
-      <c r="N57" s="13" t="s">
-        <v>607</v>
-      </c>
+      <c r="M57" s="5" t="s">
+        <v>688</v>
+      </c>
+      <c r="N57" s="5"/>
       <c r="O57" s="13" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="P57" s="13" t="s">
-        <v>607</v>
-      </c>
-      <c r="Q57" s="5" t="s">
+        <v>606</v>
+      </c>
+      <c r="Q57" s="13" t="s">
+        <v>606</v>
+      </c>
+      <c r="R57" s="5" t="s">
         <v>464</v>
       </c>
     </row>
-    <row r="58" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="4" t="s">
         <v>114</v>
       </c>
@@ -6029,25 +6098,26 @@
       <c r="H58" s="5"/>
       <c r="I58" s="5"/>
       <c r="J58" s="5"/>
-      <c r="K58" s="5" t="s">
+      <c r="K58" s="5"/>
+      <c r="L58" s="5" t="s">
         <v>371</v>
       </c>
-      <c r="L58" s="5"/>
       <c r="M58" s="5"/>
-      <c r="N58" s="14" t="s">
-        <v>608</v>
-      </c>
+      <c r="N58" s="5"/>
       <c r="O58" s="14" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="P58" s="14" t="s">
-        <v>606</v>
-      </c>
-      <c r="Q58" s="5" t="s">
+        <v>609</v>
+      </c>
+      <c r="Q58" s="14" t="s">
+        <v>605</v>
+      </c>
+      <c r="R58" s="5" t="s">
         <v>465</v>
       </c>
     </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A59" s="4" t="s">
         <v>114</v>
       </c>
@@ -6070,25 +6140,26 @@
       <c r="H59" s="5"/>
       <c r="I59" s="5"/>
       <c r="J59" s="5"/>
-      <c r="K59" s="5" t="s">
+      <c r="K59" s="5"/>
+      <c r="L59" s="5" t="s">
         <v>371</v>
       </c>
-      <c r="L59" s="5"/>
       <c r="M59" s="5"/>
-      <c r="N59" s="14" t="s">
-        <v>610</v>
-      </c>
+      <c r="N59" s="5"/>
       <c r="O59" s="14" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="P59" s="14" t="s">
-        <v>609</v>
-      </c>
-      <c r="Q59" s="5" t="s">
+        <v>605</v>
+      </c>
+      <c r="Q59" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="R59" s="5" t="s">
         <v>466</v>
       </c>
     </row>
-    <row r="60" spans="1:17" ht="67.5" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:18" ht="67.5" x14ac:dyDescent="0.3">
       <c r="A60" s="4" t="s">
         <v>114</v>
       </c>
@@ -6111,27 +6182,28 @@
       <c r="H60" s="5"/>
       <c r="I60" s="5"/>
       <c r="J60" s="5"/>
-      <c r="K60" s="5" t="s">
+      <c r="K60" s="5"/>
+      <c r="L60" s="5" t="s">
         <v>370</v>
       </c>
-      <c r="L60" s="5" t="s">
-        <v>697</v>
-      </c>
-      <c r="M60" s="5"/>
-      <c r="N60" s="14" t="s">
+      <c r="M60" s="5" t="s">
+        <v>696</v>
+      </c>
+      <c r="N60" s="5"/>
+      <c r="O60" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="P60" s="14" t="s">
         <v>609</v>
       </c>
-      <c r="O60" s="14" t="s">
-        <v>610</v>
-      </c>
-      <c r="P60" s="14" t="s">
-        <v>606</v>
-      </c>
-      <c r="Q60" s="5" t="s">
+      <c r="Q60" s="14" t="s">
+        <v>605</v>
+      </c>
+      <c r="R60" s="5" t="s">
         <v>457</v>
       </c>
     </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A61" s="4" t="s">
         <v>114</v>
       </c>
@@ -6154,25 +6226,26 @@
       <c r="H61" s="5"/>
       <c r="I61" s="5"/>
       <c r="J61" s="5"/>
-      <c r="K61" s="5" t="s">
+      <c r="K61" s="5"/>
+      <c r="L61" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="L61" s="5"/>
       <c r="M61" s="5"/>
-      <c r="N61" s="14" t="s">
-        <v>606</v>
-      </c>
+      <c r="N61" s="5"/>
       <c r="O61" s="14" t="s">
-        <v>609</v>
+        <v>605</v>
       </c>
       <c r="P61" s="14" t="s">
-        <v>606</v>
-      </c>
-      <c r="Q61" s="5" t="s">
+        <v>608</v>
+      </c>
+      <c r="Q61" s="14" t="s">
+        <v>605</v>
+      </c>
+      <c r="R61" s="5" t="s">
         <v>458</v>
       </c>
     </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A62" s="4" t="s">
         <v>114</v>
       </c>
@@ -6202,20 +6275,21 @@
       <c r="K62" s="5"/>
       <c r="L62" s="5"/>
       <c r="M62" s="5"/>
-      <c r="N62" s="14" t="s">
-        <v>606</v>
-      </c>
+      <c r="N62" s="5"/>
       <c r="O62" s="14" t="s">
-        <v>610</v>
+        <v>605</v>
       </c>
       <c r="P62" s="14" t="s">
-        <v>606</v>
-      </c>
-      <c r="Q62" s="5" t="s">
+        <v>609</v>
+      </c>
+      <c r="Q62" s="14" t="s">
+        <v>605</v>
+      </c>
+      <c r="R62" s="5" t="s">
         <v>467</v>
       </c>
     </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A63" s="4" t="s">
         <v>114</v>
       </c>
@@ -6245,20 +6319,21 @@
       <c r="K63" s="5"/>
       <c r="L63" s="5"/>
       <c r="M63" s="5"/>
-      <c r="N63" s="14" t="s">
-        <v>610</v>
-      </c>
+      <c r="N63" s="5"/>
       <c r="O63" s="14" t="s">
         <v>609</v>
       </c>
       <c r="P63" s="14" t="s">
-        <v>606</v>
-      </c>
-      <c r="Q63" s="5" t="s">
+        <v>608</v>
+      </c>
+      <c r="Q63" s="14" t="s">
+        <v>605</v>
+      </c>
+      <c r="R63" s="5" t="s">
         <v>468</v>
       </c>
     </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A64" s="4" t="s">
         <v>114</v>
       </c>
@@ -6281,25 +6356,26 @@
       <c r="H64" s="5"/>
       <c r="I64" s="5"/>
       <c r="J64" s="5"/>
-      <c r="K64" s="5" t="s">
+      <c r="K64" s="5"/>
+      <c r="L64" s="5" t="s">
         <v>370</v>
       </c>
-      <c r="L64" s="5"/>
       <c r="M64" s="5"/>
-      <c r="N64" s="14" t="s">
-        <v>606</v>
-      </c>
+      <c r="N64" s="5"/>
       <c r="O64" s="14" t="s">
-        <v>610</v>
+        <v>605</v>
       </c>
       <c r="P64" s="14" t="s">
-        <v>610</v>
-      </c>
-      <c r="Q64" s="5" t="s">
+        <v>609</v>
+      </c>
+      <c r="Q64" s="14" t="s">
+        <v>609</v>
+      </c>
+      <c r="R64" s="5" t="s">
         <v>469</v>
       </c>
     </row>
-    <row r="65" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A65" s="4" t="s">
         <v>114</v>
       </c>
@@ -6322,25 +6398,26 @@
       <c r="H65" s="5"/>
       <c r="I65" s="5"/>
       <c r="J65" s="5"/>
-      <c r="K65" s="5" t="s">
+      <c r="K65" s="5"/>
+      <c r="L65" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="L65" s="5"/>
       <c r="M65" s="5"/>
-      <c r="N65" s="14" t="s">
-        <v>610</v>
-      </c>
+      <c r="N65" s="5"/>
       <c r="O65" s="14" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="P65" s="14" t="s">
-        <v>606</v>
-      </c>
-      <c r="Q65" s="5" t="s">
+        <v>605</v>
+      </c>
+      <c r="Q65" s="14" t="s">
+        <v>605</v>
+      </c>
+      <c r="R65" s="5" t="s">
         <v>460</v>
       </c>
     </row>
-    <row r="66" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A66" s="4" t="s">
         <v>3</v>
       </c>
@@ -6363,25 +6440,26 @@
       <c r="H66" s="5"/>
       <c r="I66" s="5"/>
       <c r="J66" s="5"/>
-      <c r="K66" s="5" t="s">
+      <c r="K66" s="5"/>
+      <c r="L66" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="L66" s="5"/>
       <c r="M66" s="5"/>
-      <c r="N66" s="14" t="s">
-        <v>609</v>
-      </c>
+      <c r="N66" s="5"/>
       <c r="O66" s="14" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="P66" s="14" t="s">
-        <v>609</v>
-      </c>
-      <c r="Q66" s="5" t="s">
+        <v>608</v>
+      </c>
+      <c r="Q66" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="R66" s="5" t="s">
         <v>477</v>
       </c>
     </row>
-    <row r="67" spans="1:17" ht="162" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:18" ht="162" x14ac:dyDescent="0.3">
       <c r="A67" s="4" t="s">
         <v>3</v>
       </c>
@@ -6404,27 +6482,28 @@
       <c r="H67" s="5"/>
       <c r="I67" s="5"/>
       <c r="J67" s="5"/>
-      <c r="K67" s="5" t="s">
+      <c r="K67" s="5"/>
+      <c r="L67" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="L67" s="5"/>
-      <c r="M67" s="10" t="s">
-        <v>579</v>
-      </c>
-      <c r="N67" s="14" t="s">
-        <v>606</v>
+      <c r="M67" s="5"/>
+      <c r="N67" s="10" t="s">
+        <v>578</v>
       </c>
       <c r="O67" s="14" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="P67" s="14" t="s">
-        <v>609</v>
-      </c>
-      <c r="Q67" s="5" t="s">
+        <v>605</v>
+      </c>
+      <c r="Q67" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="R67" s="5" t="s">
         <v>474</v>
       </c>
     </row>
-    <row r="68" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A68" s="4" t="s">
         <v>3</v>
       </c>
@@ -6447,25 +6526,26 @@
       <c r="H68" s="5"/>
       <c r="I68" s="5"/>
       <c r="J68" s="5"/>
-      <c r="K68" s="5" t="s">
+      <c r="K68" s="5"/>
+      <c r="L68" s="5" t="s">
         <v>372</v>
       </c>
-      <c r="L68" s="5"/>
       <c r="M68" s="5"/>
-      <c r="N68" s="14" t="s">
-        <v>606</v>
-      </c>
+      <c r="N68" s="5"/>
       <c r="O68" s="14" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="P68" s="14" t="s">
-        <v>609</v>
-      </c>
-      <c r="Q68" s="5" t="s">
+        <v>605</v>
+      </c>
+      <c r="Q68" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="R68" s="5" t="s">
         <v>475</v>
       </c>
     </row>
-    <row r="69" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A69" s="4" t="s">
         <v>3</v>
       </c>
@@ -6488,25 +6568,26 @@
       <c r="H69" s="5"/>
       <c r="I69" s="5"/>
       <c r="J69" s="5"/>
-      <c r="K69" s="5" t="s">
+      <c r="K69" s="5"/>
+      <c r="L69" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="L69" s="5"/>
       <c r="M69" s="5"/>
-      <c r="N69" s="14" t="s">
-        <v>606</v>
-      </c>
+      <c r="N69" s="5"/>
       <c r="O69" s="14" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="P69" s="14" t="s">
-        <v>609</v>
-      </c>
-      <c r="Q69" s="5" t="s">
+        <v>605</v>
+      </c>
+      <c r="Q69" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="R69" s="5" t="s">
         <v>476</v>
       </c>
     </row>
-    <row r="70" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A70" s="4" t="s">
         <v>3</v>
       </c>
@@ -6529,25 +6610,26 @@
       <c r="H70" s="5"/>
       <c r="I70" s="5"/>
       <c r="J70" s="5"/>
-      <c r="K70" s="5" t="s">
+      <c r="K70" s="5"/>
+      <c r="L70" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="L70" s="5"/>
       <c r="M70" s="5"/>
-      <c r="N70" s="14" t="s">
-        <v>606</v>
-      </c>
+      <c r="N70" s="5"/>
       <c r="O70" s="14" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="P70" s="14" t="s">
-        <v>606</v>
-      </c>
-      <c r="Q70" s="5" t="s">
+        <v>605</v>
+      </c>
+      <c r="Q70" s="14" t="s">
+        <v>605</v>
+      </c>
+      <c r="R70" s="5" t="s">
         <v>481</v>
       </c>
     </row>
-    <row r="71" spans="1:17" ht="162" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:18" ht="162" x14ac:dyDescent="0.3">
       <c r="A71" s="4" t="s">
         <v>3</v>
       </c>
@@ -6570,29 +6652,30 @@
       <c r="H71" s="5"/>
       <c r="I71" s="5"/>
       <c r="J71" s="5"/>
-      <c r="K71" s="5" t="s">
+      <c r="K71" s="5"/>
+      <c r="L71" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="L71" s="5" t="s">
-        <v>730</v>
-      </c>
-      <c r="M71" s="10" t="s">
-        <v>580</v>
-      </c>
-      <c r="N71" s="14" t="s">
-        <v>606</v>
+      <c r="M71" s="5" t="s">
+        <v>729</v>
+      </c>
+      <c r="N71" s="10" t="s">
+        <v>579</v>
       </c>
       <c r="O71" s="14" t="s">
-        <v>609</v>
+        <v>605</v>
       </c>
       <c r="P71" s="14" t="s">
-        <v>606</v>
-      </c>
-      <c r="Q71" s="5" t="s">
+        <v>608</v>
+      </c>
+      <c r="Q71" s="14" t="s">
+        <v>605</v>
+      </c>
+      <c r="R71" s="5" t="s">
         <v>473</v>
       </c>
     </row>
-    <row r="72" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A72" s="4" t="s">
         <v>3</v>
       </c>
@@ -6615,25 +6698,26 @@
       <c r="H72" s="5"/>
       <c r="I72" s="5"/>
       <c r="J72" s="5"/>
-      <c r="K72" s="5" t="s">
+      <c r="K72" s="5"/>
+      <c r="L72" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="L72" s="5"/>
       <c r="M72" s="5"/>
-      <c r="N72" s="14" t="s">
-        <v>606</v>
-      </c>
+      <c r="N72" s="5"/>
       <c r="O72" s="14" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="P72" s="14" t="s">
-        <v>606</v>
-      </c>
-      <c r="Q72" s="5" t="s">
+        <v>605</v>
+      </c>
+      <c r="Q72" s="14" t="s">
+        <v>605</v>
+      </c>
+      <c r="R72" s="5" t="s">
         <v>482</v>
       </c>
     </row>
-    <row r="73" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="4" t="s">
         <v>3</v>
       </c>
@@ -6656,25 +6740,26 @@
       <c r="H73" s="5"/>
       <c r="I73" s="5"/>
       <c r="J73" s="5"/>
-      <c r="K73" s="5" t="s">
+      <c r="K73" s="5"/>
+      <c r="L73" s="5" t="s">
         <v>370</v>
       </c>
-      <c r="L73" s="5"/>
       <c r="M73" s="5"/>
-      <c r="N73" s="14" t="s">
-        <v>606</v>
-      </c>
+      <c r="N73" s="5"/>
       <c r="O73" s="14" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="P73" s="14" t="s">
-        <v>606</v>
-      </c>
-      <c r="Q73" s="5" t="s">
+        <v>605</v>
+      </c>
+      <c r="Q73" s="14" t="s">
+        <v>605</v>
+      </c>
+      <c r="R73" s="5" t="s">
         <v>479</v>
       </c>
     </row>
-    <row r="74" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A74" s="4" t="s">
         <v>3</v>
       </c>
@@ -6697,25 +6782,26 @@
       <c r="H74" s="5"/>
       <c r="I74" s="5"/>
       <c r="J74" s="5"/>
-      <c r="K74" s="5" t="s">
+      <c r="K74" s="5"/>
+      <c r="L74" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="L74" s="5"/>
       <c r="M74" s="5"/>
-      <c r="N74" s="14" t="s">
-        <v>606</v>
-      </c>
+      <c r="N74" s="5"/>
       <c r="O74" s="14" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="P74" s="14" t="s">
-        <v>609</v>
-      </c>
-      <c r="Q74" s="5" t="s">
+        <v>605</v>
+      </c>
+      <c r="Q74" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="R74" s="5" t="s">
         <v>472</v>
       </c>
     </row>
-    <row r="75" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A75" s="4" t="s">
         <v>3</v>
       </c>
@@ -6738,25 +6824,26 @@
       <c r="H75" s="5"/>
       <c r="I75" s="5"/>
       <c r="J75" s="5"/>
-      <c r="K75" s="5" t="s">
+      <c r="K75" s="5"/>
+      <c r="L75" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="L75" s="5"/>
       <c r="M75" s="5"/>
-      <c r="N75" s="14" t="s">
-        <v>606</v>
-      </c>
+      <c r="N75" s="5"/>
       <c r="O75" s="14" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="P75" s="14" t="s">
-        <v>609</v>
-      </c>
-      <c r="Q75" s="5" t="s">
+        <v>605</v>
+      </c>
+      <c r="Q75" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="R75" s="5" t="s">
         <v>478</v>
       </c>
     </row>
-    <row r="76" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A76" s="4" t="s">
         <v>3</v>
       </c>
@@ -6779,25 +6866,26 @@
       <c r="H76" s="5"/>
       <c r="I76" s="5"/>
       <c r="J76" s="5"/>
-      <c r="K76" s="5" t="s">
+      <c r="K76" s="5"/>
+      <c r="L76" s="5" t="s">
         <v>384</v>
       </c>
-      <c r="L76" s="5"/>
       <c r="M76" s="5"/>
-      <c r="N76" s="14" t="s">
-        <v>606</v>
-      </c>
+      <c r="N76" s="5"/>
       <c r="O76" s="14" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="P76" s="14" t="s">
-        <v>609</v>
-      </c>
-      <c r="Q76" s="5" t="s">
+        <v>605</v>
+      </c>
+      <c r="Q76" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="R76" s="5" t="s">
         <v>480</v>
       </c>
     </row>
-    <row r="77" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A77" s="4" t="s">
         <v>3</v>
       </c>
@@ -6820,25 +6908,26 @@
       <c r="H77" s="5"/>
       <c r="I77" s="5"/>
       <c r="J77" s="5"/>
-      <c r="K77" s="5" t="s">
+      <c r="K77" s="5"/>
+      <c r="L77" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="L77" s="5"/>
       <c r="M77" s="5"/>
-      <c r="N77" s="14" t="s">
-        <v>606</v>
-      </c>
+      <c r="N77" s="5"/>
       <c r="O77" s="14" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="P77" s="14" t="s">
-        <v>606</v>
-      </c>
-      <c r="Q77" s="5" t="s">
-        <v>613</v>
-      </c>
-    </row>
-    <row r="78" spans="1:17" x14ac:dyDescent="0.3">
+        <v>605</v>
+      </c>
+      <c r="Q77" s="14" t="s">
+        <v>605</v>
+      </c>
+      <c r="R77" s="5" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="78" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A78" s="4" t="s">
         <v>3</v>
       </c>
@@ -6861,25 +6950,26 @@
       <c r="H78" s="5"/>
       <c r="I78" s="5"/>
       <c r="J78" s="5"/>
-      <c r="K78" s="5" t="s">
+      <c r="K78" s="5"/>
+      <c r="L78" s="5" t="s">
         <v>372</v>
       </c>
-      <c r="L78" s="5"/>
       <c r="M78" s="5"/>
-      <c r="N78" s="14" t="s">
-        <v>606</v>
-      </c>
+      <c r="N78" s="5"/>
       <c r="O78" s="14" t="s">
+        <v>605</v>
+      </c>
+      <c r="P78" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="Q78" s="14" t="s">
         <v>609</v>
       </c>
-      <c r="P78" s="14" t="s">
-        <v>610</v>
-      </c>
-      <c r="Q78" s="5" t="s">
+      <c r="R78" s="5" t="s">
         <v>483</v>
       </c>
     </row>
-    <row r="79" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A79" s="4" t="s">
         <v>3</v>
       </c>
@@ -6902,25 +6992,26 @@
       <c r="H79" s="5"/>
       <c r="I79" s="5"/>
       <c r="J79" s="5"/>
-      <c r="K79" s="5" t="s">
+      <c r="K79" s="5"/>
+      <c r="L79" s="5" t="s">
         <v>372</v>
       </c>
-      <c r="L79" s="5"/>
       <c r="M79" s="5"/>
-      <c r="N79" s="14" t="s">
-        <v>606</v>
-      </c>
+      <c r="N79" s="5"/>
       <c r="O79" s="14" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="P79" s="14" t="s">
-        <v>606</v>
-      </c>
-      <c r="Q79" s="5" t="s">
+        <v>605</v>
+      </c>
+      <c r="Q79" s="14" t="s">
+        <v>605</v>
+      </c>
+      <c r="R79" s="5" t="s">
         <v>471</v>
       </c>
     </row>
-    <row r="80" spans="1:17" ht="94.5" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:18" ht="94.5" x14ac:dyDescent="0.3">
       <c r="A80" s="4" t="s">
         <v>101</v>
       </c>
@@ -6943,29 +7034,30 @@
       <c r="H80" s="5"/>
       <c r="I80" s="5"/>
       <c r="J80" s="5"/>
-      <c r="K80" s="5" t="s">
+      <c r="K80" s="5"/>
+      <c r="L80" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="L80" s="5" t="s">
-        <v>731</v>
-      </c>
-      <c r="M80" s="10" t="s">
-        <v>586</v>
-      </c>
-      <c r="N80" s="14" t="s">
-        <v>606</v>
+      <c r="M80" s="5" t="s">
+        <v>730</v>
+      </c>
+      <c r="N80" s="10" t="s">
+        <v>585</v>
       </c>
       <c r="O80" s="14" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="P80" s="14" t="s">
-        <v>606</v>
-      </c>
-      <c r="Q80" s="5" t="s">
+        <v>605</v>
+      </c>
+      <c r="Q80" s="14" t="s">
+        <v>605</v>
+      </c>
+      <c r="R80" s="5" t="s">
         <v>491</v>
       </c>
     </row>
-    <row r="81" spans="1:17" ht="54" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:18" ht="54" x14ac:dyDescent="0.3">
       <c r="A81" s="4" t="s">
         <v>101</v>
       </c>
@@ -6988,29 +7080,30 @@
       <c r="H81" s="5"/>
       <c r="I81" s="5"/>
       <c r="J81" s="5"/>
-      <c r="K81" s="5" t="s">
+      <c r="K81" s="5"/>
+      <c r="L81" s="5" t="s">
         <v>372</v>
       </c>
-      <c r="L81" s="5" t="s">
-        <v>699</v>
-      </c>
       <c r="M81" s="5" t="s">
-        <v>720</v>
-      </c>
-      <c r="N81" s="14" t="s">
-        <v>606</v>
+        <v>698</v>
+      </c>
+      <c r="N81" s="5" t="s">
+        <v>719</v>
       </c>
       <c r="O81" s="14" t="s">
-        <v>609</v>
+        <v>605</v>
       </c>
       <c r="P81" s="14" t="s">
-        <v>609</v>
-      </c>
-      <c r="Q81" s="5" t="s">
+        <v>608</v>
+      </c>
+      <c r="Q81" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="R81" s="5" t="s">
         <v>498</v>
       </c>
     </row>
-    <row r="82" spans="1:17" ht="27" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:18" ht="27" x14ac:dyDescent="0.3">
       <c r="A82" s="4" t="s">
         <v>101</v>
       </c>
@@ -7033,27 +7126,28 @@
       <c r="H82" s="5"/>
       <c r="I82" s="5"/>
       <c r="J82" s="5"/>
-      <c r="K82" s="5" t="s">
+      <c r="K82" s="5"/>
+      <c r="L82" s="5" t="s">
         <v>372</v>
       </c>
-      <c r="L82" s="5"/>
-      <c r="M82" s="5" t="s">
-        <v>719</v>
-      </c>
-      <c r="N82" s="14" t="s">
-        <v>609</v>
+      <c r="M82" s="5"/>
+      <c r="N82" s="5" t="s">
+        <v>718</v>
       </c>
       <c r="O82" s="14" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="P82" s="14" t="s">
         <v>609</v>
       </c>
-      <c r="Q82" s="5" t="s">
+      <c r="Q82" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="R82" s="5" t="s">
         <v>492</v>
       </c>
     </row>
-    <row r="83" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A83" s="4" t="s">
         <v>101</v>
       </c>
@@ -7076,25 +7170,26 @@
       <c r="H83" s="5"/>
       <c r="I83" s="5"/>
       <c r="J83" s="5"/>
-      <c r="K83" s="5" t="s">
+      <c r="K83" s="5"/>
+      <c r="L83" s="5" t="s">
         <v>372</v>
       </c>
-      <c r="L83" s="5"/>
       <c r="M83" s="5"/>
-      <c r="N83" s="14" t="s">
-        <v>606</v>
-      </c>
+      <c r="N83" s="5"/>
       <c r="O83" s="14" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="P83" s="14" t="s">
-        <v>609</v>
-      </c>
-      <c r="Q83" s="5" t="s">
+        <v>605</v>
+      </c>
+      <c r="Q83" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="R83" s="5" t="s">
         <v>493</v>
       </c>
     </row>
-    <row r="84" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A84" s="4" t="s">
         <v>101</v>
       </c>
@@ -7117,25 +7212,26 @@
       <c r="H84" s="5"/>
       <c r="I84" s="5"/>
       <c r="J84" s="5"/>
-      <c r="K84" s="5" t="s">
+      <c r="K84" s="5"/>
+      <c r="L84" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="L84" s="5"/>
       <c r="M84" s="5"/>
-      <c r="N84" s="14" t="s">
-        <v>606</v>
-      </c>
+      <c r="N84" s="5"/>
       <c r="O84" s="14" t="s">
-        <v>609</v>
+        <v>605</v>
       </c>
       <c r="P84" s="14" t="s">
-        <v>609</v>
-      </c>
-      <c r="Q84" s="5" t="s">
+        <v>608</v>
+      </c>
+      <c r="Q84" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="R84" s="5" t="s">
         <v>494</v>
       </c>
     </row>
-    <row r="85" spans="1:17" ht="40.5" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:18" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A85" s="4" t="s">
         <v>101</v>
       </c>
@@ -7158,27 +7254,28 @@
       <c r="H85" s="5"/>
       <c r="I85" s="5"/>
       <c r="J85" s="5"/>
-      <c r="K85" s="5" t="s">
+      <c r="K85" s="5"/>
+      <c r="L85" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="L85" s="5"/>
-      <c r="M85" s="10" t="s">
-        <v>585</v>
-      </c>
-      <c r="N85" s="14" t="s">
-        <v>606</v>
+      <c r="M85" s="5"/>
+      <c r="N85" s="10" t="s">
+        <v>584</v>
       </c>
       <c r="O85" s="14" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="P85" s="14" t="s">
-        <v>609</v>
-      </c>
-      <c r="Q85" s="5" t="s">
+        <v>605</v>
+      </c>
+      <c r="Q85" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="R85" s="5" t="s">
         <v>499</v>
       </c>
     </row>
-    <row r="86" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A86" s="4" t="s">
         <v>101</v>
       </c>
@@ -7201,25 +7298,26 @@
       <c r="H86" s="5"/>
       <c r="I86" s="5"/>
       <c r="J86" s="5"/>
-      <c r="K86" s="5" t="s">
+      <c r="K86" s="5"/>
+      <c r="L86" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="L86" s="5"/>
       <c r="M86" s="5"/>
-      <c r="N86" s="14" t="s">
-        <v>606</v>
-      </c>
+      <c r="N86" s="5"/>
       <c r="O86" s="14" t="s">
-        <v>610</v>
+        <v>605</v>
       </c>
       <c r="P86" s="14" t="s">
         <v>609</v>
       </c>
-      <c r="Q86" s="5" t="s">
+      <c r="Q86" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="R86" s="5" t="s">
         <v>486</v>
       </c>
     </row>
-    <row r="87" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A87" s="4" t="s">
         <v>101</v>
       </c>
@@ -7242,27 +7340,28 @@
       <c r="H87" s="5"/>
       <c r="I87" s="5"/>
       <c r="J87" s="5"/>
-      <c r="K87" s="5" t="s">
+      <c r="K87" s="5"/>
+      <c r="L87" s="5" t="s">
         <v>372</v>
       </c>
-      <c r="L87" s="5" t="s">
-        <v>698</v>
-      </c>
-      <c r="M87" s="5"/>
-      <c r="N87" s="14" t="s">
-        <v>606</v>
-      </c>
+      <c r="M87" s="5" t="s">
+        <v>697</v>
+      </c>
+      <c r="N87" s="5"/>
       <c r="O87" s="14" t="s">
-        <v>609</v>
+        <v>605</v>
       </c>
       <c r="P87" s="14" t="s">
-        <v>606</v>
-      </c>
-      <c r="Q87" s="5" t="s">
-        <v>692</v>
-      </c>
-    </row>
-    <row r="88" spans="1:17" x14ac:dyDescent="0.3">
+        <v>608</v>
+      </c>
+      <c r="Q87" s="14" t="s">
+        <v>605</v>
+      </c>
+      <c r="R87" s="5" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="88" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A88" s="4" t="s">
         <v>101</v>
       </c>
@@ -7285,25 +7384,26 @@
       <c r="H88" s="5"/>
       <c r="I88" s="5"/>
       <c r="J88" s="5"/>
-      <c r="K88" s="5" t="s">
+      <c r="K88" s="5"/>
+      <c r="L88" s="5" t="s">
         <v>374</v>
       </c>
-      <c r="L88" s="5"/>
       <c r="M88" s="5"/>
-      <c r="N88" s="14" t="s">
-        <v>606</v>
-      </c>
+      <c r="N88" s="5"/>
       <c r="O88" s="14" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="P88" s="14" t="s">
-        <v>606</v>
-      </c>
-      <c r="Q88" s="5" t="s">
+        <v>605</v>
+      </c>
+      <c r="Q88" s="14" t="s">
+        <v>605</v>
+      </c>
+      <c r="R88" s="5" t="s">
         <v>488</v>
       </c>
     </row>
-    <row r="89" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A89" s="4" t="s">
         <v>101</v>
       </c>
@@ -7326,25 +7426,26 @@
       <c r="H89" s="5"/>
       <c r="I89" s="5"/>
       <c r="J89" s="5"/>
-      <c r="K89" s="5" t="s">
+      <c r="K89" s="5"/>
+      <c r="L89" s="5" t="s">
         <v>374</v>
       </c>
-      <c r="L89" s="5"/>
       <c r="M89" s="5"/>
-      <c r="N89" s="14" t="s">
-        <v>606</v>
-      </c>
+      <c r="N89" s="5"/>
       <c r="O89" s="14" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="P89" s="14" t="s">
-        <v>606</v>
-      </c>
-      <c r="Q89" s="5" t="s">
+        <v>605</v>
+      </c>
+      <c r="Q89" s="14" t="s">
+        <v>605</v>
+      </c>
+      <c r="R89" s="5" t="s">
         <v>495</v>
       </c>
     </row>
-    <row r="90" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A90" s="4" t="s">
         <v>101</v>
       </c>
@@ -7367,25 +7468,26 @@
       <c r="H90" s="5"/>
       <c r="I90" s="5"/>
       <c r="J90" s="5"/>
-      <c r="K90" s="5" t="s">
+      <c r="K90" s="5"/>
+      <c r="L90" s="5" t="s">
         <v>370</v>
       </c>
-      <c r="L90" s="5"/>
       <c r="M90" s="5"/>
-      <c r="N90" s="14" t="s">
-        <v>606</v>
-      </c>
+      <c r="N90" s="5"/>
       <c r="O90" s="14" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="P90" s="14" t="s">
-        <v>606</v>
-      </c>
-      <c r="Q90" s="5" t="s">
+        <v>605</v>
+      </c>
+      <c r="Q90" s="14" t="s">
+        <v>605</v>
+      </c>
+      <c r="R90" s="5" t="s">
         <v>487</v>
       </c>
     </row>
-    <row r="91" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A91" s="4" t="s">
         <v>101</v>
       </c>
@@ -7408,25 +7510,26 @@
       <c r="H91" s="5"/>
       <c r="I91" s="5"/>
       <c r="J91" s="5"/>
-      <c r="K91" s="5" t="s">
+      <c r="K91" s="5"/>
+      <c r="L91" s="5" t="s">
         <v>372</v>
       </c>
-      <c r="L91" s="5"/>
       <c r="M91" s="5"/>
-      <c r="N91" s="14" t="s">
-        <v>606</v>
-      </c>
+      <c r="N91" s="5"/>
       <c r="O91" s="14" t="s">
-        <v>609</v>
+        <v>605</v>
       </c>
       <c r="P91" s="14" t="s">
-        <v>609</v>
-      </c>
-      <c r="Q91" s="5" t="s">
+        <v>608</v>
+      </c>
+      <c r="Q91" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="R91" s="5" t="s">
         <v>496</v>
       </c>
     </row>
-    <row r="92" spans="1:17" ht="108" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:18" ht="108" x14ac:dyDescent="0.3">
       <c r="A92" s="4" t="s">
         <v>101</v>
       </c>
@@ -7449,27 +7552,28 @@
       <c r="H92" s="5"/>
       <c r="I92" s="5"/>
       <c r="J92" s="5"/>
-      <c r="K92" s="5" t="s">
+      <c r="K92" s="5"/>
+      <c r="L92" s="5" t="s">
         <v>372</v>
       </c>
-      <c r="L92" s="5" t="s">
-        <v>700</v>
-      </c>
-      <c r="M92" s="5"/>
-      <c r="N92" s="14" t="s">
-        <v>609</v>
-      </c>
+      <c r="M92" s="5" t="s">
+        <v>699</v>
+      </c>
+      <c r="N92" s="5"/>
       <c r="O92" s="14" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="P92" s="14" t="s">
-        <v>606</v>
-      </c>
-      <c r="Q92" s="5" t="s">
+        <v>605</v>
+      </c>
+      <c r="Q92" s="14" t="s">
+        <v>605</v>
+      </c>
+      <c r="R92" s="5" t="s">
         <v>500</v>
       </c>
     </row>
-    <row r="93" spans="1:17" ht="40.5" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:18" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A93" s="4" t="s">
         <v>101</v>
       </c>
@@ -7492,27 +7596,28 @@
       <c r="H93" s="5"/>
       <c r="I93" s="5"/>
       <c r="J93" s="5"/>
-      <c r="K93" s="5" t="s">
+      <c r="K93" s="5"/>
+      <c r="L93" s="5" t="s">
         <v>375</v>
       </c>
-      <c r="L93" s="5"/>
-      <c r="M93" s="10" t="s">
-        <v>584</v>
-      </c>
-      <c r="N93" s="14" t="s">
-        <v>606</v>
+      <c r="M93" s="5"/>
+      <c r="N93" s="10" t="s">
+        <v>583</v>
       </c>
       <c r="O93" s="14" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="P93" s="14" t="s">
-        <v>606</v>
-      </c>
-      <c r="Q93" s="5" t="s">
+        <v>605</v>
+      </c>
+      <c r="Q93" s="14" t="s">
+        <v>605</v>
+      </c>
+      <c r="R93" s="5" t="s">
         <v>490</v>
       </c>
     </row>
-    <row r="94" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A94" s="4" t="s">
         <v>101</v>
       </c>
@@ -7543,39 +7648,40 @@
       <c r="J94" s="6" t="s">
         <v>358</v>
       </c>
-      <c r="K94" s="6" t="s">
+      <c r="K94" s="6"/>
+      <c r="L94" s="6" t="s">
         <v>367</v>
       </c>
-      <c r="L94" s="2"/>
       <c r="M94" s="2"/>
-      <c r="N94" s="14" t="s">
-        <v>606</v>
-      </c>
+      <c r="N94" s="2"/>
       <c r="O94" s="14" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="P94" s="14" t="s">
-        <v>606</v>
-      </c>
-      <c r="Q94" s="6" t="s">
+        <v>605</v>
+      </c>
+      <c r="Q94" s="14" t="s">
+        <v>605</v>
+      </c>
+      <c r="R94" s="6" t="s">
         <v>497</v>
       </c>
     </row>
-    <row r="95" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A95" s="4" t="s">
+        <v>720</v>
+      </c>
+      <c r="B95" s="5" t="s">
         <v>721</v>
       </c>
-      <c r="B95" s="5" t="s">
+      <c r="C95" s="5" t="s">
         <v>722</v>
       </c>
-      <c r="C95" s="5" t="s">
+      <c r="D95" s="5" t="s">
         <v>723</v>
       </c>
-      <c r="D95" s="5" t="s">
+      <c r="E95" s="5" t="s">
         <v>724</v>
-      </c>
-      <c r="E95" s="5" t="s">
-        <v>725</v>
       </c>
       <c r="F95" s="6" t="s">
         <v>358</v>
@@ -7592,21 +7698,22 @@
       <c r="J95" s="6" t="s">
         <v>358</v>
       </c>
-      <c r="K95" s="6" t="s">
-        <v>726</v>
-      </c>
-      <c r="L95" s="2" t="s">
-        <v>728</v>
-      </c>
-      <c r="M95" s="2"/>
-      <c r="N95" s="14"/>
+      <c r="K95" s="6"/>
+      <c r="L95" s="6" t="s">
+        <v>725</v>
+      </c>
+      <c r="M95" s="2" t="s">
+        <v>727</v>
+      </c>
+      <c r="N95" s="2"/>
       <c r="O95" s="14"/>
       <c r="P95" s="14"/>
-      <c r="Q95" s="6" t="s">
-        <v>727</v>
-      </c>
-    </row>
-    <row r="96" spans="1:17" ht="175.5" x14ac:dyDescent="0.3">
+      <c r="Q95" s="14"/>
+      <c r="R95" s="6" t="s">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="96" spans="1:18" ht="175.5" x14ac:dyDescent="0.3">
       <c r="A96" s="4" t="s">
         <v>101</v>
       </c>
@@ -7630,28 +7737,31 @@
       <c r="I96" s="5"/>
       <c r="J96" s="5"/>
       <c r="K96" s="5" t="s">
+        <v>365</v>
+      </c>
+      <c r="L96" s="5" t="s">
         <v>374</v>
       </c>
-      <c r="L96" s="5" t="s">
-        <v>717</v>
-      </c>
-      <c r="M96" s="10" t="s">
-        <v>583</v>
-      </c>
-      <c r="N96" s="14" t="s">
-        <v>609</v>
+      <c r="M96" s="5" t="s">
+        <v>716</v>
+      </c>
+      <c r="N96" s="10" t="s">
+        <v>582</v>
       </c>
       <c r="O96" s="14" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="P96" s="14" t="s">
-        <v>609</v>
-      </c>
-      <c r="Q96" s="5" t="s">
+        <v>605</v>
+      </c>
+      <c r="Q96" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="R96" s="5" t="s">
         <v>484</v>
       </c>
     </row>
-    <row r="97" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A97" s="4" t="s">
         <v>101</v>
       </c>
@@ -7674,25 +7784,26 @@
       <c r="H97" s="5"/>
       <c r="I97" s="5"/>
       <c r="J97" s="5"/>
-      <c r="K97" s="5" t="s">
+      <c r="K97" s="5"/>
+      <c r="L97" s="5" t="s">
         <v>374</v>
       </c>
-      <c r="L97" s="5"/>
       <c r="M97" s="5"/>
-      <c r="N97" s="14" t="s">
-        <v>606</v>
-      </c>
+      <c r="N97" s="5"/>
       <c r="O97" s="14" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="P97" s="14" t="s">
-        <v>606</v>
-      </c>
-      <c r="Q97" s="5" t="s">
+        <v>605</v>
+      </c>
+      <c r="Q97" s="14" t="s">
+        <v>605</v>
+      </c>
+      <c r="R97" s="5" t="s">
         <v>485</v>
       </c>
     </row>
-    <row r="98" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A98" s="4" t="s">
         <v>101</v>
       </c>
@@ -7715,25 +7826,26 @@
       <c r="H98" s="5"/>
       <c r="I98" s="5"/>
       <c r="J98" s="5"/>
-      <c r="K98" s="5" t="s">
+      <c r="K98" s="5"/>
+      <c r="L98" s="5" t="s">
         <v>374</v>
       </c>
-      <c r="L98" s="5"/>
       <c r="M98" s="5"/>
-      <c r="N98" s="14" t="s">
-        <v>606</v>
-      </c>
+      <c r="N98" s="5"/>
       <c r="O98" s="14" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="P98" s="14" t="s">
-        <v>606</v>
-      </c>
-      <c r="Q98" s="5" t="s">
+        <v>605</v>
+      </c>
+      <c r="Q98" s="14" t="s">
+        <v>605</v>
+      </c>
+      <c r="R98" s="5" t="s">
         <v>489</v>
       </c>
     </row>
-    <row r="99" spans="1:17" ht="40.5" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:18" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A99" s="4" t="s">
         <v>115</v>
       </c>
@@ -7756,27 +7868,28 @@
       <c r="H99" s="5"/>
       <c r="I99" s="5"/>
       <c r="J99" s="5"/>
-      <c r="K99" s="5" t="s">
+      <c r="K99" s="5"/>
+      <c r="L99" s="5" t="s">
         <v>372</v>
       </c>
-      <c r="L99" s="5" t="s">
-        <v>701</v>
-      </c>
-      <c r="M99" s="5"/>
-      <c r="N99" s="14" t="s">
-        <v>606</v>
-      </c>
+      <c r="M99" s="5" t="s">
+        <v>700</v>
+      </c>
+      <c r="N99" s="5"/>
       <c r="O99" s="14" t="s">
-        <v>609</v>
+        <v>605</v>
       </c>
       <c r="P99" s="14" t="s">
-        <v>606</v>
-      </c>
-      <c r="Q99" s="5" t="s">
+        <v>608</v>
+      </c>
+      <c r="Q99" s="14" t="s">
+        <v>605</v>
+      </c>
+      <c r="R99" s="5" t="s">
         <v>501</v>
       </c>
     </row>
-    <row r="100" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A100" s="4" t="s">
         <v>115</v>
       </c>
@@ -7799,25 +7912,26 @@
       <c r="H100" s="5"/>
       <c r="I100" s="5"/>
       <c r="J100" s="5"/>
-      <c r="K100" s="5" t="s">
+      <c r="K100" s="5"/>
+      <c r="L100" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="L100" s="5"/>
       <c r="M100" s="5"/>
-      <c r="N100" s="14" t="s">
-        <v>606</v>
-      </c>
+      <c r="N100" s="5"/>
       <c r="O100" s="14" t="s">
-        <v>609</v>
+        <v>605</v>
       </c>
       <c r="P100" s="14" t="s">
-        <v>606</v>
-      </c>
-      <c r="Q100" s="5" t="s">
+        <v>608</v>
+      </c>
+      <c r="Q100" s="14" t="s">
+        <v>605</v>
+      </c>
+      <c r="R100" s="5" t="s">
         <v>502</v>
       </c>
     </row>
-    <row r="101" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A101" s="4" t="s">
         <v>115</v>
       </c>
@@ -7840,25 +7954,26 @@
       <c r="H101" s="5"/>
       <c r="I101" s="5"/>
       <c r="J101" s="5"/>
-      <c r="K101" s="5" t="s">
+      <c r="K101" s="5"/>
+      <c r="L101" s="5" t="s">
         <v>379</v>
       </c>
-      <c r="L101" s="5"/>
       <c r="M101" s="5"/>
-      <c r="N101" s="14" t="s">
-        <v>606</v>
-      </c>
+      <c r="N101" s="5"/>
       <c r="O101" s="14" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="P101" s="14" t="s">
-        <v>606</v>
-      </c>
-      <c r="Q101" s="22" t="s">
-        <v>690</v>
-      </c>
-    </row>
-    <row r="102" spans="1:17" ht="94.5" x14ac:dyDescent="0.3">
+        <v>605</v>
+      </c>
+      <c r="Q101" s="14" t="s">
+        <v>605</v>
+      </c>
+      <c r="R101" s="22" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="102" spans="1:18" ht="94.5" x14ac:dyDescent="0.3">
       <c r="A102" s="4" t="s">
         <v>115</v>
       </c>
@@ -7881,27 +7996,28 @@
       <c r="H102" s="5"/>
       <c r="I102" s="5"/>
       <c r="J102" s="5"/>
-      <c r="K102" s="5" t="s">
+      <c r="K102" s="5"/>
+      <c r="L102" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="L102" s="5"/>
-      <c r="M102" s="10" t="s">
-        <v>587</v>
-      </c>
-      <c r="N102" s="14" t="s">
-        <v>606</v>
+      <c r="M102" s="5"/>
+      <c r="N102" s="10" t="s">
+        <v>586</v>
       </c>
       <c r="O102" s="14" t="s">
-        <v>609</v>
+        <v>605</v>
       </c>
       <c r="P102" s="14" t="s">
-        <v>609</v>
-      </c>
-      <c r="Q102" s="5" t="s">
+        <v>608</v>
+      </c>
+      <c r="Q102" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="R102" s="5" t="s">
         <v>504</v>
       </c>
     </row>
-    <row r="103" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A103" s="4" t="s">
         <v>115</v>
       </c>
@@ -7924,25 +8040,26 @@
       <c r="H103" s="5"/>
       <c r="I103" s="5"/>
       <c r="J103" s="5"/>
-      <c r="K103" s="5" t="s">
+      <c r="K103" s="5"/>
+      <c r="L103" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="L103" s="5"/>
       <c r="M103" s="5"/>
-      <c r="N103" s="14" t="s">
-        <v>606</v>
-      </c>
+      <c r="N103" s="5"/>
       <c r="O103" s="14" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="P103" s="14" t="s">
-        <v>606</v>
-      </c>
-      <c r="Q103" s="5" t="s">
-        <v>693</v>
-      </c>
-    </row>
-    <row r="104" spans="1:17" ht="95.25" x14ac:dyDescent="0.3">
+        <v>605</v>
+      </c>
+      <c r="Q103" s="14" t="s">
+        <v>605</v>
+      </c>
+      <c r="R103" s="5" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="104" spans="1:18" ht="95.25" x14ac:dyDescent="0.3">
       <c r="A104" s="4" t="s">
         <v>115</v>
       </c>
@@ -7969,27 +8086,28 @@
       <c r="J104" s="6" t="s">
         <v>405</v>
       </c>
-      <c r="K104" s="6" t="s">
+      <c r="K104" s="6"/>
+      <c r="L104" s="6" t="s">
         <v>367</v>
       </c>
-      <c r="L104" s="2"/>
-      <c r="M104" s="12" t="s">
-        <v>588</v>
-      </c>
-      <c r="N104" s="14" t="s">
-        <v>609</v>
+      <c r="M104" s="2"/>
+      <c r="N104" s="12" t="s">
+        <v>587</v>
       </c>
       <c r="O104" s="14" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="P104" s="14" t="s">
-        <v>609</v>
-      </c>
-      <c r="Q104" s="6" t="s">
+        <v>608</v>
+      </c>
+      <c r="Q104" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="R104" s="6" t="s">
         <v>509</v>
       </c>
     </row>
-    <row r="105" spans="1:17" ht="27" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:18" ht="27" x14ac:dyDescent="0.3">
       <c r="A105" s="4" t="s">
         <v>115</v>
       </c>
@@ -8012,27 +8130,28 @@
       <c r="H105" s="5"/>
       <c r="I105" s="5"/>
       <c r="J105" s="5"/>
-      <c r="K105" s="5" t="s">
+      <c r="K105" s="5"/>
+      <c r="L105" s="5" t="s">
         <v>372</v>
       </c>
-      <c r="L105" s="5" t="s">
-        <v>702</v>
-      </c>
-      <c r="M105" s="5"/>
-      <c r="N105" s="14" t="s">
-        <v>606</v>
-      </c>
+      <c r="M105" s="5" t="s">
+        <v>701</v>
+      </c>
+      <c r="N105" s="5"/>
       <c r="O105" s="14" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="P105" s="14" t="s">
-        <v>606</v>
-      </c>
-      <c r="Q105" s="5" t="s">
+        <v>605</v>
+      </c>
+      <c r="Q105" s="14" t="s">
+        <v>605</v>
+      </c>
+      <c r="R105" s="5" t="s">
         <v>503</v>
       </c>
     </row>
-    <row r="106" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A106" s="4" t="s">
         <v>115</v>
       </c>
@@ -8055,25 +8174,26 @@
       <c r="H106" s="5"/>
       <c r="I106" s="5"/>
       <c r="J106" s="5"/>
-      <c r="K106" s="5" t="s">
+      <c r="K106" s="5"/>
+      <c r="L106" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="L106" s="5"/>
       <c r="M106" s="5"/>
-      <c r="N106" s="14" t="s">
-        <v>606</v>
-      </c>
+      <c r="N106" s="5"/>
       <c r="O106" s="14" t="s">
-        <v>609</v>
+        <v>605</v>
       </c>
       <c r="P106" s="14" t="s">
-        <v>606</v>
-      </c>
-      <c r="Q106" s="5" t="s">
+        <v>608</v>
+      </c>
+      <c r="Q106" s="14" t="s">
+        <v>605</v>
+      </c>
+      <c r="R106" s="5" t="s">
         <v>510</v>
       </c>
     </row>
-    <row r="107" spans="1:17" ht="27" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:18" ht="27" x14ac:dyDescent="0.3">
       <c r="A107" s="4" t="s">
         <v>115</v>
       </c>
@@ -8096,27 +8216,28 @@
       <c r="H107" s="5"/>
       <c r="I107" s="5"/>
       <c r="J107" s="5"/>
-      <c r="K107" s="5" t="s">
+      <c r="K107" s="5"/>
+      <c r="L107" s="5" t="s">
         <v>372</v>
       </c>
-      <c r="L107" s="5" t="s">
-        <v>703</v>
-      </c>
-      <c r="M107" s="5"/>
-      <c r="N107" s="14" t="s">
-        <v>606</v>
-      </c>
+      <c r="M107" s="5" t="s">
+        <v>702</v>
+      </c>
+      <c r="N107" s="5"/>
       <c r="O107" s="14" t="s">
-        <v>609</v>
+        <v>605</v>
       </c>
       <c r="P107" s="14" t="s">
-        <v>606</v>
-      </c>
-      <c r="Q107" s="5" t="s">
+        <v>608</v>
+      </c>
+      <c r="Q107" s="14" t="s">
+        <v>605</v>
+      </c>
+      <c r="R107" s="5" t="s">
         <v>507</v>
       </c>
     </row>
-    <row r="108" spans="1:17" ht="54" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:18" ht="54" x14ac:dyDescent="0.3">
       <c r="A108" s="4" t="s">
         <v>115</v>
       </c>
@@ -8139,29 +8260,30 @@
       <c r="H108" s="5"/>
       <c r="I108" s="5"/>
       <c r="J108" s="5"/>
-      <c r="K108" s="5" t="s">
+      <c r="K108" s="5"/>
+      <c r="L108" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="L108" s="5" t="s">
-        <v>714</v>
-      </c>
-      <c r="M108" s="10" t="s">
+      <c r="M108" s="5" t="s">
         <v>713</v>
       </c>
-      <c r="N108" s="14" t="s">
-        <v>606</v>
+      <c r="N108" s="10" t="s">
+        <v>712</v>
       </c>
       <c r="O108" s="14" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="P108" s="14" t="s">
-        <v>609</v>
-      </c>
-      <c r="Q108" s="5" t="s">
+        <v>605</v>
+      </c>
+      <c r="Q108" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="R108" s="5" t="s">
         <v>505</v>
       </c>
     </row>
-    <row r="109" spans="1:17" ht="81" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:18" ht="81" x14ac:dyDescent="0.3">
       <c r="A109" s="4" t="s">
         <v>115</v>
       </c>
@@ -8187,32 +8309,33 @@
         <v>323</v>
       </c>
       <c r="I109" s="5" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="J109" s="5" t="s">
         <v>407</v>
       </c>
-      <c r="K109" s="5" t="s">
+      <c r="K109" s="5"/>
+      <c r="L109" s="5" t="s">
         <v>372</v>
       </c>
-      <c r="L109" s="5" t="s">
-        <v>704</v>
-      </c>
-      <c r="M109" s="5"/>
-      <c r="N109" s="14" t="s">
-        <v>606</v>
-      </c>
+      <c r="M109" s="5" t="s">
+        <v>703</v>
+      </c>
+      <c r="N109" s="5"/>
       <c r="O109" s="14" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="P109" s="14" t="s">
-        <v>606</v>
-      </c>
-      <c r="Q109" s="5" t="s">
+        <v>605</v>
+      </c>
+      <c r="Q109" s="14" t="s">
+        <v>605</v>
+      </c>
+      <c r="R109" s="5" t="s">
         <v>512</v>
       </c>
     </row>
-    <row r="110" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A110" s="4" t="s">
         <v>115</v>
       </c>
@@ -8235,25 +8358,26 @@
       <c r="H110" s="5"/>
       <c r="I110" s="5"/>
       <c r="J110" s="5"/>
-      <c r="K110" s="5" t="s">
+      <c r="K110" s="5"/>
+      <c r="L110" s="5" t="s">
         <v>372</v>
       </c>
-      <c r="L110" s="5"/>
       <c r="M110" s="5"/>
-      <c r="N110" s="14" t="s">
-        <v>606</v>
-      </c>
+      <c r="N110" s="5"/>
       <c r="O110" s="14" t="s">
-        <v>610</v>
+        <v>605</v>
       </c>
       <c r="P110" s="14" t="s">
-        <v>606</v>
-      </c>
-      <c r="Q110" s="5" t="s">
+        <v>609</v>
+      </c>
+      <c r="Q110" s="14" t="s">
+        <v>605</v>
+      </c>
+      <c r="R110" s="5" t="s">
         <v>511</v>
       </c>
     </row>
-    <row r="111" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A111" s="4" t="s">
         <v>115</v>
       </c>
@@ -8281,22 +8405,23 @@
         <v>405</v>
       </c>
       <c r="K111" s="6"/>
-      <c r="L111" s="2"/>
+      <c r="L111" s="6"/>
       <c r="M111" s="2"/>
-      <c r="N111" s="14" t="s">
-        <v>609</v>
-      </c>
+      <c r="N111" s="2"/>
       <c r="O111" s="14" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="P111" s="14" t="s">
-        <v>609</v>
-      </c>
-      <c r="Q111" s="6" t="s">
+        <v>608</v>
+      </c>
+      <c r="Q111" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="R111" s="6" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="112" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A112" s="4" t="s">
         <v>115</v>
       </c>
@@ -8319,25 +8444,26 @@
       <c r="H112" s="5"/>
       <c r="I112" s="5"/>
       <c r="J112" s="5"/>
-      <c r="K112" s="5" t="s">
+      <c r="K112" s="5"/>
+      <c r="L112" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="L112" s="5"/>
       <c r="M112" s="5"/>
-      <c r="N112" s="14" t="s">
-        <v>606</v>
-      </c>
+      <c r="N112" s="5"/>
       <c r="O112" s="14" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="P112" s="14" t="s">
-        <v>609</v>
-      </c>
-      <c r="Q112" s="5" t="s">
+        <v>605</v>
+      </c>
+      <c r="Q112" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="R112" s="5" t="s">
         <v>508</v>
       </c>
     </row>
-    <row r="113" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A113" s="4" t="s">
         <v>102</v>
       </c>
@@ -8360,25 +8486,26 @@
       <c r="H113" s="5"/>
       <c r="I113" s="5"/>
       <c r="J113" s="5"/>
-      <c r="K113" s="5" t="s">
+      <c r="K113" s="5"/>
+      <c r="L113" s="5" t="s">
         <v>372</v>
       </c>
-      <c r="L113" s="5"/>
       <c r="M113" s="5"/>
-      <c r="N113" s="14" t="s">
-        <v>609</v>
-      </c>
+      <c r="N113" s="5"/>
       <c r="O113" s="14" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="P113" s="14" t="s">
-        <v>606</v>
-      </c>
-      <c r="Q113" s="22" t="s">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="114" spans="1:17" x14ac:dyDescent="0.3">
+        <v>608</v>
+      </c>
+      <c r="Q113" s="14" t="s">
+        <v>605</v>
+      </c>
+      <c r="R113" s="22" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="114" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A114" s="4" t="s">
         <v>102</v>
       </c>
@@ -8401,25 +8528,26 @@
       <c r="H114" s="5"/>
       <c r="I114" s="5"/>
       <c r="J114" s="5"/>
-      <c r="K114" s="5" t="s">
+      <c r="K114" s="5"/>
+      <c r="L114" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="L114" s="5"/>
       <c r="M114" s="5"/>
-      <c r="N114" s="14" t="s">
-        <v>606</v>
-      </c>
+      <c r="N114" s="5"/>
       <c r="O114" s="14" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="P114" s="14" t="s">
-        <v>606</v>
-      </c>
-      <c r="Q114" s="5" t="s">
+        <v>605</v>
+      </c>
+      <c r="Q114" s="14" t="s">
+        <v>605</v>
+      </c>
+      <c r="R114" s="5" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="115" spans="1:17" ht="27" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:18" ht="27" x14ac:dyDescent="0.3">
       <c r="A115" s="4" t="s">
         <v>102</v>
       </c>
@@ -8442,27 +8570,28 @@
       <c r="H115" s="5"/>
       <c r="I115" s="5"/>
       <c r="J115" s="5"/>
-      <c r="K115" s="5" t="s">
+      <c r="K115" s="5"/>
+      <c r="L115" s="5" t="s">
         <v>381</v>
       </c>
-      <c r="L115" s="5" t="s">
-        <v>688</v>
-      </c>
-      <c r="M115" s="5"/>
-      <c r="N115" s="14" t="s">
-        <v>606</v>
-      </c>
+      <c r="M115" s="5" t="s">
+        <v>687</v>
+      </c>
+      <c r="N115" s="5"/>
       <c r="O115" s="14" t="s">
-        <v>609</v>
+        <v>605</v>
       </c>
       <c r="P115" s="14" t="s">
-        <v>606</v>
-      </c>
-      <c r="Q115" s="5" t="s">
+        <v>608</v>
+      </c>
+      <c r="Q115" s="14" t="s">
+        <v>605</v>
+      </c>
+      <c r="R115" s="5" t="s">
         <v>513</v>
       </c>
     </row>
-    <row r="116" spans="1:17" ht="40.5" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:18" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A116" s="4" t="s">
         <v>102</v>
       </c>
@@ -8485,27 +8614,28 @@
       <c r="H116" s="5"/>
       <c r="I116" s="5"/>
       <c r="J116" s="5"/>
-      <c r="K116" s="5" t="s">
+      <c r="K116" s="5"/>
+      <c r="L116" s="5" t="s">
         <v>370</v>
       </c>
-      <c r="L116" s="5" t="s">
-        <v>686</v>
-      </c>
-      <c r="M116" s="5"/>
-      <c r="N116" s="14" t="s">
-        <v>607</v>
-      </c>
+      <c r="M116" s="5" t="s">
+        <v>685</v>
+      </c>
+      <c r="N116" s="5"/>
       <c r="O116" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="P116" s="14" t="s">
-        <v>607</v>
-      </c>
-      <c r="Q116" s="5" t="s">
+        <v>606</v>
+      </c>
+      <c r="Q116" s="14" t="s">
+        <v>606</v>
+      </c>
+      <c r="R116" s="5" t="s">
         <v>518</v>
       </c>
     </row>
-    <row r="117" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A117" s="4" t="s">
         <v>102</v>
       </c>
@@ -8528,25 +8658,26 @@
       <c r="H117" s="5"/>
       <c r="I117" s="5"/>
       <c r="J117" s="5"/>
-      <c r="K117" s="5" t="s">
+      <c r="K117" s="5"/>
+      <c r="L117" s="5" t="s">
         <v>381</v>
       </c>
-      <c r="L117" s="5"/>
       <c r="M117" s="5"/>
-      <c r="N117" s="14" t="s">
-        <v>606</v>
-      </c>
+      <c r="N117" s="5"/>
       <c r="O117" s="14" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="P117" s="14" t="s">
-        <v>606</v>
-      </c>
-      <c r="Q117" s="5" t="s">
+        <v>605</v>
+      </c>
+      <c r="Q117" s="14" t="s">
+        <v>605</v>
+      </c>
+      <c r="R117" s="5" t="s">
         <v>517</v>
       </c>
     </row>
-    <row r="118" spans="1:17" ht="94.5" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:18" ht="94.5" x14ac:dyDescent="0.3">
       <c r="A118" s="4" t="s">
         <v>102</v>
       </c>
@@ -8569,27 +8700,28 @@
       <c r="H118" s="5"/>
       <c r="I118" s="5"/>
       <c r="J118" s="5"/>
-      <c r="K118" s="5" t="s">
+      <c r="K118" s="5"/>
+      <c r="L118" s="5" t="s">
         <v>381</v>
       </c>
-      <c r="L118" s="5"/>
-      <c r="M118" s="10" t="s">
-        <v>592</v>
-      </c>
-      <c r="N118" s="14" t="s">
-        <v>606</v>
+      <c r="M118" s="5"/>
+      <c r="N118" s="10" t="s">
+        <v>591</v>
       </c>
       <c r="O118" s="14" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="P118" s="14" t="s">
-        <v>606</v>
-      </c>
-      <c r="Q118" s="5" t="s">
+        <v>605</v>
+      </c>
+      <c r="Q118" s="14" t="s">
+        <v>605</v>
+      </c>
+      <c r="R118" s="5" t="s">
         <v>519</v>
       </c>
     </row>
-    <row r="119" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A119" s="4" t="s">
         <v>102</v>
       </c>
@@ -8612,25 +8744,26 @@
       <c r="H119" s="5"/>
       <c r="I119" s="5"/>
       <c r="J119" s="5"/>
-      <c r="K119" s="5" t="s">
+      <c r="K119" s="5"/>
+      <c r="L119" s="5" t="s">
         <v>372</v>
       </c>
-      <c r="L119" s="5"/>
       <c r="M119" s="5"/>
-      <c r="N119" s="14" t="s">
-        <v>609</v>
-      </c>
+      <c r="N119" s="5"/>
       <c r="O119" s="14" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="P119" s="14" t="s">
-        <v>609</v>
-      </c>
-      <c r="Q119" s="5" t="s">
+        <v>608</v>
+      </c>
+      <c r="Q119" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="R119" s="5" t="s">
         <v>514</v>
       </c>
     </row>
-    <row r="120" spans="1:17" ht="94.5" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:18" ht="94.5" x14ac:dyDescent="0.3">
       <c r="A120" s="4" t="s">
         <v>102</v>
       </c>
@@ -8653,27 +8786,28 @@
       <c r="H120" s="5"/>
       <c r="I120" s="5"/>
       <c r="J120" s="5"/>
-      <c r="K120" s="5" t="s">
+      <c r="K120" s="5"/>
+      <c r="L120" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="L120" s="5"/>
-      <c r="M120" s="10" t="s">
-        <v>590</v>
-      </c>
-      <c r="N120" s="14" t="s">
-        <v>607</v>
+      <c r="M120" s="5"/>
+      <c r="N120" s="10" t="s">
+        <v>589</v>
       </c>
       <c r="O120" s="14" t="s">
-        <v>607</v>
-      </c>
-      <c r="P120" s="13" t="s">
-        <v>609</v>
-      </c>
-      <c r="Q120" s="5" t="s">
+        <v>606</v>
+      </c>
+      <c r="P120" s="14" t="s">
+        <v>606</v>
+      </c>
+      <c r="Q120" s="13" t="s">
+        <v>608</v>
+      </c>
+      <c r="R120" s="5" t="s">
         <v>515</v>
       </c>
     </row>
-    <row r="121" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A121" s="4" t="s">
         <v>116</v>
       </c>
@@ -8696,25 +8830,26 @@
       <c r="H121" s="5"/>
       <c r="I121" s="5"/>
       <c r="J121" s="5"/>
-      <c r="K121" s="5" t="s">
+      <c r="K121" s="5"/>
+      <c r="L121" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="L121" s="5"/>
       <c r="M121" s="5"/>
-      <c r="N121" s="13" t="s">
-        <v>609</v>
-      </c>
+      <c r="N121" s="5"/>
       <c r="O121" s="13" t="s">
-        <v>609</v>
-      </c>
-      <c r="P121" s="14" t="s">
-        <v>607</v>
-      </c>
-      <c r="Q121" s="5" t="s">
+        <v>608</v>
+      </c>
+      <c r="P121" s="13" t="s">
+        <v>608</v>
+      </c>
+      <c r="Q121" s="14" t="s">
+        <v>606</v>
+      </c>
+      <c r="R121" s="5" t="s">
         <v>531</v>
       </c>
     </row>
-    <row r="122" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A122" s="4" t="s">
         <v>116</v>
       </c>
@@ -8737,25 +8872,26 @@
       <c r="H122" s="5"/>
       <c r="I122" s="5"/>
       <c r="J122" s="5"/>
-      <c r="K122" s="5" t="s">
+      <c r="K122" s="5"/>
+      <c r="L122" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="L122" s="5"/>
       <c r="M122" s="5"/>
-      <c r="N122" s="13" t="s">
-        <v>609</v>
-      </c>
+      <c r="N122" s="5"/>
       <c r="O122" s="13" t="s">
-        <v>609</v>
-      </c>
-      <c r="P122" s="14" t="s">
-        <v>607</v>
-      </c>
-      <c r="Q122" s="5" t="s">
+        <v>608</v>
+      </c>
+      <c r="P122" s="13" t="s">
+        <v>608</v>
+      </c>
+      <c r="Q122" s="14" t="s">
+        <v>606</v>
+      </c>
+      <c r="R122" s="5" t="s">
         <v>530</v>
       </c>
     </row>
-    <row r="123" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A123" s="4" t="s">
         <v>116</v>
       </c>
@@ -8778,25 +8914,26 @@
       <c r="H123" s="5"/>
       <c r="I123" s="5"/>
       <c r="J123" s="5"/>
-      <c r="K123" s="5" t="s">
+      <c r="K123" s="5"/>
+      <c r="L123" s="5" t="s">
         <v>372</v>
       </c>
-      <c r="L123" s="5"/>
       <c r="M123" s="5"/>
-      <c r="N123" s="14" t="s">
-        <v>606</v>
-      </c>
+      <c r="N123" s="5"/>
       <c r="O123" s="14" t="s">
-        <v>609</v>
+        <v>605</v>
       </c>
       <c r="P123" s="14" t="s">
-        <v>606</v>
-      </c>
-      <c r="Q123" s="5" t="s">
+        <v>608</v>
+      </c>
+      <c r="Q123" s="14" t="s">
+        <v>605</v>
+      </c>
+      <c r="R123" s="5" t="s">
         <v>520</v>
       </c>
     </row>
-    <row r="124" spans="1:17" ht="135" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:18" ht="135" x14ac:dyDescent="0.3">
       <c r="A124" s="4" t="s">
         <v>116</v>
       </c>
@@ -8819,27 +8956,28 @@
       <c r="H124" s="5"/>
       <c r="I124" s="5"/>
       <c r="J124" s="5"/>
-      <c r="K124" s="5" t="s">
+      <c r="K124" s="5"/>
+      <c r="L124" s="5" t="s">
         <v>370</v>
       </c>
-      <c r="L124" s="5"/>
-      <c r="M124" s="10" t="s">
-        <v>594</v>
-      </c>
-      <c r="N124" s="14" t="s">
-        <v>606</v>
+      <c r="M124" s="5"/>
+      <c r="N124" s="10" t="s">
+        <v>593</v>
       </c>
       <c r="O124" s="14" t="s">
-        <v>609</v>
+        <v>605</v>
       </c>
       <c r="P124" s="14" t="s">
-        <v>609</v>
-      </c>
-      <c r="Q124" s="5" t="s">
+        <v>608</v>
+      </c>
+      <c r="Q124" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="R124" s="5" t="s">
         <v>523</v>
       </c>
     </row>
-    <row r="125" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A125" s="4" t="s">
         <v>116</v>
       </c>
@@ -8862,25 +9000,26 @@
       <c r="H125" s="5"/>
       <c r="I125" s="5"/>
       <c r="J125" s="5"/>
-      <c r="K125" s="5" t="s">
+      <c r="K125" s="5"/>
+      <c r="L125" s="5" t="s">
         <v>376</v>
       </c>
-      <c r="L125" s="5"/>
       <c r="M125" s="5"/>
-      <c r="N125" s="14" t="s">
-        <v>606</v>
-      </c>
+      <c r="N125" s="5"/>
       <c r="O125" s="14" t="s">
-        <v>609</v>
+        <v>605</v>
       </c>
       <c r="P125" s="14" t="s">
-        <v>606</v>
-      </c>
-      <c r="Q125" s="5" t="s">
+        <v>608</v>
+      </c>
+      <c r="Q125" s="14" t="s">
+        <v>605</v>
+      </c>
+      <c r="R125" s="5" t="s">
         <v>526</v>
       </c>
     </row>
-    <row r="126" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A126" s="4" t="s">
         <v>116</v>
       </c>
@@ -8903,25 +9042,26 @@
       <c r="H126" s="5"/>
       <c r="I126" s="5"/>
       <c r="J126" s="5"/>
-      <c r="K126" s="5" t="s">
+      <c r="K126" s="5"/>
+      <c r="L126" s="5" t="s">
         <v>372</v>
       </c>
-      <c r="L126" s="5"/>
       <c r="M126" s="5"/>
-      <c r="N126" s="14" t="s">
-        <v>606</v>
-      </c>
+      <c r="N126" s="5"/>
       <c r="O126" s="14" t="s">
-        <v>609</v>
+        <v>605</v>
       </c>
       <c r="P126" s="14" t="s">
-        <v>606</v>
-      </c>
-      <c r="Q126" s="5" t="s">
+        <v>608</v>
+      </c>
+      <c r="Q126" s="14" t="s">
+        <v>605</v>
+      </c>
+      <c r="R126" s="5" t="s">
         <v>527</v>
       </c>
     </row>
-    <row r="127" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A127" s="4" t="s">
         <v>116</v>
       </c>
@@ -8944,25 +9084,26 @@
       <c r="H127" s="5"/>
       <c r="I127" s="5"/>
       <c r="J127" s="5"/>
-      <c r="K127" s="5" t="s">
+      <c r="K127" s="5"/>
+      <c r="L127" s="5" t="s">
         <v>370</v>
       </c>
-      <c r="L127" s="5"/>
       <c r="M127" s="5"/>
-      <c r="N127" s="14" t="s">
-        <v>606</v>
-      </c>
+      <c r="N127" s="5"/>
       <c r="O127" s="14" t="s">
-        <v>609</v>
+        <v>605</v>
       </c>
       <c r="P127" s="14" t="s">
-        <v>606</v>
-      </c>
-      <c r="Q127" s="5" t="s">
+        <v>608</v>
+      </c>
+      <c r="Q127" s="14" t="s">
+        <v>605</v>
+      </c>
+      <c r="R127" s="5" t="s">
         <v>524</v>
       </c>
     </row>
-    <row r="128" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A128" s="4" t="s">
         <v>116</v>
       </c>
@@ -8985,25 +9126,26 @@
       <c r="H128" s="5"/>
       <c r="I128" s="5"/>
       <c r="J128" s="5"/>
-      <c r="K128" s="5" t="s">
+      <c r="K128" s="5"/>
+      <c r="L128" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="L128" s="5"/>
       <c r="M128" s="5"/>
-      <c r="N128" s="14" t="s">
-        <v>607</v>
-      </c>
-      <c r="O128" s="13" t="s">
-        <v>609</v>
+      <c r="N128" s="5"/>
+      <c r="O128" s="14" t="s">
+        <v>606</v>
       </c>
       <c r="P128" s="13" t="s">
-        <v>609</v>
-      </c>
-      <c r="Q128" s="5" t="s">
+        <v>608</v>
+      </c>
+      <c r="Q128" s="13" t="s">
+        <v>608</v>
+      </c>
+      <c r="R128" s="5" t="s">
         <v>521</v>
       </c>
     </row>
-    <row r="129" spans="1:17" ht="40.5" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:18" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A129" s="4" t="s">
         <v>116</v>
       </c>
@@ -9026,27 +9168,28 @@
       <c r="H129" s="5"/>
       <c r="I129" s="5"/>
       <c r="J129" s="5"/>
-      <c r="K129" s="5" t="s">
+      <c r="K129" s="5"/>
+      <c r="L129" s="5" t="s">
         <v>370</v>
       </c>
-      <c r="L129" s="5"/>
-      <c r="M129" s="10" t="s">
-        <v>593</v>
-      </c>
-      <c r="N129" s="14" t="s">
-        <v>606</v>
+      <c r="M129" s="5"/>
+      <c r="N129" s="10" t="s">
+        <v>592</v>
       </c>
       <c r="O129" s="14" t="s">
-        <v>609</v>
+        <v>605</v>
       </c>
       <c r="P129" s="14" t="s">
-        <v>609</v>
-      </c>
-      <c r="Q129" s="5" t="s">
+        <v>608</v>
+      </c>
+      <c r="Q129" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="R129" s="5" t="s">
         <v>525</v>
       </c>
     </row>
-    <row r="130" spans="1:17" ht="54" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:18" ht="54" x14ac:dyDescent="0.3">
       <c r="A130" s="4" t="s">
         <v>116</v>
       </c>
@@ -9069,27 +9212,28 @@
       <c r="H130" s="5"/>
       <c r="I130" s="5"/>
       <c r="J130" s="5"/>
-      <c r="K130" s="5" t="s">
+      <c r="K130" s="5"/>
+      <c r="L130" s="5" t="s">
         <v>372</v>
       </c>
-      <c r="L130" s="5" t="s">
-        <v>705</v>
-      </c>
-      <c r="M130" s="5"/>
-      <c r="N130" s="14" t="s">
-        <v>606</v>
-      </c>
+      <c r="M130" s="5" t="s">
+        <v>704</v>
+      </c>
+      <c r="N130" s="5"/>
       <c r="O130" s="14" t="s">
-        <v>610</v>
+        <v>605</v>
       </c>
       <c r="P130" s="14" t="s">
-        <v>606</v>
-      </c>
-      <c r="Q130" s="5" t="s">
+        <v>609</v>
+      </c>
+      <c r="Q130" s="14" t="s">
+        <v>605</v>
+      </c>
+      <c r="R130" s="5" t="s">
         <v>528</v>
       </c>
     </row>
-    <row r="131" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A131" s="4" t="s">
         <v>116</v>
       </c>
@@ -9112,25 +9256,26 @@
       <c r="H131" s="5"/>
       <c r="I131" s="5"/>
       <c r="J131" s="5"/>
-      <c r="K131" s="5" t="s">
+      <c r="K131" s="5"/>
+      <c r="L131" s="5" t="s">
         <v>372</v>
       </c>
-      <c r="L131" s="5"/>
       <c r="M131" s="5"/>
-      <c r="N131" s="14" t="s">
-        <v>606</v>
-      </c>
+      <c r="N131" s="5"/>
       <c r="O131" s="14" t="s">
-        <v>609</v>
+        <v>605</v>
       </c>
       <c r="P131" s="14" t="s">
-        <v>609</v>
-      </c>
-      <c r="Q131" s="5" t="s">
+        <v>608</v>
+      </c>
+      <c r="Q131" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="R131" s="5" t="s">
         <v>522</v>
       </c>
     </row>
-    <row r="132" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A132" s="4" t="s">
         <v>116</v>
       </c>
@@ -9153,25 +9298,26 @@
       <c r="H132" s="5"/>
       <c r="I132" s="5"/>
       <c r="J132" s="5"/>
-      <c r="K132" s="5" t="s">
+      <c r="K132" s="5"/>
+      <c r="L132" s="5" t="s">
         <v>372</v>
       </c>
-      <c r="L132" s="5"/>
       <c r="M132" s="5"/>
-      <c r="N132" s="14" t="s">
-        <v>606</v>
-      </c>
+      <c r="N132" s="5"/>
       <c r="O132" s="14" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="P132" s="14" t="s">
-        <v>606</v>
-      </c>
-      <c r="Q132" s="5" t="s">
+        <v>605</v>
+      </c>
+      <c r="Q132" s="14" t="s">
+        <v>605</v>
+      </c>
+      <c r="R132" s="5" t="s">
         <v>529</v>
       </c>
     </row>
-    <row r="133" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A133" s="4" t="s">
         <v>117</v>
       </c>
@@ -9194,25 +9340,26 @@
       <c r="H133" s="5"/>
       <c r="I133" s="5"/>
       <c r="J133" s="5"/>
-      <c r="K133" s="5" t="s">
+      <c r="K133" s="5"/>
+      <c r="L133" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="L133" s="5"/>
       <c r="M133" s="5"/>
-      <c r="N133" s="14" t="s">
-        <v>607</v>
-      </c>
-      <c r="O133" s="13" t="s">
-        <v>609</v>
+      <c r="N133" s="5"/>
+      <c r="O133" s="14" t="s">
+        <v>606</v>
       </c>
       <c r="P133" s="13" t="s">
-        <v>609</v>
-      </c>
-      <c r="Q133" s="5" t="s">
+        <v>608</v>
+      </c>
+      <c r="Q133" s="13" t="s">
+        <v>608</v>
+      </c>
+      <c r="R133" s="5" t="s">
         <v>549</v>
       </c>
     </row>
-    <row r="134" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A134" s="4" t="s">
         <v>117</v>
       </c>
@@ -9235,25 +9382,26 @@
       <c r="H134" s="5"/>
       <c r="I134" s="5"/>
       <c r="J134" s="5"/>
-      <c r="K134" s="5" t="s">
+      <c r="K134" s="5"/>
+      <c r="L134" s="5" t="s">
         <v>370</v>
       </c>
-      <c r="L134" s="5"/>
       <c r="M134" s="5"/>
-      <c r="N134" s="14" t="s">
-        <v>606</v>
-      </c>
-      <c r="O134" s="13" t="s">
-        <v>609</v>
-      </c>
-      <c r="P134" s="14" t="s">
-        <v>609</v>
-      </c>
-      <c r="Q134" s="5" t="s">
+      <c r="N134" s="5"/>
+      <c r="O134" s="14" t="s">
+        <v>605</v>
+      </c>
+      <c r="P134" s="13" t="s">
+        <v>608</v>
+      </c>
+      <c r="Q134" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="R134" s="5" t="s">
         <v>538</v>
       </c>
     </row>
-    <row r="135" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A135" s="4" t="s">
         <v>117</v>
       </c>
@@ -9276,25 +9424,26 @@
       <c r="H135" s="5"/>
       <c r="I135" s="5"/>
       <c r="J135" s="5"/>
-      <c r="K135" s="5" t="s">
+      <c r="K135" s="5"/>
+      <c r="L135" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="L135" s="5"/>
       <c r="M135" s="5"/>
-      <c r="N135" s="14" t="s">
-        <v>607</v>
-      </c>
+      <c r="N135" s="5"/>
       <c r="O135" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="P135" s="14" t="s">
-        <v>607</v>
-      </c>
-      <c r="Q135" s="5" t="s">
+        <v>606</v>
+      </c>
+      <c r="Q135" s="14" t="s">
+        <v>606</v>
+      </c>
+      <c r="R135" s="5" t="s">
         <v>545</v>
       </c>
     </row>
-    <row r="136" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A136" s="4" t="s">
         <v>117</v>
       </c>
@@ -9317,25 +9466,26 @@
       <c r="H136" s="5"/>
       <c r="I136" s="5"/>
       <c r="J136" s="5"/>
-      <c r="K136" s="5" t="s">
+      <c r="K136" s="5"/>
+      <c r="L136" s="5" t="s">
         <v>372</v>
       </c>
-      <c r="L136" s="5"/>
       <c r="M136" s="5"/>
-      <c r="N136" s="14" t="s">
-        <v>606</v>
-      </c>
+      <c r="N136" s="5"/>
       <c r="O136" s="14" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="P136" s="14" t="s">
-        <v>609</v>
-      </c>
-      <c r="Q136" s="5" t="s">
+        <v>605</v>
+      </c>
+      <c r="Q136" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="R136" s="5" t="s">
         <v>533</v>
       </c>
     </row>
-    <row r="137" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A137" s="4" t="s">
         <v>117</v>
       </c>
@@ -9358,25 +9508,26 @@
       <c r="H137" s="5"/>
       <c r="I137" s="5"/>
       <c r="J137" s="5"/>
-      <c r="K137" s="5" t="s">
+      <c r="K137" s="5"/>
+      <c r="L137" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="L137" s="5"/>
       <c r="M137" s="5"/>
-      <c r="N137" s="14" t="s">
-        <v>607</v>
-      </c>
+      <c r="N137" s="5"/>
       <c r="O137" s="14" t="s">
-        <v>607</v>
-      </c>
-      <c r="P137" s="13" t="s">
-        <v>609</v>
-      </c>
-      <c r="Q137" s="5" t="s">
+        <v>606</v>
+      </c>
+      <c r="P137" s="14" t="s">
+        <v>606</v>
+      </c>
+      <c r="Q137" s="13" t="s">
+        <v>608</v>
+      </c>
+      <c r="R137" s="5" t="s">
         <v>542</v>
       </c>
     </row>
-    <row r="138" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A138" s="4" t="s">
         <v>117</v>
       </c>
@@ -9399,25 +9550,26 @@
       <c r="H138" s="5"/>
       <c r="I138" s="5"/>
       <c r="J138" s="5"/>
-      <c r="K138" s="5" t="s">
+      <c r="K138" s="5"/>
+      <c r="L138" s="5" t="s">
         <v>372</v>
       </c>
-      <c r="L138" s="5"/>
       <c r="M138" s="5"/>
-      <c r="N138" s="14" t="s">
-        <v>606</v>
-      </c>
+      <c r="N138" s="5"/>
       <c r="O138" s="14" t="s">
-        <v>609</v>
+        <v>605</v>
       </c>
       <c r="P138" s="14" t="s">
-        <v>606</v>
-      </c>
-      <c r="Q138" s="5" t="s">
+        <v>608</v>
+      </c>
+      <c r="Q138" s="14" t="s">
+        <v>605</v>
+      </c>
+      <c r="R138" s="5" t="s">
         <v>537</v>
       </c>
     </row>
-    <row r="139" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A139" s="4" t="s">
         <v>117</v>
       </c>
@@ -9440,25 +9592,26 @@
       <c r="H139" s="5"/>
       <c r="I139" s="5"/>
       <c r="J139" s="5"/>
-      <c r="K139" s="5" t="s">
+      <c r="K139" s="5"/>
+      <c r="L139" s="5" t="s">
         <v>372</v>
       </c>
-      <c r="L139" s="5"/>
       <c r="M139" s="5"/>
-      <c r="N139" s="14" t="s">
-        <v>606</v>
-      </c>
+      <c r="N139" s="5"/>
       <c r="O139" s="14" t="s">
-        <v>609</v>
+        <v>605</v>
       </c>
       <c r="P139" s="14" t="s">
-        <v>609</v>
-      </c>
-      <c r="Q139" s="5" t="s">
-        <v>695</v>
-      </c>
-    </row>
-    <row r="140" spans="1:17" x14ac:dyDescent="0.3">
+        <v>608</v>
+      </c>
+      <c r="Q139" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="R139" s="5" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="140" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A140" s="4" t="s">
         <v>117</v>
       </c>
@@ -9481,25 +9634,26 @@
       <c r="H140" s="5"/>
       <c r="I140" s="5"/>
       <c r="J140" s="5"/>
-      <c r="K140" s="5" t="s">
+      <c r="K140" s="5"/>
+      <c r="L140" s="5" t="s">
         <v>370</v>
       </c>
-      <c r="L140" s="5"/>
       <c r="M140" s="5"/>
-      <c r="N140" s="14" t="s">
-        <v>606</v>
-      </c>
+      <c r="N140" s="5"/>
       <c r="O140" s="14" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="P140" s="14" t="s">
-        <v>606</v>
-      </c>
-      <c r="Q140" s="5" t="s">
+        <v>605</v>
+      </c>
+      <c r="Q140" s="14" t="s">
+        <v>605</v>
+      </c>
+      <c r="R140" s="5" t="s">
         <v>535</v>
       </c>
     </row>
-    <row r="141" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A141" s="4" t="s">
         <v>117</v>
       </c>
@@ -9522,25 +9676,26 @@
       <c r="H141" s="5"/>
       <c r="I141" s="5"/>
       <c r="J141" s="5"/>
-      <c r="K141" s="5" t="s">
+      <c r="K141" s="5"/>
+      <c r="L141" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="L141" s="5"/>
       <c r="M141" s="5"/>
-      <c r="N141" s="14" t="s">
-        <v>607</v>
-      </c>
+      <c r="N141" s="5"/>
       <c r="O141" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="P141" s="14" t="s">
-        <v>607</v>
-      </c>
-      <c r="Q141" s="5" t="s">
+        <v>606</v>
+      </c>
+      <c r="Q141" s="14" t="s">
+        <v>606</v>
+      </c>
+      <c r="R141" s="5" t="s">
         <v>540</v>
       </c>
     </row>
-    <row r="142" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A142" s="4" t="s">
         <v>117</v>
       </c>
@@ -9563,25 +9718,26 @@
       <c r="H142" s="5"/>
       <c r="I142" s="5"/>
       <c r="J142" s="5"/>
-      <c r="K142" s="5" t="s">
+      <c r="K142" s="5"/>
+      <c r="L142" s="5" t="s">
         <v>370</v>
       </c>
-      <c r="L142" s="5"/>
       <c r="M142" s="5"/>
-      <c r="N142" s="14" t="s">
-        <v>606</v>
-      </c>
+      <c r="N142" s="5"/>
       <c r="O142" s="14" t="s">
-        <v>609</v>
+        <v>605</v>
       </c>
       <c r="P142" s="14" t="s">
-        <v>609</v>
-      </c>
-      <c r="Q142" s="5" t="s">
-        <v>696</v>
-      </c>
-    </row>
-    <row r="143" spans="1:17" x14ac:dyDescent="0.3">
+        <v>608</v>
+      </c>
+      <c r="Q142" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="R142" s="5" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="143" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A143" s="4" t="s">
         <v>117</v>
       </c>
@@ -9604,25 +9760,26 @@
       <c r="H143" s="5"/>
       <c r="I143" s="5"/>
       <c r="J143" s="5"/>
-      <c r="K143" s="5" t="s">
+      <c r="K143" s="5"/>
+      <c r="L143" s="5" t="s">
         <v>370</v>
       </c>
-      <c r="L143" s="5"/>
       <c r="M143" s="5"/>
-      <c r="N143" s="14" t="s">
-        <v>609</v>
-      </c>
+      <c r="N143" s="5"/>
       <c r="O143" s="14" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="P143" s="14" t="s">
         <v>609</v>
       </c>
-      <c r="Q143" s="5" t="s">
+      <c r="Q143" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="R143" s="5" t="s">
         <v>543</v>
       </c>
     </row>
-    <row r="144" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A144" s="4" t="s">
         <v>117</v>
       </c>
@@ -9645,25 +9802,26 @@
       <c r="H144" s="5"/>
       <c r="I144" s="5"/>
       <c r="J144" s="5"/>
-      <c r="K144" s="5" t="s">
+      <c r="K144" s="5"/>
+      <c r="L144" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="L144" s="5"/>
       <c r="M144" s="5"/>
-      <c r="N144" s="13" t="s">
-        <v>609</v>
-      </c>
-      <c r="O144" s="14" t="s">
-        <v>607</v>
-      </c>
-      <c r="P144" s="13" t="s">
-        <v>609</v>
-      </c>
-      <c r="Q144" s="5" t="s">
+      <c r="N144" s="5"/>
+      <c r="O144" s="13" t="s">
+        <v>608</v>
+      </c>
+      <c r="P144" s="14" t="s">
+        <v>606</v>
+      </c>
+      <c r="Q144" s="13" t="s">
+        <v>608</v>
+      </c>
+      <c r="R144" s="5" t="s">
         <v>544</v>
       </c>
     </row>
-    <row r="145" spans="1:17" ht="81" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:18" ht="81" x14ac:dyDescent="0.3">
       <c r="A145" s="4" t="s">
         <v>117</v>
       </c>
@@ -9686,27 +9844,28 @@
       <c r="H145" s="5"/>
       <c r="I145" s="5"/>
       <c r="J145" s="5"/>
-      <c r="K145" s="5" t="s">
+      <c r="K145" s="5"/>
+      <c r="L145" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="L145" s="5"/>
-      <c r="M145" s="10" t="s">
-        <v>595</v>
-      </c>
-      <c r="N145" s="13" t="s">
-        <v>609</v>
-      </c>
-      <c r="O145" s="14" t="s">
-        <v>607</v>
+      <c r="M145" s="5"/>
+      <c r="N145" s="10" t="s">
+        <v>594</v>
+      </c>
+      <c r="O145" s="13" t="s">
+        <v>608</v>
       </c>
       <c r="P145" s="14" t="s">
-        <v>607</v>
-      </c>
-      <c r="Q145" s="5" t="s">
+        <v>606</v>
+      </c>
+      <c r="Q145" s="14" t="s">
+        <v>606</v>
+      </c>
+      <c r="R145" s="5" t="s">
         <v>536</v>
       </c>
     </row>
-    <row r="146" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A146" s="4" t="s">
         <v>117</v>
       </c>
@@ -9729,25 +9888,26 @@
       <c r="H146" s="5"/>
       <c r="I146" s="5"/>
       <c r="J146" s="5"/>
-      <c r="K146" s="5" t="s">
+      <c r="K146" s="5"/>
+      <c r="L146" s="5" t="s">
         <v>375</v>
       </c>
-      <c r="L146" s="5"/>
       <c r="M146" s="5"/>
-      <c r="N146" s="14" t="s">
-        <v>607</v>
-      </c>
+      <c r="N146" s="5"/>
       <c r="O146" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="P146" s="14" t="s">
-        <v>607</v>
-      </c>
-      <c r="Q146" s="5" t="s">
+        <v>606</v>
+      </c>
+      <c r="Q146" s="14" t="s">
+        <v>606</v>
+      </c>
+      <c r="R146" s="5" t="s">
         <v>546</v>
       </c>
     </row>
-    <row r="147" spans="1:17" ht="148.5" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:18" ht="148.5" x14ac:dyDescent="0.3">
       <c r="A147" s="4" t="s">
         <v>117</v>
       </c>
@@ -9770,25 +9930,26 @@
       <c r="H147" s="5"/>
       <c r="I147" s="5"/>
       <c r="J147" s="5"/>
-      <c r="K147" s="5" t="s">
-        <v>707</v>
-      </c>
-      <c r="L147" s="5"/>
+      <c r="K147" s="5"/>
+      <c r="L147" s="5" t="s">
+        <v>706</v>
+      </c>
       <c r="M147" s="5"/>
-      <c r="N147" s="14" t="s">
-        <v>606</v>
-      </c>
+      <c r="N147" s="5"/>
       <c r="O147" s="14" t="s">
-        <v>609</v>
+        <v>605</v>
       </c>
       <c r="P147" s="14" t="s">
-        <v>606</v>
-      </c>
-      <c r="Q147" s="5" t="s">
+        <v>608</v>
+      </c>
+      <c r="Q147" s="14" t="s">
+        <v>605</v>
+      </c>
+      <c r="R147" s="5" t="s">
         <v>532</v>
       </c>
     </row>
-    <row r="148" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A148" s="4" t="s">
         <v>117</v>
       </c>
@@ -9811,25 +9972,26 @@
       <c r="H148" s="5"/>
       <c r="I148" s="5"/>
       <c r="J148" s="5"/>
-      <c r="K148" s="5" t="s">
-        <v>706</v>
-      </c>
-      <c r="L148" s="5"/>
+      <c r="K148" s="5"/>
+      <c r="L148" s="5" t="s">
+        <v>705</v>
+      </c>
       <c r="M148" s="5"/>
-      <c r="N148" s="14" t="s">
-        <v>607</v>
-      </c>
+      <c r="N148" s="5"/>
       <c r="O148" s="14" t="s">
-        <v>607</v>
-      </c>
-      <c r="P148" s="13" t="s">
-        <v>609</v>
-      </c>
-      <c r="Q148" s="5" t="s">
+        <v>606</v>
+      </c>
+      <c r="P148" s="14" t="s">
+        <v>606</v>
+      </c>
+      <c r="Q148" s="13" t="s">
+        <v>608</v>
+      </c>
+      <c r="R148" s="5" t="s">
         <v>534</v>
       </c>
     </row>
-    <row r="149" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A149" s="4" t="s">
         <v>117</v>
       </c>
@@ -9852,25 +10014,26 @@
       <c r="H149" s="5"/>
       <c r="I149" s="5"/>
       <c r="J149" s="5"/>
-      <c r="K149" s="5" t="s">
+      <c r="K149" s="5"/>
+      <c r="L149" s="5" t="s">
         <v>372</v>
       </c>
-      <c r="L149" s="5"/>
       <c r="M149" s="5"/>
-      <c r="N149" s="14" t="s">
-        <v>606</v>
-      </c>
+      <c r="N149" s="5"/>
       <c r="O149" s="14" t="s">
-        <v>609</v>
+        <v>605</v>
       </c>
       <c r="P149" s="14" t="s">
-        <v>606</v>
-      </c>
-      <c r="Q149" s="5" t="s">
+        <v>608</v>
+      </c>
+      <c r="Q149" s="14" t="s">
+        <v>605</v>
+      </c>
+      <c r="R149" s="5" t="s">
         <v>547</v>
       </c>
     </row>
-    <row r="150" spans="1:17" ht="135" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:18" ht="135" x14ac:dyDescent="0.3">
       <c r="A150" s="4" t="s">
         <v>117</v>
       </c>
@@ -9893,27 +10056,28 @@
       <c r="H150" s="5"/>
       <c r="I150" s="5"/>
       <c r="J150" s="5"/>
-      <c r="K150" s="5" t="s">
+      <c r="K150" s="5"/>
+      <c r="L150" s="5" t="s">
         <v>372</v>
       </c>
-      <c r="L150" s="5"/>
-      <c r="M150" s="10" t="s">
-        <v>596</v>
-      </c>
-      <c r="N150" s="14" t="s">
-        <v>610</v>
+      <c r="M150" s="5"/>
+      <c r="N150" s="10" t="s">
+        <v>595</v>
       </c>
       <c r="O150" s="14" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="P150" s="14" t="s">
-        <v>609</v>
-      </c>
-      <c r="Q150" s="5" t="s">
+        <v>605</v>
+      </c>
+      <c r="Q150" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="R150" s="5" t="s">
         <v>548</v>
       </c>
     </row>
-    <row r="151" spans="1:17" ht="148.5" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:18" ht="148.5" x14ac:dyDescent="0.3">
       <c r="A151" s="4" t="s">
         <v>117</v>
       </c>
@@ -9936,27 +10100,28 @@
       <c r="H151" s="5"/>
       <c r="I151" s="5"/>
       <c r="J151" s="5"/>
-      <c r="K151" s="5" t="s">
+      <c r="K151" s="5"/>
+      <c r="L151" s="5" t="s">
         <v>372</v>
       </c>
-      <c r="L151" s="5"/>
-      <c r="M151" s="10" t="s">
-        <v>597</v>
-      </c>
-      <c r="N151" s="14" t="s">
-        <v>606</v>
+      <c r="M151" s="5"/>
+      <c r="N151" s="10" t="s">
+        <v>596</v>
       </c>
       <c r="O151" s="14" t="s">
-        <v>610</v>
+        <v>605</v>
       </c>
       <c r="P151" s="14" t="s">
-        <v>606</v>
-      </c>
-      <c r="Q151" s="5" t="s">
+        <v>609</v>
+      </c>
+      <c r="Q151" s="14" t="s">
+        <v>605</v>
+      </c>
+      <c r="R151" s="5" t="s">
         <v>541</v>
       </c>
     </row>
-    <row r="152" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A152" s="4" t="s">
         <v>117</v>
       </c>
@@ -9979,25 +10144,26 @@
       <c r="H152" s="5"/>
       <c r="I152" s="5"/>
       <c r="J152" s="5"/>
-      <c r="K152" s="5" t="s">
+      <c r="K152" s="5"/>
+      <c r="L152" s="5" t="s">
         <v>380</v>
       </c>
-      <c r="L152" s="5"/>
       <c r="M152" s="5"/>
-      <c r="N152" s="14" t="s">
-        <v>606</v>
-      </c>
+      <c r="N152" s="5"/>
       <c r="O152" s="14" t="s">
-        <v>609</v>
+        <v>605</v>
       </c>
       <c r="P152" s="14" t="s">
-        <v>606</v>
-      </c>
-      <c r="Q152" s="5" t="s">
+        <v>608</v>
+      </c>
+      <c r="Q152" s="14" t="s">
+        <v>605</v>
+      </c>
+      <c r="R152" s="5" t="s">
         <v>550</v>
       </c>
     </row>
-    <row r="153" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A153" s="4" t="s">
         <v>117</v>
       </c>
@@ -10020,25 +10186,26 @@
       <c r="H153" s="5"/>
       <c r="I153" s="5"/>
       <c r="J153" s="5"/>
-      <c r="K153" s="5" t="s">
+      <c r="K153" s="5"/>
+      <c r="L153" s="5" t="s">
         <v>372</v>
       </c>
-      <c r="L153" s="5"/>
       <c r="M153" s="5"/>
-      <c r="N153" s="14" t="s">
-        <v>606</v>
-      </c>
+      <c r="N153" s="5"/>
       <c r="O153" s="14" t="s">
-        <v>610</v>
+        <v>605</v>
       </c>
       <c r="P153" s="14" t="s">
-        <v>606</v>
-      </c>
-      <c r="Q153" s="5" t="s">
+        <v>609</v>
+      </c>
+      <c r="Q153" s="14" t="s">
+        <v>605</v>
+      </c>
+      <c r="R153" s="5" t="s">
         <v>539</v>
       </c>
     </row>
-    <row r="154" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A154" s="4" t="s">
         <v>118</v>
       </c>
@@ -10061,25 +10228,26 @@
       <c r="H154" s="5"/>
       <c r="I154" s="5"/>
       <c r="J154" s="5"/>
-      <c r="K154" s="5" t="s">
+      <c r="K154" s="5"/>
+      <c r="L154" s="5" t="s">
         <v>372</v>
       </c>
-      <c r="L154" s="5"/>
       <c r="M154" s="5"/>
-      <c r="N154" s="14" t="s">
-        <v>610</v>
-      </c>
+      <c r="N154" s="5"/>
       <c r="O154" s="14" t="s">
         <v>609</v>
       </c>
       <c r="P154" s="14" t="s">
-        <v>606</v>
-      </c>
-      <c r="Q154" s="5" t="s">
+        <v>608</v>
+      </c>
+      <c r="Q154" s="14" t="s">
+        <v>605</v>
+      </c>
+      <c r="R154" s="5" t="s">
         <v>552</v>
       </c>
     </row>
-    <row r="155" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A155" s="4" t="s">
         <v>118</v>
       </c>
@@ -10102,25 +10270,26 @@
       <c r="H155" s="5"/>
       <c r="I155" s="5"/>
       <c r="J155" s="5"/>
-      <c r="K155" s="5" t="s">
+      <c r="K155" s="5"/>
+      <c r="L155" s="5" t="s">
         <v>372</v>
       </c>
-      <c r="L155" s="5"/>
       <c r="M155" s="5"/>
-      <c r="N155" s="13" t="s">
-        <v>609</v>
-      </c>
+      <c r="N155" s="5"/>
       <c r="O155" s="13" t="s">
-        <v>609</v>
-      </c>
-      <c r="P155" s="14" t="s">
-        <v>607</v>
-      </c>
-      <c r="Q155" s="5" t="s">
+        <v>608</v>
+      </c>
+      <c r="P155" s="13" t="s">
+        <v>608</v>
+      </c>
+      <c r="Q155" s="14" t="s">
+        <v>606</v>
+      </c>
+      <c r="R155" s="5" t="s">
         <v>553</v>
       </c>
     </row>
-    <row r="156" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A156" s="4" t="s">
         <v>118</v>
       </c>
@@ -10128,7 +10297,7 @@
         <v>300</v>
       </c>
       <c r="C156" s="5" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="D156" s="5" t="s">
         <v>4</v>
@@ -10143,25 +10312,26 @@
       <c r="H156" s="5"/>
       <c r="I156" s="5"/>
       <c r="J156" s="5"/>
-      <c r="K156" s="5" t="s">
+      <c r="K156" s="5"/>
+      <c r="L156" s="5" t="s">
         <v>383</v>
       </c>
-      <c r="L156" s="5"/>
       <c r="M156" s="5"/>
-      <c r="N156" s="14" t="s">
-        <v>606</v>
-      </c>
+      <c r="N156" s="5"/>
       <c r="O156" s="14" t="s">
-        <v>609</v>
+        <v>605</v>
       </c>
       <c r="P156" s="14" t="s">
-        <v>609</v>
-      </c>
-      <c r="Q156" s="5" t="s">
+        <v>608</v>
+      </c>
+      <c r="Q156" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="R156" s="5" t="s">
         <v>554</v>
       </c>
     </row>
-    <row r="157" spans="1:17" ht="202.5" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:18" ht="202.5" x14ac:dyDescent="0.3">
       <c r="A157" s="4" t="s">
         <v>118</v>
       </c>
@@ -10184,27 +10354,28 @@
       <c r="H157" s="5"/>
       <c r="I157" s="5"/>
       <c r="J157" s="5"/>
-      <c r="K157" s="5" t="s">
+      <c r="K157" s="5"/>
+      <c r="L157" s="5" t="s">
         <v>372</v>
       </c>
-      <c r="L157" s="5" t="s">
-        <v>729</v>
-      </c>
-      <c r="M157" s="5"/>
-      <c r="N157" s="14" t="s">
-        <v>606</v>
-      </c>
+      <c r="M157" s="5" t="s">
+        <v>728</v>
+      </c>
+      <c r="N157" s="5"/>
       <c r="O157" s="14" t="s">
-        <v>609</v>
+        <v>605</v>
       </c>
       <c r="P157" s="14" t="s">
-        <v>606</v>
-      </c>
-      <c r="Q157" s="5" t="s">
+        <v>608</v>
+      </c>
+      <c r="Q157" s="14" t="s">
+        <v>605</v>
+      </c>
+      <c r="R157" s="5" t="s">
         <v>556</v>
       </c>
     </row>
-    <row r="158" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A158" s="4" t="s">
         <v>118</v>
       </c>
@@ -10227,25 +10398,26 @@
       <c r="H158" s="5"/>
       <c r="I158" s="5"/>
       <c r="J158" s="5"/>
-      <c r="K158" s="5" t="s">
+      <c r="K158" s="5"/>
+      <c r="L158" s="5" t="s">
         <v>372</v>
       </c>
-      <c r="L158" s="5"/>
       <c r="M158" s="5"/>
-      <c r="N158" s="13" t="s">
-        <v>609</v>
-      </c>
+      <c r="N158" s="5"/>
       <c r="O158" s="13" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="P158" s="13" t="s">
-        <v>609</v>
-      </c>
-      <c r="Q158" s="5" t="s">
+        <v>608</v>
+      </c>
+      <c r="Q158" s="13" t="s">
+        <v>608</v>
+      </c>
+      <c r="R158" s="5" t="s">
         <v>551</v>
       </c>
     </row>
-    <row r="159" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A159" s="4" t="s">
         <v>118</v>
       </c>
@@ -10268,25 +10440,26 @@
       <c r="H159" s="5"/>
       <c r="I159" s="5"/>
       <c r="J159" s="5"/>
-      <c r="K159" s="5" t="s">
+      <c r="K159" s="5"/>
+      <c r="L159" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="L159" s="5"/>
       <c r="M159" s="5"/>
-      <c r="N159" s="13" t="s">
-        <v>609</v>
-      </c>
+      <c r="N159" s="5"/>
       <c r="O159" s="13" t="s">
-        <v>609</v>
-      </c>
-      <c r="P159" s="14" t="s">
-        <v>607</v>
-      </c>
-      <c r="Q159" s="5" t="s">
+        <v>608</v>
+      </c>
+      <c r="P159" s="13" t="s">
+        <v>608</v>
+      </c>
+      <c r="Q159" s="14" t="s">
+        <v>606</v>
+      </c>
+      <c r="R159" s="5" t="s">
         <v>560</v>
       </c>
     </row>
-    <row r="160" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A160" s="4" t="s">
         <v>118</v>
       </c>
@@ -10309,25 +10482,26 @@
       <c r="H160" s="5"/>
       <c r="I160" s="5"/>
       <c r="J160" s="5"/>
-      <c r="K160" s="5" t="s">
+      <c r="K160" s="5"/>
+      <c r="L160" s="5" t="s">
         <v>370</v>
       </c>
-      <c r="L160" s="5"/>
       <c r="M160" s="5"/>
-      <c r="N160" s="14" t="s">
-        <v>606</v>
-      </c>
+      <c r="N160" s="5"/>
       <c r="O160" s="14" t="s">
-        <v>609</v>
+        <v>605</v>
       </c>
       <c r="P160" s="14" t="s">
-        <v>609</v>
-      </c>
-      <c r="Q160" s="5" t="s">
+        <v>608</v>
+      </c>
+      <c r="Q160" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="R160" s="5" t="s">
         <v>561</v>
       </c>
     </row>
-    <row r="161" spans="1:17" ht="27" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:18" ht="27" x14ac:dyDescent="0.3">
       <c r="A161" s="4" t="s">
         <v>118</v>
       </c>
@@ -10350,27 +10524,28 @@
       <c r="H161" s="5"/>
       <c r="I161" s="5"/>
       <c r="J161" s="5"/>
-      <c r="K161" s="5" t="s">
+      <c r="K161" s="5"/>
+      <c r="L161" s="5" t="s">
         <v>372</v>
       </c>
-      <c r="L161" s="5" t="s">
-        <v>711</v>
-      </c>
-      <c r="M161" s="5"/>
-      <c r="N161" s="14" t="s">
-        <v>606</v>
-      </c>
+      <c r="M161" s="5" t="s">
+        <v>710</v>
+      </c>
+      <c r="N161" s="5"/>
       <c r="O161" s="14" t="s">
-        <v>609</v>
+        <v>605</v>
       </c>
       <c r="P161" s="14" t="s">
-        <v>606</v>
-      </c>
-      <c r="Q161" s="5" t="s">
+        <v>608</v>
+      </c>
+      <c r="Q161" s="14" t="s">
+        <v>605</v>
+      </c>
+      <c r="R161" s="5" t="s">
         <v>563</v>
       </c>
     </row>
-    <row r="162" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A162" s="4" t="s">
         <v>118</v>
       </c>
@@ -10393,27 +10568,28 @@
       <c r="H162" s="5"/>
       <c r="I162" s="5"/>
       <c r="J162" s="5"/>
-      <c r="K162" s="5" t="s">
+      <c r="K162" s="5"/>
+      <c r="L162" s="5" t="s">
         <v>372</v>
       </c>
-      <c r="L162" s="5" t="s">
-        <v>709</v>
-      </c>
-      <c r="M162" s="5"/>
-      <c r="N162" s="14" t="s">
-        <v>606</v>
-      </c>
+      <c r="M162" s="5" t="s">
+        <v>708</v>
+      </c>
+      <c r="N162" s="5"/>
       <c r="O162" s="14" t="s">
-        <v>610</v>
+        <v>605</v>
       </c>
       <c r="P162" s="14" t="s">
-        <v>606</v>
-      </c>
-      <c r="Q162" s="5" t="s">
+        <v>609</v>
+      </c>
+      <c r="Q162" s="14" t="s">
+        <v>605</v>
+      </c>
+      <c r="R162" s="5" t="s">
         <v>559</v>
       </c>
     </row>
-    <row r="163" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A163" s="4" t="s">
         <v>118</v>
       </c>
@@ -10436,25 +10612,26 @@
       <c r="H163" s="5"/>
       <c r="I163" s="5"/>
       <c r="J163" s="5"/>
-      <c r="K163" s="5" t="s">
+      <c r="K163" s="5"/>
+      <c r="L163" s="5" t="s">
         <v>377</v>
       </c>
-      <c r="L163" s="5"/>
       <c r="M163" s="5"/>
-      <c r="N163" s="14" t="s">
-        <v>606</v>
-      </c>
+      <c r="N163" s="5"/>
       <c r="O163" s="14" t="s">
-        <v>609</v>
+        <v>605</v>
       </c>
       <c r="P163" s="14" t="s">
-        <v>606</v>
-      </c>
-      <c r="Q163" s="5" t="s">
+        <v>608</v>
+      </c>
+      <c r="Q163" s="14" t="s">
+        <v>605</v>
+      </c>
+      <c r="R163" s="5" t="s">
         <v>566</v>
       </c>
     </row>
-    <row r="164" spans="1:17" ht="175.5" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:18" ht="175.5" x14ac:dyDescent="0.3">
       <c r="A164" s="4" t="s">
         <v>118</v>
       </c>
@@ -10477,27 +10654,28 @@
       <c r="H164" s="5"/>
       <c r="I164" s="5"/>
       <c r="J164" s="5"/>
-      <c r="K164" s="5" t="s">
+      <c r="K164" s="5"/>
+      <c r="L164" s="5" t="s">
         <v>370</v>
       </c>
-      <c r="L164" s="5" t="s">
-        <v>715</v>
-      </c>
-      <c r="M164" s="5"/>
-      <c r="N164" s="14" t="s">
-        <v>609</v>
-      </c>
+      <c r="M164" s="5" t="s">
+        <v>714</v>
+      </c>
+      <c r="N164" s="5"/>
       <c r="O164" s="14" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="P164" s="14" t="s">
-        <v>606</v>
-      </c>
-      <c r="Q164" s="5" t="s">
+        <v>608</v>
+      </c>
+      <c r="Q164" s="14" t="s">
+        <v>605</v>
+      </c>
+      <c r="R164" s="5" t="s">
         <v>567</v>
       </c>
     </row>
-    <row r="165" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A165" s="4" t="s">
         <v>118</v>
       </c>
@@ -10520,25 +10698,26 @@
       <c r="H165" s="5"/>
       <c r="I165" s="5"/>
       <c r="J165" s="5"/>
-      <c r="K165" s="5" t="s">
+      <c r="K165" s="5"/>
+      <c r="L165" s="5" t="s">
         <v>372</v>
       </c>
-      <c r="L165" s="5"/>
       <c r="M165" s="5"/>
-      <c r="N165" s="14" t="s">
-        <v>606</v>
-      </c>
+      <c r="N165" s="5"/>
       <c r="O165" s="14" t="s">
-        <v>610</v>
+        <v>605</v>
       </c>
       <c r="P165" s="14" t="s">
-        <v>606</v>
-      </c>
-      <c r="Q165" s="5" t="s">
+        <v>609</v>
+      </c>
+      <c r="Q165" s="14" t="s">
+        <v>605</v>
+      </c>
+      <c r="R165" s="5" t="s">
         <v>569</v>
       </c>
     </row>
-    <row r="166" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A166" s="4" t="s">
         <v>118</v>
       </c>
@@ -10561,25 +10740,26 @@
       <c r="H166" s="5"/>
       <c r="I166" s="5"/>
       <c r="J166" s="5"/>
-      <c r="K166" s="5" t="s">
+      <c r="K166" s="5"/>
+      <c r="L166" s="5" t="s">
         <v>377</v>
       </c>
-      <c r="L166" s="5"/>
       <c r="M166" s="5"/>
-      <c r="N166" s="14" t="s">
-        <v>606</v>
-      </c>
+      <c r="N166" s="5"/>
       <c r="O166" s="14" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="P166" s="14" t="s">
-        <v>609</v>
-      </c>
-      <c r="Q166" s="5" t="s">
+        <v>605</v>
+      </c>
+      <c r="Q166" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="R166" s="5" t="s">
         <v>555</v>
       </c>
     </row>
-    <row r="167" spans="1:17" ht="40.5" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:18" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A167" s="4" t="s">
         <v>118</v>
       </c>
@@ -10602,27 +10782,28 @@
       <c r="H167" s="5"/>
       <c r="I167" s="5"/>
       <c r="J167" s="5"/>
-      <c r="K167" s="5" t="s">
+      <c r="K167" s="5"/>
+      <c r="L167" s="5" t="s">
         <v>377</v>
       </c>
-      <c r="L167" s="5"/>
-      <c r="M167" s="10" t="s">
-        <v>598</v>
-      </c>
-      <c r="N167" s="14" t="s">
-        <v>609</v>
+      <c r="M167" s="5"/>
+      <c r="N167" s="10" t="s">
+        <v>597</v>
       </c>
       <c r="O167" s="14" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="P167" s="14" t="s">
-        <v>609</v>
-      </c>
-      <c r="Q167" s="5" t="s">
+        <v>608</v>
+      </c>
+      <c r="Q167" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="R167" s="5" t="s">
         <v>568</v>
       </c>
     </row>
-    <row r="168" spans="1:17" ht="27" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:18" ht="27" x14ac:dyDescent="0.3">
       <c r="A168" s="4" t="s">
         <v>118</v>
       </c>
@@ -10645,27 +10826,28 @@
       <c r="H168" s="5"/>
       <c r="I168" s="5"/>
       <c r="J168" s="5"/>
-      <c r="K168" s="5" t="s">
+      <c r="K168" s="5"/>
+      <c r="L168" s="5" t="s">
         <v>376</v>
       </c>
-      <c r="L168" s="5" t="s">
-        <v>708</v>
-      </c>
-      <c r="M168" s="5"/>
-      <c r="N168" s="14" t="s">
-        <v>606</v>
-      </c>
+      <c r="M168" s="5" t="s">
+        <v>707</v>
+      </c>
+      <c r="N168" s="5"/>
       <c r="O168" s="14" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="P168" s="14" t="s">
-        <v>609</v>
-      </c>
-      <c r="Q168" s="5" t="s">
+        <v>605</v>
+      </c>
+      <c r="Q168" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="R168" s="5" t="s">
         <v>557</v>
       </c>
     </row>
-    <row r="169" spans="1:17" ht="283.5" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:18" ht="283.5" x14ac:dyDescent="0.3">
       <c r="A169" s="4" t="s">
         <v>118</v>
       </c>
@@ -10688,27 +10870,28 @@
       <c r="H169" s="5"/>
       <c r="I169" s="5"/>
       <c r="J169" s="5"/>
-      <c r="K169" s="5" t="s">
+      <c r="K169" s="5"/>
+      <c r="L169" s="5" t="s">
         <v>382</v>
       </c>
-      <c r="L169" s="5"/>
-      <c r="M169" s="10" t="s">
-        <v>599</v>
-      </c>
-      <c r="N169" s="14" t="s">
-        <v>606</v>
+      <c r="M169" s="5"/>
+      <c r="N169" s="10" t="s">
+        <v>598</v>
       </c>
       <c r="O169" s="14" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="P169" s="14" t="s">
-        <v>606</v>
-      </c>
-      <c r="Q169" s="5" t="s">
+        <v>605</v>
+      </c>
+      <c r="Q169" s="14" t="s">
+        <v>605</v>
+      </c>
+      <c r="R169" s="5" t="s">
         <v>558</v>
       </c>
     </row>
-    <row r="170" spans="1:17" ht="27" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:18" ht="27" x14ac:dyDescent="0.3">
       <c r="A170" s="4" t="s">
         <v>118</v>
       </c>
@@ -10731,27 +10914,28 @@
       <c r="H170" s="5"/>
       <c r="I170" s="5"/>
       <c r="J170" s="5"/>
-      <c r="K170" s="5" t="s">
+      <c r="K170" s="5"/>
+      <c r="L170" s="5" t="s">
         <v>376</v>
       </c>
-      <c r="L170" s="5" t="s">
-        <v>710</v>
-      </c>
-      <c r="M170" s="5"/>
-      <c r="N170" s="14" t="s">
-        <v>606</v>
-      </c>
+      <c r="M170" s="5" t="s">
+        <v>709</v>
+      </c>
+      <c r="N170" s="5"/>
       <c r="O170" s="14" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="P170" s="14" t="s">
-        <v>609</v>
-      </c>
-      <c r="Q170" s="5" t="s">
+        <v>605</v>
+      </c>
+      <c r="Q170" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="R170" s="5" t="s">
         <v>562</v>
       </c>
     </row>
-    <row r="171" spans="1:17" ht="40.5" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:18" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A171" s="4" t="s">
         <v>118</v>
       </c>
@@ -10774,27 +10958,28 @@
       <c r="H171" s="5"/>
       <c r="I171" s="5"/>
       <c r="J171" s="5"/>
-      <c r="K171" s="5" t="s">
+      <c r="K171" s="5"/>
+      <c r="L171" s="5" t="s">
         <v>376</v>
       </c>
-      <c r="L171" s="5" t="s">
-        <v>712</v>
-      </c>
-      <c r="M171" s="5"/>
-      <c r="N171" s="14" t="s">
-        <v>606</v>
-      </c>
+      <c r="M171" s="5" t="s">
+        <v>711</v>
+      </c>
+      <c r="N171" s="5"/>
       <c r="O171" s="14" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="P171" s="14" t="s">
-        <v>610</v>
-      </c>
-      <c r="Q171" s="5" t="s">
+        <v>605</v>
+      </c>
+      <c r="Q171" s="14" t="s">
+        <v>609</v>
+      </c>
+      <c r="R171" s="5" t="s">
         <v>565</v>
       </c>
     </row>
-    <row r="172" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A172" s="4" t="s">
         <v>118</v>
       </c>
@@ -10817,25 +11002,26 @@
       <c r="H172" s="5"/>
       <c r="I172" s="5"/>
       <c r="J172" s="5"/>
-      <c r="K172" s="5" t="s">
+      <c r="K172" s="5"/>
+      <c r="L172" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="L172" s="5"/>
       <c r="M172" s="5"/>
-      <c r="N172" s="14" t="s">
-        <v>606</v>
-      </c>
+      <c r="N172" s="5"/>
       <c r="O172" s="14" t="s">
-        <v>609</v>
+        <v>605</v>
       </c>
       <c r="P172" s="14" t="s">
-        <v>606</v>
-      </c>
-      <c r="Q172" s="5" t="s">
+        <v>608</v>
+      </c>
+      <c r="Q172" s="14" t="s">
+        <v>605</v>
+      </c>
+      <c r="R172" s="5" t="s">
         <v>564</v>
       </c>
     </row>
-    <row r="173" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A173" s="4" t="s">
         <v>313</v>
       </c>
@@ -10858,25 +11044,26 @@
       <c r="H173" s="5"/>
       <c r="I173" s="5"/>
       <c r="J173" s="5"/>
-      <c r="K173" s="5" t="s">
+      <c r="K173" s="5"/>
+      <c r="L173" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="L173" s="5"/>
       <c r="M173" s="5"/>
-      <c r="N173" s="13" t="s">
-        <v>609</v>
-      </c>
+      <c r="N173" s="5"/>
       <c r="O173" s="13" t="s">
-        <v>609</v>
-      </c>
-      <c r="P173" s="14" t="s">
-        <v>607</v>
-      </c>
-      <c r="Q173" s="5" t="s">
+        <v>608</v>
+      </c>
+      <c r="P173" s="13" t="s">
+        <v>608</v>
+      </c>
+      <c r="Q173" s="14" t="s">
+        <v>606</v>
+      </c>
+      <c r="R173" s="5" t="s">
         <v>571</v>
       </c>
     </row>
-    <row r="174" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A174" s="4" t="s">
         <v>313</v>
       </c>
@@ -10899,25 +11086,26 @@
       <c r="H174" s="5"/>
       <c r="I174" s="5"/>
       <c r="J174" s="5"/>
-      <c r="K174" s="5" t="s">
+      <c r="K174" s="5"/>
+      <c r="L174" s="5" t="s">
         <v>372</v>
       </c>
-      <c r="L174" s="5"/>
       <c r="M174" s="5"/>
-      <c r="N174" s="14" t="s">
-        <v>609</v>
-      </c>
+      <c r="N174" s="5"/>
       <c r="O174" s="14" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="P174" s="14" t="s">
-        <v>606</v>
-      </c>
-      <c r="Q174" s="5" t="s">
+        <v>608</v>
+      </c>
+      <c r="Q174" s="14" t="s">
+        <v>605</v>
+      </c>
+      <c r="R174" s="5" t="s">
         <v>572</v>
       </c>
     </row>
-    <row r="175" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A175" s="4" t="s">
         <v>313</v>
       </c>
@@ -10940,25 +11128,26 @@
       <c r="H175" s="5"/>
       <c r="I175" s="5"/>
       <c r="J175" s="5"/>
-      <c r="K175" s="5" t="s">
+      <c r="K175" s="5"/>
+      <c r="L175" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="L175" s="5"/>
       <c r="M175" s="5"/>
-      <c r="N175" s="13" t="s">
-        <v>609</v>
-      </c>
+      <c r="N175" s="5"/>
       <c r="O175" s="13" t="s">
-        <v>609</v>
-      </c>
-      <c r="P175" s="14" t="s">
-        <v>607</v>
-      </c>
-      <c r="Q175" s="5" t="s">
+        <v>608</v>
+      </c>
+      <c r="P175" s="13" t="s">
+        <v>608</v>
+      </c>
+      <c r="Q175" s="14" t="s">
+        <v>606</v>
+      </c>
+      <c r="R175" s="5" t="s">
         <v>570</v>
       </c>
     </row>
-    <row r="176" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A176" s="4" t="s">
         <v>313</v>
       </c>
@@ -10981,25 +11170,26 @@
       <c r="H176" s="5"/>
       <c r="I176" s="5"/>
       <c r="J176" s="5"/>
-      <c r="K176" s="5" t="s">
+      <c r="K176" s="5"/>
+      <c r="L176" s="5" t="s">
         <v>378</v>
       </c>
-      <c r="L176" s="5"/>
       <c r="M176" s="5"/>
-      <c r="N176" s="14" t="s">
-        <v>609</v>
-      </c>
+      <c r="N176" s="5"/>
       <c r="O176" s="14" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="P176" s="14" t="s">
-        <v>609</v>
-      </c>
-      <c r="Q176" s="5" t="s">
+        <v>608</v>
+      </c>
+      <c r="Q176" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="R176" s="5" t="s">
         <v>573</v>
       </c>
     </row>
-    <row r="177" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A177" s="6" t="s">
         <v>360</v>
       </c>
@@ -11013,7 +11203,7 @@
         <v>331</v>
       </c>
       <c r="E177" s="6" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="F177" s="6" t="s">
         <v>332</v>
@@ -11022,19 +11212,20 @@
       <c r="H177" s="6"/>
       <c r="I177" s="6"/>
       <c r="J177" s="6"/>
-      <c r="K177" s="6" t="s">
+      <c r="K177" s="6"/>
+      <c r="L177" s="6" t="s">
         <v>333</v>
       </c>
-      <c r="L177" s="2"/>
       <c r="M177" s="2"/>
-      <c r="N177" s="16"/>
+      <c r="N177" s="2"/>
       <c r="O177" s="16"/>
       <c r="P177" s="16"/>
-      <c r="Q177" s="8" t="s">
+      <c r="Q177" s="16"/>
+      <c r="R177" s="8" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="178" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A178" s="6" t="s">
         <v>360</v>
       </c>
@@ -11042,13 +11233,13 @@
         <v>361</v>
       </c>
       <c r="C178" s="6" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="D178" s="6" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="E178" s="6" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="F178" s="6"/>
       <c r="G178" s="6" t="s">
@@ -11057,19 +11248,20 @@
       <c r="H178" s="6"/>
       <c r="I178" s="6"/>
       <c r="J178" s="6"/>
-      <c r="K178" s="6" t="s">
+      <c r="K178" s="6"/>
+      <c r="L178" s="6" t="s">
         <v>334</v>
       </c>
-      <c r="L178" s="2"/>
       <c r="M178" s="2"/>
-      <c r="N178" s="16"/>
+      <c r="N178" s="2"/>
       <c r="O178" s="16"/>
       <c r="P178" s="16"/>
-      <c r="Q178" s="8" t="s">
+      <c r="Q178" s="16"/>
+      <c r="R178" s="8" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="179" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A179" s="6" t="s">
         <v>118</v>
       </c>
@@ -11080,10 +11272,10 @@
         <v>335</v>
       </c>
       <c r="D179" s="6" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="E179" s="6" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="F179" s="6" t="s">
         <v>397</v>
@@ -11099,14 +11291,15 @@
       <c r="K179" s="7"/>
       <c r="L179" s="7"/>
       <c r="M179" s="7"/>
-      <c r="N179" s="15"/>
+      <c r="N179" s="7"/>
       <c r="O179" s="15"/>
       <c r="P179" s="15"/>
-      <c r="Q179" s="8" t="s">
+      <c r="Q179" s="15"/>
+      <c r="R179" s="8" t="s">
         <v>339</v>
       </c>
     </row>
-    <row r="180" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A180" s="6" t="s">
         <v>118</v>
       </c>
@@ -11117,10 +11310,10 @@
         <v>335</v>
       </c>
       <c r="D180" s="6" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="E180" s="6" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="F180" s="6" t="s">
         <v>397</v>
@@ -11136,14 +11329,15 @@
       <c r="K180" s="7"/>
       <c r="L180" s="7"/>
       <c r="M180" s="7"/>
-      <c r="N180" s="15"/>
+      <c r="N180" s="7"/>
       <c r="O180" s="15"/>
       <c r="P180" s="15"/>
-      <c r="Q180" s="8" t="s">
+      <c r="Q180" s="15"/>
+      <c r="R180" s="8" t="s">
         <v>339</v>
       </c>
     </row>
-    <row r="181" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A181" s="6" t="s">
         <v>118</v>
       </c>
@@ -11154,10 +11348,10 @@
         <v>342</v>
       </c>
       <c r="D181" s="6" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="E181" s="6" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="F181" s="6" t="s">
         <v>574</v>
@@ -11170,19 +11364,20 @@
       </c>
       <c r="I181" s="7"/>
       <c r="J181" s="7"/>
-      <c r="K181" s="6" t="s">
+      <c r="K181" s="7"/>
+      <c r="L181" s="6" t="s">
         <v>333</v>
       </c>
-      <c r="L181" s="6"/>
       <c r="M181" s="6"/>
-      <c r="N181" s="16"/>
+      <c r="N181" s="6"/>
       <c r="O181" s="16"/>
       <c r="P181" s="16"/>
-      <c r="Q181" s="6" t="s">
+      <c r="Q181" s="16"/>
+      <c r="R181" s="6" t="s">
         <v>341</v>
       </c>
     </row>
-    <row r="182" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A182" s="6" t="s">
         <v>118</v>
       </c>
@@ -11193,10 +11388,10 @@
         <v>342</v>
       </c>
       <c r="D182" s="6" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="E182" s="6" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="F182" s="6" t="s">
         <v>574</v>
@@ -11209,54 +11404,56 @@
       </c>
       <c r="I182" s="7"/>
       <c r="J182" s="7"/>
-      <c r="K182" s="6" t="s">
+      <c r="K182" s="7"/>
+      <c r="L182" s="6" t="s">
         <v>333</v>
       </c>
-      <c r="L182" s="6"/>
       <c r="M182" s="6"/>
-      <c r="N182" s="16"/>
+      <c r="N182" s="6"/>
       <c r="O182" s="16"/>
       <c r="P182" s="16"/>
-      <c r="Q182" s="6" t="s">
+      <c r="Q182" s="16"/>
+      <c r="R182" s="6" t="s">
         <v>341</v>
       </c>
     </row>
-    <row r="183" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A183" s="6" t="s">
         <v>118</v>
       </c>
       <c r="B183" s="6" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="C183" s="6" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="D183" s="6" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="E183" s="6" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="F183" s="7" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="G183" s="6" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="H183" s="6"/>
       <c r="I183" s="6"/>
       <c r="J183" s="6"/>
       <c r="K183" s="6"/>
-      <c r="L183" s="2"/>
+      <c r="L183" s="6"/>
       <c r="M183" s="2"/>
-      <c r="N183" s="16"/>
+      <c r="N183" s="2"/>
       <c r="O183" s="16"/>
       <c r="P183" s="16"/>
-      <c r="Q183" s="6" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="184" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="Q183" s="16"/>
+      <c r="R183" s="6" t="s">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="184" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A184" s="6" t="s">
         <v>118</v>
       </c>
@@ -11264,467 +11461,480 @@
         <v>336</v>
       </c>
       <c r="C184" s="6" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="D184" s="6" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="E184" s="6" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="F184" s="7" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="G184" s="6"/>
       <c r="H184" s="6"/>
       <c r="I184" s="6"/>
       <c r="J184" s="6"/>
       <c r="K184" s="6"/>
-      <c r="L184" s="2"/>
+      <c r="L184" s="6"/>
       <c r="M184" s="2"/>
-      <c r="N184" s="16"/>
+      <c r="N184" s="2"/>
       <c r="O184" s="16"/>
       <c r="P184" s="16"/>
-      <c r="Q184" s="6" t="s">
-        <v>644</v>
-      </c>
-    </row>
-    <row r="185" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="Q184" s="16"/>
+      <c r="R184" s="6" t="s">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="185" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A185" s="6" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="B185" s="6" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="C185" s="6" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="D185" s="6" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="E185" s="6" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="F185" s="6" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="G185" s="6"/>
       <c r="H185" s="6"/>
       <c r="I185" s="6"/>
       <c r="J185" s="6"/>
       <c r="K185" s="6"/>
-      <c r="L185" s="2"/>
+      <c r="L185" s="6"/>
       <c r="M185" s="2"/>
-      <c r="N185" s="16"/>
+      <c r="N185" s="2"/>
       <c r="O185" s="16"/>
       <c r="P185" s="16"/>
-      <c r="Q185" s="6" t="s">
-        <v>647</v>
-      </c>
-    </row>
-    <row r="186" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="Q185" s="16"/>
+      <c r="R185" s="6" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="186" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A186" s="6" t="s">
         <v>118</v>
       </c>
       <c r="B186" s="6" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="C186" s="6" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="D186" s="6" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="E186" s="6" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="F186" s="6" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="G186" s="6"/>
       <c r="H186" s="6"/>
       <c r="I186" s="6"/>
       <c r="J186" s="6"/>
       <c r="K186" s="6"/>
-      <c r="L186" s="2"/>
+      <c r="L186" s="6"/>
       <c r="M186" s="2"/>
-      <c r="N186" s="16"/>
+      <c r="N186" s="2"/>
       <c r="O186" s="16"/>
       <c r="P186" s="16"/>
-      <c r="Q186" s="6" t="s">
-        <v>650</v>
-      </c>
-    </row>
-    <row r="187" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="Q186" s="16"/>
+      <c r="R186" s="6" t="s">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="187" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A187" s="6" t="s">
         <v>116</v>
       </c>
       <c r="B187" s="6" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="C187" s="6" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="D187" s="6" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="E187" s="6" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="F187" s="6" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="G187" s="6"/>
       <c r="H187" s="6"/>
       <c r="I187" s="6"/>
       <c r="J187" s="6"/>
       <c r="K187" s="6"/>
-      <c r="L187" s="2"/>
+      <c r="L187" s="6"/>
       <c r="M187" s="2"/>
-      <c r="N187" s="16"/>
+      <c r="N187" s="2"/>
       <c r="O187" s="16"/>
       <c r="P187" s="16"/>
-      <c r="Q187" s="6" t="s">
-        <v>652</v>
-      </c>
-    </row>
-    <row r="188" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="Q187" s="16"/>
+      <c r="R187" s="6" t="s">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="188" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A188" s="6" t="s">
         <v>118</v>
       </c>
       <c r="B188" s="6" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="C188" s="6" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="D188" s="6" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="E188" s="6" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="F188" s="6" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="G188" s="6"/>
       <c r="H188" s="6"/>
       <c r="I188" s="6"/>
       <c r="J188" s="6"/>
       <c r="K188" s="6"/>
-      <c r="L188" s="2"/>
+      <c r="L188" s="6"/>
       <c r="M188" s="2"/>
-      <c r="N188" s="16"/>
+      <c r="N188" s="2"/>
       <c r="O188" s="16"/>
       <c r="P188" s="16"/>
-      <c r="Q188" s="6" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="189" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="Q188" s="16"/>
+      <c r="R188" s="6" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="189" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A189" s="6" t="s">
         <v>116</v>
       </c>
       <c r="B189" s="6" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="C189" s="6" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="D189" s="6" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="E189" s="6" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="F189" s="6" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="G189" s="6"/>
       <c r="H189" s="6"/>
       <c r="I189" s="6"/>
       <c r="J189" s="6"/>
-      <c r="K189" s="6" t="s">
-        <v>657</v>
-      </c>
-      <c r="L189" s="2"/>
+      <c r="K189" s="6"/>
+      <c r="L189" s="6" t="s">
+        <v>656</v>
+      </c>
       <c r="M189" s="2"/>
-      <c r="N189" s="16"/>
+      <c r="N189" s="2"/>
       <c r="O189" s="16"/>
       <c r="P189" s="16"/>
-      <c r="Q189" s="6" t="s">
-        <v>658</v>
-      </c>
-    </row>
-    <row r="190" spans="1:17" ht="95.25" x14ac:dyDescent="0.3">
+      <c r="Q189" s="16"/>
+      <c r="R189" s="6" t="s">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="190" spans="1:18" ht="95.25" x14ac:dyDescent="0.3">
       <c r="A190" s="6" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="B190" s="6" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="C190" s="6" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="D190" s="6" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="E190" s="6" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="F190" s="6" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="G190" s="6"/>
       <c r="H190" s="6"/>
       <c r="I190" s="6"/>
       <c r="J190" s="6"/>
-      <c r="K190" s="6" t="s">
+      <c r="K190" s="6"/>
+      <c r="L190" s="6" t="s">
+        <v>660</v>
+      </c>
+      <c r="M190" s="2"/>
+      <c r="N190" s="21" t="s">
         <v>661</v>
       </c>
-      <c r="L190" s="2"/>
-      <c r="M190" s="21" t="s">
-        <v>662</v>
-      </c>
-      <c r="N190" s="16"/>
       <c r="O190" s="16"/>
       <c r="P190" s="16"/>
-      <c r="Q190" s="6" t="s">
-        <v>659</v>
-      </c>
-    </row>
-    <row r="191" spans="1:17" ht="162.75" x14ac:dyDescent="0.3">
+      <c r="Q190" s="16"/>
+      <c r="R190" s="6" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="191" spans="1:18" ht="162.75" x14ac:dyDescent="0.3">
       <c r="A191" s="6" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="B191" s="6" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="C191" s="6" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="D191" s="6" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="E191" s="6" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="F191" s="6" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="G191" s="6"/>
       <c r="H191" s="6"/>
       <c r="I191" s="6"/>
       <c r="J191" s="6"/>
-      <c r="K191" s="5" t="s">
-        <v>664</v>
-      </c>
-      <c r="L191" s="2"/>
-      <c r="M191" s="21" t="s">
-        <v>666</v>
-      </c>
-      <c r="N191" s="16"/>
+      <c r="K191" s="6"/>
+      <c r="L191" s="5" t="s">
+        <v>663</v>
+      </c>
+      <c r="M191" s="2"/>
+      <c r="N191" s="21" t="s">
+        <v>665</v>
+      </c>
       <c r="O191" s="16"/>
       <c r="P191" s="16"/>
-      <c r="Q191" s="6" t="s">
-        <v>665</v>
-      </c>
-    </row>
-    <row r="192" spans="1:17" ht="135.75" x14ac:dyDescent="0.3">
+      <c r="Q191" s="16"/>
+      <c r="R191" s="6" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="192" spans="1:18" ht="135.75" x14ac:dyDescent="0.3">
       <c r="A192" s="6" t="s">
         <v>117</v>
       </c>
       <c r="B192" s="6" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="C192" s="6" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="D192" s="6" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="E192" s="6" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="F192" s="6" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="G192" s="6"/>
       <c r="H192" s="6"/>
       <c r="I192" s="6"/>
       <c r="J192" s="6"/>
-      <c r="K192" s="5" t="s">
-        <v>664</v>
-      </c>
-      <c r="L192" s="2"/>
-      <c r="M192" s="21" t="s">
-        <v>668</v>
-      </c>
-      <c r="N192" s="16"/>
+      <c r="K192" s="6"/>
+      <c r="L192" s="5" t="s">
+        <v>663</v>
+      </c>
+      <c r="M192" s="2"/>
+      <c r="N192" s="21" t="s">
+        <v>667</v>
+      </c>
       <c r="O192" s="16"/>
       <c r="P192" s="16"/>
-      <c r="Q192" s="6" t="s">
-        <v>667</v>
-      </c>
-    </row>
-    <row r="193" spans="1:17" ht="149.25" x14ac:dyDescent="0.3">
+      <c r="Q192" s="16"/>
+      <c r="R192" s="6" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="193" spans="1:18" ht="149.25" x14ac:dyDescent="0.3">
       <c r="A193" s="6" t="s">
         <v>117</v>
       </c>
       <c r="B193" s="6" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="C193" s="6" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="D193" s="6" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="E193" s="6" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="F193" s="6" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="G193" s="6"/>
       <c r="H193" s="6"/>
       <c r="I193" s="6"/>
       <c r="J193" s="6"/>
-      <c r="K193" s="6" t="s">
-        <v>661</v>
-      </c>
-      <c r="L193" s="2"/>
-      <c r="M193" s="21" t="s">
-        <v>670</v>
-      </c>
-      <c r="N193" s="16"/>
+      <c r="K193" s="6"/>
+      <c r="L193" s="6" t="s">
+        <v>660</v>
+      </c>
+      <c r="M193" s="2"/>
+      <c r="N193" s="21" t="s">
+        <v>669</v>
+      </c>
       <c r="O193" s="16"/>
       <c r="P193" s="16"/>
-      <c r="Q193" s="6" t="s">
-        <v>669</v>
-      </c>
-    </row>
-    <row r="194" spans="1:17" ht="27" x14ac:dyDescent="0.3">
+      <c r="Q193" s="16"/>
+      <c r="R193" s="6" t="s">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="194" spans="1:18" ht="27" x14ac:dyDescent="0.3">
       <c r="A194" s="6" t="s">
         <v>118</v>
       </c>
       <c r="B194" s="6" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="C194" s="6" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="D194" s="6" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="E194" s="6" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="F194" s="6"/>
       <c r="G194" s="7" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="H194" s="6"/>
       <c r="I194" s="6"/>
       <c r="J194" s="6"/>
-      <c r="K194" s="6" t="s">
-        <v>672</v>
-      </c>
-      <c r="L194" s="2"/>
+      <c r="K194" s="6"/>
+      <c r="L194" s="6" t="s">
+        <v>671</v>
+      </c>
       <c r="M194" s="2"/>
-      <c r="N194" s="16"/>
+      <c r="N194" s="2"/>
       <c r="O194" s="16"/>
       <c r="P194" s="16"/>
-      <c r="Q194" s="6" t="s">
-        <v>673</v>
-      </c>
-    </row>
-    <row r="195" spans="1:17" ht="54.75" x14ac:dyDescent="0.3">
+      <c r="Q194" s="16"/>
+      <c r="R194" s="6" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="195" spans="1:18" ht="54.75" x14ac:dyDescent="0.3">
       <c r="A195" s="6" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="B195" s="6" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="C195" s="6" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="D195" s="6" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="E195" s="6" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="F195" s="6" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="G195" s="6"/>
       <c r="H195" s="6"/>
       <c r="I195" s="6"/>
       <c r="J195" s="6"/>
-      <c r="K195" s="6" t="s">
-        <v>661</v>
-      </c>
-      <c r="L195" s="2"/>
-      <c r="M195" s="21" t="s">
-        <v>677</v>
-      </c>
-      <c r="N195" s="16"/>
+      <c r="K195" s="6"/>
+      <c r="L195" s="6" t="s">
+        <v>660</v>
+      </c>
+      <c r="M195" s="2"/>
+      <c r="N195" s="21" t="s">
+        <v>676</v>
+      </c>
       <c r="O195" s="16"/>
       <c r="P195" s="16"/>
-      <c r="Q195" s="6" t="s">
-        <v>674</v>
-      </c>
-    </row>
-    <row r="196" spans="1:17" ht="27.75" x14ac:dyDescent="0.3">
+      <c r="Q195" s="16"/>
+      <c r="R195" s="6" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="196" spans="1:18" ht="27.75" x14ac:dyDescent="0.3">
       <c r="A196" s="6" t="s">
         <v>117</v>
       </c>
       <c r="B196" s="6" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="C196" s="6" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="D196" s="6" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="E196" s="6" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="F196" s="6" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="G196" s="6"/>
       <c r="H196" s="6"/>
       <c r="I196" s="6"/>
       <c r="J196" s="6"/>
-      <c r="K196" s="6" t="s">
-        <v>680</v>
-      </c>
-      <c r="L196" s="2"/>
-      <c r="M196" s="21" t="s">
+      <c r="K196" s="6"/>
+      <c r="L196" s="6" t="s">
         <v>679</v>
       </c>
-      <c r="N196" s="16"/>
+      <c r="M196" s="2"/>
+      <c r="N196" s="21" t="s">
+        <v>678</v>
+      </c>
       <c r="O196" s="16"/>
       <c r="P196" s="16"/>
-      <c r="Q196" s="6" t="s">
-        <v>640</v>
+      <c r="Q196" s="16"/>
+      <c r="R196" s="6" t="s">
+        <v>639</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="B1:Q182" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="B1:R182" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="Q2:Q176">
+  <conditionalFormatting sqref="R2:R176">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <hyperlinks>
-    <hyperlink ref="Q179" r:id="rId1" xr:uid="{E8A5EE79-38DC-470C-9E4B-60B8DB179166}"/>
-    <hyperlink ref="Q177" r:id="rId2" xr:uid="{B514AFC6-F2CC-453E-A7EE-749BE8F59F63}"/>
-    <hyperlink ref="Q178" r:id="rId3" xr:uid="{D2C8DCF1-2A86-40FB-A718-5DFF8C67103B}"/>
-    <hyperlink ref="Q180" r:id="rId4" xr:uid="{2526EBF2-78DF-4B4D-A609-DDD4E216E820}"/>
-    <hyperlink ref="Q101" r:id="rId5" xr:uid="{05B60FA0-37BF-4BDF-A54A-C6015B78419C}"/>
+    <hyperlink ref="R179" r:id="rId1" xr:uid="{E8A5EE79-38DC-470C-9E4B-60B8DB179166}"/>
+    <hyperlink ref="R177" r:id="rId2" xr:uid="{B514AFC6-F2CC-453E-A7EE-749BE8F59F63}"/>
+    <hyperlink ref="R178" r:id="rId3" xr:uid="{D2C8DCF1-2A86-40FB-A718-5DFF8C67103B}"/>
+    <hyperlink ref="R180" r:id="rId4" xr:uid="{2526EBF2-78DF-4B4D-A609-DDD4E216E820}"/>
+    <hyperlink ref="R101" r:id="rId5" xr:uid="{05B60FA0-37BF-4BDF-A54A-C6015B78419C}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/app/convert/forest_sample_template.xlsx
+++ b/app/convert/forest_sample_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TAX-JUNGYOON\forest-app\app\convert\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DEE253F-BA92-4190-A3D5-807CF4286F5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93AA8A81-9513-4B07-B9E3-B481C80D5BF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="658" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2367" uniqueCount="738">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2372" uniqueCount="741">
   <si>
     <t>시설명</t>
   </si>
@@ -2755,6 +2755,18 @@
   </si>
   <si>
     <t>매월 07일 14시</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>매주 월요일 09시</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>매월 01일 08시</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>매월 01일 09시</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -5964,7 +5976,9 @@
       <c r="H55" s="5"/>
       <c r="I55" s="5"/>
       <c r="J55" s="5"/>
-      <c r="K55" s="5"/>
+      <c r="K55" s="5" t="s">
+        <v>738</v>
+      </c>
       <c r="L55" s="5" t="s">
         <v>370</v>
       </c>
@@ -6652,7 +6666,9 @@
       <c r="H71" s="5"/>
       <c r="I71" s="5"/>
       <c r="J71" s="5"/>
-      <c r="K71" s="5"/>
+      <c r="K71" s="5" t="s">
+        <v>365</v>
+      </c>
       <c r="L71" s="5" t="s">
         <v>368</v>
       </c>
@@ -8260,7 +8276,9 @@
       <c r="H108" s="5"/>
       <c r="I108" s="5"/>
       <c r="J108" s="5"/>
-      <c r="K108" s="5"/>
+      <c r="K108" s="5" t="s">
+        <v>739</v>
+      </c>
       <c r="L108" s="5" t="s">
         <v>368</v>
       </c>
@@ -10354,7 +10372,9 @@
       <c r="H157" s="5"/>
       <c r="I157" s="5"/>
       <c r="J157" s="5"/>
-      <c r="K157" s="5"/>
+      <c r="K157" s="5" t="s">
+        <v>740</v>
+      </c>
       <c r="L157" s="5" t="s">
         <v>372</v>
       </c>
@@ -10654,7 +10674,9 @@
       <c r="H164" s="5"/>
       <c r="I164" s="5"/>
       <c r="J164" s="5"/>
-      <c r="K164" s="5"/>
+      <c r="K164" s="5" t="s">
+        <v>740</v>
+      </c>
       <c r="L164" s="5" t="s">
         <v>370</v>
       </c>

--- a/app/convert/forest_sample_template.xlsx
+++ b/app/convert/forest_sample_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TAX-JUNGYOON\forest-app\app\convert\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93AA8A81-9513-4B07-B9E3-B481C80D5BF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C8A9318-42A5-45EB-B135-8D810C6405FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="658" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2372" uniqueCount="741">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2376" uniqueCount="741">
   <si>
     <t>시설명</t>
   </si>
@@ -7777,7 +7777,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="97" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:18" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A97" s="4" t="s">
         <v>101</v>
       </c>
@@ -7800,11 +7800,15 @@
       <c r="H97" s="5"/>
       <c r="I97" s="5"/>
       <c r="J97" s="5"/>
-      <c r="K97" s="5"/>
+      <c r="K97" s="5" t="s">
+        <v>365</v>
+      </c>
       <c r="L97" s="5" t="s">
         <v>374</v>
       </c>
-      <c r="M97" s="5"/>
+      <c r="M97" s="5" t="s">
+        <v>716</v>
+      </c>
       <c r="N97" s="5"/>
       <c r="O97" s="14" t="s">
         <v>605</v>
@@ -7819,7 +7823,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="98" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:18" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A98" s="4" t="s">
         <v>101</v>
       </c>
@@ -7842,11 +7846,15 @@
       <c r="H98" s="5"/>
       <c r="I98" s="5"/>
       <c r="J98" s="5"/>
-      <c r="K98" s="5"/>
+      <c r="K98" s="5" t="s">
+        <v>365</v>
+      </c>
       <c r="L98" s="5" t="s">
         <v>374</v>
       </c>
-      <c r="M98" s="5"/>
+      <c r="M98" s="5" t="s">
+        <v>716</v>
+      </c>
       <c r="N98" s="5"/>
       <c r="O98" s="14" t="s">
         <v>605</v>

--- a/app/convert/forest_sample_template.xlsx
+++ b/app/convert/forest_sample_template.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TAX-JUNGYOON\forest-app\app\convert\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C8A9318-42A5-45EB-B135-8D810C6405FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63AAEF2B-69BC-4D41-931F-01D11D666BB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="658" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2376" uniqueCount="741">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2379" uniqueCount="744">
   <si>
     <t>시설명</t>
   </si>
@@ -2654,11 +2654,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>정감록명당체험마을
-물고기자리4인 평일 126,000원 / 주말 180,000원</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>신축2인실 21호~25호
 평일 48,000원 / 주말 80,000원
 23,24호가 위쪽이라 프라이빗한데 주차장과 거리가 있어 짐나르기 힘듬</t>
@@ -2767,6 +2762,31 @@
   </si>
   <si>
     <t>매월 01일 09시</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>정감록명당체험마을
+염소자리4인, 궁수자리4인(산전망좋음)
+물고기자리4인(프라이빗함) 
+평일 126,000원 / 주말 180,000원</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>배석대4인(전망좋음)
+평일 180,000원 / 주말 180,000원</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>바다향기2~7 6인실
+평일 75,000원 / 주말 134,000원
+바다향기8~9 10인실 
+평일 124,000원 / 주말 208,000원</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>부엉이,비둘기 신축
+8인실
+평일 98,000원 / 주말 173,000원</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3313,13 +3333,13 @@
         <v>351</v>
       </c>
       <c r="K1" s="6" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="L1" s="16" t="s">
         <v>329</v>
       </c>
       <c r="M1" s="3" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="N1" s="3" t="s">
         <v>576</v>
@@ -3935,7 +3955,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
         <v>3</v>
       </c>
@@ -3971,7 +3991,9 @@
         <v>7</v>
       </c>
       <c r="M14" s="5"/>
-      <c r="N14" s="5"/>
+      <c r="N14" s="5" t="s">
+        <v>743</v>
+      </c>
       <c r="O14" s="13" t="s">
         <v>606</v>
       </c>
@@ -4289,13 +4311,13 @@
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
+        <v>730</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>732</v>
+      </c>
+      <c r="C21" s="5" t="s">
         <v>731</v>
-      </c>
-      <c r="B21" s="5" t="s">
-        <v>733</v>
-      </c>
-      <c r="C21" s="5" t="s">
-        <v>732</v>
       </c>
       <c r="D21" s="5" t="s">
         <v>112</v>
@@ -4328,7 +4350,7 @@
       <c r="P21" s="14"/>
       <c r="Q21" s="13"/>
       <c r="R21" s="5" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
     </row>
     <row r="22" spans="1:18" ht="54" x14ac:dyDescent="0.3">
@@ -4785,7 +4807,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" ht="54" x14ac:dyDescent="0.3">
       <c r="A31" s="4" t="s">
         <v>102</v>
       </c>
@@ -4821,7 +4843,9 @@
         <v>7</v>
       </c>
       <c r="M31" s="5"/>
-      <c r="N31" s="5"/>
+      <c r="N31" s="5" t="s">
+        <v>742</v>
+      </c>
       <c r="O31" s="13" t="s">
         <v>606</v>
       </c>
@@ -5929,7 +5953,7 @@
       <c r="I54" s="5"/>
       <c r="J54" s="5"/>
       <c r="K54" s="5" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="L54" s="5" t="s">
         <v>366</v>
@@ -5977,7 +6001,7 @@
       <c r="I55" s="5"/>
       <c r="J55" s="5"/>
       <c r="K55" s="5" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="L55" s="5" t="s">
         <v>370</v>
@@ -6673,7 +6697,7 @@
         <v>368</v>
       </c>
       <c r="M71" s="5" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="N71" s="10" t="s">
         <v>579</v>
@@ -7055,7 +7079,7 @@
         <v>368</v>
       </c>
       <c r="M80" s="5" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="N80" s="10" t="s">
         <v>585</v>
@@ -7104,7 +7128,7 @@
         <v>698</v>
       </c>
       <c r="N81" s="5" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="O81" s="14" t="s">
         <v>605</v>
@@ -7119,7 +7143,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="82" spans="1:18" ht="27" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:18" ht="54" x14ac:dyDescent="0.3">
       <c r="A82" s="4" t="s">
         <v>101</v>
       </c>
@@ -7148,7 +7172,7 @@
       </c>
       <c r="M82" s="5"/>
       <c r="N82" s="5" t="s">
-        <v>718</v>
+        <v>740</v>
       </c>
       <c r="O82" s="14" t="s">
         <v>608</v>
@@ -7205,7 +7229,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="84" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:18" ht="27" x14ac:dyDescent="0.3">
       <c r="A84" s="4" t="s">
         <v>101</v>
       </c>
@@ -7233,7 +7257,9 @@
         <v>368</v>
       </c>
       <c r="M84" s="5"/>
-      <c r="N84" s="5"/>
+      <c r="N84" s="5" t="s">
+        <v>741</v>
+      </c>
       <c r="O84" s="14" t="s">
         <v>605</v>
       </c>
@@ -7685,19 +7711,19 @@
     </row>
     <row r="95" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A95" s="4" t="s">
+        <v>719</v>
+      </c>
+      <c r="B95" s="5" t="s">
         <v>720</v>
       </c>
-      <c r="B95" s="5" t="s">
+      <c r="C95" s="5" t="s">
         <v>721</v>
       </c>
-      <c r="C95" s="5" t="s">
+      <c r="D95" s="5" t="s">
         <v>722</v>
       </c>
-      <c r="D95" s="5" t="s">
+      <c r="E95" s="5" t="s">
         <v>723</v>
-      </c>
-      <c r="E95" s="5" t="s">
-        <v>724</v>
       </c>
       <c r="F95" s="6" t="s">
         <v>358</v>
@@ -7716,17 +7742,17 @@
       </c>
       <c r="K95" s="6"/>
       <c r="L95" s="6" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="M95" s="2" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" s="14"/>
       <c r="P95" s="14"/>
       <c r="Q95" s="14"/>
       <c r="R95" s="6" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
     </row>
     <row r="96" spans="1:18" ht="175.5" x14ac:dyDescent="0.3">
@@ -8285,7 +8311,7 @@
       <c r="I108" s="5"/>
       <c r="J108" s="5"/>
       <c r="K108" s="5" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="L108" s="5" t="s">
         <v>368</v>
@@ -10381,13 +10407,13 @@
       <c r="I157" s="5"/>
       <c r="J157" s="5"/>
       <c r="K157" s="5" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="L157" s="5" t="s">
         <v>372</v>
       </c>
       <c r="M157" s="5" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="N157" s="5"/>
       <c r="O157" s="14" t="s">
@@ -10683,7 +10709,7 @@
       <c r="I164" s="5"/>
       <c r="J164" s="5"/>
       <c r="K164" s="5" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="L164" s="5" t="s">
         <v>370</v>

--- a/app/convert/forest_sample_template.xlsx
+++ b/app/convert/forest_sample_template.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TAX-JUNGYOON\forest-app\app\convert\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63AAEF2B-69BC-4D41-931F-01D11D666BB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D0541D7-81F2-423E-BB90-217C2E80DBA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="658" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2379" uniqueCount="744">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2384" uniqueCount="745">
   <si>
     <t>시설명</t>
   </si>
@@ -2749,10 +2749,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>매월 07일 14시</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>매주 월요일 09시</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2787,6 +2783,15 @@
     <t>부엉이,비둘기 신축
 8인실
 평일 98,000원 / 주말 173,000원</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>산림휴양관 1실(굴참나무 6인실)
+숲속의집 2실(달 4인실, 하늘 4인실)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>휴양림 시설의 50% (대상시설 격월 적용)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3992,7 +3997,7 @@
       </c>
       <c r="M14" s="5"/>
       <c r="N14" s="5" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="O14" s="13" t="s">
         <v>606</v>
@@ -4844,7 +4849,7 @@
       </c>
       <c r="M31" s="5"/>
       <c r="N31" s="5" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="O31" s="13" t="s">
         <v>606</v>
@@ -5761,7 +5766,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="50" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:18" ht="27" x14ac:dyDescent="0.3">
       <c r="A50" s="4" t="s">
         <v>114</v>
       </c>
@@ -5784,9 +5789,13 @@
       <c r="H50" s="5"/>
       <c r="I50" s="5"/>
       <c r="J50" s="5"/>
-      <c r="K50" s="5"/>
+      <c r="K50" s="5" t="s">
+        <v>365</v>
+      </c>
       <c r="L50" s="5"/>
-      <c r="M50" s="5"/>
+      <c r="M50" s="5" t="s">
+        <v>743</v>
+      </c>
       <c r="N50" s="5"/>
       <c r="O50" s="13" t="s">
         <v>606</v>
@@ -5953,7 +5962,7 @@
       <c r="I54" s="5"/>
       <c r="J54" s="5"/>
       <c r="K54" s="5" t="s">
-        <v>736</v>
+        <v>365</v>
       </c>
       <c r="L54" s="5" t="s">
         <v>366</v>
@@ -6001,7 +6010,7 @@
       <c r="I55" s="5"/>
       <c r="J55" s="5"/>
       <c r="K55" s="5" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="L55" s="5" t="s">
         <v>370</v>
@@ -6052,9 +6061,13 @@
       <c r="J56" s="6" t="s">
         <v>400</v>
       </c>
-      <c r="K56" s="6"/>
+      <c r="K56" s="6" t="s">
+        <v>659</v>
+      </c>
       <c r="L56" s="6"/>
-      <c r="M56" s="2"/>
+      <c r="M56" s="2" t="s">
+        <v>744</v>
+      </c>
       <c r="N56" s="2"/>
       <c r="O56" s="13" t="s">
         <v>606</v>
@@ -6220,7 +6233,9 @@
       <c r="H60" s="5"/>
       <c r="I60" s="5"/>
       <c r="J60" s="5"/>
-      <c r="K60" s="5"/>
+      <c r="K60" s="5" t="s">
+        <v>365</v>
+      </c>
       <c r="L60" s="5" t="s">
         <v>370</v>
       </c>
@@ -7172,7 +7187,7 @@
       </c>
       <c r="M82" s="5"/>
       <c r="N82" s="5" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="O82" s="14" t="s">
         <v>608</v>
@@ -7258,7 +7273,7 @@
       </c>
       <c r="M84" s="5"/>
       <c r="N84" s="5" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="O84" s="14" t="s">
         <v>605</v>
@@ -8311,7 +8326,7 @@
       <c r="I108" s="5"/>
       <c r="J108" s="5"/>
       <c r="K108" s="5" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="L108" s="5" t="s">
         <v>368</v>
@@ -10407,7 +10422,7 @@
       <c r="I157" s="5"/>
       <c r="J157" s="5"/>
       <c r="K157" s="5" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="L157" s="5" t="s">
         <v>372</v>
@@ -10709,7 +10724,7 @@
       <c r="I164" s="5"/>
       <c r="J164" s="5"/>
       <c r="K164" s="5" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="L164" s="5" t="s">
         <v>370</v>

--- a/app/convert/forest_sample_template.xlsx
+++ b/app/convert/forest_sample_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TAX-JUNGYOON\forest-app\app\convert\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D0541D7-81F2-423E-BB90-217C2E80DBA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C487F7B-A183-4FA6-9794-F56582757A4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="658" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,12 +18,23 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">샘플!$B$1:$R$182</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2384" uniqueCount="745">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2432" uniqueCount="773">
   <si>
     <t>시설명</t>
   </si>
@@ -2749,6 +2760,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>매월 07일 14시</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>매주 월요일 09시</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2792,6 +2807,134 @@
   </si>
   <si>
     <t>휴양림 시설의 50% (대상시설 격월 적용)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>휴양림 내 전체 숙박시설 중 100분의 50 범위
+숲속의 집 : 102호, 103호, 104호, 105호, 106호, 107호, 109호, 110호
+데크야영장 : 1호, 4호, 6호, 8호</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>매월 05일 09시</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>산림휴양관 3인실 2실,  4인실 2실</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>숲속의집 2개소(백합1, 목련6)
+산림휴양관 2개소(석류1, 동백2)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>바우처우선예약 객실
+바다동 111호, 112호, 322호 (3객실)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>휴양관(목련): 101호, 102호, 104호
+숲속의집(철쭉): 201호 
+숲속의집(매화): 301호
+야영장(홀수데크): 1.배미산/3.기룡산/5.명당산/7.산머리곡산/9.한석산/11.대암산/13.점봉산/15.설악산</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>매월 25일 10시</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>잣나무 101, 102호
+복합산막 102,103,201,202호
+휴양관 103,104,201호
+산벚나무, 사철나무</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>매월 25일 13시</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>매월 01일 10시</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>민들레, 천인국, 상사화
+함수초, 산부채, 대려화</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>숲속의집 : 빛담1호, 단풍나무1호, 향나무1호, 무궁화1호, 진달래1호, 편백나무1호, 소나무1호
+산림휴양관 : 민들레2호, 패랭이1호
+캠핑장 : 데크4, 데크5, 데크13, 데크17, 데크34, 데크36, 데크37, 데크38</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>매주 수요일 09시</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>잣나무, 전나무, 은행나무, 복자기, 떡갈나무, 진달래 A, 진달래 B, 원앙201, 202, 203, 동백D (11개실)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>매주 화요일 09시</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>바우처우선예약
+소나무1호 , 소나무2호</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>매주 수요일 08:30분</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>우선 예약 객실 : 5개 객실
+숲속의집 1-1
+힐하우스 1-2
+수련관 102, 206, 207</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>매월 1일 기준 3일전 09시</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">숲속의집 : 햇살(2인), 단풍(2인), 별빛(4인), 풀향기(4인), 소망(4인), 행복(6인), 산마루(6인), 믿음(8인)
+산림문화휴양관 : 온마루(2인), 빛마루(2인), 솔마루(8인), 숲마루(12인) </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>매월 01일 08시30분</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>매월 01일 12시30분</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>숲속의집(3, 5, 9, 12, 16, 19호), 
+산림문화휴양관(201, 301호)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>매월 01일 07시</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>야영시설 중 해당시설(30%)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">숲속의집 A동, 
+산림휴양관 A동 201호, 301호 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>매월 04일 09시</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2910,7 +3053,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -2971,6 +3114,12 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3997,7 +4146,7 @@
       </c>
       <c r="M14" s="5"/>
       <c r="N14" s="5" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="O14" s="13" t="s">
         <v>606</v>
@@ -4849,7 +4998,7 @@
       </c>
       <c r="M31" s="5"/>
       <c r="N31" s="5" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="O31" s="13" t="s">
         <v>606</v>
@@ -5794,7 +5943,7 @@
       </c>
       <c r="L50" s="5"/>
       <c r="M50" s="5" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="N50" s="5"/>
       <c r="O50" s="13" t="s">
@@ -5810,7 +5959,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="51" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:18" ht="26.25" x14ac:dyDescent="0.3">
       <c r="A51" s="4" t="s">
         <v>114</v>
       </c>
@@ -5833,11 +5982,15 @@
       <c r="H51" s="20"/>
       <c r="I51" s="20"/>
       <c r="J51" s="20"/>
-      <c r="K51" s="20"/>
+      <c r="K51" s="23" t="s">
+        <v>747</v>
+      </c>
       <c r="L51" s="19" t="s">
         <v>367</v>
       </c>
-      <c r="M51" s="9"/>
+      <c r="M51" s="24" t="s">
+        <v>749</v>
+      </c>
       <c r="N51" s="9"/>
       <c r="O51" s="13" t="s">
         <v>606</v>
@@ -5921,9 +6074,13 @@
       <c r="J53" s="5" t="s">
         <v>359</v>
       </c>
-      <c r="K53" s="5"/>
+      <c r="K53" s="5" t="s">
+        <v>365</v>
+      </c>
       <c r="L53" s="5"/>
-      <c r="M53" s="5"/>
+      <c r="M53" s="5" t="s">
+        <v>748</v>
+      </c>
       <c r="N53" s="5"/>
       <c r="O53" s="13" t="s">
         <v>606</v>
@@ -5962,7 +6119,7 @@
       <c r="I54" s="5"/>
       <c r="J54" s="5"/>
       <c r="K54" s="5" t="s">
-        <v>365</v>
+        <v>736</v>
       </c>
       <c r="L54" s="5" t="s">
         <v>366</v>
@@ -6010,7 +6167,7 @@
       <c r="I55" s="5"/>
       <c r="J55" s="5"/>
       <c r="K55" s="5" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="L55" s="5" t="s">
         <v>370</v>
@@ -6066,7 +6223,7 @@
       </c>
       <c r="L56" s="6"/>
       <c r="M56" s="2" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="13" t="s">
@@ -6105,7 +6262,9 @@
       <c r="H57" s="5"/>
       <c r="I57" s="5"/>
       <c r="J57" s="5"/>
-      <c r="K57" s="5"/>
+      <c r="K57" s="5" t="s">
+        <v>365</v>
+      </c>
       <c r="L57" s="5" t="s">
         <v>370</v>
       </c>
@@ -6325,7 +6484,9 @@
       <c r="J62" s="5" t="s">
         <v>401</v>
       </c>
-      <c r="K62" s="5"/>
+      <c r="K62" s="5" t="s">
+        <v>747</v>
+      </c>
       <c r="L62" s="5"/>
       <c r="M62" s="5"/>
       <c r="N62" s="5"/>
@@ -6369,7 +6530,9 @@
       <c r="J63" s="5" t="s">
         <v>403</v>
       </c>
-      <c r="K63" s="5"/>
+      <c r="K63" s="5" t="s">
+        <v>365</v>
+      </c>
       <c r="L63" s="5"/>
       <c r="M63" s="5"/>
       <c r="N63" s="5"/>
@@ -6428,7 +6591,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="65" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:18" ht="67.5" x14ac:dyDescent="0.3">
       <c r="A65" s="4" t="s">
         <v>114</v>
       </c>
@@ -6451,11 +6614,15 @@
       <c r="H65" s="5"/>
       <c r="I65" s="5"/>
       <c r="J65" s="5"/>
-      <c r="K65" s="5"/>
+      <c r="K65" s="5" t="s">
+        <v>365</v>
+      </c>
       <c r="L65" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="M65" s="5"/>
+      <c r="M65" s="5" t="s">
+        <v>746</v>
+      </c>
       <c r="N65" s="5"/>
       <c r="O65" s="14" t="s">
         <v>609</v>
@@ -6470,7 +6637,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="66" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:18" ht="27" x14ac:dyDescent="0.3">
       <c r="A66" s="4" t="s">
         <v>3</v>
       </c>
@@ -6497,7 +6664,9 @@
       <c r="L66" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="M66" s="5"/>
+      <c r="M66" s="5" t="s">
+        <v>750</v>
+      </c>
       <c r="N66" s="5"/>
       <c r="O66" s="14" t="s">
         <v>608</v>
@@ -6663,7 +6832,9 @@
       <c r="H70" s="5"/>
       <c r="I70" s="5"/>
       <c r="J70" s="5"/>
-      <c r="K70" s="5"/>
+      <c r="K70" s="5" t="s">
+        <v>365</v>
+      </c>
       <c r="L70" s="5" t="s">
         <v>368</v>
       </c>
@@ -6730,7 +6901,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="72" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:18" ht="81" x14ac:dyDescent="0.3">
       <c r="A72" s="4" t="s">
         <v>3</v>
       </c>
@@ -6753,11 +6924,15 @@
       <c r="H72" s="5"/>
       <c r="I72" s="5"/>
       <c r="J72" s="5"/>
-      <c r="K72" s="5"/>
+      <c r="K72" s="5" t="s">
+        <v>365</v>
+      </c>
       <c r="L72" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="M72" s="5"/>
+      <c r="M72" s="5" t="s">
+        <v>751</v>
+      </c>
       <c r="N72" s="5"/>
       <c r="O72" s="14" t="s">
         <v>605</v>
@@ -7187,7 +7362,7 @@
       </c>
       <c r="M82" s="5"/>
       <c r="N82" s="5" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="O82" s="14" t="s">
         <v>608</v>
@@ -7273,7 +7448,7 @@
       </c>
       <c r="M84" s="5"/>
       <c r="N84" s="5" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="O84" s="14" t="s">
         <v>605</v>
@@ -7397,7 +7572,9 @@
       <c r="H87" s="5"/>
       <c r="I87" s="5"/>
       <c r="J87" s="5"/>
-      <c r="K87" s="5"/>
+      <c r="K87" s="5" t="s">
+        <v>365</v>
+      </c>
       <c r="L87" s="5" t="s">
         <v>372</v>
       </c>
@@ -7418,7 +7595,7 @@
         <v>691</v>
       </c>
     </row>
-    <row r="88" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:18" ht="54" x14ac:dyDescent="0.3">
       <c r="A88" s="4" t="s">
         <v>101</v>
       </c>
@@ -7441,11 +7618,15 @@
       <c r="H88" s="5"/>
       <c r="I88" s="5"/>
       <c r="J88" s="5"/>
-      <c r="K88" s="5"/>
+      <c r="K88" s="5" t="s">
+        <v>752</v>
+      </c>
       <c r="L88" s="5" t="s">
         <v>374</v>
       </c>
-      <c r="M88" s="5"/>
+      <c r="M88" s="5" t="s">
+        <v>753</v>
+      </c>
       <c r="N88" s="5"/>
       <c r="O88" s="14" t="s">
         <v>605</v>
@@ -7460,7 +7641,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="89" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:18" ht="27" x14ac:dyDescent="0.3">
       <c r="A89" s="4" t="s">
         <v>101</v>
       </c>
@@ -7483,11 +7664,15 @@
       <c r="H89" s="5"/>
       <c r="I89" s="5"/>
       <c r="J89" s="5"/>
-      <c r="K89" s="5"/>
+      <c r="K89" s="5" t="s">
+        <v>752</v>
+      </c>
       <c r="L89" s="5" t="s">
         <v>374</v>
       </c>
-      <c r="M89" s="5"/>
+      <c r="M89" s="5" t="s">
+        <v>756</v>
+      </c>
       <c r="N89" s="5"/>
       <c r="O89" s="14" t="s">
         <v>605</v>
@@ -7609,7 +7794,9 @@
       <c r="H92" s="5"/>
       <c r="I92" s="5"/>
       <c r="J92" s="5"/>
-      <c r="K92" s="5"/>
+      <c r="K92" s="5" t="s">
+        <v>758</v>
+      </c>
       <c r="L92" s="5" t="s">
         <v>372</v>
       </c>
@@ -7653,7 +7840,9 @@
       <c r="H93" s="5"/>
       <c r="I93" s="5"/>
       <c r="J93" s="5"/>
-      <c r="K93" s="5"/>
+      <c r="K93" s="5" t="s">
+        <v>754</v>
+      </c>
       <c r="L93" s="5" t="s">
         <v>375</v>
       </c>
@@ -7674,7 +7863,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="94" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:18" ht="108" x14ac:dyDescent="0.3">
       <c r="A94" s="4" t="s">
         <v>101</v>
       </c>
@@ -7705,11 +7894,15 @@
       <c r="J94" s="6" t="s">
         <v>358</v>
       </c>
-      <c r="K94" s="6"/>
+      <c r="K94" s="6" t="s">
+        <v>755</v>
+      </c>
       <c r="L94" s="6" t="s">
         <v>367</v>
       </c>
-      <c r="M94" s="2"/>
+      <c r="M94" s="5" t="s">
+        <v>757</v>
+      </c>
       <c r="N94" s="2"/>
       <c r="O94" s="14" t="s">
         <v>605</v>
@@ -7996,7 +8189,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="101" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:18" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A101" s="4" t="s">
         <v>115</v>
       </c>
@@ -8019,11 +8212,15 @@
       <c r="H101" s="5"/>
       <c r="I101" s="5"/>
       <c r="J101" s="5"/>
-      <c r="K101" s="5"/>
+      <c r="K101" s="5" t="s">
+        <v>758</v>
+      </c>
       <c r="L101" s="5" t="s">
         <v>379</v>
       </c>
-      <c r="M101" s="5"/>
+      <c r="M101" s="5" t="s">
+        <v>759</v>
+      </c>
       <c r="N101" s="5"/>
       <c r="O101" s="14" t="s">
         <v>605</v>
@@ -8195,7 +8392,9 @@
       <c r="H105" s="5"/>
       <c r="I105" s="5"/>
       <c r="J105" s="5"/>
-      <c r="K105" s="5"/>
+      <c r="K105" s="5" t="s">
+        <v>659</v>
+      </c>
       <c r="L105" s="5" t="s">
         <v>372</v>
       </c>
@@ -8326,7 +8525,7 @@
       <c r="I108" s="5"/>
       <c r="J108" s="5"/>
       <c r="K108" s="5" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="L108" s="5" t="s">
         <v>368</v>
@@ -8381,7 +8580,9 @@
       <c r="J109" s="5" t="s">
         <v>407</v>
       </c>
-      <c r="K109" s="5"/>
+      <c r="K109" s="5" t="s">
+        <v>760</v>
+      </c>
       <c r="L109" s="5" t="s">
         <v>372</v>
       </c>
@@ -8511,7 +8712,9 @@
       <c r="H112" s="5"/>
       <c r="I112" s="5"/>
       <c r="J112" s="5"/>
-      <c r="K112" s="5"/>
+      <c r="K112" s="5" t="s">
+        <v>365</v>
+      </c>
       <c r="L112" s="5" t="s">
         <v>368</v>
       </c>
@@ -8553,7 +8756,9 @@
       <c r="H113" s="5"/>
       <c r="I113" s="5"/>
       <c r="J113" s="5"/>
-      <c r="K113" s="5"/>
+      <c r="K113" s="5" t="s">
+        <v>365</v>
+      </c>
       <c r="L113" s="5" t="s">
         <v>372</v>
       </c>
@@ -8637,7 +8842,9 @@
       <c r="H115" s="5"/>
       <c r="I115" s="5"/>
       <c r="J115" s="5"/>
-      <c r="K115" s="5"/>
+      <c r="K115" s="5" t="s">
+        <v>737</v>
+      </c>
       <c r="L115" s="5" t="s">
         <v>381</v>
       </c>
@@ -8681,7 +8888,9 @@
       <c r="H116" s="5"/>
       <c r="I116" s="5"/>
       <c r="J116" s="5"/>
-      <c r="K116" s="5"/>
+      <c r="K116" s="5" t="s">
+        <v>760</v>
+      </c>
       <c r="L116" s="5" t="s">
         <v>370</v>
       </c>
@@ -8811,7 +9020,9 @@
       <c r="H119" s="5"/>
       <c r="I119" s="5"/>
       <c r="J119" s="5"/>
-      <c r="K119" s="5"/>
+      <c r="K119" s="5" t="s">
+        <v>365</v>
+      </c>
       <c r="L119" s="5" t="s">
         <v>372</v>
       </c>
@@ -9407,11 +9618,15 @@
       <c r="H133" s="5"/>
       <c r="I133" s="5"/>
       <c r="J133" s="5"/>
-      <c r="K133" s="5"/>
+      <c r="K133" s="5" t="s">
+        <v>769</v>
+      </c>
       <c r="L133" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="M133" s="5"/>
+      <c r="M133" s="5" t="s">
+        <v>770</v>
+      </c>
       <c r="N133" s="5"/>
       <c r="O133" s="14" t="s">
         <v>606</v>
@@ -9468,7 +9683,7 @@
         <v>538</v>
       </c>
     </row>
-    <row r="135" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:18" ht="81" x14ac:dyDescent="0.3">
       <c r="A135" s="4" t="s">
         <v>117</v>
       </c>
@@ -9491,11 +9706,15 @@
       <c r="H135" s="5"/>
       <c r="I135" s="5"/>
       <c r="J135" s="5"/>
-      <c r="K135" s="5"/>
+      <c r="K135" s="5" t="s">
+        <v>766</v>
+      </c>
       <c r="L135" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="M135" s="5"/>
+      <c r="M135" s="5" t="s">
+        <v>765</v>
+      </c>
       <c r="N135" s="5"/>
       <c r="O135" s="14" t="s">
         <v>606</v>
@@ -9552,7 +9771,7 @@
         <v>533</v>
       </c>
     </row>
-    <row r="137" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:18" ht="94.5" x14ac:dyDescent="0.3">
       <c r="A137" s="4" t="s">
         <v>117</v>
       </c>
@@ -9575,11 +9794,15 @@
       <c r="H137" s="5"/>
       <c r="I137" s="5"/>
       <c r="J137" s="5"/>
-      <c r="K137" s="5"/>
+      <c r="K137" s="5" t="s">
+        <v>764</v>
+      </c>
       <c r="L137" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="M137" s="5"/>
+      <c r="M137" s="5" t="s">
+        <v>763</v>
+      </c>
       <c r="N137" s="5"/>
       <c r="O137" s="14" t="s">
         <v>606</v>
@@ -9932,7 +10155,7 @@
         <v>536</v>
       </c>
     </row>
-    <row r="146" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:18" ht="27" x14ac:dyDescent="0.3">
       <c r="A146" s="4" t="s">
         <v>117</v>
       </c>
@@ -9955,11 +10178,15 @@
       <c r="H146" s="5"/>
       <c r="I146" s="5"/>
       <c r="J146" s="5"/>
-      <c r="K146" s="5"/>
+      <c r="K146" s="5" t="s">
+        <v>767</v>
+      </c>
       <c r="L146" s="5" t="s">
         <v>375</v>
       </c>
-      <c r="M146" s="5"/>
+      <c r="M146" s="5" t="s">
+        <v>768</v>
+      </c>
       <c r="N146" s="5"/>
       <c r="O146" s="14" t="s">
         <v>606</v>
@@ -10001,7 +10228,9 @@
       <c r="L147" s="5" t="s">
         <v>706</v>
       </c>
-      <c r="M147" s="5"/>
+      <c r="M147" s="5" t="s">
+        <v>761</v>
+      </c>
       <c r="N147" s="5"/>
       <c r="O147" s="14" t="s">
         <v>605</v>
@@ -10081,7 +10310,9 @@
       <c r="H149" s="5"/>
       <c r="I149" s="5"/>
       <c r="J149" s="5"/>
-      <c r="K149" s="5"/>
+      <c r="K149" s="5" t="s">
+        <v>760</v>
+      </c>
       <c r="L149" s="5" t="s">
         <v>372</v>
       </c>
@@ -10167,7 +10398,9 @@
       <c r="H151" s="5"/>
       <c r="I151" s="5"/>
       <c r="J151" s="5"/>
-      <c r="K151" s="5"/>
+      <c r="K151" s="5" t="s">
+        <v>762</v>
+      </c>
       <c r="L151" s="5" t="s">
         <v>372</v>
       </c>
@@ -10422,7 +10655,7 @@
       <c r="I157" s="5"/>
       <c r="J157" s="5"/>
       <c r="K157" s="5" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="L157" s="5" t="s">
         <v>372</v>
@@ -10486,7 +10719,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="159" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:18" ht="27" x14ac:dyDescent="0.3">
       <c r="A159" s="4" t="s">
         <v>118</v>
       </c>
@@ -10509,11 +10742,15 @@
       <c r="H159" s="5"/>
       <c r="I159" s="5"/>
       <c r="J159" s="5"/>
-      <c r="K159" s="5"/>
+      <c r="K159" s="5" t="s">
+        <v>365</v>
+      </c>
       <c r="L159" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="M159" s="5"/>
+      <c r="M159" s="5" t="s">
+        <v>771</v>
+      </c>
       <c r="N159" s="5"/>
       <c r="O159" s="13" t="s">
         <v>608</v>
@@ -10593,7 +10830,9 @@
       <c r="H161" s="5"/>
       <c r="I161" s="5"/>
       <c r="J161" s="5"/>
-      <c r="K161" s="5"/>
+      <c r="K161" s="5" t="s">
+        <v>772</v>
+      </c>
       <c r="L161" s="5" t="s">
         <v>372</v>
       </c>
@@ -10724,7 +10963,7 @@
       <c r="I164" s="5"/>
       <c r="J164" s="5"/>
       <c r="K164" s="5" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="L164" s="5" t="s">
         <v>370</v>
@@ -10897,7 +11136,9 @@
       <c r="H168" s="5"/>
       <c r="I168" s="5"/>
       <c r="J168" s="5"/>
-      <c r="K168" s="5"/>
+      <c r="K168" s="5" t="s">
+        <v>365</v>
+      </c>
       <c r="L168" s="5" t="s">
         <v>376</v>
       </c>
@@ -10985,7 +11226,9 @@
       <c r="H170" s="5"/>
       <c r="I170" s="5"/>
       <c r="J170" s="5"/>
-      <c r="K170" s="5"/>
+      <c r="K170" s="5" t="s">
+        <v>365</v>
+      </c>
       <c r="L170" s="5" t="s">
         <v>376</v>
       </c>
@@ -11029,7 +11272,9 @@
       <c r="H171" s="5"/>
       <c r="I171" s="5"/>
       <c r="J171" s="5"/>
-      <c r="K171" s="5"/>
+      <c r="K171" s="5" t="s">
+        <v>365</v>
+      </c>
       <c r="L171" s="5" t="s">
         <v>376</v>
       </c>
